--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -38,6 +38,120 @@
   </x:si>
   <x:si>
     <x:t>Maliyet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -388,7 +502,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I1"/>
+  <x:dimension ref="A1:I39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -418,6 +532,1108 @@
       </x:c>
       <x:c r="I1" s="0" t="s">
         <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9">
+      <x:c r="A2" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B2" s="0">
+        <x:v>40202</x:v>
+      </x:c>
+      <x:c r="C2" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="D2" s="0">
+        <x:v>1755</x:v>
+      </x:c>
+      <x:c r="E2" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F2" s="0">
+        <x:v>41957</x:v>
+      </x:c>
+      <x:c r="G2" s="0">
+        <x:v>23.191169480096</x:v>
+      </x:c>
+      <x:c r="H2" s="0">
+        <x:v>38447</x:v>
+      </x:c>
+      <x:c r="I2" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9">
+      <x:c r="A3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>30055</x:v>
+      </x:c>
+      <x:c r="C3" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="D3" s="0">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E3" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F3" s="0">
+        <x:v>30138</x:v>
+      </x:c>
+      <x:c r="G3" s="0">
+        <x:v>16.6583756176832</x:v>
+      </x:c>
+      <x:c r="H3" s="0">
+        <x:v>29972</x:v>
+      </x:c>
+      <x:c r="I3" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:9">
+      <x:c r="A4" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C4" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F4" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G4" s="0">
+        <x:v>0.00055273659890116</x:v>
+      </x:c>
+      <x:c r="H4" s="0">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="I4" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:9">
+      <x:c r="A5" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C5" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="0">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E5" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F5" s="0">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G5" s="0">
+        <x:v>0.00608010258791276</x:v>
+      </x:c>
+      <x:c r="H5" s="0">
+        <x:v>-11</x:v>
+      </x:c>
+      <x:c r="I5" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9">
+      <x:c r="A6" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C6" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E6" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F6" s="0">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G6" s="0">
+        <x:v>0.013818414972529</x:v>
+      </x:c>
+      <x:c r="H6" s="0">
+        <x:v>-25</x:v>
+      </x:c>
+      <x:c r="I6" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:9">
+      <x:c r="A7" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B7" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C7" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="0">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E7" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F7" s="0">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G7" s="0">
+        <x:v>0.0149238881703313</x:v>
+      </x:c>
+      <x:c r="H7" s="0">
+        <x:v>-27</x:v>
+      </x:c>
+      <x:c r="I7" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9">
+      <x:c r="A8" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="0">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E8" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F8" s="0">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G8" s="0">
+        <x:v>0.0149238881703313</x:v>
+      </x:c>
+      <x:c r="H8" s="0">
+        <x:v>-27</x:v>
+      </x:c>
+      <x:c r="I8" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:9">
+      <x:c r="A9" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C9" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="0">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E9" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F9" s="0">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G9" s="0">
+        <x:v>0.0149238881703313</x:v>
+      </x:c>
+      <x:c r="H9" s="0">
+        <x:v>-27</x:v>
+      </x:c>
+      <x:c r="I9" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:9">
+      <x:c r="A10" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="0">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E10" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F10" s="0">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G10" s="0">
+        <x:v>0.0149238881703313</x:v>
+      </x:c>
+      <x:c r="H10" s="0">
+        <x:v>-27</x:v>
+      </x:c>
+      <x:c r="I10" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:9">
+      <x:c r="A11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C11" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="0">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E11" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F11" s="0">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G11" s="0">
+        <x:v>0.0154766247692325</x:v>
+      </x:c>
+      <x:c r="H11" s="0">
+        <x:v>-28</x:v>
+      </x:c>
+      <x:c r="I11" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:9">
+      <x:c r="A12" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="0">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E12" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F12" s="0">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G12" s="0">
+        <x:v>0.0154766247692325</x:v>
+      </x:c>
+      <x:c r="H12" s="0">
+        <x:v>-28</x:v>
+      </x:c>
+      <x:c r="I12" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:9">
+      <x:c r="A13" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B13" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="0">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F13" s="0">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G13" s="0">
+        <x:v>0.0154766247692325</x:v>
+      </x:c>
+      <x:c r="H13" s="0">
+        <x:v>-28</x:v>
+      </x:c>
+      <x:c r="I13" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:9">
+      <x:c r="A14" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C14" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="0">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E14" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F14" s="0">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G14" s="0">
+        <x:v>0.0304005129395638</x:v>
+      </x:c>
+      <x:c r="H14" s="0">
+        <x:v>-55</x:v>
+      </x:c>
+      <x:c r="I14" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:9">
+      <x:c r="A15" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C15" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="0">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E15" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F15" s="0">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G15" s="0">
+        <x:v>0.0326114593351684</x:v>
+      </x:c>
+      <x:c r="H15" s="0">
+        <x:v>-59</x:v>
+      </x:c>
+      <x:c r="I15" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:9">
+      <x:c r="A16" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B16" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C16" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="0">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E16" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F16" s="0">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G16" s="0">
+        <x:v>0.0447716645109939</x:v>
+      </x:c>
+      <x:c r="H16" s="0">
+        <x:v>-81</x:v>
+      </x:c>
+      <x:c r="I16" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:9">
+      <x:c r="A17" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B17" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C17" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="0">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E17" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F17" s="0">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G17" s="0">
+        <x:v>0.0608010258791276</x:v>
+      </x:c>
+      <x:c r="H17" s="0">
+        <x:v>-110</x:v>
+      </x:c>
+      <x:c r="I17" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:9">
+      <x:c r="A18" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C18" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="0">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E18" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F18" s="0">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G18" s="0">
+        <x:v>0.0757249140494589</x:v>
+      </x:c>
+      <x:c r="H18" s="0">
+        <x:v>-137</x:v>
+      </x:c>
+      <x:c r="I18" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:9">
+      <x:c r="A19" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B19" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C19" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="E19" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F19" s="0">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="G19" s="0">
+        <x:v>0.124365734752761</x:v>
+      </x:c>
+      <x:c r="H19" s="0">
+        <x:v>-225</x:v>
+      </x:c>
+      <x:c r="I19" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:9">
+      <x:c r="A20" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C20" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="0">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="E20" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F20" s="0">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="G20" s="0">
+        <x:v>0.128234890945069</x:v>
+      </x:c>
+      <x:c r="H20" s="0">
+        <x:v>-232</x:v>
+      </x:c>
+      <x:c r="I20" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:9">
+      <x:c r="A21" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B21" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C21" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="0">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="E21" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F21" s="0">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="G21" s="0">
+        <x:v>0.129340364142871</x:v>
+      </x:c>
+      <x:c r="H21" s="0">
+        <x:v>-234</x:v>
+      </x:c>
+      <x:c r="I21" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:9">
+      <x:c r="A22" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B22" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C22" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="0">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="E22" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F22" s="0">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="G22" s="0">
+        <x:v>0.136525939928586</x:v>
+      </x:c>
+      <x:c r="H22" s="0">
+        <x:v>-247</x:v>
+      </x:c>
+      <x:c r="I22" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:9">
+      <x:c r="A23" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C23" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="0">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="E23" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F23" s="0">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="G23" s="0">
+        <x:v>0.159740877082435</x:v>
+      </x:c>
+      <x:c r="H23" s="0">
+        <x:v>-289</x:v>
+      </x:c>
+      <x:c r="I23" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:9">
+      <x:c r="A24" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C24" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="0">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="E24" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F24" s="0">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="G24" s="0">
+        <x:v>0.174112028653865</x:v>
+      </x:c>
+      <x:c r="H24" s="0">
+        <x:v>-315</x:v>
+      </x:c>
+      <x:c r="I24" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:9">
+      <x:c r="A25" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C25" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D25" s="0">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="E25" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F25" s="0">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="G25" s="0">
+        <x:v>0.191799599818702</x:v>
+      </x:c>
+      <x:c r="H25" s="0">
+        <x:v>-347</x:v>
+      </x:c>
+      <x:c r="I25" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:9">
+      <x:c r="A26" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C26" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="0">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="E26" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F26" s="0">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="G26" s="0">
+        <x:v>0.291844924219812</x:v>
+      </x:c>
+      <x:c r="H26" s="0">
+        <x:v>-528</x:v>
+      </x:c>
+      <x:c r="I26" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:9">
+      <x:c r="A27" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C27" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="0">
+        <x:v>1015</x:v>
+      </x:c>
+      <x:c r="E27" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F27" s="0">
+        <x:v>1015</x:v>
+      </x:c>
+      <x:c r="G27" s="0">
+        <x:v>0.561027647884677</x:v>
+      </x:c>
+      <x:c r="H27" s="0">
+        <x:v>-1015</x:v>
+      </x:c>
+      <x:c r="I27" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:9">
+      <x:c r="A28" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B28" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" s="0">
+        <x:v>1037</x:v>
+      </x:c>
+      <x:c r="E28" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F28" s="0">
+        <x:v>1037</x:v>
+      </x:c>
+      <x:c r="G28" s="0">
+        <x:v>0.573187853060503</x:v>
+      </x:c>
+      <x:c r="H28" s="0">
+        <x:v>-1037</x:v>
+      </x:c>
+      <x:c r="I28" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:9">
+      <x:c r="A29" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D29" s="0">
+        <x:v>1173</x:v>
+      </x:c>
+      <x:c r="E29" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F29" s="0">
+        <x:v>1173</x:v>
+      </x:c>
+      <x:c r="G29" s="0">
+        <x:v>0.64836003051106</x:v>
+      </x:c>
+      <x:c r="H29" s="0">
+        <x:v>-1173</x:v>
+      </x:c>
+      <x:c r="I29" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:9">
+      <x:c r="A30" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C30" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D30" s="0">
+        <x:v>2232</x:v>
+      </x:c>
+      <x:c r="E30" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F30" s="0">
+        <x:v>2232</x:v>
+      </x:c>
+      <x:c r="G30" s="0">
+        <x:v>1.23370808874739</x:v>
+      </x:c>
+      <x:c r="H30" s="0">
+        <x:v>-2232</x:v>
+      </x:c>
+      <x:c r="I30" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:9">
+      <x:c r="A31" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D31" s="0">
+        <x:v>2775</x:v>
+      </x:c>
+      <x:c r="E31" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F31" s="0">
+        <x:v>2775</x:v>
+      </x:c>
+      <x:c r="G31" s="0">
+        <x:v>1.53384406195072</x:v>
+      </x:c>
+      <x:c r="H31" s="0">
+        <x:v>-2775</x:v>
+      </x:c>
+      <x:c r="I31" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:9">
+      <x:c r="A32" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C32" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="0">
+        <x:v>3206</x:v>
+      </x:c>
+      <x:c r="E32" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F32" s="0">
+        <x:v>3206</x:v>
+      </x:c>
+      <x:c r="G32" s="0">
+        <x:v>1.77207353607712</x:v>
+      </x:c>
+      <x:c r="H32" s="0">
+        <x:v>-3206</x:v>
+      </x:c>
+      <x:c r="I32" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:9">
+      <x:c r="A33" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C33" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D33" s="0">
+        <x:v>3268</x:v>
+      </x:c>
+      <x:c r="E33" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F33" s="0">
+        <x:v>3268</x:v>
+      </x:c>
+      <x:c r="G33" s="0">
+        <x:v>1.80634320520899</x:v>
+      </x:c>
+      <x:c r="H33" s="0">
+        <x:v>-3268</x:v>
+      </x:c>
+      <x:c r="I33" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:9">
+      <x:c r="A34" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B34" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C34" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="0">
+        <x:v>4755</x:v>
+      </x:c>
+      <x:c r="E34" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F34" s="0">
+        <x:v>4755</x:v>
+      </x:c>
+      <x:c r="G34" s="0">
+        <x:v>2.62826252777501</x:v>
+      </x:c>
+      <x:c r="H34" s="0">
+        <x:v>-4755</x:v>
+      </x:c>
+      <x:c r="I34" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:9">
+      <x:c r="A35" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C35" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="0">
+        <x:v>5005</x:v>
+      </x:c>
+      <x:c r="E35" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F35" s="0">
+        <x:v>5005</x:v>
+      </x:c>
+      <x:c r="G35" s="0">
+        <x:v>2.7664466775003</x:v>
+      </x:c>
+      <x:c r="H35" s="0">
+        <x:v>-5005</x:v>
+      </x:c>
+      <x:c r="I35" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:9">
+      <x:c r="A36" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B36" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C36" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D36" s="0">
+        <x:v>7250</x:v>
+      </x:c>
+      <x:c r="E36" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F36" s="0">
+        <x:v>7250</x:v>
+      </x:c>
+      <x:c r="G36" s="0">
+        <x:v>4.00734034203341</x:v>
+      </x:c>
+      <x:c r="H36" s="0">
+        <x:v>-7250</x:v>
+      </x:c>
+      <x:c r="I36" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:9">
+      <x:c r="A37" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C37" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D37" s="0">
+        <x:v>7360</x:v>
+      </x:c>
+      <x:c r="E37" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F37" s="0">
+        <x:v>7360</x:v>
+      </x:c>
+      <x:c r="G37" s="0">
+        <x:v>4.06814136791254</x:v>
+      </x:c>
+      <x:c r="H37" s="0">
+        <x:v>-7360</x:v>
+      </x:c>
+      <x:c r="I37" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:9">
+      <x:c r="A38" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B38" s="0">
+        <x:v>20202</x:v>
+      </x:c>
+      <x:c r="C38" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="D38" s="0">
+        <x:v>28520</x:v>
+      </x:c>
+      <x:c r="E38" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F38" s="0">
+        <x:v>48722</x:v>
+      </x:c>
+      <x:c r="G38" s="0">
+        <x:v>26.9304325716623</x:v>
+      </x:c>
+      <x:c r="H38" s="0">
+        <x:v>-8318</x:v>
+      </x:c>
+      <x:c r="I38" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:9">
+      <x:c r="A39" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C39" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="0">
+        <x:v>17937</x:v>
+      </x:c>
+      <x:c r="E39" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F39" s="0">
+        <x:v>17937</x:v>
+      </x:c>
+      <x:c r="G39" s="0">
+        <x:v>9.9144363744901</x:v>
+      </x:c>
+      <x:c r="H39" s="0">
+        <x:v>-17937</x:v>
+      </x:c>
+      <x:c r="I39" s="0">
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -46,82 +46,94 @@
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALTERNATIF</x:t>
   </x:si>
   <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
     <x:t>DESTEK</x:t>
   </x:si>
   <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
     <x:t>ACAR</x:t>
   </x:si>
   <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
+    <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
     <x:t>TEB</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
+    <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
     <x:t>HALK</x:t>
@@ -133,22 +145,16 @@
     <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
-    <x:t>A1 CAPITAL</x:t>
+    <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
     <x:t>IS</x:t>
   </x:si>
   <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
     <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
     <x:t>OYAK</x:t>
@@ -502,7 +508,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I39"/>
+  <x:dimension ref="A1:I41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -545,19 +551,19 @@
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>1755</x:v>
+        <x:v>3046</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>41957</x:v>
+        <x:v>43248</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>23.191169480096</x:v>
+        <x:v>17.4274661508704</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>38447</x:v>
+        <x:v>37156</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>49.5</x:v>
@@ -583,7 +589,7 @@
         <x:v>30138</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>16.6583756176832</x:v>
+        <x:v>12.144584139265</x:v>
       </x:c>
       <x:c r="H3" s="0">
         <x:v>29972</x:v>
@@ -597,25 +603,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>0</x:v>
+        <x:v>20111</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>0</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>1</x:v>
+        <x:v>2360</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1</x:v>
+        <x:v>22471</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>0.00055273659890116</x:v>
+        <x:v>9.05504513217279</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>-1</x:v>
+        <x:v>17751</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>49.5</x:v>
@@ -626,25 +632,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>0</x:v>
+        <x:v>33712</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>0</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>11</x:v>
+        <x:v>28713</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>11</x:v>
+        <x:v>62425</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>0.00608010258791276</x:v>
+        <x:v>25.1551418439716</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>-11</x:v>
+        <x:v>4999</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>49.5</x:v>
@@ -661,19 +667,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>25</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>25</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.013818414972529</x:v>
+        <x:v>0.000402965828497743</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>-25</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>49.5</x:v>
@@ -690,19 +696,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.0149238881703313</x:v>
+        <x:v>0.000402965828497743</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>-27</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>49.5</x:v>
@@ -719,19 +725,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.0149238881703313</x:v>
+        <x:v>0.00443262411347518</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>-27</x:v>
+        <x:v>-11</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>49.5</x:v>
@@ -757,7 +763,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.0149238881703313</x:v>
+        <x:v>0.0108800773694391</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>-27</x:v>
@@ -777,19 +783,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.0149238881703313</x:v>
+        <x:v>0.0112830431979368</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>-27</x:v>
+        <x:v>-28</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>49.5</x:v>
@@ -815,7 +821,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.0154766247692325</x:v>
+        <x:v>0.0112830431979368</x:v>
       </x:c>
       <x:c r="H11" s="0">
         <x:v>-28</x:v>
@@ -844,7 +850,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.0154766247692325</x:v>
+        <x:v>0.0112830431979368</x:v>
       </x:c>
       <x:c r="H12" s="0">
         <x:v>-28</x:v>
@@ -873,7 +879,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.0154766247692325</x:v>
+        <x:v>0.0112830431979368</x:v>
       </x:c>
       <x:c r="H13" s="0">
         <x:v>-28</x:v>
@@ -893,19 +899,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0304005129395638</x:v>
+        <x:v>0.0213571889103804</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>-55</x:v>
+        <x:v>-53</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>49.5</x:v>
@@ -922,19 +928,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0326114593351684</x:v>
+        <x:v>0.0217601547388781</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>-59</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>49.5</x:v>
@@ -951,19 +957,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>81</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>81</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0447716645109939</x:v>
+        <x:v>0.0217601547388781</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>-81</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>49.5</x:v>
@@ -989,7 +995,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0608010258791276</x:v>
+        <x:v>0.0443262411347518</x:v>
       </x:c>
       <x:c r="H17" s="0">
         <x:v>-110</x:v>
@@ -1009,19 +1015,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>137</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>137</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0757249140494589</x:v>
+        <x:v>0.0660863958736299</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>-137</x:v>
+        <x:v>-164</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>49.5</x:v>
@@ -1038,19 +1044,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>225</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>225</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.124365734752761</x:v>
+        <x:v>0.0765635074145712</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-225</x:v>
+        <x:v>-190</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>49.5</x:v>
@@ -1067,19 +1073,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>232</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>232</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.128234890945069</x:v>
+        <x:v>0.0975177304964539</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-232</x:v>
+        <x:v>-242</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>49.5</x:v>
@@ -1096,19 +1102,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>234</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>234</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.129340364142871</x:v>
+        <x:v>0.103965183752418</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-234</x:v>
+        <x:v>-258</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>49.5</x:v>
@@ -1125,19 +1131,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>247</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="E22" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>247</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.136525939928586</x:v>
+        <x:v>0.112830431979368</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-247</x:v>
+        <x:v>-280</x:v>
       </x:c>
       <x:c r="I22" s="0">
         <x:v>49.5</x:v>
@@ -1154,19 +1160,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>289</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>289</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.159740877082435</x:v>
+        <x:v>0.113233397807866</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-289</x:v>
+        <x:v>-281</x:v>
       </x:c>
       <x:c r="I23" s="0">
         <x:v>49.5</x:v>
@@ -1183,19 +1189,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>315</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>315</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.174112028653865</x:v>
+        <x:v>0.118068987749839</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-315</x:v>
+        <x:v>-293</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>49.5</x:v>
@@ -1212,19 +1218,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>347</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>347</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.191799599818702</x:v>
+        <x:v>0.147888459058672</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-347</x:v>
+        <x:v>-367</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>49.5</x:v>
@@ -1241,19 +1247,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>528</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>528</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.291844924219812</x:v>
+        <x:v>0.168842682140554</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-528</x:v>
+        <x:v>-419</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>49.5</x:v>
@@ -1270,19 +1276,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1015</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1015</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.561027647884677</x:v>
+        <x:v>0.245406189555126</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1015</x:v>
+        <x:v>-609</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>49.5</x:v>
@@ -1299,19 +1305,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1037</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1037</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.573187853060503</x:v>
+        <x:v>0.288926499032882</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1037</x:v>
+        <x:v>-717</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>49.5</x:v>
@@ -1328,19 +1334,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1173</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1173</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.64836003051106</x:v>
+        <x:v>0.292150225660864</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1173</x:v>
+        <x:v>-725</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>49.5</x:v>
@@ -1357,19 +1363,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>2232</x:v>
+        <x:v>1069</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>2232</x:v>
+        <x:v>1069</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>1.23370808874739</x:v>
+        <x:v>0.430770470664088</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-2232</x:v>
+        <x:v>-1069</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>49.5</x:v>
@@ -1386,19 +1392,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>2775</x:v>
+        <x:v>1173</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>2775</x:v>
+        <x:v>1173</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>1.53384406195072</x:v>
+        <x:v>0.472678916827853</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-2775</x:v>
+        <x:v>-1173</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>49.5</x:v>
@@ -1415,19 +1421,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>3206</x:v>
+        <x:v>1796</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>3206</x:v>
+        <x:v>1796</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>1.77207353607712</x:v>
+        <x:v>0.723726627981947</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-3206</x:v>
+        <x:v>-1796</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>49.5</x:v>
@@ -1444,19 +1450,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>3268</x:v>
+        <x:v>3738</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>3268</x:v>
+        <x:v>3738</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>1.80634320520899</x:v>
+        <x:v>1.50628626692456</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-3268</x:v>
+        <x:v>-3738</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>49.5</x:v>
@@ -1473,19 +1479,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>4755</x:v>
+        <x:v>3849</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>4755</x:v>
+        <x:v>3849</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>2.62826252777501</x:v>
+        <x:v>1.55101547388781</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-4755</x:v>
+        <x:v>-3849</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>49.5</x:v>
@@ -1502,19 +1508,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>5005</x:v>
+        <x:v>4837</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>5005</x:v>
+        <x:v>4837</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>2.7664466775003</x:v>
+        <x:v>1.94914571244358</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-5005</x:v>
+        <x:v>-4837</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>49.5</x:v>
@@ -1531,19 +1537,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>7250</x:v>
+        <x:v>5058</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>7250</x:v>
+        <x:v>5058</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>4.00734034203341</x:v>
+        <x:v>2.03820116054159</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-7250</x:v>
+        <x:v>-5058</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>49.5</x:v>
@@ -1560,19 +1566,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>7360</x:v>
+        <x:v>8108</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>7360</x:v>
+        <x:v>8108</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>4.06814136791254</x:v>
+        <x:v>3.2672469374597</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-7360</x:v>
+        <x:v>-8108</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>49.5</x:v>
@@ -1583,25 +1589,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>20202</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>49.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>28520</x:v>
+        <x:v>10441</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>48722</x:v>
+        <x:v>10441</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>26.9304325716623</x:v>
+        <x:v>4.20736621534494</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-8318</x:v>
+        <x:v>-10441</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>49.5</x:v>
@@ -1618,21 +1624,79 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>17937</x:v>
+        <x:v>12355</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>17937</x:v>
+        <x:v>12355</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>9.9144363744901</x:v>
+        <x:v>4.97864281108962</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-17937</x:v>
+        <x:v>-12355</x:v>
       </x:c>
       <x:c r="I39" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:9">
+      <x:c r="A40" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B40" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C40" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" s="0">
+        <x:v>14079</x:v>
+      </x:c>
+      <x:c r="E40" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F40" s="0">
+        <x:v>14079</x:v>
+      </x:c>
+      <x:c r="G40" s="0">
+        <x:v>5.67335589941973</x:v>
+      </x:c>
+      <x:c r="H40" s="0">
+        <x:v>-14079</x:v>
+      </x:c>
+      <x:c r="I40" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:9">
+      <x:c r="A41" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D41" s="0">
+        <x:v>18407</x:v>
+      </x:c>
+      <x:c r="E41" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F41" s="0">
+        <x:v>18407</x:v>
+      </x:c>
+      <x:c r="G41" s="0">
+        <x:v>7.41739200515796</x:v>
+      </x:c>
+      <x:c r="H41" s="0">
+        <x:v>-18407</x:v>
+      </x:c>
+      <x:c r="I41" s="0">
         <x:v>49.5</x:v>
       </x:c>
     </x:row>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -49,6 +49,9 @@
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
@@ -67,60 +70,57 @@
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>INVEST AZ</x:t>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
     <x:t>ING</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
+    <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
     <x:t>TEB</x:t>
   </x:si>
   <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
@@ -154,10 +154,10 @@
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -551,19 +551,19 @@
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>3046</x:v>
+        <x:v>4199</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>43248</x:v>
+        <x:v>44401</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>17.4274661508704</x:v>
+        <x:v>15.2838112285291</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>37156</x:v>
+        <x:v>36003</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>49.5</x:v>
@@ -580,19 +580,19 @@
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>83</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>30138</x:v>
+        <x:v>30160</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>12.144584139265</x:v>
+        <x:v>10.3817424529276</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>29972</x:v>
+        <x:v>29950</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>49.5</x:v>
@@ -609,19 +609,19 @@
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>2360</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>22471</x:v>
+        <x:v>22665</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>9.05504513217279</x:v>
+        <x:v>7.80179684003993</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>17751</x:v>
+        <x:v>17557</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>49.5</x:v>
@@ -632,25 +632,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>33712</x:v>
+        <x:v>14483</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>28713</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>62425</x:v>
+        <x:v>14903</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>25.1551418439716</x:v>
+        <x:v>5.12994389177653</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>4999</x:v>
+        <x:v>14063</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>49.5</x:v>
@@ -661,25 +661,25 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>0</x:v>
+        <x:v>40404</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>0</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>1</x:v>
+        <x:v>28796</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1</x:v>
+        <x:v>69200</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.000402965828497743</x:v>
+        <x:v>23.8201783071151</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>-1</x:v>
+        <x:v>11608</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>49.5</x:v>
@@ -705,7 +705,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.000402965828497743</x:v>
+        <x:v>0.000344222229871605</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>-1</x:v>
@@ -725,19 +725,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>11</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.00443262411347518</x:v>
+        <x:v>0.000344222229871605</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>-11</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>49.5</x:v>
@@ -754,19 +754,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.0108800773694391</x:v>
+        <x:v>0.00378644452858766</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>-27</x:v>
+        <x:v>-11</x:v>
       </x:c>
       <x:c r="I9" s="0">
         <x:v>49.5</x:v>
@@ -783,19 +783,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.0112830431979368</x:v>
+        <x:v>0.00929400020653334</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>-28</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>49.5</x:v>
@@ -821,7 +821,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.0112830431979368</x:v>
+        <x:v>0.00963822243640494</x:v>
       </x:c>
       <x:c r="H11" s="0">
         <x:v>-28</x:v>
@@ -850,7 +850,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.0112830431979368</x:v>
+        <x:v>0.00963822243640494</x:v>
       </x:c>
       <x:c r="H12" s="0">
         <x:v>-28</x:v>
@@ -870,19 +870,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>28</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>28</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.0112830431979368</x:v>
+        <x:v>0.016522667033837</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>-28</x:v>
+        <x:v>-48</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>49.5</x:v>
@@ -899,19 +899,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0213571889103804</x:v>
+        <x:v>0.0185880004130667</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>-53</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>49.5</x:v>
@@ -937,7 +937,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0217601547388781</x:v>
+        <x:v>0.0185880004130667</x:v>
       </x:c>
       <x:c r="H15" s="0">
         <x:v>-54</x:v>
@@ -957,19 +957,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>54</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>54</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0217601547388781</x:v>
+        <x:v>0.0275377783897284</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>-54</x:v>
+        <x:v>-80</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>49.5</x:v>
@@ -986,19 +986,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>110</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>110</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0443262411347518</x:v>
+        <x:v>0.0285704450793432</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>-110</x:v>
+        <x:v>-83</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>49.5</x:v>
@@ -1015,19 +1015,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>164</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>164</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0660863958736299</x:v>
+        <x:v>0.0382086675157482</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>-164</x:v>
+        <x:v>-111</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>49.5</x:v>
@@ -1044,19 +1044,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>190</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>190</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0765635074145712</x:v>
+        <x:v>0.057485112388558</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-190</x:v>
+        <x:v>-167</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>49.5</x:v>
@@ -1073,19 +1073,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>242</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>242</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0975177304964539</x:v>
+        <x:v>0.0956937799043062</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-242</x:v>
+        <x:v>-278</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>49.5</x:v>
@@ -1102,19 +1102,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>258</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>258</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.103965183752418</x:v>
+        <x:v>0.11359333585763</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-258</x:v>
+        <x:v>-330</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>49.5</x:v>
@@ -1131,19 +1131,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>280</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="E22" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>280</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.112830431979368</x:v>
+        <x:v>0.146294447695432</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-280</x:v>
+        <x:v>-425</x:v>
       </x:c>
       <x:c r="I22" s="0">
         <x:v>49.5</x:v>
@@ -1160,19 +1160,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>281</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>281</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.113233397807866</x:v>
+        <x:v>0.146982892155175</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-281</x:v>
+        <x:v>-427</x:v>
       </x:c>
       <x:c r="I23" s="0">
         <x:v>49.5</x:v>
@@ -1189,19 +1189,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>293</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>293</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.118068987749839</x:v>
+        <x:v>0.163161336959141</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-293</x:v>
+        <x:v>-474</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>49.5</x:v>
@@ -1218,19 +1218,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>367</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>367</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.147888459058672</x:v>
+        <x:v>0.171766892705931</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-367</x:v>
+        <x:v>-499</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>49.5</x:v>
@@ -1247,19 +1247,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>419</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>419</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.168842682140554</x:v>
+        <x:v>0.176586003924133</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-419</x:v>
+        <x:v>-513</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>49.5</x:v>
@@ -1276,19 +1276,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>609</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>609</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.245406189555126</x:v>
+        <x:v>0.256445561254346</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-609</x:v>
+        <x:v>-745</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>49.5</x:v>
@@ -1305,19 +1305,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>717</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>717</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.288926499032882</x:v>
+        <x:v>0.290523562011635</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-717</x:v>
+        <x:v>-844</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>49.5</x:v>
@@ -1334,19 +1334,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>725</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>725</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.292150225660864</x:v>
+        <x:v>0.305669340125985</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-725</x:v>
+        <x:v>-888</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>49.5</x:v>
@@ -1363,19 +1363,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1069</x:v>
+        <x:v>1151</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1069</x:v>
+        <x:v>1151</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.430770470664088</x:v>
+        <x:v>0.396199786582217</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-1069</x:v>
+        <x:v>-1151</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>49.5</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>1173</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.472678916827853</x:v>
+        <x:v>0.403772675639393</x:v>
       </x:c>
       <x:c r="H31" s="0">
         <x:v>-1173</x:v>
@@ -1421,19 +1421,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>1796</x:v>
+        <x:v>1844</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>1796</x:v>
+        <x:v>1844</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.723726627981947</x:v>
+        <x:v>0.63474579188324</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-1796</x:v>
+        <x:v>-1844</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>49.5</x:v>
@@ -1450,19 +1450,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>3738</x:v>
+        <x:v>3825</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>3738</x:v>
+        <x:v>3825</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>1.50628626692456</x:v>
+        <x:v>1.31665002925889</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-3738</x:v>
+        <x:v>-3825</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>49.5</x:v>
@@ -1479,19 +1479,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>3849</x:v>
+        <x:v>4802</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>3849</x:v>
+        <x:v>4802</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>1.55101547388781</x:v>
+        <x:v>1.65295514784345</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-3849</x:v>
+        <x:v>-4802</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>49.5</x:v>
@@ -1508,19 +1508,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>4837</x:v>
+        <x:v>6279</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>4837</x:v>
+        <x:v>6279</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>1.94914571244358</x:v>
+        <x:v>2.16137138136381</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-4837</x:v>
+        <x:v>-6279</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>49.5</x:v>
@@ -1537,19 +1537,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>5058</x:v>
+        <x:v>6303</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>5058</x:v>
+        <x:v>6303</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>2.03820116054159</x:v>
+        <x:v>2.16963271488073</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-5058</x:v>
+        <x:v>-6303</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>49.5</x:v>
@@ -1566,19 +1566,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>8108</x:v>
+        <x:v>10517</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>8108</x:v>
+        <x:v>10517</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>3.2672469374597</x:v>
+        <x:v>3.62018519155967</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-8108</x:v>
+        <x:v>-10517</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>49.5</x:v>
@@ -1595,19 +1595,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>10441</x:v>
+        <x:v>13523</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>10441</x:v>
+        <x:v>13523</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>4.20736621534494</x:v>
+        <x:v>4.65491721455372</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-10441</x:v>
+        <x:v>-13523</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>49.5</x:v>
@@ -1624,19 +1624,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>12355</x:v>
+        <x:v>15387</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>12355</x:v>
+        <x:v>15387</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>4.97864281108962</x:v>
+        <x:v>5.29654745103439</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-12355</x:v>
+        <x:v>-15387</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>49.5</x:v>
@@ -1653,19 +1653,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>14079</x:v>
+        <x:v>18867</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>14079</x:v>
+        <x:v>18867</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>5.67335589941973</x:v>
+        <x:v>6.49444081098757</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-14079</x:v>
+        <x:v>-18867</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>49.5</x:v>
@@ -1682,19 +1682,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>18407</x:v>
+        <x:v>19394</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>18407</x:v>
+        <x:v>19394</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>7.41739200515796</x:v>
+        <x:v>6.67584592612991</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-18407</x:v>
+        <x:v>-19394</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>49.5</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -46,12 +46,12 @@
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
@@ -67,21 +67,21 @@
     <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
@@ -100,21 +100,21 @@
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
     <x:t>ING</x:t>
   </x:si>
   <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
@@ -124,10 +124,10 @@
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
     <x:t>OSMANLI</x:t>
@@ -545,25 +545,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>40202</x:v>
+        <x:v>44702</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>4199</x:v>
+        <x:v>4619</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>44401</x:v>
+        <x:v>49321</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>15.2838112285291</x:v>
+        <x:v>15.8626168284415</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>36003</x:v>
+        <x:v>40083</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>49.5</x:v>
@@ -589,7 +589,7 @@
         <x:v>30160</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>10.3817424529276</x:v>
+        <x:v>9.70005724834848</x:v>
       </x:c>
       <x:c r="H3" s="0">
         <x:v>29950</x:v>
@@ -603,25 +603,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>20111</x:v>
+        <x:v>20191</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>2554</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>22665</x:v>
+        <x:v>20659</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.80179684003993</x:v>
+        <x:v>6.64434624315754</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>17557</x:v>
+        <x:v>19723</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>49.5</x:v>
@@ -632,25 +632,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>14483</x:v>
+        <x:v>20111</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>420</x:v>
+        <x:v>2554</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>14903</x:v>
+        <x:v>22665</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>5.12994389177653</x:v>
+        <x:v>7.28951583334941</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>14063</x:v>
+        <x:v>17557</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>49.5</x:v>
@@ -667,19 +667,19 @@
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>28796</x:v>
+        <x:v>28866</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>69200</x:v>
+        <x:v>69270</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>23.8201783071151</x:v>
+        <x:v>22.2786129175431</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>11608</x:v>
+        <x:v>11538</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>49.5</x:v>
@@ -705,7 +705,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.000344222229871605</x:v>
+        <x:v>0.000321619935290069</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>-1</x:v>
@@ -734,7 +734,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.000344222229871605</x:v>
+        <x:v>0.000321619935290069</x:v>
       </x:c>
       <x:c r="H8" s="0">
         <x:v>-1</x:v>
@@ -763,7 +763,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.00378644452858766</x:v>
+        <x:v>0.00353781928819076</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>-11</x:v>
@@ -792,7 +792,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.00929400020653334</x:v>
+        <x:v>0.00868373825283186</x:v>
       </x:c>
       <x:c r="H10" s="0">
         <x:v>-27</x:v>
@@ -821,7 +821,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.00963822243640494</x:v>
+        <x:v>0.00900535818812193</x:v>
       </x:c>
       <x:c r="H11" s="0">
         <x:v>-28</x:v>
@@ -841,19 +841,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>28</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>28</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.00963822243640494</x:v>
+        <x:v>0.0154377568939233</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>-28</x:v>
+        <x:v>-48</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>49.5</x:v>
@@ -870,19 +870,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.016522667033837</x:v>
+        <x:v>0.0173674765056637</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>-48</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>49.5</x:v>
@@ -908,7 +908,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0185880004130667</x:v>
+        <x:v>0.0173674765056637</x:v>
       </x:c>
       <x:c r="H14" s="0">
         <x:v>-54</x:v>
@@ -928,19 +928,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0185880004130667</x:v>
+        <x:v>0.0180107163762439</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>-54</x:v>
+        <x:v>-56</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>49.5</x:v>
@@ -957,19 +957,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0275377783897284</x:v>
+        <x:v>0.0260512147584956</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>-80</x:v>
+        <x:v>-81</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>49.5</x:v>
@@ -995,7 +995,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0285704450793432</x:v>
+        <x:v>0.0266944546290757</x:v>
       </x:c>
       <x:c r="H17" s="0">
         <x:v>-83</x:v>
@@ -1024,7 +1024,7 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0382086675157482</x:v>
+        <x:v>0.0356998128171977</x:v>
       </x:c>
       <x:c r="H18" s="0">
         <x:v>-111</x:v>
@@ -1044,19 +1044,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>167</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>167</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.057485112388558</x:v>
+        <x:v>0.0578915883522124</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-167</x:v>
+        <x:v>-180</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>49.5</x:v>
@@ -1082,7 +1082,7 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0956937799043062</x:v>
+        <x:v>0.0894103420106392</x:v>
       </x:c>
       <x:c r="H20" s="0">
         <x:v>-278</x:v>
@@ -1102,19 +1102,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>330</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>330</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.11359333585763</x:v>
+        <x:v>0.13893981204531</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-330</x:v>
+        <x:v>-432</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>49.5</x:v>
@@ -1131,19 +1131,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>425</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="E22" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>425</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.146294447695432</x:v>
+        <x:v>0.146658690492271</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-425</x:v>
+        <x:v>-456</x:v>
       </x:c>
       <x:c r="I22" s="0">
         <x:v>49.5</x:v>
@@ -1160,19 +1160,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>427</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>427</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.146982892155175</x:v>
+        <x:v>0.162418067321485</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-427</x:v>
+        <x:v>-505</x:v>
       </x:c>
       <x:c r="I23" s="0">
         <x:v>49.5</x:v>
@@ -1189,19 +1189,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>474</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>474</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.163161336959141</x:v>
+        <x:v>0.170136945768446</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-474</x:v>
+        <x:v>-529</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>49.5</x:v>
@@ -1218,19 +1218,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>499</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>499</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.171766892705931</x:v>
+        <x:v>0.182680123244759</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-499</x:v>
+        <x:v>-568</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>49.5</x:v>
@@ -1247,19 +1247,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>513</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>513</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.176586003924133</x:v>
+        <x:v>0.18718280233882</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-513</x:v>
+        <x:v>-582</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>49.5</x:v>
@@ -1285,7 +1285,7 @@
         <x:v>745</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.256445561254346</x:v>
+        <x:v>0.239606851791101</x:v>
       </x:c>
       <x:c r="H27" s="0">
         <x:v>-745</x:v>
@@ -1305,19 +1305,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>844</x:v>
+        <x:v>899</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>844</x:v>
+        <x:v>899</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.290523562011635</x:v>
+        <x:v>0.289136321825772</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-844</x:v>
+        <x:v>-899</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>49.5</x:v>
@@ -1334,19 +1334,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>888</x:v>
+        <x:v>1025</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>888</x:v>
+        <x:v>1025</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.305669340125985</x:v>
+        <x:v>0.329660433672321</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-888</x:v>
+        <x:v>-1025</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>49.5</x:v>
@@ -1363,19 +1363,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1151</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1151</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.396199786582217</x:v>
+        <x:v>0.385943922348083</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-1151</x:v>
+        <x:v>-1200</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>49.5</x:v>
@@ -1392,19 +1392,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>1173</x:v>
+        <x:v>1232</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>1173</x:v>
+        <x:v>1232</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.403772675639393</x:v>
+        <x:v>0.396235760277365</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-1173</x:v>
+        <x:v>-1232</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>49.5</x:v>
@@ -1421,19 +1421,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>1844</x:v>
+        <x:v>1901</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>1844</x:v>
+        <x:v>1901</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.63474579188324</x:v>
+        <x:v>0.611399496986421</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-1844</x:v>
+        <x:v>-1901</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>49.5</x:v>
@@ -1459,7 +1459,7 @@
         <x:v>3825</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>1.31665002925889</x:v>
+        <x:v>1.23019625248451</x:v>
       </x:c>
       <x:c r="H33" s="0">
         <x:v>-3825</x:v>
@@ -1479,19 +1479,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>4802</x:v>
+        <x:v>5276</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>4802</x:v>
+        <x:v>5276</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>1.65295514784345</x:v>
+        <x:v>1.6968667785904</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-4802</x:v>
+        <x:v>-5276</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>49.5</x:v>
@@ -1508,19 +1508,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>6279</x:v>
+        <x:v>6948</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>6279</x:v>
+        <x:v>6948</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>2.16137138136381</x:v>
+        <x:v>2.2346153103954</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-6279</x:v>
+        <x:v>-6948</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>49.5</x:v>
@@ -1537,19 +1537,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>6303</x:v>
+        <x:v>6959</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>6303</x:v>
+        <x:v>6959</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>2.16963271488073</x:v>
+        <x:v>2.23815312968359</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-6303</x:v>
+        <x:v>-6959</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>49.5</x:v>
@@ -1566,19 +1566,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>10517</x:v>
+        <x:v>11402</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>10517</x:v>
+        <x:v>11402</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>3.62018519155967</x:v>
+        <x:v>3.66711050217737</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-10517</x:v>
+        <x:v>-11402</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>49.5</x:v>
@@ -1595,19 +1595,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>13523</x:v>
+        <x:v>15748</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>13523</x:v>
+        <x:v>15748</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>4.65491721455372</x:v>
+        <x:v>5.06487074094801</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-13523</x:v>
+        <x:v>-15748</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>49.5</x:v>
@@ -1624,19 +1624,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>15387</x:v>
+        <x:v>16870</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>15387</x:v>
+        <x:v>16870</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>5.29654745103439</x:v>
+        <x:v>5.42572830834346</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-15387</x:v>
+        <x:v>-16870</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>49.5</x:v>
@@ -1653,19 +1653,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>18867</x:v>
+        <x:v>19021</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>18867</x:v>
+        <x:v>19021</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>6.49444081098757</x:v>
+        <x:v>6.1175327891524</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-18867</x:v>
+        <x:v>-19021</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>49.5</x:v>
@@ -1682,19 +1682,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>19394</x:v>
+        <x:v>21715</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>19394</x:v>
+        <x:v>21715</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>6.67584592612991</x:v>
+        <x:v>6.98397689482385</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-19394</x:v>
+        <x:v>-21715</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>49.5</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -55,18 +55,21 @@
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALTERNATIF</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
     <x:t>DESTEK</x:t>
   </x:si>
   <x:si>
     <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
@@ -79,15 +82,15 @@
     <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
@@ -97,24 +100,27 @@
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
-    <x:t>FIBA</x:t>
+    <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
     <x:t>ING</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
+    <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
@@ -122,9 +128,6 @@
   </x:si>
   <x:si>
     <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
     <x:t>ATA</x:t>
@@ -508,7 +511,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I41"/>
+  <x:dimension ref="A1:I42"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -545,25 +548,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>44702</x:v>
+        <x:v>60404</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>4619</x:v>
+        <x:v>5372</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>49321</x:v>
+        <x:v>65776</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>15.8626168284415</x:v>
+        <x:v>19.1382882148926</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>40083</x:v>
+        <x:v>55032</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>49.5</x:v>
@@ -580,19 +583,19 @@
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>105</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.504</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>30160</x:v>
+        <x:v>30188</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>9.70005724834848</x:v>
+        <x:v>8.78354786899746</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>29950</x:v>
+        <x:v>29922</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>49.5</x:v>
@@ -618,7 +621,7 @@
         <x:v>20659</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>6.64434624315754</x:v>
+        <x:v>6.0109750704127</x:v>
       </x:c>
       <x:c r="H4" s="0">
         <x:v>19723</x:v>
@@ -638,19 +641,19 @@
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>2554</x:v>
+        <x:v>2581</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>22665</x:v>
+        <x:v>22692</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>7.28951583334941</x:v>
+        <x:v>6.60249994180769</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>17557</x:v>
+        <x:v>17530</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>49.5</x:v>
@@ -667,19 +670,19 @@
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>28866</x:v>
+        <x:v>28947</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>69270</x:v>
+        <x:v>69351</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>22.2786129175431</x:v>
+        <x:v>20.1784758269128</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>11538</x:v>
+        <x:v>11457</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>49.5</x:v>
@@ -699,19 +702,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>49.5</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.000321619935290069</x:v>
+        <x:v>0.000290961569795861</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>-1</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>49.5</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -725,19 +728,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.000321619935290069</x:v>
+        <x:v>0.000581923139591723</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>-1</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>49.5</x:v>
@@ -757,19 +760,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.455</x:v>
       </x:c>
       <x:c r="F9" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.00353781928819076</x:v>
+        <x:v>0.00320057726775447</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>-11</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.455</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -786,19 +789,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.481</x:v>
       </x:c>
       <x:c r="F10" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.00868373825283186</x:v>
+        <x:v>0.00785596238448826</x:v>
       </x:c>
       <x:c r="H10" s="0">
         <x:v>-27</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.481</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -821,7 +824,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.00900535818812193</x:v>
+        <x:v>0.00814692395428412</x:v>
       </x:c>
       <x:c r="H11" s="0">
         <x:v>-28</x:v>
@@ -841,19 +844,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>48</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>48</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.0154377568939233</x:v>
+        <x:v>0.00814692395428412</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>-48</x:v>
+        <x:v>-28</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>49.5</x:v>
@@ -870,19 +873,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.0173674765056637</x:v>
+        <x:v>0.0139661553502013</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>-54</x:v>
+        <x:v>-48</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>49.5</x:v>
@@ -908,7 +911,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0173674765056637</x:v>
+        <x:v>0.0157119247689765</x:v>
       </x:c>
       <x:c r="H14" s="0">
         <x:v>-54</x:v>
@@ -928,19 +931,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0180107163762439</x:v>
+        <x:v>0.0157119247689765</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>-56</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>49.5</x:v>
@@ -960,19 +963,19 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.506</x:v>
       </x:c>
       <x:c r="F16" s="0">
         <x:v>81</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0260512147584956</x:v>
+        <x:v>0.0235678871534648</x:v>
       </x:c>
       <x:c r="H16" s="0">
         <x:v>-81</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.506</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -989,19 +992,19 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.494</x:v>
       </x:c>
       <x:c r="F17" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0266944546290757</x:v>
+        <x:v>0.0241498102930565</x:v>
       </x:c>
       <x:c r="H17" s="0">
         <x:v>-83</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.494</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1015,19 +1018,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>111</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>111</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0356998128171977</x:v>
+        <x:v>0.0244407718628524</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>-111</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>49.5</x:v>
@@ -1044,22 +1047,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>180</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.495</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>180</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0578915883522124</x:v>
+        <x:v>0.0322967342473406</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-180</x:v>
+        <x:v>-111</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.495</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1073,19 +1076,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>278</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>278</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0894103420106392</x:v>
+        <x:v>0.0564465445403971</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-278</x:v>
+        <x:v>-194</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>49.5</x:v>
@@ -1102,19 +1105,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>432</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>432</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.13893981204531</x:v>
+        <x:v>0.0808873164032495</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-432</x:v>
+        <x:v>-278</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>49.5</x:v>
@@ -1131,22 +1134,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>456</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.501</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>456</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.146658690492271</x:v>
+        <x:v>0.153918670422011</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-456</x:v>
+        <x:v>-529</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.501</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1160,22 +1163,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>505</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.499</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>505</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.162418067321485</x:v>
+        <x:v>0.156828286119969</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-505</x:v>
+        <x:v>-539</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.499</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1189,19 +1192,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>529</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>529</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.170136945768446</x:v>
+        <x:v>0.158283093968949</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-529</x:v>
+        <x:v>-544</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>49.5</x:v>
@@ -1212,28 +1215,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>0</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>0</x:v>
+        <x:v>49.499</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>568</x:v>
+        <x:v>1225</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>568</x:v>
+        <x:v>1904</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.182680123244759</x:v>
+        <x:v>0.55399082889132</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-568</x:v>
+        <x:v>-546</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.502</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1247,22 +1250,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>582</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.499</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>582</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.18718280233882</x:v>
+        <x:v>0.162647517515887</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-582</x:v>
+        <x:v>-559</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.499</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1276,19 +1279,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>745</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>745</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.239606851791101</x:v>
+        <x:v>0.196690021182002</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-745</x:v>
+        <x:v>-676</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>49.5</x:v>
@@ -1305,19 +1308,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>899</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>899</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.289136321825772</x:v>
+        <x:v>0.221130793044855</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-899</x:v>
+        <x:v>-760</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>49.5</x:v>
@@ -1334,22 +1337,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1025</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.501</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1025</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.329660433672321</x:v>
+        <x:v>0.224913293452201</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1025</x:v>
+        <x:v>-773</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.501</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1363,19 +1366,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1200</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1200</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.385943922348083</x:v>
+        <x:v>0.308128302413817</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-1200</x:v>
+        <x:v>-1059</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>49.5</x:v>
@@ -1392,19 +1395,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>1232</x:v>
+        <x:v>1323</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>1232</x:v>
+        <x:v>1323</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.396235760277365</x:v>
+        <x:v>0.384942156839925</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-1232</x:v>
+        <x:v>-1323</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>49.5</x:v>
@@ -1421,19 +1424,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>1901</x:v>
+        <x:v>1535</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>1901</x:v>
+        <x:v>1535</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.611399496986421</x:v>
+        <x:v>0.446626009636647</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-1901</x:v>
+        <x:v>-1535</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>49.5</x:v>
@@ -1450,19 +1453,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>3825</x:v>
+        <x:v>1965</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>3825</x:v>
+        <x:v>1965</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>1.23019625248451</x:v>
+        <x:v>0.571739484648868</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-3825</x:v>
+        <x:v>-1965</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>49.5</x:v>
@@ -1479,19 +1482,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>5276</x:v>
+        <x:v>3907</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>5276</x:v>
+        <x:v>3907</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>1.6968667785904</x:v>
+        <x:v>1.13678685319243</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-5276</x:v>
+        <x:v>-3907</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>49.5</x:v>
@@ -1508,19 +1511,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>6948</x:v>
+        <x:v>6371</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>6948</x:v>
+        <x:v>6371</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>2.2346153103954</x:v>
+        <x:v>1.85371616116943</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-6948</x:v>
+        <x:v>-6371</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>49.5</x:v>
@@ -1537,19 +1540,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>6959</x:v>
+        <x:v>7908</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>6959</x:v>
+        <x:v>7908</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>2.23815312968359</x:v>
+        <x:v>2.30092409394567</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-6959</x:v>
+        <x:v>-7908</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>49.5</x:v>
@@ -1566,19 +1569,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>11402</x:v>
+        <x:v>8250</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>11402</x:v>
+        <x:v>8250</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>3.66711050217737</x:v>
+        <x:v>2.40043295081586</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-11402</x:v>
+        <x:v>-8250</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>49.5</x:v>
@@ -1595,19 +1598,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>15748</x:v>
+        <x:v>13226</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>15748</x:v>
+        <x:v>13226</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>5.06487074094801</x:v>
+        <x:v>3.84825772212006</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-15748</x:v>
+        <x:v>-13226</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>49.5</x:v>
@@ -1624,19 +1627,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>16870</x:v>
+        <x:v>18043</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>16870</x:v>
+        <x:v>18043</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>5.42572830834346</x:v>
+        <x:v>5.24981960382673</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-16870</x:v>
+        <x:v>-18043</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>49.5</x:v>
@@ -1653,19 +1656,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>19021</x:v>
+        <x:v>18766</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>19021</x:v>
+        <x:v>18766</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>6.1175327891524</x:v>
+        <x:v>5.46018481878913</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-19021</x:v>
+        <x:v>-18766</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>49.5</x:v>
@@ -1682,21 +1685,50 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>21715</x:v>
+        <x:v>19265</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>21715</x:v>
+        <x:v>19265</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>6.98397689482385</x:v>
+        <x:v>5.60537464211727</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-21715</x:v>
+        <x:v>-19265</x:v>
       </x:c>
       <x:c r="I41" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:9">
+      <x:c r="A42" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B42" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C42" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D42" s="0">
+        <x:v>26036</x:v>
+      </x:c>
+      <x:c r="E42" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F42" s="0">
+        <x:v>26036</x:v>
+      </x:c>
+      <x:c r="G42" s="0">
+        <x:v>7.57547543120505</x:v>
+      </x:c>
+      <x:c r="H42" s="0">
+        <x:v>-26036</x:v>
+      </x:c>
+      <x:c r="I42" s="0">
         <x:v>49.5</x:v>
       </x:c>
     </x:row>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -52,6 +52,9 @@
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
@@ -103,16 +106,16 @@
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
+    <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
     <x:t>BURGAN</x:t>
@@ -121,9 +124,6 @@
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEB</x:t>
   </x:si>
   <x:si>
@@ -151,13 +151,13 @@
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
     <x:t>IS</x:t>
   </x:si>
   <x:si>
     <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
   </x:si>
   <x:si>
     <x:t>ZIRAAT</x:t>
@@ -554,19 +554,19 @@
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>5372</x:v>
+        <x:v>5996</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>65776</x:v>
+        <x:v>66400</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>19.1382882148926</x:v>
+        <x:v>17.8003678027805</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>55032</x:v>
+        <x:v>54408</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>49.5</x:v>
@@ -586,13 +586,13 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>49.504</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F3" s="0">
         <x:v>30188</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>8.78354786899746</x:v>
+        <x:v>8.09273348238461</x:v>
       </x:c>
       <x:c r="H3" s="0">
         <x:v>29922</x:v>
@@ -612,19 +612,19 @@
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>468</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>20659</x:v>
+        <x:v>20687</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>6.0109750704127</x:v>
+        <x:v>5.54572603518253</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>19723</x:v>
+        <x:v>19695</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>49.5</x:v>
@@ -641,19 +641,19 @@
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>2581</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>22692</x:v>
+        <x:v>22731</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>6.60249994180769</x:v>
+        <x:v>6.09367711634042</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>17530</x:v>
+        <x:v>17491</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>49.5</x:v>
@@ -664,25 +664,25 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>40404</x:v>
+        <x:v>15348</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>28947</x:v>
+        <x:v>1225</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>69351</x:v>
+        <x:v>16573</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>20.1784758269128</x:v>
+        <x:v>4.44285384932954</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>11457</x:v>
+        <x:v>14123</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>49.5</x:v>
@@ -693,28 +693,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>0</x:v>
+        <x:v>40404</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>0</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>1</x:v>
+        <x:v>28947</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>50</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1</x:v>
+        <x:v>69351</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.000290961569795861</x:v>
+        <x:v>18.5914654742565</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>-1</x:v>
+        <x:v>11457</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>50</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -728,19 +728,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.000581923139591723</x:v>
+        <x:v>0.000268077828355128</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>-2</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>49.5</x:v>
@@ -757,22 +757,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>49.455</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.00320057726775447</x:v>
+        <x:v>0.000536155656710256</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>-11</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>49.455</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -786,22 +786,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>49.481</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.00785596238448826</x:v>
+        <x:v>0.00294885611190641</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>-27</x:v>
+        <x:v>-11</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>49.481</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -815,19 +815,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.00814692395428412</x:v>
+        <x:v>0.00723810136558846</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>-28</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>49.5</x:v>
@@ -853,7 +853,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.00814692395428412</x:v>
+        <x:v>0.00750617919394358</x:v>
       </x:c>
       <x:c r="H12" s="0">
         <x:v>-28</x:v>
@@ -873,19 +873,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>48</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>48</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.0139661553502013</x:v>
+        <x:v>0.00750617919394358</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>-48</x:v>
+        <x:v>-28</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>49.5</x:v>
@@ -902,19 +902,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0157119247689765</x:v>
+        <x:v>0.0128677357610461</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>-54</x:v>
+        <x:v>-48</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>49.5</x:v>
@@ -940,7 +940,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0157119247689765</x:v>
+        <x:v>0.0144762027311769</x:v>
       </x:c>
       <x:c r="H15" s="0">
         <x:v>-54</x:v>
@@ -960,22 +960,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>81</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>49.506</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>81</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0235678871534648</x:v>
+        <x:v>0.0144762027311769</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>-81</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>49.506</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -989,22 +989,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>49.494</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0241498102930565</x:v>
+        <x:v>0.0217143040967654</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>-83</x:v>
+        <x:v>-81</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>49.494</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1018,19 +1018,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0244407718628524</x:v>
+        <x:v>0.0222504597534756</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>-84</x:v>
+        <x:v>-83</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>49.5</x:v>
@@ -1047,22 +1047,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>111</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>49.495</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>111</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0322967342473406</x:v>
+        <x:v>0.0225185375818308</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-111</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>49.495</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1076,19 +1076,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>194</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>194</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0564465445403971</x:v>
+        <x:v>0.0297566389474192</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-194</x:v>
+        <x:v>-111</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>49.5</x:v>
@@ -1105,19 +1105,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>278</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>278</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0808873164032495</x:v>
+        <x:v>0.0520070987008948</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-278</x:v>
+        <x:v>-194</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>49.5</x:v>
@@ -1134,22 +1134,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>529</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>49.501</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>529</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.153918670422011</x:v>
+        <x:v>0.0772064145662769</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-529</x:v>
+        <x:v>-288</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>49.501</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1163,22 +1163,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>539</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>49.499</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>539</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.156828286119969</x:v>
+        <x:v>0.149051272565451</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-539</x:v>
+        <x:v>-556</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>49.499</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1192,19 +1192,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>544</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>544</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.158283093968949</x:v>
+        <x:v>0.1672805648936</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-544</x:v>
+        <x:v>-624</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>49.5</x:v>
@@ -1215,28 +1215,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>679</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>49.499</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>1225</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>1904</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.55399082889132</x:v>
+        <x:v>0.173446354945768</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-546</x:v>
+        <x:v>-647</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>49.502</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1250,22 +1250,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>559</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>49.499</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>559</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.162647517515887</x:v>
+        <x:v>0.173714432774123</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-559</x:v>
+        <x:v>-648</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>49.499</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1279,19 +1279,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>676</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>676</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.196690021182002</x:v>
+        <x:v>0.214462262684102</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-676</x:v>
+        <x:v>-800</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>49.5</x:v>
@@ -1308,19 +1308,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>760</x:v>
+        <x:v>860</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>760</x:v>
+        <x:v>860</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.221130793044855</x:v>
+        <x:v>0.23054693238541</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-760</x:v>
+        <x:v>-860</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>49.5</x:v>
@@ -1337,22 +1337,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>773</x:v>
+        <x:v>878</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>49.501</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>773</x:v>
+        <x:v>878</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.224913293452201</x:v>
+        <x:v>0.235372333295802</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-773</x:v>
+        <x:v>-878</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>49.501</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1366,19 +1366,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1059</x:v>
+        <x:v>1158</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1059</x:v>
+        <x:v>1158</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.308128302413817</x:v>
+        <x:v>0.310434125235238</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-1059</x:v>
+        <x:v>-1158</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>49.5</x:v>
@@ -1395,19 +1395,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>1323</x:v>
+        <x:v>1625</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>1323</x:v>
+        <x:v>1625</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.384942156839925</x:v>
+        <x:v>0.435626471077083</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-1323</x:v>
+        <x:v>-1625</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>49.5</x:v>
@@ -1424,19 +1424,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>1535</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>1535</x:v>
+        <x:v>1664</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.446626009636647</x:v>
+        <x:v>0.446081506382933</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-1535</x:v>
+        <x:v>-1664</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>49.5</x:v>
@@ -1453,19 +1453,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>1965</x:v>
+        <x:v>1968</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>1965</x:v>
+        <x:v>1968</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.571739484648868</x:v>
+        <x:v>0.527577166202892</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-1965</x:v>
+        <x:v>-1968</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>49.5</x:v>
@@ -1482,19 +1482,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>3907</x:v>
+        <x:v>3989</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>3907</x:v>
+        <x:v>3989</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>1.13678685319243</x:v>
+        <x:v>1.06936245730861</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-3907</x:v>
+        <x:v>-3989</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>49.5</x:v>
@@ -1511,19 +1511,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>6371</x:v>
+        <x:v>7536</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>6371</x:v>
+        <x:v>7536</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>1.85371616116943</x:v>
+        <x:v>2.02023451448424</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-6371</x:v>
+        <x:v>-7536</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>49.5</x:v>
@@ -1540,19 +1540,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>7908</x:v>
+        <x:v>9167</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>7908</x:v>
+        <x:v>9167</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>2.30092409394567</x:v>
+        <x:v>2.45746945253146</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-7908</x:v>
+        <x:v>-9167</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>49.5</x:v>
@@ -1569,19 +1569,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>8250</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>8250</x:v>
+        <x:v>9483</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>2.40043295081586</x:v>
+        <x:v>2.54218204629168</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-8250</x:v>
+        <x:v>-9483</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>49.5</x:v>
@@ -1598,19 +1598,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>13226</x:v>
+        <x:v>14870</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>13226</x:v>
+        <x:v>14870</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>3.84825772212006</x:v>
+        <x:v>3.98631730764075</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-13226</x:v>
+        <x:v>-14870</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>49.5</x:v>
@@ -1627,19 +1627,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>18043</x:v>
+        <x:v>19654</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>18043</x:v>
+        <x:v>19654</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>5.24981960382673</x:v>
+        <x:v>5.26880163849169</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-18043</x:v>
+        <x:v>-19654</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>49.5</x:v>
@@ -1656,19 +1656,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>18766</x:v>
+        <x:v>20464</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>18766</x:v>
+        <x:v>20464</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>5.46018481878913</x:v>
+        <x:v>5.48594467945934</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-18766</x:v>
+        <x:v>-20464</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>49.5</x:v>
@@ -1685,19 +1685,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>19265</x:v>
+        <x:v>20559</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>19265</x:v>
+        <x:v>20559</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>5.60537464211727</x:v>
+        <x:v>5.51141207315308</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-19265</x:v>
+        <x:v>-20559</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>49.5</x:v>
@@ -1714,19 +1714,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>26036</x:v>
+        <x:v>28852</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>26036</x:v>
+        <x:v>28852</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>7.57547543120505</x:v>
+        <x:v>7.73458150370216</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-26036</x:v>
+        <x:v>-28852</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>49.5</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -43,6 +43,12 @@
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
@@ -52,9 +58,6 @@
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
@@ -67,97 +70,91 @@
     <x:t>DESTEK</x:t>
   </x:si>
   <x:si>
-    <x:t>INTEGRAL</x:t>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
   </x:si>
   <x:si>
     <x:t>BIZIM</x:t>
   </x:si>
   <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
-    <x:t>ALNUS</x:t>
+    <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
     <x:t>ING</x:t>
   </x:si>
   <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
-    <x:t>TEB</x:t>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
     <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
     <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
     <x:t>ZIRAAT</x:t>
@@ -511,7 +508,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I42"/>
+  <x:dimension ref="A1:I41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -548,25 +545,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>60404</x:v>
+        <x:v>79147</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>5996</x:v>
+        <x:v>8561</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>66400</x:v>
+        <x:v>87708</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>17.8003678027805</x:v>
+        <x:v>16.8414665524803</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>54408</x:v>
+        <x:v>70586</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>49.5</x:v>
@@ -577,25 +574,25 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>30055</x:v>
+        <x:v>40399</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>133</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.501</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>30188</x:v>
+        <x:v>40928</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>8.09273348238461</x:v>
+        <x:v>7.85889021594283</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>29922</x:v>
+        <x:v>39870</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>49.5</x:v>
@@ -606,25 +603,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>20191</x:v>
+        <x:v>40328</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>496</x:v>
+        <x:v>1279</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>20687</x:v>
+        <x:v>41607</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>5.54572603518253</x:v>
+        <x:v>7.98927006486349</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>19695</x:v>
+        <x:v>39049</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>49.5</x:v>
@@ -635,25 +632,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>20111</x:v>
+        <x:v>24463</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>2620</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.504</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>22731</x:v>
+        <x:v>24596</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>6.09367711634042</x:v>
+        <x:v>4.72286121362709</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>17491</x:v>
+        <x:v>24330</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>49.5</x:v>
@@ -664,25 +661,25 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>15348</x:v>
+        <x:v>20191</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>1225</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>16573</x:v>
+        <x:v>20713</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>4.44285384932954</x:v>
+        <x:v>3.97725745315734</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>14123</x:v>
+        <x:v>19669</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>49.5</x:v>
@@ -693,25 +690,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>40404</x:v>
+        <x:v>15923</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>28947</x:v>
+        <x:v>2367</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>69351</x:v>
+        <x:v>18290</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>18.5914654742565</x:v>
+        <x:v>3.51199917048461</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>11457</x:v>
+        <x:v>13556</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>49.5</x:v>
@@ -722,25 +719,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>0</x:v>
+        <x:v>36049</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>0</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>1</x:v>
+        <x:v>28982</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>1</x:v>
+        <x:v>65031</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.000268077828355128</x:v>
+        <x:v>12.4870868264508</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>-1</x:v>
+        <x:v>7067</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>49.5</x:v>
@@ -757,22 +754,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>49.5</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.000536155656710256</x:v>
+        <x:v>0.000192017450545906</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>-2</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>49.5</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -786,19 +783,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.00294885611190641</x:v>
+        <x:v>0.000384034901091811</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>-11</x:v>
+        <x:v>-2</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>49.5</x:v>
@@ -815,22 +812,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.455</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>27</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.00723810136558846</x:v>
+        <x:v>0.00211219195600496</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>-27</x:v>
+        <x:v>-11</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.455</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -844,22 +841,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.481</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.00750617919394358</x:v>
+        <x:v>0.00518447116473945</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>-28</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.481</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -882,7 +879,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.00750617919394358</x:v>
+        <x:v>0.00537648861528536</x:v>
       </x:c>
       <x:c r="H13" s="0">
         <x:v>-28</x:v>
@@ -911,7 +908,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0128677357610461</x:v>
+        <x:v>0.00921683762620347</x:v>
       </x:c>
       <x:c r="H14" s="0">
         <x:v>-48</x:v>
@@ -940,7 +937,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0144762027311769</x:v>
+        <x:v>0.0103689423294789</x:v>
       </x:c>
       <x:c r="H15" s="0">
         <x:v>-54</x:v>
@@ -960,19 +957,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0144762027311769</x:v>
+        <x:v>0.0107529772305707</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>-54</x:v>
+        <x:v>-56</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>49.5</x:v>
@@ -989,22 +986,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.494</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0217143040967654</x:v>
+        <x:v>0.0159374483953102</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>-81</x:v>
+        <x:v>-83</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.494</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1018,22 +1015,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.506</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0222504597534756</x:v>
+        <x:v>0.016321483296402</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>-83</x:v>
+        <x:v>-85</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.506</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1047,19 +1044,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>84</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>84</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0225185375818308</x:v>
+        <x:v>0.0222740242633251</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-84</x:v>
+        <x:v>-116</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>49.5</x:v>
@@ -1076,22 +1073,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>111</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.504</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>111</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0297566389474192</x:v>
+        <x:v>0.0263063907247891</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-111</x:v>
+        <x:v>-137</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.504</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1105,22 +1102,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>194</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.502</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>194</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0520070987008948</x:v>
+        <x:v>0.0462762055815633</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-194</x:v>
+        <x:v>-241</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.502</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1134,22 +1131,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>288</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.498</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>288</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0772064145662769</x:v>
+        <x:v>0.0520367290979404</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-288</x:v>
+        <x:v>-271</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.498</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1163,22 +1160,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>556</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.501</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>556</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.149051272565451</x:v>
+        <x:v>0.0877519748994789</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-556</x:v>
+        <x:v>-457</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.501</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1192,22 +1189,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>624</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.499</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>624</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.1672805648936</x:v>
+        <x:v>0.159566501403648</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-624</x:v>
+        <x:v>-831</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>49.5</x:v>
+        <x:v>49.499</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1221,19 +1218,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>647</x:v>
+        <x:v>1148</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>647</x:v>
+        <x:v>1148</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.173446354945768</x:v>
+        <x:v>0.2204360332267</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-647</x:v>
+        <x:v>-1148</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>49.5</x:v>
@@ -1250,19 +1247,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>648</x:v>
+        <x:v>1241</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>648</x:v>
+        <x:v>1241</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.173714432774123</x:v>
+        <x:v>0.238293656127469</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-648</x:v>
+        <x:v>-1241</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>49.5</x:v>
@@ -1279,19 +1276,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>800</x:v>
+        <x:v>1536</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>800</x:v>
+        <x:v>1536</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.214462262684102</x:v>
+        <x:v>0.294938804038511</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-800</x:v>
+        <x:v>-1536</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>49.5</x:v>
@@ -1308,19 +1305,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>860</x:v>
+        <x:v>1590</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>860</x:v>
+        <x:v>1590</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.23054693238541</x:v>
+        <x:v>0.30530774636799</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-860</x:v>
+        <x:v>-1590</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>49.5</x:v>
@@ -1337,19 +1334,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>878</x:v>
+        <x:v>1715</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>878</x:v>
+        <x:v>1715</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.235372333295802</x:v>
+        <x:v>0.329309927686228</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-878</x:v>
+        <x:v>-1715</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>49.5</x:v>
@@ -1366,19 +1363,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1158</x:v>
+        <x:v>1892</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1158</x:v>
+        <x:v>1892</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.310434125235238</x:v>
+        <x:v>0.363297016432853</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-1158</x:v>
+        <x:v>-1892</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>49.5</x:v>
@@ -1395,19 +1392,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>1625</x:v>
+        <x:v>2151</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>1625</x:v>
+        <x:v>2151</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.435626471077083</x:v>
+        <x:v>0.413029536124243</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-1625</x:v>
+        <x:v>-2151</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>49.5</x:v>
@@ -1424,19 +1421,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>1664</x:v>
+        <x:v>2268</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>1664</x:v>
+        <x:v>2268</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.446081506382933</x:v>
+        <x:v>0.435495577838114</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-1664</x:v>
+        <x:v>-2268</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>49.5</x:v>
@@ -1453,19 +1450,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>1968</x:v>
+        <x:v>10069</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>1968</x:v>
+        <x:v>10069</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.527577166202892</x:v>
+        <x:v>1.93342370954672</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-1968</x:v>
+        <x:v>-10069</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>49.5</x:v>
@@ -1482,19 +1479,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>3989</x:v>
+        <x:v>13134</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>3989</x:v>
+        <x:v>13134</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>1.06936245730861</x:v>
+        <x:v>2.52195719546992</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-3989</x:v>
+        <x:v>-13134</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>49.5</x:v>
@@ -1511,19 +1508,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>7536</x:v>
+        <x:v>13564</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>7536</x:v>
+        <x:v>13564</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>2.02023451448424</x:v>
+        <x:v>2.60452469920466</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-7536</x:v>
+        <x:v>-13564</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>49.5</x:v>
@@ -1540,19 +1537,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>9167</x:v>
+        <x:v>20284</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>9167</x:v>
+        <x:v>20284</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>2.45746945253146</x:v>
+        <x:v>3.89488196687315</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-9167</x:v>
+        <x:v>-20284</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>49.5</x:v>
@@ -1569,19 +1566,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>9483</x:v>
+        <x:v>21330</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>9483</x:v>
+        <x:v>21330</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>2.54218204629168</x:v>
+        <x:v>4.09573222014417</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-9483</x:v>
+        <x:v>-21330</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>49.5</x:v>
@@ -1598,19 +1595,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>14870</x:v>
+        <x:v>24783</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>14870</x:v>
+        <x:v>24783</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>3.98631730764075</x:v>
+        <x:v>4.75876847687918</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-14870</x:v>
+        <x:v>-24783</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>49.5</x:v>
@@ -1621,25 +1618,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>0</x:v>
+        <x:v>3893</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>0</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>19654</x:v>
+        <x:v>30459</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>19654</x:v>
+        <x:v>34352</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>5.26880163849169</x:v>
+        <x:v>6.59618346115295</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-19654</x:v>
+        <x:v>-26566</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>49.5</x:v>
@@ -1656,19 +1653,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>20464</x:v>
+        <x:v>27588</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>20464</x:v>
+        <x:v>27588</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>5.48594467945934</x:v>
+        <x:v>5.29737742566044</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-20464</x:v>
+        <x:v>-27588</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>49.5</x:v>
@@ -1685,50 +1682,21 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>20559</x:v>
+        <x:v>40820</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>20559</x:v>
+        <x:v>40820</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>5.51141207315308</x:v>
+        <x:v>7.83815233128387</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-20559</x:v>
+        <x:v>-40820</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>49.5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:9">
-      <x:c r="A42" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B42" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C42" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D42" s="0">
-        <x:v>28852</x:v>
-      </x:c>
-      <x:c r="E42" s="0">
-        <x:v>49.5</x:v>
-      </x:c>
-      <x:c r="F42" s="0">
-        <x:v>28852</x:v>
-      </x:c>
-      <x:c r="G42" s="0">
-        <x:v>7.73458150370216</x:v>
-      </x:c>
-      <x:c r="H42" s="0">
-        <x:v>-28852</x:v>
-      </x:c>
-      <x:c r="I42" s="0">
         <x:v>49.5</x:v>
       </x:c>
     </x:row>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -70,39 +70,45 @@
     <x:t>DESTEK</x:t>
   </x:si>
   <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
     <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
     <x:t>BIZIM</x:t>
   </x:si>
   <x:si>
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
-    <x:t>PUSULA YAT.</x:t>
+    <x:t>UNLU</x:t>
   </x:si>
   <x:si>
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
@@ -142,6 +148,9 @@
     <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>OYAK</x:t>
   </x:si>
   <x:si>
@@ -149,9 +158,6 @@
   </x:si>
   <x:si>
     <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
     <x:t>IS</x:t>
@@ -508,7 +514,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I41"/>
+  <x:dimension ref="A1:I43"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -545,25 +551,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>79147</x:v>
+        <x:v>80595</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>8561</x:v>
+        <x:v>9224</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>87708</x:v>
+        <x:v>89819</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>16.8414665524803</x:v>
+        <x:v>15.5780524269218</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>70586</x:v>
+        <x:v>71371</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>49.5</x:v>
@@ -580,19 +586,19 @@
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>529</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>49.501</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>40928</x:v>
+        <x:v>41010</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>7.85889021594283</x:v>
+        <x:v>7.11270365989448</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>39870</x:v>
+        <x:v>39788</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>49.5</x:v>
@@ -603,25 +609,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>40328</x:v>
+        <x:v>40363</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>1279</x:v>
+        <x:v>1307</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>41607</x:v>
+        <x:v>41670</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.98927006486349</x:v>
+        <x:v>7.22717292142899</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>39049</x:v>
+        <x:v>39056</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>49.5</x:v>
@@ -632,7 +638,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>24463</x:v>
+        <x:v>30055</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>49.5</x:v>
@@ -641,16 +647,16 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>49.504</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>24596</x:v>
+        <x:v>30188</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>4.72286121362709</x:v>
+        <x:v>5.23575464727858</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>24330</x:v>
+        <x:v>29922</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>49.5</x:v>
@@ -667,19 +673,19 @@
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>522</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>20713</x:v>
+        <x:v>20769</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>3.97725745315734</x:v>
+        <x:v>3.60213953456104</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>19669</x:v>
+        <x:v>19613</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>49.5</x:v>
@@ -690,25 +696,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>15923</x:v>
+        <x:v>20111</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>2367</x:v>
+        <x:v>2847</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>18290</x:v>
+        <x:v>22958</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>3.51199917048461</x:v>
+        <x:v>3.98179591865051</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>13556</x:v>
+        <x:v>17264</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>49.5</x:v>
@@ -719,25 +725,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>36049</x:v>
+        <x:v>40404</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>28982</x:v>
+        <x:v>29169</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>65031</x:v>
+        <x:v>69573</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>12.4870868264508</x:v>
+        <x:v>12.0666211102131</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>7067</x:v>
+        <x:v>11235</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>49.5</x:v>
@@ -757,19 +763,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>50</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F9" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.000192017450545906</x:v>
+        <x:v>0.000173438275052292</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>-1</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>50</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -792,7 +798,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.000384034901091811</x:v>
+        <x:v>0.000346876550104583</x:v>
       </x:c>
       <x:c r="H10" s="0">
         <x:v>-2</x:v>
@@ -815,19 +821,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>49.455</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F11" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.00211219195600496</x:v>
+        <x:v>0.00190782102557521</x:v>
       </x:c>
       <x:c r="H11" s="0">
         <x:v>-11</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>49.455</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -844,19 +850,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>49.481</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F12" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.00518447116473945</x:v>
+        <x:v>0.00468283342641187</x:v>
       </x:c>
       <x:c r="H12" s="0">
         <x:v>-27</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>49.481</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -879,7 +885,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.00537648861528536</x:v>
+        <x:v>0.00485627170146417</x:v>
       </x:c>
       <x:c r="H13" s="0">
         <x:v>-28</x:v>
@@ -899,19 +905,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>48</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>48</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.00921683762620347</x:v>
+        <x:v>0.00485627170146417</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>-48</x:v>
+        <x:v>-28</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>49.5</x:v>
@@ -928,19 +934,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0103689423294789</x:v>
+        <x:v>0.00832503720251</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>-54</x:v>
+        <x:v>-48</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>49.5</x:v>
@@ -957,19 +963,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0107529772305707</x:v>
+        <x:v>0.00936566685282375</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>-56</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>49.5</x:v>
@@ -986,22 +992,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>83</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>49.494</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>83</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0159374483953102</x:v>
+        <x:v>0.00936566685282375</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>-83</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>49.494</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1015,22 +1021,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>85</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>49.506</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>85</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.016321483296402</x:v>
+        <x:v>0.00971254340292833</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>-85</x:v>
+        <x:v>-56</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>49.506</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1044,19 +1050,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>116</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>116</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0222740242633251</x:v>
+        <x:v>0.0143953768293402</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-116</x:v>
+        <x:v>-83</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>49.5</x:v>
@@ -1076,19 +1082,19 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>49.504</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F20" s="0">
         <x:v>137</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0263063907247891</x:v>
+        <x:v>0.023761043682164</x:v>
       </x:c>
       <x:c r="H20" s="0">
         <x:v>-137</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>49.504</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1102,22 +1108,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>241</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>49.502</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>241</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0462762055815633</x:v>
+        <x:v>0.0241079202322685</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-241</x:v>
+        <x:v>-139</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>49.502</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1131,22 +1137,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>271</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>49.498</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>271</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0520367290979404</x:v>
+        <x:v>0.0244547967823731</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-271</x:v>
+        <x:v>-141</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>49.498</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1160,22 +1166,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>457</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>49.501</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>457</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0877519748994789</x:v>
+        <x:v>0.0565408776670471</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-457</x:v>
+        <x:v>-326</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>49.501</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1189,22 +1195,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>831</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>49.499</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>831</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.159566501403648</x:v>
+        <x:v>0.0593158900678837</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-831</x:v>
+        <x:v>-342</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>49.499</x:v>
+        <x:v>49.5</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1218,19 +1224,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>1148</x:v>
+        <x:v>861</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>1148</x:v>
+        <x:v>861</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.2204360332267</x:v>
+        <x:v>0.149330354820023</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-1148</x:v>
+        <x:v>-861</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>49.5</x:v>
@@ -1247,19 +1253,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1241</x:v>
+        <x:v>905</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1241</x:v>
+        <x:v>905</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.238293656127469</x:v>
+        <x:v>0.156961638922324</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-1241</x:v>
+        <x:v>-905</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>49.5</x:v>
@@ -1276,19 +1282,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1536</x:v>
+        <x:v>1176</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1536</x:v>
+        <x:v>1176</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.294938804038511</x:v>
+        <x:v>0.203963411461495</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1536</x:v>
+        <x:v>-1176</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>49.5</x:v>
@@ -1305,19 +1311,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1590</x:v>
+        <x:v>1279</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1590</x:v>
+        <x:v>1279</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.30530774636799</x:v>
+        <x:v>0.221827553791881</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1590</x:v>
+        <x:v>-1279</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>49.5</x:v>
@@ -1334,19 +1340,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1715</x:v>
+        <x:v>1679</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1715</x:v>
+        <x:v>1679</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.329309927686228</x:v>
+        <x:v>0.291202863812798</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1715</x:v>
+        <x:v>-1679</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>49.5</x:v>
@@ -1363,19 +1369,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1892</x:v>
+        <x:v>1729</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1892</x:v>
+        <x:v>1729</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.363297016432853</x:v>
+        <x:v>0.299874777565412</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-1892</x:v>
+        <x:v>-1729</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>49.5</x:v>
@@ -1392,19 +1398,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>2151</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>2151</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.413029536124243</x:v>
+        <x:v>0.329532722599354</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-2151</x:v>
+        <x:v>-1900</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>49.5</x:v>
@@ -1421,19 +1427,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>2268</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>2268</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.435495577838114</x:v>
+        <x:v>0.346876550104583</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-2268</x:v>
+        <x:v>-2000</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>49.5</x:v>
@@ -1450,19 +1456,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>10069</x:v>
+        <x:v>2163</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>10069</x:v>
+        <x:v>2163</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>1.93342370954672</x:v>
+        <x:v>0.375146988938107</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-10069</x:v>
+        <x:v>-2163</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>49.5</x:v>
@@ -1479,19 +1485,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>13134</x:v>
+        <x:v>2402</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>13134</x:v>
+        <x:v>2402</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>2.52195719546992</x:v>
+        <x:v>0.416598736675605</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-13134</x:v>
+        <x:v>-2402</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>49.5</x:v>
@@ -1508,19 +1514,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>13564</x:v>
+        <x:v>10855</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>13564</x:v>
+        <x:v>10855</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>2.60452469920466</x:v>
+        <x:v>1.88267247569263</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-13564</x:v>
+        <x:v>-10855</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>49.5</x:v>
@@ -1537,19 +1543,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>20284</x:v>
+        <x:v>14284</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>20284</x:v>
+        <x:v>14284</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>3.89488196687315</x:v>
+        <x:v>2.47739232084693</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-20284</x:v>
+        <x:v>-14284</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>49.5</x:v>
@@ -1566,19 +1572,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>21330</x:v>
+        <x:v>14686</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>21330</x:v>
+        <x:v>14686</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>4.09573222014417</x:v>
+        <x:v>2.54711450741796</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-21330</x:v>
+        <x:v>-14686</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>49.5</x:v>
@@ -1589,25 +1595,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>0</x:v>
+        <x:v>16169</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>0</x:v>
+        <x:v>49.5</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>24783</x:v>
+        <x:v>32488</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>24783</x:v>
+        <x:v>48657</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>4.75876847687918</x:v>
+        <x:v>8.43898614921936</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-24783</x:v>
+        <x:v>-16319</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>49.5</x:v>
@@ -1618,25 +1624,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>3893</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>49.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>30459</x:v>
+        <x:v>20752</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>34352</x:v>
+        <x:v>20752</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>6.59618346115295</x:v>
+        <x:v>3.59919108388516</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-26566</x:v>
+        <x:v>-20752</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>49.5</x:v>
@@ -1653,19 +1659,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>27588</x:v>
+        <x:v>23216</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>27588</x:v>
+        <x:v>23216</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>5.29737742566044</x:v>
+        <x:v>4.026542993614</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-27588</x:v>
+        <x:v>-23216</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>49.5</x:v>
@@ -1682,21 +1688,79 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>40820</x:v>
+        <x:v>27642</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>49.5</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>40820</x:v>
+        <x:v>27642</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>7.83815233128387</x:v>
+        <x:v>4.79418079899545</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-40820</x:v>
+        <x:v>-27642</x:v>
       </x:c>
       <x:c r="I41" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:9">
+      <x:c r="A42" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B42" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C42" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D42" s="0">
+        <x:v>38016</x:v>
+      </x:c>
+      <x:c r="E42" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F42" s="0">
+        <x:v>38016</x:v>
+      </x:c>
+      <x:c r="G42" s="0">
+        <x:v>6.59342946438792</x:v>
+      </x:c>
+      <x:c r="H42" s="0">
+        <x:v>-38016</x:v>
+      </x:c>
+      <x:c r="I42" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:9">
+      <x:c r="A43" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B43" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C43" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D43" s="0">
+        <x:v>44908</x:v>
+      </x:c>
+      <x:c r="E43" s="0">
+        <x:v>49.5</x:v>
+      </x:c>
+      <x:c r="F43" s="0">
+        <x:v>44908</x:v>
+      </x:c>
+      <x:c r="G43" s="0">
+        <x:v>7.78876605604831</x:v>
+      </x:c>
+      <x:c r="H43" s="0">
+        <x:v>-44908</x:v>
+      </x:c>
+      <x:c r="I43" s="0">
         <x:v>49.5</x:v>
       </x:c>
     </x:row>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -43,121 +43,109 @@
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
+    <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
     <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
     <x:t>IS</x:t>
@@ -514,7 +502,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I43"/>
+  <x:dimension ref="A1:I39"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -551,28 +539,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>80595</x:v>
+        <x:v>55999</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>9224</x:v>
+        <x:v>3958</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>89819</x:v>
+        <x:v>59957</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>15.5780524269218</x:v>
+        <x:v>29.0430241908139</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>71371</x:v>
+        <x:v>52041</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -580,28 +568,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>40399</x:v>
+        <x:v>18334</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>611</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.444</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>41010</x:v>
+        <x:v>18361</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>7.11270365989448</x:v>
+        <x:v>8.89402350296936</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>39788</x:v>
+        <x:v>18307</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -609,28 +597,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>40363</x:v>
+        <x:v>18365</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>1307</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.448</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>41670</x:v>
+        <x:v>18577</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.22717292142899</x:v>
+        <x:v>8.99865337479776</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>39056</x:v>
+        <x:v>18153</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -638,28 +626,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>30055</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>49.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>133</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.5</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>30188</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>5.23575464727858</x:v>
+        <x:v>0.00290638532856686</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>29922</x:v>
+        <x:v>-6</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -667,28 +655,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>20191</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>49.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>578</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.464</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>20769</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>3.60213953456104</x:v>
+        <x:v>0.013563131533312</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>19613</x:v>
+        <x:v>-28</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.464</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -696,28 +684,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>20111</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>49.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>2847</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.464</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>22958</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>3.98179591865051</x:v>
+        <x:v>0.013563131533312</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>17264</x:v>
+        <x:v>-28</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.464</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -725,28 +713,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>40404</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>49.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>29169</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.457</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>69573</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>12.0666211102131</x:v>
+        <x:v>0.0222822875190126</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>11235</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.457</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -760,22 +748,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>1</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.444</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>1</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.000173438275052292</x:v>
+        <x:v>0.0261574679571018</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>-1</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.444</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -789,22 +777,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>2</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.448</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>2</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.000346876550104583</x:v>
+        <x:v>0.0280950581761463</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>-2</x:v>
+        <x:v>-58</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.448</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -818,22 +806,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>11</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.448</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>11</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.00190782102557521</x:v>
+        <x:v>0.0280950581761463</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>-11</x:v>
+        <x:v>-58</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.448</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -847,22 +835,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>27</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.446</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>27</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.00468283342641187</x:v>
+        <x:v>0.0445645750380252</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>-27</x:v>
+        <x:v>-92</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.446</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -876,22 +864,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>28</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.451</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>28</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.00485627170146417</x:v>
+        <x:v>0.0494085505856366</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>-28</x:v>
+        <x:v>-102</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.451</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -905,22 +893,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>28</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.453</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>28</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.00485627170146417</x:v>
+        <x:v>0.0566745139070538</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>-28</x:v>
+        <x:v>-117</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.453</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -934,22 +922,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>48</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.453</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>48</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.00832503720251</x:v>
+        <x:v>0.0770192112070218</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>-48</x:v>
+        <x:v>-159</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.453</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -963,22 +951,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>54</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.447</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>54</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.00936566685282375</x:v>
+        <x:v>0.0823475843093944</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>-54</x:v>
+        <x:v>-170</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.447</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -992,22 +980,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>54</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.448</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>54</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.00936566685282375</x:v>
+        <x:v>0.0939731256236619</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>-54</x:v>
+        <x:v>-194</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.448</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1021,22 +1009,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>56</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.451</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>56</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.00971254340292833</x:v>
+        <x:v>0.094457523178423</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>-56</x:v>
+        <x:v>-195</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.451</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1050,22 +1038,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>83</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>83</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0143953768293402</x:v>
+        <x:v>0.097848306061751</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-83</x:v>
+        <x:v>-202</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1079,22 +1067,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>137</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>137</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.023761043682164</x:v>
+        <x:v>0.121583786245047</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-137</x:v>
+        <x:v>-251</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1108,22 +1096,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>139</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.451</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>139</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0241079202322685</x:v>
+        <x:v>0.134178122668837</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-139</x:v>
+        <x:v>-277</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.451</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1137,22 +1125,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>141</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>141</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0244547967823731</x:v>
+        <x:v>0.158398000406894</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-141</x:v>
+        <x:v>-327</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1166,22 +1154,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>326</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>326</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0565408776670471</x:v>
+        <x:v>0.229120043402021</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-326</x:v>
+        <x:v>-473</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1195,22 +1183,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>342</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.451</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>342</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0593158900678837</x:v>
+        <x:v>0.255761908913884</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-342</x:v>
+        <x:v>-528</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.451</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1224,22 +1212,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>861</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>861</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.149330354820023</x:v>
+        <x:v>0.30904563993761</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-861</x:v>
+        <x:v>-638</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1253,22 +1241,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>905</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>905</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.156961638922324</x:v>
+        <x:v>0.328421542128055</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-905</x:v>
+        <x:v>-678</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1282,22 +1270,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1176</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1176</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.203963411461495</x:v>
+        <x:v>0.365235756289902</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1176</x:v>
+        <x:v>-754</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1311,22 +1299,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1279</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.451</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1279</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.221827553791881</x:v>
+        <x:v>0.367657744063708</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1279</x:v>
+        <x:v>-759</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.451</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1340,22 +1328,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1679</x:v>
+        <x:v>955</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1679</x:v>
+        <x:v>955</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.291202863812798</x:v>
+        <x:v>0.462599664796892</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1679</x:v>
+        <x:v>-955</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1369,22 +1357,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1729</x:v>
+        <x:v>1392</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1729</x:v>
+        <x:v>1392</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.299874777565412</x:v>
+        <x:v>0.674281396227512</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-1729</x:v>
+        <x:v>-1392</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1398,22 +1386,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>1900</x:v>
+        <x:v>4379</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>1900</x:v>
+        <x:v>4379</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.329532722599354</x:v>
+        <x:v>2.12117689229905</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-1900</x:v>
+        <x:v>-4379</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1427,22 +1415,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>2000</x:v>
+        <x:v>4639</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>2000</x:v>
+        <x:v>4639</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.346876550104583</x:v>
+        <x:v>2.24712025653695</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-2000</x:v>
+        <x:v>-4639</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1456,22 +1444,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>2163</x:v>
+        <x:v>5654</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>2163</x:v>
+        <x:v>5654</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.375146988938107</x:v>
+        <x:v>2.73878377461951</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-2163</x:v>
+        <x:v>-5654</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1485,22 +1473,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>2402</x:v>
+        <x:v>6570</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>2402</x:v>
+        <x:v>6570</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.416598736675605</x:v>
+        <x:v>3.18249193478071</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-2402</x:v>
+        <x:v>-6570</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1508,28 +1496,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>0</x:v>
+        <x:v>10523</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>0</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>10855</x:v>
+        <x:v>19596</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>10855</x:v>
+        <x:v>30119</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>1.88267247569263</x:v>
+        <x:v>14.5895699518509</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-10855</x:v>
+        <x:v>-9073</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1543,22 +1531,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>14284</x:v>
+        <x:v>10134</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>14284</x:v>
+        <x:v>10134</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>2.47739232084693</x:v>
+        <x:v>4.90888481994943</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-14284</x:v>
+        <x:v>-10134</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1572,22 +1560,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>14686</x:v>
+        <x:v>10283</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>14686</x:v>
+        <x:v>10283</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>2.54711450741796</x:v>
+        <x:v>4.98106005560884</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-14686</x:v>
+        <x:v>-10283</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1595,28 +1583,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>16169</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>49.5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>32488</x:v>
+        <x:v>11568</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>48657</x:v>
+        <x:v>11568</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>8.43898614921936</x:v>
+        <x:v>5.60351091347691</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-16319</x:v>
+        <x:v>-11568</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1630,138 +1618,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>20752</x:v>
+        <x:v>17660</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>20752</x:v>
+        <x:v>17660</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>3.59919108388516</x:v>
+        <x:v>8.55446081708179</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-20752</x:v>
+        <x:v>-17660</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>49.5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:9">
-      <x:c r="A40" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B40" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C40" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D40" s="0">
-        <x:v>23216</x:v>
-      </x:c>
-      <x:c r="E40" s="0">
-        <x:v>49.5</x:v>
-      </x:c>
-      <x:c r="F40" s="0">
-        <x:v>23216</x:v>
-      </x:c>
-      <x:c r="G40" s="0">
-        <x:v>4.026542993614</x:v>
-      </x:c>
-      <x:c r="H40" s="0">
-        <x:v>-23216</x:v>
-      </x:c>
-      <x:c r="I40" s="0">
-        <x:v>49.5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:9">
-      <x:c r="A41" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B41" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C41" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D41" s="0">
-        <x:v>27642</x:v>
-      </x:c>
-      <x:c r="E41" s="0">
-        <x:v>49.5</x:v>
-      </x:c>
-      <x:c r="F41" s="0">
-        <x:v>27642</x:v>
-      </x:c>
-      <x:c r="G41" s="0">
-        <x:v>4.79418079899545</x:v>
-      </x:c>
-      <x:c r="H41" s="0">
-        <x:v>-27642</x:v>
-      </x:c>
-      <x:c r="I41" s="0">
-        <x:v>49.5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:9">
-      <x:c r="A42" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B42" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C42" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D42" s="0">
-        <x:v>38016</x:v>
-      </x:c>
-      <x:c r="E42" s="0">
-        <x:v>49.5</x:v>
-      </x:c>
-      <x:c r="F42" s="0">
-        <x:v>38016</x:v>
-      </x:c>
-      <x:c r="G42" s="0">
-        <x:v>6.59342946438792</x:v>
-      </x:c>
-      <x:c r="H42" s="0">
-        <x:v>-38016</x:v>
-      </x:c>
-      <x:c r="I42" s="0">
-        <x:v>49.5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:9">
-      <x:c r="A43" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B43" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C43" s="0">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D43" s="0">
-        <x:v>44908</x:v>
-      </x:c>
-      <x:c r="E43" s="0">
-        <x:v>49.5</x:v>
-      </x:c>
-      <x:c r="F43" s="0">
-        <x:v>44908</x:v>
-      </x:c>
-      <x:c r="G43" s="0">
-        <x:v>7.78876605604831</x:v>
-      </x:c>
-      <x:c r="H43" s="0">
-        <x:v>-44908</x:v>
-      </x:c>
-      <x:c r="I43" s="0">
-        <x:v>49.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -49,97 +49,97 @@
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
     <x:t>DINAMIK</x:t>
   </x:si>
   <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
+    <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
     <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
+    <x:t>ATA</x:t>
   </x:si>
   <x:si>
     <x:t>ING</x:t>
   </x:si>
   <x:si>
-    <x:t>ATA</x:t>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
   </x:si>
   <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEB</x:t>
   </x:si>
   <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
     <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
     <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
   <x:si>
     <x:t>VAKIF</x:t>
@@ -545,19 +545,19 @@
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>3958</x:v>
+        <x:v>5049</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>59957</x:v>
+        <x:v>61048</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>29.0430241908139</x:v>
+        <x:v>24.7217947679598</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>52041</x:v>
+        <x:v>50950</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>54.45</x:v>
@@ -583,7 +583,7 @@
         <x:v>18361</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>8.89402350296936</x:v>
+        <x:v>7.435409411193</x:v>
       </x:c>
       <x:c r="H3" s="0">
         <x:v>18307</x:v>
@@ -603,19 +603,19 @@
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>212</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>54.448</x:v>
+        <x:v>54.449</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>18577</x:v>
+        <x:v>18659</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>8.99865337479776</x:v>
+        <x:v>7.55608649874463</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>18153</x:v>
+        <x:v>18071</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>54.45</x:v>
@@ -626,28 +626,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>0</x:v>
+        <x:v>12903</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>0</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>6</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>54.5</x:v>
+        <x:v>54.449</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>6</x:v>
+        <x:v>13275</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>0.00290638532856686</x:v>
+        <x:v>5.37579978942253</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>-6</x:v>
+        <x:v>12531</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>54.5</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -670,7 +670,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.013563131533312</x:v>
+        <x:v>0.0113387867498178</x:v>
       </x:c>
       <x:c r="H6" s="0">
         <x:v>-28</x:v>
@@ -699,7 +699,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.013563131533312</x:v>
+        <x:v>0.0113387867498178</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>-28</x:v>
@@ -719,22 +719,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>54.457</x:v>
+        <x:v>54.441</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.0222822875190126</x:v>
+        <x:v>0.0137685267676359</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>-46</x:v>
+        <x:v>-34</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>54.457</x:v>
+        <x:v>54.441</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -748,22 +748,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>54.444</x:v>
+        <x:v>54.457</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.0261574679571018</x:v>
+        <x:v>0.0186280068032721</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>-54</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>54.444</x:v>
+        <x:v>54.457</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -777,22 +777,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>54.448</x:v>
+        <x:v>54.444</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.0280950581761463</x:v>
+        <x:v>0.0218676601603628</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>-58</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>54.448</x:v>
+        <x:v>54.444</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -815,7 +815,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.0280950581761463</x:v>
+        <x:v>0.0234874868389082</x:v>
       </x:c>
       <x:c r="H11" s="0">
         <x:v>-58</x:v>
@@ -844,7 +844,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.0445645750380252</x:v>
+        <x:v>0.0372560136065441</x:v>
       </x:c>
       <x:c r="H12" s="0">
         <x:v>-92</x:v>
@@ -864,22 +864,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>102</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>54.451</x:v>
+        <x:v>54.446</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>102</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.0494085505856366</x:v>
+        <x:v>0.0453551469992711</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>-102</x:v>
+        <x:v>-112</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>54.451</x:v>
+        <x:v>54.446</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -893,22 +893,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>117</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>54.453</x:v>
+        <x:v>54.449</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>117</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0566745139070538</x:v>
+        <x:v>0.0514294970438163</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>-117</x:v>
+        <x:v>-127</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>54.453</x:v>
+        <x:v>54.449</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -922,22 +922,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>159</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>54.453</x:v>
+        <x:v>54.446</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>159</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0770192112070218</x:v>
+        <x:v>0.0526443670527254</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>-159</x:v>
+        <x:v>-130</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>54.453</x:v>
+        <x:v>54.446</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -951,22 +951,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>170</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>54.447</x:v>
+        <x:v>54.453</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>170</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0823475843093944</x:v>
+        <x:v>0.0643881104721795</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>-170</x:v>
+        <x:v>-159</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>54.447</x:v>
+        <x:v>54.453</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -980,22 +980,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>194</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>54.448</x:v>
+        <x:v>54.447</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>194</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0939731256236619</x:v>
+        <x:v>0.0688426338381793</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>-194</x:v>
+        <x:v>-170</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>54.448</x:v>
+        <x:v>54.447</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1018,7 +1018,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.094457523178423</x:v>
+        <x:v>0.078966550579088</x:v>
       </x:c>
       <x:c r="H18" s="0">
         <x:v>-195</x:v>
@@ -1047,7 +1047,7 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.097848306061751</x:v>
+        <x:v>0.0818012472665425</x:v>
       </x:c>
       <x:c r="H19" s="0">
         <x:v>-202</x:v>
@@ -1067,22 +1067,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>251</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.449</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>251</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.121583786245047</x:v>
+        <x:v>0.110148214141087</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-251</x:v>
+        <x:v>-272</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.449</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1096,22 +1096,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>277</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>54.451</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>277</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.134178122668837</x:v>
+        <x:v>0.117842390864178</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-277</x:v>
+        <x:v>-291</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>54.451</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1125,22 +1125,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>327</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.451</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>327</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.158398000406894</x:v>
+        <x:v>0.120272130881996</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-327</x:v>
+        <x:v>-297</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.451</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1154,19 +1154,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>473</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>473</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.229120043402021</x:v>
+        <x:v>0.247428525147809</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-473</x:v>
+        <x:v>-611</x:v>
       </x:c>
       <x:c r="I23" s="0">
         <x:v>54.45</x:v>
@@ -1183,22 +1183,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>528</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>54.451</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>528</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.255761908913884</x:v>
+        <x:v>0.257552441888718</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-528</x:v>
+        <x:v>-636</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>54.451</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1212,22 +1212,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>638</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.449</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>638</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.30904563993761</x:v>
+        <x:v>0.320725682351988</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-638</x:v>
+        <x:v>-792</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.449</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1241,19 +1241,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>678</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>678</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.328421542128055</x:v>
+        <x:v>0.33935368915526</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-678</x:v>
+        <x:v>-838</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>54.45</x:v>
@@ -1270,22 +1270,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>754</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.451</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>754</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.365235756289902</x:v>
+        <x:v>0.347857779217624</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-754</x:v>
+        <x:v>-859</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.451</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1299,22 +1299,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>759</x:v>
+        <x:v>915</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>54.451</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>759</x:v>
+        <x:v>915</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.367657744063708</x:v>
+        <x:v>0.370535352717259</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-759</x:v>
+        <x:v>-915</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>54.451</x:v>
+        <x:v>54.45</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1328,19 +1328,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>955</x:v>
+        <x:v>1179</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>955</x:v>
+        <x:v>1179</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.462599664796892</x:v>
+        <x:v>0.477443913501255</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-955</x:v>
+        <x:v>-1179</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>54.45</x:v>
@@ -1357,19 +1357,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1392</x:v>
+        <x:v>1761</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1392</x:v>
+        <x:v>1761</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.674281396227512</x:v>
+        <x:v>0.713128695229611</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-1392</x:v>
+        <x:v>-1761</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>54.45</x:v>
@@ -1380,25 +1380,25 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>0</x:v>
+        <x:v>17869</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>0</x:v>
+        <x:v>54.45</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>4379</x:v>
+        <x:v>19730</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>4379</x:v>
+        <x:v>37599</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>2.12117689229905</x:v>
+        <x:v>15.2259658216571</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-4379</x:v>
+        <x:v>-1861</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>54.45</x:v>
@@ -1415,19 +1415,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>4639</x:v>
+        <x:v>5097</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>4639</x:v>
+        <x:v>5097</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>2.24712025653695</x:v>
+        <x:v>2.06406414513647</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-4639</x:v>
+        <x:v>-5097</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>54.45</x:v>
@@ -1444,19 +1444,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>5654</x:v>
+        <x:v>5249</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>5654</x:v>
+        <x:v>5249</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>2.73878377461951</x:v>
+        <x:v>2.1256175589212</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-5654</x:v>
+        <x:v>-5249</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>54.45</x:v>
@@ -1473,19 +1473,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>6570</x:v>
+        <x:v>7136</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>6570</x:v>
+        <x:v>7136</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>3.18249193478071</x:v>
+        <x:v>2.88977079452499</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-6570</x:v>
+        <x:v>-7136</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>54.45</x:v>
@@ -1496,25 +1496,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>10523</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>54.45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>19596</x:v>
+        <x:v>7801</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>30119</x:v>
+        <x:v>7801</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>14.5895699518509</x:v>
+        <x:v>3.15906697983316</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-9073</x:v>
+        <x:v>-7801</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>54.45</x:v>
@@ -1531,19 +1531,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>10134</x:v>
+        <x:v>12614</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>10134</x:v>
+        <x:v>12614</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>4.90888481994943</x:v>
+        <x:v>5.10812343079291</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-10134</x:v>
+        <x:v>-12614</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>54.45</x:v>
@@ -1560,19 +1560,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>10283</x:v>
+        <x:v>13585</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>10283</x:v>
+        <x:v>13585</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>4.98106005560884</x:v>
+        <x:v>5.5013363570098</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-10283</x:v>
+        <x:v>-13585</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>54.45</x:v>
@@ -1589,19 +1589,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>11568</x:v>
+        <x:v>14579</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>11568</x:v>
+        <x:v>14579</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>5.60351091347691</x:v>
+        <x:v>5.90386328662833</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-11568</x:v>
+        <x:v>-14579</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>54.45</x:v>
@@ -1618,19 +1618,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>17660</x:v>
+        <x:v>22051</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>54.45</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>17660</x:v>
+        <x:v>22051</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>8.55446081708179</x:v>
+        <x:v>8.92969952215113</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-17660</x:v>
+        <x:v>-22051</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>54.45</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -52,18 +52,21 @@
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
-    <x:t>ACAR</x:t>
+    <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>DINAMIK</x:t>
   </x:si>
   <x:si>
@@ -76,12 +79,12 @@
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
@@ -97,18 +100,18 @@
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
-    <x:t>A1 CAPITAL</x:t>
+    <x:t>ING</x:t>
   </x:si>
   <x:si>
     <x:t>ATA</x:t>
   </x:si>
   <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
@@ -125,9 +128,6 @@
   </x:si>
   <x:si>
     <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
   <x:si>
     <x:t>OYAK</x:t>
@@ -542,25 +542,25 @@
         <x:v>55999</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>5049</x:v>
+        <x:v>5534</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>61048</x:v>
+        <x:v>61533</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>24.7217947679598</x:v>
+        <x:v>22.137357893222</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>50950</x:v>
+        <x:v>50465</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -571,25 +571,25 @@
         <x:v>18334</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D3" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>54.444</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F3" s="0">
         <x:v>18361</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>7.435409411193</x:v>
+        <x:v>6.60562670887898</x:v>
       </x:c>
       <x:c r="H3" s="0">
         <x:v>18307</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -600,25 +600,25 @@
         <x:v>18365</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>294</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>54.449</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>18659</x:v>
+        <x:v>18746</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.55608649874463</x:v>
+        <x:v>6.74413584688444</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>18071</x:v>
+        <x:v>17984</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -626,28 +626,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>12903</x:v>
+        <x:v>18360</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>372</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>54.449</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>13275</x:v>
+        <x:v>18769</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>5.37579978942253</x:v>
+        <x:v>6.75241041876529</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>12531</x:v>
+        <x:v>17951</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -655,28 +655,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>0</x:v>
+        <x:v>27922</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>0</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>28</x:v>
+        <x:v>19838</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>54.464</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>28</x:v>
+        <x:v>47760</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.0113387867498178</x:v>
+        <x:v>17.1823283925745</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>-28</x:v>
+        <x:v>8084</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>54.464</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -693,19 +693,19 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>54.464</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>28</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.0113387867498178</x:v>
+        <x:v>0.0100733918549432</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>-28</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>54.464</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -719,22 +719,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>54.441</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.0137685267676359</x:v>
+        <x:v>0.0100733918549432</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>-34</x:v>
+        <x:v>-28</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>54.441</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -751,19 +751,19 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>54.457</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F9" s="0">
         <x:v>46</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.0186280068032721</x:v>
+        <x:v>0.0165491437616923</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>54.457</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -777,22 +777,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>54.444</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.0218676601603628</x:v>
+        <x:v>0.0179881997409699</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>-54</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>54.444</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -806,22 +806,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>54.448</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.0234874868389082</x:v>
+        <x:v>0.0194272557202475</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>-58</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>54.448</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -835,22 +835,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>92</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>54.446</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>92</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.0372560136065441</x:v>
+        <x:v>0.0208663116995251</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>-92</x:v>
+        <x:v>-58</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>54.446</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -864,22 +864,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>112</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>54.446</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>112</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.0453551469992711</x:v>
+        <x:v>0.0330982875233847</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>-112</x:v>
+        <x:v>-92</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>54.446</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -893,22 +893,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>127</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>54.449</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>127</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0514294970438163</x:v>
+        <x:v>0.0402935674197726</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>-127</x:v>
+        <x:v>-112</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>54.449</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -922,22 +922,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>130</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>54.446</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>130</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0526443670527254</x:v>
+        <x:v>0.051446251259174</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>-130</x:v>
+        <x:v>-143</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>54.446</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -951,22 +951,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>54.453</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0643881104721795</x:v>
+        <x:v>0.056842711181465</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>-159</x:v>
+        <x:v>-158</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>54.453</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -980,22 +980,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>170</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>54.447</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>170</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0688426338381793</x:v>
+        <x:v>0.0572024751762844</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>-170</x:v>
+        <x:v>-159</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>54.447</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1009,22 +1009,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>195</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>54.451</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>195</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.078966550579088</x:v>
+        <x:v>0.0611598791192978</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>-195</x:v>
+        <x:v>-170</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>54.451</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1038,22 +1038,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>202</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>202</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0818012472665425</x:v>
+        <x:v>0.0701539789897827</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-202</x:v>
+        <x:v>-195</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1067,22 +1067,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>272</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>54.449</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>272</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.110148214141087</x:v>
+        <x:v>0.0726723269535185</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-272</x:v>
+        <x:v>-202</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>54.449</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1096,22 +1096,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>291</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>291</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.117842390864178</x:v>
+        <x:v>0.0978558065908764</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-291</x:v>
+        <x:v>-272</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1128,19 +1128,19 @@
         <x:v>297</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>54.451</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F22" s="0">
         <x:v>297</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.120272130881996</x:v>
+        <x:v>0.106849906461361</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-297</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>54.451</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1154,22 +1154,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>611</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>611</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.247428525147809</x:v>
+        <x:v>0.132033386098719</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-611</x:v>
+        <x:v>-367</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1183,22 +1183,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>636</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>636</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.257552441888718</x:v>
+        <x:v>0.248237156425385</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-636</x:v>
+        <x:v>-690</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1212,22 +1212,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>792</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>54.449</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>792</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.320725682351988</x:v>
+        <x:v>0.259749604259606</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-792</x:v>
+        <x:v>-722</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>54.449</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1241,22 +1241,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>838</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>838</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.33935368915526</x:v>
+        <x:v>0.284933083896964</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-838</x:v>
+        <x:v>-792</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1270,22 +1270,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>859</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>54.451</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>859</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.347857779217624</x:v>
+        <x:v>0.301482227658656</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-859</x:v>
+        <x:v>-838</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>54.451</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1299,22 +1299,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>915</x:v>
+        <x:v>1066</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>915</x:v>
+        <x:v>1066</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.370535352717259</x:v>
+        <x:v>0.383508418477479</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-915</x:v>
+        <x:v>-1066</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1328,22 +1328,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1179</x:v>
+        <x:v>1090</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1179</x:v>
+        <x:v>1090</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.477443913501255</x:v>
+        <x:v>0.392142754353144</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1179</x:v>
+        <x:v>-1090</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1357,22 +1357,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1761</x:v>
+        <x:v>1371</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1761</x:v>
+        <x:v>1371</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.713128695229611</x:v>
+        <x:v>0.493236436897395</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-1761</x:v>
+        <x:v>-1371</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1380,28 +1380,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>17869</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>54.45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>19730</x:v>
+        <x:v>2057</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>37599</x:v>
+        <x:v>2057</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>15.2259658216571</x:v>
+        <x:v>0.740034537343503</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-1861</x:v>
+        <x:v>-2057</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1415,22 +1415,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>5097</x:v>
+        <x:v>5338</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>5097</x:v>
+        <x:v>5338</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>2.06406414513647</x:v>
+        <x:v>1.92042020434595</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-5097</x:v>
+        <x:v>-5338</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1444,22 +1444,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>5249</x:v>
+        <x:v>6220</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>5249</x:v>
+        <x:v>6220</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>2.1256175589212</x:v>
+        <x:v>2.23773204777666</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-5249</x:v>
+        <x:v>-6220</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1473,22 +1473,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>7136</x:v>
+        <x:v>8429</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>7136</x:v>
+        <x:v>8429</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>2.88977079452499</x:v>
+        <x:v>3.03245071233271</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-7136</x:v>
+        <x:v>-8429</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1502,22 +1502,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>7801</x:v>
+        <x:v>8704</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>7801</x:v>
+        <x:v>8704</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>3.15906697983316</x:v>
+        <x:v>3.13138581090804</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-7801</x:v>
+        <x:v>-8704</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1531,22 +1531,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>12614</x:v>
+        <x:v>14627</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>12614</x:v>
+        <x:v>14627</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>5.10812343079291</x:v>
+        <x:v>5.26226795222334</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-12614</x:v>
+        <x:v>-14627</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1560,22 +1560,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>13585</x:v>
+        <x:v>15867</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>13585</x:v>
+        <x:v>15867</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>5.5013363570098</x:v>
+        <x:v>5.7083753057994</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-13585</x:v>
+        <x:v>-15867</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1589,22 +1589,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>14579</x:v>
+        <x:v>16906</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>14579</x:v>
+        <x:v>16906</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>5.90386328662833</x:v>
+        <x:v>6.08217009641675</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-14579</x:v>
+        <x:v>-16906</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1618,22 +1618,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>22051</x:v>
+        <x:v>25643</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>22051</x:v>
+        <x:v>25643</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>8.92969952215113</x:v>
+        <x:v>9.22542811915384</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-22051</x:v>
+        <x:v>-25643</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>54.45</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -46,21 +46,27 @@
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
     <x:t>ACAR</x:t>
   </x:si>
   <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
@@ -79,42 +85,39 @@
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
     <x:t>ING</x:t>
   </x:si>
   <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
@@ -136,10 +139,10 @@
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
     <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
   </x:si>
   <x:si>
     <x:t>VAKIF</x:t>
@@ -502,7 +505,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I39"/>
+  <x:dimension ref="A1:I40"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -539,25 +542,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>55999</x:v>
+        <x:v>66946</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>5534</x:v>
+        <x:v>7329</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>61533</x:v>
+        <x:v>74275</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>22.137357893222</x:v>
+        <x:v>21.0378582313187</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>50465</x:v>
+        <x:v>59617</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>54.4500007629394</x:v>
@@ -583,7 +586,7 @@
         <x:v>18361</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>6.60562670887898</x:v>
+        <x:v>5.2006208681958</x:v>
       </x:c>
       <x:c r="H3" s="0">
         <x:v>18307</x:v>
@@ -603,19 +606,19 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>381</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>18746</x:v>
+        <x:v>18747</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>6.74413584688444</x:v>
+        <x:v>5.30995258515694</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>17984</x:v>
+        <x:v>17983</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>54.4500007629394</x:v>
@@ -632,19 +635,19 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>409</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>18769</x:v>
+        <x:v>18879</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>6.75241041876529</x:v>
+        <x:v>5.34734063344418</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>17951</x:v>
+        <x:v>17841</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>54.4500007629394</x:v>
@@ -655,25 +658,25 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>27922</x:v>
+        <x:v>18365</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>19838</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>47760</x:v>
+        <x:v>18937</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>17.1823283925745</x:v>
+        <x:v>5.36376871526735</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>8084</x:v>
+        <x:v>17793</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>54.4500007629394</x:v>
@@ -684,25 +687,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>0</x:v>
+        <x:v>36157</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>0</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>28</x:v>
+        <x:v>19956</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>28</x:v>
+        <x:v>56113</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.0100733918549432</x:v>
+        <x:v>15.8936026783438</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>-28</x:v>
+        <x:v>16201</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>54.4500007629394</x:v>
@@ -728,7 +731,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.0100733918549432</x:v>
+        <x:v>0.00793079812153382</x:v>
       </x:c>
       <x:c r="H8" s="0">
         <x:v>-28</x:v>
@@ -748,19 +751,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>46</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>46</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.0165491437616923</x:v>
+        <x:v>0.00793079812153382</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>-46</x:v>
+        <x:v>-28</x:v>
       </x:c>
       <x:c r="I9" s="0">
         <x:v>54.4500007629394</x:v>
@@ -777,19 +780,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.0179881997409699</x:v>
+        <x:v>0.00849728370164338</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>-50</x:v>
+        <x:v>-30</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>54.4500007629394</x:v>
@@ -806,19 +809,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>54</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.0194272557202475</x:v>
+        <x:v>0.0130291683425198</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>-54</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>54.4500007629394</x:v>
@@ -835,19 +838,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.0208663116995251</x:v>
+        <x:v>0.014162139502739</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>-58</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>54.4500007629394</x:v>
@@ -864,19 +867,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>92</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>92</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.0330982875233847</x:v>
+        <x:v>0.0152951106629581</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>-92</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>54.4500007629394</x:v>
@@ -893,19 +896,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>112</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>112</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0402935674197726</x:v>
+        <x:v>0.0164280818231772</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>-112</x:v>
+        <x:v>-58</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>54.4500007629394</x:v>
@@ -922,19 +925,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>143</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>143</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.051446251259174</x:v>
+        <x:v>0.0260583366850397</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>-143</x:v>
+        <x:v>-92</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>54.4500007629394</x:v>
@@ -960,7 +963,7 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.056842711181465</x:v>
+        <x:v>0.0447523608286551</x:v>
       </x:c>
       <x:c r="H16" s="0">
         <x:v>-158</x:v>
@@ -980,19 +983,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>159</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0572024751762844</x:v>
+        <x:v>0.0447523608286551</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>-159</x:v>
+        <x:v>-158</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1018,7 +1021,7 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0611598791192978</x:v>
+        <x:v>0.0481512743093124</x:v>
       </x:c>
       <x:c r="H18" s="0">
         <x:v>-170</x:v>
@@ -1038,19 +1041,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>195</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>195</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0701539789897827</x:v>
+        <x:v>0.0526831589501889</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-195</x:v>
+        <x:v>-186</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1067,19 +1070,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>202</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>202</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0726723269535185</x:v>
+        <x:v>0.0651458417125992</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-202</x:v>
+        <x:v>-230</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1096,19 +1099,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>272</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>272</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0978558065908764</x:v>
+        <x:v>0.07052745472364</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-272</x:v>
+        <x:v>-249</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1125,19 +1128,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>297</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="E22" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>297</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.106849906461361</x:v>
+        <x:v>0.0727933970440782</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-297</x:v>
+        <x:v>-257</x:v>
       </x:c>
       <x:c r="I22" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1154,19 +1157,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>367</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>367</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.132033386098719</x:v>
+        <x:v>0.099984704889337</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-367</x:v>
+        <x:v>-353</x:v>
       </x:c>
       <x:c r="I23" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1183,19 +1186,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>690</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>690</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.248237156425385</x:v>
+        <x:v>0.134823568066075</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-690</x:v>
+        <x:v>-476</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1212,19 +1215,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>722</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>722</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.259749604259606</x:v>
+        <x:v>0.231409359474755</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-722</x:v>
+        <x:v>-817</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1241,19 +1244,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>792</x:v>
+        <x:v>986</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>792</x:v>
+        <x:v>986</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.284933083896964</x:v>
+        <x:v>0.279277390994012</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-792</x:v>
+        <x:v>-986</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1270,19 +1273,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>838</x:v>
+        <x:v>1027</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>838</x:v>
+        <x:v>1027</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.301482227658656</x:v>
+        <x:v>0.290890345386258</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-838</x:v>
+        <x:v>-1027</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1299,19 +1302,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1066</x:v>
+        <x:v>1052</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1066</x:v>
+        <x:v>1052</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.383508418477479</x:v>
+        <x:v>0.297971415137628</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1066</x:v>
+        <x:v>-1052</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1328,19 +1331,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1090</x:v>
+        <x:v>1346</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1090</x:v>
+        <x:v>1346</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.392142754353144</x:v>
+        <x:v>0.381244795413733</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1090</x:v>
+        <x:v>-1346</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1357,19 +1360,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1371</x:v>
+        <x:v>1637</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1371</x:v>
+        <x:v>1637</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.493236436897395</x:v>
+        <x:v>0.463668447319674</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-1371</x:v>
+        <x:v>-1637</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1386,19 +1389,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>2057</x:v>
+        <x:v>1672</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>2057</x:v>
+        <x:v>1672</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.740034537343503</x:v>
+        <x:v>0.473581944971591</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-2057</x:v>
+        <x:v>-1672</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1415,19 +1418,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>5338</x:v>
+        <x:v>2443</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>5338</x:v>
+        <x:v>2443</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>1.92042020434595</x:v>
+        <x:v>0.691962136103826</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-5338</x:v>
+        <x:v>-2443</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1444,19 +1447,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>6220</x:v>
+        <x:v>6005</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>6220</x:v>
+        <x:v>6005</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>2.23773204777666</x:v>
+        <x:v>1.70087295427895</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-6220</x:v>
+        <x:v>-6005</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1473,19 +1476,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>8429</x:v>
+        <x:v>7831</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>8429</x:v>
+        <x:v>7831</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>3.03245071233271</x:v>
+        <x:v>2.21807428891898</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-8429</x:v>
+        <x:v>-7831</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1502,19 +1505,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>8704</x:v>
+        <x:v>11435</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>8704</x:v>
+        <x:v>11435</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>3.13138581090804</x:v>
+        <x:v>3.2388813042764</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-8704</x:v>
+        <x:v>-11435</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1531,19 +1534,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>14627</x:v>
+        <x:v>11800</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>14627</x:v>
+        <x:v>11800</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>5.26226795222334</x:v>
+        <x:v>3.34226492264639</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-14627</x:v>
+        <x:v>-11800</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1560,19 +1563,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>15867</x:v>
+        <x:v>19484</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>15867</x:v>
+        <x:v>19484</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>5.7083753057994</x:v>
+        <x:v>5.51870252142732</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-15867</x:v>
+        <x:v>-19484</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1589,19 +1592,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>16906</x:v>
+        <x:v>21432</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>16906</x:v>
+        <x:v>21432</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>6.08217009641675</x:v>
+        <x:v>6.07045947645403</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-16906</x:v>
+        <x:v>-21432</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1618,21 +1621,50 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>25643</x:v>
+        <x:v>22531</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>25643</x:v>
+        <x:v>22531</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>9.22542811915384</x:v>
+        <x:v>6.38174330272423</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-25643</x:v>
+        <x:v>-22531</x:v>
       </x:c>
       <x:c r="I39" s="0">
+        <x:v>54.4500007629394</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:9">
+      <x:c r="A40" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B40" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C40" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" s="0">
+        <x:v>33621</x:v>
+      </x:c>
+      <x:c r="E40" s="0">
+        <x:v>54.4500007629394</x:v>
+      </x:c>
+      <x:c r="F40" s="0">
+        <x:v>33621</x:v>
+      </x:c>
+      <x:c r="G40" s="0">
+        <x:v>9.52290584443173</x:v>
+      </x:c>
+      <x:c r="H40" s="0">
+        <x:v>-33621</x:v>
+      </x:c>
+      <x:c r="I40" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -82,15 +82,15 @@
     <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
@@ -115,10 +115,10 @@
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
     <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
   </x:si>
   <x:si>
     <x:t>BTCTURK</x:t>
@@ -542,25 +542,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>66946</x:v>
+        <x:v>82779</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>7329</x:v>
+        <x:v>7948</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>74275</x:v>
+        <x:v>90727</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>21.0378582313187</x:v>
+        <x:v>23.5826055312955</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>59617</x:v>
+        <x:v>74831</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>54.4500007629394</x:v>
@@ -586,7 +586,7 @@
         <x:v>18361</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>5.2006208681958</x:v>
+        <x:v>4.77256186317322</x:v>
       </x:c>
       <x:c r="H3" s="0">
         <x:v>18307</x:v>
@@ -606,19 +606,19 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>382</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>18747</x:v>
+        <x:v>18775</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>5.30995258515694</x:v>
+        <x:v>4.88017259305469</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>17983</x:v>
+        <x:v>17955</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>54.4500007629394</x:v>
@@ -635,19 +635,19 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>519</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>18879</x:v>
+        <x:v>18909</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>5.34734063344418</x:v>
+        <x:v>4.91500311915159</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>17841</x:v>
+        <x:v>17811</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>54.4500007629394</x:v>
@@ -664,19 +664,19 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>572</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>18937</x:v>
+        <x:v>19073</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>5.36376871526735</x:v>
+        <x:v>4.95763152422541</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>17793</x:v>
+        <x:v>17657</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>54.4500007629394</x:v>
@@ -693,19 +693,19 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>19956</x:v>
+        <x:v>19970</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>56113</x:v>
+        <x:v>56127</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>15.8936026783438</x:v>
+        <x:v>14.5890517779164</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>16201</x:v>
+        <x:v>16187</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>54.4500007629394</x:v>
@@ -731,7 +731,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.00793079812153382</x:v>
+        <x:v>0.00727802037845706</x:v>
       </x:c>
       <x:c r="H8" s="0">
         <x:v>-28</x:v>
@@ -760,7 +760,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.00793079812153382</x:v>
+        <x:v>0.00727802037845706</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>-28</x:v>
@@ -789,7 +789,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.00849728370164338</x:v>
+        <x:v>0.00779787897691828</x:v>
       </x:c>
       <x:c r="H10" s="0">
         <x:v>-30</x:v>
@@ -818,7 +818,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.0130291683425198</x:v>
+        <x:v>0.011956747764608</x:v>
       </x:c>
       <x:c r="H11" s="0">
         <x:v>-46</x:v>
@@ -847,7 +847,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.014162139502739</x:v>
+        <x:v>0.0129964649615305</x:v>
       </x:c>
       <x:c r="H12" s="0">
         <x:v>-50</x:v>
@@ -876,7 +876,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.0152951106629581</x:v>
+        <x:v>0.0140361821584529</x:v>
       </x:c>
       <x:c r="H13" s="0">
         <x:v>-54</x:v>
@@ -905,7 +905,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0164280818231772</x:v>
+        <x:v>0.0150758993553753</x:v>
       </x:c>
       <x:c r="H14" s="0">
         <x:v>-58</x:v>
@@ -925,19 +925,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>92</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>92</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0260583366850397</x:v>
+        <x:v>0.0311915159076731</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>-92</x:v>
+        <x:v>-120</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>54.4500007629394</x:v>
@@ -963,7 +963,7 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0447523608286551</x:v>
+        <x:v>0.0410688292784363</x:v>
       </x:c>
       <x:c r="H16" s="0">
         <x:v>-158</x:v>
@@ -983,19 +983,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>158</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>158</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0447523608286551</x:v>
+        <x:v>0.0441879808692036</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>-158</x:v>
+        <x:v>-170</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1012,19 +1012,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>170</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>170</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0481512743093124</x:v>
+        <x:v>0.0483468496568933</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>-170</x:v>
+        <x:v>-186</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1050,7 +1050,7 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0526831589501889</x:v>
+        <x:v>0.0483468496568933</x:v>
       </x:c>
       <x:c r="H19" s="0">
         <x:v>-186</x:v>
@@ -1079,7 +1079,7 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0651458417125992</x:v>
+        <x:v>0.0597837388230401</x:v>
       </x:c>
       <x:c r="H20" s="0">
         <x:v>-230</x:v>
@@ -1099,19 +1099,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>249</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>249</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.07052745472364</x:v>
+        <x:v>0.0652422541068829</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-249</x:v>
+        <x:v>-251</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1137,7 +1137,7 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0727933970440782</x:v>
+        <x:v>0.0668018299022666</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-257</x:v>
@@ -1166,7 +1166,7 @@
         <x:v>353</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.099984704889337</x:v>
+        <x:v>0.0917550426284051</x:v>
       </x:c>
       <x:c r="H23" s="0">
         <x:v>-353</x:v>
@@ -1186,19 +1186,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>476</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>476</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.134823568066075</x:v>
+        <x:v>0.134903306300686</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-476</x:v>
+        <x:v>-519</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1215,19 +1215,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>817</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>817</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.231409359474755</x:v>
+        <x:v>0.21340195466833</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-817</x:v>
+        <x:v>-821</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1244,19 +1244,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>986</x:v>
+        <x:v>1014</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>986</x:v>
+        <x:v>1014</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.279277390994012</x:v>
+        <x:v>0.263568309419838</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-986</x:v>
+        <x:v>-1014</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1273,19 +1273,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1027</x:v>
+        <x:v>1052</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1027</x:v>
+        <x:v>1052</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.290890345386258</x:v>
+        <x:v>0.273445622790601</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1027</x:v>
+        <x:v>-1052</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1302,19 +1302,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1052</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1052</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.297971415137628</x:v>
+        <x:v>0.291120815138282</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1052</x:v>
+        <x:v>-1120</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1331,19 +1331,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1346</x:v>
+        <x:v>1490</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1346</x:v>
+        <x:v>1490</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.381244795413733</x:v>
+        <x:v>0.387294655853608</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1346</x:v>
+        <x:v>-1490</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1360,19 +1360,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1637</x:v>
+        <x:v>1822</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1637</x:v>
+        <x:v>1822</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.463668447319674</x:v>
+        <x:v>0.47359118319817</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-1637</x:v>
+        <x:v>-1822</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1389,19 +1389,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>1672</x:v>
+        <x:v>1829</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>1672</x:v>
+        <x:v>1829</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.473581944971591</x:v>
+        <x:v>0.475410688292784</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-1672</x:v>
+        <x:v>-1829</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1418,19 +1418,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>2443</x:v>
+        <x:v>2716</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>2443</x:v>
+        <x:v>2716</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.691962136103826</x:v>
+        <x:v>0.705967976710335</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-2443</x:v>
+        <x:v>-2716</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1447,19 +1447,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>6005</x:v>
+        <x:v>6230</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>6005</x:v>
+        <x:v>6230</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>1.70087295427895</x:v>
+        <x:v>1.6193595342067</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-6005</x:v>
+        <x:v>-6230</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1476,19 +1476,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>7831</x:v>
+        <x:v>8624</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>7831</x:v>
+        <x:v>8624</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>2.21807428891898</x:v>
+        <x:v>2.24163027656477</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-7831</x:v>
+        <x:v>-8624</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1505,19 +1505,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>11435</x:v>
+        <x:v>12842</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>11435</x:v>
+        <x:v>12842</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>3.2388813042764</x:v>
+        <x:v>3.33801206071948</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-11435</x:v>
+        <x:v>-12842</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1534,19 +1534,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>11800</x:v>
+        <x:v>13063</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>11800</x:v>
+        <x:v>13063</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>3.34226492264639</x:v>
+        <x:v>3.39545643584945</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-11800</x:v>
+        <x:v>-13063</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1563,19 +1563,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>19484</x:v>
+        <x:v>21053</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>19484</x:v>
+        <x:v>21053</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>5.51870252142732</x:v>
+        <x:v>5.47229153670202</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-19484</x:v>
+        <x:v>-21053</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1592,19 +1592,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>21432</x:v>
+        <x:v>24250</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>21432</x:v>
+        <x:v>24250</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>6.07045947645403</x:v>
+        <x:v>6.30328550634228</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-21432</x:v>
+        <x:v>-24250</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1621,19 +1621,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>22531</x:v>
+        <x:v>24660</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>22531</x:v>
+        <x:v>24660</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>6.38174330272423</x:v>
+        <x:v>6.40985651902682</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-22531</x:v>
+        <x:v>-24660</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1650,19 +1650,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>33621</x:v>
+        <x:v>37438</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>33621</x:v>
+        <x:v>37438</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>9.52290584443173</x:v>
+        <x:v>9.73123310459555</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-33621</x:v>
+        <x:v>-37438</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>54.4500007629394</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -58,64 +58,64 @@
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
+    <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
     <x:t>ATA</x:t>
   </x:si>
   <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
     <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
   </x:si>
   <x:si>
     <x:t>ING</x:t>
@@ -542,25 +542,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>82779</x:v>
+        <x:v>92729</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>7948</x:v>
+        <x:v>8923</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>90727</x:v>
+        <x:v>101652</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>23.5826055312955</x:v>
+        <x:v>24.0653409090909</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>74831</x:v>
+        <x:v>83806</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>54.4500007629394</x:v>
@@ -586,7 +586,7 @@
         <x:v>18361</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>4.77256186317322</x:v>
+        <x:v>4.34682765151515</x:v>
       </x:c>
       <x:c r="H3" s="0">
         <x:v>18307</x:v>
@@ -615,7 +615,7 @@
         <x:v>18775</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.88017259305469</x:v>
+        <x:v>4.44483901515152</x:v>
       </x:c>
       <x:c r="H4" s="0">
         <x:v>17955</x:v>
@@ -635,19 +635,19 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>549</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>18909</x:v>
+        <x:v>18936</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>4.91500311915159</x:v>
+        <x:v>4.48295454545455</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>17811</x:v>
+        <x:v>17784</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>54.4500007629394</x:v>
@@ -664,19 +664,19 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>708</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>19073</x:v>
+        <x:v>19128</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>4.95763152422541</x:v>
+        <x:v>4.52840909090909</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>17657</x:v>
+        <x:v>17602</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>54.4500007629394</x:v>
@@ -693,19 +693,19 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>19970</x:v>
+        <x:v>20032</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>56127</x:v>
+        <x:v>56189</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>14.5890517779164</x:v>
+        <x:v>13.3023200757576</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>16187</x:v>
+        <x:v>16125</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>54.4500007629394</x:v>
@@ -716,25 +716,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>0</x:v>
+        <x:v>8890</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>0</x:v>
+        <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>28</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>28</x:v>
+        <x:v>9243</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.00727802037845706</x:v>
+        <x:v>2.18821022727273</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>-28</x:v>
+        <x:v>8537</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>54.4500007629394</x:v>
@@ -760,7 +760,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.00727802037845706</x:v>
+        <x:v>0.00662878787878788</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>-28</x:v>
@@ -789,7 +789,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.00779787897691828</x:v>
+        <x:v>0.00710227272727273</x:v>
       </x:c>
       <x:c r="H10" s="0">
         <x:v>-30</x:v>
@@ -818,7 +818,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.011956747764608</x:v>
+        <x:v>0.0108901515151515</x:v>
       </x:c>
       <x:c r="H11" s="0">
         <x:v>-46</x:v>
@@ -847,7 +847,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.0129964649615305</x:v>
+        <x:v>0.0118371212121212</x:v>
       </x:c>
       <x:c r="H12" s="0">
         <x:v>-50</x:v>
@@ -876,7 +876,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.0140361821584529</x:v>
+        <x:v>0.0127840909090909</x:v>
       </x:c>
       <x:c r="H13" s="0">
         <x:v>-54</x:v>
@@ -905,7 +905,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0150758993553753</x:v>
+        <x:v>0.0137310606060606</x:v>
       </x:c>
       <x:c r="H14" s="0">
         <x:v>-58</x:v>
@@ -934,7 +934,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0311915159076731</x:v>
+        <x:v>0.0284090909090909</x:v>
       </x:c>
       <x:c r="H15" s="0">
         <x:v>-120</x:v>
@@ -963,7 +963,7 @@
         <x:v>158</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0410688292784363</x:v>
+        <x:v>0.037405303030303</x:v>
       </x:c>
       <x:c r="H16" s="0">
         <x:v>-158</x:v>
@@ -992,7 +992,7 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0441879808692036</x:v>
+        <x:v>0.0402462121212121</x:v>
       </x:c>
       <x:c r="H17" s="0">
         <x:v>-170</x:v>
@@ -1021,7 +1021,7 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0483468496568933</x:v>
+        <x:v>0.0440340909090909</x:v>
       </x:c>
       <x:c r="H18" s="0">
         <x:v>-186</x:v>
@@ -1050,7 +1050,7 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0483468496568933</x:v>
+        <x:v>0.0440340909090909</x:v>
       </x:c>
       <x:c r="H19" s="0">
         <x:v>-186</x:v>
@@ -1070,19 +1070,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>230</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>230</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0597837388230401</x:v>
+        <x:v>0.0556344696969697</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-230</x:v>
+        <x:v>-235</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1099,19 +1099,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>251</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>251</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0652422541068829</x:v>
+        <x:v>0.056344696969697</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-251</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1137,7 +1137,7 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0668018299022666</x:v>
+        <x:v>0.060842803030303</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-257</x:v>
@@ -1157,19 +1157,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>353</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>353</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0917550426284051</x:v>
+        <x:v>0.0625</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-353</x:v>
+        <x:v>-264</x:v>
       </x:c>
       <x:c r="I23" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1195,7 +1195,7 @@
         <x:v>519</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.134903306300686</x:v>
+        <x:v>0.122869318181818</x:v>
       </x:c>
       <x:c r="H24" s="0">
         <x:v>-519</x:v>
@@ -1215,19 +1215,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>821</x:v>
+        <x:v>983</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>821</x:v>
+        <x:v>983</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.21340195466833</x:v>
+        <x:v>0.232717803030303</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-821</x:v>
+        <x:v>-983</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1244,19 +1244,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1014</x:v>
+        <x:v>1114</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1014</x:v>
+        <x:v>1114</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.263568309419838</x:v>
+        <x:v>0.263731060606061</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-1014</x:v>
+        <x:v>-1114</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1273,19 +1273,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1052</x:v>
+        <x:v>1152</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1052</x:v>
+        <x:v>1152</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.273445622790601</x:v>
+        <x:v>0.272727272727273</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1052</x:v>
+        <x:v>-1152</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1302,19 +1302,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1120</x:v>
+        <x:v>1234</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1120</x:v>
+        <x:v>1234</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.291120815138282</x:v>
+        <x:v>0.292140151515152</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1120</x:v>
+        <x:v>-1234</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1331,19 +1331,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1490</x:v>
+        <x:v>1746</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1490</x:v>
+        <x:v>1746</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.387294655853608</x:v>
+        <x:v>0.413352272727273</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1490</x:v>
+        <x:v>-1746</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1360,19 +1360,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1822</x:v>
+        <x:v>1931</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1822</x:v>
+        <x:v>1931</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.47359118319817</x:v>
+        <x:v>0.457149621212121</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-1822</x:v>
+        <x:v>-1931</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1389,19 +1389,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>1829</x:v>
+        <x:v>1995</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>1829</x:v>
+        <x:v>1995</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.475410688292784</x:v>
+        <x:v>0.472301136363636</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-1829</x:v>
+        <x:v>-1995</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1418,19 +1418,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>2716</x:v>
+        <x:v>2883</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>2716</x:v>
+        <x:v>2883</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.705967976710335</x:v>
+        <x:v>0.682528409090909</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-2716</x:v>
+        <x:v>-2883</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1447,19 +1447,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>6230</x:v>
+        <x:v>6434</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>6230</x:v>
+        <x:v>6434</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>1.6193595342067</x:v>
+        <x:v>1.52320075757576</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-6230</x:v>
+        <x:v>-6434</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1476,19 +1476,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>8624</x:v>
+        <x:v>9521</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>8624</x:v>
+        <x:v>9521</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>2.24163027656477</x:v>
+        <x:v>2.25402462121212</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-8624</x:v>
+        <x:v>-9521</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1505,19 +1505,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>12842</x:v>
+        <x:v>14291</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>12842</x:v>
+        <x:v>14291</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>3.33801206071948</x:v>
+        <x:v>3.38328598484848</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-12842</x:v>
+        <x:v>-14291</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1534,19 +1534,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>13063</x:v>
+        <x:v>14814</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>13063</x:v>
+        <x:v>14814</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>3.39545643584945</x:v>
+        <x:v>3.50710227272727</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-13063</x:v>
+        <x:v>-14814</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1563,19 +1563,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>21053</x:v>
+        <x:v>23560</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>21053</x:v>
+        <x:v>23560</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>5.47229153670202</x:v>
+        <x:v>5.57765151515152</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-21053</x:v>
+        <x:v>-23560</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1592,19 +1592,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>24250</x:v>
+        <x:v>26777</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>24250</x:v>
+        <x:v>26777</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>6.30328550634228</x:v>
+        <x:v>6.33925189393939</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-24250</x:v>
+        <x:v>-26777</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1621,19 +1621,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>24660</x:v>
+        <x:v>27548</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>24660</x:v>
+        <x:v>27548</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>6.40985651902682</x:v>
+        <x:v>6.5217803030303</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-24660</x:v>
+        <x:v>-27548</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1650,19 +1650,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>37438</x:v>
+        <x:v>41534</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>37438</x:v>
+        <x:v>41534</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>9.73123310459555</x:v>
+        <x:v>9.83285984848485</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-37438</x:v>
+        <x:v>-41534</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>54.4500007629394</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -43,22 +43,25 @@
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>MARBAS</x:t>
+    <x:t>BIZIM</x:t>
   </x:si>
   <x:si>
     <x:t>ICBC TURKEY</x:t>
@@ -82,28 +85,28 @@
     <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
-    <x:t>PUSULA YAT.</x:t>
+    <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
   </x:si>
   <x:si>
     <x:t>BURGAN</x:t>
@@ -505,7 +508,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I40"/>
+  <x:dimension ref="A1:I41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -548,19 +551,19 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>8923</x:v>
+        <x:v>9301</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>101652</x:v>
+        <x:v>102030</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>24.0653409090909</x:v>
+        <x:v>22.5951040619367</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>83806</x:v>
+        <x:v>83428</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>54.4500007629394</x:v>
@@ -571,25 +574,25 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>18334</x:v>
+        <x:v>23496</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>27</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>18361</x:v>
+        <x:v>24072</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>4.34682765151515</x:v>
+        <x:v>5.3308766537189</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>18307</x:v>
+        <x:v>22920</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>54.4500007629394</x:v>
@@ -600,25 +603,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>18365</x:v>
+        <x:v>18334</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>410</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>18775</x:v>
+        <x:v>18361</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.44483901515152</x:v>
+        <x:v>4.06614432697461</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>17955</x:v>
+        <x:v>18307</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>54.4500007629394</x:v>
@@ -629,25 +632,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>18360</x:v>
+        <x:v>18333</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>576</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>18936</x:v>
+        <x:v>18713</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>4.48295454545455</x:v>
+        <x:v>4.14409666089406</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>17784</x:v>
+        <x:v>17953</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>54.4500007629394</x:v>
@@ -664,19 +667,19 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>763</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>19128</x:v>
+        <x:v>18884</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>4.52840909090909</x:v>
+        <x:v>4.18196555038334</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>17602</x:v>
+        <x:v>17846</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>54.4500007629394</x:v>
@@ -687,25 +690,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>36157</x:v>
+        <x:v>18365</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>20032</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>56189</x:v>
+        <x:v>19189</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>13.3023200757576</x:v>
+        <x:v>4.24950947608059</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>16125</x:v>
+        <x:v>17541</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>54.4500007629394</x:v>
@@ -716,25 +719,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>8890</x:v>
+        <x:v>36157</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>353</x:v>
+        <x:v>20140</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>9243</x:v>
+        <x:v>56297</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>2.18821022727273</x:v>
+        <x:v>12.4672799507483</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>8537</x:v>
+        <x:v>16017</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>54.4500007629394</x:v>
@@ -751,19 +754,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>28</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>28</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.00662878787878788</x:v>
+        <x:v>0.000885821976357412</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>-28</x:v>
+        <x:v>-4</x:v>
       </x:c>
       <x:c r="I9" s="0">
         <x:v>54.4500007629394</x:v>
@@ -780,19 +783,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.00710227272727273</x:v>
+        <x:v>0.00620075383450188</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>-30</x:v>
+        <x:v>-28</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>54.4500007629394</x:v>
@@ -809,19 +812,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>46</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>46</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.0108901515151515</x:v>
+        <x:v>0.00664366482268059</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>-46</x:v>
+        <x:v>-30</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>54.4500007629394</x:v>
@@ -838,19 +841,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.0118371212121212</x:v>
+        <x:v>0.0101869527281102</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>-50</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>54.4500007629394</x:v>
@@ -867,19 +870,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.0127840909090909</x:v>
+        <x:v>0.0110727747044676</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>-54</x:v>
+        <x:v>-50</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>54.4500007629394</x:v>
@@ -896,19 +899,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0137310606060606</x:v>
+        <x:v>0.0119585966808251</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>-58</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>54.4500007629394</x:v>
@@ -925,19 +928,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>120</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>120</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0284090909090909</x:v>
+        <x:v>0.0128444186571825</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>-120</x:v>
+        <x:v>-58</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>54.4500007629394</x:v>
@@ -954,19 +957,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>158</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>158</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.037405303030303</x:v>
+        <x:v>0.0265746592907223</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>-158</x:v>
+        <x:v>-120</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>54.4500007629394</x:v>
@@ -992,7 +995,7 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0402462121212121</x:v>
+        <x:v>0.03764743399519</x:v>
       </x:c>
       <x:c r="H17" s="0">
         <x:v>-170</x:v>
@@ -1012,19 +1015,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>186</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0440340909090909</x:v>
+        <x:v>0.0409692664065303</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>-186</x:v>
+        <x:v>-185</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1050,7 +1053,7 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0440340909090909</x:v>
+        <x:v>0.0411907219006196</x:v>
       </x:c>
       <x:c r="H19" s="0">
         <x:v>-186</x:v>
@@ -1070,19 +1073,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>235</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>235</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0556344696969697</x:v>
+        <x:v>0.0453983762883173</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-235</x:v>
+        <x:v>-205</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1099,19 +1102,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>238</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>238</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.056344696969697</x:v>
+        <x:v>0.0520420411109979</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-238</x:v>
+        <x:v>-235</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1128,19 +1131,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>257</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E22" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>257</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.060842803030303</x:v>
+        <x:v>0.052706407593266</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-257</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="I22" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1157,19 +1160,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>264</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>264</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0625</x:v>
+        <x:v>0.0637791822977336</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-264</x:v>
+        <x:v>-288</x:v>
       </x:c>
       <x:c r="I23" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1186,19 +1189,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>519</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>519</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.122869318181818</x:v>
+        <x:v>0.0695370251440568</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-519</x:v>
+        <x:v>-314</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1215,19 +1218,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>983</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>983</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.232717803030303</x:v>
+        <x:v>0.126229631630931</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-983</x:v>
+        <x:v>-570</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1244,19 +1247,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1114</x:v>
+        <x:v>1073</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1114</x:v>
+        <x:v>1073</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.263731060606061</x:v>
+        <x:v>0.237621745157876</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-1114</x:v>
+        <x:v>-1073</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1273,19 +1276,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1152</x:v>
+        <x:v>1175</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1152</x:v>
+        <x:v>1175</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.272727272727273</x:v>
+        <x:v>0.26021020555499</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1152</x:v>
+        <x:v>-1175</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1302,19 +1305,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1234</x:v>
+        <x:v>1207</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1234</x:v>
+        <x:v>1207</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.292140151515152</x:v>
+        <x:v>0.267296781365849</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1234</x:v>
+        <x:v>-1207</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1331,19 +1334,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1746</x:v>
+        <x:v>1288</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1746</x:v>
+        <x:v>1288</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.413352272727273</x:v>
+        <x:v>0.285234676387086</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1746</x:v>
+        <x:v>-1288</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1360,19 +1363,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1931</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1931</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.457149621212121</x:v>
+        <x:v>0.418772339322966</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-1931</x:v>
+        <x:v>-1891</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1389,19 +1392,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>1995</x:v>
+        <x:v>2004</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>1995</x:v>
+        <x:v>2004</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.472301136363636</x:v>
+        <x:v>0.443796810155063</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-1995</x:v>
+        <x:v>-2004</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1418,19 +1421,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>2883</x:v>
+        <x:v>2194</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>2883</x:v>
+        <x:v>2194</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.682528409090909</x:v>
+        <x:v>0.48587335403204</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-2883</x:v>
+        <x:v>-2194</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1447,19 +1450,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>6434</x:v>
+        <x:v>3022</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>6434</x:v>
+        <x:v>3022</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>1.52320075757576</x:v>
+        <x:v>0.669238503138024</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-6434</x:v>
+        <x:v>-3022</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1476,19 +1479,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>9521</x:v>
+        <x:v>6783</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>9521</x:v>
+        <x:v>6783</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>2.25402462121212</x:v>
+        <x:v>1.50213261640808</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-9521</x:v>
+        <x:v>-6783</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1505,19 +1508,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>14291</x:v>
+        <x:v>10376</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>14291</x:v>
+        <x:v>10376</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>3.38328598484848</x:v>
+        <x:v>2.29782220667113</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-14291</x:v>
+        <x:v>-10376</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1534,19 +1537,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>14814</x:v>
+        <x:v>15198</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>14814</x:v>
+        <x:v>15198</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>3.50710227272727</x:v>
+        <x:v>3.36568059916998</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-14814</x:v>
+        <x:v>-15198</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1563,19 +1566,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>23560</x:v>
+        <x:v>16153</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>23560</x:v>
+        <x:v>16153</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>5.57765151515152</x:v>
+        <x:v>3.57717059602532</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-23560</x:v>
+        <x:v>-16153</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1592,19 +1595,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>26777</x:v>
+        <x:v>25357</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>26777</x:v>
+        <x:v>25357</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>6.33925189393939</x:v>
+        <x:v>5.61544696362372</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-26777</x:v>
+        <x:v>-25357</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1621,19 +1624,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>27548</x:v>
+        <x:v>28699</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>27548</x:v>
+        <x:v>28699</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>6.5217803030303</x:v>
+        <x:v>6.35555122487034</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-27548</x:v>
+        <x:v>-28699</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1650,21 +1653,50 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>41534</x:v>
+        <x:v>29705</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>41534</x:v>
+        <x:v>29705</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>9.83285984848485</x:v>
+        <x:v>6.57833545192423</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-41534</x:v>
+        <x:v>-29705</x:v>
       </x:c>
       <x:c r="I40" s="0">
+        <x:v>54.4500007629394</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:9">
+      <x:c r="A41" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C41" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D41" s="0">
+        <x:v>45106</x:v>
+      </x:c>
+      <x:c r="E41" s="0">
+        <x:v>54.4500007629394</x:v>
+      </x:c>
+      <x:c r="F41" s="0">
+        <x:v>45106</x:v>
+      </x:c>
+      <x:c r="G41" s="0">
+        <x:v>9.98897151639435</x:v>
+      </x:c>
+      <x:c r="H41" s="0">
+        <x:v>-45106</x:v>
+      </x:c>
+      <x:c r="I41" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
     </x:row>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -73,40 +73,40 @@
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
     <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
-    <x:t>BULLS YATIRIM</x:t>
+    <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
     <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
     <x:t>BURGAN</x:t>
@@ -551,19 +551,19 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>9301</x:v>
+        <x:v>9729</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>102030</x:v>
+        <x:v>102458</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>22.5951040619367</x:v>
+        <x:v>21.8361849228067</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>83428</x:v>
+        <x:v>83000</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>54.4500007629394</x:v>
@@ -574,7 +574,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>23496</x:v>
+        <x:v>32323</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>54.4500007629394</x:v>
@@ -586,13 +586,13 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>24072</x:v>
+        <x:v>32899</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>5.3308766537189</x:v>
+        <x:v>7.01154275679224</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>22920</x:v>
+        <x:v>31747</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>54.4500007629394</x:v>
@@ -618,7 +618,7 @@
         <x:v>18361</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.06614432697461</x:v>
+        <x:v>3.91315652626105</x:v>
       </x:c>
       <x:c r="H4" s="0">
         <x:v>18307</x:v>
@@ -647,7 +647,7 @@
         <x:v>18713</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>4.14409666089406</x:v>
+        <x:v>3.98817592047944</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>17953</x:v>
@@ -676,7 +676,7 @@
         <x:v>18884</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>4.18196555038334</x:v>
+        <x:v>4.02462000119349</x:v>
       </x:c>
       <x:c r="H6" s="0">
         <x:v>17846</x:v>
@@ -696,19 +696,19 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>824</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>19189</x:v>
+        <x:v>19217</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>4.24950947608059</x:v>
+        <x:v>4.09559005311032</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>17541</x:v>
+        <x:v>17513</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>54.4500007629394</x:v>
@@ -725,19 +725,19 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>20140</x:v>
+        <x:v>20168</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>56297</x:v>
+        <x:v>56325</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>12.4672799507483</x:v>
+        <x:v>12.0041686913378</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>16017</x:v>
+        <x:v>15989</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>54.4500007629394</x:v>
@@ -763,7 +763,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.000885821976357412</x:v>
+        <x:v>0.000852493116118087</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>-4</x:v>
@@ -792,7 +792,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.00620075383450188</x:v>
+        <x:v>0.00596745181282661</x:v>
       </x:c>
       <x:c r="H10" s="0">
         <x:v>-28</x:v>
@@ -821,7 +821,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.00664366482268059</x:v>
+        <x:v>0.00639369837088566</x:v>
       </x:c>
       <x:c r="H11" s="0">
         <x:v>-30</x:v>
@@ -850,7 +850,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.0101869527281102</x:v>
+        <x:v>0.009803670835358</x:v>
       </x:c>
       <x:c r="H12" s="0">
         <x:v>-46</x:v>
@@ -870,19 +870,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.0110727747044676</x:v>
+        <x:v>0.0115086570675942</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>-50</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>54.4500007629394</x:v>
@@ -899,19 +899,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0119585966808251</x:v>
+        <x:v>0.0123611501837123</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>-54</x:v>
+        <x:v>-58</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>54.4500007629394</x:v>
@@ -937,7 +937,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0128444186571825</x:v>
+        <x:v>0.0123611501837123</x:v>
       </x:c>
       <x:c r="H15" s="0">
         <x:v>-58</x:v>
@@ -966,7 +966,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0265746592907223</x:v>
+        <x:v>0.0255747934835426</x:v>
       </x:c>
       <x:c r="H16" s="0">
         <x:v>-120</x:v>
@@ -986,19 +986,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>170</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>170</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.03764743399519</x:v>
+        <x:v>0.0394278066204615</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>-170</x:v>
+        <x:v>-185</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1015,19 +1015,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0409692664065303</x:v>
+        <x:v>0.0396409298994911</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>-185</x:v>
+        <x:v>-186</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1044,19 +1044,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>186</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>186</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0411907219006196</x:v>
+        <x:v>0.0415590394107568</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-186</x:v>
+        <x:v>-195</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1082,7 +1082,7 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0453983762883173</x:v>
+        <x:v>0.043690272201052</x:v>
       </x:c>
       <x:c r="H20" s="0">
         <x:v>-205</x:v>
@@ -1102,19 +1102,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0520420411109979</x:v>
+        <x:v>0.0507233404090262</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-235</x:v>
+        <x:v>-238</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1131,19 +1131,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>238</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E22" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>238</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.052706407593266</x:v>
+        <x:v>0.0564776689428233</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-238</x:v>
+        <x:v>-265</x:v>
       </x:c>
       <x:c r="I22" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1160,19 +1160,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>288</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>288</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0637791822977336</x:v>
+        <x:v>0.068625695847506</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-288</x:v>
+        <x:v>-322</x:v>
       </x:c>
       <x:c r="I23" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1189,19 +1189,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>314</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>314</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0695370251440568</x:v>
+        <x:v>0.0786424899618936</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-314</x:v>
+        <x:v>-369</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1227,7 +1227,7 @@
         <x:v>570</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.126229631630931</x:v>
+        <x:v>0.121480269046827</x:v>
       </x:c>
       <x:c r="H25" s="0">
         <x:v>-570</x:v>
@@ -1247,19 +1247,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1073</x:v>
+        <x:v>1124</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1073</x:v>
+        <x:v>1124</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.237621745157876</x:v>
+        <x:v>0.239550565629183</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-1073</x:v>
+        <x:v>-1124</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1285,7 +1285,7 @@
         <x:v>1175</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.26021020555499</x:v>
+        <x:v>0.250419852859688</x:v>
       </x:c>
       <x:c r="H27" s="0">
         <x:v>-1175</x:v>
@@ -1305,19 +1305,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1207</x:v>
+        <x:v>1278</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1207</x:v>
+        <x:v>1278</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.267296781365849</x:v>
+        <x:v>0.272371550599729</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1207</x:v>
+        <x:v>-1278</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1334,19 +1334,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1288</x:v>
+        <x:v>1310</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1288</x:v>
+        <x:v>1310</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.285234676387086</x:v>
+        <x:v>0.279191495528674</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1288</x:v>
+        <x:v>-1310</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1363,19 +1363,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1891</x:v>
+        <x:v>2059</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1891</x:v>
+        <x:v>2059</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.418772339322966</x:v>
+        <x:v>0.438820831521786</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-1891</x:v>
+        <x:v>-2059</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1392,19 +1392,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>2004</x:v>
+        <x:v>2065</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>2004</x:v>
+        <x:v>2065</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.443796810155063</x:v>
+        <x:v>0.440099571195963</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-2004</x:v>
+        <x:v>-2065</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1421,19 +1421,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>2194</x:v>
+        <x:v>2295</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>2194</x:v>
+        <x:v>2295</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.48587335403204</x:v>
+        <x:v>0.489117925372753</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-2194</x:v>
+        <x:v>-2295</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1450,19 +1450,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>3022</x:v>
+        <x:v>3159</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>3022</x:v>
+        <x:v>3159</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.669238503138024</x:v>
+        <x:v>0.67325643845426</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-3022</x:v>
+        <x:v>-3159</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1479,19 +1479,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>6783</x:v>
+        <x:v>6958</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>6783</x:v>
+        <x:v>6958</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>1.50213261640808</x:v>
+        <x:v>1.48291177548741</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-6783</x:v>
+        <x:v>-6958</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1508,19 +1508,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>10376</x:v>
+        <x:v>10781</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>10376</x:v>
+        <x:v>10781</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>2.29782220667113</x:v>
+        <x:v>2.29768207121728</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-10376</x:v>
+        <x:v>-10781</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1537,19 +1537,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>15198</x:v>
+        <x:v>15820</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>15198</x:v>
+        <x:v>15820</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>3.36568059916998</x:v>
+        <x:v>3.37161027424704</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-15198</x:v>
+        <x:v>-15820</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1566,19 +1566,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>16153</x:v>
+        <x:v>16943</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>16153</x:v>
+        <x:v>16943</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>3.57717059602532</x:v>
+        <x:v>3.61094771659719</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-16153</x:v>
+        <x:v>-16943</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1595,19 +1595,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>25357</x:v>
+        <x:v>26492</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>25357</x:v>
+        <x:v>26492</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>5.61544696362372</x:v>
+        <x:v>5.64606190805009</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-25357</x:v>
+        <x:v>-26492</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1624,19 +1624,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>28699</x:v>
+        <x:v>29840</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>28699</x:v>
+        <x:v>29840</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>6.35555122487034</x:v>
+        <x:v>6.35959864624093</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-28699</x:v>
+        <x:v>-29840</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1653,19 +1653,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>29705</x:v>
+        <x:v>31277</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>29705</x:v>
+        <x:v>31277</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>6.57833545192423</x:v>
+        <x:v>6.66585679820635</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-29705</x:v>
+        <x:v>-31277</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1682,19 +1682,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>45106</x:v>
+        <x:v>46846</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>45106</x:v>
+        <x:v>46846</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>9.98897151639435</x:v>
+        <x:v>9.98397312941698</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-45106</x:v>
+        <x:v>-46846</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>54.4500007629394</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -70,16 +70,16 @@
     <x:t>ACAR</x:t>
   </x:si>
   <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
     <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
   </x:si>
   <x:si>
     <x:t>GLOBAL</x:t>
@@ -545,25 +545,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>92729</x:v>
+        <x:v>93097</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>9729</x:v>
+        <x:v>9783</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>102458</x:v>
+        <x:v>102880</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>21.8361849228067</x:v>
+        <x:v>21.8273163942495</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>83000</x:v>
+        <x:v>83314</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>54.4500007629394</x:v>
@@ -574,7 +574,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>32323</x:v>
+        <x:v>33017</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>54.4500007629394</x:v>
@@ -586,13 +586,13 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>32899</x:v>
+        <x:v>33593</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>7.01154275679224</x:v>
+        <x:v>7.12718739922264</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>31747</x:v>
+        <x:v>32441</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>54.4500007629394</x:v>
@@ -618,7 +618,7 @@
         <x:v>18361</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>3.91315652626105</x:v>
+        <x:v>3.8955225147241</x:v>
       </x:c>
       <x:c r="H4" s="0">
         <x:v>18307</x:v>
@@ -647,7 +647,7 @@
         <x:v>18713</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>3.98817592047944</x:v>
+        <x:v>3.97020384608856</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>17953</x:v>
@@ -676,7 +676,7 @@
         <x:v>18884</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>4.02462000119349</x:v>
+        <x:v>4.00648369740482</x:v>
       </x:c>
       <x:c r="H6" s="0">
         <x:v>17846</x:v>
@@ -705,7 +705,7 @@
         <x:v>19217</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>4.09559005311032</x:v>
+        <x:v>4.07713393417859</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>17513</x:v>
@@ -725,19 +725,19 @@
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>20168</x:v>
+        <x:v>20190</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>56325</x:v>
+        <x:v>56347</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>12.0041686913378</x:v>
+        <x:v>11.9547414158902</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>15989</x:v>
+        <x:v>15967</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>54.4500007629394</x:v>
@@ -763,7 +763,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.000852493116118087</x:v>
+        <x:v>0.000848651492777976</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>-4</x:v>
@@ -792,7 +792,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.00596745181282661</x:v>
+        <x:v>0.00594056044944583</x:v>
       </x:c>
       <x:c r="H10" s="0">
         <x:v>-28</x:v>
@@ -821,7 +821,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.00639369837088566</x:v>
+        <x:v>0.00636488619583482</x:v>
       </x:c>
       <x:c r="H11" s="0">
         <x:v>-30</x:v>
@@ -841,19 +841,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.009803670835358</x:v>
+        <x:v>0.0114567951525027</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>-46</x:v>
+        <x:v>-54</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>54.4500007629394</x:v>
@@ -870,19 +870,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.0115086570675942</x:v>
+        <x:v>0.0123054466452806</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>-54</x:v>
+        <x:v>-58</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>54.4500007629394</x:v>
@@ -908,7 +908,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0123611501837123</x:v>
+        <x:v>0.0123054466452806</x:v>
       </x:c>
       <x:c r="H14" s="0">
         <x:v>-58</x:v>
@@ -928,19 +928,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0123611501837123</x:v>
+        <x:v>0.0154878897431981</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>-58</x:v>
+        <x:v>-73</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>54.4500007629394</x:v>
@@ -966,7 +966,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0255747934835426</x:v>
+        <x:v>0.0254595447833393</x:v>
       </x:c>
       <x:c r="H16" s="0">
         <x:v>-120</x:v>
@@ -995,7 +995,7 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0394278066204615</x:v>
+        <x:v>0.0392501315409814</x:v>
       </x:c>
       <x:c r="H17" s="0">
         <x:v>-185</x:v>
@@ -1024,7 +1024,7 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0396409298994911</x:v>
+        <x:v>0.0394622944141759</x:v>
       </x:c>
       <x:c r="H18" s="0">
         <x:v>-186</x:v>
@@ -1053,7 +1053,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0415590394107568</x:v>
+        <x:v>0.0413717602729263</x:v>
       </x:c>
       <x:c r="H19" s="0">
         <x:v>-195</x:v>
@@ -1082,7 +1082,7 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.043690272201052</x:v>
+        <x:v>0.0434933890048713</x:v>
       </x:c>
       <x:c r="H20" s="0">
         <x:v>-205</x:v>
@@ -1111,7 +1111,7 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0507233404090262</x:v>
+        <x:v>0.0504947638202896</x:v>
       </x:c>
       <x:c r="H21" s="0">
         <x:v>-238</x:v>
@@ -1140,7 +1140,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0564776689428233</x:v>
+        <x:v>0.0562231613965409</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-265</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>322</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.068625695847506</x:v>
+        <x:v>0.068316445168627</x:v>
       </x:c>
       <x:c r="H23" s="0">
         <x:v>-322</x:v>
@@ -1198,7 +1198,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0786424899618936</x:v>
+        <x:v>0.0782881002087683</x:v>
       </x:c>
       <x:c r="H24" s="0">
         <x:v>-369</x:v>
@@ -1227,7 +1227,7 @@
         <x:v>570</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.121480269046827</x:v>
+        <x:v>0.120932837720862</x:v>
       </x:c>
       <x:c r="H25" s="0">
         <x:v>-570</x:v>
@@ -1256,7 +1256,7 @@
         <x:v>1124</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.239550565629183</x:v>
+        <x:v>0.238471069470611</x:v>
       </x:c>
       <x:c r="H26" s="0">
         <x:v>-1124</x:v>
@@ -1285,7 +1285,7 @@
         <x:v>1175</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.250419852859688</x:v>
+        <x:v>0.24929137600353</x:v>
       </x:c>
       <x:c r="H27" s="0">
         <x:v>-1175</x:v>
@@ -1305,19 +1305,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1278</x:v>
+        <x:v>1306</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1278</x:v>
+        <x:v>1306</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.272371550599729</x:v>
+        <x:v>0.277084712392009</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1278</x:v>
+        <x:v>-1306</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1343,7 +1343,7 @@
         <x:v>1310</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.279191495528674</x:v>
+        <x:v>0.277933363884787</x:v>
       </x:c>
       <x:c r="H29" s="0">
         <x:v>-1310</x:v>
@@ -1372,7 +1372,7 @@
         <x:v>2059</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.438820831521786</x:v>
+        <x:v>0.436843355907463</x:v>
       </x:c>
       <x:c r="H30" s="0">
         <x:v>-2059</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>2065</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.440099571195963</x:v>
+        <x:v>0.43811633314663</x:v>
       </x:c>
       <x:c r="H31" s="0">
         <x:v>-2065</x:v>
@@ -1430,7 +1430,7 @@
         <x:v>2295</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.489117925372753</x:v>
+        <x:v>0.486913793981364</x:v>
       </x:c>
       <x:c r="H32" s="0">
         <x:v>-2295</x:v>
@@ -1459,7 +1459,7 @@
         <x:v>3159</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.67325643845426</x:v>
+        <x:v>0.670222516421406</x:v>
       </x:c>
       <x:c r="H33" s="0">
         <x:v>-3159</x:v>
@@ -1479,19 +1479,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>6958</x:v>
+        <x:v>6987</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>6958</x:v>
+        <x:v>6987</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>1.48291177548741</x:v>
+        <x:v>1.48238199500993</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-6958</x:v>
+        <x:v>-6987</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1517,7 +1517,7 @@
         <x:v>10781</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>2.29768207121728</x:v>
+        <x:v>2.28732793590984</x:v>
       </x:c>
       <x:c r="H35" s="0">
         <x:v>-10781</x:v>
@@ -1537,19 +1537,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>15820</x:v>
+        <x:v>15834</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>15820</x:v>
+        <x:v>15834</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>3.37161027424704</x:v>
+        <x:v>3.35938693416162</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-15820</x:v>
+        <x:v>-15834</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1566,19 +1566,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>16943</x:v>
+        <x:v>17055</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>16943</x:v>
+        <x:v>17055</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>3.61094771659719</x:v>
+        <x:v>3.61843780233209</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-16943</x:v>
+        <x:v>-17055</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1595,19 +1595,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>26492</x:v>
+        <x:v>26587</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>26492</x:v>
+        <x:v>26587</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>5.64606190805009</x:v>
+        <x:v>5.64077430962201</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-26492</x:v>
+        <x:v>-26587</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1624,19 +1624,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>29840</x:v>
+        <x:v>29949</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>29840</x:v>
+        <x:v>29949</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>6.35959864624093</x:v>
+        <x:v>6.3540658893019</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-29840</x:v>
+        <x:v>-29949</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1653,19 +1653,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>31277</x:v>
+        <x:v>31407</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>31277</x:v>
+        <x:v>31407</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>6.66585679820635</x:v>
+        <x:v>6.66339935841947</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-31277</x:v>
+        <x:v>-31407</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>54.4500007629394</x:v>
@@ -1682,19 +1682,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>46846</x:v>
+        <x:v>47288</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>54.4500007629394</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>46846</x:v>
+        <x:v>47288</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>9.98397312941698</x:v>
+        <x:v>10.0327579476212</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-46846</x:v>
+        <x:v>-47288</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>54.4500007629394</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -43,121 +43,130 @@
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
-    <x:t>TERA</x:t>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -508,7 +517,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I41"/>
+  <x:dimension ref="A1:I44"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -545,28 +554,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>93097</x:v>
+        <x:v>349328</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>9783</x:v>
+        <x:v>20490</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>102880</x:v>
+        <x:v>369818</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>21.8273163942495</x:v>
+        <x:v>23.1124982657095</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>83314</x:v>
+        <x:v>328838</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -574,28 +583,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>33017</x:v>
+        <x:v>133664</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>576</x:v>
+        <x:v>28641</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>33593</x:v>
+        <x:v>162305</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>7.12718739922264</x:v>
+        <x:v>10.1435680010599</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>32441</x:v>
+        <x:v>105023</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -603,28 +612,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>18334</x:v>
+        <x:v>66800</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>27</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.849</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>18361</x:v>
+        <x:v>67151</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>3.8955225147241</x:v>
+        <x:v>4.19673290927067</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>18307</x:v>
+        <x:v>66449</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -632,28 +641,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>18333</x:v>
+        <x:v>33404</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>380</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.857</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>18713</x:v>
+        <x:v>33460</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>3.97020384608856</x:v>
+        <x:v>2.09114805653224</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>17953</x:v>
+        <x:v>33348</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -661,28 +670,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>18365</x:v>
+        <x:v>33332</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>519</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>18884</x:v>
+        <x:v>33332</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>4.00648369740482</x:v>
+        <x:v>2.08314844651323</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>17846</x:v>
+        <x:v>33332</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -690,28 +699,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>18365</x:v>
+        <x:v>33386</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>852</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.851</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>19217</x:v>
+        <x:v>33507</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>4.07713393417859</x:v>
+        <x:v>2.0940854133361</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>17513</x:v>
+        <x:v>33265</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -719,28 +728,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>36157</x:v>
+        <x:v>33416</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>20190</x:v>
+        <x:v>5245</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>56347</x:v>
+        <x:v>38661</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>11.9547414158902</x:v>
+        <x:v>2.41619471050786</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>15967</x:v>
+        <x:v>28171</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -748,28 +757,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>0</x:v>
+        <x:v>19199</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>4</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>4</x:v>
+        <x:v>19553</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.000848651492777976</x:v>
+        <x:v>1.22200292735729</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>-4</x:v>
+        <x:v>18845</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -777,28 +786,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>0</x:v>
+        <x:v>16699</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.852</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>28</x:v>
+        <x:v>16726</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.00594056044944583</x:v>
+        <x:v>1.04532404045303</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>-28</x:v>
+        <x:v>16672</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -806,28 +815,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>0</x:v>
+        <x:v>16708</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>30</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.849</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>30</x:v>
+        <x:v>17146</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.00636488619583482</x:v>
+        <x:v>1.07157276082791</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>-30</x:v>
+        <x:v>16270</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -835,28 +844,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>0</x:v>
+        <x:v>16700</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>54</x:v>
+        <x:v>1088</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>54</x:v>
+        <x:v>17788</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.0114567951525027</x:v>
+        <x:v>1.11169580482951</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>-54</x:v>
+        <x:v>15612</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -864,28 +873,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>0</x:v>
+        <x:v>18000</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>58</x:v>
+        <x:v>3697</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>58</x:v>
+        <x:v>21697</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.0123054466452806</x:v>
+        <x:v>1.35599639517574</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>-58</x:v>
+        <x:v>14303</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -893,28 +902,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>0</x:v>
+        <x:v>25917</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>58</x:v>
+        <x:v>21032</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>58</x:v>
+        <x:v>46949</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0123054466452806</x:v>
+        <x:v>2.93416945923886</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>-58</x:v>
+        <x:v>4885</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -922,28 +931,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>0</x:v>
+        <x:v>3486</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>0</x:v>
+        <x:v>59.851</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>73</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>73</x:v>
+        <x:v>4065</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0154878897431981</x:v>
+        <x:v>0.254050115056891</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>-73</x:v>
+        <x:v>2907</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.851</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -957,22 +966,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>120</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.839</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>120</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0254595447833393</x:v>
+        <x:v>0.00193740555147937</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>-120</x:v>
+        <x:v>-31</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.839</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -986,22 +995,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>185</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.839</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>185</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0392501315409814</x:v>
+        <x:v>0.00193740555147937</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>-185</x:v>
+        <x:v>-31</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.839</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1015,22 +1024,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>186</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.852</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>186</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0394622944141759</x:v>
+        <x:v>0.00506225321515576</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>-186</x:v>
+        <x:v>-81</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.852</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1044,22 +1053,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>195</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.853</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>195</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0413717602729263</x:v>
+        <x:v>0.0101870033835851</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-195</x:v>
+        <x:v>-163</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.853</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1073,22 +1082,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>205</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.852</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>205</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0434933890048713</x:v>
+        <x:v>0.0164366987109378</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-205</x:v>
+        <x:v>-263</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.852</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1102,22 +1111,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>238</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.849</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>238</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0504947638202896</x:v>
+        <x:v>0.0182491103558702</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-238</x:v>
+        <x:v>-292</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.849</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1131,22 +1140,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>265</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>265</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0562231613965409</x:v>
+        <x:v>0.0187490859820584</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-265</x:v>
+        <x:v>-300</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1160,22 +1169,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>322</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.851</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>322</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.068316445168627</x:v>
+        <x:v>0.0284986106927287</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-322</x:v>
+        <x:v>-456</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.851</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1189,22 +1198,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>369</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.849</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>369</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0782881002087683</x:v>
+        <x:v>0.0306235071040287</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-369</x:v>
+        <x:v>-490</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.849</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1218,22 +1227,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>570</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>570</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.120932837720862</x:v>
+        <x:v>0.0358107542257315</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-570</x:v>
+        <x:v>-573</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1247,22 +1256,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1124</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1124</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.238471069470611</x:v>
+        <x:v>0.050435041291737</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-1124</x:v>
+        <x:v>-807</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1276,22 +1285,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1175</x:v>
+        <x:v>911</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1175</x:v>
+        <x:v>911</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.24929137600353</x:v>
+        <x:v>0.0569347244321839</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1175</x:v>
+        <x:v>-911</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1305,22 +1314,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1306</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1306</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.277084712392009</x:v>
+        <x:v>0.0586221421705692</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1306</x:v>
+        <x:v>-938</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1334,22 +1343,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1310</x:v>
+        <x:v>1034</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1310</x:v>
+        <x:v>1034</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.277933363884787</x:v>
+        <x:v>0.0646218496848279</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1310</x:v>
+        <x:v>-1034</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1363,22 +1372,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>2059</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>2059</x:v>
+        <x:v>1296</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.436843355907463</x:v>
+        <x:v>0.0809960514424922</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-2059</x:v>
+        <x:v>-1296</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1392,22 +1401,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>2065</x:v>
+        <x:v>1863</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>2065</x:v>
+        <x:v>1863</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.43811633314663</x:v>
+        <x:v>0.116431823948583</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-2065</x:v>
+        <x:v>-1863</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1421,22 +1430,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>2295</x:v>
+        <x:v>2102</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>2295</x:v>
+        <x:v>2102</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.486913793981364</x:v>
+        <x:v>0.131368595780956</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-2295</x:v>
+        <x:v>-2102</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1450,22 +1459,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>3159</x:v>
+        <x:v>2258</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>3159</x:v>
+        <x:v>2258</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.670222516421406</x:v>
+        <x:v>0.141118120491626</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-3159</x:v>
+        <x:v>-2258</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1479,22 +1488,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>6987</x:v>
+        <x:v>4829</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>6987</x:v>
+        <x:v>4829</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>1.48238199500993</x:v>
+        <x:v>0.301797787357866</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-6987</x:v>
+        <x:v>-4829</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1508,22 +1517,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>10781</x:v>
+        <x:v>16506</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>10781</x:v>
+        <x:v>16506</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>2.28732793590984</x:v>
+        <x:v>1.03157471073285</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-10781</x:v>
+        <x:v>-16506</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1537,22 +1546,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>15834</x:v>
+        <x:v>17352</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>15834</x:v>
+        <x:v>17352</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>3.35938693416162</x:v>
+        <x:v>1.08444713320226</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-15834</x:v>
+        <x:v>-17352</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1566,22 +1575,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>17055</x:v>
+        <x:v>18895</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>17055</x:v>
+        <x:v>18895</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>3.61843780233209</x:v>
+        <x:v>1.18087993210331</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-17055</x:v>
+        <x:v>-18895</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1595,22 +1604,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>26587</x:v>
+        <x:v>26044</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>26587</x:v>
+        <x:v>26044</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>5.64077430962201</x:v>
+        <x:v>1.62767065105576</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-26587</x:v>
+        <x:v>-26044</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1624,22 +1633,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>29949</x:v>
+        <x:v>31786</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>29949</x:v>
+        <x:v>31786</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>6.3540658893019</x:v>
+        <x:v>1.98652815675236</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-29949</x:v>
+        <x:v>-31786</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1653,22 +1662,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>31407</x:v>
+        <x:v>51997</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>31407</x:v>
+        <x:v>51997</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>6.66339935841947</x:v>
+        <x:v>3.24965407936363</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-31407</x:v>
+        <x:v>-51997</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1682,22 +1691,109 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>47288</x:v>
+        <x:v>55835</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>47288</x:v>
+        <x:v>55835</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>10.0327579476212</x:v>
+        <x:v>3.48951738602743</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-47288</x:v>
+        <x:v>-55835</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>54.4500007629394</x:v>
+        <x:v>59.85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:9">
+      <x:c r="A42" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B42" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C42" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D42" s="0">
+        <x:v>68597</x:v>
+      </x:c>
+      <x:c r="E42" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="F42" s="0">
+        <x:v>68597</x:v>
+      </x:c>
+      <x:c r="G42" s="0">
+        <x:v>4.28710350370419</x:v>
+      </x:c>
+      <x:c r="H42" s="0">
+        <x:v>-68597</x:v>
+      </x:c>
+      <x:c r="I42" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:9">
+      <x:c r="A43" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B43" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C43" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D43" s="0">
+        <x:v>103061</x:v>
+      </x:c>
+      <x:c r="E43" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="F43" s="0">
+        <x:v>103061</x:v>
+      </x:c>
+      <x:c r="G43" s="0">
+        <x:v>6.44099850132306</x:v>
+      </x:c>
+      <x:c r="H43" s="0">
+        <x:v>-103061</x:v>
+      </x:c>
+      <x:c r="I43" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:9">
+      <x:c r="A44" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B44" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C44" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D44" s="0">
+        <x:v>309129</x:v>
+      </x:c>
+      <x:c r="E44" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="F44" s="0">
+        <x:v>309129</x:v>
+      </x:c>
+      <x:c r="G44" s="0">
+        <x:v>19.3196206684924</x:v>
+      </x:c>
+      <x:c r="H44" s="0">
+        <x:v>-309129</x:v>
+      </x:c>
+      <x:c r="I44" s="0">
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -43,130 +43,139 @@
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
     <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -517,7 +526,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I44"/>
+  <x:dimension ref="A1:I47"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -554,25 +563,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>349328</x:v>
+        <x:v>2171182</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>20490</x:v>
+        <x:v>79091</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>369818</x:v>
+        <x:v>2250273</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>23.1124982657095</x:v>
+        <x:v>13.8191699113212</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>328838</x:v>
+        <x:v>2092091</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>59.85</x:v>
@@ -583,25 +592,25 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>133664</x:v>
+        <x:v>1953009</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>28641</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.851</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>162305</x:v>
+        <x:v>1953565</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>10.1435680010599</x:v>
+        <x:v>11.9970539875873</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>105023</x:v>
+        <x:v>1952453</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>59.85</x:v>
@@ -612,25 +621,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>66800</x:v>
+        <x:v>747173</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>351</x:v>
+        <x:v>1076</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>59.849</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>67151</x:v>
+        <x:v>748249</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.19673290927067</x:v>
+        <x:v>4.5950780491861</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>66449</x:v>
+        <x:v>746097</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>59.85</x:v>
@@ -641,25 +650,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>33404</x:v>
+        <x:v>551711</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>56</x:v>
+        <x:v>159245</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>59.857</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>33460</x:v>
+        <x:v>710956</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.09114805653224</x:v>
+        <x:v>4.36605770209804</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>33348</x:v>
+        <x:v>392466</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>59.85</x:v>
@@ -670,25 +679,25 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>33332</x:v>
+        <x:v>317444</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>0</x:v>
+        <x:v>25819</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>33332</x:v>
+        <x:v>343263</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>2.08314844651323</x:v>
+        <x:v>2.10801521471832</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>33332</x:v>
+        <x:v>291625</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>59.85</x:v>
@@ -699,25 +708,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>33386</x:v>
+        <x:v>219274</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>121</x:v>
+        <x:v>24873</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>59.851</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>33507</x:v>
+        <x:v>244147</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>2.0940854133361</x:v>
+        <x:v>1.49933313706352</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>33265</x:v>
+        <x:v>194401</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>59.85</x:v>
@@ -728,25 +737,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>33416</x:v>
+        <x:v>185346</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>5245</x:v>
+        <x:v>3826</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>38661</x:v>
+        <x:v>189172</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>2.41619471050786</x:v>
+        <x:v>1.16172571526408</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>28171</x:v>
+        <x:v>181520</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>59.85</x:v>
@@ -757,25 +766,25 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>19199</x:v>
+        <x:v>166983</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>354</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.857</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>19553</x:v>
+        <x:v>167039</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.22200292735729</x:v>
+        <x:v>1.0258045680756</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>18845</x:v>
+        <x:v>166927</x:v>
       </x:c>
       <x:c r="I9" s="0">
         <x:v>59.85</x:v>
@@ -786,25 +795,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>16699</x:v>
+        <x:v>315862</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>27</x:v>
+        <x:v>165158</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>59.852</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>16726</x:v>
+        <x:v>481020</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.04532404045303</x:v>
+        <x:v>2.95399585327812</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>16672</x:v>
+        <x:v>150704</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>59.85</x:v>
@@ -815,25 +824,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>16708</x:v>
+        <x:v>149994</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>438</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>59.849</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>17146</x:v>
+        <x:v>149994</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>1.07157276082791</x:v>
+        <x:v>0.921129379270296</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>16270</x:v>
+        <x:v>149994</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>59.85</x:v>
@@ -844,25 +853,25 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>16700</x:v>
+        <x:v>250660</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>1088</x:v>
+        <x:v>114282</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>17788</x:v>
+        <x:v>364942</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>1.11169580482951</x:v>
+        <x:v>2.24114829879636</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>15612</x:v>
+        <x:v>136378</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>59.85</x:v>
@@ -873,25 +882,25 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>18000</x:v>
+        <x:v>76374</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>3697</x:v>
+        <x:v>1678</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>21697</x:v>
+        <x:v>78052</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>1.35599639517574</x:v>
+        <x:v>0.479325775103039</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>14303</x:v>
+        <x:v>74696</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>59.85</x:v>
@@ -902,25 +911,25 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>25917</x:v>
+        <x:v>74296</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>21032</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.849</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>46949</x:v>
+        <x:v>74781</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>2.93416945923886</x:v>
+        <x:v>0.459238210269824</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>4885</x:v>
+        <x:v>73811</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>59.85</x:v>
@@ -931,28 +940,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>3486</x:v>
+        <x:v>33417</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>59.851</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>579</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>4065</x:v>
+        <x:v>33884</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.254050115056891</x:v>
+        <x:v>0.208085309327005</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>2907</x:v>
+        <x:v>32950</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>59.851</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -960,28 +969,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>0</x:v>
+        <x:v>16699</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>31</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>59.839</x:v>
+        <x:v>59.852</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>31</x:v>
+        <x:v>16753</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.00193740555147937</x:v>
+        <x:v>0.102881985218844</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>-31</x:v>
+        <x:v>16645</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>59.839</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -989,28 +998,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>0</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>31</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>59.839</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>31</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.00193740555147937</x:v>
+        <x:v>0.0982577307647289</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>-31</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>59.839</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1018,28 +1027,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>0</x:v>
+        <x:v>20754</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>81</x:v>
+        <x:v>5688</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>59.852</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>81</x:v>
+        <x:v>26442</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.00506225321515576</x:v>
+        <x:v>0.16238318230506</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>-81</x:v>
+        <x:v>15066</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>59.852</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1047,28 +1056,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>0</x:v>
+        <x:v>55000</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>163</x:v>
+        <x:v>44104</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>59.853</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>163</x:v>
+        <x:v>99104</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0101870033835851</x:v>
+        <x:v>0.608608384356731</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-163</x:v>
+        <x:v>10896</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>59.853</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1076,28 +1085,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>0</x:v>
+        <x:v>3639</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>263</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>59.852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>263</x:v>
+        <x:v>3639</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0164366987109378</x:v>
+        <x:v>0.022347492640803</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-263</x:v>
+        <x:v>3639</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>59.852</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1111,22 +1120,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>292</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>59.849</x:v>
+        <x:v>59.852</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>292</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0182491103558702</x:v>
+        <x:v>0.00016580992066548</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-292</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>59.849</x:v>
+        <x:v>59.852</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1140,22 +1149,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>300</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.839</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>300</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0187490859820584</x:v>
+        <x:v>0.000190374353356662</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-300</x:v>
+        <x:v>-31</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.839</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1169,22 +1178,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>456</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>59.851</x:v>
+        <x:v>59.845</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>456</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0284986106927287</x:v>
+        <x:v>0.000356184274022142</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-456</x:v>
+        <x:v>-58</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>59.851</x:v>
+        <x:v>59.845</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1198,22 +1207,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>490</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>59.849</x:v>
+        <x:v>59.852</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>490</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0306235071040287</x:v>
+        <x:v>0.00161511144944523</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-490</x:v>
+        <x:v>-263</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>59.849</x:v>
+        <x:v>59.852</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1227,19 +1236,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>573</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>573</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0358107542257315</x:v>
+        <x:v>0.00167652253117319</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-573</x:v>
+        <x:v>-273</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>59.85</x:v>
@@ -1256,19 +1265,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>807</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>807</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.050435041291737</x:v>
+        <x:v>0.00404084917769947</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-807</x:v>
+        <x:v>-658</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>59.85</x:v>
@@ -1285,19 +1294,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>911</x:v>
+        <x:v>896</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>911</x:v>
+        <x:v>896</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0569347244321839</x:v>
+        <x:v>0.00550243292282482</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-911</x:v>
+        <x:v>-896</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>59.85</x:v>
@@ -1314,19 +1323,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>938</x:v>
+        <x:v>1489</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>938</x:v>
+        <x:v>1489</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0586221421705692</x:v>
+        <x:v>0.00914411006929258</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-938</x:v>
+        <x:v>-1489</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>59.85</x:v>
@@ -1343,19 +1352,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1034</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1034</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0646218496848279</x:v>
+        <x:v>0.0116681055283116</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1034</x:v>
+        <x:v>-1900</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>59.85</x:v>
@@ -1372,19 +1381,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1296</x:v>
+        <x:v>2787</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1296</x:v>
+        <x:v>2787</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0809960514424922</x:v>
+        <x:v>0.0171152684775812</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-1296</x:v>
+        <x:v>-2787</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>59.85</x:v>
@@ -1401,19 +1410,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>1863</x:v>
+        <x:v>3060</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>1863</x:v>
+        <x:v>3060</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.116431823948583</x:v>
+        <x:v>0.0187917910087544</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-1863</x:v>
+        <x:v>-3060</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>59.85</x:v>
@@ -1430,19 +1439,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>2102</x:v>
+        <x:v>3131</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>2102</x:v>
+        <x:v>3131</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.131368595780956</x:v>
+        <x:v>0.0192278096890229</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-2102</x:v>
+        <x:v>-3131</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>59.85</x:v>
@@ -1453,25 +1462,25 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>0</x:v>
+        <x:v>47512</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>2258</x:v>
+        <x:v>50647</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>2258</x:v>
+        <x:v>98159</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.141118120491626</x:v>
+        <x:v>0.602805037133439</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-2258</x:v>
+        <x:v>-3135</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>59.85</x:v>
@@ -1488,19 +1497,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>4829</x:v>
+        <x:v>7260</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>4829</x:v>
+        <x:v>7260</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.301797787357866</x:v>
+        <x:v>0.0445844453344957</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-4829</x:v>
+        <x:v>-7260</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>59.85</x:v>
@@ -1511,25 +1520,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>0</x:v>
+        <x:v>250496</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>16506</x:v>
+        <x:v>260525</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>16506</x:v>
+        <x:v>511021</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>1.03157471073285</x:v>
+        <x:v>3.13823523957016</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-16506</x:v>
+        <x:v>-10029</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>59.85</x:v>
@@ -1540,25 +1549,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>0</x:v>
+        <x:v>3325</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>17352</x:v>
+        <x:v>25371</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>17352</x:v>
+        <x:v>28696</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>1.08444713320226</x:v>
+        <x:v>0.176225240126541</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-17352</x:v>
+        <x:v>-22046</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>59.85</x:v>
@@ -1569,25 +1578,25 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>0</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0</x:v>
+        <x:v>59.849</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>18895</x:v>
+        <x:v>38247</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>18895</x:v>
+        <x:v>38413</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>1.18087993210331</x:v>
+        <x:v>0.235898388241596</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-18895</x:v>
+        <x:v>-38081</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>59.85</x:v>
@@ -1604,19 +1613,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>26044</x:v>
+        <x:v>78396</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>26044</x:v>
+        <x:v>78396</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>1.62767065105576</x:v>
+        <x:v>0.48143831631448</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-26044</x:v>
+        <x:v>-78396</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>59.85</x:v>
@@ -1627,25 +1636,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>0</x:v>
+        <x:v>12900</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>31786</x:v>
+        <x:v>106169</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>31786</x:v>
+        <x:v>119069</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>1.98652815675236</x:v>
+        <x:v>0.731215609026594</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-31786</x:v>
+        <x:v>-93269</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>59.85</x:v>
@@ -1656,25 +1665,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>0</x:v>
+        <x:v>9015</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>51997</x:v>
+        <x:v>106397</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>51997</x:v>
+        <x:v>115412</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>3.24965407936363</x:v>
+        <x:v>0.708757576438681</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-51997</x:v>
+        <x:v>-97382</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>59.85</x:v>
@@ -1685,25 +1694,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>55835</x:v>
+        <x:v>117918</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>55835</x:v>
+        <x:v>117919</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>3.48951738602743</x:v>
+        <x:v>0.724153334627879</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-55835</x:v>
+        <x:v>-117917</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>59.85</x:v>
@@ -1714,25 +1723,25 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>0</x:v>
+        <x:v>100114</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>68597</x:v>
+        <x:v>310227</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>68597</x:v>
+        <x:v>410341</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>4.28710350370419</x:v>
+        <x:v>2.5199484687331</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-68597</x:v>
+        <x:v>-210113</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>59.85</x:v>
@@ -1743,25 +1752,25 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>0</x:v>
+        <x:v>32290</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>103061</x:v>
+        <x:v>540822</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>103061</x:v>
+        <x:v>573112</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>6.44099850132306</x:v>
+        <x:v>3.51954278712721</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-103061</x:v>
+        <x:v>-508532</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>59.85</x:v>
@@ -1778,21 +1787,108 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>309129</x:v>
+        <x:v>520346</x:v>
       </x:c>
       <x:c r="E44" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>309129</x:v>
+        <x:v>520346</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>19.3196206684924</x:v>
+        <x:v>3.19550107328148</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-309129</x:v>
+        <x:v>-520346</x:v>
       </x:c>
       <x:c r="I44" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:9">
+      <x:c r="A45" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B45" s="0">
+        <x:v>116907</x:v>
+      </x:c>
+      <x:c r="C45" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="D45" s="0">
+        <x:v>1040994</x:v>
+      </x:c>
+      <x:c r="E45" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="F45" s="0">
+        <x:v>1157901</x:v>
+      </x:c>
+      <x:c r="G45" s="0">
+        <x:v>7.11079529438814</x:v>
+      </x:c>
+      <x:c r="H45" s="0">
+        <x:v>-924087</x:v>
+      </x:c>
+      <x:c r="I45" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:9">
+      <x:c r="A46" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B46" s="0">
+        <x:v>161090</x:v>
+      </x:c>
+      <x:c r="C46" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="D46" s="0">
+        <x:v>1826254</x:v>
+      </x:c>
+      <x:c r="E46" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="F46" s="0">
+        <x:v>1987344</x:v>
+      </x:c>
+      <x:c r="G46" s="0">
+        <x:v>12.2044944805562</x:v>
+      </x:c>
+      <x:c r="H46" s="0">
+        <x:v>-1665164</x:v>
+      </x:c>
+      <x:c r="I46" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:9">
+      <x:c r="A47" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B47" s="0">
+        <x:v>83220</x:v>
+      </x:c>
+      <x:c r="C47" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="D47" s="0">
+        <x:v>2471249</x:v>
+      </x:c>
+      <x:c r="E47" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="F47" s="0">
+        <x:v>2554469</x:v>
+      </x:c>
+      <x:c r="G47" s="0">
+        <x:v>15.6872704530529</x:v>
+      </x:c>
+      <x:c r="H47" s="0">
+        <x:v>-2388029</x:v>
+      </x:c>
+      <x:c r="I47" s="0">
         <x:v>59.85</x:v>
       </x:c>
     </x:row>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -40,139 +40,145 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
+    <x:t>TERA</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
     <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>MARBAS</x:t>
@@ -526,7 +532,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I47"/>
+  <x:dimension ref="A1:I49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -563,25 +569,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>2171182</x:v>
+        <x:v>3567849</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>79091</x:v>
+        <x:v>522528</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2250273</x:v>
+        <x:v>4090377</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>13.8191699113212</x:v>
+        <x:v>12.1289937480652</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>2092091</x:v>
+        <x:v>3045321</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>59.85</x:v>
@@ -592,25 +598,25 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1953009</x:v>
+        <x:v>4057204</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>556</x:v>
+        <x:v>1040692</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>59.851</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1953565</x:v>
+        <x:v>5097896</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>11.9970539875873</x:v>
+        <x:v>15.1165402876768</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>1952453</x:v>
+        <x:v>3016512</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>59.85</x:v>
@@ -621,25 +627,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>747173</x:v>
+        <x:v>2316548</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>1076</x:v>
+        <x:v>186766</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>748249</x:v>
+        <x:v>2503314</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.5950780491861</x:v>
+        <x:v>7.42295388797757</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>746097</x:v>
+        <x:v>2129782</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>59.85</x:v>
@@ -650,25 +656,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>551711</x:v>
+        <x:v>904357</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>159245</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.852</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>710956</x:v>
+        <x:v>904384</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>4.36605770209804</x:v>
+        <x:v>2.68172539642438</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>392466</x:v>
+        <x:v>904330</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>59.85</x:v>
@@ -679,25 +685,25 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>317444</x:v>
+        <x:v>903652</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>25819</x:v>
+        <x:v>411775</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>343263</x:v>
+        <x:v>1315427</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>2.10801521471832</x:v>
+        <x:v>3.90057098869765</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>291625</x:v>
+        <x:v>491877</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>59.85</x:v>
@@ -708,25 +714,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>219274</x:v>
+        <x:v>391273</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>24873</x:v>
+        <x:v>207635</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>244147</x:v>
+        <x:v>598908</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.49933313706352</x:v>
+        <x:v>1.77591243732942</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>194401</x:v>
+        <x:v>183638</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>59.85</x:v>
@@ -737,25 +743,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>185346</x:v>
+        <x:v>167070</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>3826</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.845</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>189172</x:v>
+        <x:v>167154</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>1.16172571526408</x:v>
+        <x:v>0.495653535349941</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>181520</x:v>
+        <x:v>166986</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>59.85</x:v>
@@ -766,25 +772,25 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>166983</x:v>
+        <x:v>315862</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>56</x:v>
+        <x:v>167454</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>59.857</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>167039</x:v>
+        <x:v>483316</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.0258045680756</x:v>
+        <x:v>1.43315316469359</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>166927</x:v>
+        <x:v>148408</x:v>
       </x:c>
       <x:c r="I9" s="0">
         <x:v>59.85</x:v>
@@ -795,25 +801,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>315862</x:v>
+        <x:v>269274</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>165158</x:v>
+        <x:v>152929</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>481020</x:v>
+        <x:v>422203</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>2.95399585327812</x:v>
+        <x:v>1.25193779141002</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>150704</x:v>
+        <x:v>116345</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>59.85</x:v>
@@ -824,25 +830,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>149994</x:v>
+        <x:v>155000</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>0</x:v>
+        <x:v>52555</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>149994</x:v>
+        <x:v>207555</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.921129379270296</x:v>
+        <x:v>0.615452633676472</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>149994</x:v>
+        <x:v>102445</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>59.85</x:v>
@@ -853,25 +859,25 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>250660</x:v>
+        <x:v>141100</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>114282</x:v>
+        <x:v>58309</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>364942</x:v>
+        <x:v>199409</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>2.24114829879636</x:v>
+        <x:v>0.591297700507295</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>136378</x:v>
+        <x:v>82791</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>59.85</x:v>
@@ -888,19 +894,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>1678</x:v>
+        <x:v>7823</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>78052</x:v>
+        <x:v>84197</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.479325775103039</x:v>
+        <x:v>0.249665223182568</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>74696</x:v>
+        <x:v>68551</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>59.85</x:v>
@@ -911,25 +917,25 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>74296</x:v>
+        <x:v>188746</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>485</x:v>
+        <x:v>130775</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>59.849</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>74781</x:v>
+        <x:v>319521</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.459238210269824</x:v>
+        <x:v>0.94745990684368</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>73811</x:v>
+        <x:v>57971</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>59.85</x:v>
@@ -940,25 +946,25 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>33417</x:v>
+        <x:v>93198</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>467</x:v>
+        <x:v>62800</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>33884</x:v>
+        <x:v>155998</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.208085309327005</x:v>
+        <x:v>0.46257319721646</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>32950</x:v>
+        <x:v>30398</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>59.85</x:v>
@@ -969,25 +975,25 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>16699</x:v>
+        <x:v>20347</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>54</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>59.852</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>16753</x:v>
+        <x:v>20347</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.102881985218844</x:v>
+        <x:v>0.0603339584082059</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>16645</x:v>
+        <x:v>20347</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>59.85</x:v>
@@ -998,25 +1004,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>16000</x:v>
+        <x:v>25000</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>0</x:v>
+        <x:v>5317</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>16000</x:v>
+        <x:v>30317</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0982577307647289</x:v>
+        <x:v>0.0898975090707023</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>16000</x:v>
+        <x:v>19683</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>59.85</x:v>
@@ -1027,25 +1033,25 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>20754</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>5688</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.849</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>26442</x:v>
+        <x:v>20464</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.16238318230506</x:v>
+        <x:v>0.0606808927539945</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>15066</x:v>
+        <x:v>19536</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>59.85</x:v>
@@ -1056,25 +1062,25 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>55000</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>44104</x:v>
+        <x:v>6000</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>99104</x:v>
+        <x:v>22000</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.608608384356731</x:v>
+        <x:v>0.0652355180115265</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>10896</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>59.85</x:v>
@@ -1085,7 +1091,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>3639</x:v>
+        <x:v>2860</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>59.85</x:v>
@@ -1097,13 +1103,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>3639</x:v>
+        <x:v>2860</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.022347492640803</x:v>
+        <x:v>0.00848061734149845</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>3639</x:v>
+        <x:v>2860</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>59.85</x:v>
@@ -1129,7 +1135,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.00016580992066548</x:v>
+        <x:v>8.00617721050553E-05</x:v>
       </x:c>
       <x:c r="H21" s="0">
         <x:v>-27</x:v>
@@ -1149,22 +1155,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>59.839</x:v>
+        <x:v>59.852</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.000190374353356662</x:v>
+        <x:v>8.00617721050553E-05</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-31</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>59.839</x:v>
+        <x:v>59.852</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1178,22 +1184,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>58</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>59.845</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>58</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.000356184274022142</x:v>
+        <x:v>0.00037658685397563</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-58</x:v>
+        <x:v>-127</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>59.845</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1207,22 +1213,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>263</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>59.852</x:v>
+        <x:v>59.848</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>263</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.00161511144944523</x:v>
+        <x:v>0.000859922737424668</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-263</x:v>
+        <x:v>-290</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>59.852</x:v>
+        <x:v>59.848</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1230,25 +1236,25 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>0</x:v>
+        <x:v>33417</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>273</x:v>
+        <x:v>33964</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>273</x:v>
+        <x:v>67381</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.00167652253117319</x:v>
+        <x:v>0.199801565415212</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-273</x:v>
+        <x:v>-547</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>59.85</x:v>
@@ -1265,19 +1271,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>658</x:v>
+        <x:v>978</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>658</x:v>
+        <x:v>978</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00404084917769947</x:v>
+        <x:v>0.00290001530069422</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-658</x:v>
+        <x:v>-978</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>59.85</x:v>
@@ -1294,19 +1300,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>896</x:v>
+        <x:v>1123</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>896</x:v>
+        <x:v>1123</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00550243292282482</x:v>
+        <x:v>0.00332997666940656</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-896</x:v>
+        <x:v>-1123</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>59.85</x:v>
@@ -1317,25 +1323,25 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>0</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0</x:v>
+        <x:v>59.848</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1489</x:v>
+        <x:v>1720</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1489</x:v>
+        <x:v>1970</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00914411006929258</x:v>
+        <x:v>0.00584154411285033</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1489</x:v>
+        <x:v>-1470</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>59.85</x:v>
@@ -1346,25 +1352,25 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>0</x:v>
+        <x:v>16699</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1900</x:v>
+        <x:v>18229</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1900</x:v>
+        <x:v>34928</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0116681055283116</x:v>
+        <x:v>0.103570280595754</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1900</x:v>
+        <x:v>-1530</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>59.85</x:v>
@@ -1381,19 +1387,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>2787</x:v>
+        <x:v>2329</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>2787</x:v>
+        <x:v>2329</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0171152684775812</x:v>
+        <x:v>0.00690606915676569</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-2787</x:v>
+        <x:v>-2329</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>59.85</x:v>
@@ -1404,25 +1410,25 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>0</x:v>
+        <x:v>1340</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>3060</x:v>
+        <x:v>3967</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>3060</x:v>
+        <x:v>5307</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0187917910087544</x:v>
+        <x:v>0.0157365860948714</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-3060</x:v>
+        <x:v>-2627</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>59.85</x:v>
@@ -1433,25 +1439,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>3131</x:v>
+        <x:v>3378</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>3131</x:v>
+        <x:v>3379</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0192278096890229</x:v>
+        <x:v>0.0100195825164067</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-3131</x:v>
+        <x:v>-3377</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>59.85</x:v>
@@ -1462,25 +1468,25 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>47512</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>59.85</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>50647</x:v>
+        <x:v>3680</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>98159</x:v>
+        <x:v>3680</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.602805037133439</x:v>
+        <x:v>0.0109121230128372</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-3135</x:v>
+        <x:v>-3680</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>59.85</x:v>
@@ -1491,25 +1497,25 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>0</x:v>
+        <x:v>21126</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>7260</x:v>
+        <x:v>25375</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>7260</x:v>
+        <x:v>46501</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0445844453344957</x:v>
+        <x:v>0.137887128320636</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-7260</x:v>
+        <x:v>-4249</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>59.85</x:v>
@@ -1520,25 +1526,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>250496</x:v>
+        <x:v>250596</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>260525</x:v>
+        <x:v>260775</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>511021</x:v>
+        <x:v>511371</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>3.13823523957016</x:v>
+        <x:v>1.51634327641238</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-10029</x:v>
+        <x:v>-10179</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>59.85</x:v>
@@ -1549,25 +1555,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>3325</x:v>
+        <x:v>15306</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>25371</x:v>
+        <x:v>32177</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>28696</x:v>
+        <x:v>47483</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.176225240126541</x:v>
+        <x:v>0.140799004624605</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-22046</x:v>
+        <x:v>-16871</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>59.85</x:v>
@@ -1578,25 +1584,25 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>166</x:v>
+        <x:v>222846</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>59.849</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>38247</x:v>
+        <x:v>244669</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>38413</x:v>
+        <x:v>467515</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.235898388241596</x:v>
+        <x:v>1.38629923650722</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-38081</x:v>
+        <x:v>-21823</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>59.85</x:v>
@@ -1607,25 +1613,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>0</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>0</x:v>
+        <x:v>59.849</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>78396</x:v>
+        <x:v>26101</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>78396</x:v>
+        <x:v>26903</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.48143831631448</x:v>
+        <x:v>0.0797741427756408</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-78396</x:v>
+        <x:v>-25299</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>59.85</x:v>
@@ -1636,25 +1642,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>12900</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="C39" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>106169</x:v>
+        <x:v>44426</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>119069</x:v>
+        <x:v>45092</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.731215609026594</x:v>
+        <x:v>0.13370908991708</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-93269</x:v>
+        <x:v>-43760</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>59.85</x:v>
@@ -1665,25 +1671,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>9015</x:v>
+        <x:v>38386</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>106397</x:v>
+        <x:v>110140</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>115412</x:v>
+        <x:v>148526</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.708757576438681</x:v>
+        <x:v>0.44041684309909</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-97382</x:v>
+        <x:v>-71754</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>59.85</x:v>
@@ -1694,25 +1700,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>1</x:v>
+        <x:v>12900</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>59</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>117918</x:v>
+        <x:v>107305</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>117919</x:v>
+        <x:v>120205</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.724153334627879</x:v>
+        <x:v>0.356437974662525</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-117917</x:v>
+        <x:v>-94405</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>59.85</x:v>
@@ -1723,25 +1729,25 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>100114</x:v>
+        <x:v>10001</x:v>
       </x:c>
       <x:c r="C42" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>310227</x:v>
+        <x:v>159639</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>410341</x:v>
+        <x:v>169640</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>2.5199484687331</x:v>
+        <x:v>0.503025148885244</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-210113</x:v>
+        <x:v>-149638</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>59.85</x:v>
@@ -1752,25 +1758,25 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>32290</x:v>
+        <x:v>100114</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>540822</x:v>
+        <x:v>317033</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>573112</x:v>
+        <x:v>417147</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>3.51954278712721</x:v>
+        <x:v>1.23694548327065</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-508532</x:v>
+        <x:v>-216919</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>59.85</x:v>
@@ -1781,25 +1787,25 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>0</x:v>
+        <x:v>1670</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>520346</x:v>
+        <x:v>520541</x:v>
       </x:c>
       <x:c r="E44" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>520346</x:v>
+        <x:v>522211</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>3.19550107328148</x:v>
+        <x:v>1.54848659528715</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-520346</x:v>
+        <x:v>-518871</x:v>
       </x:c>
       <x:c r="I44" s="0">
         <x:v>59.85</x:v>
@@ -1810,25 +1816,25 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>116907</x:v>
+        <x:v>118207</x:v>
       </x:c>
       <x:c r="C45" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>1040994</x:v>
+        <x:v>1041721</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>1157901</x:v>
+        <x:v>1159928</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>7.11079529438814</x:v>
+        <x:v>3.43947745163972</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-924087</x:v>
+        <x:v>-923514</x:v>
       </x:c>
       <x:c r="I45" s="0">
         <x:v>59.85</x:v>
@@ -1839,25 +1845,25 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>161090</x:v>
+        <x:v>161290</x:v>
       </x:c>
       <x:c r="C46" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>1826254</x:v>
+        <x:v>2023282</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>1987344</x:v>
+        <x:v>2184572</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>12.2044944805562</x:v>
+        <x:v>6.47780391152166</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-1665164</x:v>
+        <x:v>-1861992</x:v>
       </x:c>
       <x:c r="I46" s="0">
         <x:v>59.85</x:v>
@@ -1868,27 +1874,85 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>83220</x:v>
+        <x:v>32790</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>2471249</x:v>
+        <x:v>1895260</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>2554469</x:v>
+        <x:v>1928050</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>15.6872704530529</x:v>
+        <x:v>5.71715184100562</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-2388029</x:v>
+        <x:v>-1862470</x:v>
       </x:c>
       <x:c r="I47" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:9">
+      <x:c r="A48" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B48" s="0">
+        <x:v>2103639</x:v>
+      </x:c>
+      <x:c r="C48" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="D48" s="0">
+        <x:v>4380175</x:v>
+      </x:c>
+      <x:c r="E48" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="F48" s="0">
+        <x:v>6483814</x:v>
+      </x:c>
+      <x:c r="G48" s="0">
+        <x:v>19.2261347718358</x:v>
+      </x:c>
+      <x:c r="H48" s="0">
+        <x:v>-2276536</x:v>
+      </x:c>
+      <x:c r="I48" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:9">
+      <x:c r="A49" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B49" s="0">
+        <x:v>88220</x:v>
+      </x:c>
+      <x:c r="C49" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="D49" s="0">
+        <x:v>2589589</x:v>
+      </x:c>
+      <x:c r="E49" s="0">
+        <x:v>59.85</x:v>
+      </x:c>
+      <x:c r="F49" s="0">
+        <x:v>2677809</x:v>
+      </x:c>
+      <x:c r="G49" s="0">
+        <x:v>7.94037532958763</x:v>
+      </x:c>
+      <x:c r="H49" s="0">
+        <x:v>-2501369</x:v>
+      </x:c>
+      <x:c r="I49" s="0">
         <x:v>59.85</x:v>
       </x:c>
     </x:row>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -55,48 +55,51 @@
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
     <x:t>IKON</x:t>
   </x:si>
   <x:si>
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>DESTEK</x:t>
   </x:si>
   <x:si>
@@ -106,58 +109,55 @@
     <x:t>BIZIM</x:t>
   </x:si>
   <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
     <x:t>DINAMIK</x:t>
   </x:si>
   <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
   </x:si>
   <x:si>
     <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
     <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
     <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
   </x:si>
   <x:si>
     <x:t>IS</x:t>
@@ -569,28 +569,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>3567849</x:v>
+        <x:v>3635734</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>522528</x:v>
+        <x:v>522881</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>4090377</x:v>
+        <x:v>4158615</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>12.1289937480652</x:v>
+        <x:v>11.9940384773458</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>3045321</x:v>
+        <x:v>3112853</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -601,25 +601,25 @@
         <x:v>4057204</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1040692</x:v>
+        <x:v>1040962</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>5097896</x:v>
+        <x:v>5098166</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>15.1165402876768</x:v>
+        <x:v>14.7038374958721</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>3016512</x:v>
+        <x:v>3016242</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -627,28 +627,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>2316548</x:v>
+        <x:v>2317678</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>186766</x:v>
+        <x:v>239526</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>2503314</x:v>
+        <x:v>2557204</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.42295388797757</x:v>
+        <x:v>7.37534086959782</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>2129782</x:v>
+        <x:v>2078152</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -659,25 +659,25 @@
         <x:v>904357</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>27</x:v>
+        <x:v>1369</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>59.852</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>904384</x:v>
+        <x:v>905726</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.68172539642438</x:v>
+        <x:v>2.61224289671741</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>904330</x:v>
+        <x:v>902988</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -685,28 +685,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>903652</x:v>
+        <x:v>907492</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>411775</x:v>
+        <x:v>420733</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1315427</x:v>
+        <x:v>1328225</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>3.90057098869765</x:v>
+        <x:v>3.83079024063843</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>491877</x:v>
+        <x:v>486759</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -714,28 +714,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>391273</x:v>
+        <x:v>167070</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>207635</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>598908</x:v>
+        <x:v>167154</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.77591243732942</x:v>
+        <x:v>0.48209596407512</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>183638</x:v>
+        <x:v>166986</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -743,28 +743,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>167070</x:v>
+        <x:v>315862</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>84</x:v>
+        <x:v>167826</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>59.845</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>167154</x:v>
+        <x:v>483688</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.495653535349941</x:v>
+        <x:v>1.39502514251269</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>166986</x:v>
+        <x:v>148036</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -772,28 +772,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>315862</x:v>
+        <x:v>269815</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>167454</x:v>
+        <x:v>155296</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>483316</x:v>
+        <x:v>425111</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.43315316469359</x:v>
+        <x:v>1.22608072426588</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>148408</x:v>
+        <x:v>114519</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -801,28 +801,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>269274</x:v>
+        <x:v>391273</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>152929</x:v>
+        <x:v>277352</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>422203</x:v>
+        <x:v>668625</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.25193779141002</x:v>
+        <x:v>1.92840981358345</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>116345</x:v>
+        <x:v>113921</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -830,28 +830,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>155000</x:v>
+        <x:v>157815</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>52555</x:v>
+        <x:v>68594</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>207555</x:v>
+        <x:v>226409</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.615452633676472</x:v>
+        <x:v>0.652995830971942</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>102445</x:v>
+        <x:v>89221</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -859,28 +859,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>141100</x:v>
+        <x:v>97409</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>58309</x:v>
+        <x:v>8204</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>199409</x:v>
+        <x:v>105613</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.591297700507295</x:v>
+        <x:v>0.304602947305274</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>82791</x:v>
+        <x:v>89205</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -888,28 +888,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>76374</x:v>
+        <x:v>141100</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>7823</x:v>
+        <x:v>58554</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>84197</x:v>
+        <x:v>199654</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.249665223182568</x:v>
+        <x:v>0.575830597003088</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>68551</x:v>
+        <x:v>82546</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -917,28 +917,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>188746</x:v>
+        <x:v>137556</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>130775</x:v>
+        <x:v>90042</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>319521</x:v>
+        <x:v>227598</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.94745990684368</x:v>
+        <x:v>0.656425076465829</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>57971</x:v>
+        <x:v>47514</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -946,28 +946,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>93198</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>62800</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>155998</x:v>
+        <x:v>24597</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.46257319721646</x:v>
+        <x:v>0.0709412543424371</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>30398</x:v>
+        <x:v>23403</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -978,7 +978,7 @@
         <x:v>20347</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D16" s="0">
         <x:v>0</x:v>
@@ -990,13 +990,13 @@
         <x:v>20347</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0603339584082059</x:v>
+        <x:v>0.0586836484980107</x:v>
       </x:c>
       <x:c r="H16" s="0">
         <x:v>20347</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1004,28 +1004,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>25000</x:v>
+        <x:v>25501</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>5317</x:v>
+        <x:v>7997</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>30317</x:v>
+        <x:v>33498</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0898975090707023</x:v>
+        <x:v>0.0966130071944936</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>19683</x:v>
+        <x:v>17504</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1033,28 +1033,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>20000</x:v>
+        <x:v>197476</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>464</x:v>
+        <x:v>185850</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>59.849</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>20464</x:v>
+        <x:v>383326</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0606808927539945</x:v>
+        <x:v>1.10556682774603</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>19536</x:v>
+        <x:v>11626</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1065,25 +1065,25 @@
         <x:v>16000</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>6000</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>22000</x:v>
+        <x:v>23000</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0652355180115265</x:v>
+        <x:v>0.0663352786874844</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>10000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1091,10 +1091,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>2860</x:v>
+        <x:v>4024</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D20" s="0">
         <x:v>0</x:v>
@@ -1103,16 +1103,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>2860</x:v>
+        <x:v>4024</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.00848061734149845</x:v>
+        <x:v>0.0116057896277581</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>2860</x:v>
+        <x:v>4024</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1120,28 +1120,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>0</x:v>
+        <x:v>4100</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>27</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>59.852</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>27</x:v>
+        <x:v>4472</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>8.00617721050553E-05</x:v>
+        <x:v>0.0128978854908883</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-27</x:v>
+        <x:v>3728</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>59.852</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1158,19 +1158,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>59.852</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F22" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>8.00617721050553E-05</x:v>
+        <x:v>7.78718488940034E-05</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-27</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>59.852</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1184,22 +1184,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>127</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>127</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.00037658685397563</x:v>
+        <x:v>0.000271109399853197</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-127</x:v>
+        <x:v>-94</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1213,22 +1213,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>290</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>59.848</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>290</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.000859922737424668</x:v>
+        <x:v>0.000458578665709131</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-290</x:v>
+        <x:v>-159</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>59.848</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1239,25 +1239,25 @@
         <x:v>33417</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>33964</x:v>
+        <x:v>34018</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>67381</x:v>
+        <x:v>67435</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.199801565415212</x:v>
+        <x:v>0.194492152969153</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-547</x:v>
+        <x:v>-601</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1265,28 +1265,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>0</x:v>
+        <x:v>1280</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>978</x:v>
+        <x:v>2456</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>978</x:v>
+        <x:v>3736</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00290001530069422</x:v>
+        <x:v>0.0107751565728888</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-978</x:v>
+        <x:v>-1176</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1300,22 +1300,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1123</x:v>
+        <x:v>1204</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1123</x:v>
+        <x:v>1204</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00332997666940656</x:v>
+        <x:v>0.00347250763216223</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1123</x:v>
+        <x:v>-1204</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1323,28 +1323,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>59.848</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1720</x:v>
+        <x:v>1650</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1970</x:v>
+        <x:v>1650</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00584154411285033</x:v>
+        <x:v>0.0047588352101891</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1470</x:v>
+        <x:v>-1650</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1352,28 +1352,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>16699</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>59.85</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>18229</x:v>
+        <x:v>3009</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>34928</x:v>
+        <x:v>3009</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.103570280595754</x:v>
+        <x:v>0.00867838493785394</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-1530</x:v>
+        <x:v>-3009</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1381,28 +1381,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>2329</x:v>
+        <x:v>4623</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>2329</x:v>
+        <x:v>4624</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00690606915676569</x:v>
+        <x:v>0.013336275158736</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-2329</x:v>
+        <x:v>-4622</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1410,28 +1410,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>1340</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>59.85</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>3967</x:v>
+        <x:v>5222</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>5307</x:v>
+        <x:v>5222</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0157365860948714</x:v>
+        <x:v>0.0150609924046106</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-2627</x:v>
+        <x:v>-5222</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1439,28 +1439,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>1</x:v>
+        <x:v>22381</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>59</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>3378</x:v>
+        <x:v>30759</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>3379</x:v>
+        <x:v>53140</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0100195825164067</x:v>
+        <x:v>0.153263335193605</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-3377</x:v>
+        <x:v>-8378</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1468,28 +1468,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>0</x:v>
+        <x:v>1756</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>3680</x:v>
+        <x:v>10479</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>3680</x:v>
+        <x:v>12235</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0109121230128372</x:v>
+        <x:v>0.0352874841191901</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-3680</x:v>
+        <x:v>-8723</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1497,28 +1497,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>21126</x:v>
+        <x:v>16712</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>25375</x:v>
+        <x:v>26226</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>46501</x:v>
+        <x:v>42938</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.137887128320636</x:v>
+        <x:v>0.123839312881878</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-4249</x:v>
+        <x:v>-9514</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1529,25 +1529,25 @@
         <x:v>250596</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>260775</x:v>
+        <x:v>263332</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>511371</x:v>
+        <x:v>513928</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>1.51634327641238</x:v>
+        <x:v>1.48224161327398</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-10179</x:v>
+        <x:v>-12736</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1555,28 +1555,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>15306</x:v>
+        <x:v>16931</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>32177</x:v>
+        <x:v>33825</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>47483</x:v>
+        <x:v>50756</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.140799004624605</x:v>
+        <x:v>0.14638753935052</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-16871</x:v>
+        <x:v>-16894</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1584,28 +1584,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>222846</x:v>
+        <x:v>225784</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>244669</x:v>
+        <x:v>245538</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>467515</x:v>
+        <x:v>471322</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>1.38629923650722</x:v>
+        <x:v>1.35935983571924</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-21823</x:v>
+        <x:v>-19754</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1613,28 +1613,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>802</x:v>
+        <x:v>18082</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>59.849</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>26101</x:v>
+        <x:v>43343</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>26903</x:v>
+        <x:v>61425</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.0797741427756408</x:v>
+        <x:v>0.177158456233858</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-25299</x:v>
+        <x:v>-25261</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1642,28 +1642,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>666</x:v>
+        <x:v>7027</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>44426</x:v>
+        <x:v>65809</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>45092</x:v>
+        <x:v>72836</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.13370908991708</x:v>
+        <x:v>0.210069406890505</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-43760</x:v>
+        <x:v>-58782</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1671,28 +1671,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>38386</x:v>
+        <x:v>12900</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>110140</x:v>
+        <x:v>110160</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>148526</x:v>
+        <x:v>123060</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.44041684309909</x:v>
+        <x:v>0.354922582403558</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-71754</x:v>
+        <x:v>-97260</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1700,28 +1700,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>12900</x:v>
+        <x:v>52362</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>107305</x:v>
+        <x:v>152427</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>120205</x:v>
+        <x:v>204789</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.356437974662525</x:v>
+        <x:v>0.590640669005706</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-94405</x:v>
+        <x:v>-100065</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1729,28 +1729,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>10001</x:v>
+        <x:v>20001</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>159639</x:v>
+        <x:v>208710</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>169640</x:v>
+        <x:v>228711</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.503025148885244</x:v>
+        <x:v>0.659635127125793</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-149638</x:v>
+        <x:v>-188709</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1761,25 +1761,25 @@
         <x:v>100114</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>317033</x:v>
+        <x:v>320585</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>417147</x:v>
+        <x:v>420699</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>1.23694548327065</x:v>
+        <x:v>1.21335588732809</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-216919</x:v>
+        <x:v>-220471</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1790,25 +1790,25 @@
         <x:v>1670</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>520541</x:v>
+        <x:v>520787</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>522211</x:v>
+        <x:v>522457</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>1.54848659528715</x:v>
+        <x:v>1.50684046509683</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-518871</x:v>
+        <x:v>-519117</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1819,25 +1819,25 @@
         <x:v>118207</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>1041721</x:v>
+        <x:v>1042384</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>1159928</x:v>
+        <x:v>1160591</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>3.43947745163972</x:v>
+        <x:v>3.34730988813853</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-923514</x:v>
+        <x:v>-924177</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1848,25 +1848,25 @@
         <x:v>161290</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>2023282</x:v>
+        <x:v>2023390</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>2184572</x:v>
+        <x:v>2184680</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>6.47780391152166</x:v>
+        <x:v>6.3009285496945</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-1861992</x:v>
+        <x:v>-1862100</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1874,28 +1874,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>32790</x:v>
+        <x:v>33177</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1895260</x:v>
+        <x:v>1936866</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1928050</x:v>
+        <x:v>1970043</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>5.71715184100562</x:v>
+        <x:v>5.68188484484034</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-1862470</x:v>
+        <x:v>-1903689</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1903,28 +1903,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>2103639</x:v>
+        <x:v>2362115</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>4380175</x:v>
+        <x:v>4392731</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>6483814</x:v>
+        <x:v>6754846</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>19.2261347718358</x:v>
+        <x:v>19.4819387783061</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-2276536</x:v>
+        <x:v>-2030616</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1935,25 +1935,25 @@
         <x:v>88220</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>2589589</x:v>
+        <x:v>2603462</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>2677809</x:v>
+        <x:v>2691682</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>7.94037532958763</x:v>
+        <x:v>7.76319459165589</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-2501369</x:v>
+        <x:v>-2515242</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -64,18 +64,18 @@
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
@@ -88,64 +88,67 @@
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
     <x:t>AK</x:t>
@@ -532,7 +535,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I49"/>
+  <x:dimension ref="A1:I50"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -569,25 +572,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>3635734</x:v>
+        <x:v>3862922</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>522881</x:v>
+        <x:v>523101</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>4158615</x:v>
+        <x:v>4386023</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>11.9940384773458</x:v>
+        <x:v>12.4783330218034</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>3112853</x:v>
+        <x:v>3339821</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>59.8499984741211</x:v>
@@ -604,19 +607,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1040962</x:v>
+        <x:v>1041044</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>5098166</x:v>
+        <x:v>5098248</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>14.7038374958721</x:v>
+        <x:v>14.504628993451</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>3016242</x:v>
+        <x:v>3016160</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>59.8499984741211</x:v>
@@ -633,19 +636,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>239526</x:v>
+        <x:v>245808</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>2557204</x:v>
+        <x:v>2563486</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.37534086959782</x:v>
+        <x:v>7.29317470627279</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>2078152</x:v>
+        <x:v>2071870</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>59.8499984741211</x:v>
@@ -662,19 +665,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>1369</x:v>
+        <x:v>1445</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>905726</x:v>
+        <x:v>905802</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.61224289671741</x:v>
+        <x:v>2.57702684363843</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>902988</x:v>
+        <x:v>902912</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>59.8499984741211</x:v>
@@ -691,19 +694,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>420733</x:v>
+        <x:v>427361</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1328225</x:v>
+        <x:v>1334853</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>3.83079024063843</x:v>
+        <x:v>3.79768648480715</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>486759</x:v>
+        <x:v>480131</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>59.8499984741211</x:v>
@@ -720,19 +723,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>84</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>167154</x:v>
+        <x:v>167230</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.48209596407512</x:v>
+        <x:v>0.4757730707833</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>166986</x:v>
+        <x:v>166910</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>59.8499984741211</x:v>
@@ -749,19 +752,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>167826</x:v>
+        <x:v>168289</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>483688</x:v>
+        <x:v>484151</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>1.39502514251269</x:v>
+        <x:v>1.37742036711598</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>148036</x:v>
+        <x:v>147573</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>59.8499984741211</x:v>
@@ -778,19 +781,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>155296</x:v>
+        <x:v>166210</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>425111</x:v>
+        <x:v>436025</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.22608072426588</x:v>
+        <x:v>1.24050082633671</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>114519</x:v>
+        <x:v>103605</x:v>
       </x:c>
       <x:c r="I9" s="0">
         <x:v>59.8499984741211</x:v>
@@ -801,25 +804,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>391273</x:v>
+        <x:v>97409</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>277352</x:v>
+        <x:v>8622</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>668625</x:v>
+        <x:v>106031</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.92840981358345</x:v>
+        <x:v>0.301660554136364</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>113921</x:v>
+        <x:v>88787</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>59.8499984741211</x:v>
@@ -830,25 +833,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>157815</x:v>
+        <x:v>141100</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>68594</x:v>
+        <x:v>58638</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>226409</x:v>
+        <x:v>199738</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.652995830971942</x:v>
+        <x:v>0.568259054069932</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>89221</x:v>
+        <x:v>82462</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>59.8499984741211</x:v>
@@ -859,25 +862,25 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>97409</x:v>
+        <x:v>160649</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>8204</x:v>
+        <x:v>79812</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>105613</x:v>
+        <x:v>240461</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.304602947305274</x:v>
+        <x:v>0.684116895136178</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>89205</x:v>
+        <x:v>80837</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>59.8499984741211</x:v>
@@ -888,25 +891,25 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>141100</x:v>
+        <x:v>391273</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>58554</x:v>
+        <x:v>317036</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>199654</x:v>
+        <x:v>708309</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.575830597003088</x:v>
+        <x:v>2.01515486451862</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>82546</x:v>
+        <x:v>74237</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>59.8499984741211</x:v>
@@ -923,19 +926,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>90042</x:v>
+        <x:v>110406</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>227598</x:v>
+        <x:v>247962</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.656425076465829</x:v>
+        <x:v>0.705457407029652</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>47514</x:v>
+        <x:v>27150</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>59.8499984741211</x:v>
@@ -952,19 +955,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>597</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>24597</x:v>
+        <x:v>24624</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0709412543424371</x:v>
+        <x:v>0.0700558278716019</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>23403</x:v>
+        <x:v>23376</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>59.8499984741211</x:v>
@@ -990,7 +993,7 @@
         <x:v>20347</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0586836484980107</x:v>
+        <x:v>0.0578876677105053</x:v>
       </x:c>
       <x:c r="H16" s="0">
         <x:v>20347</x:v>
@@ -1010,19 +1013,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>7997</x:v>
+        <x:v>8024</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>33498</x:v>
+        <x:v>33525</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0966130071944936</x:v>
+        <x:v>0.0953793709143702</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>17504</x:v>
+        <x:v>17477</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1033,25 +1036,25 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>197476</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>185850</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>383326</x:v>
+        <x:v>23000</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>1.10556682774603</x:v>
+        <x:v>0.0654355117384196</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>11626</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1062,25 +1065,25 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>16000</x:v>
+        <x:v>4024</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>7000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>23000</x:v>
+        <x:v>4024</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0663352786874844</x:v>
+        <x:v>0.0114483695319739</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>9000</x:v>
+        <x:v>4024</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1091,25 +1094,25 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>4024</x:v>
+        <x:v>4100</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>0</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>4024</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0116057896277581</x:v>
+        <x:v>0.0128026001227343</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>4024</x:v>
+        <x:v>3700</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1120,25 +1123,25 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>4100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>372</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>4472</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0128978854908883</x:v>
+        <x:v>7.68156007364056E-05</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>3728</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1164,7 +1167,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>7.78718488940034E-05</x:v>
+        <x:v>7.68156007364056E-05</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-27</x:v>
@@ -1184,19 +1187,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>94</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>94</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.000271109399853197</x:v>
+        <x:v>0.000344247692189077</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-94</x:v>
+        <x:v>-121</x:v>
       </x:c>
       <x:c r="I23" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1213,19 +1216,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>159</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>159</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.000458578665709131</x:v>
+        <x:v>0.000529174138406349</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-159</x:v>
+        <x:v>-186</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1251,7 +1254,7 @@
         <x:v>67435</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.194492152969153</x:v>
+        <x:v>0.191854075394797</x:v>
       </x:c>
       <x:c r="H25" s="0">
         <x:v>-601</x:v>
@@ -1265,25 +1268,25 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>1280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>2456</x:v>
+        <x:v>1360</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>3736</x:v>
+        <x:v>1360</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0107751565728888</x:v>
+        <x:v>0.00386923025931524</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-1176</x:v>
+        <x:v>-1360</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1294,25 +1297,25 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>0</x:v>
+        <x:v>1280</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1204</x:v>
+        <x:v>2758</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1204</x:v>
+        <x:v>4038</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00347250763216223</x:v>
+        <x:v>0.0114881998434669</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1204</x:v>
+        <x:v>-1478</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1329,19 +1332,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1650</x:v>
+        <x:v>2127</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1650</x:v>
+        <x:v>2127</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0047588352101891</x:v>
+        <x:v>0.00605136232467906</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1650</x:v>
+        <x:v>-2127</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1358,19 +1361,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>3009</x:v>
+        <x:v>3714</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>3009</x:v>
+        <x:v>3714</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.00867838493785394</x:v>
+        <x:v>0.01056641263463</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-3009</x:v>
+        <x:v>-3714</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1387,19 +1390,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>4623</x:v>
+        <x:v>5221</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>4624</x:v>
+        <x:v>5222</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.013336275158736</x:v>
+        <x:v>0.0148567061868707</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-4622</x:v>
+        <x:v>-5220</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1416,19 +1419,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>5222</x:v>
+        <x:v>6525</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>5222</x:v>
+        <x:v>6525</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0150609924046106</x:v>
+        <x:v>0.0185637701779647</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-5222</x:v>
+        <x:v>-6525</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1439,25 +1442,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>22381</x:v>
+        <x:v>16712</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>30759</x:v>
+        <x:v>26253</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>53140</x:v>
+        <x:v>42965</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.153263335193605</x:v>
+        <x:v>0.122236380949617</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-8378</x:v>
+        <x:v>-9541</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1468,25 +1471,25 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>1756</x:v>
+        <x:v>25431</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>10479</x:v>
+        <x:v>35517</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>12235</x:v>
+        <x:v>60948</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0352874841191901</x:v>
+        <x:v>0.173398416062313</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-8723</x:v>
+        <x:v>-10086</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1497,25 +1500,25 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>16712</x:v>
+        <x:v>1856</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>26226</x:v>
+        <x:v>12129</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>42938</x:v>
+        <x:v>13985</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.123839312881878</x:v>
+        <x:v>0.0397876361592086</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-9514</x:v>
+        <x:v>-10273</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1526,25 +1529,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>250596</x:v>
+        <x:v>22381</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>263332</x:v>
+        <x:v>33959</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>513928</x:v>
+        <x:v>56340</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>1.48224161327398</x:v>
+        <x:v>0.160288553536633</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-12736</x:v>
+        <x:v>-11578</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1555,25 +1558,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>16931</x:v>
+        <x:v>250596</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>33825</x:v>
+        <x:v>263389</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>50756</x:v>
+        <x:v>513985</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.14638753935052</x:v>
+        <x:v>1.46229876090746</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-16894</x:v>
+        <x:v>-12793</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1590,19 +1593,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>245538</x:v>
+        <x:v>245931</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>471322</x:v>
+        <x:v>471715</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>1.35935983571924</x:v>
+        <x:v>1.34203967042124</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-19754</x:v>
+        <x:v>-20147</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1613,25 +1616,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>18082</x:v>
+        <x:v>197560</x:v>
       </x:c>
       <x:c r="C38" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>43343</x:v>
+        <x:v>227768</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>61425</x:v>
+        <x:v>425328</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.177158456233858</x:v>
+        <x:v>1.21006762333385</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-25261</x:v>
+        <x:v>-30208</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1642,25 +1645,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>7027</x:v>
+        <x:v>18082</x:v>
       </x:c>
       <x:c r="C39" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>65809</x:v>
+        <x:v>54864</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>72836</x:v>
+        <x:v>72946</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.210069406890505</x:v>
+        <x:v>0.207532993011772</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-58782</x:v>
+        <x:v>-36782</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1671,25 +1674,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>12900</x:v>
+        <x:v>7040</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>110160</x:v>
+        <x:v>77584</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>123060</x:v>
+        <x:v>84624</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.354922582403558</x:v>
+        <x:v>0.240757162841392</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-97260</x:v>
+        <x:v>-70544</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1700,25 +1703,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>52362</x:v>
+        <x:v>12900</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>152427</x:v>
+        <x:v>112271</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>204789</x:v>
+        <x:v>125171</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.590640669005706</x:v>
+        <x:v>0.356114279991727</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-100065</x:v>
+        <x:v>-99371</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1729,25 +1732,25 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>20001</x:v>
+        <x:v>52362</x:v>
       </x:c>
       <x:c r="C42" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>208710</x:v>
+        <x:v>182933</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>228711</x:v>
+        <x:v>235295</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.659635127125793</x:v>
+        <x:v>0.66941951019528</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-188709</x:v>
+        <x:v>-130571</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1758,25 +1761,25 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>100114</x:v>
+        <x:v>20001</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>320585</x:v>
+        <x:v>233154</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>420699</x:v>
+        <x:v>253155</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>1.21335588732809</x:v>
+        <x:v>0.720231607571287</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-220471</x:v>
+        <x:v>-213153</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1787,25 +1790,25 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>1670</x:v>
+        <x:v>100114</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>520787</x:v>
+        <x:v>321463</x:v>
       </x:c>
       <x:c r="E44" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>522457</x:v>
+        <x:v>421577</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>1.50684046509683</x:v>
+        <x:v>1.19939594487599</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-519117</x:v>
+        <x:v>-221349</x:v>
       </x:c>
       <x:c r="I44" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1816,25 +1819,25 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>118207</x:v>
+        <x:v>1670</x:v>
       </x:c>
       <x:c r="C45" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>1042384</x:v>
+        <x:v>520868</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>1160591</x:v>
+        <x:v>522538</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>3.34730988813853</x:v>
+        <x:v>1.4866322362074</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-924177</x:v>
+        <x:v>-519198</x:v>
       </x:c>
       <x:c r="I45" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1845,25 +1848,25 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>161290</x:v>
+        <x:v>118207</x:v>
       </x:c>
       <x:c r="C46" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>2023390</x:v>
+        <x:v>1042995</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>2184680</x:v>
+        <x:v>1161202</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>6.3009285496945</x:v>
+        <x:v>3.30364552615984</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-1862100</x:v>
+        <x:v>-924788</x:v>
       </x:c>
       <x:c r="I46" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1874,25 +1877,25 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>33177</x:v>
+        <x:v>161290</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1936866</x:v>
+        <x:v>2023417</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1970043</x:v>
+        <x:v>2184707</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>5.68188484484034</x:v>
+        <x:v>6.21554002363076</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-1903689</x:v>
+        <x:v>-1862127</x:v>
       </x:c>
       <x:c r="I47" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1903,25 +1906,25 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>2362115</x:v>
+        <x:v>33177</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>4392731</x:v>
+        <x:v>1941485</x:v>
       </x:c>
       <x:c r="E48" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>6754846</x:v>
+        <x:v>1974662</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>19.4819387783061</x:v>
+        <x:v>5.61795732523526</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-2030616</x:v>
+        <x:v>-1908308</x:v>
       </x:c>
       <x:c r="I48" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1932,27 +1935,56 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
+        <x:v>2362115</x:v>
+      </x:c>
+      <x:c r="C49" s="0">
+        <x:v>59.8499984741211</x:v>
+      </x:c>
+      <x:c r="D49" s="0">
+        <x:v>4394856</x:v>
+      </x:c>
+      <x:c r="E49" s="0">
+        <x:v>59.8499984741211</x:v>
+      </x:c>
+      <x:c r="F49" s="0">
+        <x:v>6756971</x:v>
+      </x:c>
+      <x:c r="G49" s="0">
+        <x:v>19.2237328342026</x:v>
+      </x:c>
+      <x:c r="H49" s="0">
+        <x:v>-2032741</x:v>
+      </x:c>
+      <x:c r="I49" s="0">
+        <x:v>59.8499984741211</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:9">
+      <x:c r="A50" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B50" s="0">
         <x:v>88220</x:v>
       </x:c>
-      <x:c r="C49" s="0">
-        <x:v>59.8499984741211</x:v>
-      </x:c>
-      <x:c r="D49" s="0">
-        <x:v>2603462</x:v>
-      </x:c>
-      <x:c r="E49" s="0">
-        <x:v>59.8499984741211</x:v>
-      </x:c>
-      <x:c r="F49" s="0">
-        <x:v>2691682</x:v>
-      </x:c>
-      <x:c r="G49" s="0">
-        <x:v>7.76319459165589</x:v>
-      </x:c>
-      <x:c r="H49" s="0">
-        <x:v>-2515242</x:v>
-      </x:c>
-      <x:c r="I49" s="0">
+      <x:c r="C50" s="0">
+        <x:v>59.8499984741211</x:v>
+      </x:c>
+      <x:c r="D50" s="0">
+        <x:v>2603655</x:v>
+      </x:c>
+      <x:c r="E50" s="0">
+        <x:v>59.8499984741211</x:v>
+      </x:c>
+      <x:c r="F50" s="0">
+        <x:v>2691875</x:v>
+      </x:c>
+      <x:c r="G50" s="0">
+        <x:v>7.6584442678634</x:v>
+      </x:c>
+      <x:c r="H50" s="0">
+        <x:v>-2515435</x:v>
+      </x:c>
+      <x:c r="I50" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -97,12 +97,12 @@
     <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
     <x:t>DESTEK</x:t>
   </x:si>
   <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALTERNATIF</x:t>
   </x:si>
   <x:si>
@@ -148,10 +148,10 @@
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
   </x:si>
   <x:si>
     <x:t>HALK</x:t>
@@ -572,28 +572,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>3862922</x:v>
+        <x:v>3903230</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D2" s="0">
         <x:v>523101</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>4386023</x:v>
+        <x:v>4426331</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>12.4783330218034</x:v>
+        <x:v>12.5641936585031</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>3339821</x:v>
+        <x:v>3380129</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -604,25 +604,25 @@
         <x:v>4057204</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D3" s="0">
         <x:v>1041044</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F3" s="0">
         <x:v>5098248</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>14.504628993451</x:v>
+        <x:v>14.47143812586</x:v>
       </x:c>
       <x:c r="H3" s="0">
         <x:v>3016160</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -633,25 +633,25 @@
         <x:v>2317678</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>245808</x:v>
+        <x:v>247989</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>2563486</x:v>
+        <x:v>2565667</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.29317470627279</x:v>
+        <x:v>7.28267656694236</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>2071870</x:v>
+        <x:v>2069689</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -662,25 +662,25 @@
         <x:v>904357</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D5" s="0">
         <x:v>1445</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F5" s="0">
         <x:v>905802</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.57702684363843</x:v>
+        <x:v>2.57112984642571</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>902912</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -691,25 +691,25 @@
         <x:v>907492</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>427361</x:v>
+        <x:v>428160</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1334853</x:v>
+        <x:v>1335652</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>3.79768648480715</x:v>
+        <x:v>3.79126422953162</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>480131</x:v>
+        <x:v>479332</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -720,25 +720,25 @@
         <x:v>167070</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D7" s="0">
         <x:v>160</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>167230</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.4757730707833</x:v>
+        <x:v>0.474684361723392</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>166910</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -749,25 +749,25 @@
         <x:v>315862</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D8" s="0">
         <x:v>168289</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F8" s="0">
         <x:v>484151</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>1.37742036711598</x:v>
+        <x:v>1.37426842320602</x:v>
       </x:c>
       <x:c r="H8" s="0">
         <x:v>147573</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -778,25 +778,25 @@
         <x:v>269815</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D9" s="0">
         <x:v>166210</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F9" s="0">
         <x:v>436025</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.24050082633671</x:v>
+        <x:v>1.23766219470455</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>103605</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -807,25 +807,25 @@
         <x:v>97409</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>8622</x:v>
+        <x:v>8718</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>106031</x:v>
+        <x:v>106127</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.301660554136364</x:v>
+        <x:v>0.301242763000768</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>88787</x:v>
+        <x:v>88691</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -836,25 +836,25 @@
         <x:v>141100</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>58638</x:v>
+        <x:v>58890</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>199738</x:v>
+        <x:v>199990</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.568259054069932</x:v>
+        <x:v>0.567674014836221</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>82462</x:v>
+        <x:v>82210</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -865,25 +865,25 @@
         <x:v>160649</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>79812</x:v>
+        <x:v>82028</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>240461</x:v>
+        <x:v>242677</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.684116895136178</x:v>
+        <x:v>0.688841576570877</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>80837</x:v>
+        <x:v>78621</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -894,25 +894,25 @@
         <x:v>391273</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>317036</x:v>
+        <x:v>317318</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>708309</x:v>
+        <x:v>708591</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>2.01515486451862</x:v>
+        <x:v>2.01134405643689</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>74237</x:v>
+        <x:v>73955</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -923,25 +923,25 @@
         <x:v>137556</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>110406</x:v>
+        <x:v>113984</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>247962</x:v>
+        <x:v>251540</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.705457407029652</x:v>
+        <x:v>0.713999308424936</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>27150</x:v>
+        <x:v>23572</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -952,25 +952,25 @@
         <x:v>24000</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D15" s="0">
         <x:v>624</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.849</x:v>
       </x:c>
       <x:c r="F15" s="0">
         <x:v>24624</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0700558278716019</x:v>
+        <x:v>0.0698955194826096</x:v>
       </x:c>
       <x:c r="H15" s="0">
         <x:v>23376</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -981,7 +981,7 @@
         <x:v>20347</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D16" s="0">
         <x:v>0</x:v>
@@ -993,13 +993,13 @@
         <x:v>20347</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0578876677105053</x:v>
+        <x:v>0.0577552036595459</x:v>
       </x:c>
       <x:c r="H16" s="0">
         <x:v>20347</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1010,25 +1010,25 @@
         <x:v>25501</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>8024</x:v>
+        <x:v>8133</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>33525</x:v>
+        <x:v>33634</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0953793709143702</x:v>
+        <x:v>0.0954705126006373</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>17477</x:v>
+        <x:v>17368</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1039,25 +1039,25 @@
         <x:v>16000</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D18" s="0">
         <x:v>7000</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F18" s="0">
         <x:v>23000</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0654355117384196</x:v>
+        <x:v>0.0652857759949652</x:v>
       </x:c>
       <x:c r="H18" s="0">
         <x:v>9000</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,7 +1068,7 @@
         <x:v>4024</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D19" s="0">
         <x:v>0</x:v>
@@ -1080,13 +1080,13 @@
         <x:v>4024</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0114483695319739</x:v>
+        <x:v>0.0114221722871191</x:v>
       </x:c>
       <x:c r="H19" s="0">
         <x:v>4024</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1097,25 +1097,25 @@
         <x:v>4100</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D20" s="0">
         <x:v>400</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F20" s="0">
         <x:v>4500</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0128026001227343</x:v>
+        <x:v>0.0127733039990149</x:v>
       </x:c>
       <x:c r="H20" s="0">
         <x:v>3700</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1132,19 +1132,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.852</x:v>
       </x:c>
       <x:c r="F21" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>7.68156007364056E-05</x:v>
+        <x:v>7.66398239940895E-05</x:v>
       </x:c>
       <x:c r="H21" s="0">
         <x:v>-27</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.852</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1161,19 +1161,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.852</x:v>
       </x:c>
       <x:c r="F22" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>7.68156007364056E-05</x:v>
+        <x:v>7.66398239940895E-05</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-27</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.852</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1190,19 +1190,19 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.851</x:v>
       </x:c>
       <x:c r="F23" s="0">
         <x:v>121</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.000344247692189077</x:v>
+        <x:v>0.000343459951973512</x:v>
       </x:c>
       <x:c r="H23" s="0">
         <x:v>-121</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.851</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1219,19 +1219,19 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.849</x:v>
       </x:c>
       <x:c r="F24" s="0">
         <x:v>186</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.000529174138406349</x:v>
+        <x:v>0.000527963231959283</x:v>
       </x:c>
       <x:c r="H24" s="0">
         <x:v>-186</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.849</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1242,25 +1242,25 @@
         <x:v>33417</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D25" s="0">
         <x:v>34018</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F25" s="0">
         <x:v>67435</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.191854075394797</x:v>
+        <x:v>0.191415056705238</x:v>
       </x:c>
       <x:c r="H25" s="0">
         <x:v>-601</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1274,22 +1274,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1360</x:v>
+        <x:v>1414</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1360</x:v>
+        <x:v>1414</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00386923025931524</x:v>
+        <x:v>0.00401365596769047</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-1360</x:v>
+        <x:v>-1414</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1300,25 +1300,25 @@
         <x:v>1280</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>2758</x:v>
+        <x:v>3378</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>4038</x:v>
+        <x:v>4658</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0114881998434669</x:v>
+        <x:v>0.0132217888949803</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1478</x:v>
+        <x:v>-2098</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1332,22 +1332,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>2127</x:v>
+        <x:v>2182</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>2127</x:v>
+        <x:v>2182</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00605136232467906</x:v>
+        <x:v>0.00619363318352235</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-2127</x:v>
+        <x:v>-2182</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1361,22 +1361,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>3714</x:v>
+        <x:v>3849</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>3714</x:v>
+        <x:v>3849</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.01056641263463</x:v>
+        <x:v>0.0109254326871574</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-3714</x:v>
+        <x:v>-3849</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1387,25 +1387,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>5221</x:v>
+        <x:v>5331</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>5222</x:v>
+        <x:v>5332</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0148567061868707</x:v>
+        <x:v>0.0151349459828328</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-5220</x:v>
+        <x:v>-5330</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1419,22 +1419,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>6525</x:v>
+        <x:v>6743</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>6525</x:v>
+        <x:v>6743</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0185637701779647</x:v>
+        <x:v>0.0191400864145239</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-6525</x:v>
+        <x:v>-6743</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1445,25 +1445,25 @@
         <x:v>16712</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D32" s="0">
         <x:v>26253</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F32" s="0">
         <x:v>42965</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.122236380949617</x:v>
+        <x:v>0.121956668070595</x:v>
       </x:c>
       <x:c r="H32" s="0">
         <x:v>-9541</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1474,25 +1474,25 @@
         <x:v>25431</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>35517</x:v>
+        <x:v>35685</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>60948</x:v>
+        <x:v>61116</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.173398416062313</x:v>
+        <x:v>0.173478499378621</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-10086</x:v>
+        <x:v>-10254</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1503,25 +1503,25 @@
         <x:v>1856</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>12129</x:v>
+        <x:v>12319</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>13985</x:v>
+        <x:v>14175</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0397876361592086</x:v>
+        <x:v>0.040235907596897</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-10273</x:v>
+        <x:v>-10463</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1532,25 +1532,25 @@
         <x:v>22381</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>33959</x:v>
+        <x:v>34535</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>56340</x:v>
+        <x:v>56916</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.160288553536633</x:v>
+        <x:v>0.161556748979541</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-11578</x:v>
+        <x:v>-12154</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1561,25 +1561,25 @@
         <x:v>250596</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D36" s="0">
         <x:v>263389</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F36" s="0">
         <x:v>513985</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>1.46229876090746</x:v>
+        <x:v>1.45895259020749</x:v>
       </x:c>
       <x:c r="H36" s="0">
         <x:v>-12793</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1590,25 +1590,25 @@
         <x:v>225784</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>245931</x:v>
+        <x:v>245986</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>471715</x:v>
+        <x:v>471770</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>1.34203967042124</x:v>
+        <x:v>1.33912480613673</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-20147</x:v>
+        <x:v>-20202</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1616,28 +1616,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>197560</x:v>
+        <x:v>18082</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>227768</x:v>
+        <x:v>57070</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>425328</x:v>
+        <x:v>75152</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>1.21006762333385</x:v>
+        <x:v>0.213319853807549</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-30208</x:v>
+        <x:v>-38988</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1645,28 +1645,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>18082</x:v>
+        <x:v>197560</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>54864</x:v>
+        <x:v>236626</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>72946</x:v>
+        <x:v>434186</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.207532993011772</x:v>
+        <x:v>1.23244217113695</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-36782</x:v>
+        <x:v>-39066</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1677,25 +1677,25 @@
         <x:v>7040</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>77584</x:v>
+        <x:v>79911</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>84624</x:v>
+        <x:v>86951</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.240757162841392</x:v>
+        <x:v>0.246811456892966</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-70544</x:v>
+        <x:v>-72871</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1706,25 +1706,25 @@
         <x:v>12900</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>112271</x:v>
+        <x:v>112480</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>125171</x:v>
+        <x:v>125380</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.356114279991727</x:v>
+        <x:v>0.355892634532554</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-99371</x:v>
+        <x:v>-99580</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1735,25 +1735,25 @@
         <x:v>52362</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>182933</x:v>
+        <x:v>189427</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>235295</x:v>
+        <x:v>241789</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.66941951019528</x:v>
+        <x:v>0.686320977915071</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-130571</x:v>
+        <x:v>-137065</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1764,25 +1764,25 @@
         <x:v>20001</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>233154</x:v>
+        <x:v>238232</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>253155</x:v>
+        <x:v>258233</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.720231607571287</x:v>
+        <x:v>0.732997469239471</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-213153</x:v>
+        <x:v>-218231</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1793,25 +1793,25 @@
         <x:v>100114</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>321463</x:v>
+        <x:v>321544</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>421577</x:v>
+        <x:v>421658</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>1.19939594487599</x:v>
+        <x:v>1.1968812928037</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-221349</x:v>
+        <x:v>-221430</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1822,25 +1822,25 @@
         <x:v>1670</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D45" s="0">
         <x:v>520868</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F45" s="0">
         <x:v>522538</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.4866322362074</x:v>
+        <x:v>1.48323038334161</x:v>
       </x:c>
       <x:c r="H45" s="0">
         <x:v>-519198</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1851,25 +1851,25 @@
         <x:v>118207</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>1042995</x:v>
+        <x:v>1043078</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>1161202</x:v>
+        <x:v>1161285</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>3.30364552615984</x:v>
+        <x:v>3.29632140766579</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-924788</x:v>
+        <x:v>-924871</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1880,25 +1880,25 @@
         <x:v>161290</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>2023417</x:v>
+        <x:v>2023444</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>2184707</x:v>
+        <x:v>2184734</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>6.21554002363076</x:v>
+        <x:v>6.20139367532975</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-1862127</x:v>
+        <x:v>-1862154</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1909,25 +1909,25 @@
         <x:v>33177</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>1941485</x:v>
+        <x:v>1942840</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>1974662</x:v>
+        <x:v>1976017</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>5.61795732523526</x:v>
+        <x:v>5.60894796627144</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-1908308</x:v>
+        <x:v>-1909663</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1938,25 +1938,25 @@
         <x:v>2362115</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>4394856</x:v>
+        <x:v>4396708</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>6756971</x:v>
+        <x:v>6758823</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>19.2237328342026</x:v>
+        <x:v>19.1850001898965</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-2032741</x:v>
+        <x:v>-2034593</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1967,25 +1967,25 @@
         <x:v>88220</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>2603655</x:v>
+        <x:v>2603699</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>2691875</x:v>
+        <x:v>2691919</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>7.6584442678634</x:v>
+        <x:v>7.64104438393872</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-2515435</x:v>
+        <x:v>-2515479</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>59.85</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -70,24 +70,24 @@
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
     <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
-    <x:t>GEDIK</x:t>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
     <x:t>IKON</x:t>
   </x:si>
   <x:si>
@@ -97,12 +97,12 @@
     <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
     <x:t>TURKISH</x:t>
   </x:si>
   <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
     <x:t>ALTERNATIF</x:t>
   </x:si>
   <x:si>
@@ -115,12 +115,12 @@
     <x:t>ACAR</x:t>
   </x:si>
   <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
@@ -133,18 +133,18 @@
     <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
@@ -163,10 +163,10 @@
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
     <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
   </x:si>
   <x:si>
     <x:t>INVEST AZ</x:t>
@@ -572,7 +572,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>3903230</x:v>
+        <x:v>4012220</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>59.85</x:v>
@@ -584,13 +584,13 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>4426331</x:v>
+        <x:v>4535321</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>12.5641936585031</x:v>
+        <x:v>12.7943991636582</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>3380129</x:v>
+        <x:v>3489119</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>59.85</x:v>
@@ -607,19 +607,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1041044</x:v>
+        <x:v>1041099</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>5098248</x:v>
+        <x:v>5098303</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>14.47143812586</x:v>
+        <x:v>14.3826034892075</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>3016160</x:v>
+        <x:v>3016105</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>59.85</x:v>
@@ -636,19 +636,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>247989</x:v>
+        <x:v>251926</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>2565667</x:v>
+        <x:v>2569604</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.28267656694236</x:v>
+        <x:v>7.2489994133894</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>2069689</x:v>
+        <x:v>2065752</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>59.85</x:v>
@@ -674,7 +674,7 @@
         <x:v>905802</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.57112984642571</x:v>
+        <x:v>2.55531909455579</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>902912</x:v>
@@ -694,19 +694,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>428160</x:v>
+        <x:v>430605</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1335652</x:v>
+        <x:v>1338097</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>3.79126422953162</x:v>
+        <x:v>3.77484794079482</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>479332</x:v>
+        <x:v>476887</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>59.85</x:v>
@@ -732,7 +732,7 @@
         <x:v>167230</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.474684361723392</x:v>
+        <x:v>0.471765366142452</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>166910</x:v>
@@ -752,19 +752,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>168289</x:v>
+        <x:v>168344</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>484151</x:v>
+        <x:v>484206</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>1.37426842320602</x:v>
+        <x:v>1.36597273741776</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>147573</x:v>
+        <x:v>147518</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>59.85</x:v>
@@ -781,19 +781,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>166210</x:v>
+        <x:v>166266</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>436025</x:v>
+        <x:v>436081</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.23766219470455</x:v>
+        <x:v>1.23020936813231</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>103605</x:v>
+        <x:v>103549</x:v>
       </x:c>
       <x:c r="I9" s="0">
         <x:v>59.85</x:v>
@@ -810,19 +810,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>8718</x:v>
+        <x:v>8839</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>106127</x:v>
+        <x:v>106248</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.301242763000768</x:v>
+        <x:v>0.29973166669798</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>88691</x:v>
+        <x:v>88570</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>59.85</x:v>
@@ -848,7 +848,7 @@
         <x:v>199990</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.567674014836221</x:v>
+        <x:v>0.564183194252401</x:v>
       </x:c>
       <x:c r="H11" s="0">
         <x:v>82210</x:v>
@@ -862,25 +862,25 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>160649</x:v>
+        <x:v>391273</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>82028</x:v>
+        <x:v>317877</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>242677</x:v>
+        <x:v>709150</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.688841576570877</x:v>
+        <x:v>2.00055258864988</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>78621</x:v>
+        <x:v>73396</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>59.85</x:v>
@@ -891,25 +891,25 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>391273</x:v>
+        <x:v>160649</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>317318</x:v>
+        <x:v>87992</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>708591</x:v>
+        <x:v>248641</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>2.01134405643689</x:v>
+        <x:v>0.701430439532533</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>73955</x:v>
+        <x:v>72657</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>59.85</x:v>
@@ -920,25 +920,25 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>137556</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>113984</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>251540</x:v>
+        <x:v>24680</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.713999308424936</x:v>
+        <x:v>0.069623687355114</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>23572</x:v>
+        <x:v>23320</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>59.85</x:v>
@@ -949,25 +949,25 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>24000</x:v>
+        <x:v>20347</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>624</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>59.849</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>24624</x:v>
+        <x:v>20347</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0698955194826096</x:v>
+        <x:v>0.0574000472696315</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>23376</x:v>
+        <x:v>20347</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>59.85</x:v>
@@ -978,25 +978,25 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>20347</x:v>
+        <x:v>25501</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>0</x:v>
+        <x:v>8215</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>20347</x:v>
+        <x:v>33716</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0577552036595459</x:v>
+        <x:v>0.095114758625001</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>20347</x:v>
+        <x:v>17286</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>59.85</x:v>
@@ -1007,25 +1007,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>25501</x:v>
+        <x:v>137556</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>8133</x:v>
+        <x:v>127258</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>33634</x:v>
+        <x:v>264814</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0954705126006373</x:v>
+        <x:v>0.747055394783516</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>17368</x:v>
+        <x:v>10298</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>59.85</x:v>
@@ -1051,7 +1051,7 @@
         <x:v>23000</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0652857759949652</x:v>
+        <x:v>0.0648843115546038</x:v>
       </x:c>
       <x:c r="H18" s="0">
         <x:v>9000</x:v>
@@ -1071,19 +1071,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>0</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>0</x:v>
+        <x:v>59.857</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>4024</x:v>
+        <x:v>4052</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0114221722871191</x:v>
+        <x:v>0.0114309230617067</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>4024</x:v>
+        <x:v>3996</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>59.85</x:v>
@@ -1109,7 +1109,7 @@
         <x:v>4500</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0127733039990149</x:v>
+        <x:v>0.0126947566085094</x:v>
       </x:c>
       <x:c r="H20" s="0">
         <x:v>3700</x:v>
@@ -1138,7 +1138,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>7.66398239940895E-05</x:v>
+        <x:v>7.61685396510567E-05</x:v>
       </x:c>
       <x:c r="H21" s="0">
         <x:v>-27</x:v>
@@ -1167,7 +1167,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>7.66398239940895E-05</x:v>
+        <x:v>7.61685396510567E-05</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-27</x:v>
@@ -1187,19 +1187,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>121</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>59.851</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>121</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.000343459951973512</x:v>
+        <x:v>0.000417516439568755</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-121</x:v>
+        <x:v>-148</x:v>
       </x:c>
       <x:c r="I23" s="0">
         <x:v>59.851</x:v>
@@ -1225,7 +1225,7 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.000527963231959283</x:v>
+        <x:v>0.000524716606485057</x:v>
       </x:c>
       <x:c r="H24" s="0">
         <x:v>-186</x:v>
@@ -1254,7 +1254,7 @@
         <x:v>67435</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.191415056705238</x:v>
+        <x:v>0.190237980421074</x:v>
       </x:c>
       <x:c r="H25" s="0">
         <x:v>-601</x:v>
@@ -1274,19 +1274,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1414</x:v>
+        <x:v>1522</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1414</x:v>
+        <x:v>1522</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00401365596769047</x:v>
+        <x:v>0.00429364879070031</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-1414</x:v>
+        <x:v>-1522</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>59.85</x:v>
@@ -1297,25 +1297,25 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>1280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>59.85</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>3378</x:v>
+        <x:v>2264</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>4658</x:v>
+        <x:v>2264</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0132217888949803</x:v>
+        <x:v>0.00638687310259231</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-2098</x:v>
+        <x:v>-2264</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>59.85</x:v>
@@ -1326,25 +1326,25 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>0</x:v>
+        <x:v>1280</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0</x:v>
+        <x:v>59.85</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>2182</x:v>
+        <x:v>3676</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>2182</x:v>
+        <x:v>4956</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00619363318352235</x:v>
+        <x:v>0.0139811586115051</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-2182</x:v>
+        <x:v>-2396</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>59.85</x:v>
@@ -1361,19 +1361,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>3849</x:v>
+        <x:v>4068</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>3849</x:v>
+        <x:v>4068</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0109254326871574</x:v>
+        <x:v>0.0114760599740925</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-3849</x:v>
+        <x:v>-4068</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>59.85</x:v>
@@ -1390,19 +1390,19 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>5331</x:v>
+        <x:v>5450</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>5332</x:v>
+        <x:v>5451</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0151349459828328</x:v>
+        <x:v>0.0153775818384411</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-5330</x:v>
+        <x:v>-5449</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>59.85</x:v>
@@ -1419,19 +1419,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>6743</x:v>
+        <x:v>7580</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>6743</x:v>
+        <x:v>7580</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0191400864145239</x:v>
+        <x:v>0.0213836122427781</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-6743</x:v>
+        <x:v>-7580</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>59.85</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>42965</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.121956668070595</x:v>
+        <x:v>0.121206715041024</x:v>
       </x:c>
       <x:c r="H32" s="0">
         <x:v>-9541</x:v>
@@ -1471,25 +1471,25 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>25431</x:v>
+        <x:v>1856</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>35685</x:v>
+        <x:v>13085</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>61116</x:v>
+        <x:v>14941</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.173478499378621</x:v>
+        <x:v>0.0421494129972755</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-10254</x:v>
+        <x:v>-11229</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>59.85</x:v>
@@ -1500,25 +1500,25 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>1856</x:v>
+        <x:v>250596</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>12319</x:v>
+        <x:v>263416</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>14175</x:v>
+        <x:v>514012</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.040235907596897</x:v>
+        <x:v>1.45005716307848</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-10463</x:v>
+        <x:v>-12820</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>59.85</x:v>
@@ -1529,25 +1529,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>22381</x:v>
+        <x:v>25431</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>34535</x:v>
+        <x:v>39059</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>56916</x:v>
+        <x:v>64490</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.161556748979541</x:v>
+        <x:v>0.181929967485061</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-12154</x:v>
+        <x:v>-13628</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>59.85</x:v>
@@ -1558,25 +1558,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>250596</x:v>
+        <x:v>22381</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>263389</x:v>
+        <x:v>37530</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>513985</x:v>
+        <x:v>59911</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>1.45895259020749</x:v>
+        <x:v>0.169012347371647</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-12793</x:v>
+        <x:v>-15149</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>59.85</x:v>
@@ -1593,19 +1593,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>245986</x:v>
+        <x:v>246769</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>471770</x:v>
+        <x:v>472553</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>1.33912480613673</x:v>
+        <x:v>1.33309895991577</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-20202</x:v>
+        <x:v>-20985</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>59.85</x:v>
@@ -1622,19 +1622,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>57070</x:v>
+        <x:v>61668</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>75152</x:v>
+        <x:v>79750</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.213319853807549</x:v>
+        <x:v>0.224979297673029</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-38988</x:v>
+        <x:v>-43586</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>59.85</x:v>
@@ -1651,19 +1651,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>236626</x:v>
+        <x:v>264360</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>434186</x:v>
+        <x:v>461920</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>1.23244217113695</x:v>
+        <x:v>1.30310266057837</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-39066</x:v>
+        <x:v>-66800</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>59.85</x:v>
@@ -1680,19 +1680,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>79911</x:v>
+        <x:v>86400</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>86951</x:v>
+        <x:v>93440</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.246811456892966</x:v>
+        <x:v>0.263599568333138</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-72871</x:v>
+        <x:v>-79360</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>59.85</x:v>
@@ -1709,19 +1709,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>112480</x:v>
+        <x:v>113256</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>125380</x:v>
+        <x:v>126156</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.355892634532554</x:v>
+        <x:v>0.355893269934026</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-99580</x:v>
+        <x:v>-100356</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>59.85</x:v>
@@ -1738,19 +1738,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>189427</x:v>
+        <x:v>206008</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>241789</x:v>
+        <x:v>258370</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.686320977915071</x:v>
+        <x:v>0.72887650332013</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-137065</x:v>
+        <x:v>-153646</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>59.85</x:v>
@@ -1761,25 +1761,25 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>20001</x:v>
+        <x:v>100114</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>238232</x:v>
+        <x:v>322088</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>258233</x:v>
+        <x:v>422202</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.732997469239471</x:v>
+        <x:v>1.19105591769465</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-218231</x:v>
+        <x:v>-221974</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>59.85</x:v>
@@ -1790,25 +1790,25 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>100114</x:v>
+        <x:v>20001</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>321544</x:v>
+        <x:v>250615</x:v>
       </x:c>
       <x:c r="E44" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>421658</x:v>
+        <x:v>270616</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>1.1968812928037</x:v>
+        <x:v>0.763423167637421</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-221430</x:v>
+        <x:v>-230614</x:v>
       </x:c>
       <x:c r="I44" s="0">
         <x:v>59.85</x:v>
@@ -1825,19 +1825,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>520868</x:v>
+        <x:v>520895</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>522538</x:v>
+        <x:v>522565</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.48323038334161</x:v>
+        <x:v>1.47418566380572</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-519198</x:v>
+        <x:v>-519225</x:v>
       </x:c>
       <x:c r="I45" s="0">
         <x:v>59.85</x:v>
@@ -1854,19 +1854,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>1043078</x:v>
+        <x:v>1043159</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>1161285</x:v>
+        <x:v>1161366</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>3.29632140766579</x:v>
+        <x:v>3.27627971186626</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-924871</x:v>
+        <x:v>-924952</x:v>
       </x:c>
       <x:c r="I46" s="0">
         <x:v>59.85</x:v>
@@ -1883,19 +1883,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>2023444</x:v>
+        <x:v>2023481</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>2184734</x:v>
+        <x:v>2184771</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>6.20139367532975</x:v>
+        <x:v>6.16336357562884</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-1862154</x:v>
+        <x:v>-1862191</x:v>
       </x:c>
       <x:c r="I47" s="0">
         <x:v>59.85</x:v>
@@ -1912,19 +1912,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>1942840</x:v>
+        <x:v>1944776</x:v>
       </x:c>
       <x:c r="E48" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>1976017</x:v>
+        <x:v>1977953</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>5.60894796627144</x:v>
+        <x:v>5.5799182040158</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-1909663</x:v>
+        <x:v>-1911599</x:v>
       </x:c>
       <x:c r="I48" s="0">
         <x:v>59.85</x:v>
@@ -1941,19 +1941,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>4396708</x:v>
+        <x:v>4398190</x:v>
       </x:c>
       <x:c r="E49" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>6758823</x:v>
+        <x:v>6760305</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>19.1850001898965</x:v>
+        <x:v>19.0712059053977</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-2034593</x:v>
+        <x:v>-2036075</x:v>
       </x:c>
       <x:c r="I49" s="0">
         <x:v>59.85</x:v>
@@ -1970,19 +1970,19 @@
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>2603699</x:v>
+        <x:v>2603754</x:v>
       </x:c>
       <x:c r="E50" s="0">
         <x:v>59.85</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>2691919</x:v>
+        <x:v>2691974</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>7.64104438393872</x:v>
+        <x:v>7.59421216143014</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-2515479</x:v>
+        <x:v>-2515534</x:v>
       </x:c>
       <x:c r="I50" s="0">
         <x:v>59.85</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -85,18 +85,18 @@
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
     <x:t>DESTEK</x:t>
   </x:si>
   <x:si>
@@ -115,12 +115,12 @@
     <x:t>ACAR</x:t>
   </x:si>
   <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
@@ -151,10 +151,10 @@
     <x:t>AK</x:t>
   </x:si>
   <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
   </x:si>
   <x:si>
     <x:t>TEB</x:t>
@@ -572,28 +572,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>4012220</x:v>
+        <x:v>4104377</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>523101</x:v>
+        <x:v>523155</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>4535321</x:v>
+        <x:v>4627532</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>12.7943991636582</x:v>
+        <x:v>12.9870043853815</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>3489119</x:v>
+        <x:v>3581222</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -604,25 +604,25 @@
         <x:v>4057204</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1041099</x:v>
+        <x:v>1041235</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>5098303</x:v>
+        <x:v>5098439</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>14.3826034892075</x:v>
+        <x:v>14.3085881743443</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>3016105</x:v>
+        <x:v>3015969</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -633,25 +633,25 @@
         <x:v>2317678</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>251926</x:v>
+        <x:v>255102</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>2569604</x:v>
+        <x:v>2572780</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.2489994133894</x:v>
+        <x:v>7.22041579455782</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>2065752</x:v>
+        <x:v>2062576</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -662,25 +662,25 @@
         <x:v>904357</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>1445</x:v>
+        <x:v>1473</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>905802</x:v>
+        <x:v>905830</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.55531909455579</x:v>
+        <x:v>2.54217975854302</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>902912</x:v>
+        <x:v>902884</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -691,25 +691,25 @@
         <x:v>907492</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>430605</x:v>
+        <x:v>432975</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1338097</x:v>
+        <x:v>1340467</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>3.77484794079482</x:v>
+        <x:v>3.76197307926971</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>476887</x:v>
+        <x:v>474517</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -720,25 +720,25 @@
         <x:v>167070</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D7" s="0">
         <x:v>160</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>167230</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.471765366142452</x:v>
+        <x:v>0.469325062121092</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>166910</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -749,25 +749,25 @@
         <x:v>315862</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>168344</x:v>
+        <x:v>168427</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>484206</x:v>
+        <x:v>484289</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>1.36597273741776</x:v>
+        <x:v>1.35913989720482</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>147518</x:v>
+        <x:v>147435</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -778,25 +778,25 @@
         <x:v>269815</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>166266</x:v>
+        <x:v>166416</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>436081</x:v>
+        <x:v>436231</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.23020936813231</x:v>
+        <x:v>1.22426682517578</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>103549</x:v>
+        <x:v>103399</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -807,25 +807,25 @@
         <x:v>97409</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>8839</x:v>
+        <x:v>9393</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>106248</x:v>
+        <x:v>106802</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.29973166669798</x:v>
+        <x:v>0.299736023947</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>88570</x:v>
+        <x:v>88016</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -836,25 +836,25 @@
         <x:v>141100</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>58890</x:v>
+        <x:v>58944</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>199990</x:v>
+        <x:v>200044</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.564183194252401</x:v>
+        <x:v>0.561416388967002</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>82210</x:v>
+        <x:v>82156</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -865,25 +865,25 @@
         <x:v>391273</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>317877</x:v>
+        <x:v>318208</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>709150</x:v>
+        <x:v>709481</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>2.00055258864988</x:v>
+        <x:v>1.99113325598717</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>73396</x:v>
+        <x:v>73065</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -894,25 +894,25 @@
         <x:v>160649</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>87992</x:v>
+        <x:v>94615</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>248641</x:v>
+        <x:v>255264</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.701430439532533</x:v>
+        <x:v>0.716389359907185</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>72657</x:v>
+        <x:v>66034</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -923,25 +923,25 @@
         <x:v>24000</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D14" s="0">
         <x:v>680</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F14" s="0">
         <x:v>24680</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.069623687355114</x:v>
+        <x:v>0.069263544418756</x:v>
       </x:c>
       <x:c r="H14" s="0">
         <x:v>23320</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -952,7 +952,7 @@
         <x:v>20347</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D15" s="0">
         <x:v>0</x:v>
@@ -964,13 +964,13 @@
         <x:v>20347</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0574000472696315</x:v>
+        <x:v>0.0571031336421567</x:v>
       </x:c>
       <x:c r="H15" s="0">
         <x:v>20347</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -981,25 +981,25 @@
         <x:v>25501</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D16" s="0">
         <x:v>8215</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F16" s="0">
         <x:v>33716</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.095114758625001</x:v>
+        <x:v>0.0946227578453312</x:v>
       </x:c>
       <x:c r="H16" s="0">
         <x:v>17286</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1007,28 +1007,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>137556</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>127258</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>264814</x:v>
+        <x:v>23000</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.747055394783516</x:v>
+        <x:v>0.0645486840207207</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>10298</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1036,28 +1036,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>16000</x:v>
+        <x:v>4024</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>7000</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>23000</x:v>
+        <x:v>4052</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0648843115546038</x:v>
+        <x:v>0.0113717942457374</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>9000</x:v>
+        <x:v>3996</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1065,28 +1065,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>4024</x:v>
+        <x:v>4100</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>28</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>59.857</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>4052</x:v>
+        <x:v>4500</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0114309230617067</x:v>
+        <x:v>0.0126290903518801</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>3996</x:v>
+        <x:v>3700</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1094,28 +1094,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>4100</x:v>
+        <x:v>137556</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>400</x:v>
+        <x:v>137152</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>4500</x:v>
+        <x:v>274708</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0126947566085094</x:v>
+        <x:v>0.770958256085397</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>3700</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1132,19 +1132,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>59.852</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F21" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>7.61685396510567E-05</x:v>
+        <x:v>7.57745421112808E-05</x:v>
       </x:c>
       <x:c r="H21" s="0">
         <x:v>-27</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>59.852</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1161,19 +1161,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>59.852</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F22" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>7.61685396510567E-05</x:v>
+        <x:v>7.57745421112808E-05</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-27</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>59.852</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1187,22 +1187,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>148</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>59.851</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>148</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.000417516439568755</x:v>
+        <x:v>0.000479905433371445</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-148</x:v>
+        <x:v>-171</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>59.851</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1216,22 +1216,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>186</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>59.849</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>186</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.000524716606485057</x:v>
+        <x:v>0.000600583407844966</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-186</x:v>
+        <x:v>-214</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>59.849</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1242,25 +1242,25 @@
         <x:v>33417</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D25" s="0">
         <x:v>34018</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F25" s="0">
         <x:v>67435</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.190237980421074</x:v>
+        <x:v>0.18925393508423</x:v>
       </x:c>
       <x:c r="H25" s="0">
         <x:v>-601</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1277,19 +1277,19 @@
         <x:v>1522</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F26" s="0">
         <x:v>1522</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00429364879070031</x:v>
+        <x:v>0.00427143900345813</x:v>
       </x:c>
       <x:c r="H26" s="0">
         <x:v>-1522</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1297,28 +1297,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>0</x:v>
+        <x:v>1280</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>2264</x:v>
+        <x:v>3703</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>2264</x:v>
+        <x:v>4983</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00638687310259231</x:v>
+        <x:v>0.0139846127163153</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-2264</x:v>
+        <x:v>-2423</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1326,28 +1326,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>1280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>59.85</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>3676</x:v>
+        <x:v>2480</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>4956</x:v>
+        <x:v>2480</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0139811586115051</x:v>
+        <x:v>0.00696003201614727</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-2396</x:v>
+        <x:v>-2480</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1361,22 +1361,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>4068</x:v>
+        <x:v>4367</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>4068</x:v>
+        <x:v>4367</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0114760599740925</x:v>
+        <x:v>0.012255830570369</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-4068</x:v>
+        <x:v>-4367</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1387,25 +1387,25 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>59</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>5450</x:v>
+        <x:v>5690</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>5451</x:v>
+        <x:v>5691</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0153775818384411</x:v>
+        <x:v>0.0159715895983444</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-5449</x:v>
+        <x:v>-5689</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1419,22 +1419,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>7580</x:v>
+        <x:v>7889</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>7580</x:v>
+        <x:v>7889</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0213836122427781</x:v>
+        <x:v>0.0221401986191072</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-7580</x:v>
+        <x:v>-7889</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1445,25 +1445,25 @@
         <x:v>16712</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D32" s="0">
         <x:v>26253</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F32" s="0">
         <x:v>42965</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.121206715041024</x:v>
+        <x:v>0.120579748215229</x:v>
       </x:c>
       <x:c r="H32" s="0">
         <x:v>-9541</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1474,25 +1474,25 @@
         <x:v>1856</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>13085</x:v>
+        <x:v>13462</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>14941</x:v>
+        <x:v>15318</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0421494129972755</x:v>
+        <x:v>0.0429894235578</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-11229</x:v>
+        <x:v>-11606</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1503,25 +1503,25 @@
         <x:v>250596</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>263416</x:v>
+        <x:v>263419</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>514012</x:v>
+        <x:v>514015</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>1.45005716307848</x:v>
+        <x:v>1.44256486160482</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-12820</x:v>
+        <x:v>-12823</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1532,25 +1532,25 @@
         <x:v>25431</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>39059</x:v>
+        <x:v>39814</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>64490</x:v>
+        <x:v>65245</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.181929967485061</x:v>
+        <x:v>0.183107777779649</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-13628</x:v>
+        <x:v>-14383</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1561,25 +1561,25 @@
         <x:v>22381</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>37530</x:v>
+        <x:v>38642</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>59911</x:v>
+        <x:v>61023</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.169012347371647</x:v>
+        <x:v>0.171258884565063</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-15149</x:v>
+        <x:v>-16261</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1590,25 +1590,25 @@
         <x:v>225784</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>246769</x:v>
+        <x:v>247063</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>472553</x:v>
+        <x:v>472847</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>1.33309895991577</x:v>
+        <x:v>1.32702833013677</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-20985</x:v>
+        <x:v>-21279</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1619,25 +1619,25 @@
         <x:v>18082</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>61668</x:v>
+        <x:v>66407</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>79750</x:v>
+        <x:v>84489</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.224979297673029</x:v>
+        <x:v>0.237115381053334</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-43586</x:v>
+        <x:v>-48325</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1645,28 +1645,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>197560</x:v>
+        <x:v>7040</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>264360</x:v>
+        <x:v>91755</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>461920</x:v>
+        <x:v>98795</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>1.30310266057837</x:v>
+        <x:v>0.277264662514222</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-66800</x:v>
+        <x:v>-84715</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1674,28 +1674,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>7040</x:v>
+        <x:v>197560</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>86400</x:v>
+        <x:v>285343</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>93440</x:v>
+        <x:v>482903</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.263599568333138</x:v>
+        <x:v>1.35525013737644</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-79360</x:v>
+        <x:v>-87783</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1706,25 +1706,25 @@
         <x:v>12900</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>113256</x:v>
+        <x:v>113859</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>126156</x:v>
+        <x:v>126759</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.355893269934026</x:v>
+        <x:v>0.355744636425328</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-100356</x:v>
+        <x:v>-100959</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1735,25 +1735,25 @@
         <x:v>52362</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>206008</x:v>
+        <x:v>221893</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>258370</x:v>
+        <x:v>274255</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.72887650332013</x:v>
+        <x:v>0.769686927656641</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-153646</x:v>
+        <x:v>-169531</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1764,25 +1764,25 @@
         <x:v>100114</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>322088</x:v>
+        <x:v>322567</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>422202</x:v>
+        <x:v>422681</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>1.19105591769465</x:v>
+        <x:v>1.18623923089401</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-221974</x:v>
+        <x:v>-222453</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1793,25 +1793,25 @@
         <x:v>20001</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>250615</x:v>
+        <x:v>261254</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>270616</x:v>
+        <x:v>281255</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.763423167637421</x:v>
+        <x:v>0.789332179315122</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-230614</x:v>
+        <x:v>-241253</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1822,25 +1822,25 @@
         <x:v>1670</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>520895</x:v>
+        <x:v>520922</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>522565</x:v>
+        <x:v>522592</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.47418566380572</x:v>
+        <x:v>1.4666359078155</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-519225</x:v>
+        <x:v>-519252</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1851,25 +1851,25 @@
         <x:v>118207</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>1043159</x:v>
+        <x:v>1043385</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>1161366</x:v>
+        <x:v>1161592</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>3.27627971186626</x:v>
+        <x:v>3.25996673778248</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-924952</x:v>
+        <x:v>-925178</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1880,25 +1880,25 @@
         <x:v>161290</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>2023481</x:v>
+        <x:v>2023508</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>2184771</x:v>
+        <x:v>2184798</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>6.16336357562884</x:v>
+        <x:v>6.13155807613489</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-1862191</x:v>
+        <x:v>-1862218</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1909,25 +1909,25 @@
         <x:v>33177</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>1944776</x:v>
+        <x:v>1947738</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>1977953</x:v>
+        <x:v>1980915</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>5.5799182040158</x:v>
+        <x:v>5.55936766986548</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-1911599</x:v>
+        <x:v>-1914561</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1938,25 +1938,25 @@
         <x:v>2362115</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>4398190</x:v>
+        <x:v>4400344</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>6760305</x:v>
+        <x:v>6762459</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>19.0712059053977</x:v>
+        <x:v>18.9786012693078</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-2036075</x:v>
+        <x:v>-2038229</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1967,25 +1967,25 @@
         <x:v>88220</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>2603754</x:v>
+        <x:v>2604696</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>2691974</x:v>
+        <x:v>2692916</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>7.59421216143014</x:v>
+        <x:v>7.5575732164497</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-2515534</x:v>
+        <x:v>-2516476</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>59.85</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -55,118 +55,121 @@
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
-    <x:t>MEKSA</x:t>
+    <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
+    <x:t>ANADOLU</x:t>
   </x:si>
   <x:si>
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
-    <x:t>YAPI KREDI</x:t>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
   </x:si>
   <x:si>
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
   </x:si>
   <x:si>
     <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
     <x:t>DINAMIK</x:t>
   </x:si>
   <x:si>
     <x:t>ACAR</x:t>
   </x:si>
   <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
     <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
     <x:t>ING</x:t>
   </x:si>
   <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
     <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
   </x:si>
   <x:si>
     <x:t>INVEST AZ</x:t>
@@ -535,7 +538,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I50"/>
+  <x:dimension ref="A1:I51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -572,25 +575,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>4104377</x:v>
+        <x:v>4577950</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>523155</x:v>
+        <x:v>523209</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>4627532</x:v>
+        <x:v>5101159</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>12.9870043853815</x:v>
+        <x:v>13.728387647226</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>3581222</x:v>
+        <x:v>4054741</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>59.8499984741211</x:v>
@@ -607,19 +610,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1041235</x:v>
+        <x:v>1041359</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>5098439</x:v>
+        <x:v>5098563</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>14.3085881743443</x:v>
+        <x:v>13.7214012164302</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>3015969</x:v>
+        <x:v>3015845</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>59.8499984741211</x:v>
@@ -630,25 +633,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>2317678</x:v>
+        <x:v>2319719</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>255102</x:v>
+        <x:v>381673</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>2572780</x:v>
+        <x:v>2701392</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.22041579455782</x:v>
+        <x:v>7.27006481529301</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>2062576</x:v>
+        <x:v>1938046</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>59.8499984741211</x:v>
@@ -665,19 +668,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>1473</x:v>
+        <x:v>1527</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>905830</x:v>
+        <x:v>905884</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.54217975854302</x:v>
+        <x:v>2.43794140026212</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>902884</x:v>
+        <x:v>902830</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>59.8499984741211</x:v>
@@ -688,25 +691,25 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>907492</x:v>
+        <x:v>912064</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>432975</x:v>
+        <x:v>452879</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1340467</x:v>
+        <x:v>1364943</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>3.76197307926971</x:v>
+        <x:v>3.67337434892103</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>474517</x:v>
+        <x:v>459185</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>59.8499984741211</x:v>
@@ -717,25 +720,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>167070</x:v>
+        <x:v>315868</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>160</x:v>
+        <x:v>168709</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>167230</x:v>
+        <x:v>484577</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.469325062121092</x:v>
+        <x:v>1.30410773334645</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>166910</x:v>
+        <x:v>147159</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>59.8499984741211</x:v>
@@ -746,25 +749,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>315862</x:v>
+        <x:v>167070</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>168427</x:v>
+        <x:v>33658</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>484289</x:v>
+        <x:v>200728</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>1.35913989720482</x:v>
+        <x:v>0.540205038825959</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>147435</x:v>
+        <x:v>133412</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>59.8499984741211</x:v>
@@ -775,25 +778,25 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>269815</x:v>
+        <x:v>106215</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>166416</x:v>
+        <x:v>10211</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>436231</x:v>
+        <x:v>116426</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.22426682517578</x:v>
+        <x:v>0.313329041540548</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>103399</x:v>
+        <x:v>96004</x:v>
       </x:c>
       <x:c r="I9" s="0">
         <x:v>59.8499984741211</x:v>
@@ -804,25 +807,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>97409</x:v>
+        <x:v>269815</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>9393</x:v>
+        <x:v>174924</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>106802</x:v>
+        <x:v>444739</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.299736023947</x:v>
+        <x:v>1.19689454765861</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>88016</x:v>
+        <x:v>94891</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>59.8499984741211</x:v>
@@ -833,25 +836,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>141100</x:v>
+        <x:v>71000</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>58944</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>200044</x:v>
+        <x:v>71000</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.561416388967002</x:v>
+        <x:v>0.191077267529408</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>82156</x:v>
+        <x:v>71000</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>59.8499984741211</x:v>
@@ -862,25 +865,25 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>391273</x:v>
+        <x:v>141100</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>318208</x:v>
+        <x:v>75645</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>709481</x:v>
+        <x:v>216745</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>1.99113325598717</x:v>
+        <x:v>0.583310455643121</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>73065</x:v>
+        <x:v>65455</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>59.8499984741211</x:v>
@@ -891,25 +894,25 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>160649</x:v>
+        <x:v>164040</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>94615</x:v>
+        <x:v>103364</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>255264</x:v>
+        <x:v>267404</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.716389359907185</x:v>
+        <x:v>0.719645431639914</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>66034</x:v>
+        <x:v>60676</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>59.8499984741211</x:v>
@@ -920,25 +923,25 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>24000</x:v>
+        <x:v>401273</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>680</x:v>
+        <x:v>353412</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>24680</x:v>
+        <x:v>754685</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.069263544418756</x:v>
+        <x:v>2.0310302485272</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>23320</x:v>
+        <x:v>47861</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>59.8499984741211</x:v>
@@ -964,7 +967,7 @@
         <x:v>20347</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0571031336421567</x:v>
+        <x:v>0.0547584389073362</x:v>
       </x:c>
       <x:c r="H15" s="0">
         <x:v>20347</x:v>
@@ -978,25 +981,25 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>25501</x:v>
+        <x:v>168120</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>8215</x:v>
+        <x:v>152870</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>33716</x:v>
+        <x:v>320990</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0946227578453312</x:v>
+        <x:v>0.863857635271335</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>17286</x:v>
+        <x:v>15250</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1007,25 +1010,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>16000</x:v>
+        <x:v>26528</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>7000</x:v>
+        <x:v>11397</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>23000</x:v>
+        <x:v>37925</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0645486840207207</x:v>
+        <x:v>0.102064864381026</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>9000</x:v>
+        <x:v>15131</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1036,7 +1039,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>4024</x:v>
+        <x:v>5492</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1048,13 +1051,13 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>4052</x:v>
+        <x:v>5520</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0113717942457374</x:v>
+        <x:v>0.0148555847431315</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>3996</x:v>
+        <x:v>5464</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1065,25 +1068,25 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>4100</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>400</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>4500</x:v>
+        <x:v>27000</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0126290903518801</x:v>
+        <x:v>0.0726631862435778</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>3700</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1094,25 +1097,25 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>137556</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>137152</x:v>
+        <x:v>20680</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>274708</x:v>
+        <x:v>44680</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.770958256085397</x:v>
+        <x:v>0.120244117087521</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>404</x:v>
+        <x:v>3320</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1138,7 +1141,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>7.57745421112808E-05</x:v>
+        <x:v>7.26631862435778E-05</x:v>
       </x:c>
       <x:c r="H21" s="0">
         <x:v>-27</x:v>
@@ -1167,7 +1170,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>7.57745421112808E-05</x:v>
+        <x:v>7.26631862435778E-05</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-27</x:v>
@@ -1196,7 +1199,7 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.000479905433371445</x:v>
+        <x:v>0.00046020017954266</x:v>
       </x:c>
       <x:c r="H23" s="0">
         <x:v>-171</x:v>
@@ -1225,7 +1228,7 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.000600583407844966</x:v>
+        <x:v>0.000575923031708358</x:v>
       </x:c>
       <x:c r="H24" s="0">
         <x:v>-214</x:v>
@@ -1239,25 +1242,25 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>33417</x:v>
+        <x:v>4100</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>34018</x:v>
+        <x:v>4527</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>67435</x:v>
+        <x:v>8627</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.18925393508423</x:v>
+        <x:v>0.0232172336193832</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-601</x:v>
+        <x:v>-427</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1268,25 +1271,25 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>0</x:v>
+        <x:v>33417</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1522</x:v>
+        <x:v>34018</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1522</x:v>
+        <x:v>67435</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00427143900345813</x:v>
+        <x:v>0.181483035716136</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-1522</x:v>
+        <x:v>-601</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1297,25 +1300,25 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>1280</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C27" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>3703</x:v>
+        <x:v>1549</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>4983</x:v>
+        <x:v>1572</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0139846127163153</x:v>
+        <x:v>0.00423061217684831</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-2423</x:v>
+        <x:v>-1526</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1332,19 +1335,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>2480</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>2480</x:v>
+        <x:v>2589</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00696003201614727</x:v>
+        <x:v>0.00696759219202307</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-2480</x:v>
+        <x:v>-2589</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1355,25 +1358,25 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>0</x:v>
+        <x:v>1280</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>4367</x:v>
+        <x:v>3921</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>4367</x:v>
+        <x:v>5201</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.012255830570369</x:v>
+        <x:v>0.0139970826538092</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-4367</x:v>
+        <x:v>-2641</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1384,25 +1387,25 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>5690</x:v>
+        <x:v>4828</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>5691</x:v>
+        <x:v>4828</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0159715895983444</x:v>
+        <x:v>0.0129932541919998</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-5689</x:v>
+        <x:v>-4828</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1413,25 +1416,25 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>7889</x:v>
+        <x:v>6153</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>7889</x:v>
+        <x:v>6154</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0221401986191072</x:v>
+        <x:v>0.0165618240052955</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-7889</x:v>
+        <x:v>-6152</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1442,25 +1445,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>16712</x:v>
+        <x:v>32851</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>26253</x:v>
+        <x:v>40826</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>42965</x:v>
+        <x:v>73677</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.120579748215229</x:v>
+        <x:v>0.198281687884003</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-9541</x:v>
+        <x:v>-7975</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1471,25 +1474,25 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>1856</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>13462</x:v>
+        <x:v>8815</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>15318</x:v>
+        <x:v>8815</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0429894235578</x:v>
+        <x:v>0.0237231846939681</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-11606</x:v>
+        <x:v>-8815</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1500,25 +1503,25 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>250596</x:v>
+        <x:v>16712</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>263419</x:v>
+        <x:v>26253</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>514015</x:v>
+        <x:v>42965</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>1.44256486160482</x:v>
+        <x:v>0.115628659146493</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-12823</x:v>
+        <x:v>-9541</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1529,25 +1532,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>25431</x:v>
+        <x:v>29182</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>39814</x:v>
+        <x:v>41336</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>65245</x:v>
+        <x:v>70518</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.183107777779649</x:v>
+        <x:v>0.189780095093504</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-14383</x:v>
+        <x:v>-12154</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1558,25 +1561,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>22381</x:v>
+        <x:v>1856</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>38642</x:v>
+        <x:v>14031</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>61023</x:v>
+        <x:v>15887</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.171258884565063</x:v>
+        <x:v>0.0427555570315452</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-16261</x:v>
+        <x:v>-12175</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1587,25 +1590,25 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>225784</x:v>
+        <x:v>226357</x:v>
       </x:c>
       <x:c r="C37" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>247063</x:v>
+        <x:v>254513</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>472847</x:v>
+        <x:v>480870</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>1.32702833013677</x:v>
+        <x:v>1.29413134699812</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-21279</x:v>
+        <x:v>-28156</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1616,25 +1619,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>18082</x:v>
+        <x:v>29618</x:v>
       </x:c>
       <x:c r="C38" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>66407</x:v>
+        <x:v>80837</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>84489</x:v>
+        <x:v>110455</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.237115381053334</x:v>
+        <x:v>0.297259712464237</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-48325</x:v>
+        <x:v>-51219</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1645,25 +1648,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>7040</x:v>
+        <x:v>37389</x:v>
       </x:c>
       <x:c r="C39" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>91755</x:v>
+        <x:v>98539</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>98795</x:v>
+        <x:v>135928</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.277264662514222</x:v>
+        <x:v>0.365813391841372</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-84715</x:v>
+        <x:v>-61150</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1674,25 +1677,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>197560</x:v>
+        <x:v>253417</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>285343</x:v>
+        <x:v>317695</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>482903</x:v>
+        <x:v>571112</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>1.35525013737644</x:v>
+        <x:v>1.53699324525712</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-87783</x:v>
+        <x:v>-64278</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1709,19 +1712,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>113859</x:v>
+        <x:v>115106</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>126759</x:v>
+        <x:v>128006</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.355744636425328</x:v>
+        <x:v>0.344493474751682</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-100959</x:v>
+        <x:v>-102206</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1732,25 +1735,25 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>52362</x:v>
+        <x:v>71197</x:v>
       </x:c>
       <x:c r="C42" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>221893</x:v>
+        <x:v>245774</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>274255</x:v>
+        <x:v>316971</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.769686927656641</x:v>
+        <x:v>0.853041585437522</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-169531</x:v>
+        <x:v>-174577</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1767,19 +1770,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>322567</x:v>
+        <x:v>323532</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>422681</x:v>
+        <x:v>423646</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>1.18623923089401</x:v>
+        <x:v>1.14012845182766</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-222453</x:v>
+        <x:v>-223418</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1790,25 +1793,25 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>20001</x:v>
+        <x:v>24173</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>261254</x:v>
+        <x:v>288264</x:v>
       </x:c>
       <x:c r="E44" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>281255</x:v>
+        <x:v>312437</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.789332179315122</x:v>
+        <x:v>0.840839552606842</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-241253</x:v>
+        <x:v>-264091</x:v>
       </x:c>
       <x:c r="I44" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1819,25 +1822,25 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>1670</x:v>
+        <x:v>251062</x:v>
       </x:c>
       <x:c r="C45" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>520922</x:v>
+        <x:v>566106</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>522592</x:v>
+        <x:v>817168</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.4666359078155</x:v>
+        <x:v>2.19918631764044</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-519252</x:v>
+        <x:v>-315044</x:v>
       </x:c>
       <x:c r="I45" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1848,25 +1851,25 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>118207</x:v>
+        <x:v>1670</x:v>
       </x:c>
       <x:c r="C46" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>1043385</x:v>
+        <x:v>521005</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>1161592</x:v>
+        <x:v>522675</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>3.25996673778248</x:v>
+        <x:v>1.40663818036526</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-925178</x:v>
+        <x:v>-519335</x:v>
       </x:c>
       <x:c r="I46" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1877,25 +1880,25 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>161290</x:v>
+        <x:v>118208</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>2023508</x:v>
+        <x:v>1043523</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>2184798</x:v>
+        <x:v>1161731</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>6.13155807613489</x:v>
+        <x:v>3.12648429696066</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-1862218</x:v>
+        <x:v>-925315</x:v>
       </x:c>
       <x:c r="I47" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1906,25 +1909,25 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>33177</x:v>
+        <x:v>161290</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>1947738</x:v>
+        <x:v>2023535</x:v>
       </x:c>
       <x:c r="E48" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>1980915</x:v>
+        <x:v>2184825</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>5.55936766986548</x:v>
+        <x:v>5.87986466239352</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-1914561</x:v>
+        <x:v>-1862245</x:v>
       </x:c>
       <x:c r="I48" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1935,25 +1938,25 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>2362115</x:v>
+        <x:v>36486</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>4400344</x:v>
+        <x:v>1951001</x:v>
       </x:c>
       <x:c r="E49" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>6762459</x:v>
+        <x:v>1987487</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>18.9786012693078</x:v>
+        <x:v>5.34878289028481</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-2038229</x:v>
+        <x:v>-1914515</x:v>
       </x:c>
       <x:c r="I49" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1964,27 +1967,56 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>88220</x:v>
+        <x:v>2369290</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>2604696</x:v>
+        <x:v>4437043</x:v>
       </x:c>
       <x:c r="E50" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>2692916</x:v>
+        <x:v>6806333</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>7.5575732164497</x:v>
+        <x:v>18.3174015709189</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-2516476</x:v>
+        <x:v>-2067753</x:v>
       </x:c>
       <x:c r="I50" s="0">
+        <x:v>59.8499984741211</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:9">
+      <x:c r="A51" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B51" s="0">
+        <x:v>98130</x:v>
+      </x:c>
+      <x:c r="C51" s="0">
+        <x:v>59.8499984741211</x:v>
+      </x:c>
+      <x:c r="D51" s="0">
+        <x:v>2606555</x:v>
+      </x:c>
+      <x:c r="E51" s="0">
+        <x:v>59.8499984741211</x:v>
+      </x:c>
+      <x:c r="F51" s="0">
+        <x:v>2704685</x:v>
+      </x:c>
+      <x:c r="G51" s="0">
+        <x:v>7.2789270327856</x:v>
+      </x:c>
+      <x:c r="H51" s="0">
+        <x:v>-2508425</x:v>
+      </x:c>
+      <x:c r="I51" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
     </x:row>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -52,6 +52,9 @@
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
@@ -61,90 +64,87 @@
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>ANADOLU</x:t>
   </x:si>
   <x:si>
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
     <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
     <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
@@ -154,22 +154,22 @@
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
     <x:t>INVEST AZ</x:t>
@@ -581,19 +581,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>523209</x:v>
+        <x:v>524442</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>5101159</x:v>
+        <x:v>5102392</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>13.728387647226</x:v>
+        <x:v>13.3180100109705</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>4054741</x:v>
+        <x:v>4053508</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>59.8499984741211</x:v>
@@ -610,19 +610,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1041359</x:v>
+        <x:v>1041687</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>5098563</x:v>
+        <x:v>5098891</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>13.7214012164302</x:v>
+        <x:v>13.3088718747692</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>3015845</x:v>
+        <x:v>3015517</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>59.8499984741211</x:v>
@@ -639,19 +639,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>381673</x:v>
+        <x:v>588714</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>2701392</x:v>
+        <x:v>2908433</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.27006481529301</x:v>
+        <x:v>7.59144726830805</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>1938046</x:v>
+        <x:v>1731005</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>59.8499984741211</x:v>
@@ -668,19 +668,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>1527</x:v>
+        <x:v>1930</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>905884</x:v>
+        <x:v>906287</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.43794140026212</x:v>
+        <x:v>2.36554528519416</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>902830</x:v>
+        <x:v>902427</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>59.8499984741211</x:v>
@@ -691,25 +691,25 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>912064</x:v>
+        <x:v>589661</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>452879</x:v>
+        <x:v>52689</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1364943</x:v>
+        <x:v>642350</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>3.67337434892103</x:v>
+        <x:v>1.6766300453879</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>459185</x:v>
+        <x:v>536972</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>59.8499984741211</x:v>
@@ -720,25 +720,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>315868</x:v>
+        <x:v>912093</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>168709</x:v>
+        <x:v>467927</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>484577</x:v>
+        <x:v>1380020</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.30410773334645</x:v>
+        <x:v>3.60205961739895</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>147159</x:v>
+        <x:v>444166</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>59.8499984741211</x:v>
@@ -749,25 +749,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>167070</x:v>
+        <x:v>315868</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>33658</x:v>
+        <x:v>168796</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>200728</x:v>
+        <x:v>484664</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.540205038825959</x:v>
+        <x:v>1.2650458851372</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>133412</x:v>
+        <x:v>147072</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>59.8499984741211</x:v>
@@ -778,25 +778,25 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>106215</x:v>
+        <x:v>167070</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>10211</x:v>
+        <x:v>33686</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>116426</x:v>
+        <x:v>200756</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.313329041540548</x:v>
+        <x:v>0.524003333683963</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>96004</x:v>
+        <x:v>133384</x:v>
       </x:c>
       <x:c r="I9" s="0">
         <x:v>59.8499984741211</x:v>
@@ -813,19 +813,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>174924</x:v>
+        <x:v>175971</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>444739</x:v>
+        <x:v>445786</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.19689454765861</x:v>
+        <x:v>1.16356846176273</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>94891</x:v>
+        <x:v>93844</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>59.8499984741211</x:v>
@@ -836,25 +836,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>71000</x:v>
+        <x:v>106215</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>0</x:v>
+        <x:v>13301</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>71000</x:v>
+        <x:v>119516</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.191077267529408</x:v>
+        <x:v>0.311954723288831</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>71000</x:v>
+        <x:v>92914</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>59.8499984741211</x:v>
@@ -865,25 +865,25 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>141100</x:v>
+        <x:v>71000</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>75645</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>216745</x:v>
+        <x:v>71000</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.583310455643121</x:v>
+        <x:v>0.185320671320217</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>65455</x:v>
+        <x:v>71000</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>59.8499984741211</x:v>
@@ -894,25 +894,25 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>164040</x:v>
+        <x:v>141100</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>103364</x:v>
+        <x:v>75692</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>267404</x:v>
+        <x:v>216792</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.719645431639914</x:v>
+        <x:v>0.56585970389933</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>60676</x:v>
+        <x:v>65408</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>59.8499984741211</x:v>
@@ -929,19 +929,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>353412</x:v>
+        <x:v>354895</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>754685</x:v>
+        <x:v>756168</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>2.0310302485272</x:v>
+        <x:v>1.97371213226571</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>47861</x:v>
+        <x:v>46378</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>59.8499984741211</x:v>
@@ -952,25 +952,25 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>20347</x:v>
+        <x:v>164330</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>0</x:v>
+        <x:v>118683</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>20347</x:v>
+        <x:v>283013</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.0547584389073362</x:v>
+        <x:v>0.738706466934486</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>20347</x:v>
+        <x:v>45647</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>59.8499984741211</x:v>
@@ -981,25 +981,25 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>168120</x:v>
+        <x:v>20347</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>152870</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>320990</x:v>
+        <x:v>20347</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.863857635271335</x:v>
+        <x:v>0.0531087281598936</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>15250</x:v>
+        <x:v>20347</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1016,19 +1016,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>11397</x:v>
+        <x:v>17143</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>37925</x:v>
+        <x:v>43671</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.102064864381026</x:v>
+        <x:v>0.113987873763735</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>15131</x:v>
+        <x:v>9385</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1039,7 +1039,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>5492</x:v>
+        <x:v>5714</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1051,13 +1051,13 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>5520</x:v>
+        <x:v>5742</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0148555847431315</x:v>
+        <x:v>0.014987483024235</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>5464</x:v>
+        <x:v>5686</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1068,25 +1068,25 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>16000</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>11000</x:v>
+        <x:v>20708</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>27000</x:v>
+        <x:v>44708</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0726631862435778</x:v>
+        <x:v>0.11669459962513</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>5000</x:v>
+        <x:v>3292</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1097,25 +1097,25 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>24000</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>20680</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>44680</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.120244117087521</x:v>
+        <x:v>0.0783045090085422</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>3320</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1141,7 +1141,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>7.26631862435778E-05</x:v>
+        <x:v>7.0474058107688E-05</x:v>
       </x:c>
       <x:c r="H21" s="0">
         <x:v>-27</x:v>
@@ -1170,7 +1170,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>7.26631862435778E-05</x:v>
+        <x:v>7.0474058107688E-05</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-27</x:v>
@@ -1190,19 +1190,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>171</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>171</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.00046020017954266</x:v>
+        <x:v>0.000589893967864352</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-171</x:v>
+        <x:v>-226</x:v>
       </x:c>
       <x:c r="I23" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1219,19 +1219,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>214</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>214</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.000575923031708358</x:v>
+        <x:v>0.000702130430776595</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-214</x:v>
+        <x:v>-269</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1248,19 +1248,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>4527</x:v>
+        <x:v>4554</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>8627</x:v>
+        <x:v>8654</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0232172336193832</x:v>
+        <x:v>0.0225882406986642</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-427</x:v>
+        <x:v>-454</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>67435</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.181483035716136</x:v>
+        <x:v>0.176015485499702</x:v>
       </x:c>
       <x:c r="H26" s="0">
         <x:v>-601</x:v>
@@ -1306,19 +1306,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1549</x:v>
+        <x:v>1653</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1572</x:v>
+        <x:v>1676</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00423061217684831</x:v>
+        <x:v>0.00437461190327723</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1526</x:v>
+        <x:v>-1630</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1329,25 +1329,25 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>0</x:v>
+        <x:v>1280</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>2589</x:v>
+        <x:v>4218</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>2589</x:v>
+        <x:v>5498</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00696759219202307</x:v>
+        <x:v>0.0143506063509655</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-2589</x:v>
+        <x:v>-2938</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1358,25 +1358,25 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>1280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>3921</x:v>
+        <x:v>3019</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>5201</x:v>
+        <x:v>3019</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0139970826538092</x:v>
+        <x:v>0.00788004375655964</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-2641</x:v>
+        <x:v>-3019</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1387,25 +1387,25 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>0</x:v>
+        <x:v>168120</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>4828</x:v>
+        <x:v>173534</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>4828</x:v>
+        <x:v>341654</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0129932541919998</x:v>
+        <x:v>0.891768290693483</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-4828</x:v>
+        <x:v>-5414</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1416,25 +1416,25 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>6153</x:v>
+        <x:v>5555</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>6154</x:v>
+        <x:v>5555</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0165618240052955</x:v>
+        <x:v>0.0144993849180817</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-6152</x:v>
+        <x:v>-5555</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1445,25 +1445,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>32851</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>40826</x:v>
+        <x:v>7221</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>73677</x:v>
+        <x:v>7222</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.198281687884003</x:v>
+        <x:v>0.0188505054686564</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-7975</x:v>
+        <x:v>-7220</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1480,19 +1480,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>8815</x:v>
+        <x:v>9286</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>8815</x:v>
+        <x:v>9286</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0237231846939681</x:v>
+        <x:v>0.0242378556884441</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-8815</x:v>
+        <x:v>-9286</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1518,7 +1518,7 @@
         <x:v>42965</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.115628659146493</x:v>
+        <x:v>0.112145107651734</x:v>
       </x:c>
       <x:c r="H34" s="0">
         <x:v>-9541</x:v>
@@ -1532,25 +1532,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>29182</x:v>
+        <x:v>1856</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>41336</x:v>
+        <x:v>15311</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>70518</x:v>
+        <x:v>17167</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.189780095093504</x:v>
+        <x:v>0.0448084502049882</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-12154</x:v>
+        <x:v>-13455</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1561,25 +1561,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>1856</x:v>
+        <x:v>29188</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>14031</x:v>
+        <x:v>43442</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>15887</x:v>
+        <x:v>72630</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.0427555570315452</x:v>
+        <x:v>0.189575216309681</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-12175</x:v>
+        <x:v>-14254</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1596,19 +1596,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>254513</x:v>
+        <x:v>254921</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>480870</x:v>
+        <x:v>481278</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>1.29413134699812</x:v>
+        <x:v>1.25620791622044</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-28156</x:v>
+        <x:v>-28564</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1619,25 +1619,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>29618</x:v>
+        <x:v>29690</x:v>
       </x:c>
       <x:c r="C38" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>80837</x:v>
+        <x:v>89810</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>110455</x:v>
+        <x:v>119500</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.297259712464237</x:v>
+        <x:v>0.311912960884027</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-51219</x:v>
+        <x:v>-60120</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1648,25 +1648,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>37389</x:v>
+        <x:v>39389</x:v>
       </x:c>
       <x:c r="C39" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>98539</x:v>
+        <x:v>109582</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>135928</x:v>
+        <x:v>148971</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.365813391841372</x:v>
+        <x:v>0.388836700383718</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-61150</x:v>
+        <x:v>-70193</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1677,25 +1677,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>253417</x:v>
+        <x:v>12900</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>317695</x:v>
+        <x:v>116025</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>571112</x:v>
+        <x:v>128925</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>1.53699324525712</x:v>
+        <x:v>0.33651362746421</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-64278</x:v>
+        <x:v>-103125</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1706,25 +1706,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>12900</x:v>
+        <x:v>253489</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>115106</x:v>
+        <x:v>369496</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>128006</x:v>
+        <x:v>622985</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.344493474751682</x:v>
+        <x:v>1.62608448482289</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-102206</x:v>
+        <x:v>-116007</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1735,25 +1735,25 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>71197</x:v>
+        <x:v>72645</x:v>
       </x:c>
       <x:c r="C42" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>245774</x:v>
+        <x:v>290824</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>316971</x:v>
+        <x:v>363469</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.853041585437522</x:v>
+        <x:v>0.948708719494195</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-174577</x:v>
+        <x:v>-218179</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1764,25 +1764,25 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>100114</x:v>
+        <x:v>40209</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>323532</x:v>
+        <x:v>310749</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>423646</x:v>
+        <x:v>350958</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>1.14012845182766</x:v>
+        <x:v>0.916053129087332</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-223418</x:v>
+        <x:v>-270540</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1793,25 +1793,25 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>24173</x:v>
+        <x:v>251062</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>288264</x:v>
+        <x:v>566905</x:v>
       </x:c>
       <x:c r="E44" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>312437</x:v>
+        <x:v>817967</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.840839552606842</x:v>
+        <x:v>2.13501681067301</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-264091</x:v>
+        <x:v>-315843</x:v>
       </x:c>
       <x:c r="I44" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1822,25 +1822,25 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>251062</x:v>
+        <x:v>100114</x:v>
       </x:c>
       <x:c r="C45" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>566106</x:v>
+        <x:v>425007</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>817168</x:v>
+        <x:v>525121</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>2.19918631764044</x:v>
+        <x:v>1.37064473583582</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-315044</x:v>
+        <x:v>-324893</x:v>
       </x:c>
       <x:c r="I45" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1857,19 +1857,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>521005</x:v>
+        <x:v>521032</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>522675</x:v>
+        <x:v>522702</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.40663818036526</x:v>
+        <x:v>1.36433078225943</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-519335</x:v>
+        <x:v>-519362</x:v>
       </x:c>
       <x:c r="I46" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1886,19 +1886,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1043523</x:v>
+        <x:v>1043746</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1161731</x:v>
+        <x:v>1161954</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>3.12648429696066</x:v>
+        <x:v>3.03287458201706</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-925315</x:v>
+        <x:v>-925538</x:v>
       </x:c>
       <x:c r="I47" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1915,19 +1915,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>2023535</x:v>
+        <x:v>2023562</x:v>
       </x:c>
       <x:c r="E48" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>2184825</x:v>
+        <x:v>2184852</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>5.87986466239352</x:v>
+        <x:v>5.70279210387772</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-1862245</x:v>
+        <x:v>-1862272</x:v>
       </x:c>
       <x:c r="I48" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1944,19 +1944,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>1951001</x:v>
+        <x:v>1984495</x:v>
       </x:c>
       <x:c r="E49" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>1987487</x:v>
+        <x:v>2020981</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>5.34878289028481</x:v>
+        <x:v>5.27506416401976</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-1914515</x:v>
+        <x:v>-1948009</x:v>
       </x:c>
       <x:c r="I49" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1967,25 +1967,25 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>2369290</x:v>
+        <x:v>2369405</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>4437043</x:v>
+        <x:v>4443849</x:v>
       </x:c>
       <x:c r="E50" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>6806333</x:v>
+        <x:v>6813254</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>18.3174015709189</x:v>
+        <x:v>17.7836169740162</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-2067753</x:v>
+        <x:v>-2074444</x:v>
       </x:c>
       <x:c r="I50" s="0">
         <x:v>59.8499984741211</x:v>
@@ -2002,19 +2002,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2606555</x:v>
+        <x:v>2607077</x:v>
       </x:c>
       <x:c r="E51" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>2704685</x:v>
+        <x:v>2705207</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>7.2789270327856</x:v>
+        <x:v>7.06099686338238</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-2508425</x:v>
+        <x:v>-2508947</x:v>
       </x:c>
       <x:c r="I51" s="0">
         <x:v>59.8499984741211</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -49,105 +49,105 @@
     <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
@@ -160,16 +160,16 @@
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
-    <x:t>IS</x:t>
+    <x:t>ATA</x:t>
   </x:si>
   <x:si>
     <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
   </x:si>
   <x:si>
     <x:t>INVEST AZ</x:t>
@@ -581,19 +581,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>524442</x:v>
+        <x:v>524702</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>5102392</x:v>
+        <x:v>5102652</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>13.3180100109705</x:v>
+        <x:v>12.6501429937996</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>4053508</x:v>
+        <x:v>4053248</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>59.8499984741211</x:v>
@@ -610,19 +610,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1041687</x:v>
+        <x:v>1041775</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>5098891</x:v>
+        <x:v>5098979</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>13.3088718747692</x:v>
+        <x:v>12.641037145465</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>3015517</x:v>
+        <x:v>3015429</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>59.8499984741211</x:v>
@@ -633,25 +633,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>2319719</x:v>
+        <x:v>2331576</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>588714</x:v>
+        <x:v>700428</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>2908433</x:v>
+        <x:v>3032004</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.59144726830805</x:v>
+        <x:v>7.51673525017432</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>1731005</x:v>
+        <x:v>1631148</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>59.8499984741211</x:v>
@@ -662,25 +662,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>904357</x:v>
+        <x:v>1032851</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>1930</x:v>
+        <x:v>53888</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>906287</x:v>
+        <x:v>1086739</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.36554528519416</x:v>
+        <x:v>2.69416839457969</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>902427</x:v>
+        <x:v>978963</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>59.8499984741211</x:v>
@@ -691,25 +691,25 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>589661</x:v>
+        <x:v>904357</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>52689</x:v>
+        <x:v>2036</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>642350</x:v>
+        <x:v>906393</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.6766300453879</x:v>
+        <x:v>2.24706702682821</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>536972</x:v>
+        <x:v>902321</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>59.8499984741211</x:v>
@@ -720,25 +720,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>912093</x:v>
+        <x:v>922521</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>467927</x:v>
+        <x:v>510238</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1380020</x:v>
+        <x:v>1432759</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>3.60205961739895</x:v>
+        <x:v>3.55199731936518</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>444166</x:v>
+        <x:v>412283</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>59.8499984741211</x:v>
@@ -749,25 +749,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>315868</x:v>
+        <x:v>252167</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>168796</x:v>
+        <x:v>125755</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>484664</x:v>
+        <x:v>377922</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>1.2650458851372</x:v>
+        <x:v>0.936918163437904</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>147072</x:v>
+        <x:v>126412</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>59.8499984741211</x:v>
@@ -778,25 +778,25 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>167070</x:v>
+        <x:v>315868</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>33686</x:v>
+        <x:v>203850</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>200756</x:v>
+        <x:v>519718</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.524003333683963</x:v>
+        <x:v>1.28844902933838</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>133384</x:v>
+        <x:v>112018</x:v>
       </x:c>
       <x:c r="I9" s="0">
         <x:v>59.8499984741211</x:v>
@@ -807,25 +807,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>269815</x:v>
+        <x:v>106287</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>175971</x:v>
+        <x:v>14463</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>445786</x:v>
+        <x:v>120750</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.16356846176273</x:v>
+        <x:v>0.299355073891245</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>93844</x:v>
+        <x:v>91824</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>59.8499984741211</x:v>
@@ -836,25 +836,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>106215</x:v>
+        <x:v>71084</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>13301</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>119516</x:v>
+        <x:v>71084</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.311954723288831</x:v>
+        <x:v>0.176226551324929</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>92914</x:v>
+        <x:v>71084</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>59.8499984741211</x:v>
@@ -865,25 +865,25 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>71000</x:v>
+        <x:v>269815</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>0</x:v>
+        <x:v>214689</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>71000</x:v>
+        <x:v>484504</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.185320671320217</x:v>
+        <x:v>1.20114890865924</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>71000</x:v>
+        <x:v>55126</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>59.8499984741211</x:v>
@@ -894,25 +894,25 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>141100</x:v>
+        <x:v>50113</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>75692</x:v>
+        <x:v>26253</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>216792</x:v>
+        <x:v>76366</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.56585970389933</x:v>
+        <x:v>0.189321321513696</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>65408</x:v>
+        <x:v>23860</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>59.8499984741211</x:v>
@@ -923,25 +923,25 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>401273</x:v>
+        <x:v>20347</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>354895</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>756168</x:v>
+        <x:v>20347</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>1.97371213226571</x:v>
+        <x:v>0.0504428794075789</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>46378</x:v>
+        <x:v>20347</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>59.8499984741211</x:v>
@@ -952,25 +952,25 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>164330</x:v>
+        <x:v>167070</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>118683</x:v>
+        <x:v>150562</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>283013</x:v>
+        <x:v>317632</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.738706466934486</x:v>
+        <x:v>0.787451352631253</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>45647</x:v>
+        <x:v>16508</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>59.8499984741211</x:v>
@@ -981,25 +981,25 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>20347</x:v>
+        <x:v>156203</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>0</x:v>
+        <x:v>142525</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>20347</x:v>
+        <x:v>298728</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.0531087281598936</x:v>
+        <x:v>0.740585859324089</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>20347</x:v>
+        <x:v>13678</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1010,25 +1010,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>26528</x:v>
+        <x:v>7587</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>17143</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>43671</x:v>
+        <x:v>7615</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.113987873763735</x:v>
+        <x:v>0.0188785829207605</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>9385</x:v>
+        <x:v>7559</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1039,25 +1039,25 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>5714</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>28</x:v>
+        <x:v>21116</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>5742</x:v>
+        <x:v>45116</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.014987483024235</x:v>
+        <x:v>0.111848476303747</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>5686</x:v>
+        <x:v>2884</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1068,25 +1068,25 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>24000</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>20708</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>44708</x:v>
+        <x:v>30000</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.11669459962513</x:v>
+        <x:v>0.0743739314015514</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>3292</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1097,25 +1097,25 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>16000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>14000</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>30000</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0783045090085422</x:v>
+        <x:v>6.69365382613963E-05</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>2000</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1141,7 +1141,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>7.0474058107688E-05</x:v>
+        <x:v>6.69365382613963E-05</x:v>
       </x:c>
       <x:c r="H21" s="0">
         <x:v>-27</x:v>
@@ -1161,19 +1161,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>27</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="E22" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>27</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>7.0474058107688E-05</x:v>
+        <x:v>0.000733822789828641</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-27</x:v>
+        <x:v>-296</x:v>
       </x:c>
       <x:c r="I22" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1184,25 +1184,25 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>226</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>226</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.000589893967864352</x:v>
+        <x:v>0.000783405410763008</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-226</x:v>
+        <x:v>-298</x:v>
       </x:c>
       <x:c r="I23" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1213,25 +1213,25 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>0</x:v>
+        <x:v>4100</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>269</x:v>
+        <x:v>4581</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>269</x:v>
+        <x:v>8681</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.000702130430776595</x:v>
+        <x:v>0.0215213366165623</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-269</x:v>
+        <x:v>-481</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1242,25 +1242,25 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>4100</x:v>
+        <x:v>33417</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>4554</x:v>
+        <x:v>34018</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>8654</x:v>
+        <x:v>67435</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0225882406986642</x:v>
+        <x:v>0.167180202135454</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-454</x:v>
+        <x:v>-601</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1271,25 +1271,25 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>33417</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>34018</x:v>
+        <x:v>1713</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>67435</x:v>
+        <x:v>1736</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.176015485499702</x:v>
+        <x:v>0.00430377149710311</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-601</x:v>
+        <x:v>-1690</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1300,25 +1300,25 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>23</x:v>
+        <x:v>43233</x:v>
       </x:c>
       <x:c r="C27" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1653</x:v>
+        <x:v>46302</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1676</x:v>
+        <x:v>89535</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00437461190327723</x:v>
+        <x:v>0.22196899826793</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1630</x:v>
+        <x:v>-3069</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1335,19 +1335,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>4218</x:v>
+        <x:v>4436</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>5498</x:v>
+        <x:v>5716</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0143506063509655</x:v>
+        <x:v>0.0141707130630423</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-2938</x:v>
+        <x:v>-3156</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1364,19 +1364,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>3019</x:v>
+        <x:v>3264</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>3019</x:v>
+        <x:v>3264</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.00788004375655964</x:v>
+        <x:v>0.0080918837364888</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-3019</x:v>
+        <x:v>-3264</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1387,25 +1387,25 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>168120</x:v>
+        <x:v>2078</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>173534</x:v>
+        <x:v>5760</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>341654</x:v>
+        <x:v>7838</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.891768290693483</x:v>
+        <x:v>0.0194314291441787</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-5414</x:v>
+        <x:v>-3682</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1416,25 +1416,25 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>0</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>5555</x:v>
+        <x:v>9734</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>5555</x:v>
+        <x:v>10106</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0144993849180817</x:v>
+        <x:v>0.025054098358136</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-5555</x:v>
+        <x:v>-9362</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1451,19 +1451,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>7221</x:v>
+        <x:v>10410</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>7222</x:v>
+        <x:v>10411</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0188505054686564</x:v>
+        <x:v>0.0258102333273851</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-7220</x:v>
+        <x:v>-10409</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1474,25 +1474,25 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>0</x:v>
+        <x:v>2889</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>0</x:v>
+        <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>9286</x:v>
+        <x:v>17057</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>9286</x:v>
+        <x:v>19946</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0242378556884441</x:v>
+        <x:v>0.0494487478578448</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-9286</x:v>
+        <x:v>-14168</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1503,25 +1503,25 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>16712</x:v>
+        <x:v>30219</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>26253</x:v>
+        <x:v>47157</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>42965</x:v>
+        <x:v>77376</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.112145107651734</x:v>
+        <x:v>0.191825243870882</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-9541</x:v>
+        <x:v>-16938</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1532,25 +1532,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>1856</x:v>
+        <x:v>170103</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>15311</x:v>
+        <x:v>188975</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>17167</x:v>
+        <x:v>359078</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.0448084502049882</x:v>
+        <x:v>0.890201417993543</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-13455</x:v>
+        <x:v>-18872</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1561,25 +1561,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>29188</x:v>
+        <x:v>226357</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>43442</x:v>
+        <x:v>255319</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>72630</x:v>
+        <x:v>481676</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.189575216309681</x:v>
+        <x:v>1.19413792605912</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-14254</x:v>
+        <x:v>-28962</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1590,25 +1590,25 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>226357</x:v>
+        <x:v>402083</x:v>
       </x:c>
       <x:c r="C37" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>254921</x:v>
+        <x:v>442298</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>481278</x:v>
+        <x:v>844381</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>1.25620791622044</x:v>
+        <x:v>2.09333115235911</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-28564</x:v>
+        <x:v>-40215</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1619,25 +1619,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>29690</x:v>
+        <x:v>32133</x:v>
       </x:c>
       <x:c r="C38" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>89810</x:v>
+        <x:v>96129</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>119500</x:v>
+        <x:v>128262</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.311912960884027</x:v>
+        <x:v>0.317978306314193</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-60120</x:v>
+        <x:v>-63996</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1648,25 +1648,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>39389</x:v>
+        <x:v>51943</x:v>
       </x:c>
       <x:c r="C39" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>109582</x:v>
+        <x:v>117267</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>148971</x:v>
+        <x:v>169210</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.388836700383718</x:v>
+        <x:v>0.419493764415217</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-70193</x:v>
+        <x:v>-65324</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1677,25 +1677,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>12900</x:v>
+        <x:v>21033</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>116025</x:v>
+        <x:v>116779</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>128925</x:v>
+        <x:v>137812</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.33651362746421</x:v>
+        <x:v>0.341654007810354</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-103125</x:v>
+        <x:v>-95746</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1706,25 +1706,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>253489</x:v>
+        <x:v>261618</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>369496</x:v>
+        <x:v>399905</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>622985</x:v>
+        <x:v>661523</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>1.62608448482289</x:v>
+        <x:v>1.64000220741828</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-116007</x:v>
+        <x:v>-138287</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1735,25 +1735,25 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>72645</x:v>
+        <x:v>114499</x:v>
       </x:c>
       <x:c r="C42" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>290824</x:v>
+        <x:v>324530</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>363469</x:v>
+        <x:v>439029</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.948708719494195</x:v>
+        <x:v>1.08841042430972</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-218179</x:v>
+        <x:v>-210031</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1764,25 +1764,25 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>40209</x:v>
+        <x:v>86822</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>310749</x:v>
+        <x:v>314001</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>350958</x:v>
+        <x:v>400823</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.916053129087332</x:v>
+        <x:v>0.993692743538802</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-270540</x:v>
+        <x:v>-227179</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1793,25 +1793,25 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>251062</x:v>
+        <x:v>140414</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>566905</x:v>
+        <x:v>426312</x:v>
       </x:c>
       <x:c r="E44" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>817967</x:v>
+        <x:v>566726</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>2.13501681067301</x:v>
+        <x:v>1.40498802158252</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-315843</x:v>
+        <x:v>-285898</x:v>
       </x:c>
       <x:c r="I44" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1822,25 +1822,25 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>100114</x:v>
+        <x:v>252062</x:v>
       </x:c>
       <x:c r="C45" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>425007</x:v>
+        <x:v>585285</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>525121</x:v>
+        <x:v>837347</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.37064473583582</x:v>
+        <x:v>2.0758929445765</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-324893</x:v>
+        <x:v>-333223</x:v>
       </x:c>
       <x:c r="I45" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1857,19 +1857,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>521032</x:v>
+        <x:v>521437</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>522702</x:v>
+        <x:v>523107</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.36433078225943</x:v>
+        <x:v>1.29685080445571</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-519362</x:v>
+        <x:v>-519767</x:v>
       </x:c>
       <x:c r="I46" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1886,19 +1886,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1043746</x:v>
+        <x:v>1177425</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1161954</x:v>
+        <x:v>1295633</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>3.03287458201706</x:v>
+        <x:v>3.21204399545288</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-925538</x:v>
+        <x:v>-1059217</x:v>
       </x:c>
       <x:c r="I47" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1915,19 +1915,19 @@
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>2023562</x:v>
+        <x:v>2023643</x:v>
       </x:c>
       <x:c r="E48" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>2184852</x:v>
+        <x:v>2184933</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>5.70279210387772</x:v>
+        <x:v>5.41673523529953</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-1862272</x:v>
+        <x:v>-1862353</x:v>
       </x:c>
       <x:c r="I48" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1938,25 +1938,25 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>36486</x:v>
+        <x:v>39606</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>1984495</x:v>
+        <x:v>1988059</x:v>
       </x:c>
       <x:c r="E49" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>2020981</x:v>
+        <x:v>2027665</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>5.27506416401976</x:v>
+        <x:v>5.02684725384423</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-1948009</x:v>
+        <x:v>-1948453</x:v>
       </x:c>
       <x:c r="I49" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1967,25 +1967,25 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>2369405</x:v>
+        <x:v>2489493</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>4443849</x:v>
+        <x:v>4652188</x:v>
       </x:c>
       <x:c r="E50" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>6813254</x:v>
+        <x:v>7141681</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>17.7836169740162</x:v>
+        <x:v>17.7051630928588</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-2074444</x:v>
+        <x:v>-2162695</x:v>
       </x:c>
       <x:c r="I50" s="0">
         <x:v>59.8499984741211</x:v>
@@ -1996,25 +1996,25 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>98130</x:v>
+        <x:v>198402</x:v>
       </x:c>
       <x:c r="C51" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2607077</x:v>
+        <x:v>2607408</x:v>
       </x:c>
       <x:c r="E51" s="0">
         <x:v>59.8499984741211</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>2705207</x:v>
+        <x:v>2805810</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>7.06099686338238</x:v>
+        <x:v>6.9559706821929</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-2508947</x:v>
+        <x:v>-2409006</x:v>
       </x:c>
       <x:c r="I51" s="0">
         <x:v>59.8499984741211</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -40,154 +40,154 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -575,28 +575,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>4577950</x:v>
+        <x:v>1091803</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>524702</x:v>
+        <x:v>226716</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>5102652</x:v>
+        <x:v>1318519</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>12.6501429937996</x:v>
+        <x:v>11.8765979356185</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>4053248</x:v>
+        <x:v>865087</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -604,28 +604,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>4057204</x:v>
+        <x:v>1577641</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1041775</x:v>
+        <x:v>823234</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>5098979</x:v>
+        <x:v>2400875</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>12.641037145465</x:v>
+        <x:v>21.6259508347457</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>3015429</x:v>
+        <x:v>754407</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -633,28 +633,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>2331576</x:v>
+        <x:v>172440</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>700428</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>3032004</x:v>
+        <x:v>172440</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.51673525017432</x:v>
+        <x:v>1.55325827539691</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>1631148</x:v>
+        <x:v>172440</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -662,28 +662,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>1032851</x:v>
+        <x:v>167102</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>53888</x:v>
+        <x:v>47432</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>1086739</x:v>
+        <x:v>214534</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.69416839457969</x:v>
+        <x:v>1.93242119493157</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>978963</x:v>
+        <x:v>119670</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -691,28 +691,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>904357</x:v>
+        <x:v>114458</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>2036</x:v>
+        <x:v>12656</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>906393</x:v>
+        <x:v>127114</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>2.24706702682821</x:v>
+        <x:v>1.14498302260962</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>902321</x:v>
+        <x:v>101802</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -720,28 +720,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>922521</x:v>
+        <x:v>173412</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>510238</x:v>
+        <x:v>72453</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1432759</x:v>
+        <x:v>245865</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>3.55199731936518</x:v>
+        <x:v>2.2146360814223</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>412283</x:v>
+        <x:v>100959</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -749,28 +749,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>252167</x:v>
+        <x:v>94365</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>125755</x:v>
+        <x:v>6663</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>377922</x:v>
+        <x:v>101028</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.936918163437904</x:v>
+        <x:v>0.91001262495244</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>126412</x:v>
+        <x:v>87702</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -778,28 +778,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>315868</x:v>
+        <x:v>80000</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>203850</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>519718</x:v>
+        <x:v>82027</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.28844902933838</x:v>
+        <x:v>0.738860569218175</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>112018</x:v>
+        <x:v>77973</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -807,28 +807,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>106287</x:v>
+        <x:v>60904</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>14463</x:v>
+        <x:v>10747</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>120750</x:v>
+        <x:v>71651</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.299355073891245</x:v>
+        <x:v>0.645398449840315</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>91824</x:v>
+        <x:v>50157</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -836,28 +836,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>71084</x:v>
+        <x:v>64272</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>0</x:v>
+        <x:v>19968</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>71084</x:v>
+        <x:v>84240</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.176226551324929</x:v>
+        <x:v>0.758794230569679</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>71084</x:v>
+        <x:v>44304</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -865,28 +865,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>269815</x:v>
+        <x:v>44116</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>214689</x:v>
+        <x:v>7715</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>484504</x:v>
+        <x:v>51831</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>1.20114890865924</x:v>
+        <x:v>0.466869227975511</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>55126</x:v>
+        <x:v>36401</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -894,28 +894,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>50113</x:v>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>26253</x:v>
+        <x:v>3278</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>76366</x:v>
+        <x:v>38278</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.189321321513696</x:v>
+        <x:v>0.344790189431935</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>23860</x:v>
+        <x:v>31722</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -923,28 +923,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>20347</x:v>
+        <x:v>21885</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>0</x:v>
+        <x:v>3260</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>20347</x:v>
+        <x:v>25145</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.0504428794075789</x:v>
+        <x:v>0.226494313006583</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>20347</x:v>
+        <x:v>18625</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -952,28 +952,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>167070</x:v>
+        <x:v>23291</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>150562</x:v>
+        <x:v>11805</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>317632</x:v>
+        <x:v>35096</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.787451352631253</x:v>
+        <x:v>0.316128232621955</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>16508</x:v>
+        <x:v>11486</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -981,28 +981,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>156203</x:v>
+        <x:v>8001</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>142525</x:v>
+        <x:v>1224</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>298728</x:v>
+        <x:v>9225</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.740585859324089</x:v>
+        <x:v>0.083094453668154</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>13678</x:v>
+        <x:v>6777</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1010,28 +1010,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>7587</x:v>
+        <x:v>16941</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>28</x:v>
+        <x:v>15116</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>7615</x:v>
+        <x:v>32057</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0188785829207605</x:v>
+        <x:v>0.288754352437942</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>7559</x:v>
+        <x:v>1825</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1039,28 +1039,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>24000</x:v>
+        <x:v>8352</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>21116</x:v>
+        <x:v>6697</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>45116</x:v>
+        <x:v>15049</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.111848476303747</x:v>
+        <x:v>0.135554301707539</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>2884</x:v>
+        <x:v>1655</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,28 +1068,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>16000</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>14000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>30000</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.0743739314015514</x:v>
+        <x:v>9.00752885291642E-06</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>2000</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1106,19 +1106,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F20" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>6.69365382613963E-05</x:v>
+        <x:v>0.000243203279028743</x:v>
       </x:c>
       <x:c r="H20" s="0">
         <x:v>-27</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1132,22 +1132,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>27</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>27</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>6.69365382613963E-05</x:v>
+        <x:v>0.000756632423644979</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-27</x:v>
+        <x:v>-84</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1161,22 +1161,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>296</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>296</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.000733822789828641</x:v>
+        <x:v>0.00255813819422826</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-296</x:v>
+        <x:v>-284</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1184,28 +1184,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>307</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>316</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.000783405410763008</x:v>
+        <x:v>0.00744922636136188</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-298</x:v>
+        <x:v>-827</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1213,28 +1213,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>4100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>4581</x:v>
+        <x:v>2860</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>8681</x:v>
+        <x:v>2860</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0215213366165623</x:v>
+        <x:v>0.025761532519341</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-481</x:v>
+        <x:v>-2860</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1242,28 +1242,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>33417</x:v>
+        <x:v>1230</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>34018</x:v>
+        <x:v>4143</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>67435</x:v>
+        <x:v>5373</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.167180202135454</x:v>
+        <x:v>0.0483974525267199</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-601</x:v>
+        <x:v>-2913</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1271,28 +1271,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>23</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1713</x:v>
+        <x:v>3005</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1736</x:v>
+        <x:v>3005</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00430377149710311</x:v>
+        <x:v>0.0270676242030138</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-1690</x:v>
+        <x:v>-3005</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1300,28 +1300,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>43233</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>46302</x:v>
+        <x:v>3609</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>89535</x:v>
+        <x:v>3609</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.22196899826793</x:v>
+        <x:v>0.0325081716301754</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-3069</x:v>
+        <x:v>-3609</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1329,28 +1329,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>1280</x:v>
+        <x:v>2540</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>4436</x:v>
+        <x:v>7136</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>5716</x:v>
+        <x:v>9676</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0141707130630423</x:v>
+        <x:v>0.0871568491808193</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-3156</x:v>
+        <x:v>-4596</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1358,28 +1358,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>0</x:v>
+        <x:v>1413</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>3264</x:v>
+        <x:v>7709</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>3264</x:v>
+        <x:v>9122</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0080918837364888</x:v>
+        <x:v>0.0821666781963036</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-3264</x:v>
+        <x:v>-6296</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1387,28 +1387,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>2078</x:v>
+        <x:v>48403</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>5760</x:v>
+        <x:v>55190</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>7838</x:v>
+        <x:v>103593</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0194314291441787</x:v>
+        <x:v>0.933116936460171</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-3682</x:v>
+        <x:v>-6787</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1416,28 +1416,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>372</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>9734</x:v>
+        <x:v>22560</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>10106</x:v>
+        <x:v>33560</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.025054098358136</x:v>
+        <x:v>0.302292668303875</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-9362</x:v>
+        <x:v>-11560</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1445,28 +1445,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>1</x:v>
+        <x:v>198263</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>10410</x:v>
+        <x:v>212332</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>10411</x:v>
+        <x:v>410595</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0258102333273851</x:v>
+        <x:v>3.69844630936322</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-10409</x:v>
+        <x:v>-14069</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1474,28 +1474,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>2889</x:v>
+        <x:v>1448</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>17057</x:v>
+        <x:v>17091</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>19946</x:v>
+        <x:v>18539</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0494487478578448</x:v>
+        <x:v>0.166990577404218</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-14168</x:v>
+        <x:v>-15643</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1503,28 +1503,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>30219</x:v>
+        <x:v>6547</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>47157</x:v>
+        <x:v>31684</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>77376</x:v>
+        <x:v>38231</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.191825243870882</x:v>
+        <x:v>0.344366835575848</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-16938</x:v>
+        <x:v>-25137</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1532,28 +1532,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>170103</x:v>
+        <x:v>4898</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>188975</x:v>
+        <x:v>33253</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>359078</x:v>
+        <x:v>38151</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.890201417993543</x:v>
+        <x:v>0.343646233267614</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-18872</x:v>
+        <x:v>-28355</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1561,28 +1561,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>226357</x:v>
+        <x:v>26484</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>255319</x:v>
+        <x:v>58597</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>481676</x:v>
+        <x:v>85081</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>1.19413792605912</x:v>
+        <x:v>0.766369562334982</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-28962</x:v>
+        <x:v>-32113</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1590,28 +1590,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>402083</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>442298</x:v>
+        <x:v>33457</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>844381</x:v>
+        <x:v>33457</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>2.09333115235911</x:v>
+        <x:v>0.301364892832025</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-40215</x:v>
+        <x:v>-33457</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1619,28 +1619,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>32133</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>96129</x:v>
+        <x:v>38595</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>128262</x:v>
+        <x:v>38595</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.317978306314193</x:v>
+        <x:v>0.347645576078309</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-63996</x:v>
+        <x:v>-38595</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1648,28 +1648,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>51943</x:v>
+        <x:v>173986</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>117267</x:v>
+        <x:v>213716</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>169210</x:v>
+        <x:v>387702</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.419493764415217</x:v>
+        <x:v>3.4922369513334</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-65324</x:v>
+        <x:v>-39730</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1677,28 +1677,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>21033</x:v>
+        <x:v>164315</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>116779</x:v>
+        <x:v>218603</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>137812</x:v>
+        <x:v>382918</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.341654007810354</x:v>
+        <x:v>3.44914493330105</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-95746</x:v>
+        <x:v>-54288</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1706,28 +1706,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>261618</x:v>
+        <x:v>64125</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>399905</x:v>
+        <x:v>127969</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>661523</x:v>
+        <x:v>192094</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>1.64000220741828</x:v>
+        <x:v>1.73029224747213</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-138287</x:v>
+        <x:v>-63844</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1735,28 +1735,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>114499</x:v>
+        <x:v>35958</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>324530</x:v>
+        <x:v>105352</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>439029</x:v>
+        <x:v>141310</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.08841042430972</x:v>
+        <x:v>1.27285390220562</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-210031</x:v>
+        <x:v>-69394</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1764,28 +1764,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>86822</x:v>
+        <x:v>29390</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>314001</x:v>
+        <x:v>106383</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>400823</x:v>
+        <x:v>135773</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.993692743538802</x:v>
+        <x:v>1.22297921494702</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-227179</x:v>
+        <x:v>-76993</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1793,28 +1793,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>140414</x:v>
+        <x:v>29033</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>426312</x:v>
+        <x:v>112257</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>566726</x:v>
+        <x:v>141290</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>1.40498802158252</x:v>
+        <x:v>1.27267375162856</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-285898</x:v>
+        <x:v>-83224</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1822,28 +1822,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>252062</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>585285</x:v>
+        <x:v>134771</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>837347</x:v>
+        <x:v>134771</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>2.0758929445765</x:v>
+        <x:v>1.2139536710364</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-333223</x:v>
+        <x:v>-134771</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1851,28 +1851,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>1670</x:v>
+        <x:v>69079</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>521437</x:v>
+        <x:v>262134</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>523107</x:v>
+        <x:v>331213</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.29685080445571</x:v>
+        <x:v>2.98341065396101</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-519767</x:v>
+        <x:v>-193055</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1880,28 +1880,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>118208</x:v>
+        <x:v>456047</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1177425</x:v>
+        <x:v>683623</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1295633</x:v>
+        <x:v>1139670</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>3.21204399545288</x:v>
+        <x:v>10.2656104078033</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-1059217</x:v>
+        <x:v>-227576</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1909,28 +1909,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>161290</x:v>
+        <x:v>150888</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>2023643</x:v>
+        <x:v>391334</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>2184933</x:v>
+        <x:v>542222</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>5.41673523529953</x:v>
+        <x:v>4.88408030968605</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-1862353</x:v>
+        <x:v>-240446</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1938,28 +1938,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>39606</x:v>
+        <x:v>52233</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>1988059</x:v>
+        <x:v>308757</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>2027665</x:v>
+        <x:v>360990</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>5.02684725384423</x:v>
+        <x:v>3.2516278406143</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-1948453</x:v>
+        <x:v>-256524</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1967,28 +1967,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>2489493</x:v>
+        <x:v>90184</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>4652188</x:v>
+        <x:v>352086</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>7141681</x:v>
+        <x:v>442270</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>17.7051630928588</x:v>
+        <x:v>3.98375978577935</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-2162695</x:v>
+        <x:v>-261902</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1996,28 +1996,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>198402</x:v>
+        <x:v>179464</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2607408</x:v>
+        <x:v>730493</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>2805810</x:v>
+        <x:v>909957</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>6.9559706821929</x:v>
+        <x:v>8.19646393241327</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-2409006</x:v>
+        <x:v>-551029</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>59.8499984741211</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -55,55 +55,61 @@
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
+    <x:t>DESTEK</x:t>
   </x:si>
   <x:si>
     <x:t>ACAR</x:t>
@@ -112,9 +118,6 @@
     <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
@@ -124,48 +127,48 @@
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>OYAK</x:t>
   </x:si>
   <x:si>
-    <x:t>PUSULA YAT.</x:t>
+    <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
@@ -175,16 +178,13 @@
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
-    <x:t>A1 CAPITAL</x:t>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
     <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
@@ -575,25 +575,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1091803</x:v>
+        <x:v>1092803</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>226716</x:v>
+        <x:v>294618</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>1318519</x:v>
+        <x:v>1387421</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>11.8765979356185</x:v>
+        <x:v>11.1543778220173</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>865087</x:v>
+        <x:v>798185</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>65.8000030517578</x:v>
@@ -604,25 +604,25 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1577641</x:v>
+        <x:v>1617114</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>823234</x:v>
+        <x:v>846483</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>2400875</x:v>
+        <x:v>2463597</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>21.6259508347457</x:v>
+        <x:v>19.8064550984801</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>754407</x:v>
+        <x:v>770631</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>65.8000030517578</x:v>
@@ -633,7 +633,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>172440</x:v>
+        <x:v>222893</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>65.8000030517578</x:v>
@@ -645,13 +645,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>172440</x:v>
+        <x:v>222893</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>1.55325827539691</x:v>
+        <x:v>1.79198147922145</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>172440</x:v>
+        <x:v>222893</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>65.8000030517578</x:v>
@@ -668,19 +668,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>47432</x:v>
+        <x:v>47459</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>214534</x:v>
+        <x:v>214561</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.93242119493157</x:v>
+        <x:v>1.7249951239529</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>119670</x:v>
+        <x:v>119643</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>65.8000030517578</x:v>
@@ -691,25 +691,25 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>114458</x:v>
+        <x:v>114637</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>12656</x:v>
+        <x:v>12815</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>127114</x:v>
+        <x:v>127452</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.14498302260962</x:v>
+        <x:v>1.02466934129709</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>101802</x:v>
+        <x:v>101822</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>65.8000030517578</x:v>
@@ -720,25 +720,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>173412</x:v>
+        <x:v>796392</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>72453</x:v>
+        <x:v>695726</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>245865</x:v>
+        <x:v>1492118</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>2.2146360814223</x:v>
+        <x:v>11.9961049508641</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>100959</x:v>
+        <x:v>100666</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>65.8000030517578</x:v>
@@ -749,25 +749,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>94365</x:v>
+        <x:v>97672</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>6663</x:v>
+        <x:v>3904</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>101028</x:v>
+        <x:v>101576</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.91001262495244</x:v>
+        <x:v>0.816635384392501</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>87702</x:v>
+        <x:v>93768</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>65.8000030517578</x:v>
@@ -778,25 +778,25 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>80000</x:v>
+        <x:v>94365</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>2027</x:v>
+        <x:v>7329</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>82027</x:v>
+        <x:v>101694</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.738860569218175</x:v>
+        <x:v>0.817584062971676</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>77973</x:v>
+        <x:v>87036</x:v>
       </x:c>
       <x:c r="I9" s="0">
         <x:v>65.8000030517578</x:v>
@@ -807,25 +807,25 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>60904</x:v>
+        <x:v>97108</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>10747</x:v>
+        <x:v>13001</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>71651</x:v>
+        <x:v>110109</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.645398449840315</x:v>
+        <x:v>0.88523770910524</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>50157</x:v>
+        <x:v>84107</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>65.8000030517578</x:v>
@@ -836,25 +836,25 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>64272</x:v>
+        <x:v>80000</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>19968</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>84240</x:v>
+        <x:v>82027</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.758794230569679</x:v>
+        <x:v>0.65946828655946</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>44304</x:v>
+        <x:v>77973</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>65.8000030517578</x:v>
@@ -865,25 +865,25 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>44116</x:v>
+        <x:v>64451</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>7715</x:v>
+        <x:v>22544</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>51831</x:v>
+        <x:v>86995</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.466869227975511</x:v>
+        <x:v>0.699409262672537</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>36401</x:v>
+        <x:v>41907</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>65.8000030517578</x:v>
@@ -894,25 +894,25 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>35000</x:v>
+        <x:v>44116</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>3278</x:v>
+        <x:v>9733</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>38278</x:v>
+        <x:v>53849</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.344790189431935</x:v>
+        <x:v>0.432927057711977</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>31722</x:v>
+        <x:v>34383</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>65.8000030517578</x:v>
@@ -923,25 +923,25 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>21885</x:v>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>3260</x:v>
+        <x:v>3407</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>25145</x:v>
+        <x:v>38407</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.226494313006583</x:v>
+        <x:v>0.308778798223624</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>18625</x:v>
+        <x:v>31593</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>65.8000030517578</x:v>
@@ -952,25 +952,25 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>23291</x:v>
+        <x:v>173412</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>11805</x:v>
+        <x:v>157898</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>35096</x:v>
+        <x:v>331310</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.316128232621955</x:v>
+        <x:v>2.66361610225919</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>11486</x:v>
+        <x:v>15514</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>65.8000030517578</x:v>
@@ -981,25 +981,25 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>8001</x:v>
+        <x:v>23291</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>1224</x:v>
+        <x:v>12254</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>9225</x:v>
+        <x:v>35545</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.083094453668154</x:v>
+        <x:v>0.285769322854133</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>6777</x:v>
+        <x:v>11037</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1010,25 +1010,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>16941</x:v>
+        <x:v>8001</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>15116</x:v>
+        <x:v>1246</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>32057</x:v>
+        <x:v>9247</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.288754352437942</x:v>
+        <x:v>0.0743426340816478</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>1825</x:v>
+        <x:v>6755</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1039,25 +1039,25 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>8352</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>6697</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>15049</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.135554301707539</x:v>
+        <x:v>8.03964897606227E-06</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>1655</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1068,25 +1068,25 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>1</x:v>
+        <x:v>8367</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>0</x:v>
+        <x:v>8382</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>1</x:v>
+        <x:v>16749</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>9.00752885291642E-06</x:v>
+        <x:v>0.134656080700067</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>1</x:v>
+        <x:v>-15</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1112,7 +1112,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.000243203279028743</x:v>
+        <x:v>0.000217070522353681</x:v>
       </x:c>
       <x:c r="H20" s="0">
         <x:v>-27</x:v>
@@ -1132,19 +1132,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>84</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>84</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.000756632423644979</x:v>
+        <x:v>0.00155165225238002</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-84</x:v>
+        <x:v>-193</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1161,19 +1161,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>284</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="E22" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>284</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.00255813819422826</x:v>
+        <x:v>0.00266916346005267</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-284</x:v>
+        <x:v>-332</x:v>
       </x:c>
       <x:c r="I22" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1199,7 +1199,7 @@
         <x:v>827</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.00744922636136188</x:v>
+        <x:v>0.00664878970320349</x:v>
       </x:c>
       <x:c r="H23" s="0">
         <x:v>-827</x:v>
@@ -1213,25 +1213,25 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>0</x:v>
+        <x:v>16941</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>2860</x:v>
+        <x:v>19413</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>2860</x:v>
+        <x:v>36354</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.025761532519341</x:v>
+        <x:v>0.292273398875768</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-2860</x:v>
+        <x:v>-2472</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1242,25 +1242,25 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>1230</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>4143</x:v>
+        <x:v>3027</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>5373</x:v>
+        <x:v>3027</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0483974525267199</x:v>
+        <x:v>0.0243360174505405</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-2913</x:v>
+        <x:v>-3027</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1277,19 +1277,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>3005</x:v>
+        <x:v>3071</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>3005</x:v>
+        <x:v>3071</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0270676242030138</x:v>
+        <x:v>0.0246897620054872</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-3005</x:v>
+        <x:v>-3071</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1300,25 +1300,25 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>0</x:v>
+        <x:v>1930</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>3609</x:v>
+        <x:v>5244</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>3609</x:v>
+        <x:v>7174</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0325081716301754</x:v>
+        <x:v>0.0576764417542707</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-3609</x:v>
+        <x:v>-3314</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1329,25 +1329,25 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>2540</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>7136</x:v>
+        <x:v>3799</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>9676</x:v>
+        <x:v>3799</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0871568491808193</x:v>
+        <x:v>0.0305426264600606</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-4596</x:v>
+        <x:v>-3799</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1358,25 +1358,25 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>1413</x:v>
+        <x:v>2940</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>7709</x:v>
+        <x:v>9662</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>9122</x:v>
+        <x:v>12602</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0821666781963036</x:v>
+        <x:v>0.101315656396337</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-6296</x:v>
+        <x:v>-6722</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1387,25 +1387,25 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>48403</x:v>
+        <x:v>1413</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>55190</x:v>
+        <x:v>9007</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>103593</x:v>
+        <x:v>10420</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.933116936460171</x:v>
+        <x:v>0.0837731423305688</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-6787</x:v>
+        <x:v>-7594</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1422,19 +1422,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>22560</x:v>
+        <x:v>24684</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>33560</x:v>
+        <x:v>35684</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.302292668303875</x:v>
+        <x:v>0.286886834061806</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-11560</x:v>
+        <x:v>-13684</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1445,25 +1445,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>198263</x:v>
+        <x:v>1448</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>212332</x:v>
+        <x:v>20628</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>410595</x:v>
+        <x:v>22076</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>3.69844630936322</x:v>
+        <x:v>0.177483290795551</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-14069</x:v>
+        <x:v>-19180</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1474,25 +1474,25 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>1448</x:v>
+        <x:v>86958</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>17091</x:v>
+        <x:v>107839</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>18539</x:v>
+        <x:v>194797</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.166990577404218</x:v>
+        <x:v>1.56609950159</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-15643</x:v>
+        <x:v>-20881</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1509,19 +1509,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>31684</x:v>
+        <x:v>32270</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>38231</x:v>
+        <x:v>38817</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.344366835575848</x:v>
+        <x:v>0.312075054303809</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-25137</x:v>
+        <x:v>-25723</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1538,19 +1538,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>33253</x:v>
+        <x:v>37965</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>38151</x:v>
+        <x:v>42863</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.343646233267614</x:v>
+        <x:v>0.344603474060957</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-28355</x:v>
+        <x:v>-33067</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1561,25 +1561,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>26484</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>58597</x:v>
+        <x:v>33485</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>85081</x:v>
+        <x:v>33485</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.766369562334982</x:v>
+        <x:v>0.269207645963445</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-32113</x:v>
+        <x:v>-33485</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1590,25 +1590,25 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>0</x:v>
+        <x:v>3039</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>33457</x:v>
+        <x:v>38811</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>33457</x:v>
+        <x:v>41850</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.301364892832025</x:v>
+        <x:v>0.336459309648206</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-33457</x:v>
+        <x:v>-35772</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1619,25 +1619,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>0</x:v>
+        <x:v>26484</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>38595</x:v>
+        <x:v>65530</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>38595</x:v>
+        <x:v>92014</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.347645576078309</x:v>
+        <x:v>0.739760260883394</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-38595</x:v>
+        <x:v>-39046</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1654,19 +1654,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>213716</x:v>
+        <x:v>213918</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>387702</x:v>
+        <x:v>387904</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>3.4922369513334</x:v>
+        <x:v>3.11861199641046</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-39730</x:v>
+        <x:v>-39932</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1677,25 +1677,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>164315</x:v>
+        <x:v>178752</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>218603</x:v>
+        <x:v>221592</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>382918</x:v>
+        <x:v>400344</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>3.44914493330105</x:v>
+        <x:v>3.21862522967267</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-54288</x:v>
+        <x:v>-42840</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1706,25 +1706,25 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>64125</x:v>
+        <x:v>48403</x:v>
       </x:c>
       <x:c r="C41" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>127969</x:v>
+        <x:v>95520</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>192094</x:v>
+        <x:v>143923</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>1.73029224747213</x:v>
+        <x:v>1.15709039958181</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-63844</x:v>
+        <x:v>-47117</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1735,25 +1735,25 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>35958</x:v>
+        <x:v>29390</x:v>
       </x:c>
       <x:c r="C42" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>105352</x:v>
+        <x:v>107264</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>141310</x:v>
+        <x:v>136654</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.27285390220562</x:v>
+        <x:v>1.09865019117481</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-69394</x:v>
+        <x:v>-77874</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1764,25 +1764,25 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>29390</x:v>
+        <x:v>198996</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>106383</x:v>
+        <x:v>277381</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>135773</x:v>
+        <x:v>476377</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>1.22297921494702</x:v>
+        <x:v>3.82990386026961</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-76993</x:v>
+        <x:v>-78385</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1793,25 +1793,25 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>29033</x:v>
+        <x:v>65170</x:v>
       </x:c>
       <x:c r="C44" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>112257</x:v>
+        <x:v>159194</x:v>
       </x:c>
       <x:c r="E44" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>141290</x:v>
+        <x:v>224364</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>1.27267375162856</x:v>
+        <x:v>1.80380780286523</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-83224</x:v>
+        <x:v>-94024</x:v>
       </x:c>
       <x:c r="I44" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1822,25 +1822,25 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>0</x:v>
+        <x:v>35643</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>134771</x:v>
+        <x:v>145788</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>134771</x:v>
+        <x:v>181431</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.2139536710364</x:v>
+        <x:v>1.45864155337595</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-134771</x:v>
+        <x:v>-110145</x:v>
       </x:c>
       <x:c r="I45" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1851,25 +1851,25 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>69079</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>262134</x:v>
+        <x:v>134933</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>331213</x:v>
+        <x:v>134933</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>2.98341065396101</x:v>
+        <x:v>1.08481395528701</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-193055</x:v>
+        <x:v>-134933</x:v>
       </x:c>
       <x:c r="I46" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1880,25 +1880,25 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>456047</x:v>
+        <x:v>69079</x:v>
       </x:c>
       <x:c r="C47" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>683623</x:v>
+        <x:v>262702</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1139670</x:v>
+        <x:v>331781</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>10.2656104078033</x:v>
+        <x:v>2.66740277692692</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-227576</x:v>
+        <x:v>-193623</x:v>
       </x:c>
       <x:c r="I47" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1909,25 +1909,25 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>150888</x:v>
+        <x:v>105627</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>391334</x:v>
+        <x:v>386451</x:v>
       </x:c>
       <x:c r="E48" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>542222</x:v>
+        <x:v>492078</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>4.88408030968605</x:v>
+        <x:v>3.95613438884277</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-240446</x:v>
+        <x:v>-280824</x:v>
       </x:c>
       <x:c r="I48" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1938,25 +1938,25 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>52233</x:v>
+        <x:v>65192</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>308757</x:v>
+        <x:v>407218</x:v>
       </x:c>
       <x:c r="E49" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>360990</x:v>
+        <x:v>472410</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.2516278406143</x:v>
+        <x:v>3.79801057278158</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-256524</x:v>
+        <x:v>-342026</x:v>
       </x:c>
       <x:c r="I49" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1967,25 +1967,25 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>90184</x:v>
+        <x:v>152096</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>352086</x:v>
+        <x:v>509190</x:v>
       </x:c>
       <x:c r="E50" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>442270</x:v>
+        <x:v>661286</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>3.98375978577935</x:v>
+        <x:v>5.31650731278431</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-261902</x:v>
+        <x:v>-357094</x:v>
       </x:c>
       <x:c r="I50" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1996,25 +1996,25 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>179464</x:v>
+        <x:v>196520</x:v>
       </x:c>
       <x:c r="C51" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>730493</x:v>
+        <x:v>743386</x:v>
       </x:c>
       <x:c r="E51" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>909957</x:v>
+        <x:v>939906</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>8.19646393241327</x:v>
+        <x:v>7.55651431049478</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-551029</x:v>
+        <x:v>-546866</x:v>
       </x:c>
       <x:c r="I51" s="0">
         <x:v>65.8000030517578</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -40,12 +40,12 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>IS</x:t>
   </x:si>
   <x:si>
-    <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
@@ -91,21 +91,21 @@
     <x:t>ANADOLU</x:t>
   </x:si>
   <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
@@ -121,10 +121,13 @@
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
-    <x:t>FIBA</x:t>
+    <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
     <x:t>PUSULA YAT.</x:t>
@@ -139,49 +142,46 @@
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEB</x:t>
   </x:si>
   <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>OYAK</x:t>
   </x:si>
   <x:si>
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>ALNUS</x:t>
+    <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
     <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
     <x:t>ZIRAAT</x:t>
@@ -575,25 +575,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1092803</x:v>
+        <x:v>1617114</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>294618</x:v>
+        <x:v>856540</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>1387421</x:v>
+        <x:v>2473654</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>11.1543778220173</x:v>
+        <x:v>18.7789400485406</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>798185</x:v>
+        <x:v>760574</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>65.8000030517578</x:v>
@@ -604,25 +604,25 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1617114</x:v>
+        <x:v>1092803</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>846483</x:v>
+        <x:v>339406</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>2463597</x:v>
+        <x:v>1432209</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>19.8064550984801</x:v>
+        <x:v>10.8727279352651</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>770631</x:v>
+        <x:v>753397</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>65.8000030517578</x:v>
@@ -648,7 +648,7 @@
         <x:v>222893</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>1.79198147922145</x:v>
+        <x:v>1.69210984407656</x:v>
       </x:c>
       <x:c r="H4" s="0">
         <x:v>222893</x:v>
@@ -677,7 +677,7 @@
         <x:v>214561</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.7249951239529</x:v>
+        <x:v>1.62885680687554</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>119643</x:v>
@@ -697,19 +697,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>12815</x:v>
+        <x:v>13289</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>127452</x:v>
+        <x:v>127926</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.02466934129709</x:v>
+        <x:v>0.971160350093263</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>101822</x:v>
+        <x:v>101348</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>65.8000030517578</x:v>
@@ -720,25 +720,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>796392</x:v>
+        <x:v>811589</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>695726</x:v>
+        <x:v>715408</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1492118</x:v>
+        <x:v>1526997</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>11.9961049508641</x:v>
+        <x:v>11.5923185365865</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>100666</x:v>
+        <x:v>96181</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>65.8000030517578</x:v>
@@ -755,19 +755,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>3904</x:v>
+        <x:v>4289</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>101576</x:v>
+        <x:v>101961</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.816635384392501</x:v>
+        <x:v>0.774044998326057</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>93768</x:v>
+        <x:v>93383</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>65.8000030517578</x:v>
@@ -784,19 +784,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>7329</x:v>
+        <x:v>7821</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>101694</x:v>
+        <x:v>102186</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.817584062971676</x:v>
+        <x:v>0.775753103627332</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>87036</x:v>
+        <x:v>86544</x:v>
       </x:c>
       <x:c r="I9" s="0">
         <x:v>65.8000030517578</x:v>
@@ -813,19 +813,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>13001</x:v>
+        <x:v>16892</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>110109</x:v>
+        <x:v>114000</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.88523770910524</x:v>
+        <x:v>0.865440019312977</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>84107</x:v>
+        <x:v>80216</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>65.8000030517578</x:v>
@@ -851,7 +851,7 @@
         <x:v>82027</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.65946828655946</x:v>
+        <x:v>0.622714460212154</x:v>
       </x:c>
       <x:c r="H11" s="0">
         <x:v>77973</x:v>
@@ -871,19 +871,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>22544</x:v>
+        <x:v>23350</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>86995</x:v>
+        <x:v>87801</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.699409262672537</x:v>
+        <x:v>0.666548238032445</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>41907</x:v>
+        <x:v>41101</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>65.8000030517578</x:v>
@@ -900,19 +900,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>9733</x:v>
+        <x:v>10719</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>53849</x:v>
+        <x:v>54835</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.432927057711977</x:v>
+        <x:v>0.416284240868659</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>34383</x:v>
+        <x:v>33397</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>65.8000030517578</x:v>
@@ -929,19 +929,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>3407</x:v>
+        <x:v>3489</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>38407</x:v>
+        <x:v>38489</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.308778798223624</x:v>
+        <x:v>0.292192288625765</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>31593</x:v>
+        <x:v>31511</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>65.8000030517578</x:v>
@@ -958,19 +958,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>157898</x:v>
+        <x:v>161949</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>331310</x:v>
+        <x:v>335361</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>2.66361610225919</x:v>
+        <x:v>2.54591956418263</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>15514</x:v>
+        <x:v>11463</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>65.8000030517578</x:v>
@@ -987,19 +987,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>12254</x:v>
+        <x:v>14109</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>35545</x:v>
+        <x:v>37400</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.285769322854133</x:v>
+        <x:v>0.283925058967591</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>11037</x:v>
+        <x:v>9182</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1016,19 +1016,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>1246</x:v>
+        <x:v>1274</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>9247</x:v>
+        <x:v>9275</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0743426340816478</x:v>
+        <x:v>0.0704118963081392</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>6755</x:v>
+        <x:v>6727</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1054,7 +1054,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>8.03964897606227E-06</x:v>
+        <x:v>7.5915791167805E-06</x:v>
       </x:c>
       <x:c r="H18" s="0">
         <x:v>1</x:v>
@@ -1068,25 +1068,25 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>8367</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>8382</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>16749</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.134656080700067</x:v>
+        <x:v>0.000204972636153074</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-15</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1103,19 +1103,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>27</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>27</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.000217070522353681</x:v>
+        <x:v>0.00172328845950917</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-27</x:v>
+        <x:v>-227</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1132,19 +1132,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>193</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>193</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.00155165225238002</x:v>
+        <x:v>0.00252040426677113</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-193</x:v>
+        <x:v>-332</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1161,19 +1161,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>332</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="E22" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>332</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.00266916346005267</x:v>
+        <x:v>0.00627823592957748</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-332</x:v>
+        <x:v>-827</x:v>
       </x:c>
       <x:c r="I22" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1184,25 +1184,25 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>0</x:v>
+        <x:v>8367</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>827</x:v>
+        <x:v>9516</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>827</x:v>
+        <x:v>17883</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.00664878970320349</x:v>
+        <x:v>0.135760209345386</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-827</x:v>
+        <x:v>-1149</x:v>
       </x:c>
       <x:c r="I23" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1219,19 +1219,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>19413</x:v>
+        <x:v>19976</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>36354</x:v>
+        <x:v>36917</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.292273398875768</x:v>
+        <x:v>0.280258326254186</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-2472</x:v>
+        <x:v>-3035</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1248,19 +1248,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>3027</x:v>
+        <x:v>3054</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>3027</x:v>
+        <x:v>3054</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0243360174505405</x:v>
+        <x:v>0.0231846826226477</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-3027</x:v>
+        <x:v>-3054</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1277,19 +1277,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>3071</x:v>
+        <x:v>3314</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>3071</x:v>
+        <x:v>3314</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0246897620054872</x:v>
+        <x:v>0.0251584931930106</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-3071</x:v>
+        <x:v>-3314</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1306,19 +1306,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>5244</x:v>
+        <x:v>5410</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>7174</x:v>
+        <x:v>7340</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0576764417542707</x:v>
+        <x:v>0.0557221907171689</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-3314</x:v>
+        <x:v>-3480</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1335,19 +1335,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>3799</x:v>
+        <x:v>4007</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>3799</x:v>
+        <x:v>4007</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0305426264600606</x:v>
+        <x:v>0.0304194575209395</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-3799</x:v>
+        <x:v>-4007</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1358,25 +1358,25 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>2940</x:v>
+        <x:v>1413</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>9662</x:v>
+        <x:v>9777</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>12602</x:v>
+        <x:v>11190</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.101315656396337</x:v>
+        <x:v>0.0849497703167738</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-6722</x:v>
+        <x:v>-8364</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1387,25 +1387,25 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>1413</x:v>
+        <x:v>2940</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>9007</x:v>
+        <x:v>11464</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>10420</x:v>
+        <x:v>14404</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0837731423305688</x:v>
+        <x:v>0.109349105598106</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-7594</x:v>
+        <x:v>-8524</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1416,25 +1416,25 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>11000</x:v>
+        <x:v>204380</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>24684</x:v>
+        <x:v>214039</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>35684</x:v>
+        <x:v>418419</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.286886834061806</x:v>
+        <x:v>3.17646094246418</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-13684</x:v>
+        <x:v>-9659</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1445,25 +1445,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>1448</x:v>
+        <x:v>11000</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>20628</x:v>
+        <x:v>24913</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>22076</x:v>
+        <x:v>35913</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.177483290795551</x:v>
+        <x:v>0.272636380820938</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-19180</x:v>
+        <x:v>-13913</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1474,25 +1474,25 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>86958</x:v>
+        <x:v>1448</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>107839</x:v>
+        <x:v>23599</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>194797</x:v>
+        <x:v>25047</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>1.56609950159</x:v>
+        <x:v>0.190146282138001</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-20881</x:v>
+        <x:v>-22151</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1503,25 +1503,25 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>6547</x:v>
+        <x:v>86958</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>32270</x:v>
+        <x:v>109412</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>38817</x:v>
+        <x:v>196370</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.312075054303809</x:v>
+        <x:v>1.49075839116219</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-25723</x:v>
+        <x:v>-22454</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1532,25 +1532,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>4898</x:v>
+        <x:v>6547</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>37965</x:v>
+        <x:v>32885</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>42863</x:v>
+        <x:v>39432</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.344603474060957</x:v>
+        <x:v>0.299351147732889</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-33067</x:v>
+        <x:v>-26338</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1576,7 +1576,7 @@
         <x:v>33485</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.269207645963445</x:v>
+        <x:v>0.254204026725395</x:v>
       </x:c>
       <x:c r="H36" s="0">
         <x:v>-33485</x:v>
@@ -1590,25 +1590,25 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>3039</x:v>
+        <x:v>4898</x:v>
       </x:c>
       <x:c r="C37" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>38811</x:v>
+        <x:v>40146</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>41850</x:v>
+        <x:v>45044</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.336459309648206</x:v>
+        <x:v>0.341955089736261</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-35772</x:v>
+        <x:v>-35248</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1619,25 +1619,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>26484</x:v>
+        <x:v>3039</x:v>
       </x:c>
       <x:c r="C38" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>65530</x:v>
+        <x:v>38811</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>92014</x:v>
+        <x:v>41850</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.739760260883394</x:v>
+        <x:v>0.317707586037264</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-39046</x:v>
+        <x:v>-35772</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1648,25 +1648,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>173986</x:v>
+        <x:v>178752</x:v>
       </x:c>
       <x:c r="C39" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>213918</x:v>
+        <x:v>221834</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>387904</x:v>
+        <x:v>400586</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>3.11861199641046</x:v>
+        <x:v>3.04108031207463</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-39932</x:v>
+        <x:v>-43082</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1677,25 +1677,25 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>178752</x:v>
+        <x:v>26484</x:v>
       </x:c>
       <x:c r="C40" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>221592</x:v>
+        <x:v>69991</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>400344</x:v>
+        <x:v>96475</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>3.21862522967267</x:v>
+        <x:v>0.732397595291399</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-42840</x:v>
+        <x:v>-43507</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1712,19 +1712,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>95520</x:v>
+        <x:v>102207</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>143923</x:v>
+        <x:v>150610</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>1.15709039958181</x:v>
+        <x:v>1.14336773077831</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-47117</x:v>
+        <x:v>-53804</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1741,19 +1741,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>107264</x:v>
+        <x:v>107770</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>136654</x:v>
+        <x:v>137160</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.09865019117481</x:v>
+        <x:v>1.04126099165761</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-77874</x:v>
+        <x:v>-78380</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1764,25 +1764,25 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>198996</x:v>
+        <x:v>175458</x:v>
       </x:c>
       <x:c r="C43" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>277381</x:v>
+        <x:v>262895</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>476377</x:v>
+        <x:v>438353</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>3.82990386026961</x:v>
+        <x:v>3.32779148057808</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-78385</x:v>
+        <x:v>-87437</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1799,19 +1799,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>159194</x:v>
+        <x:v>178653</x:v>
       </x:c>
       <x:c r="E44" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>224364</x:v>
+        <x:v>243823</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>1.80380780286523</x:v>
+        <x:v>1.85100159499077</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-94024</x:v>
+        <x:v>-113483</x:v>
       </x:c>
       <x:c r="I44" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1822,25 +1822,25 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>35643</x:v>
+        <x:v>198996</x:v>
       </x:c>
       <x:c r="C45" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>145788</x:v>
+        <x:v>321035</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>181431</x:v>
+        <x:v>520031</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.45864155337595</x:v>
+        <x:v>3.94785647967848</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-110145</x:v>
+        <x:v>-122039</x:v>
       </x:c>
       <x:c r="I45" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1851,25 +1851,25 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>0</x:v>
+        <x:v>35643</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>134933</x:v>
+        <x:v>169105</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>134933</x:v>
+        <x:v>204748</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.08481395528701</x:v>
+        <x:v>1.55436064100257</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-134933</x:v>
+        <x:v>-133462</x:v>
       </x:c>
       <x:c r="I46" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1880,25 +1880,25 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>69079</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>262702</x:v>
+        <x:v>134971</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>331781</x:v>
+        <x:v>134971</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>2.66740277692692</x:v>
+        <x:v>1.02464302497098</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-193623</x:v>
+        <x:v>-134971</x:v>
       </x:c>
       <x:c r="I47" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1909,25 +1909,25 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>105627</x:v>
+        <x:v>173911</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>386451</x:v>
+        <x:v>464404</x:v>
       </x:c>
       <x:c r="E48" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>492078</x:v>
+        <x:v>638315</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>3.95613438884277</x:v>
+        <x:v>4.84581882392775</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-280824</x:v>
+        <x:v>-290493</x:v>
       </x:c>
       <x:c r="I48" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1938,25 +1938,25 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>65192</x:v>
+        <x:v>105627</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>407218</x:v>
+        <x:v>409719</x:v>
       </x:c>
       <x:c r="E49" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>472410</x:v>
+        <x:v>515346</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.79801057278158</x:v>
+        <x:v>3.91228993151636</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-342026</x:v>
+        <x:v>-304092</x:v>
       </x:c>
       <x:c r="I49" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1973,19 +1973,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>509190</x:v>
+        <x:v>592504</x:v>
       </x:c>
       <x:c r="E50" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>661286</x:v>
+        <x:v>744600</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>5.31650731278431</x:v>
+        <x:v>5.65268981035476</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-357094</x:v>
+        <x:v>-440408</x:v>
       </x:c>
       <x:c r="I50" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1996,25 +1996,25 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>196520</x:v>
+        <x:v>302899</x:v>
       </x:c>
       <x:c r="C51" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>743386</x:v>
+        <x:v>747915</x:v>
       </x:c>
       <x:c r="E51" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>939906</x:v>
+        <x:v>1050814</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>7.55651431049478</x:v>
+        <x:v>7.97733761802059</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-546866</x:v>
+        <x:v>-445016</x:v>
       </x:c>
       <x:c r="I51" s="0">
         <x:v>65.8000030517578</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -49,42 +49,45 @@
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
     <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
     <x:t>ATA</x:t>
   </x:si>
   <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
     <x:t>ALTERNATIF</x:t>
   </x:si>
   <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
@@ -106,55 +109,55 @@
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
+    <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
     <x:t>ING</x:t>
   </x:si>
   <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
     <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEB</x:t>
   </x:si>
   <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
-    <x:t>OSMANLI</x:t>
+    <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
     <x:t>OYAK</x:t>
@@ -163,31 +166,28 @@
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
     <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -575,28 +575,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1617114</x:v>
+        <x:v>1617216</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>856540</x:v>
+        <x:v>878816</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2473654</x:v>
+        <x:v>2496032</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>18.7789400485406</x:v>
+        <x:v>18.0265070031649</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>760574</x:v>
+        <x:v>738400</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -604,28 +604,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1092803</x:v>
+        <x:v>1092813</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>339406</x:v>
+        <x:v>375821</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1432209</x:v>
+        <x:v>1468634</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>10.8727279352651</x:v>
+        <x:v>10.606571184218</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>753397</x:v>
+        <x:v>716992</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -633,10 +633,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>222893</x:v>
+        <x:v>235509</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D4" s="0">
         <x:v>0</x:v>
@@ -645,16 +645,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>222893</x:v>
+        <x:v>235509</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>1.69210984407656</x:v>
+        <x:v>1.70086146243652</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>222893</x:v>
+        <x:v>235509</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -662,28 +662,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>167102</x:v>
+        <x:v>916518</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>47459</x:v>
+        <x:v>718347</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>214561</x:v>
+        <x:v>1634865</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.62885680687554</x:v>
+        <x:v>11.8071023815917</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>119643</x:v>
+        <x:v>198171</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -691,28 +691,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>114637</x:v>
+        <x:v>167102</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>13289</x:v>
+        <x:v>47459</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>127926</x:v>
+        <x:v>214561</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.971160350093263</x:v>
+        <x:v>1.5495736309094</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>101348</x:v>
+        <x:v>119643</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -720,28 +720,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>811589</x:v>
+        <x:v>114641</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>715408</x:v>
+        <x:v>15305</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1526997</x:v>
+        <x:v>129946</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>11.5923185365865</x:v>
+        <x:v>0.938478544759546</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>96181</x:v>
+        <x:v>99336</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -752,25 +752,25 @@
         <x:v>97672</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>4289</x:v>
+        <x:v>4532</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>101961</x:v>
+        <x:v>102204</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.774044998326057</x:v>
+        <x:v>0.738123999111975</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>93383</x:v>
+        <x:v>93140</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -778,28 +778,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>94365</x:v>
+        <x:v>90000</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>7821</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>102186</x:v>
+        <x:v>92027</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.775753103627332</x:v>
+        <x:v>0.66462503685059</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>86544</x:v>
+        <x:v>87973</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -807,28 +807,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>97108</x:v>
+        <x:v>94365</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>16892</x:v>
+        <x:v>8065</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>114000</x:v>
+        <x:v>102430</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.865440019312977</x:v>
+        <x:v>0.739756185952013</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>80216</x:v>
+        <x:v>86300</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -836,28 +836,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>80000</x:v>
+        <x:v>97108</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>2027</x:v>
+        <x:v>19346</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>82027</x:v>
+        <x:v>116454</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.622714460212154</x:v>
+        <x:v>0.841038434822374</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>77973</x:v>
+        <x:v>77762</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -865,28 +865,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>64451</x:v>
+        <x:v>65101</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>23350</x:v>
+        <x:v>23990</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>87801</x:v>
+        <x:v>89091</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.666548238032445</x:v>
+        <x:v>0.643421052061416</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>41101</x:v>
+        <x:v>41111</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -894,28 +894,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>44116</x:v>
+        <x:v>59901</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>10719</x:v>
+        <x:v>25171</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>54835</x:v>
+        <x:v>85072</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.416284240868659</x:v>
+        <x:v>0.614395570158251</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>33397</x:v>
+        <x:v>34730</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -923,28 +923,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>35000</x:v>
+        <x:v>44116</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>3489</x:v>
+        <x:v>11662</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>38489</x:v>
+        <x:v>55778</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.292192288625765</x:v>
+        <x:v>0.402832378600326</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>31511</x:v>
+        <x:v>32454</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -952,28 +952,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>173412</x:v>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>161949</x:v>
+        <x:v>3517</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>335361</x:v>
+        <x:v>38517</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>2.54591956418263</x:v>
+        <x:v>0.278172303175961</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>11463</x:v>
+        <x:v>31483</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -984,25 +984,25 @@
         <x:v>23291</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>14109</x:v>
+        <x:v>14449</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>37400</x:v>
+        <x:v>37740</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.283925058967591</x:v>
+        <x:v>0.27256075815512</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>9182</x:v>
+        <x:v>8842</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1010,28 +1010,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>8001</x:v>
+        <x:v>173412</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>1274</x:v>
+        <x:v>165717</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>9275</x:v>
+        <x:v>339129</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0704118963081392</x:v>
+        <x:v>2.44921190652856</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>6727</x:v>
+        <x:v>7695</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1039,28 +1039,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>1</x:v>
+        <x:v>8001</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>0</x:v>
+        <x:v>1302</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1</x:v>
+        <x:v>9303</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>7.5915791167805E-06</x:v>
+        <x:v>0.0671868768711469</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>1</x:v>
+        <x:v>6699</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,28 +1068,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>0</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.000204972636153074</x:v>
+        <x:v>7.22206566388766E-06</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1103,22 +1103,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>227</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.815</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>227</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.00172328845950917</x:v>
+        <x:v>0.000194995772924967</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-227</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.815</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1132,22 +1132,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>332</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.802</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>332</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.00252040426677113</x:v>
+        <x:v>0.0016394089057025</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-332</x:v>
+        <x:v>-227</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.802</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1161,22 +1161,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>827</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.801</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>827</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.00627823592957748</x:v>
+        <x:v>0.0023977258004107</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-827</x:v>
+        <x:v>-332</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.801</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1184,28 +1184,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>8367</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>9516</x:v>
+        <x:v>1016</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>17883</x:v>
+        <x:v>1016</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.135760209345386</x:v>
+        <x:v>0.00733761871450987</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-1149</x:v>
+        <x:v>-1016</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1213,28 +1213,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>16941</x:v>
+        <x:v>8367</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>19976</x:v>
+        <x:v>10681</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>36917</x:v>
+        <x:v>19048</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.280258326254186</x:v>
+        <x:v>0.137565906765732</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-3035</x:v>
+        <x:v>-2314</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1251,19 +1251,19 @@
         <x:v>3054</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F25" s="0">
         <x:v>3054</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0231846826226477</x:v>
+        <x:v>0.0220561885375129</x:v>
       </x:c>
       <x:c r="H25" s="0">
         <x:v>-3054</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1277,22 +1277,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>3314</x:v>
+        <x:v>3386</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>3314</x:v>
+        <x:v>3386</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0251584931930106</x:v>
+        <x:v>0.0244539143379236</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-3314</x:v>
+        <x:v>-3386</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1303,25 +1303,25 @@
         <x:v>1930</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>5410</x:v>
+        <x:v>5605</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>7340</x:v>
+        <x:v>7535</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0557221907171689</x:v>
+        <x:v>0.0544182647773935</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-3480</x:v>
+        <x:v>-3675</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1329,28 +1329,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>0</x:v>
+        <x:v>16941</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>4007</x:v>
+        <x:v>20713</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>4007</x:v>
+        <x:v>37654</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0304194575209395</x:v>
+        <x:v>0.271939660508026</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-4007</x:v>
+        <x:v>-3772</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1358,28 +1358,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>1413</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>9777</x:v>
+        <x:v>4128</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>11190</x:v>
+        <x:v>4128</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0849497703167738</x:v>
+        <x:v>0.0298126870605283</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-8364</x:v>
+        <x:v>-4128</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1387,28 +1387,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>2940</x:v>
+        <x:v>1413</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>11464</x:v>
+        <x:v>10310</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>14404</x:v>
+        <x:v>11723</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.109349105598106</x:v>
+        <x:v>0.0846642757777551</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-8524</x:v>
+        <x:v>-8897</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1419,25 +1419,25 @@
         <x:v>204380</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>214039</x:v>
+        <x:v>214082</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>418419</x:v>
+        <x:v>418462</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>3.17646094246418</x:v>
+        <x:v>3.02216004184176</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-9659</x:v>
+        <x:v>-9702</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1445,28 +1445,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>11000</x:v>
+        <x:v>2940</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>24913</x:v>
+        <x:v>12760</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>35913</x:v>
+        <x:v>15700</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.272636380820938</x:v>
+        <x:v>0.113386430923036</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-13913</x:v>
+        <x:v>-9820</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1474,28 +1474,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>1448</x:v>
+        <x:v>97846</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>23599</x:v>
+        <x:v>114636</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>25047</x:v>
+        <x:v>212482</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.190146282138001</x:v>
+        <x:v>1.53455895639418</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-22151</x:v>
+        <x:v>-16790</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1503,28 +1503,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>86958</x:v>
+        <x:v>1448</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>109412</x:v>
+        <x:v>25262</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>196370</x:v>
+        <x:v>26710</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>1.49075839116219</x:v>
+        <x:v>0.19290137388244</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-22454</x:v>
+        <x:v>-23814</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1535,25 +1535,25 @@
         <x:v>6547</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>32885</x:v>
+        <x:v>33218</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>39432</x:v>
+        <x:v>39765</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.299351147732889</x:v>
+        <x:v>0.287185441124493</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-26338</x:v>
+        <x:v>-26671</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1561,28 +1561,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>0</x:v>
+        <x:v>43984</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>33485</x:v>
+        <x:v>73956</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>33485</x:v>
+        <x:v>117940</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.254204026725395</x:v>
+        <x:v>0.851770424398911</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-33485</x:v>
+        <x:v>-29972</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1590,28 +1590,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>4898</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>40146</x:v>
+        <x:v>33485</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>45044</x:v>
+        <x:v>33485</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.341955089736261</x:v>
+        <x:v>0.241830868755278</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-35248</x:v>
+        <x:v>-33485</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1622,25 +1622,25 @@
         <x:v>3039</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>38811</x:v>
+        <x:v>38812</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>41850</x:v>
+        <x:v>41851</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.317707586037264</x:v>
+        <x:v>0.302250670099363</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-35772</x:v>
+        <x:v>-35773</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1648,28 +1648,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>178752</x:v>
+        <x:v>4898</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>221834</x:v>
+        <x:v>42071</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>400586</x:v>
+        <x:v>46969</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>3.04108031207463</x:v>
+        <x:v>0.33921320216714</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-43082</x:v>
+        <x:v>-37173</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1677,28 +1677,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>26484</x:v>
+        <x:v>178752</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>69991</x:v>
+        <x:v>221880</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>96475</x:v>
+        <x:v>400632</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.732397595291399</x:v>
+        <x:v>2.89339061105464</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-43507</x:v>
+        <x:v>-43128</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1706,28 +1706,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>48403</x:v>
+        <x:v>211939</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>102207</x:v>
+        <x:v>262976</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>150610</x:v>
+        <x:v>474915</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>1.14336773077831</x:v>
+        <x:v>3.42986731476521</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-53804</x:v>
+        <x:v>-51037</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1735,28 +1735,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>29390</x:v>
+        <x:v>48404</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>107770</x:v>
+        <x:v>107745</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>137160</x:v>
+        <x:v>156149</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.04126099165761</x:v>
+        <x:v>1.12771833135039</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-78380</x:v>
+        <x:v>-59341</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1764,28 +1764,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>175458</x:v>
+        <x:v>29390</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>262895</x:v>
+        <x:v>108105</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>438353</x:v>
+        <x:v>137495</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>3.32779148057808</x:v>
+        <x:v>0.992997918456234</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-87437</x:v>
+        <x:v>-78715</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1793,28 +1793,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>65170</x:v>
+        <x:v>67582</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>178653</x:v>
+        <x:v>197904</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>243823</x:v>
+        <x:v>265486</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>1.85100159499077</x:v>
+        <x:v>1.91735732484288</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-113483</x:v>
+        <x:v>-130322</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1822,28 +1822,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>198996</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>321035</x:v>
+        <x:v>135109</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>520031</x:v>
+        <x:v>135109</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>3.94785647967848</x:v>
+        <x:v>0.975766069782198</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-122039</x:v>
+        <x:v>-135109</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1851,28 +1851,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>35643</x:v>
+        <x:v>38022</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>169105</x:v>
+        <x:v>186070</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>204748</x:v>
+        <x:v>224092</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.55436064100257</x:v>
+        <x:v>1.61840713875191</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-133462</x:v>
+        <x:v>-148048</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1880,28 +1880,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>0</x:v>
+        <x:v>199046</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>134971</x:v>
+        <x:v>363596</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>134971</x:v>
+        <x:v>562642</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>1.02464302497098</x:v>
+        <x:v>4.06343746926108</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-134971</x:v>
+        <x:v>-164550</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1909,28 +1909,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>173911</x:v>
+        <x:v>218049</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>464404</x:v>
+        <x:v>515822</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>638315</x:v>
+        <x:v>733871</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>4.84581882392775</x:v>
+        <x:v>5.3000645508229</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-290493</x:v>
+        <x:v>-297773</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1938,28 +1938,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>105627</x:v>
+        <x:v>105687</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>409719</x:v>
+        <x:v>433867</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>515346</x:v>
+        <x:v>539554</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.91228993151636</x:v>
+        <x:v>3.89669441721324</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-304092</x:v>
+        <x:v>-328180</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1967,28 +1967,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>152096</x:v>
+        <x:v>348076</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>592504</x:v>
+        <x:v>759071</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>744600</x:v>
+        <x:v>1107147</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>5.65268981035476</x:v>
+        <x:v>7.99588833357623</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-440408</x:v>
+        <x:v>-410995</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1996,28 +1996,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>302899</x:v>
+        <x:v>152780</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>747915</x:v>
+        <x:v>667795</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>1050814</x:v>
+        <x:v>820575</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>7.97733761802059</x:v>
+        <x:v>5.92624653214462</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-445016</x:v>
+        <x:v>-515015</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -46,12 +46,12 @@
     <x:t>IS</x:t>
   </x:si>
   <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
@@ -139,6 +139,9 @@
     <x:t>ING</x:t>
   </x:si>
   <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
@@ -148,9 +151,6 @@
     <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEB</x:t>
   </x:si>
   <x:si>
@@ -166,10 +166,10 @@
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>AK</x:t>
@@ -581,19 +581,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>878816</x:v>
+        <x:v>886362</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2496032</x:v>
+        <x:v>2503578</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>18.0265070031649</x:v>
+        <x:v>17.8182387032968</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>738400</x:v>
+        <x:v>730854</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>65.8</x:v>
@@ -604,25 +604,25 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1092813</x:v>
+        <x:v>1093013</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>375821</x:v>
+        <x:v>388232</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1468634</x:v>
+        <x:v>1481245</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>10.606571184218</x:v>
+        <x:v>10.5421828231694</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>716992</x:v>
+        <x:v>704781</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>65.8</x:v>
@@ -633,25 +633,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>235509</x:v>
+        <x:v>999443</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>0</x:v>
+        <x:v>719400</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>235509</x:v>
+        <x:v>1718843</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>1.70086146243652</x:v>
+        <x:v>12.2331938000297</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>235509</x:v>
+        <x:v>280043</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>65.8</x:v>
@@ -662,25 +662,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>916518</x:v>
+        <x:v>235509</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>718347</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>65.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>1634865</x:v>
+        <x:v>235509</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>11.8071023815917</x:v>
+        <x:v>1.6761433351686</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>198171</x:v>
+        <x:v>235509</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>65.8</x:v>
@@ -706,7 +706,7 @@
         <x:v>214561</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.5495736309094</x:v>
+        <x:v>1.52705412590224</x:v>
       </x:c>
       <x:c r="H6" s="0">
         <x:v>119643</x:v>
@@ -720,25 +720,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>114641</x:v>
+        <x:v>114642</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>15305</x:v>
+        <x:v>15663</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>129946</x:v>
+        <x:v>130305</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.938478544759546</x:v>
+        <x:v>0.927394950040738</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>99336</x:v>
+        <x:v>98979</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>65.8</x:v>
@@ -755,19 +755,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>4532</x:v>
+        <x:v>4560</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>102204</x:v>
+        <x:v>102232</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.738123999111975</x:v>
+        <x:v>0.727596335770421</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>93140</x:v>
+        <x:v>93112</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>65.8</x:v>
@@ -793,7 +793,7 @@
         <x:v>92027</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.66462503685059</x:v>
+        <x:v>0.65496623358581</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>87973</x:v>
@@ -813,19 +813,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>8065</x:v>
+        <x:v>8120</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>102430</x:v>
+        <x:v>102485</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.739756185952013</x:v>
+        <x:v>0.729396964467404</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>86300</x:v>
+        <x:v>86245</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>65.8</x:v>
@@ -842,19 +842,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>19346</x:v>
+        <x:v>19505</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>116454</x:v>
+        <x:v>116613</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.841038434822374</x:v>
+        <x:v>0.829947487119455</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>77762</x:v>
+        <x:v>77603</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>65.8</x:v>
@@ -871,19 +871,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>23990</x:v>
+        <x:v>24218</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>89091</x:v>
+        <x:v>89319</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.643421052061416</x:v>
+        <x:v>0.635693101129571</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>41111</x:v>
+        <x:v>40883</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>65.8</x:v>
@@ -900,19 +900,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>25171</x:v>
+        <x:v>25226</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>85072</x:v>
+        <x:v>85127</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.614395570158251</x:v>
+        <x:v>0.60585817821356</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>34730</x:v>
+        <x:v>34675</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>65.8</x:v>
@@ -929,19 +929,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>11662</x:v>
+        <x:v>11881</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>55778</x:v>
+        <x:v>55997</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.402832378600326</x:v>
+        <x:v>0.398536779228972</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>32454</x:v>
+        <x:v>32235</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>65.8</x:v>
@@ -958,19 +958,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>3517</x:v>
+        <x:v>3571</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>38517</x:v>
+        <x:v>38571</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.278172303175961</x:v>
+        <x:v>0.27451402953088</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>31483</x:v>
+        <x:v>31429</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>65.8</x:v>
@@ -987,19 +987,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>14449</x:v>
+        <x:v>14614</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>37740</x:v>
+        <x:v>37905</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.27256075815512</x:v>
+        <x:v>0.269774034621037</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>8842</x:v>
+        <x:v>8677</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>65.8</x:v>
@@ -1016,19 +1016,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>165717</x:v>
+        <x:v>166673</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>339129</x:v>
+        <x:v>340085</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2.44921190652856</x:v>
+        <x:v>2.42042217554664</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>7695</x:v>
+        <x:v>6739</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>65.8</x:v>
@@ -1054,7 +1054,7 @@
         <x:v>9303</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0671868768711469</x:v>
+        <x:v>0.0662104694388472</x:v>
       </x:c>
       <x:c r="H18" s="0">
         <x:v>6699</x:v>
@@ -1083,7 +1083,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>7.22206566388766E-06</x:v>
+        <x:v>7.1171094742392E-06</x:v>
       </x:c>
       <x:c r="H19" s="0">
         <x:v>1</x:v>
@@ -1112,7 +1112,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.000194995772924967</x:v>
+        <x:v>0.000192161955804458</x:v>
       </x:c>
       <x:c r="H20" s="0">
         <x:v>-27</x:v>
@@ -1141,7 +1141,7 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0016394089057025</x:v>
+        <x:v>0.0016155838506523</x:v>
       </x:c>
       <x:c r="H21" s="0">
         <x:v>-227</x:v>
@@ -1170,7 +1170,7 @@
         <x:v>332</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0023977258004107</x:v>
+        <x:v>0.00236288034544741</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-332</x:v>
@@ -1199,7 +1199,7 @@
         <x:v>1016</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.00733761871450987</x:v>
+        <x:v>0.00723098322582702</x:v>
       </x:c>
       <x:c r="H23" s="0">
         <x:v>-1016</x:v>
@@ -1219,19 +1219,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>10681</x:v>
+        <x:v>11125</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>19048</x:v>
+        <x:v>19492</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.137565906765732</x:v>
+        <x:v>0.13872669787187</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-2314</x:v>
+        <x:v>-2758</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>65.8</x:v>
@@ -1257,7 +1257,7 @@
         <x:v>3054</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0220561885375129</x:v>
+        <x:v>0.0217356523343265</x:v>
       </x:c>
       <x:c r="H25" s="0">
         <x:v>-3054</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>3386</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0244539143379236</x:v>
+        <x:v>0.0240985326797739</x:v>
       </x:c>
       <x:c r="H26" s="0">
         <x:v>-3386</x:v>
@@ -1306,19 +1306,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>5605</x:v>
+        <x:v>5632</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>7535</x:v>
+        <x:v>7562</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0544182647773935</x:v>
+        <x:v>0.0538195818441968</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-3675</x:v>
+        <x:v>-3702</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>65.8</x:v>
@@ -1335,19 +1335,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>20713</x:v>
+        <x:v>20962</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>37654</x:v>
+        <x:v>37903</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.271939660508026</x:v>
+        <x:v>0.269759800402088</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-3772</x:v>
+        <x:v>-4021</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>65.8</x:v>
@@ -1364,19 +1364,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>4128</x:v>
+        <x:v>4164</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>4128</x:v>
+        <x:v>4164</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0298126870605283</x:v>
+        <x:v>0.029635643850732</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-4128</x:v>
+        <x:v>-4164</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>65.8</x:v>
@@ -1393,19 +1393,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>10310</x:v>
+        <x:v>10501</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>11723</x:v>
+        <x:v>11914</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0846642757777551</x:v>
+        <x:v>0.0847932422760858</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-8897</x:v>
+        <x:v>-9088</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>65.8</x:v>
@@ -1422,19 +1422,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>214082</x:v>
+        <x:v>214137</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>418462</x:v>
+        <x:v>418517</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>3.02216004184176</x:v>
+        <x:v>2.97863130583017</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-9702</x:v>
+        <x:v>-9757</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>65.8</x:v>
@@ -1451,19 +1451,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>12760</x:v>
+        <x:v>13294</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>15700</x:v>
+        <x:v>16234</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.113386430923036</x:v>
+        <x:v>0.115539155204799</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-9820</x:v>
+        <x:v>-10354</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>65.8</x:v>
@@ -1474,25 +1474,25 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>97846</x:v>
+        <x:v>104846</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>114636</x:v>
+        <x:v>115383</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>212482</x:v>
+        <x:v>220229</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>1.53455895639418</x:v>
+        <x:v>1.56739390240222</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-16790</x:v>
+        <x:v>-10537</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>65.8</x:v>
@@ -1509,19 +1509,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>25262</x:v>
+        <x:v>25685</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>26710</x:v>
+        <x:v>27133</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.19290137388244</x:v>
+        <x:v>0.193108531364532</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-23814</x:v>
+        <x:v>-24237</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>65.8</x:v>
@@ -1532,25 +1532,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>6547</x:v>
+        <x:v>14150</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>33218</x:v>
+        <x:v>38812</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>39765</x:v>
+        <x:v>52962</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.287185441124493</x:v>
+        <x:v>0.376936351974656</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-26671</x:v>
+        <x:v>-24662</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>65.8</x:v>
@@ -1561,25 +1561,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>43984</x:v>
+        <x:v>6547</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>73956</x:v>
+        <x:v>33322</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>117940</x:v>
+        <x:v>39869</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.851770424398911</x:v>
+        <x:v>0.283752037628442</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-29972</x:v>
+        <x:v>-26775</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>65.8</x:v>
@@ -1590,25 +1590,25 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>0</x:v>
+        <x:v>43984</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>33485</x:v>
+        <x:v>75300</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>33485</x:v>
+        <x:v>119284</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.241830868755278</x:v>
+        <x:v>0.848957286525148</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-33485</x:v>
+        <x:v>-31316</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>65.8</x:v>
@@ -1619,25 +1619,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>3039</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>65.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>38812</x:v>
+        <x:v>33485</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>41851</x:v>
+        <x:v>33485</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.302250670099363</x:v>
+        <x:v>0.238316410744899</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-35773</x:v>
+        <x:v>-33485</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>65.8</x:v>
@@ -1654,19 +1654,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>42071</x:v>
+        <x:v>42593</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>46969</x:v>
+        <x:v>47491</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.33921320216714</x:v>
+        <x:v>0.337998646041094</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-37173</x:v>
+        <x:v>-37695</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>65.8</x:v>
@@ -1683,19 +1683,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>221880</x:v>
+        <x:v>221899</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>400632</x:v>
+        <x:v>400651</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>2.89339061105464</x:v>
+        <x:v>2.85147702796341</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-43128</x:v>
+        <x:v>-43147</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>65.8</x:v>
@@ -1712,19 +1712,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>262976</x:v>
+        <x:v>263103</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>474915</x:v>
+        <x:v>475042</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>3.42986731476521</x:v>
+        <x:v>3.38092591886154</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-51037</x:v>
+        <x:v>-51164</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>65.8</x:v>
@@ -1741,19 +1741,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>107745</x:v>
+        <x:v>109546</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>156149</x:v>
+        <x:v>157950</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.12771833135039</x:v>
+        <x:v>1.12414744145608</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-59341</x:v>
+        <x:v>-61142</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>65.8</x:v>
@@ -1770,19 +1770,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>108105</x:v>
+        <x:v>108402</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>137495</x:v>
+        <x:v>137792</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.992997918456234</x:v>
+        <x:v>0.980680748674367</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-78715</x:v>
+        <x:v>-79012</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>65.8</x:v>
@@ -1793,25 +1793,25 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>67582</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>65.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>197904</x:v>
+        <x:v>135192</x:v>
       </x:c>
       <x:c r="E44" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>265486</x:v>
+        <x:v>135192</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>1.91735732484288</x:v>
+        <x:v>0.962176264041345</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-130322</x:v>
+        <x:v>-135192</x:v>
       </x:c>
       <x:c r="I44" s="0">
         <x:v>65.8</x:v>
@@ -1822,25 +1822,25 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>0</x:v>
+        <x:v>67582</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>135109</x:v>
+        <x:v>203916</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>135109</x:v>
+        <x:v>271498</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.975766069782198</x:v>
+        <x:v>1.93228098803699</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-135109</x:v>
+        <x:v>-136334</x:v>
       </x:c>
       <x:c r="I45" s="0">
         <x:v>65.8</x:v>
@@ -1857,19 +1857,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>186070</x:v>
+        <x:v>192302</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>224092</x:v>
+        <x:v>230324</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.61840713875191</x:v>
+        <x:v>1.63924112254467</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-148048</x:v>
+        <x:v>-154280</x:v>
       </x:c>
       <x:c r="I46" s="0">
         <x:v>65.8</x:v>
@@ -1886,19 +1886,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>363596</x:v>
+        <x:v>376551</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>562642</x:v>
+        <x:v>575597</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>4.06343746926108</x:v>
+        <x:v>4.09658686204366</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-164550</x:v>
+        <x:v>-177505</x:v>
       </x:c>
       <x:c r="I47" s="0">
         <x:v>65.8</x:v>
@@ -1915,19 +1915,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>515822</x:v>
+        <x:v>531154</x:v>
       </x:c>
       <x:c r="E48" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>733871</x:v>
+        <x:v>749203</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>5.3000645508229</x:v>
+        <x:v>5.33215976942843</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-297773</x:v>
+        <x:v>-313105</x:v>
       </x:c>
       <x:c r="I48" s="0">
         <x:v>65.8</x:v>
@@ -1944,19 +1944,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>433867</x:v>
+        <x:v>440510</x:v>
       </x:c>
       <x:c r="E49" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>539554</x:v>
+        <x:v>546197</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.89669441721324</x:v>
+        <x:v>3.88734384350103</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-328180</x:v>
+        <x:v>-334823</x:v>
       </x:c>
       <x:c r="I49" s="0">
         <x:v>65.8</x:v>
@@ -1967,25 +1967,25 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>348076</x:v>
+        <x:v>348077</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>759071</x:v>
+        <x:v>760646</x:v>
       </x:c>
       <x:c r="E50" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>1107147</x:v>
+        <x:v>1108723</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>7.99588833357623</x:v>
+        <x:v>7.8909029676069</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-410995</x:v>
+        <x:v>-412569</x:v>
       </x:c>
       <x:c r="I50" s="0">
         <x:v>65.8</x:v>
@@ -1996,25 +1996,25 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>152780</x:v>
+        <x:v>153639</x:v>
       </x:c>
       <x:c r="C51" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>667795</x:v>
+        <x:v>690853</x:v>
       </x:c>
       <x:c r="E51" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>820575</x:v>
+        <x:v>844492</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>5.92624653214462</x:v>
+        <x:v>6.01034201411921</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-515015</x:v>
+        <x:v>-537214</x:v>
       </x:c>
       <x:c r="I51" s="0">
         <x:v>65.8</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -85,12 +85,12 @@
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
     <x:t>ANADOLU</x:t>
   </x:si>
   <x:si>
@@ -136,10 +136,10 @@
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
     <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
   </x:si>
   <x:si>
     <x:t>AHLATCI</x:t>
@@ -581,19 +581,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>886362</x:v>
+        <x:v>891869</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2503578</x:v>
+        <x:v>2509085</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>17.8182387032968</x:v>
+        <x:v>17.4980333685746</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>730854</x:v>
+        <x:v>725347</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>65.8</x:v>
@@ -610,19 +610,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>388232</x:v>
+        <x:v>404876</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1481245</x:v>
+        <x:v>1497889</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>10.5421828231694</x:v>
+        <x:v>10.4460836139154</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>704781</x:v>
+        <x:v>688137</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>65.8</x:v>
@@ -633,25 +633,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>999443</x:v>
+        <x:v>1143739</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>719400</x:v>
+        <x:v>720707</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1718843</x:v>
+        <x:v>1864446</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>12.2331938000297</x:v>
+        <x:v>13.0024045904804</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>280043</x:v>
+        <x:v>423032</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>65.8</x:v>
@@ -677,7 +677,7 @@
         <x:v>235509</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.6761433351686</x:v>
+        <x:v>1.64240922113027</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>235509</x:v>
@@ -697,19 +697,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>47459</x:v>
+        <x:v>47515</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>214561</x:v>
+        <x:v>214617</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.52705412590224</x:v>
+        <x:v>1.49671112276522</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>119643</x:v>
+        <x:v>119587</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>65.8</x:v>
@@ -726,19 +726,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>15663</x:v>
+        <x:v>15697</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>130305</x:v>
+        <x:v>130339</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.927394950040738</x:v>
+        <x:v>0.908967281390088</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>98979</x:v>
+        <x:v>98945</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>65.8</x:v>
@@ -755,19 +755,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>4560</x:v>
+        <x:v>4669</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>102232</x:v>
+        <x:v>102341</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.727596335770421</x:v>
+        <x:v>0.713712860653703</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>93112</x:v>
+        <x:v>93003</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>65.8</x:v>
@@ -793,7 +793,7 @@
         <x:v>92027</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.65496623358581</x:v>
+        <x:v>0.641784362351143</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>87973</x:v>
@@ -813,19 +813,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>8120</x:v>
+        <x:v>8224</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>102485</x:v>
+        <x:v>102589</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.729396964467404</x:v>
+        <x:v>0.715442380488785</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>86245</x:v>
+        <x:v>86141</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>65.8</x:v>
@@ -842,19 +842,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>19505</x:v>
+        <x:v>19918</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>116613</x:v>
+        <x:v>117026</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.829947487119455</x:v>
+        <x:v>0.816124146049582</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>77603</x:v>
+        <x:v>77190</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>65.8</x:v>
@@ -871,19 +871,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>24218</x:v>
+        <x:v>24755</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>89319</x:v>
+        <x:v>89856</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.635693101129571</x:v>
+        <x:v>0.626644089923873</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>40883</x:v>
+        <x:v>40346</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>65.8</x:v>
@@ -900,19 +900,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>25226</x:v>
+        <x:v>25307</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>85127</x:v>
+        <x:v>85208</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.60585817821356</x:v>
+        <x:v>0.594229540756693</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>34675</x:v>
+        <x:v>34594</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>65.8</x:v>
@@ -929,19 +929,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>11881</x:v>
+        <x:v>12484</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>55997</x:v>
+        <x:v>56600</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.398536779228972</x:v>
+        <x:v>0.394721059135631</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>32235</x:v>
+        <x:v>31632</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>65.8</x:v>
@@ -958,19 +958,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>3571</x:v>
+        <x:v>3626</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>38571</x:v>
+        <x:v>38626</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.27451402953088</x:v>
+        <x:v>0.269372714314008</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>31429</x:v>
+        <x:v>31374</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>65.8</x:v>
@@ -987,19 +987,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>14614</x:v>
+        <x:v>14750</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>37905</x:v>
+        <x:v>38041</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.269774034621037</x:v>
+        <x:v>0.2652930001869</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>8677</x:v>
+        <x:v>8541</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>65.8</x:v>
@@ -1010,25 +1010,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>173412</x:v>
+        <x:v>8001</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>166673</x:v>
+        <x:v>1302</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>340085</x:v>
+        <x:v>9303</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2.42042217554664</x:v>
+        <x:v>0.0648779154264801</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>6739</x:v>
+        <x:v>6699</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>65.8</x:v>
@@ -1039,25 +1039,25 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>8001</x:v>
+        <x:v>173412</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>1302</x:v>
+        <x:v>167955</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>9303</x:v>
+        <x:v>341367</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0662104694388472</x:v>
+        <x:v>2.38064918363874</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>6699</x:v>
+        <x:v>5457</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>65.8</x:v>
@@ -1083,7 +1083,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>7.1171094742392E-06</x:v>
+        <x:v>6.97387030274966E-06</x:v>
       </x:c>
       <x:c r="H19" s="0">
         <x:v>1</x:v>
@@ -1112,7 +1112,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.000192161955804458</x:v>
+        <x:v>0.000188294498174241</x:v>
       </x:c>
       <x:c r="H20" s="0">
         <x:v>-27</x:v>
@@ -1132,22 +1132,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>227</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>65.802</x:v>
+        <x:v>65.798</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>227</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0016155838506523</x:v>
+        <x:v>0.00172951983508192</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-227</x:v>
+        <x:v>-248</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>65.802</x:v>
+        <x:v>65.798</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1170,7 +1170,7 @@
         <x:v>332</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.00236288034544741</x:v>
+        <x:v>0.00231532494051289</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-332</x:v>
@@ -1199,7 +1199,7 @@
         <x:v>1016</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.00723098322582702</x:v>
+        <x:v>0.00708545222759365</x:v>
       </x:c>
       <x:c r="H23" s="0">
         <x:v>-1016</x:v>
@@ -1219,19 +1219,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>11125</x:v>
+        <x:v>11443</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>19492</x:v>
+        <x:v>19810</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.13872669787187</x:v>
+        <x:v>0.138152370697471</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-2758</x:v>
+        <x:v>-3076</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>65.8</x:v>
@@ -1248,19 +1248,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>3054</x:v>
+        <x:v>3081</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>3054</x:v>
+        <x:v>3081</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0217356523343265</x:v>
+        <x:v>0.0214864944027717</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-3054</x:v>
+        <x:v>-3081</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>65.8</x:v>
@@ -1277,19 +1277,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>3386</x:v>
+        <x:v>3440</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>3386</x:v>
+        <x:v>3440</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0240985326797739</x:v>
+        <x:v>0.0239901138414588</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-3386</x:v>
+        <x:v>-3440</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>65.8</x:v>
@@ -1306,19 +1306,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>5632</x:v>
+        <x:v>5714</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>7562</x:v>
+        <x:v>7644</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0538195818441968</x:v>
+        <x:v>0.0533082645942184</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-3702</x:v>
+        <x:v>-3784</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>65.8</x:v>
@@ -1335,19 +1335,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>20962</x:v>
+        <x:v>21125</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>37903</x:v>
+        <x:v>38066</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.269759800402088</x:v>
+        <x:v>0.265467346944468</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-4021</x:v>
+        <x:v>-4184</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>65.8</x:v>
@@ -1364,19 +1364,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>4164</x:v>
+        <x:v>4245</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>4164</x:v>
+        <x:v>4245</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.029635643850732</x:v>
+        <x:v>0.0296040794351723</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-4164</x:v>
+        <x:v>-4245</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>65.8</x:v>
@@ -1393,19 +1393,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>10501</x:v>
+        <x:v>10847</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>11914</x:v>
+        <x:v>12260</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0847932422760858</x:v>
+        <x:v>0.0854996499117108</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-9088</x:v>
+        <x:v>-9434</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>65.8</x:v>
@@ -1422,19 +1422,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>214137</x:v>
+        <x:v>214248</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>418517</x:v>
+        <x:v>418628</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>2.97863130583017</x:v>
+        <x:v>2.91945737709948</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-9757</x:v>
+        <x:v>-9868</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>65.8</x:v>
@@ -1451,19 +1451,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>13294</x:v>
+        <x:v>13995</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>16234</x:v>
+        <x:v>16935</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.115539155204799</x:v>
+        <x:v>0.118102493577065</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-10354</x:v>
+        <x:v>-11055</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>65.8</x:v>
@@ -1480,19 +1480,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>115383</x:v>
+        <x:v>115985</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>220229</x:v>
+        <x:v>220831</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>1.56739390240222</x:v>
+        <x:v>1.54004675282651</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-10537</x:v>
+        <x:v>-11139</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>65.8</x:v>
@@ -1503,25 +1503,25 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>1448</x:v>
+        <x:v>14150</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>25685</x:v>
+        <x:v>38839</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>27133</x:v>
+        <x:v>52989</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.193108531364532</x:v>
+        <x:v>0.369538413472402</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-24237</x:v>
+        <x:v>-24689</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>65.8</x:v>
@@ -1532,25 +1532,25 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>14150</x:v>
+        <x:v>1448</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>38812</x:v>
+        <x:v>26438</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>52962</x:v>
+        <x:v>27886</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.376936351974656</x:v>
+        <x:v>0.194473347262477</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-24662</x:v>
+        <x:v>-24990</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>65.8</x:v>
@@ -1567,19 +1567,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>33322</x:v>
+        <x:v>33485</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>39869</x:v>
+        <x:v>40032</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.283752037628442</x:v>
+        <x:v>0.279177975959674</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-26775</x:v>
+        <x:v>-26938</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>65.8</x:v>
@@ -1596,19 +1596,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>75300</x:v>
+        <x:v>77088</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>119284</x:v>
+        <x:v>121072</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.848957286525148</x:v>
+        <x:v>0.844340425294507</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-31316</x:v>
+        <x:v>-33104</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>65.8</x:v>
@@ -1634,7 +1634,7 @@
         <x:v>33485</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.238316410744899</x:v>
+        <x:v>0.233520047087572</x:v>
       </x:c>
       <x:c r="H38" s="0">
         <x:v>-33485</x:v>
@@ -1654,19 +1654,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>42593</x:v>
+        <x:v>43972</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>47491</x:v>
+        <x:v>48870</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.337998646041094</x:v>
+        <x:v>0.340813041695376</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-37695</x:v>
+        <x:v>-39074</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>65.8</x:v>
@@ -1683,19 +1683,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>221899</x:v>
+        <x:v>221926</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>400651</x:v>
+        <x:v>400678</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>2.85147702796341</x:v>
+        <x:v>2.79427640516513</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-43147</x:v>
+        <x:v>-43174</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>65.8</x:v>
@@ -1712,19 +1712,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>263103</x:v>
+        <x:v>263184</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>475042</x:v>
+        <x:v>475123</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>3.38092591886154</x:v>
+        <x:v>3.31344617985333</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-51164</x:v>
+        <x:v>-51245</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>65.8</x:v>
@@ -1741,19 +1741,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>109546</x:v>
+        <x:v>111826</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>157950</x:v>
+        <x:v>160230</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.12414744145608</x:v>
+        <x:v>1.11742323860958</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-61142</x:v>
+        <x:v>-63422</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>65.8</x:v>
@@ -1770,19 +1770,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>108402</x:v>
+        <x:v>109177</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>137792</x:v>
+        <x:v>138567</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.980680748674367</x:v>
+        <x:v>0.966348286241112</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-79012</x:v>
+        <x:v>-79787</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>65.8</x:v>
@@ -1799,19 +1799,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>135192</x:v>
+        <x:v>135220</x:v>
       </x:c>
       <x:c r="E44" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>135192</x:v>
+        <x:v>135220</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.962176264041345</x:v>
+        <x:v>0.943006742337809</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-135192</x:v>
+        <x:v>-135220</x:v>
       </x:c>
       <x:c r="I44" s="0">
         <x:v>65.8</x:v>
@@ -1828,19 +1828,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>203916</x:v>
+        <x:v>212677</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>271498</x:v>
+        <x:v>280259</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.93228098803699</x:v>
+        <x:v>1.95448991717832</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-136334</x:v>
+        <x:v>-145095</x:v>
       </x:c>
       <x:c r="I45" s="0">
         <x:v>65.8</x:v>
@@ -1857,19 +1857,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>192302</x:v>
+        <x:v>201463</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>230324</x:v>
+        <x:v>239485</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.63924112254467</x:v>
+        <x:v>1.670137329454</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-154280</x:v>
+        <x:v>-163441</x:v>
       </x:c>
       <x:c r="I46" s="0">
         <x:v>65.8</x:v>
@@ -1886,19 +1886,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>376551</x:v>
+        <x:v>395899</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>575597</x:v>
+        <x:v>594945</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>4.09658686204366</x:v>
+        <x:v>4.14906926726939</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-177505</x:v>
+        <x:v>-196853</x:v>
       </x:c>
       <x:c r="I47" s="0">
         <x:v>65.8</x:v>
@@ -1915,19 +1915,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>531154</x:v>
+        <x:v>554227</x:v>
       </x:c>
       <x:c r="E48" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>749203</x:v>
+        <x:v>772276</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>5.33215976942843</x:v>
+        <x:v>5.38575266192629</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-313105</x:v>
+        <x:v>-336178</x:v>
       </x:c>
       <x:c r="I48" s="0">
         <x:v>65.8</x:v>
@@ -1944,19 +1944,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>440510</x:v>
+        <x:v>449336</x:v>
       </x:c>
       <x:c r="E49" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>546197</x:v>
+        <x:v>555023</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.88734384350103</x:v>
+        <x:v>3.87065841704302</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-334823</x:v>
+        <x:v>-343649</x:v>
       </x:c>
       <x:c r="I49" s="0">
         <x:v>65.8</x:v>
@@ -1973,19 +1973,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>760646</x:v>
+        <x:v>763767</x:v>
       </x:c>
       <x:c r="E50" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>1108723</x:v>
+        <x:v>1111844</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>7.8909029676069</x:v>
+        <x:v>7.75385585289039</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-412569</x:v>
+        <x:v>-415690</x:v>
       </x:c>
       <x:c r="I50" s="0">
         <x:v>65.8</x:v>
@@ -2002,19 +2002,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>690853</x:v>
+        <x:v>726184</x:v>
       </x:c>
       <x:c r="E51" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>844492</x:v>
+        <x:v>879823</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>6.01034201411921</x:v>
+        <x:v>6.13577149137611</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-537214</x:v>
+        <x:v>-572545</x:v>
       </x:c>
       <x:c r="I51" s="0">
         <x:v>65.8</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -76,12 +76,12 @@
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
@@ -106,15 +106,15 @@
     <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
     <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
@@ -145,12 +145,12 @@
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
     <x:t>TEB</x:t>
   </x:si>
   <x:si>
@@ -178,10 +178,10 @@
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
     <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
@@ -575,25 +575,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1617216</x:v>
+        <x:v>1632413</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>891869</x:v>
+        <x:v>895558</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2509085</x:v>
+        <x:v>2527971</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>17.4980333685746</x:v>
+        <x:v>17.3017844996955</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>725347</x:v>
+        <x:v>736855</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>65.8</x:v>
@@ -610,19 +610,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>404876</x:v>
+        <x:v>421966</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1497889</x:v>
+        <x:v>1514979</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>10.4460836139154</x:v>
+        <x:v>10.368726611011</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>688137</x:v>
+        <x:v>671047</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>65.8</x:v>
@@ -633,25 +633,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>1143739</x:v>
+        <x:v>1226324</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>720707</x:v>
+        <x:v>721410</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1864446</x:v>
+        <x:v>1947734</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>13.0024045904804</x:v>
+        <x:v>13.3305619133803</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>423032</x:v>
+        <x:v>504914</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>65.8</x:v>
@@ -677,7 +677,7 @@
         <x:v>235509</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.64240922113027</x:v>
+        <x:v>1.61185629334308</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>235509</x:v>
@@ -697,19 +697,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>47515</x:v>
+        <x:v>47518</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>214617</x:v>
+        <x:v>214620</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.49671112276522</x:v>
+        <x:v>1.46888907717875</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>119587</x:v>
+        <x:v>119584</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>65.8</x:v>
@@ -726,19 +726,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>15697</x:v>
+        <x:v>15848</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>130339</x:v>
+        <x:v>130490</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.908967281390088</x:v>
+        <x:v>0.893091676829072</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>98945</x:v>
+        <x:v>98794</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>65.8</x:v>
@@ -755,19 +755,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>4669</x:v>
+        <x:v>4723</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>102341</x:v>
+        <x:v>102395</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.713712860653703</x:v>
+        <x:v>0.700805596205938</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>93003</x:v>
+        <x:v>92949</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>65.8</x:v>
@@ -793,7 +793,7 @@
         <x:v>92027</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.641784362351143</x:v>
+        <x:v>0.629845564744801</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>87973</x:v>
@@ -813,19 +813,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>8224</x:v>
+        <x:v>8306</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>102589</x:v>
+        <x:v>102671</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.715442380488785</x:v>
+        <x:v>0.702694578524927</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>86141</x:v>
+        <x:v>86059</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>65.8</x:v>
@@ -842,19 +842,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>19918</x:v>
+        <x:v>20437</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>117026</x:v>
+        <x:v>117545</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.816124146049582</x:v>
+        <x:v>0.804494299585204</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>77190</x:v>
+        <x:v>76671</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>65.8</x:v>
@@ -871,19 +871,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>24755</x:v>
+        <x:v>25136</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>89856</x:v>
+        <x:v>90237</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.626644089923873</x:v>
+        <x:v>0.617594556226722</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>40346</x:v>
+        <x:v>39965</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>65.8</x:v>
@@ -900,19 +900,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>25307</x:v>
+        <x:v>25362</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>85208</x:v>
+        <x:v>85263</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.594229540756693</x:v>
+        <x:v>0.583551809651906</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>34594</x:v>
+        <x:v>34539</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>65.8</x:v>
@@ -923,25 +923,25 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>44116</x:v>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>12484</x:v>
+        <x:v>3653</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>56600</x:v>
+        <x:v>38653</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.394721059135631</x:v>
+        <x:v>0.264546498463285</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>31632</x:v>
+        <x:v>31347</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>65.8</x:v>
@@ -952,25 +952,25 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>35000</x:v>
+        <x:v>44116</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>3626</x:v>
+        <x:v>13006</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>38626</x:v>
+        <x:v>57122</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.269372714314008</x:v>
+        <x:v>0.390950898642273</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>31374</x:v>
+        <x:v>31110</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>65.8</x:v>
@@ -987,19 +987,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>14750</x:v>
+        <x:v>15486</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>38041</x:v>
+        <x:v>38777</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.2652930001869</x:v>
+        <x:v>0.265395171679063</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>8541</x:v>
+        <x:v>7805</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>65.8</x:v>
@@ -1025,7 +1025,7 @@
         <x:v>9303</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0648779154264801</x:v>
+        <x:v>0.0636710235998227</x:v>
       </x:c>
       <x:c r="H17" s="0">
         <x:v>6699</x:v>
@@ -1045,19 +1045,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>167955</x:v>
+        <x:v>170125</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>341367</x:v>
+        <x:v>343537</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>2.38064918363874</x:v>
+        <x:v>2.35121492361736</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>5457</x:v>
+        <x:v>3287</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>65.8</x:v>
@@ -1083,7 +1083,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>6.97387030274966E-06</x:v>
+        <x:v>6.84413883691526E-06</x:v>
       </x:c>
       <x:c r="H19" s="0">
         <x:v>1</x:v>
@@ -1112,7 +1112,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.000188294498174241</x:v>
+        <x:v>0.000184791748596712</x:v>
       </x:c>
       <x:c r="H20" s="0">
         <x:v>-27</x:v>
@@ -1141,7 +1141,7 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.00172951983508192</x:v>
+        <x:v>0.00169734643155498</x:v>
       </x:c>
       <x:c r="H21" s="0">
         <x:v>-248</x:v>
@@ -1170,7 +1170,7 @@
         <x:v>332</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.00231532494051289</x:v>
+        <x:v>0.00227225409385587</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-332</x:v>
@@ -1199,7 +1199,7 @@
         <x:v>1016</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.00708545222759365</x:v>
+        <x:v>0.0069536450583059</x:v>
       </x:c>
       <x:c r="H23" s="0">
         <x:v>-1016</x:v>
@@ -1213,25 +1213,25 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>8367</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>65.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>11443</x:v>
+        <x:v>3081</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>19810</x:v>
+        <x:v>3081</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.138152370697471</x:v>
+        <x:v>0.0210867917565359</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-3076</x:v>
+        <x:v>-3081</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>65.8</x:v>
@@ -1248,19 +1248,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>3081</x:v>
+        <x:v>3440</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>3081</x:v>
+        <x:v>3440</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0214864944027717</x:v>
+        <x:v>0.0235438375989885</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-3081</x:v>
+        <x:v>-3440</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>65.8</x:v>
@@ -1271,25 +1271,25 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>0</x:v>
+        <x:v>8367</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>3440</x:v>
+        <x:v>11981</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>3440</x:v>
+        <x:v>20348</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0239901138414588</x:v>
+        <x:v>0.139264537053552</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-3440</x:v>
+        <x:v>-3614</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>65.8</x:v>
@@ -1306,19 +1306,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>5714</x:v>
+        <x:v>5797</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>7644</x:v>
+        <x:v>7727</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0533082645942184</x:v>
+        <x:v>0.0528846607928442</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-3784</x:v>
+        <x:v>-3867</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>65.8</x:v>
@@ -1335,19 +1335,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>21125</x:v>
+        <x:v>21289</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>38066</x:v>
+        <x:v>38230</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.265467346944468</x:v>
+        <x:v>0.26165142773527</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-4184</x:v>
+        <x:v>-4348</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>65.8</x:v>
@@ -1364,19 +1364,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>4245</x:v>
+        <x:v>4354</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>4245</x:v>
+        <x:v>4354</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0296040794351723</x:v>
+        <x:v>0.029799380495929</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-4245</x:v>
+        <x:v>-4354</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>65.8</x:v>
@@ -1393,19 +1393,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>10847</x:v>
+        <x:v>11064</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>12260</x:v>
+        <x:v>12477</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0854996499117108</x:v>
+        <x:v>0.0853943202681917</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-9434</x:v>
+        <x:v>-9651</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>65.8</x:v>
@@ -1431,7 +1431,7 @@
         <x:v>418628</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>2.91945737709948</x:v>
+        <x:v>2.86514815302016</x:v>
       </x:c>
       <x:c r="H31" s="0">
         <x:v>-9868</x:v>
@@ -1451,19 +1451,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>13995</x:v>
+        <x:v>14458</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>16935</x:v>
+        <x:v>17398</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.118102493577065</x:v>
+        <x:v>0.119074327484652</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-11055</x:v>
+        <x:v>-11518</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>65.8</x:v>
@@ -1480,19 +1480,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>115985</x:v>
+        <x:v>116926</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>220831</x:v>
+        <x:v>221772</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>1.54004675282651</x:v>
+        <x:v>1.51783835814037</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-11139</x:v>
+        <x:v>-12080</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>65.8</x:v>
@@ -1518,7 +1518,7 @@
         <x:v>52989</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.369538413472402</x:v>
+        <x:v>0.362664072829303</x:v>
       </x:c>
       <x:c r="H34" s="0">
         <x:v>-24689</x:v>
@@ -1538,19 +1538,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>26438</x:v>
+        <x:v>27149</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>27886</x:v>
+        <x:v>28597</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.194473347262477</x:v>
+        <x:v>0.195721838319266</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-24990</x:v>
+        <x:v>-25701</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>65.8</x:v>
@@ -1567,19 +1567,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>33485</x:v>
+        <x:v>33594</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>40032</x:v>
+        <x:v>40141</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.279177975959674</x:v>
+        <x:v>0.274730577052615</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-26938</x:v>
+        <x:v>-27047</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>65.8</x:v>
@@ -1590,25 +1590,25 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>43984</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>65.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>77088</x:v>
+        <x:v>33485</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>121072</x:v>
+        <x:v>33485</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.844340425294507</x:v>
+        <x:v>0.229175988954107</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-33104</x:v>
+        <x:v>-33485</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>65.8</x:v>
@@ -1619,25 +1619,25 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>0</x:v>
+        <x:v>43984</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>33485</x:v>
+        <x:v>78516</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>33485</x:v>
+        <x:v>122500</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.233520047087572</x:v>
+        <x:v>0.838407007522119</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-33485</x:v>
+        <x:v>-34532</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>65.8</x:v>
@@ -1654,19 +1654,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>43972</x:v>
+        <x:v>45124</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>48870</x:v>
+        <x:v>50022</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.340813041695376</x:v>
+        <x:v>0.342357512900175</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-39074</x:v>
+        <x:v>-40226</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>65.8</x:v>
@@ -1683,19 +1683,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>221926</x:v>
+        <x:v>222035</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>400678</x:v>
+        <x:v>400787</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>2.79427640516513</x:v>
+        <x:v>2.74304187203076</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-43174</x:v>
+        <x:v>-43283</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>65.8</x:v>
@@ -1712,19 +1712,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>263184</x:v>
+        <x:v>263212</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>475123</x:v>
+        <x:v>475151</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>3.31344617985333</x:v>
+        <x:v>3.25199941249912</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-51245</x:v>
+        <x:v>-51273</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>65.8</x:v>
@@ -1741,19 +1741,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>111826</x:v>
+        <x:v>113573</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>160230</x:v>
+        <x:v>161977</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.11742323860958</x:v>
+        <x:v>1.10859307638702</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-63422</x:v>
+        <x:v>-65169</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>65.8</x:v>
@@ -1770,19 +1770,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>109177</x:v>
+        <x:v>109477</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>138567</x:v>
+        <x:v>138867</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.966348286241112</x:v>
+        <x:v>0.950425027865911</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-79787</x:v>
+        <x:v>-80087</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>65.8</x:v>
@@ -1799,19 +1799,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>135220</x:v>
+        <x:v>135275</x:v>
       </x:c>
       <x:c r="E44" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>135220</x:v>
+        <x:v>135275</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.943006742337809</x:v>
+        <x:v>0.925840881163712</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-135220</x:v>
+        <x:v>-135275</x:v>
       </x:c>
       <x:c r="I44" s="0">
         <x:v>65.8</x:v>
@@ -1828,19 +1828,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>212677</x:v>
+        <x:v>220232</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>280259</x:v>
+        <x:v>287814</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.95448991717832</x:v>
+        <x:v>1.96983897520793</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-145095</x:v>
+        <x:v>-152650</x:v>
       </x:c>
       <x:c r="I45" s="0">
         <x:v>65.8</x:v>
@@ -1857,19 +1857,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>201463</x:v>
+        <x:v>210365</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>239485</x:v>
+        <x:v>248387</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.670137329454</x:v>
+        <x:v>1.69999511328487</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-163441</x:v>
+        <x:v>-172343</x:v>
       </x:c>
       <x:c r="I46" s="0">
         <x:v>65.8</x:v>
@@ -1886,19 +1886,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>395899</x:v>
+        <x:v>412959</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>594945</x:v>
+        <x:v>612005</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>4.14906926726939</x:v>
+        <x:v>4.18864718888632</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-196853</x:v>
+        <x:v>-213913</x:v>
       </x:c>
       <x:c r="I47" s="0">
         <x:v>65.8</x:v>
@@ -1909,25 +1909,25 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>218049</x:v>
+        <x:v>105687</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>554227</x:v>
+        <x:v>458475</x:v>
       </x:c>
       <x:c r="E48" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>772276</x:v>
+        <x:v>564162</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>5.38575266192629</x:v>
+        <x:v>3.86120305451179</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-336178</x:v>
+        <x:v>-352788</x:v>
       </x:c>
       <x:c r="I48" s="0">
         <x:v>65.8</x:v>
@@ -1938,25 +1938,25 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>105687</x:v>
+        <x:v>218049</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>449336</x:v>
+        <x:v>577949</x:v>
       </x:c>
       <x:c r="E49" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>555023</x:v>
+        <x:v>795998</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.87065841704302</x:v>
+        <x:v>5.44792082590687</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-343649</x:v>
+        <x:v>-359900</x:v>
       </x:c>
       <x:c r="I49" s="0">
         <x:v>65.8</x:v>
@@ -1967,25 +1967,25 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>348077</x:v>
+        <x:v>386196</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>763767</x:v>
+        <x:v>765340</x:v>
       </x:c>
       <x:c r="E50" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>1111844</x:v>
+        <x:v>1151536</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>7.75385585289039</x:v>
+        <x:v>7.88127225970605</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-415690</x:v>
+        <x:v>-379144</x:v>
       </x:c>
       <x:c r="I50" s="0">
         <x:v>65.8</x:v>
@@ -2002,19 +2002,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>726184</x:v>
+        <x:v>759798</x:v>
       </x:c>
       <x:c r="E51" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>879823</x:v>
+        <x:v>913437</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>6.13577149137611</x:v>
+        <x:v>6.25168964677536</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-572545</x:v>
+        <x:v>-606159</x:v>
       </x:c>
       <x:c r="I51" s="0">
         <x:v>65.8</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -112,24 +112,24 @@
     <x:t>ACAR</x:t>
   </x:si>
   <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
-    <x:t>GLOBAL</x:t>
+    <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
-    <x:t>INVEST AZ</x:t>
+    <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
@@ -178,13 +178,13 @@
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
     <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
     <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
   <x:si>
     <x:t>ZIRAAT</x:t>
@@ -575,25 +575,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1632413</x:v>
+        <x:v>1760051</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>895558</x:v>
+        <x:v>907824</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2527971</x:v>
+        <x:v>2667875</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>17.3017844996955</x:v>
+        <x:v>17.6987742427515</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>736855</x:v>
+        <x:v>852227</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>65.8</x:v>
@@ -610,19 +610,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>421966</x:v>
+        <x:v>448107</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1514979</x:v>
+        <x:v>1541120</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>10.368726611011</x:v>
+        <x:v>10.2238429315426</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>671047</x:v>
+        <x:v>644906</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>65.8</x:v>
@@ -639,19 +639,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>721410</x:v>
+        <x:v>724202</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1947734</x:v>
+        <x:v>1950526</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>13.3305619133803</x:v>
+        <x:v>12.9398563758111</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>504914</x:v>
+        <x:v>502122</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>65.8</x:v>
@@ -677,7 +677,7 @@
         <x:v>235509</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.61185629334308</x:v>
+        <x:v>1.5623747826027</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>235509</x:v>
@@ -706,7 +706,7 @@
         <x:v>214620</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.46888907717875</x:v>
+        <x:v>1.42379644023027</x:v>
       </x:c>
       <x:c r="H6" s="0">
         <x:v>119584</x:v>
@@ -726,19 +726,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>15848</x:v>
+        <x:v>16048</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>130490</x:v>
+        <x:v>130690</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.893091676829072</x:v>
+        <x:v>0.867001941914519</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>98794</x:v>
+        <x:v>98594</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>65.8</x:v>
@@ -755,19 +755,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>4723</x:v>
+        <x:v>4798</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>102395</x:v>
+        <x:v>102470</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.700805596205938</x:v>
+        <x:v>0.679789494131003</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>92949</x:v>
+        <x:v>92874</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>65.8</x:v>
@@ -793,7 +793,7 @@
         <x:v>92027</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.629845564744801</x:v>
+        <x:v>0.610510273996231</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>87973</x:v>
@@ -813,19 +813,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>8306</x:v>
+        <x:v>8465</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>102671</x:v>
+        <x:v>102830</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.702694578524927</x:v>
+        <x:v>0.68217774647693</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>86059</x:v>
+        <x:v>85900</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>65.8</x:v>
@@ -842,19 +842,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>20437</x:v>
+        <x:v>21084</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>117545</x:v>
+        <x:v>118192</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.804494299585204</x:v>
+        <x:v>0.784089781305079</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>76671</x:v>
+        <x:v>76024</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>65.8</x:v>
@@ -871,19 +871,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>25136</x:v>
+        <x:v>25451</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>90237</x:v>
+        <x:v>90552</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.617594556226722</x:v>
+        <x:v>0.600725073412223</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>39965</x:v>
+        <x:v>39650</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>65.8</x:v>
@@ -900,19 +900,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>25362</x:v>
+        <x:v>25606</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>85263</x:v>
+        <x:v>85507</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.583551809651906</x:v>
+        <x:v>0.567256370397771</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>34539</x:v>
+        <x:v>34295</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>65.8</x:v>
@@ -938,7 +938,7 @@
         <x:v>38653</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.264546498463285</x:v>
+        <x:v>0.256425327575345</x:v>
       </x:c>
       <x:c r="H14" s="0">
         <x:v>31347</x:v>
@@ -958,19 +958,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>13006</x:v>
+        <x:v>13620</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>57122</x:v>
+        <x:v>57736</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.390950898642273</x:v>
+        <x:v>0.38302260401237</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>31110</x:v>
+        <x:v>30496</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>65.8</x:v>
@@ -987,19 +987,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>15486</x:v>
+        <x:v>15694</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>38777</x:v>
+        <x:v>38985</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.265395171679063</x:v>
+        <x:v>0.258627826961034</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>7805</x:v>
+        <x:v>7597</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>65.8</x:v>
@@ -1025,7 +1025,7 @@
         <x:v>9303</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0636710235998227</x:v>
+        <x:v>0.0617164210393356</x:v>
       </x:c>
       <x:c r="H17" s="0">
         <x:v>6699</x:v>
@@ -1045,22 +1045,22 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>170125</x:v>
+        <x:v>172834</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>343537</x:v>
+        <x:v>346246</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>2.35121492361736</x:v>
+        <x:v>2.2970078382442</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>3287</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.799</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1083,7 +1083,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>6.84413883691526E-06</x:v>
+        <x:v>6.63403429424224E-06</x:v>
       </x:c>
       <x:c r="H19" s="0">
         <x:v>1</x:v>
@@ -1112,7 +1112,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.000184791748596712</x:v>
+        <x:v>0.000179118925944541</x:v>
       </x:c>
       <x:c r="H20" s="0">
         <x:v>-27</x:v>
@@ -1141,7 +1141,7 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.00169734643155498</x:v>
+        <x:v>0.00164524050497208</x:v>
       </x:c>
       <x:c r="H21" s="0">
         <x:v>-248</x:v>
@@ -1170,7 +1170,7 @@
         <x:v>332</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.00227225409385587</x:v>
+        <x:v>0.00220249938568842</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-332</x:v>
@@ -1190,19 +1190,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>1016</x:v>
+        <x:v>1125</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>1016</x:v>
+        <x:v>1125</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0069536450583059</x:v>
+        <x:v>0.00746328858102252</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-1016</x:v>
+        <x:v>-1125</x:v>
       </x:c>
       <x:c r="I23" s="0">
         <x:v>65.8</x:v>
@@ -1228,7 +1228,7 @@
         <x:v>3081</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0210867917565359</x:v>
+        <x:v>0.0204394596605603</x:v>
       </x:c>
       <x:c r="H24" s="0">
         <x:v>-3081</x:v>
@@ -1248,19 +1248,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>3440</x:v>
+        <x:v>3468</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>3440</x:v>
+        <x:v>3468</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0235438375989885</x:v>
+        <x:v>0.0230068309324321</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-3440</x:v>
+        <x:v>-3468</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>65.8</x:v>
@@ -1271,25 +1271,25 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>8367</x:v>
+        <x:v>1930</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>11981</x:v>
+        <x:v>5853</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>20348</x:v>
+        <x:v>7783</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.139264537053552</x:v>
+        <x:v>0.0516326889120874</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-3614</x:v>
+        <x:v>-3923</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>65.8</x:v>
@@ -1300,25 +1300,25 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>1930</x:v>
+        <x:v>8367</x:v>
       </x:c>
       <x:c r="C27" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>5797</x:v>
+        <x:v>12579</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>7727</x:v>
+        <x:v>20946</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0528846607928442</x:v>
+        <x:v>0.138956482327198</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-3867</x:v>
+        <x:v>-4212</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>65.8</x:v>
@@ -1329,25 +1329,25 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>16941</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>65.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>21289</x:v>
+        <x:v>4354</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>38230</x:v>
+        <x:v>4354</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.26165142773527</x:v>
+        <x:v>0.0288845853171307</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-4348</x:v>
+        <x:v>-4354</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>65.8</x:v>
@@ -1358,25 +1358,25 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>0</x:v>
+        <x:v>16941</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>4354</x:v>
+        <x:v>21420</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>4354</x:v>
+        <x:v>38361</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.029799380495929</x:v>
+        <x:v>0.254488189561427</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-4354</x:v>
+        <x:v>-4479</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>65.8</x:v>
@@ -1387,25 +1387,25 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>1413</x:v>
+        <x:v>204380</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>11064</x:v>
+        <x:v>214248</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>12477</x:v>
+        <x:v>418628</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0853943202681917</x:v>
+        <x:v>2.77719250853004</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-9651</x:v>
+        <x:v>-9868</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>65.8</x:v>
@@ -1416,25 +1416,25 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>204380</x:v>
+        <x:v>1413</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>214248</x:v>
+        <x:v>11498</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>418628</x:v>
+        <x:v>12911</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>2.86514815302016</x:v>
+        <x:v>0.0856520167729616</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-9868</x:v>
+        <x:v>-10085</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>65.8</x:v>
@@ -1451,19 +1451,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>14458</x:v>
+        <x:v>15404</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>17398</x:v>
+        <x:v>18344</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.119074327484652</x:v>
+        <x:v>0.12169472509358</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-11518</x:v>
+        <x:v>-12464</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>65.8</x:v>
@@ -1480,19 +1480,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>116926</x:v>
+        <x:v>117881</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>221772</x:v>
+        <x:v>222727</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>1.51783835814037</x:v>
+        <x:v>1.47757855625369</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-12080</x:v>
+        <x:v>-13035</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>65.8</x:v>
@@ -1509,19 +1509,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>38839</x:v>
+        <x:v>38866</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>52989</x:v>
+        <x:v>53016</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.362664072829303</x:v>
+        <x:v>0.351709962143547</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-24689</x:v>
+        <x:v>-24716</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>65.8</x:v>
@@ -1538,19 +1538,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>27149</x:v>
+        <x:v>28170</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>28597</x:v>
+        <x:v>29618</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.195721838319266</x:v>
+        <x:v>0.196486827726867</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-25701</x:v>
+        <x:v>-26722</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>65.8</x:v>
@@ -1567,19 +1567,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>33594</x:v>
+        <x:v>33777</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>40141</x:v>
+        <x:v>40324</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.274730577052615</x:v>
+        <x:v>0.267510798881024</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-27047</x:v>
+        <x:v>-27230</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>65.8</x:v>
@@ -1605,7 +1605,7 @@
         <x:v>33485</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.229175988954107</x:v>
+        <x:v>0.222140638342701</x:v>
       </x:c>
       <x:c r="H37" s="0">
         <x:v>-33485</x:v>
@@ -1625,19 +1625,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>78516</x:v>
+        <x:v>81885</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>122500</x:v>
+        <x:v>125869</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.838407007522119</x:v>
+        <x:v>0.835019262581977</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-34532</x:v>
+        <x:v>-37901</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>65.8</x:v>
@@ -1654,19 +1654,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>45124</x:v>
+        <x:v>46517</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>50022</x:v>
+        <x:v>51415</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.342357512900175</x:v>
+        <x:v>0.341088873238465</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-40226</x:v>
+        <x:v>-41619</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>65.8</x:v>
@@ -1683,19 +1683,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>222035</x:v>
+        <x:v>222136</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>400787</x:v>
+        <x:v>400888</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>2.74304187203076</x:v>
+        <x:v>2.65950474015018</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-43283</x:v>
+        <x:v>-43384</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>65.8</x:v>
@@ -1712,19 +1712,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>263212</x:v>
+        <x:v>263232</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>475151</x:v>
+        <x:v>475171</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>3.25199941249912</x:v>
+        <x:v>3.15230070962938</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-51273</x:v>
+        <x:v>-51293</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>65.8</x:v>
@@ -1741,19 +1741,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>113573</x:v>
+        <x:v>117156</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>161977</x:v>
+        <x:v>165560</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.10859307638702</x:v>
+        <x:v>1.09833071775475</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-65169</x:v>
+        <x:v>-68752</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>65.8</x:v>
@@ -1770,19 +1770,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>109477</x:v>
+        <x:v>109640</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>138867</x:v>
+        <x:v>139030</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.950425027865911</x:v>
+        <x:v>0.922329787928499</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-80087</x:v>
+        <x:v>-80250</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>65.8</x:v>
@@ -1799,19 +1799,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>135275</x:v>
+        <x:v>135363</x:v>
       </x:c>
       <x:c r="E44" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>135275</x:v>
+        <x:v>135363</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.925840881163712</x:v>
+        <x:v>0.898002784171513</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-135275</x:v>
+        <x:v>-135363</x:v>
       </x:c>
       <x:c r="I44" s="0">
         <x:v>65.8</x:v>
@@ -1828,19 +1828,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>220232</x:v>
+        <x:v>234683</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>287814</x:v>
+        <x:v>302265</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.96983897520793</x:v>
+        <x:v>2.00523637594913</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-152650</x:v>
+        <x:v>-167101</x:v>
       </x:c>
       <x:c r="I45" s="0">
         <x:v>65.8</x:v>
@@ -1857,19 +1857,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>210365</x:v>
+        <x:v>223460</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>248387</x:v>
+        <x:v>261482</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.69999511328487</x:v>
+        <x:v>1.73468055532705</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-172343</x:v>
+        <x:v>-185438</x:v>
       </x:c>
       <x:c r="I46" s="0">
         <x:v>65.8</x:v>
@@ -1886,19 +1886,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>412959</x:v>
+        <x:v>441779</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>612005</x:v>
+        <x:v>640825</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>4.18864718888632</x:v>
+        <x:v>4.25125502660778</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-213913</x:v>
+        <x:v>-242733</x:v>
       </x:c>
       <x:c r="I47" s="0">
         <x:v>65.8</x:v>
@@ -1909,25 +1909,25 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>105687</x:v>
+        <x:v>489929</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>458475</x:v>
+        <x:v>768871</x:v>
       </x:c>
       <x:c r="E48" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>564162</x:v>
+        <x:v>1258800</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>3.86120305451179</x:v>
+        <x:v>8.35092236959213</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-352788</x:v>
+        <x:v>-278942</x:v>
       </x:c>
       <x:c r="I48" s="0">
         <x:v>65.8</x:v>
@@ -1938,25 +1938,25 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>218049</x:v>
+        <x:v>105687</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>577949</x:v>
+        <x:v>473001</x:v>
       </x:c>
       <x:c r="E49" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>795998</x:v>
+        <x:v>578688</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>5.44792082590687</x:v>
+        <x:v>3.83903603766645</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-359900</x:v>
+        <x:v>-367314</x:v>
       </x:c>
       <x:c r="I49" s="0">
         <x:v>65.8</x:v>
@@ -1967,25 +1967,25 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>386196</x:v>
+        <x:v>218049</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>765340</x:v>
+        <x:v>616699</x:v>
       </x:c>
       <x:c r="E50" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>1151536</x:v>
+        <x:v>834748</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>7.88127225970605</x:v>
+        <x:v>5.53774685905012</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-379144</x:v>
+        <x:v>-398650</x:v>
       </x:c>
       <x:c r="I50" s="0">
         <x:v>65.8</x:v>
@@ -2002,19 +2002,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>759798</x:v>
+        <x:v>818421</x:v>
       </x:c>
       <x:c r="E51" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>913437</x:v>
+        <x:v>972060</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>6.25168964677536</x:v>
+        <x:v>6.44867937606111</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-606159</x:v>
+        <x:v>-664782</x:v>
       </x:c>
       <x:c r="I51" s="0">
         <x:v>65.8</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -55,15 +55,15 @@
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
@@ -88,15 +88,15 @@
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
     <x:t>BIZIM</x:t>
   </x:si>
   <x:si>
@@ -112,28 +112,28 @@
     <x:t>ACAR</x:t>
   </x:si>
   <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
     <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
     <x:t>TERA</x:t>
@@ -575,25 +575,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1760051</x:v>
+        <x:v>1770051</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>907824</x:v>
+        <x:v>910714</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2667875</x:v>
+        <x:v>2680765</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>17.6987742427515</x:v>
+        <x:v>17.5802094412099</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>852227</x:v>
+        <x:v>859337</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>65.8</x:v>
@@ -610,19 +610,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>448107</x:v>
+        <x:v>457145</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1541120</x:v>
+        <x:v>1550158</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>10.2238429315426</x:v>
+        <x:v>10.1657930877817</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>644906</x:v>
+        <x:v>635868</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>65.8</x:v>
@@ -633,25 +633,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>1226324</x:v>
+        <x:v>1233926</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>724202</x:v>
+        <x:v>725236</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1950526</x:v>
+        <x:v>1959162</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>12.9398563758111</x:v>
+        <x:v>12.8480035696003</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>502122</x:v>
+        <x:v>508690</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>65.8</x:v>
@@ -677,7 +677,7 @@
         <x:v>235509</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.5623747826027</x:v>
+        <x:v>1.54444628503054</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>235509</x:v>
@@ -706,7 +706,7 @@
         <x:v>214620</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.42379644023027</x:v>
+        <x:v>1.40745815103989</x:v>
       </x:c>
       <x:c r="H6" s="0">
         <x:v>119584</x:v>
@@ -720,25 +720,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>114642</x:v>
+        <x:v>110000</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>16048</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>130690</x:v>
+        <x:v>112027</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.867001941914519</x:v>
+        <x:v>0.734662726151087</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>98594</x:v>
+        <x:v>107973</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>65.8</x:v>
@@ -749,25 +749,25 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>97672</x:v>
+        <x:v>114642</x:v>
       </x:c>
       <x:c r="C8" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>4798</x:v>
+        <x:v>16068</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>102470</x:v>
+        <x:v>130710</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.679789494131003</x:v>
+        <x:v>0.857184115750743</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>92874</x:v>
+        <x:v>98574</x:v>
       </x:c>
       <x:c r="I8" s="0">
         <x:v>65.8</x:v>
@@ -778,25 +778,25 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>90000</x:v>
+        <x:v>97672</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>2027</x:v>
+        <x:v>4805</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>92027</x:v>
+        <x:v>102477</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.610510273996231</x:v>
+        <x:v>0.672034707595356</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>87973</x:v>
+        <x:v>92867</x:v>
       </x:c>
       <x:c r="I9" s="0">
         <x:v>65.8</x:v>
@@ -813,19 +813,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>8465</x:v>
+        <x:v>8519</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>102830</x:v>
+        <x:v>102884</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.68217774647693</x:v>
+        <x:v>0.674703776030139</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>85900</x:v>
+        <x:v>85846</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>65.8</x:v>
@@ -842,19 +842,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>21084</x:v>
+        <x:v>21858</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>118192</x:v>
+        <x:v>118966</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.784089781305079</x:v>
+        <x:v>0.78016804769645</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>76024</x:v>
+        <x:v>75250</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>65.8</x:v>
@@ -865,25 +865,25 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>65101</x:v>
+        <x:v>85858</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>25451</x:v>
+        <x:v>25530</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>90552</x:v>
+        <x:v>111388</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.600725073412223</x:v>
+        <x:v>0.730472223129399</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>39650</x:v>
+        <x:v>60328</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>65.8</x:v>
@@ -894,7 +894,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>59901</x:v>
+        <x:v>69901</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>65.8</x:v>
@@ -906,13 +906,13 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>85507</x:v>
+        <x:v>95507</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.567256370397771</x:v>
+        <x:v>0.626326090911225</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>34295</x:v>
+        <x:v>44295</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>65.8</x:v>
@@ -938,7 +938,7 @@
         <x:v>38653</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.256425327575345</x:v>
+        <x:v>0.253482806412007</x:v>
       </x:c>
       <x:c r="H14" s="0">
         <x:v>31347</x:v>
@@ -958,19 +958,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>13620</x:v>
+        <x:v>13810</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>57736</x:v>
+        <x:v>57926</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.38302260401237</x:v>
+        <x:v>0.379873361555945</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>30496</x:v>
+        <x:v>30306</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>65.8</x:v>
@@ -987,19 +987,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>15694</x:v>
+        <x:v>15774</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>38985</x:v>
+        <x:v>39065</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.258627826961034</x:v>
+        <x:v>0.256184664385302</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>7597</x:v>
+        <x:v>7517</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>65.8</x:v>
@@ -1025,7 +1025,7 @@
         <x:v>9303</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0617164210393356</x:v>
+        <x:v>0.0610082153532948</x:v>
       </x:c>
       <x:c r="H17" s="0">
         <x:v>6699</x:v>
@@ -1039,28 +1039,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>173412</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>172834</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>65.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>346246</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>2.2970078382442</x:v>
+        <x:v>6.55790770217079E-06</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>578</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>65.799</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,28 +1068,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>65</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>0</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>0</x:v>
+        <x:v>65.815</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>1</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>6.63403429424224E-06</x:v>
+        <x:v>0.000177063507958611</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>1</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>65</x:v>
+        <x:v>65.815</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1097,28 +1097,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>0</x:v>
+        <x:v>173412</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>27</x:v>
+        <x:v>173453</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>65.815</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>27</x:v>
+        <x:v>346865</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.000179118925944541</x:v>
+        <x:v>2.27470865511347</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-27</x:v>
+        <x:v>-41</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>65.815</x:v>
+        <x:v>65.829</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1141,7 +1141,7 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.00164524050497208</x:v>
+        <x:v>0.00162636111013835</x:v>
       </x:c>
       <x:c r="H21" s="0">
         <x:v>-248</x:v>
@@ -1170,7 +1170,7 @@
         <x:v>332</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.00220249938568842</x:v>
+        <x:v>0.0021772253571207</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>-332</x:v>
@@ -1199,7 +1199,7 @@
         <x:v>1125</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.00746328858102252</x:v>
+        <x:v>0.00737764616494213</x:v>
       </x:c>
       <x:c r="H23" s="0">
         <x:v>-1125</x:v>
@@ -1228,7 +1228,7 @@
         <x:v>3081</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0204394596605603</x:v>
+        <x:v>0.0202049136303882</x:v>
       </x:c>
       <x:c r="H24" s="0">
         <x:v>-3081</x:v>
@@ -1248,19 +1248,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>3468</x:v>
+        <x:v>3474</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>3468</x:v>
+        <x:v>3474</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0230068309324321</x:v>
+        <x:v>0.0227821713573413</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-3468</x:v>
+        <x:v>-3474</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>65.8</x:v>
@@ -1271,25 +1271,25 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>1930</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>65.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>5853</x:v>
+        <x:v>4354</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>7783</x:v>
+        <x:v>4354</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0516326889120874</x:v>
+        <x:v>0.0285531301352516</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-3923</x:v>
+        <x:v>-4354</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>65.8</x:v>
@@ -1306,19 +1306,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>12579</x:v>
+        <x:v>12761</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>20946</x:v>
+        <x:v>21128</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.138956482327198</x:v>
+        <x:v>0.138555473931464</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-4212</x:v>
+        <x:v>-4394</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>65.8</x:v>
@@ -1329,25 +1329,25 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>0</x:v>
+        <x:v>16941</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>4354</x:v>
+        <x:v>21530</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>4354</x:v>
+        <x:v>38471</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0288845853171307</x:v>
+        <x:v>0.252289267210212</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-4354</x:v>
+        <x:v>-4589</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>65.8</x:v>
@@ -1358,25 +1358,25 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>16941</x:v>
+        <x:v>112106</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>21420</x:v>
+        <x:v>117991</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>38361</x:v>
+        <x:v>230097</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.254488189561427</x:v>
+        <x:v>1.50895488854639</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-4479</x:v>
+        <x:v>-5885</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>65.8</x:v>
@@ -1402,7 +1402,7 @@
         <x:v>418628</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>2.77719250853004</x:v>
+        <x:v>2.74532378554435</x:v>
       </x:c>
       <x:c r="H30" s="0">
         <x:v>-9868</x:v>
@@ -1422,19 +1422,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>11498</x:v>
+        <x:v>11679</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>12911</x:v>
+        <x:v>13092</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0856520167729616</x:v>
+        <x:v>0.0858561276368199</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-10085</x:v>
+        <x:v>-10266</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>65.8</x:v>
@@ -1445,25 +1445,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>2940</x:v>
+        <x:v>3340</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>15404</x:v>
+        <x:v>15813</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>18344</x:v>
+        <x:v>19153</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.12169472509358</x:v>
+        <x:v>0.125603606219677</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-12464</x:v>
+        <x:v>-12473</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>65.8</x:v>
@@ -1474,25 +1474,25 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>104846</x:v>
+        <x:v>2029</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>117881</x:v>
+        <x:v>20881</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>222727</x:v>
+        <x:v>22910</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>1.47757855625369</x:v>
+        <x:v>0.150241665456733</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-13035</x:v>
+        <x:v>-18852</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>65.8</x:v>
@@ -1518,7 +1518,7 @@
         <x:v>53016</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.351709962143547</x:v>
+        <x:v>0.347674034738286</x:v>
       </x:c>
       <x:c r="H34" s="0">
         <x:v>-24716</x:v>
@@ -1538,19 +1538,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>28170</x:v>
+        <x:v>28468</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>29618</x:v>
+        <x:v>29916</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.196486827726867</x:v>
+        <x:v>0.196186366818141</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-26722</x:v>
+        <x:v>-27020</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>65.8</x:v>
@@ -1567,19 +1567,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>33777</x:v>
+        <x:v>33858</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>40324</x:v>
+        <x:v>40405</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.267510798881024</x:v>
+        <x:v>0.264972260706211</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-27230</x:v>
+        <x:v>-27311</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>65.8</x:v>
@@ -1605,7 +1605,7 @@
         <x:v>33485</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.222140638342701</x:v>
+        <x:v>0.219591539407189</x:v>
       </x:c>
       <x:c r="H37" s="0">
         <x:v>-33485</x:v>
@@ -1625,19 +1625,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>81885</x:v>
+        <x:v>82466</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>125869</x:v>
+        <x:v>126450</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.835019262581977</x:v>
+        <x:v>0.829247428939496</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-37901</x:v>
+        <x:v>-38482</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>65.8</x:v>
@@ -1654,19 +1654,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>46517</x:v>
+        <x:v>47054</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>51415</x:v>
+        <x:v>51952</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.341088873238465</x:v>
+        <x:v>0.340696420943177</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-41619</x:v>
+        <x:v>-42156</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>65.8</x:v>
@@ -1683,19 +1683,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>222136</x:v>
+        <x:v>222148</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>400888</x:v>
+        <x:v>400900</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>2.65950474015018</x:v>
+        <x:v>2.62906519780027</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-43384</x:v>
+        <x:v>-43396</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>65.8</x:v>
@@ -1712,19 +1712,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>263232</x:v>
+        <x:v>263259</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>475171</x:v>
+        <x:v>475198</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>3.15230070962938</x:v>
+        <x:v>3.11630462425615</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-51293</x:v>
+        <x:v>-51320</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>65.8</x:v>
@@ -1741,19 +1741,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>117156</x:v>
+        <x:v>117767</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>165560</x:v>
+        <x:v>166171</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.09833071775475</x:v>
+        <x:v>1.08973408077742</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-68752</x:v>
+        <x:v>-69363</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>65.8</x:v>
@@ -1770,19 +1770,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>109640</x:v>
+        <x:v>109743</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>139030</x:v>
+        <x:v>139133</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.922329787928499</x:v>
+        <x:v>0.912421372326128</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-80250</x:v>
+        <x:v>-80353</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>65.8</x:v>
@@ -1808,7 +1808,7 @@
         <x:v>135363</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.898002784171513</x:v>
+        <x:v>0.887698060288944</x:v>
       </x:c>
       <x:c r="H44" s="0">
         <x:v>-135363</x:v>
@@ -1822,25 +1822,25 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>67582</x:v>
+        <x:v>77582</x:v>
       </x:c>
       <x:c r="C45" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>234683</x:v>
+        <x:v>238690</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>302265</x:v>
+        <x:v>316272</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>2.00523637594913</x:v>
+        <x:v>2.07408258478096</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-167101</x:v>
+        <x:v>-161108</x:v>
       </x:c>
       <x:c r="I45" s="0">
         <x:v>65.8</x:v>
@@ -1851,25 +1851,25 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>38022</x:v>
+        <x:v>38082</x:v>
       </x:c>
       <x:c r="C46" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>223460</x:v>
+        <x:v>227985</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>261482</x:v>
+        <x:v>266067</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.73468055532705</x:v>
+        <x:v>1.74484282859347</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-185438</x:v>
+        <x:v>-189903</x:v>
       </x:c>
       <x:c r="I46" s="0">
         <x:v>65.8</x:v>
@@ -1886,19 +1886,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>441779</x:v>
+        <x:v>450453</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>640825</x:v>
+        <x:v>649499</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>4.25125502660778</x:v>
+        <x:v>4.25935449465222</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-242733</x:v>
+        <x:v>-251407</x:v>
       </x:c>
       <x:c r="I47" s="0">
         <x:v>65.8</x:v>
@@ -1909,25 +1909,25 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>489929</x:v>
+        <x:v>490980</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>768871</x:v>
+        <x:v>769204</x:v>
       </x:c>
       <x:c r="E48" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>1258800</x:v>
+        <x:v>1260184</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>8.35092236959213</x:v>
+        <x:v>8.26417035975239</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-278942</x:v>
+        <x:v>-278224</x:v>
       </x:c>
       <x:c r="I48" s="0">
         <x:v>65.8</x:v>
@@ -1938,25 +1938,25 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>105687</x:v>
+        <x:v>105830</x:v>
       </x:c>
       <x:c r="C49" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>473001</x:v>
+        <x:v>477983</x:v>
       </x:c>
       <x:c r="E49" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>578688</x:v>
+        <x:v>583813</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.83903603766645</x:v>
+        <x:v>3.82859176932743</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-367314</x:v>
+        <x:v>-372153</x:v>
       </x:c>
       <x:c r="I49" s="0">
         <x:v>65.8</x:v>
@@ -1967,25 +1967,25 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>218049</x:v>
+        <x:v>218062</x:v>
       </x:c>
       <x:c r="C50" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>616699</x:v>
+        <x:v>628526</x:v>
       </x:c>
       <x:c r="E50" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>834748</x:v>
+        <x:v>846588</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>5.53774685905012</x:v>
+        <x:v>5.55184596576536</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-398650</x:v>
+        <x:v>-410464</x:v>
       </x:c>
       <x:c r="I50" s="0">
         <x:v>65.8</x:v>
@@ -1996,25 +1996,25 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>153639</x:v>
+        <x:v>153745</x:v>
       </x:c>
       <x:c r="C51" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>818421</x:v>
+        <x:v>838503</x:v>
       </x:c>
       <x:c r="E51" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>972060</x:v>
+        <x:v>992248</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>6.44867937606111</x:v>
+        <x:v>6.50707080166356</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-664782</x:v>
+        <x:v>-684758</x:v>
       </x:c>
       <x:c r="I51" s="0">
         <x:v>65.8</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -64,15 +64,15 @@
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
     <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
     <x:t>ATA</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
@@ -82,6 +82,9 @@
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
@@ -94,7 +97,7 @@
     <x:t>TURKISH</x:t>
   </x:si>
   <x:si>
-    <x:t>QNB YATIRIM</x:t>
+    <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
     <x:t>BIZIM</x:t>
@@ -121,9 +124,6 @@
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
@@ -136,13 +136,13 @@
     <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
     <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
     <x:t>PIRAMIT</x:t>
@@ -575,28 +575,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1770051</x:v>
+        <x:v>1770073</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>910714</x:v>
+        <x:v>914867</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2680765</x:v>
+        <x:v>2684940</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>17.5802094412099</x:v>
+        <x:v>17.4144496852552</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>859337</x:v>
+        <x:v>855206</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -604,28 +604,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1093013</x:v>
+        <x:v>1093015</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>457145</x:v>
+        <x:v>468106</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1550158</x:v>
+        <x:v>1561121</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>10.1657930877817</x:v>
+        <x:v>10.1253894340638</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>635868</x:v>
+        <x:v>624909</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -636,25 +636,25 @@
         <x:v>1233926</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>725236</x:v>
+        <x:v>725554</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1959162</x:v>
+        <x:v>1959480</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>12.8480035696003</x:v>
+        <x:v>12.7091353509813</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>508690</x:v>
+        <x:v>508372</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -665,7 +665,7 @@
         <x:v>235509</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D5" s="0">
         <x:v>0</x:v>
@@ -677,13 +677,13 @@
         <x:v>235509</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.54444628503054</x:v>
+        <x:v>1.52750513267513</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>235509</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -694,25 +694,25 @@
         <x:v>167102</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>47518</x:v>
+        <x:v>47529</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>214620</x:v>
+        <x:v>214631</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.40745815103989</x:v>
+        <x:v>1.39209097797195</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>119584</x:v>
+        <x:v>119573</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -723,25 +723,25 @@
         <x:v>110000</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D7" s="0">
         <x:v>2027</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>112027</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.734662726151087</x:v>
+        <x:v>0.726604153124494</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>107973</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -749,28 +749,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>114642</x:v>
+        <x:v>114792</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>16068</x:v>
+        <x:v>16106</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>130710</x:v>
+        <x:v>130898</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.857184115750743</x:v>
+        <x:v>0.849000959016042</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>98574</x:v>
+        <x:v>98686</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -781,25 +781,25 @@
         <x:v>97672</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>4805</x:v>
+        <x:v>4940</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>102477</x:v>
+        <x:v>102612</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.672034707595356</x:v>
+        <x:v>0.665538712635442</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>92867</x:v>
+        <x:v>92732</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -807,28 +807,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>94365</x:v>
+        <x:v>115101</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>8519</x:v>
+        <x:v>25657</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>102884</x:v>
+        <x:v>140758</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.674703776030139</x:v>
+        <x:v>0.912952657711959</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>85846</x:v>
+        <x:v>89444</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -836,28 +836,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>97108</x:v>
+        <x:v>94365</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>21858</x:v>
+        <x:v>8601</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>118966</x:v>
+        <x:v>102966</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.78016804769645</x:v>
+        <x:v>0.667834747253936</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>75250</x:v>
+        <x:v>85764</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -865,28 +865,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>85858</x:v>
+        <x:v>97108</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>25530</x:v>
+        <x:v>22116</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>111388</x:v>
+        <x:v>119224</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.730472223129399</x:v>
+        <x:v>0.773283704393715</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>60328</x:v>
+        <x:v>74992</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -897,25 +897,25 @@
         <x:v>69901</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>25606</x:v>
+        <x:v>25768</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>95507</x:v>
+        <x:v>95669</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.626326090911225</x:v>
+        <x:v>0.620506598634858</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>44295</x:v>
+        <x:v>44133</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -926,25 +926,25 @@
         <x:v>35000</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D14" s="0">
         <x:v>3653</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F14" s="0">
         <x:v>38653</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.253482806412007</x:v>
+        <x:v>0.250702333640293</x:v>
       </x:c>
       <x:c r="H14" s="0">
         <x:v>31347</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -955,25 +955,25 @@
         <x:v>44116</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>13810</x:v>
+        <x:v>13945</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>57926</x:v>
+        <x:v>58061</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.379873361555945</x:v>
+        <x:v>0.376582107300573</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>30306</x:v>
+        <x:v>30171</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -981,28 +981,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>23291</x:v>
+        <x:v>203412</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>15774</x:v>
+        <x:v>175008</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>39065</x:v>
+        <x:v>378420</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.256184664385302</x:v>
+        <x:v>2.45442209132951</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>7517</x:v>
+        <x:v>28404</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1010,28 +1010,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>8001</x:v>
+        <x:v>25791</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>1302</x:v>
+        <x:v>15829</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>9303</x:v>
+        <x:v>41620</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.0610082153532948</x:v>
+        <x:v>0.269946217010555</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>6699</x:v>
+        <x:v>9962</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1039,28 +1039,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>1</x:v>
+        <x:v>8001</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>65</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>0</x:v>
+        <x:v>1329</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1</x:v>
+        <x:v>9330</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>6.55790770217079E-06</x:v>
+        <x:v>0.0605141327416742</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>1</x:v>
+        <x:v>6672</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>65</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,28 +1068,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>65.815</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.000177063507958611</x:v>
+        <x:v>6.48597349857172E-06</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>-27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>65.815</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1097,28 +1097,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>173412</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>65.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>173453</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>346865</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>2.27470865511347</x:v>
+        <x:v>0.000175121284461437</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-41</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>65.829</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1126,28 +1126,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>0</x:v>
+        <x:v>118106</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>248</x:v>
+        <x:v>118159</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>65.798</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>248</x:v>
+        <x:v>236265</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.00162636111013835</x:v>
+        <x:v>1.53240852864005</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-248</x:v>
+        <x:v>-53</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>65.798</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1161,22 +1161,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>332</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>65.801</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>332</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0021772253571207</x:v>
+        <x:v>0.00160852142764579</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-332</x:v>
+        <x:v>-248</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>65.801</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1190,22 +1190,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>1125</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>1125</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.00737764616494213</x:v>
+        <x:v>0.00231549253899011</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-1125</x:v>
+        <x:v>-357</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1219,22 +1219,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>3081</x:v>
+        <x:v>1125</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>3081</x:v>
+        <x:v>1125</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0202049136303882</x:v>
+        <x:v>0.00729672018589319</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-3081</x:v>
+        <x:v>-1125</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1248,22 +1248,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>3474</x:v>
+        <x:v>3081</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>3474</x:v>
+        <x:v>3081</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0227821713573413</x:v>
+        <x:v>0.0199832843490995</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-3474</x:v>
+        <x:v>-3081</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1277,22 +1277,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>4354</x:v>
+        <x:v>3474</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>4354</x:v>
+        <x:v>3474</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0285531301352516</x:v>
+        <x:v>0.0225322719340382</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-4354</x:v>
+        <x:v>-3474</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1300,28 +1300,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>8367</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>65.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>12761</x:v>
+        <x:v>4381</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>21128</x:v>
+        <x:v>4381</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.138555473931464</x:v>
+        <x:v>0.0284150498972427</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-4394</x:v>
+        <x:v>-4381</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1329,28 +1329,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>16941</x:v>
+        <x:v>8367</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>21530</x:v>
+        <x:v>12921</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>38471</x:v>
+        <x:v>21288</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.252289267210212</x:v>
+        <x:v>0.138073403837595</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-4589</x:v>
+        <x:v>-4554</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1358,28 +1358,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>112106</x:v>
+        <x:v>16941</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>117991</x:v>
+        <x:v>21624</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>230097</x:v>
+        <x:v>38565</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>1.50895488854639</x:v>
+        <x:v>0.250131567972419</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-5885</x:v>
+        <x:v>-4683</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1390,25 +1390,25 @@
         <x:v>204380</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>214248</x:v>
+        <x:v>214296</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>418628</x:v>
+        <x:v>418676</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>2.74532378554435</x:v>
+        <x:v>2.71552144048802</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-9868</x:v>
+        <x:v>-9916</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1419,25 +1419,25 @@
         <x:v>1413</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>11679</x:v>
+        <x:v>11923</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>13092</x:v>
+        <x:v>13336</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0858561276368199</x:v>
+        <x:v>0.0864969425769525</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-10266</x:v>
+        <x:v>-10510</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1448,25 +1448,25 @@
         <x:v>3340</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>15813</x:v>
+        <x:v>16263</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>19153</x:v>
+        <x:v>19603</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.125603606219677</x:v>
+        <x:v>0.127144538492502</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-12473</x:v>
+        <x:v>-12923</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1477,25 +1477,25 @@
         <x:v>2029</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>20881</x:v>
+        <x:v>20937</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>22910</x:v>
+        <x:v>22966</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.150241665456733</x:v>
+        <x:v>0.148956867368198</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-18852</x:v>
+        <x:v>-18908</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1503,28 +1503,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>14150</x:v>
+        <x:v>11756</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>38866</x:v>
+        <x:v>33886</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>53016</x:v>
+        <x:v>45642</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.347674034738286</x:v>
+        <x:v>0.296032802421811</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-24716</x:v>
+        <x:v>-22130</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1532,28 +1532,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>1448</x:v>
+        <x:v>14150</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>28468</x:v>
+        <x:v>38893</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>29916</x:v>
+        <x:v>53043</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.196186366818141</x:v>
+        <x:v>0.34403549228474</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-27020</x:v>
+        <x:v>-24743</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1561,28 +1561,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>6547</x:v>
+        <x:v>1448</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>33858</x:v>
+        <x:v>28656</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>40405</x:v>
+        <x:v>30104</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.264972260706211</x:v>
+        <x:v>0.195253746201003</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-27311</x:v>
+        <x:v>-27208</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1599,19 +1599,19 @@
         <x:v>33485</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F37" s="0">
         <x:v>33485</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.219591539407189</x:v>
+        <x:v>0.217182822599674</x:v>
       </x:c>
       <x:c r="H37" s="0">
         <x:v>-33485</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1622,25 +1622,25 @@
         <x:v>43984</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>82466</x:v>
+        <x:v>83318</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>126450</x:v>
+        <x:v>127302</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.829247428939496</x:v>
+        <x:v>0.825677398315178</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-38482</x:v>
+        <x:v>-39334</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1651,25 +1651,25 @@
         <x:v>4898</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>47054</x:v>
+        <x:v>47811</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>51952</x:v>
+        <x:v>52709</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.340696420943177</x:v>
+        <x:v>0.341869177136217</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-42156</x:v>
+        <x:v>-42913</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1680,25 +1680,25 @@
         <x:v>178752</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>222148</x:v>
+        <x:v>222202</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>400900</x:v>
+        <x:v>400954</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>2.62906519780027</x:v>
+        <x:v>2.60057701814633</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-43396</x:v>
+        <x:v>-43450</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1706,28 +1706,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>211939</x:v>
+        <x:v>214438</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>263259</x:v>
+        <x:v>263287</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>475198</x:v>
+        <x:v>477725</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>3.11630462425615</x:v>
+        <x:v>3.09851168960518</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-51320</x:v>
+        <x:v>-48849</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1735,28 +1735,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>48404</x:v>
+        <x:v>48554</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>117767</x:v>
+        <x:v>119230</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>166171</x:v>
+        <x:v>167784</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.08973408077742</x:v>
+        <x:v>1.08824257748436</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-69363</x:v>
+        <x:v>-70676</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1767,25 +1767,25 @@
         <x:v>29390</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>109743</x:v>
+        <x:v>109825</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>139133</x:v>
+        <x:v>139215</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.912421372326128</x:v>
+        <x:v>0.902944800603662</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-80353</x:v>
+        <x:v>-80435</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1802,19 +1802,19 @@
         <x:v>135363</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F44" s="0">
         <x:v>135363</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.887698060288944</x:v>
+        <x:v>0.877960830687164</x:v>
       </x:c>
       <x:c r="H44" s="0">
         <x:v>-135363</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1822,28 +1822,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>77582</x:v>
+        <x:v>77633</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>238690</x:v>
+        <x:v>243925</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>316272</x:v>
+        <x:v>321558</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>2.07408258478096</x:v>
+        <x:v>2.08561666625373</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-161108</x:v>
+        <x:v>-166292</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1851,28 +1851,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>38082</x:v>
+        <x:v>46770</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>227985</x:v>
+        <x:v>233074</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>266067</x:v>
+        <x:v>279844</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.74484282859347</x:v>
+        <x:v>1.81506076773431</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-189903</x:v>
+        <x:v>-186304</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1883,25 +1883,25 @@
         <x:v>199046</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>450453</x:v>
+        <x:v>460852</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>649499</x:v>
+        <x:v>659898</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>4.25935449465222</x:v>
+        <x:v>4.28008093976048</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-251407</x:v>
+        <x:v>-261806</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1912,25 +1912,25 @@
         <x:v>490980</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>769204</x:v>
+        <x:v>769744</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>1260184</x:v>
+        <x:v>1260724</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>8.26417035975239</x:v>
+        <x:v>8.17702245301334</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-278224</x:v>
+        <x:v>-278764</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1941,25 +1941,25 @@
         <x:v>105830</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>477983</x:v>
+        <x:v>483587</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>583813</x:v>
+        <x:v>589417</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.82859176932743</x:v>
+        <x:v>3.82294304160765</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-372153</x:v>
+        <x:v>-377757</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1967,28 +1967,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>218062</x:v>
+        <x:v>218108</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>628526</x:v>
+        <x:v>641583</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>846588</x:v>
+        <x:v>859691</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>5.55184596576536</x:v>
+        <x:v>5.57593304296062</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-410464</x:v>
+        <x:v>-423475</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1999,25 +1999,25 @@
         <x:v>153745</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>838503</x:v>
+        <x:v>860371</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>992248</x:v>
+        <x:v>1014116</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>6.50707080166356</x:v>
+        <x:v>6.57752950047756</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-684758</x:v>
+        <x:v>-706626</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -73,6 +73,9 @@
     <x:t>ATA</x:t>
   </x:si>
   <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
@@ -88,18 +91,21 @@
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>ANADOLU</x:t>
   </x:si>
   <x:si>
     <x:t>TURKISH</x:t>
   </x:si>
   <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
     <x:t>BIZIM</x:t>
   </x:si>
   <x:si>
@@ -118,30 +124,24 @@
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
     <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
     <x:t>ING</x:t>
   </x:si>
   <x:si>
@@ -151,10 +151,10 @@
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
     <x:t>ALNUS</x:t>
@@ -575,28 +575,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1770073</x:v>
+        <x:v>1770074</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>914867</x:v>
+        <x:v>919450</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2684940</x:v>
+        <x:v>2689524</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>17.4144496852552</x:v>
+        <x:v>17.1669889185028</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>855206</x:v>
+        <x:v>850624</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -604,28 +604,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1093015</x:v>
+        <x:v>1093017</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>468106</x:v>
+        <x:v>481977</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1561121</x:v>
+        <x:v>1574994</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>10.1253894340638</x:v>
+        <x:v>10.0530445330506</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>624909</x:v>
+        <x:v>611040</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -633,28 +633,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>1233926</x:v>
+        <x:v>1233927</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>725554</x:v>
+        <x:v>727297</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1959480</x:v>
+        <x:v>1961224</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>12.7091353509813</x:v>
+        <x:v>12.5183157594807</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>508372</x:v>
+        <x:v>506630</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -665,7 +665,7 @@
         <x:v>235509</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D5" s="0">
         <x:v>0</x:v>
@@ -677,13 +677,13 @@
         <x:v>235509</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.52750513267513</x:v>
+        <x:v>1.50323268846371</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>235509</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -694,25 +694,25 @@
         <x:v>167102</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D6" s="0">
         <x:v>47529</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F6" s="0">
         <x:v>214631</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.39209097797195</x:v>
+        <x:v>1.36997029904443</x:v>
       </x:c>
       <x:c r="H6" s="0">
         <x:v>119573</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -723,25 +723,25 @@
         <x:v>110000</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D7" s="0">
         <x:v>2027</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>112027</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.726604153124494</x:v>
+        <x:v>0.715058228732336</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>107973</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -749,28 +749,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>114792</x:v>
+        <x:v>114793</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>16106</x:v>
+        <x:v>16126</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>130898</x:v>
+        <x:v>130919</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.849000959016042</x:v>
+        <x:v>0.835644159420575</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>98686</x:v>
+        <x:v>98667</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -781,25 +781,25 @@
         <x:v>97672</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>4940</x:v>
+        <x:v>4967</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>102612</x:v>
+        <x:v>102639</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.665538712635442</x:v>
+        <x:v>0.655135472152769</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>92732</x:v>
+        <x:v>92705</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -810,25 +810,25 @@
         <x:v>115101</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>25657</x:v>
+        <x:v>25798</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>140758</x:v>
+        <x:v>140899</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.912952657711959</x:v>
+        <x:v>0.899345598562467</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>89444</x:v>
+        <x:v>89303</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -839,25 +839,25 @@
         <x:v>94365</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>8601</x:v>
+        <x:v>8872</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>102966</x:v>
+        <x:v>103237</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.667834747253936</x:v>
+        <x:v>0.658952452173496</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>85764</x:v>
+        <x:v>85493</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -868,25 +868,25 @@
         <x:v>97108</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>22116</x:v>
+        <x:v>22622</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>119224</x:v>
+        <x:v>119730</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.773283704393715</x:v>
+        <x:v>0.764225782410692</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>74992</x:v>
+        <x:v>74486</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -894,28 +894,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>69901</x:v>
+        <x:v>112934</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>25768</x:v>
+        <x:v>38920</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>95669</x:v>
+        <x:v>151854</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.620506598634858</x:v>
+        <x:v>0.969270374694674</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>44133</x:v>
+        <x:v>74014</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -923,28 +923,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>35000</x:v>
+        <x:v>69901</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>3653</x:v>
+        <x:v>34669</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>38653</x:v>
+        <x:v>104570</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.250702333640293</x:v>
+        <x:v>0.66746087084846</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>31347</x:v>
+        <x:v>35232</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -952,28 +952,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>44116</x:v>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>13945</x:v>
+        <x:v>3680</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>58061</x:v>
+        <x:v>38680</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.376582107300573</x:v>
+        <x:v>0.246890948497833</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>30171</x:v>
+        <x:v>31320</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -981,28 +981,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>203412</x:v>
+        <x:v>44116</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>175008</x:v>
+        <x:v>14474</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>378420</x:v>
+        <x:v>58590</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>2.45442209132951</x:v>
+        <x:v>0.373974681294934</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>28404</x:v>
+        <x:v>29642</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1010,28 +1010,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>25791</x:v>
+        <x:v>203412</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>15829</x:v>
+        <x:v>176436</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>41620</x:v>
+        <x:v>379848</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.269946217010555</x:v>
+        <x:v>2.42453549650995</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>9962</x:v>
+        <x:v>26976</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1039,28 +1039,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>8001</x:v>
+        <x:v>25792</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>1329</x:v>
+        <x:v>15965</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>9330</x:v>
+        <x:v>41757</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.0605141327416742</x:v>
+        <x:v>0.266531161748294</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>6672</x:v>
+        <x:v>9827</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,28 +1068,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>1</x:v>
+        <x:v>128108</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>0</x:v>
+        <x:v>118326</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>1</x:v>
+        <x:v>246434</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>6.48597349857172E-06</x:v>
+        <x:v>1.5729659773039</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>1</x:v>
+        <x:v>9782</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1097,28 +1097,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>0</x:v>
+        <x:v>8001</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>27</x:v>
+        <x:v>1329</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>27</x:v>
+        <x:v>9330</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.000175121284461437</x:v>
+        <x:v>0.0595525478150151</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>-27</x:v>
+        <x:v>6672</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1126,28 +1126,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>118106</x:v>
+        <x:v>214379</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>118159</x:v>
+        <x:v>214304</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>236265</x:v>
+        <x:v>428683</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>1.53240852864005</x:v>
+        <x:v>2.73624489335307</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>-53</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1155,28 +1155,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>0</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>248</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>248</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.00160852142764579</x:v>
+        <x:v>6.3829097336565E-06</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>-248</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1190,22 +1190,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>357</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.815</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>357</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.00231549253899011</x:v>
+        <x:v>0.000172338562808725</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-357</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.815</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1219,22 +1219,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>1125</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.798</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1125</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.00729672018589319</x:v>
+        <x:v>0.00158296161394681</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-1125</x:v>
+        <x:v>-248</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.798</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1248,22 +1248,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>3081</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.801</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>3081</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0199832843490995</x:v>
+        <x:v>0.00227869877491537</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-3081</x:v>
+        <x:v>-357</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.801</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1277,22 +1277,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>3474</x:v>
+        <x:v>1206</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>3474</x:v>
+        <x:v>1206</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0225322719340382</x:v>
+        <x:v>0.00769778913878973</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-3474</x:v>
+        <x:v>-1206</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1306,22 +1306,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>4381</x:v>
+        <x:v>3468</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>4381</x:v>
+        <x:v>3468</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0284150498972427</x:v>
+        <x:v>0.0221359309563207</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-4381</x:v>
+        <x:v>-3468</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1329,28 +1329,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>8367</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>12921</x:v>
+        <x:v>3582</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>21288</x:v>
+        <x:v>3582</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.138073403837595</x:v>
+        <x:v>0.0228635826659576</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-4554</x:v>
+        <x:v>-3582</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1358,28 +1358,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>16941</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>21624</x:v>
+        <x:v>4381</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>38565</x:v>
+        <x:v>4381</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.250131567972419</x:v>
+        <x:v>0.0279635275431491</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-4683</x:v>
+        <x:v>-4381</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1387,28 +1387,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>204380</x:v>
+        <x:v>16941</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>214296</x:v>
+        <x:v>21725</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>418676</x:v>
+        <x:v>38666</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>2.71552144048802</x:v>
+        <x:v>0.246801587761562</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-9916</x:v>
+        <x:v>-4784</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1416,28 +1416,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>1413</x:v>
+        <x:v>8367</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>11923</x:v>
+        <x:v>13378</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>13336</x:v>
+        <x:v>21745</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0864969425769525</x:v>
+        <x:v>0.138796372158361</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-10510</x:v>
+        <x:v>-5011</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1445,28 +1445,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>3340</x:v>
+        <x:v>1413</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>16263</x:v>
+        <x:v>12207</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>19603</x:v>
+        <x:v>13620</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.127144538492502</x:v>
+        <x:v>0.0869352305724015</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-12923</x:v>
+        <x:v>-10794</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1474,28 +1474,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>2029</x:v>
+        <x:v>3340</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>20937</x:v>
+        <x:v>16887</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>22966</x:v>
+        <x:v>20227</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.148956867368198</x:v>
+        <x:v>0.12910711518267</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-18908</x:v>
+        <x:v>-13547</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1503,28 +1503,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>11756</x:v>
+        <x:v>16364</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>33886</x:v>
+        <x:v>33913</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>45642</x:v>
+        <x:v>50277</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.296032802421811</x:v>
+        <x:v>0.320913552679048</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-22130</x:v>
+        <x:v>-17549</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1532,28 +1532,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>14150</x:v>
+        <x:v>2029</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>38893</x:v>
+        <x:v>20965</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>53043</x:v>
+        <x:v>22994</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.34403549228474</x:v>
+        <x:v>0.146768626415697</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-24743</x:v>
+        <x:v>-18936</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1564,25 +1564,25 @@
         <x:v>1448</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>28656</x:v>
+        <x:v>29013</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>30104</x:v>
+        <x:v>30461</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.195253746201003</x:v>
+        <x:v>0.194429813396911</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-27208</x:v>
+        <x:v>-27565</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1596,22 +1596,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>33485</x:v>
+        <x:v>33490</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>33485</x:v>
+        <x:v>33490</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.217182822599674</x:v>
+        <x:v>0.213763646980156</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-33485</x:v>
+        <x:v>-33490</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1622,25 +1622,25 @@
         <x:v>43984</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>83318</x:v>
+        <x:v>84558</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>127302</x:v>
+        <x:v>128542</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.825677398315178</x:v>
+        <x:v>0.820471982983673</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-39334</x:v>
+        <x:v>-40574</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1648,28 +1648,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>4898</x:v>
+        <x:v>178752</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>47811</x:v>
+        <x:v>222204</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>52709</x:v>
+        <x:v>400956</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.341869177136217</x:v>
+        <x:v>2.55926595516797</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-42913</x:v>
+        <x:v>-43452</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1677,28 +1677,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>178752</x:v>
+        <x:v>4898</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>222202</x:v>
+        <x:v>48458</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>400954</x:v>
+        <x:v>53356</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>2.60057701814633</x:v>
+        <x:v>0.340566531748976</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-43450</x:v>
+        <x:v>-43560</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1709,25 +1709,25 @@
         <x:v>214438</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>263287</x:v>
+        <x:v>263314</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>477725</x:v>
+        <x:v>477752</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>3.09851168960518</x:v>
+        <x:v>3.04944789107386</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-48849</x:v>
+        <x:v>-48876</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1738,25 +1738,25 @@
         <x:v>48554</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>119230</x:v>
+        <x:v>120907</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>167784</x:v>
+        <x:v>169461</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.08824257748436</x:v>
+        <x:v>1.08165426637516</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-70676</x:v>
+        <x:v>-72353</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1767,25 +1767,25 @@
         <x:v>29390</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>109825</x:v>
+        <x:v>110335</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>139215</x:v>
+        <x:v>139725</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.902944800603662</x:v>
+        <x:v>0.891852062535154</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-80435</x:v>
+        <x:v>-80945</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1799,22 +1799,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>135363</x:v>
+        <x:v>135439</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>135363</x:v>
+        <x:v>135439</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.877960830687164</x:v>
+        <x:v>0.864494911416702</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-135363</x:v>
+        <x:v>-135439</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1825,25 +1825,25 @@
         <x:v>77633</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>243925</x:v>
+        <x:v>250538</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>321558</x:v>
+        <x:v>328171</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>2.08561666625373</x:v>
+        <x:v>2.09468587020379</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-166292</x:v>
+        <x:v>-172905</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1851,28 +1851,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>46770</x:v>
+        <x:v>47846</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>233074</x:v>
+        <x:v>240368</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>279844</x:v>
+        <x:v>288214</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.81506076773431</x:v>
+        <x:v>1.83964394597607</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-186304</x:v>
+        <x:v>-192522</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1883,25 +1883,25 @@
         <x:v>199046</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>460852</x:v>
+        <x:v>476553</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>659898</x:v>
+        <x:v>675599</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>4.28008093976048</x:v>
+        <x:v>4.31228743314859</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-261806</x:v>
+        <x:v>-277507</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1912,25 +1912,25 @@
         <x:v>490980</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>769744</x:v>
+        <x:v>771189</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>1260724</x:v>
+        <x:v>1262169</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>8.17702245301334</x:v>
+        <x:v>8.05631079561948</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-278764</x:v>
+        <x:v>-280209</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1941,25 +1941,25 @@
         <x:v>105830</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>483587</x:v>
+        <x:v>490645</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>589417</x:v>
+        <x:v>596475</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.82294304160765</x:v>
+        <x:v>3.80724608338276</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-377757</x:v>
+        <x:v>-384815</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1970,25 +1970,25 @@
         <x:v>218108</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>641583</x:v>
+        <x:v>659371</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>859691</x:v>
+        <x:v>877479</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>5.57593304296062</x:v>
+        <x:v>5.60086925017917</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-423475</x:v>
+        <x:v>-441263</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1999,25 +1999,25 @@
         <x:v>153745</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>860371</x:v>
+        <x:v>889924</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>1014116</x:v>
+        <x:v>1043669</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>6.57752950047756</x:v>
+        <x:v>6.66164501881554</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-706626</x:v>
+        <x:v>-736179</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -52,6 +52,9 @@
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
@@ -73,9 +76,6 @@
     <x:t>ATA</x:t>
   </x:si>
   <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
@@ -124,12 +124,12 @@
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
@@ -175,10 +175,10 @@
     <x:t>AK</x:t>
   </x:si>
   <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
     <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
   <x:si>
     <x:t>YAPI KREDI</x:t>
@@ -578,25 +578,25 @@
         <x:v>1770074</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>919450</x:v>
+        <x:v>921986</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2689524</x:v>
+        <x:v>2692060</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>17.1669889185028</x:v>
+        <x:v>17.0005250342308</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>850624</x:v>
+        <x:v>848088</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -607,25 +607,25 @@
         <x:v>1093017</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>481977</x:v>
+        <x:v>493039</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1574994</x:v>
+        <x:v>1586056</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>10.0530445330506</x:v>
+        <x:v>10.0160415197625</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>611040</x:v>
+        <x:v>599978</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -636,25 +636,25 @@
         <x:v>1233927</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>727297</x:v>
+        <x:v>728122</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1961224</x:v>
+        <x:v>1962049</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>12.5183157594807</x:v>
+        <x:v>12.3904605182973</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>506630</x:v>
+        <x:v>505805</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -665,7 +665,7 @@
         <x:v>235509</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D5" s="0">
         <x:v>0</x:v>
@@ -677,13 +677,13 @@
         <x:v>235509</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.50323268846371</x:v>
+        <x:v>1.48725386889098</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>235509</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -691,28 +691,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>167102</x:v>
+        <x:v>197095</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>47529</x:v>
+        <x:v>38920</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>214631</x:v>
+        <x:v>236015</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.36997029904443</x:v>
+        <x:v>1.4904492901176</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>119573</x:v>
+        <x:v>158175</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -720,28 +720,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>110000</x:v>
+        <x:v>167102</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>2027</x:v>
+        <x:v>47529</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>112027</x:v>
+        <x:v>214631</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>0.715058228732336</x:v>
+        <x:v>1.3554080104537</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>107973</x:v>
+        <x:v>119573</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -749,28 +749,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>114793</x:v>
+        <x:v>110000</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>16126</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>130919</x:v>
+        <x:v>112027</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.835644159420575</x:v>
+        <x:v>0.707457418486131</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>98667</x:v>
+        <x:v>107973</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -778,28 +778,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>97672</x:v>
+        <x:v>114793</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>4967</x:v>
+        <x:v>16126</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>102639</x:v>
+        <x:v>130919</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.655135472152769</x:v>
+        <x:v>0.826761564362036</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>92705</x:v>
+        <x:v>98667</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -807,28 +807,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>115101</x:v>
+        <x:v>97672</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>25798</x:v>
+        <x:v>5021</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>140899</x:v>
+        <x:v>102693</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.899345598562467</x:v>
+        <x:v>0.648512632459998</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>89303</x:v>
+        <x:v>92651</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -836,28 +836,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>94365</x:v>
+        <x:v>115101</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>8872</x:v>
+        <x:v>25938</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>103237</x:v>
+        <x:v>141039</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.658952452173496</x:v>
+        <x:v>0.890669988894332</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>85493</x:v>
+        <x:v>89163</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -865,28 +865,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>97108</x:v>
+        <x:v>94365</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>22622</x:v>
+        <x:v>9012</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>119730</x:v>
+        <x:v>103377</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.764225782410692</x:v>
+        <x:v>0.65283213467147</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>74486</x:v>
+        <x:v>85353</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -894,28 +894,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>112934</x:v>
+        <x:v>97108</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>38920</x:v>
+        <x:v>22924</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>151854</x:v>
+        <x:v>120032</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.969270374694674</x:v>
+        <x:v>0.758009487496115</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>74014</x:v>
+        <x:v>74184</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -926,25 +926,25 @@
         <x:v>69901</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D14" s="0">
         <x:v>34669</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F14" s="0">
         <x:v>104570</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.66746087084846</x:v>
+        <x:v>0.660366003294694</x:v>
       </x:c>
       <x:c r="H14" s="0">
         <x:v>35232</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -955,25 +955,25 @@
         <x:v>35000</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D15" s="0">
         <x:v>3680</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F15" s="0">
         <x:v>38680</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.246890948497833</x:v>
+        <x:v>0.244266587046369</x:v>
       </x:c>
       <x:c r="H15" s="0">
         <x:v>31320</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -984,25 +984,25 @@
         <x:v>44116</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>14474</x:v>
+        <x:v>14680</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>58590</x:v>
+        <x:v>58796</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.373974681294934</x:v>
+        <x:v>0.371300368458591</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>29642</x:v>
+        <x:v>29436</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1013,25 +1013,25 @@
         <x:v>203412</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>176436</x:v>
+        <x:v>177110</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>379848</x:v>
+        <x:v>380522</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2.42453549650995</x:v>
+        <x:v>2.4030199130315</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>26976</x:v>
+        <x:v>26302</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1042,25 +1042,25 @@
         <x:v>25792</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>15965</x:v>
+        <x:v>16020</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>41757</x:v>
+        <x:v>41812</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.266531161748294</x:v>
+        <x:v>0.264045360330475</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>9827</x:v>
+        <x:v>9772</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1071,25 +1071,25 @@
         <x:v>128108</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>118326</x:v>
+        <x:v>118630</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>246434</x:v>
+        <x:v>246738</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>1.5729659773039</x:v>
+        <x:v>1.55816569686264</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>9782</x:v>
+        <x:v>9478</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1100,25 +1100,25 @@
         <x:v>8001</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>1329</x:v>
+        <x:v>1344</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>9330</x:v>
+        <x:v>9345</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0595525478150151</x:v>
+        <x:v>0.0590142517049719</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>6672</x:v>
+        <x:v>6657</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1129,25 +1129,25 @@
         <x:v>214379</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D21" s="0">
         <x:v>214304</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F21" s="0">
         <x:v>428683</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>2.73624489335307</x:v>
+        <x:v>2.70715960017576</x:v>
       </x:c>
       <x:c r="H21" s="0">
         <x:v>75</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1158,7 +1158,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>65</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D22" s="0">
         <x:v>0</x:v>
@@ -1170,13 +1170,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>6.3829097336565E-06</x:v>
+        <x:v>6.31506171267758E-06</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>65</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1193,19 +1193,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>65.815</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F23" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.000172338562808725</x:v>
+        <x:v>0.000170506666242295</x:v>
       </x:c>
       <x:c r="H23" s="0">
         <x:v>-27</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>65.815</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1222,19 +1222,19 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>65.798</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F24" s="0">
         <x:v>248</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.00158296161394681</x:v>
+        <x:v>0.00156613530474404</x:v>
       </x:c>
       <x:c r="H24" s="0">
         <x:v>-248</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>65.798</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1251,19 +1251,19 @@
         <x:v>357</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>65.801</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F25" s="0">
         <x:v>357</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.00227869877491537</x:v>
+        <x:v>0.00225447703142589</x:v>
       </x:c>
       <x:c r="H25" s="0">
         <x:v>-357</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>65.801</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1280,19 +1280,19 @@
         <x:v>1206</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F26" s="0">
         <x:v>1206</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00769778913878973</x:v>
+        <x:v>0.00761596442548916</x:v>
       </x:c>
       <x:c r="H26" s="0">
         <x:v>-1206</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1309,19 +1309,19 @@
         <x:v>3468</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F27" s="0">
         <x:v>3468</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0221359309563207</x:v>
+        <x:v>0.0219006340195658</x:v>
       </x:c>
       <x:c r="H27" s="0">
         <x:v>-3468</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1338,19 +1338,19 @@
         <x:v>3582</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F28" s="0">
         <x:v>3582</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0228635826659576</x:v>
+        <x:v>0.0226205510548111</x:v>
       </x:c>
       <x:c r="H28" s="0">
         <x:v>-3582</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1367,19 +1367,19 @@
         <x:v>4381</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F29" s="0">
         <x:v>4381</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0279635275431491</x:v>
+        <x:v>0.0276662853632405</x:v>
       </x:c>
       <x:c r="H29" s="0">
         <x:v>-4381</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1387,28 +1387,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>16941</x:v>
+        <x:v>8367</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>21725</x:v>
+        <x:v>13695</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>38666</x:v>
+        <x:v>22062</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.246801587761562</x:v>
+        <x:v>0.139322891505093</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-4784</x:v>
+        <x:v>-5328</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1416,28 +1416,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>8367</x:v>
+        <x:v>16941</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>13378</x:v>
+        <x:v>23493</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>21745</x:v>
+        <x:v>40434</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.138796372158361</x:v>
+        <x:v>0.255343205290405</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-5011</x:v>
+        <x:v>-6552</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1448,25 +1448,25 @@
         <x:v>1413</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>12207</x:v>
+        <x:v>12455</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>13620</x:v>
+        <x:v>13868</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0869352305724015</x:v>
+        <x:v>0.0875772758314126</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-10794</x:v>
+        <x:v>-11042</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1477,25 +1477,25 @@
         <x:v>3340</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>16887</x:v>
+        <x:v>17203</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>20227</x:v>
+        <x:v>20543</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.12910711518267</x:v>
+        <x:v>0.129730312763535</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-13547</x:v>
+        <x:v>-13863</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1506,25 +1506,25 @@
         <x:v>16364</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>33913</x:v>
+        <x:v>34129</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>50277</x:v>
+        <x:v>50493</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.320913552679048</x:v>
+        <x:v>0.318866411058229</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-17549</x:v>
+        <x:v>-17765</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1535,25 +1535,25 @@
         <x:v>2029</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D35" s="0">
         <x:v>20965</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F35" s="0">
         <x:v>22994</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.146768626415697</x:v>
+        <x:v>0.145208529021308</x:v>
       </x:c>
       <x:c r="H35" s="0">
         <x:v>-18936</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1564,25 +1564,25 @@
         <x:v>1448</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>29013</x:v>
+        <x:v>29555</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>30461</x:v>
+        <x:v>31003</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.194429813396911</x:v>
+        <x:v>0.195785858278143</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-27565</x:v>
+        <x:v>-28107</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1599,19 +1599,19 @@
         <x:v>33490</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F37" s="0">
         <x:v>33490</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.213763646980156</x:v>
+        <x:v>0.211491416757572</x:v>
       </x:c>
       <x:c r="H37" s="0">
         <x:v>-33490</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1622,25 +1622,25 @@
         <x:v>43984</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>84558</x:v>
+        <x:v>86187</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>128542</x:v>
+        <x:v>130171</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.820471982983673</x:v>
+        <x:v>0.822037898200953</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-40574</x:v>
+        <x:v>-42203</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1651,25 +1651,25 @@
         <x:v>178752</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D39" s="0">
         <x:v>222204</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F39" s="0">
         <x:v>400956</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>2.55926595516797</x:v>
+        <x:v>2.53206188406835</x:v>
       </x:c>
       <x:c r="H39" s="0">
         <x:v>-43452</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1680,25 +1680,25 @@
         <x:v>4898</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>48458</x:v>
+        <x:v>49099</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>53356</x:v>
+        <x:v>53997</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.340566531748976</x:v>
+        <x:v>0.340994387299451</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-43560</x:v>
+        <x:v>-44201</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1709,25 +1709,25 @@
         <x:v>214438</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>263314</x:v>
+        <x:v>263360</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>477752</x:v>
+        <x:v>477798</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>3.04944789107386</x:v>
+        <x:v>3.01732385619392</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-48876</x:v>
+        <x:v>-48922</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1738,25 +1738,25 @@
         <x:v>48554</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>120907</x:v>
+        <x:v>121998</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>169461</x:v>
+        <x:v>170552</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.08165426637516</x:v>
+        <x:v>1.07704640522059</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-72353</x:v>
+        <x:v>-73444</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1767,25 +1767,25 @@
         <x:v>29390</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>110335</x:v>
+        <x:v>110423</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>139725</x:v>
+        <x:v>139813</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.891852062535154</x:v>
+        <x:v>0.88292772323459</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-80945</x:v>
+        <x:v>-81033</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1802,19 +1802,19 @@
         <x:v>135439</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F44" s="0">
         <x:v>135439</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.864494911416702</x:v>
+        <x:v>0.855305643303338</x:v>
       </x:c>
       <x:c r="H44" s="0">
         <x:v>-135439</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1825,25 +1825,25 @@
         <x:v>77633</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>250538</x:v>
+        <x:v>255789</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>328171</x:v>
+        <x:v>333422</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>2.09468587020379</x:v>
+        <x:v>2.10558050636438</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-172905</x:v>
+        <x:v>-178156</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1854,25 +1854,25 @@
         <x:v>47846</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>240368</x:v>
+        <x:v>245678</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>288214</x:v>
+        <x:v>293524</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.83964394597607</x:v>
+        <x:v>1.85362217415197</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-192522</x:v>
+        <x:v>-197832</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1880,28 +1880,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>199046</x:v>
+        <x:v>490980</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>476553</x:v>
+        <x:v>772271</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>675599</x:v>
+        <x:v>1263251</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>4.31228743314859</x:v>
+        <x:v>7.97750802360166</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-277507</x:v>
+        <x:v>-281291</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1909,28 +1909,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>490980</x:v>
+        <x:v>199046</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>771189</x:v>
+        <x:v>486955</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>1262169</x:v>
+        <x:v>686001</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>8.05631079561948</x:v>
+        <x:v>4.33213864995853</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-280209</x:v>
+        <x:v>-287909</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1941,25 +1941,25 @@
         <x:v>105830</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>490645</x:v>
+        <x:v>495690</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>596475</x:v>
+        <x:v>601520</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.80724608338276</x:v>
+        <x:v>3.79863592140981</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-384815</x:v>
+        <x:v>-389860</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1970,25 +1970,25 @@
         <x:v>218108</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>659371</x:v>
+        <x:v>673105</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>877479</x:v>
+        <x:v>891213</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>5.60086925017917</x:v>
+        <x:v>5.62806509414052</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-441263</x:v>
+        <x:v>-454997</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1999,25 +1999,25 @@
         <x:v>153745</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>889924</x:v>
+        <x:v>910046</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>1043669</x:v>
+        <x:v>1063791</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>6.66164501881554</x:v>
+        <x:v>6.71790581439099</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-736179</x:v>
+        <x:v>-756301</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -49,12 +49,12 @@
     <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
@@ -124,6 +124,9 @@
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
@@ -134,9 +137,6 @@
   </x:si>
   <x:si>
     <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
     <x:t>GLOBAL</x:t>
@@ -578,25 +578,25 @@
         <x:v>1770074</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>921986</x:v>
+        <x:v>925315</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2692060</x:v>
+        <x:v>2695389</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>17.0005250342308</x:v>
+        <x:v>16.787339526542</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>848088</x:v>
+        <x:v>844759</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -604,28 +604,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1093017</x:v>
+        <x:v>1093189</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>493039</x:v>
+        <x:v>503269</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1586056</x:v>
+        <x:v>1596458</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>10.0160415197625</x:v>
+        <x:v>9.94301100355616</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>599978</x:v>
+        <x:v>589920</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -636,25 +636,25 @@
         <x:v>1233927</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>728122</x:v>
+        <x:v>728783</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1962049</x:v>
+        <x:v>1962710</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>12.3904605182973</x:v>
+        <x:v>12.2240905346647</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>505805</x:v>
+        <x:v>505144</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -662,28 +662,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>235509</x:v>
+        <x:v>295149</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>0</x:v>
+        <x:v>38945</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>235509</x:v>
+        <x:v>334094</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>1.48725386889098</x:v>
+        <x:v>2.0807940567319</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>235509</x:v>
+        <x:v>256204</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -691,28 +691,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>197095</x:v>
+        <x:v>235509</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>38920</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>236015</x:v>
+        <x:v>235509</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.4904492901176</x:v>
+        <x:v>1.46678996781407</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>158175</x:v>
+        <x:v>235509</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -723,25 +723,25 @@
         <x:v>167102</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D7" s="0">
         <x:v>47529</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>214631</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.3554080104537</x:v>
+        <x:v>1.3367582452556</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>119573</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -752,25 +752,25 @@
         <x:v>110000</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D8" s="0">
         <x:v>2027</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F8" s="0">
         <x:v>112027</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.707457418486131</x:v>
+        <x:v>0.697723143167804</x:v>
       </x:c>
       <x:c r="H8" s="0">
         <x:v>107973</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -781,25 +781,25 @@
         <x:v>114793</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>16126</x:v>
+        <x:v>16130</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>130919</x:v>
+        <x:v>130923</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.826761564362036</x:v>
+        <x:v>0.815410633802194</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>98667</x:v>
+        <x:v>98663</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -810,25 +810,25 @@
         <x:v>97672</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>5021</x:v>
+        <x:v>5073</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>102693</x:v>
+        <x:v>102745</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.648512632459998</x:v>
+        <x:v>0.639913273985522</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>92651</x:v>
+        <x:v>92599</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -839,25 +839,25 @@
         <x:v>115101</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>25938</x:v>
+        <x:v>26155</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>141039</x:v>
+        <x:v>141256</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.890669988894332</x:v>
+        <x:v>0.879766309115761</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>89163</x:v>
+        <x:v>88946</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -868,25 +868,25 @@
         <x:v>94365</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>9012</x:v>
+        <x:v>9060</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>103377</x:v>
+        <x:v>103425</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.65283213467147</x:v>
+        <x:v>0.644148429236971</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>85353</x:v>
+        <x:v>85305</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -897,25 +897,25 @@
         <x:v>97108</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>22924</x:v>
+        <x:v>23275</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>120032</x:v>
+        <x:v>120383</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.758009487496115</x:v>
+        <x:v>0.749765727404731</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>74184</x:v>
+        <x:v>73833</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -926,25 +926,25 @@
         <x:v>69901</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>34669</x:v>
+        <x:v>34751</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>104570</x:v>
+        <x:v>104652</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.660366003294694</x:v>
+        <x:v>0.651790393198042</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>35232</x:v>
+        <x:v>35150</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -955,25 +955,25 @@
         <x:v>35000</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D15" s="0">
         <x:v>3680</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F15" s="0">
         <x:v>38680</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.244266587046369</x:v>
+        <x:v>0.240905595773614</x:v>
       </x:c>
       <x:c r="H15" s="0">
         <x:v>31320</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -984,25 +984,25 @@
         <x:v>44116</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>14680</x:v>
+        <x:v>14931</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>58796</x:v>
+        <x:v>59047</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.371300368458591</x:v>
+        <x:v>0.367754723724007</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>29436</x:v>
+        <x:v>29185</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1013,25 +1013,25 @@
         <x:v>203412</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>177110</x:v>
+        <x:v>178071</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>380522</x:v>
+        <x:v>381483</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2.4030199130315</x:v>
+        <x:v>2.3759407805715</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>26302</x:v>
+        <x:v>25341</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1042,25 +1042,25 @@
         <x:v>25792</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>16020</x:v>
+        <x:v>16059</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>41812</x:v>
+        <x:v>41851</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.264045360330475</x:v>
+        <x:v>0.26065512121824</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>9772</x:v>
+        <x:v>9733</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1071,25 +1071,25 @@
         <x:v>128108</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>118630</x:v>
+        <x:v>118852</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>246738</x:v>
+        <x:v>246960</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>1.55816569686264</x:v>
+        <x:v>1.53810873661457</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>9478</x:v>
+        <x:v>9256</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1100,25 +1100,25 @@
         <x:v>8001</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D20" s="0">
         <x:v>1344</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F20" s="0">
         <x:v>9345</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0590142517049719</x:v>
+        <x:v>0.0582022438599903</x:v>
       </x:c>
       <x:c r="H20" s="0">
         <x:v>6657</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1129,25 +1129,25 @@
         <x:v>214379</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D21" s="0">
         <x:v>214304</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F21" s="0">
         <x:v>428683</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>2.70715960017576</x:v>
+        <x:v>2.66991038037798</x:v>
       </x:c>
       <x:c r="H21" s="0">
         <x:v>75</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1158,7 +1158,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D22" s="0">
         <x:v>0</x:v>
@@ -1170,13 +1170,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>6.31506171267758E-06</x:v>
+        <x:v>6.22816948742539E-06</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1193,19 +1193,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.815</x:v>
       </x:c>
       <x:c r="F23" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.000170506666242295</x:v>
+        <x:v>0.000168160576160485</x:v>
       </x:c>
       <x:c r="H23" s="0">
         <x:v>-27</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.815</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1222,19 +1222,19 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.798</x:v>
       </x:c>
       <x:c r="F24" s="0">
         <x:v>248</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.00156613530474404</x:v>
+        <x:v>0.0015445860328815</x:v>
       </x:c>
       <x:c r="H24" s="0">
         <x:v>-248</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.798</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1248,22 +1248,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>357</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.799</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>357</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.00225447703142589</x:v>
+        <x:v>0.00239161708317135</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-357</x:v>
+        <x:v>-384</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.799</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1277,22 +1277,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1206</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1206</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00761596442548916</x:v>
+        <x:v>0.00888759785855603</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-1206</x:v>
+        <x:v>-1427</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1306,22 +1306,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>3468</x:v>
+        <x:v>3496</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>3468</x:v>
+        <x:v>3496</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0219006340195658</x:v>
+        <x:v>0.0217736805280392</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-3468</x:v>
+        <x:v>-3496</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1335,22 +1335,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>3582</x:v>
+        <x:v>3610</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>3582</x:v>
+        <x:v>3610</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0226205510548111</x:v>
+        <x:v>0.0224836918496057</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-3582</x:v>
+        <x:v>-3610</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1364,22 +1364,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>4381</x:v>
+        <x:v>4408</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>4381</x:v>
+        <x:v>4408</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0276662853632405</x:v>
+        <x:v>0.0274537711005711</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-4381</x:v>
+        <x:v>-4408</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1387,28 +1387,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>8367</x:v>
+        <x:v>28600</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>13695</x:v>
+        <x:v>34157</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>22062</x:v>
+        <x:v>62757</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.139322891505093</x:v>
+        <x:v>0.390861232522355</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-5328</x:v>
+        <x:v>-5557</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1416,28 +1416,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>16941</x:v>
+        <x:v>8367</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>23493</x:v>
+        <x:v>14064</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>40434</x:v>
+        <x:v>22431</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.255343205290405</x:v>
+        <x:v>0.139704069772439</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-6552</x:v>
+        <x:v>-5697</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1445,28 +1445,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>1413</x:v>
+        <x:v>16941</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>12455</x:v>
+        <x:v>23762</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>13868</x:v>
+        <x:v>40703</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0875772758314126</x:v>
+        <x:v>0.253505182646676</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-11042</x:v>
+        <x:v>-6821</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1474,28 +1474,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>3340</x:v>
+        <x:v>1413</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>17203</x:v>
+        <x:v>12747</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>20543</x:v>
+        <x:v>14160</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.129730312763535</x:v>
+        <x:v>0.0881908799419435</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-13863</x:v>
+        <x:v>-11334</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1503,28 +1503,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>16364</x:v>
+        <x:v>3340</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>34129</x:v>
+        <x:v>17619</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>50493</x:v>
+        <x:v>20959</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.318866411058229</x:v>
+        <x:v>0.130536204286949</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-17765</x:v>
+        <x:v>-14279</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1535,25 +1535,25 @@
         <x:v>2029</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>20965</x:v>
+        <x:v>21020</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>22994</x:v>
+        <x:v>23049</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.145208529021308</x:v>
+        <x:v>0.143553078515668</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-18936</x:v>
+        <x:v>-18991</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1564,25 +1564,25 @@
         <x:v>1448</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>29555</x:v>
+        <x:v>29956</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>31003</x:v>
+        <x:v>31404</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.195785858278143</x:v>
+        <x:v>0.195589434583107</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-28107</x:v>
+        <x:v>-28508</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1599,19 +1599,19 @@
         <x:v>33490</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F37" s="0">
         <x:v>33490</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.211491416757572</x:v>
+        <x:v>0.208581396133876</x:v>
       </x:c>
       <x:c r="H37" s="0">
         <x:v>-33490</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1622,25 +1622,25 @@
         <x:v>43984</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>86187</x:v>
+        <x:v>86798</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>130171</x:v>
+        <x:v>130782</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.822037898200953</x:v>
+        <x:v>0.814532461904467</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-42203</x:v>
+        <x:v>-42814</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1651,25 +1651,25 @@
         <x:v>178752</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>222204</x:v>
+        <x:v>222259</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>400956</x:v>
+        <x:v>401011</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>2.53206188406835</x:v>
+        <x:v>2.49756447432194</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-43452</x:v>
+        <x:v>-43507</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1680,25 +1680,25 @@
         <x:v>4898</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>49099</x:v>
+        <x:v>49688</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>53997</x:v>
+        <x:v>54586</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.340994387299451</x:v>
+        <x:v>0.339970859640602</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-44201</x:v>
+        <x:v>-44790</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1709,25 +1709,25 @@
         <x:v>214438</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>263360</x:v>
+        <x:v>263498</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>477798</x:v>
+        <x:v>477936</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>3.01732385619392</x:v>
+        <x:v>2.97666641214214</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-48922</x:v>
+        <x:v>-49060</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1738,25 +1738,25 @@
         <x:v>48554</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>121998</x:v>
+        <x:v>124252</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>170552</x:v>
+        <x:v>172806</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.07704640522059</x:v>
+        <x:v>1.07626505644403</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-73444</x:v>
+        <x:v>-75698</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1767,25 +1767,25 @@
         <x:v>29390</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>110423</x:v>
+        <x:v>110497</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>139813</x:v>
+        <x:v>139887</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.88292772323459</x:v>
+        <x:v>0.871239945087475</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-81033</x:v>
+        <x:v>-81107</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1799,22 +1799,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>135439</x:v>
+        <x:v>135495</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>135439</x:v>
+        <x:v>135495</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.855305643303338</x:v>
+        <x:v>0.843885824698703</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-135439</x:v>
+        <x:v>-135495</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1825,25 +1825,25 @@
         <x:v>77633</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>255789</x:v>
+        <x:v>261054</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>333422</x:v>
+        <x:v>338687</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>2.10558050636438</x:v>
+        <x:v>2.10940003918764</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-178156</x:v>
+        <x:v>-183421</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1854,25 +1854,25 @@
         <x:v>47846</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>245678</x:v>
+        <x:v>279031</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>293524</x:v>
+        <x:v>326877</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.85362217415197</x:v>
+        <x:v>2.03584535754115</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-197832</x:v>
+        <x:v>-231185</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1883,25 +1883,25 @@
         <x:v>490980</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>772271</x:v>
+        <x:v>773227</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1263251</x:v>
+        <x:v>1264207</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>7.97750802360166</x:v>
+        <x:v>7.87369546318959</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-281291</x:v>
+        <x:v>-282247</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1912,25 +1912,25 @@
         <x:v>199046</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>486955</x:v>
+        <x:v>496773</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>686001</x:v>
+        <x:v>695819</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>4.33213864995853</x:v>
+        <x:v>4.33367866457085</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-287909</x:v>
+        <x:v>-297727</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1941,25 +1941,25 @@
         <x:v>105830</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>495690</x:v>
+        <x:v>500368</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>601520</x:v>
+        <x:v>606198</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.79863592140981</x:v>
+        <x:v>3.7755038869383</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-389860</x:v>
+        <x:v>-394538</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1970,25 +1970,25 @@
         <x:v>218108</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>673105</x:v>
+        <x:v>686172</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>891213</x:v>
+        <x:v>904280</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>5.62806509414052</x:v>
+        <x:v>5.63200910408903</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-454997</x:v>
+        <x:v>-468064</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1999,25 +1999,25 @@
         <x:v>153745</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>910046</x:v>
+        <x:v>930961</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>1063791</x:v>
+        <x:v>1084706</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>6.71790581439099</x:v>
+        <x:v>6.75573281202724</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-756301</x:v>
+        <x:v>-777216</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -79,6 +79,9 @@
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALTERNATIF</x:t>
   </x:si>
   <x:si>
@@ -94,12 +97,12 @@
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
     <x:t>ANADOLU</x:t>
   </x:si>
   <x:si>
@@ -122,9 +125,6 @@
   </x:si>
   <x:si>
     <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
     <x:t>BTCTURK</x:t>
@@ -581,19 +581,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>925315</x:v>
+        <x:v>927175</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2695389</x:v>
+        <x:v>2697249</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>16.787339526542</x:v>
+        <x:v>16.6818956602625</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>844759</x:v>
+        <x:v>842899</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>65.8</x:v>
@@ -604,25 +604,25 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1093189</x:v>
+        <x:v>1093249</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>503269</x:v>
+        <x:v>510197</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1596458</x:v>
+        <x:v>1603446</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>9.94301100355616</x:v>
+        <x:v>9.91696312385891</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>589920</x:v>
+        <x:v>583052</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>65.8</x:v>
@@ -639,19 +639,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>728783</x:v>
+        <x:v>729303</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1962710</x:v>
+        <x:v>1963230</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>12.2240905346647</x:v>
+        <x:v>12.1421485436077</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>505144</x:v>
+        <x:v>504624</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>65.8</x:v>
@@ -668,19 +668,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>38945</x:v>
+        <x:v>38972</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>334094</x:v>
+        <x:v>334121</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.0807940567319</x:v>
+        <x:v>2.06646537264545</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>256204</x:v>
+        <x:v>256177</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>65.8</x:v>
@@ -706,7 +706,7 @@
         <x:v>235509</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.46678996781407</x:v>
+        <x:v>1.45657170140865</x:v>
       </x:c>
       <x:c r="H6" s="0">
         <x:v>235509</x:v>
@@ -735,7 +735,7 @@
         <x:v>214631</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.3367582452556</x:v>
+        <x:v>1.3274458336838</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>119573</x:v>
@@ -764,7 +764,7 @@
         <x:v>112027</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.697723143167804</x:v>
+        <x:v>0.692862514781628</x:v>
       </x:c>
       <x:c r="H8" s="0">
         <x:v>107973</x:v>
@@ -793,7 +793,7 @@
         <x:v>130923</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.815410633802194</x:v>
+        <x:v>0.809730145614495</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>98663</x:v>
@@ -813,19 +813,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>5073</x:v>
+        <x:v>5154</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>102745</x:v>
+        <x:v>102826</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.639913273985522</x:v>
+        <x:v>0.635956340390581</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>92599</x:v>
+        <x:v>92518</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>65.8</x:v>
@@ -842,19 +842,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>26155</x:v>
+        <x:v>26262</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>141256</x:v>
+        <x:v>141363</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.879766309115761</x:v>
+        <x:v>0.874299264258395</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>88946</x:v>
+        <x:v>88839</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>65.8</x:v>
@@ -871,19 +871,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>9060</x:v>
+        <x:v>9114</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>103425</x:v>
+        <x:v>103479</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.644148429236971</x:v>
+        <x:v>0.639995002696565</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>85305</x:v>
+        <x:v>85251</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>65.8</x:v>
@@ -900,19 +900,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>23275</x:v>
+        <x:v>23410</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>120383</x:v>
+        <x:v>120518</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.749765727404731</x:v>
+        <x:v>0.745377494322371</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>73833</x:v>
+        <x:v>73698</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>65.8</x:v>
@@ -938,7 +938,7 @@
         <x:v>104652</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.651790393198042</x:v>
+        <x:v>0.647249751371785</x:v>
       </x:c>
       <x:c r="H14" s="0">
         <x:v>35150</x:v>
@@ -952,25 +952,25 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>35000</x:v>
+        <x:v>66364</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>3680</x:v>
+        <x:v>34265</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>38680</x:v>
+        <x:v>100629</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.240905595773614</x:v>
+        <x:v>0.622368375480558</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>31320</x:v>
+        <x:v>32099</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>65.8</x:v>
@@ -981,25 +981,25 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>44116</x:v>
+        <x:v>35000</x:v>
       </x:c>
       <x:c r="C16" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>14931</x:v>
+        <x:v>3707</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>59047</x:v>
+        <x:v>38707</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.367754723724007</x:v>
+        <x:v>0.239394336719295</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>29185</x:v>
+        <x:v>31293</x:v>
       </x:c>
       <x:c r="I16" s="0">
         <x:v>65.8</x:v>
@@ -1010,25 +1010,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>203412</x:v>
+        <x:v>44116</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>178071</x:v>
+        <x:v>15179</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>381483</x:v>
+        <x:v>59295</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2.3759407805715</x:v>
+        <x:v>0.366726617815139</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>25341</x:v>
+        <x:v>28937</x:v>
       </x:c>
       <x:c r="I17" s="0">
         <x:v>65.8</x:v>
@@ -1039,25 +1039,25 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>25792</x:v>
+        <x:v>203412</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>16059</x:v>
+        <x:v>178747</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>41851</x:v>
+        <x:v>382159</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.26065512121824</x:v>
+        <x:v>2.3635699053481</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>9733</x:v>
+        <x:v>24665</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>65.8</x:v>
@@ -1068,25 +1068,25 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>128108</x:v>
+        <x:v>25792</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>118852</x:v>
+        <x:v>16222</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>246960</x:v>
+        <x:v>42014</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>1.53810873661457</x:v>
+        <x:v>0.259847409071343</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>9256</x:v>
+        <x:v>9570</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>65.8</x:v>
@@ -1097,25 +1097,25 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>8001</x:v>
+        <x:v>128108</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>1344</x:v>
+        <x:v>119037</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>9345</x:v>
+        <x:v>247145</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.0582022438599903</x:v>
+        <x:v>1.52853781870179</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>6657</x:v>
+        <x:v>9071</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>65.8</x:v>
@@ -1126,25 +1126,25 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>214379</x:v>
+        <x:v>223066</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>214304</x:v>
+        <x:v>214386</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>428683</x:v>
+        <x:v>437452</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>2.66991038037798</x:v>
+        <x:v>2.70554502768308</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>75</x:v>
+        <x:v>8680</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>65.8</x:v>
@@ -1155,28 +1155,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>1</x:v>
+        <x:v>8001</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>65</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>0</x:v>
+        <x:v>1344</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>1</x:v>
+        <x:v>9345</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>6.22816948742539E-06</x:v>
+        <x:v>0.0577967829240657</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>1</x:v>
+        <x:v>6657</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>65</x:v>
+        <x:v>65.8</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1184,28 +1184,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>0</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>65.815</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.000168160576160485</x:v>
+        <x:v>6.18478147930077E-06</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>-27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>65.815</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1219,22 +1219,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>248</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>65.798</x:v>
+        <x:v>65.815</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>248</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0015445860328815</x:v>
+        <x:v>0.000166989099941121</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-248</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>65.798</x:v>
+        <x:v>65.815</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1248,22 +1248,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>384</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>65.799</x:v>
+        <x:v>65.798</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>384</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.00239161708317135</x:v>
+        <x:v>0.00153382580686659</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-384</x:v>
+        <x:v>-248</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>65.799</x:v>
+        <x:v>65.798</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1277,22 +1277,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1427</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.799</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1427</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00888759785855603</x:v>
+        <x:v>0.0023749560880515</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-1427</x:v>
+        <x:v>-384</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.799</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1306,19 +1306,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>3496</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>3496</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0217736805280392</x:v>
+        <x:v>0.00899267227090332</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-3496</x:v>
+        <x:v>-1454</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>65.8</x:v>
@@ -1335,19 +1335,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>3610</x:v>
+        <x:v>3496</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>3610</x:v>
+        <x:v>3496</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0224836918496057</x:v>
+        <x:v>0.0216219960516355</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-3610</x:v>
+        <x:v>-3496</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>65.8</x:v>
@@ -1364,19 +1364,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>4408</x:v>
+        <x:v>3610</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>4408</x:v>
+        <x:v>3610</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0274537711005711</x:v>
+        <x:v>0.0223270611402758</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-4408</x:v>
+        <x:v>-3610</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>65.8</x:v>
@@ -1387,25 +1387,25 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>28600</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>65.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>34157</x:v>
+        <x:v>4463</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>62757</x:v>
+        <x:v>4463</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.390861232522355</x:v>
+        <x:v>0.0276026797421194</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-5557</x:v>
+        <x:v>-4463</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>65.8</x:v>
@@ -1422,19 +1422,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>14064</x:v>
+        <x:v>14263</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>22431</x:v>
+        <x:v>22630</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.139704069772439</x:v>
+        <x:v>0.139961604876577</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-5697</x:v>
+        <x:v>-5896</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>65.8</x:v>
@@ -1451,19 +1451,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>23762</x:v>
+        <x:v>23816</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>40703</x:v>
+        <x:v>40757</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.253505182646676</x:v>
+        <x:v>0.252073138751862</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-6821</x:v>
+        <x:v>-6875</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>65.8</x:v>
@@ -1480,19 +1480,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>12747</x:v>
+        <x:v>12882</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>14160</x:v>
+        <x:v>14295</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0881908799419435</x:v>
+        <x:v>0.0884114512466046</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-11334</x:v>
+        <x:v>-11469</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>65.8</x:v>
@@ -1509,19 +1509,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>17619</x:v>
+        <x:v>18006</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>20959</x:v>
+        <x:v>21346</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.130536204286949</x:v>
+        <x:v>0.132020345457154</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-14279</x:v>
+        <x:v>-14666</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>65.8</x:v>
@@ -1547,7 +1547,7 @@
         <x:v>23049</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.143553078515668</x:v>
+        <x:v>0.142553028316404</x:v>
       </x:c>
       <x:c r="H35" s="0">
         <x:v>-18991</x:v>
@@ -1567,19 +1567,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>29956</x:v>
+        <x:v>30326</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>31404</x:v>
+        <x:v>31774</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.195589434583107</x:v>
+        <x:v>0.196515246723303</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-28508</x:v>
+        <x:v>-28878</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>65.8</x:v>
@@ -1605,7 +1605,7 @@
         <x:v>33490</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.208581396133876</x:v>
+        <x:v>0.207128331741783</x:v>
       </x:c>
       <x:c r="H37" s="0">
         <x:v>-33490</x:v>
@@ -1625,19 +1625,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>86798</x:v>
+        <x:v>87274</x:v>
       </x:c>
       <x:c r="E38" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>130782</x:v>
+        <x:v>131258</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.814532461904467</x:v>
+        <x:v>0.811802047410061</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-42814</x:v>
+        <x:v>-43290</x:v>
       </x:c>
       <x:c r="I38" s="0">
         <x:v>65.8</x:v>
@@ -1654,19 +1654,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>222259</x:v>
+        <x:v>222287</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>401011</x:v>
+        <x:v>401039</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>2.49756447432194</x:v>
+        <x:v>2.4803385796773</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-43507</x:v>
+        <x:v>-43535</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>65.8</x:v>
@@ -1683,19 +1683,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>49688</x:v>
+        <x:v>49823</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>54586</x:v>
+        <x:v>54721</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.339970859640602</x:v>
+        <x:v>0.338437427328818</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-44790</x:v>
+        <x:v>-44925</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>65.8</x:v>
@@ -1712,19 +1712,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>263498</x:v>
+        <x:v>264452</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>477936</x:v>
+        <x:v>478890</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>2.97666641214214</x:v>
+        <x:v>2.96183000262235</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-49060</x:v>
+        <x:v>-50014</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>65.8</x:v>
@@ -1741,19 +1741,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>124252</x:v>
+        <x:v>126537</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>172806</x:v>
+        <x:v>175091</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.07626505644403</x:v>
+        <x:v>1.08289957399225</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-75698</x:v>
+        <x:v>-77983</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>65.8</x:v>
@@ -1770,19 +1770,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>110497</x:v>
+        <x:v>110580</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>139887</x:v>
+        <x:v>139970</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.871239945087475</x:v>
+        <x:v>0.865683863657729</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-81107</x:v>
+        <x:v>-81190</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>65.8</x:v>
@@ -1808,7 +1808,7 @@
         <x:v>135495</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.843885824698703</x:v>
+        <x:v>0.838006966537858</x:v>
       </x:c>
       <x:c r="H44" s="0">
         <x:v>-135495</x:v>
@@ -1822,25 +1822,25 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>77633</x:v>
+        <x:v>87438</x:v>
       </x:c>
       <x:c r="C45" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>261054</x:v>
+        <x:v>264139</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>338687</x:v>
+        <x:v>351577</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>2.10940003918764</x:v>
+        <x:v>2.17442691814813</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-183421</x:v>
+        <x:v>-176701</x:v>
       </x:c>
       <x:c r="I45" s="0">
         <x:v>65.8</x:v>
@@ -1857,19 +1857,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>279031</x:v>
+        <x:v>282047</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>326877</x:v>
+        <x:v>329893</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>2.03584535754115</x:v>
+        <x:v>2.04031611655097</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-231185</x:v>
+        <x:v>-234201</x:v>
       </x:c>
       <x:c r="I46" s="0">
         <x:v>65.8</x:v>
@@ -1886,19 +1886,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>773227</x:v>
+        <x:v>773931</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1264207</x:v>
+        <x:v>1264911</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>7.87369546318959</x:v>
+        <x:v>7.82319812576382</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-282247</x:v>
+        <x:v>-282951</x:v>
       </x:c>
       <x:c r="I47" s="0">
         <x:v>65.8</x:v>
@@ -1909,25 +1909,25 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>199046</x:v>
+        <x:v>199049</x:v>
       </x:c>
       <x:c r="C48" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>496773</x:v>
+        <x:v>502926</x:v>
       </x:c>
       <x:c r="E48" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>695819</x:v>
+        <x:v>701975</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>4.33367866457085</x:v>
+        <x:v>4.34156197893216</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-297727</x:v>
+        <x:v>-303877</x:v>
       </x:c>
       <x:c r="I48" s="0">
         <x:v>65.8</x:v>
@@ -1944,19 +1944,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>500368</x:v>
+        <x:v>503742</x:v>
       </x:c>
       <x:c r="E49" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>606198</x:v>
+        <x:v>609572</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.7755038869383</x:v>
+        <x:v>3.77006961590033</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-394538</x:v>
+        <x:v>-397912</x:v>
       </x:c>
       <x:c r="I49" s="0">
         <x:v>65.8</x:v>
@@ -1973,19 +1973,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>686172</x:v>
+        <x:v>695539</x:v>
       </x:c>
       <x:c r="E50" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>904280</x:v>
+        <x:v>913647</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>5.63200910408903</x:v>
+        <x:v>5.65070704421871</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-468064</x:v>
+        <x:v>-477431</x:v>
       </x:c>
       <x:c r="I50" s="0">
         <x:v>65.8</x:v>
@@ -2002,19 +2002,19 @@
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>930961</x:v>
+        <x:v>945192</x:v>
       </x:c>
       <x:c r="E51" s="0">
         <x:v>65.8</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>1084706</x:v>
+        <x:v>1098937</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>6.75573281202724</x:v>
+        <x:v>6.79668520451835</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-777216</x:v>
+        <x:v>-791447</x:v>
       </x:c>
       <x:c r="I51" s="0">
         <x:v>65.8</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -85,6 +85,9 @@
     <x:t>ALTERNATIF</x:t>
   </x:si>
   <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
@@ -97,9 +100,6 @@
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
@@ -142,6 +142,9 @@
     <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>ING</x:t>
   </x:si>
   <x:si>
@@ -149,9 +152,6 @@
   </x:si>
   <x:si>
     <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
     <x:t>TEB</x:t>
@@ -578,25 +578,25 @@
         <x:v>1770074</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>927175</x:v>
+        <x:v>928646</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2697249</x:v>
+        <x:v>2698720</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>16.6818956602625</x:v>
+        <x:v>16.5949608806536</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>842899</x:v>
+        <x:v>841428</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -607,25 +607,25 @@
         <x:v>1093249</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>510197</x:v>
+        <x:v>515891</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1603446</x:v>
+        <x:v>1609140</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>9.91696312385891</x:v>
+        <x:v>9.89491883244459</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>583052</x:v>
+        <x:v>577358</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -636,25 +636,25 @@
         <x:v>1233927</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>729303</x:v>
+        <x:v>729791</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1963230</x:v>
+        <x:v>1963718</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>12.1421485436077</x:v>
+        <x:v>12.0752888001109</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>504624</x:v>
+        <x:v>504136</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -665,25 +665,25 @@
         <x:v>295149</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D5" s="0">
         <x:v>38972</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F5" s="0">
         <x:v>334121</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.06646537264545</x:v>
+        <x:v>2.05457584499498</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>256177</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -694,7 +694,7 @@
         <x:v>235509</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D6" s="0">
         <x:v>0</x:v>
@@ -706,13 +706,13 @@
         <x:v>235509</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.45657170140865</x:v>
+        <x:v>1.44819123215518</x:v>
       </x:c>
       <x:c r="H6" s="0">
         <x:v>235509</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -723,25 +723,25 @@
         <x:v>167102</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D7" s="0">
         <x:v>47529</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>214631</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.3274458336838</x:v>
+        <x:v>1.31980829755423</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>119573</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -752,25 +752,25 @@
         <x:v>110000</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D8" s="0">
         <x:v>2027</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F8" s="0">
         <x:v>112027</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.692862514781628</x:v>
+        <x:v>0.688876090360236</x:v>
       </x:c>
       <x:c r="H8" s="0">
         <x:v>107973</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -781,25 +781,25 @@
         <x:v>114793</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D9" s="0">
         <x:v>16130</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F9" s="0">
         <x:v>130923</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.809730145614495</x:v>
+        <x:v>0.805071316541844</x:v>
       </x:c>
       <x:c r="H9" s="0">
         <x:v>98663</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -810,25 +810,25 @@
         <x:v>97672</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>5154</x:v>
+        <x:v>5206</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>102826</x:v>
+        <x:v>102878</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.635956340390581</x:v>
+        <x:v>0.632617087167204</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>92518</x:v>
+        <x:v>92466</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -839,25 +839,25 @@
         <x:v>115101</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>26262</x:v>
+        <x:v>26595</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>141363</x:v>
+        <x:v>141696</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.874299264258395</x:v>
+        <x:v>0.871316615634481</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>88839</x:v>
+        <x:v>88506</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -868,25 +868,25 @@
         <x:v>94365</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>9114</x:v>
+        <x:v>9142</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>103479</x:v>
+        <x:v>103507</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.639995002696565</x:v>
+        <x:v>0.636484932069206</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>85251</x:v>
+        <x:v>85223</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -897,25 +897,25 @@
         <x:v>97108</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>23410</x:v>
+        <x:v>23732</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>120518</x:v>
+        <x:v>120840</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.745377494322371</x:v>
+        <x:v>0.743068963367143</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>73698</x:v>
+        <x:v>73376</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -926,25 +926,25 @@
         <x:v>69901</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D14" s="0">
         <x:v>34751</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F14" s="0">
         <x:v>104652</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.647249751371785</x:v>
+        <x:v>0.643525762614186</x:v>
       </x:c>
       <x:c r="H14" s="0">
         <x:v>35150</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -955,25 +955,25 @@
         <x:v>66364</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>34265</x:v>
+        <x:v>34807</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>100629</x:v>
+        <x:v>101171</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.622368375480558</x:v>
+        <x:v>0.62212040791805</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>32099</x:v>
+        <x:v>31557</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -984,25 +984,25 @@
         <x:v>35000</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>3707</x:v>
+        <x:v>3734</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>38707</x:v>
+        <x:v>38734</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.239394336719295</x:v>
+        <x:v>0.238182995920746</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>31293</x:v>
+        <x:v>31266</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1010,28 +1010,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>44116</x:v>
+        <x:v>244376</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>15179</x:v>
+        <x:v>214386</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>59295</x:v>
+        <x:v>458762</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.366726617815139</x:v>
+        <x:v>2.82101790609266</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>28937</x:v>
+        <x:v>29990</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1039,28 +1039,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>203412</x:v>
+        <x:v>44116</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>178747</x:v>
+        <x:v>15314</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>382159</x:v>
+        <x:v>59430</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>2.3635699053481</x:v>
+        <x:v>0.365446776670881</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>24665</x:v>
+        <x:v>28802</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,28 +1068,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>25792</x:v>
+        <x:v>203412</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>16222</x:v>
+        <x:v>179144</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>42014</x:v>
+        <x:v>382556</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.259847409071343</x:v>
+        <x:v>2.3524122008431</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>9570</x:v>
+        <x:v>24268</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1097,28 +1097,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>128108</x:v>
+        <x:v>25792</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>119037</x:v>
+        <x:v>16269</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>247145</x:v>
+        <x:v>42061</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>1.52853781870179</x:v>
+        <x:v>0.258641374281574</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>9071</x:v>
+        <x:v>9523</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1126,28 +1126,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>223066</x:v>
+        <x:v>128108</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>214386</x:v>
+        <x:v>120211</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>437452</x:v>
+        <x:v>248319</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>2.70554502768308</x:v>
+        <x:v>1.5269624455012</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>8680</x:v>
+        <x:v>7897</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1158,25 +1158,25 @@
         <x:v>8001</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D22" s="0">
         <x:v>1344</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F22" s="0">
         <x:v>9345</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0577967829240657</x:v>
+        <x:v>0.057464245801605</x:v>
       </x:c>
       <x:c r="H22" s="0">
         <x:v>6657</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1187,7 +1187,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>65</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D23" s="0">
         <x:v>0</x:v>
@@ -1199,13 +1199,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>6.18478147930077E-06</x:v>
+        <x:v>6.14919698251525E-06</x:v>
       </x:c>
       <x:c r="H23" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>65</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1222,19 +1222,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>65.815</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F24" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.000166989099941121</x:v>
+        <x:v>0.000166028318527912</x:v>
       </x:c>
       <x:c r="H24" s="0">
         <x:v>-27</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>65.815</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1251,19 +1251,19 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>65.798</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F25" s="0">
         <x:v>248</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.00153382580686659</x:v>
+        <x:v>0.00152500085166378</x:v>
       </x:c>
       <x:c r="H25" s="0">
         <x:v>-248</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>65.798</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1280,19 +1280,19 @@
         <x:v>384</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>65.799</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F26" s="0">
         <x:v>384</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0023749560880515</x:v>
+        <x:v>0.00236129164128586</x:v>
       </x:c>
       <x:c r="H26" s="0">
         <x:v>-384</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>65.799</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1309,19 +1309,19 @@
         <x:v>1454</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F27" s="0">
         <x:v>1454</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00899267227090332</x:v>
+        <x:v>0.00894093241257717</x:v>
       </x:c>
       <x:c r="H27" s="0">
         <x:v>-1454</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1338,19 +1338,19 @@
         <x:v>3496</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F28" s="0">
         <x:v>3496</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0216219960516355</x:v>
+        <x:v>0.0214975926508733</x:v>
       </x:c>
       <x:c r="H28" s="0">
         <x:v>-3496</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1367,19 +1367,19 @@
         <x:v>3610</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F29" s="0">
         <x:v>3610</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0223270611402758</x:v>
+        <x:v>0.0221986011068801</x:v>
       </x:c>
       <x:c r="H29" s="0">
         <x:v>-3610</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1393,22 +1393,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>4463</x:v>
+        <x:v>4490</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>4463</x:v>
+        <x:v>4490</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0276026797421194</x:v>
+        <x:v>0.0276098944514935</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-4463</x:v>
+        <x:v>-4490</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1419,25 +1419,25 @@
         <x:v>8367</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>14263</x:v>
+        <x:v>14414</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>22630</x:v>
+        <x:v>22781</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.139961604876577</x:v>
+        <x:v>0.14008485645868</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-5896</x:v>
+        <x:v>-6047</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1448,25 +1448,25 @@
         <x:v>16941</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>23816</x:v>
+        <x:v>23871</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>40757</x:v>
+        <x:v>40812</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.252073138751862</x:v>
+        <x:v>0.250961027250412</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-6875</x:v>
+        <x:v>-6930</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1477,25 +1477,25 @@
         <x:v>1413</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>12882</x:v>
+        <x:v>12936</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>14295</x:v>
+        <x:v>14349</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0884114512466046</x:v>
+        <x:v>0.0882348275021113</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-11469</x:v>
+        <x:v>-11523</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1506,25 +1506,25 @@
         <x:v>3340</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>18006</x:v>
+        <x:v>18185</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>21346</x:v>
+        <x:v>21525</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.132020345457154</x:v>
+        <x:v>0.132361465048641</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-14666</x:v>
+        <x:v>-14845</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1535,25 +1535,25 @@
         <x:v>2029</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D35" s="0">
         <x:v>21020</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F35" s="0">
         <x:v>23049</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.142553028316404</x:v>
+        <x:v>0.141732841249994</x:v>
       </x:c>
       <x:c r="H35" s="0">
         <x:v>-18991</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1561,28 +1561,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>1448</x:v>
+        <x:v>194225</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>30326</x:v>
+        <x:v>222287</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>31774</x:v>
+        <x:v>416512</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.196515246723303</x:v>
+        <x:v>2.56121433358139</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-28878</x:v>
+        <x:v>-28062</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1590,28 +1590,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>0</x:v>
+        <x:v>1448</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>33490</x:v>
+        <x:v>30645</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>33490</x:v>
+        <x:v>32093</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.207128331741783</x:v>
+        <x:v>0.197346178759862</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-33490</x:v>
+        <x:v>-29197</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1619,28 +1619,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>43984</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>65.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>87274</x:v>
+        <x:v>33490</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>131258</x:v>
+        <x:v>33490</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.811802047410061</x:v>
+        <x:v>0.205936606944436</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-43290</x:v>
+        <x:v>-33490</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1648,28 +1648,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>178752</x:v>
+        <x:v>43984</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>222287</x:v>
+        <x:v>87541</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>401039</x:v>
+        <x:v>131525</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>2.4803385796773</x:v>
+        <x:v>0.808773133125318</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-43535</x:v>
+        <x:v>-43557</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1680,25 +1680,25 @@
         <x:v>4898</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>49823</x:v>
+        <x:v>50623</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>54721</x:v>
+        <x:v>55521</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.338437427328818</x:v>
+        <x:v>0.341409565666229</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-44925</x:v>
+        <x:v>-45725</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1709,25 +1709,25 @@
         <x:v>214438</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D41" s="0">
         <x:v>264452</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F41" s="0">
         <x:v>478890</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>2.96183000262235</x:v>
+        <x:v>2.94478894295673</x:v>
       </x:c>
       <x:c r="H41" s="0">
         <x:v>-50014</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1738,25 +1738,25 @@
         <x:v>48554</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>126537</x:v>
+        <x:v>127598</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>175091</x:v>
+        <x:v>176152</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.08289957399225</x:v>
+        <x:v>1.08319334686403</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-77983</x:v>
+        <x:v>-79044</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1767,25 +1767,25 @@
         <x:v>29390</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>110580</x:v>
+        <x:v>110665</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>139970</x:v>
+        <x:v>140055</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.865683863657729</x:v>
+        <x:v>0.861225783386173</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-81190</x:v>
+        <x:v>-81275</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1802,19 +1802,19 @@
         <x:v>135495</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F44" s="0">
         <x:v>135495</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.838006966537858</x:v>
+        <x:v>0.833185445145904</x:v>
       </x:c>
       <x:c r="H44" s="0">
         <x:v>-135495</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1825,25 +1825,25 @@
         <x:v>87438</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>264139</x:v>
+        <x:v>266641</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>351577</x:v>
+        <x:v>354079</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>2.17442691814813</x:v>
+        <x:v>2.17730151837202</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-176701</x:v>
+        <x:v>-179203</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1854,25 +1854,25 @@
         <x:v>47846</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>282047</x:v>
+        <x:v>284392</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>329893</x:v>
+        <x:v>332238</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>2.04031611655097</x:v>
+        <x:v>2.0429969070769</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-234201</x:v>
+        <x:v>-236546</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1880,28 +1880,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>490980</x:v>
+        <x:v>500980</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>773931</x:v>
+        <x:v>775395</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1264911</x:v>
+        <x:v>1276375</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>7.82319812576382</x:v>
+        <x:v>7.8486812985579</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-282951</x:v>
+        <x:v>-274415</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1912,25 +1912,25 @@
         <x:v>199049</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>502926</x:v>
+        <x:v>507348</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>701975</x:v>
+        <x:v>706397</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>4.34156197893216</x:v>
+        <x:v>4.34377430085782</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-303877</x:v>
+        <x:v>-308299</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1941,25 +1941,25 @@
         <x:v>105830</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>503742</x:v>
+        <x:v>506527</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>609572</x:v>
+        <x:v>612357</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.77006961590033</x:v>
+        <x:v>3.76550381662209</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-397912</x:v>
+        <x:v>-400697</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1970,25 +1970,25 @@
         <x:v>218108</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>695539</x:v>
+        <x:v>704132</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>913647</x:v>
+        <x:v>922240</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>5.65070704421871</x:v>
+        <x:v>5.67103542515486</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-477431</x:v>
+        <x:v>-486024</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1999,25 +1999,25 @@
         <x:v>153745</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>945192</x:v>
+        <x:v>956156</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>1098937</x:v>
+        <x:v>1109901</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>6.79668520451835</x:v>
+        <x:v>6.82499988009066</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-791447</x:v>
+        <x:v>-802411</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>65.8</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -91,18 +91,21 @@
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
     <x:t>ICBC TURKEY</x:t>
   </x:si>
   <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>ANADOLU</x:t>
   </x:si>
   <x:si>
@@ -136,13 +139,10 @@
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
     <x:t>ING</x:t>
@@ -575,25 +575,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1770074</x:v>
+        <x:v>1771538</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>928646</x:v>
+        <x:v>930674</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2698720</x:v>
+        <x:v>2702212</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>16.5949608806536</x:v>
+        <x:v>16.491803386743</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>841428</x:v>
+        <x:v>840864</x:v>
       </x:c>
       <x:c r="I2" s="0">
         <x:v>65.8000030517578</x:v>
@@ -610,19 +610,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>515891</x:v>
+        <x:v>522858</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1609140</x:v>
+        <x:v>1616107</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>9.89491883244459</x:v>
+        <x:v>9.86322275822142</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>577358</x:v>
+        <x:v>570391</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>65.8000030517578</x:v>
@@ -639,19 +639,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>729791</x:v>
+        <x:v>730717</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1963718</x:v>
+        <x:v>1964644</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>12.0752888001109</x:v>
+        <x:v>11.9903703236253</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>504136</x:v>
+        <x:v>503210</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>65.8000030517578</x:v>
@@ -677,7 +677,7 @@
         <x:v>334121</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.05457584499498</x:v>
+        <x:v>2.03916563148337</x:v>
       </x:c>
       <x:c r="H5" s="0">
         <x:v>256177</x:v>
@@ -706,7 +706,7 @@
         <x:v>235509</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.44819123215518</x:v>
+        <x:v>1.43732916729274</x:v>
       </x:c>
       <x:c r="H6" s="0">
         <x:v>235509</x:v>
@@ -735,7 +735,7 @@
         <x:v>214631</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.31980829755423</x:v>
+        <x:v>1.30990916060621</x:v>
       </x:c>
       <x:c r="H7" s="0">
         <x:v>119573</x:v>
@@ -764,7 +764,7 @@
         <x:v>112027</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.688876090360236</x:v>
+        <x:v>0.683709219708393</x:v>
       </x:c>
       <x:c r="H8" s="0">
         <x:v>107973</x:v>
@@ -784,19 +784,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>16130</x:v>
+        <x:v>16162</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>130923</x:v>
+        <x:v>130955</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.805071316541844</x:v>
+        <x:v>0.799228229506392</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>98663</x:v>
+        <x:v>98631</x:v>
       </x:c>
       <x:c r="I9" s="0">
         <x:v>65.8000030517578</x:v>
@@ -813,19 +813,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>5206</x:v>
+        <x:v>5233</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>102878</x:v>
+        <x:v>102905</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.632617087167204</x:v>
+        <x:v>0.628036966571381</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>92466</x:v>
+        <x:v>92439</x:v>
       </x:c>
       <x:c r="I10" s="0">
         <x:v>65.8000030517578</x:v>
@@ -842,19 +842,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>26595</x:v>
+        <x:v>26622</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>141696</x:v>
+        <x:v>141723</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.871316615634481</x:v>
+        <x:v>0.864946144632388</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>88506</x:v>
+        <x:v>88479</x:v>
       </x:c>
       <x:c r="I11" s="0">
         <x:v>65.8000030517578</x:v>
@@ -871,19 +871,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>9142</x:v>
+        <x:v>9243</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>103507</x:v>
+        <x:v>103608</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.636484932069206</x:v>
+        <x:v>0.63232742852658</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>85223</x:v>
+        <x:v>85122</x:v>
       </x:c>
       <x:c r="I12" s="0">
         <x:v>65.8000030517578</x:v>
@@ -900,19 +900,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>23732</x:v>
+        <x:v>23952</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>120840</x:v>
+        <x:v>121060</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.743068963367143</x:v>
+        <x:v>0.738838299141261</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>73376</x:v>
+        <x:v>73156</x:v>
       </x:c>
       <x:c r="I13" s="0">
         <x:v>65.8000030517578</x:v>
@@ -929,19 +929,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>34751</x:v>
+        <x:v>34778</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>104652</x:v>
+        <x:v>104679</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.643525762614186</x:v>
+        <x:v>0.63886382220228</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>35150</x:v>
+        <x:v>35123</x:v>
       </x:c>
       <x:c r="I14" s="0">
         <x:v>65.8000030517578</x:v>
@@ -958,19 +958,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>34807</x:v>
+        <x:v>34965</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>101171</x:v>
+        <x:v>101329</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.62212040791805</x:v>
+        <x:v>0.618418519855318</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>31557</x:v>
+        <x:v>31399</x:v>
       </x:c>
       <x:c r="I15" s="0">
         <x:v>65.8000030517578</x:v>
@@ -996,7 +996,7 @@
         <x:v>38734</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.238182995920746</x:v>
+        <x:v>0.236396519733501</x:v>
       </x:c>
       <x:c r="H16" s="0">
         <x:v>31266</x:v>
@@ -1025,7 +1025,7 @@
         <x:v>458762</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2.82101790609266</x:v>
+        <x:v>2.79985904337224</x:v>
       </x:c>
       <x:c r="H17" s="0">
         <x:v>29990</x:v>
@@ -1045,19 +1045,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>15314</x:v>
+        <x:v>15379</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>59430</x:v>
+        <x:v>59495</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.365446776670881</x:v>
+        <x:v>0.363102466606718</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>28802</x:v>
+        <x:v>28737</x:v>
       </x:c>
       <x:c r="I18" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1068,25 +1068,25 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>203412</x:v>
+        <x:v>147384</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>179144</x:v>
+        <x:v>120390</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>382556</x:v>
+        <x:v>267774</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>2.3524122008431</x:v>
+        <x:v>1.63424489273296</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>24268</x:v>
+        <x:v>26994</x:v>
       </x:c>
       <x:c r="I19" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1097,25 +1097,25 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>25792</x:v>
+        <x:v>203412</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>16269</x:v>
+        <x:v>180528</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>42061</x:v>
+        <x:v>383940</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.258641374281574</x:v>
+        <x:v>2.34321474122167</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>9523</x:v>
+        <x:v>22884</x:v>
       </x:c>
       <x:c r="I20" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1126,25 +1126,25 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>128108</x:v>
+        <x:v>25792</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>120211</x:v>
+        <x:v>16351</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>248319</x:v>
+        <x:v>42143</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>1.5269624455012</x:v>
+        <x:v>0.257201903524782</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>7897</x:v>
+        <x:v>9441</x:v>
       </x:c>
       <x:c r="I21" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1161,19 +1161,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>1344</x:v>
+        <x:v>1371</x:v>
       </x:c>
       <x:c r="E22" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>9345</x:v>
+        <x:v>9372</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.057464245801605</x:v>
+        <x:v>0.0571980219688741</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>6657</x:v>
+        <x:v>6630</x:v>
       </x:c>
       <x:c r="I22" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1184,25 +1184,25 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>1</x:v>
+        <x:v>228752</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>0</x:v>
+        <x:v>225287</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>1</x:v>
+        <x:v>454039</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>6.14919698251525E-06</x:v>
+        <x:v>2.77103421860068</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>1</x:v>
+        <x:v>3465</x:v>
       </x:c>
       <x:c r="I23" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1213,25 +1213,25 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>0</x:v>
+        <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.000166028318527912</x:v>
+        <x:v>6.10307532745135E-06</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>-27</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I24" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1248,19 +1248,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>248</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>248</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.00152500085166378</x:v>
+        <x:v>0.000164783033841186</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-248</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I25" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1277,19 +1277,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>384</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>384</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00236129164128586</x:v>
+        <x:v>0.00151356268120794</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-384</x:v>
+        <x:v>-248</x:v>
       </x:c>
       <x:c r="I26" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1306,19 +1306,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>1454</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1454</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00894093241257717</x:v>
+        <x:v>0.00234358092574132</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-1454</x:v>
+        <x:v>-384</x:v>
       </x:c>
       <x:c r="I27" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1335,19 +1335,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>3496</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>3496</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0214975926508733</x:v>
+        <x:v>0.00887387152611427</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-3496</x:v>
+        <x:v>-1454</x:v>
       </x:c>
       <x:c r="I28" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1364,19 +1364,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>3610</x:v>
+        <x:v>3496</x:v>
       </x:c>
       <x:c r="E29" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>3610</x:v>
+        <x:v>3496</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0221986011068801</x:v>
+        <x:v>0.0213363513447699</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-3610</x:v>
+        <x:v>-3496</x:v>
       </x:c>
       <x:c r="I29" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1393,19 +1393,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>4490</x:v>
+        <x:v>3623</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>4490</x:v>
+        <x:v>3623</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0276098944514935</x:v>
+        <x:v>0.0221114419113562</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-4490</x:v>
+        <x:v>-3623</x:v>
       </x:c>
       <x:c r="I30" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1416,25 +1416,25 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>8367</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>14414</x:v>
+        <x:v>4572</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>22781</x:v>
+        <x:v>4572</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.14008485645868</x:v>
+        <x:v>0.0279032603971076</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-6047</x:v>
+        <x:v>-4572</x:v>
       </x:c>
       <x:c r="I31" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1445,25 +1445,25 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>16941</x:v>
+        <x:v>8367</x:v>
       </x:c>
       <x:c r="C32" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>23871</x:v>
+        <x:v>14520</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>40812</x:v>
+        <x:v>22887</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.250961027250412</x:v>
+        <x:v>0.139681085019379</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-6930</x:v>
+        <x:v>-6153</x:v>
       </x:c>
       <x:c r="I32" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1474,25 +1474,25 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>1413</x:v>
+        <x:v>16941</x:v>
       </x:c>
       <x:c r="C33" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>12936</x:v>
+        <x:v>23978</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>14349</x:v>
+        <x:v>40919</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0882348275021113</x:v>
+        <x:v>0.249731739323982</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-11523</x:v>
+        <x:v>-7037</x:v>
       </x:c>
       <x:c r="I33" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1503,25 +1503,25 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>3340</x:v>
+        <x:v>1413</x:v>
       </x:c>
       <x:c r="C34" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>18185</x:v>
+        <x:v>12990</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>21525</x:v>
+        <x:v>14403</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.132361465048641</x:v>
+        <x:v>0.0879025939412818</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-14845</x:v>
+        <x:v>-11577</x:v>
       </x:c>
       <x:c r="I34" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1532,7 +1532,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>2029</x:v>
+        <x:v>8210</x:v>
       </x:c>
       <x:c r="C35" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1544,13 +1544,13 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>23049</x:v>
+        <x:v>29230</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.141732841249994</x:v>
+        <x:v>0.178392891821403</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-18991</x:v>
+        <x:v>-12810</x:v>
       </x:c>
       <x:c r="I35" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1561,25 +1561,25 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>194225</x:v>
+        <x:v>3340</x:v>
       </x:c>
       <x:c r="C36" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>222287</x:v>
+        <x:v>18356</x:v>
       </x:c>
       <x:c r="E36" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>416512</x:v>
+        <x:v>21696</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>2.56121433358139</x:v>
+        <x:v>0.132412322304385</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-28062</x:v>
+        <x:v>-15016</x:v>
       </x:c>
       <x:c r="I36" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1596,19 +1596,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>30645</x:v>
+        <x:v>30911</x:v>
       </x:c>
       <x:c r="E37" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>32093</x:v>
+        <x:v>32359</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.197346178759862</x:v>
+        <x:v>0.197489414520998</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-29197</x:v>
+        <x:v>-29463</x:v>
       </x:c>
       <x:c r="I37" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1634,7 +1634,7 @@
         <x:v>33490</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.205936606944436</x:v>
+        <x:v>0.204391992716346</x:v>
       </x:c>
       <x:c r="H38" s="0">
         <x:v>-33490</x:v>
@@ -1654,19 +1654,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>87541</x:v>
+        <x:v>88159</x:v>
       </x:c>
       <x:c r="E39" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>131525</x:v>
+        <x:v>132143</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.808773133125318</x:v>
+        <x:v>0.806478682995404</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-43557</x:v>
+        <x:v>-44175</x:v>
       </x:c>
       <x:c r="I39" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1683,19 +1683,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>50623</x:v>
+        <x:v>51092</x:v>
       </x:c>
       <x:c r="E40" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>55521</x:v>
+        <x:v>55990</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.341409565666229</x:v>
+        <x:v>0.341711187584001</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-45725</x:v>
+        <x:v>-46194</x:v>
       </x:c>
       <x:c r="I40" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1712,19 +1712,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>264452</x:v>
+        <x:v>264769</x:v>
       </x:c>
       <x:c r="E41" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>478890</x:v>
+        <x:v>479207</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>2.94478894295673</x:v>
+        <x:v>2.92463641844198</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-50014</x:v>
+        <x:v>-50331</x:v>
       </x:c>
       <x:c r="I41" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1741,19 +1741,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>127598</x:v>
+        <x:v>128784</x:v>
       </x:c>
       <x:c r="E42" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>176152</x:v>
+        <x:v>177338</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.08319334686403</x:v>
+        <x:v>1.08230717241957</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-79044</x:v>
+        <x:v>-80230</x:v>
       </x:c>
       <x:c r="I42" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1770,19 +1770,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>110665</x:v>
+        <x:v>110779</x:v>
       </x:c>
       <x:c r="E43" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>140055</x:v>
+        <x:v>140169</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.861225783386173</x:v>
+        <x:v>0.855461965573528</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-81275</x:v>
+        <x:v>-81389</x:v>
       </x:c>
       <x:c r="I43" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1799,19 +1799,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>135495</x:v>
+        <x:v>135532</x:v>
       </x:c>
       <x:c r="E44" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>135495</x:v>
+        <x:v>135532</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.833185445145904</x:v>
+        <x:v>0.827162005280136</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-135495</x:v>
+        <x:v>-135532</x:v>
       </x:c>
       <x:c r="I44" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1828,19 +1828,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>266641</x:v>
+        <x:v>269563</x:v>
       </x:c>
       <x:c r="E45" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>354079</x:v>
+        <x:v>357001</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>2.17730151837202</x:v>
+        <x:v>2.17880399497546</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-179203</x:v>
+        <x:v>-182125</x:v>
       </x:c>
       <x:c r="I45" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1857,19 +1857,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>284392</x:v>
+        <x:v>287418</x:v>
       </x:c>
       <x:c r="E46" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>332238</x:v>
+        <x:v>335264</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>2.0429969070769</x:v>
+        <x:v>2.04614144658265</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-236546</x:v>
+        <x:v>-239572</x:v>
       </x:c>
       <x:c r="I46" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1886,19 +1886,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>775395</x:v>
+        <x:v>778361</x:v>
       </x:c>
       <x:c r="E47" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1276375</x:v>
+        <x:v>1279341</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>7.8486812985579</x:v>
+        <x:v>7.80791449249694</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-274415</x:v>
+        <x:v>-277381</x:v>
       </x:c>
       <x:c r="I47" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1915,19 +1915,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>507348</x:v>
+        <x:v>512638</x:v>
       </x:c>
       <x:c r="E48" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>706397</x:v>
+        <x:v>711687</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>4.34377430085782</x:v>
+        <x:v>4.34347937056787</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-308299</x:v>
+        <x:v>-313589</x:v>
       </x:c>
       <x:c r="I48" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1944,19 +1944,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>506527</x:v>
+        <x:v>511414</x:v>
       </x:c>
       <x:c r="E49" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>612357</x:v>
+        <x:v>617244</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.76550381662209</x:v>
+        <x:v>3.76708662741738</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-400697</x:v>
+        <x:v>-405584</x:v>
       </x:c>
       <x:c r="I49" s="0">
         <x:v>65.8000030517578</x:v>
@@ -1973,19 +1973,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>704132</x:v>
+        <x:v>712644</x:v>
       </x:c>
       <x:c r="E50" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>922240</x:v>
+        <x:v>930752</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>5.67103542515486</x:v>
+        <x:v>5.680449567176</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-486024</x:v>
+        <x:v>-494536</x:v>
       </x:c>
       <x:c r="I50" s="0">
         <x:v>65.8000030517578</x:v>
@@ -2002,19 +2002,19 @@
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>956156</x:v>
+        <x:v>971211</x:v>
       </x:c>
       <x:c r="E51" s="0">
         <x:v>65.8000030517578</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>1109901</x:v>
+        <x:v>1124956</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>6.82499988009066</x:v>
+        <x:v>6.86569120806836</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-802411</x:v>
+        <x:v>-817466</x:v>
       </x:c>
       <x:c r="I51" s="0">
         <x:v>65.8000030517578</x:v>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -40,154 +40,151 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -538,7 +535,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I51"/>
+  <x:dimension ref="A1:I50"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -575,28 +572,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1771538</x:v>
+        <x:v>302726</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.979625216533</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>930674</x:v>
+        <x:v>26610</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9669952378242</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2702212</x:v>
+        <x:v>329336</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>16.491803386743</x:v>
+        <x:v>5.76273630235503</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>840864</x:v>
+        <x:v>276116</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9808423996496</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -604,28 +601,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1093249</x:v>
+        <x:v>329276</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0480760213743</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>522858</x:v>
+        <x:v>70824</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9562559221527</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1616107</x:v>
+        <x:v>400100</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>9.86322275822142</x:v>
+        <x:v>7.00096799187531</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>570391</x:v>
+        <x:v>258452</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0732376247175</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -633,28 +630,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>1233927</x:v>
+        <x:v>264423</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9589295758408</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>730717</x:v>
+        <x:v>22448</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.8592887573895</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1964644</x:v>
+        <x:v>286871</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>11.9903703236253</x:v>
+        <x:v>5.01968180154277</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>503210</x:v>
+        <x:v>241975</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.968173246024</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -662,28 +659,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>295149</x:v>
+        <x:v>238255</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9699787035901</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>38972</x:v>
+        <x:v>63859</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9451218958396</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>334121</x:v>
+        <x:v>302114</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.03916563148337</x:v>
+        <x:v>5.28640450861639</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>256177</x:v>
+        <x:v>174396</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9790805802739</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -691,28 +688,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>235509</x:v>
+        <x:v>213553</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9228664120477</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>0</x:v>
+        <x:v>51604</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>0</x:v>
+        <x:v>67.9483065607012</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>235509</x:v>
+        <x:v>265157</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.43732916729274</x:v>
+        <x:v>4.63972924224364</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>235509</x:v>
+        <x:v>161949</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9147600734404</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -720,28 +717,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>167102</x:v>
+        <x:v>156434</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9421642184515</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>47529</x:v>
+        <x:v>11519</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9512384512201</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>214631</x:v>
+        <x:v>167953</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.30990916060621</x:v>
+        <x:v>2.93884923054095</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>119573</x:v>
+        <x:v>144915</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9414429260576</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -749,28 +746,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>110000</x:v>
+        <x:v>109145</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.8184780884348</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>2027</x:v>
+        <x:v>4576</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0526431790599</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>112027</x:v>
+        <x:v>113721</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>0.683709219708393</x:v>
+        <x:v>1.98989522870295</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>107973</x:v>
+        <x:v>104569</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.8082308884549</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -778,28 +775,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>114793</x:v>
+        <x:v>106490</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9351616058364</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>16162</x:v>
+        <x:v>16974</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9513703408392</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>130955</x:v>
+        <x:v>123464</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.799228229506392</x:v>
+        <x:v>2.16037868570081</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>98631</x:v>
+        <x:v>89516</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9320881098364</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -807,28 +804,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>97672</x:v>
+        <x:v>95482</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9851738163529</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>5233</x:v>
+        <x:v>19710</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9570344496233</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>102905</x:v>
+        <x:v>115192</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>0.628036966571381</x:v>
+        <x:v>2.01563485358685</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>92439</x:v>
+        <x:v>75772</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9924934980063</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -836,28 +833,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>115101</x:v>
+        <x:v>144279</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.947750366711</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>26622</x:v>
+        <x:v>71771</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9160323892368</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>141723</x:v>
+        <x:v>216050</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.864946144632388</x:v>
+        <x:v>3.78045272343079</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>88479</x:v>
+        <x:v>72508</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9791459501128</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -865,28 +862,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>94365</x:v>
+        <x:v>123251</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0174772854644</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>9243</x:v>
+        <x:v>52197</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9980959861304</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>103608</x:v>
+        <x:v>175448</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.63232742852658</x:v>
+        <x:v>3.06999708132602</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>85122</x:v>
+        <x:v>71054</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0317149875126</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -894,28 +891,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>97108</x:v>
+        <x:v>45309</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9169745404944</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>23952</x:v>
+        <x:v>1130</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.875928213744</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>121060</x:v>
+        <x:v>46439</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.738838299141261</x:v>
+        <x:v>0.812591733503368</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>73156</x:v>
+        <x:v>44179</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9180244137199</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -923,28 +920,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>69901</x:v>
+        <x:v>39182</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9881796652602</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>34778</x:v>
+        <x:v>913</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0194425885805</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>104679</x:v>
+        <x:v>40095</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.63886382220228</x:v>
+        <x:v>0.701584133052338</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>35123</x:v>
+        <x:v>38269</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9874338122462</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -952,28 +949,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>66364</x:v>
+        <x:v>47236</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.069689212256</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>34965</x:v>
+        <x:v>16924</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9469108991774</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>101329</x:v>
+        <x:v>64160</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.618418519855318</x:v>
+        <x:v>1.12267459724749</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>31399</x:v>
+        <x:v>30312</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.1382396269612</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -981,28 +978,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>35000</x:v>
+        <x:v>35083</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.1152668980587</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>3734</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0166642930773</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>38734</x:v>
+        <x:v>44083</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.236396519733501</x:v>
+        <x:v>0.771366338380003</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>31266</x:v>
+        <x:v>26083</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.1492899569413</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1010,28 +1007,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>244376</x:v>
+        <x:v>30966</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.051616850283</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>214386</x:v>
+        <x:v>9310</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9975989918448</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>458762</x:v>
+        <x:v>40276</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2.79985904337224</x:v>
+        <x:v>0.704751279282104</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>29990</x:v>
+        <x:v>21656</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0748393411428</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1039,28 +1036,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>44116</x:v>
+        <x:v>23216</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9833215799601</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>15379</x:v>
+        <x:v>3064</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.002169439749</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>59495</x:v>
+        <x:v>26280</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.363102466606718</x:v>
+        <x:v>0.459848634907481</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>28737</x:v>
+        <x:v>20152</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.980455867257</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,28 +1065,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>147384</x:v>
+        <x:v>28225</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0180286344624</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>120390</x:v>
+        <x:v>12771</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0788897764579</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>267774</x:v>
+        <x:v>40996</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>1.63424489273296</x:v>
+        <x:v>0.717349872019296</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>26994</x:v>
+        <x:v>15454</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9677337176497</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1097,28 +1094,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>203412</x:v>
+        <x:v>13961</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9491374109598</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>180528</x:v>
+        <x:v>1463</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9316449637944</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>383940</x:v>
+        <x:v>15424</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>2.34321474122167</x:v>
+        <x:v>0.269889853303386</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>22884</x:v>
+        <x:v>12498</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.951185054599</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1126,28 +1123,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>25792</x:v>
+        <x:v>12010</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>66.7383548263308</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>16351</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.1463621197325</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>42143</x:v>
+        <x:v>12340</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.257201903524782</x:v>
+        <x:v>0.215925881079083</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>9441</x:v>
+        <x:v>11680</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>66.726827223007</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1155,28 +1152,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>8001</x:v>
+        <x:v>7416</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.144591573244</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>1371</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0071618954341</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>9372</x:v>
+        <x:v>7800</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0571980219688741</x:v>
+        <x:v>0.136484754652905</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>6630</x:v>
+        <x:v>7032</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.1520962655476</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1184,28 +1181,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>228752</x:v>
+        <x:v>7487</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9689569902528</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>225287</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0031684058053</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>454039</x:v>
+        <x:v>8607</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>2.77103421860068</x:v>
+        <x:v>0.15060567734584</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>3465</x:v>
+        <x:v>6367</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9629389620734</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1213,28 +1210,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>1</x:v>
+        <x:v>52735</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.5224917110068</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>0</x:v>
+        <x:v>46669</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>0</x:v>
+        <x:v>67.7069616135674</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1</x:v>
+        <x:v>99404</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>6.10307532745135E-06</x:v>
+        <x:v>1.739375711733</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>1</x:v>
+        <x:v>6066</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>66.1032655516592</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1242,28 +1239,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>0</x:v>
+        <x:v>3907</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>0</x:v>
+        <x:v>66.7521499817348</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>27</x:v>
+        <x:v>903</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9104075637767</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>27</x:v>
+        <x:v>4810</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.000164783033841186</x:v>
+        <x:v>0.0841655987026249</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>-27</x:v>
+        <x:v>3004</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>66.4039786779452</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1271,28 +1268,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>0</x:v>
+        <x:v>5246</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>0</x:v>
+        <x:v>67.7768841364254</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>248</x:v>
+        <x:v>2854</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>66.9737760146849</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>248</x:v>
+        <x:v>8100</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00151356268120794</x:v>
+        <x:v>0.141734168293402</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>-248</x:v>
+        <x:v>2392</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.7351076228164</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1300,28 +1297,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>0</x:v>
+        <x:v>1762</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>0</x:v>
+        <x:v>67.7986355195928</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>384</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0081883134513</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>384</x:v>
+        <x:v>2110</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00234358092574132</x:v>
+        <x:v>0.0369208759381577</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>-384</x:v>
+        <x:v>1414</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.7470624133249</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1329,28 +1326,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>0</x:v>
+        <x:v>2501</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>0</x:v>
+        <x:v>67.8800298179068</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1454</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9499969482422</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1454</x:v>
+        <x:v>3822</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00887387152611427</x:v>
+        <x:v>0.0668775297799236</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>-1454</x:v>
+        <x:v>1180</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.8017022084382</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1358,28 +1355,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>0</x:v>
+        <x:v>2353</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>0</x:v>
+        <x:v>67.8031218107639</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>3496</x:v>
+        <x:v>1214</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9765637254794</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>3496</x:v>
+        <x:v>3567</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0213363513447699</x:v>
+        <x:v>0.0624155281855017</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>-3496</x:v>
+        <x:v>1139</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.6182592256327</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1387,28 +1384,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C30" s="0">
+        <x:v>68.3943761825562</x:v>
+      </x:c>
+      <x:c r="D30" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C30" s="0">
+      <x:c r="E30" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D30" s="0">
-        <x:v>3623</x:v>
-      </x:c>
-      <x:c r="E30" s="0">
-        <x:v>65.8000030517578</x:v>
-      </x:c>
       <x:c r="F30" s="0">
-        <x:v>3623</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0221114419113562</x:v>
+        <x:v>0.0013998436374657</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-3623</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.3943761825562</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1416,28 +1413,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>0</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>0</x:v>
+        <x:v>66.3499984741211</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>4572</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9499969482422</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>4572</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0279032603971076</x:v>
+        <x:v>0.000962392500757665</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-4572</x:v>
+        <x:v>-1</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>111.149955749512</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1445,28 +1442,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>8367</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>14520</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9499969482422</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>22887</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.139681085019379</x:v>
+        <x:v>0.000174980454683212</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-6153</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9499969482422</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1474,28 +1471,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>16941</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>23978</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>40919</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.249731739323982</x:v>
+        <x:v>0.000472447227644672</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-7037</x:v>
+        <x:v>-27</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1503,28 +1500,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>1413</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>12990</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0565769797877</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>14403</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0879025939412818</x:v>
+        <x:v>0.000664925727796205</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-11577</x:v>
+        <x:v>-38</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0565769797877</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1532,28 +1529,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>8210</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>21020</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.1000022888184</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>29230</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.178392891821403</x:v>
+        <x:v>0.000979890546225987</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-12810</x:v>
+        <x:v>-56</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.1000022888184</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1561,28 +1558,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>3340</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0500030517578</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>18356</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.1375646245294</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>21696</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.132412322304385</x:v>
+        <x:v>0.00384957000303066</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-15016</x:v>
+        <x:v>-166</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.1518065670887</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1590,28 +1587,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>1448</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9234036384745</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>30911</x:v>
+        <x:v>890</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0068541194616</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>32359</x:v>
+        <x:v>984</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.197489414520998</x:v>
+        <x:v>0.017218076740828</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-29463</x:v>
+        <x:v>-796</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0167088245028</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1619,28 +1616,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>0</x:v>
+        <x:v>3798</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>0</x:v>
+        <x:v>68.1072254934206</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>33490</x:v>
+        <x:v>4818</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.325851798305</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>33490</x:v>
+        <x:v>8616</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.204391992716346</x:v>
+        <x:v>0.150763159755055</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-33490</x:v>
+        <x:v>-1020</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>64.4163838629629</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1648,28 +1645,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>43984</x:v>
+        <x:v>5367</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.965445090433</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>88159</x:v>
+        <x:v>7721</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9698869339343</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>132143</x:v>
+        <x:v>13088</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.806478682995404</x:v>
+        <x:v>0.229014419089388</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-44175</x:v>
+        <x:v>-2354</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9800141106851</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1677,28 +1674,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>4898</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9499969482422</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>51092</x:v>
+        <x:v>9150</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9502975613954</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>55990</x:v>
+        <x:v>12350</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.341711187584001</x:v>
+        <x:v>0.216100861533767</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-46194</x:v>
+        <x:v>-5950</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9504592356962</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1706,28 +1703,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>214438</x:v>
+        <x:v>28250</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>66.8192971434467</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>264769</x:v>
+        <x:v>49144</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.932838065644</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>479207</x:v>
+        <x:v>77394</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>2.92463641844198</x:v>
+        <x:v>1.35424373097525</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-50331</x:v>
+        <x:v>-20894</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>69.438415315193</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1735,28 +1732,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>48554</x:v>
+        <x:v>14863</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9492400351022</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>128784</x:v>
+        <x:v>40426</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9476321558263</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>177338</x:v>
+        <x:v>55289</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.08230717241957</x:v>
+        <x:v>0.96744943589801</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-80230</x:v>
+        <x:v>-25563</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9466972925599</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1764,28 +1761,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>29390</x:v>
+        <x:v>8191</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.2978373441253</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>110779</x:v>
+        <x:v>51903</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9344979224034</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>140169</x:v>
+        <x:v>60094</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.855461965573528</x:v>
+        <x:v>1.05152754437329</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-81389</x:v>
+        <x:v>-43712</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0537989563684</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1793,28 +1790,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>0</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>0</x:v>
+        <x:v>67.9735021635135</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>135532</x:v>
+        <x:v>60763</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9500339783598</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>135532</x:v>
+        <x:v>61848</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.827162005280136</x:v>
+        <x:v>1.08221911612473</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-135532</x:v>
+        <x:v>-59678</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9496073055341</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1822,28 +1819,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>87438</x:v>
+        <x:v>16322</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.7895161638422</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>269563</x:v>
+        <x:v>95438</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0933799731661</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>357001</x:v>
+        <x:v>111760</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>2.17880399497546</x:v>
+        <x:v>1.95558156153958</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-182125</x:v>
+        <x:v>-79116</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.15606849503</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1851,28 +1848,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>47846</x:v>
+        <x:v>9468</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.969325211867</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>287418</x:v>
+        <x:v>93548</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9830569128098</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>335264</x:v>
+        <x:v>103016</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>2.04614144658265</x:v>
+        <x:v>1.80257865196458</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-239572</x:v>
+        <x:v>-84080</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9846031990196</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1880,28 +1877,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>500980</x:v>
+        <x:v>137978</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9265913928552</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>778361</x:v>
+        <x:v>259651</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9979858125761</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1279341</x:v>
+        <x:v>397629</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>7.80791449249694</x:v>
+        <x:v>6.95773032152308</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-277381</x:v>
+        <x:v>-121673</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>68.0789475645198</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1909,28 +1906,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>199049</x:v>
+        <x:v>11803</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9510772415494</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>512638</x:v>
+        <x:v>143576</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9500631237918</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>711687</x:v>
+        <x:v>155379</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>4.34347937056787</x:v>
+        <x:v>2.71882880682228</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-313589</x:v>
+        <x:v>-131773</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9499722885532</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1938,28 +1935,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>105830</x:v>
+        <x:v>124572</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9501244542809</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>511414</x:v>
+        <x:v>464213</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.8591529158595</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>617244</x:v>
+        <x:v>588785</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.76708662741738</x:v>
+        <x:v>10.3025867010655</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-405584</x:v>
+        <x:v>-339641</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.8257867837253</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1967,57 +1964,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>218108</x:v>
+        <x:v>50428</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9513524706721</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>712644</x:v>
+        <x:v>1054059</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9498547044642</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>930752</x:v>
+        <x:v>1104487</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>5.680449567176</x:v>
+        <x:v>19.3263637451697</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-494536</x:v>
+        <x:v>-1003631</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>65.8000030517578</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:9">
-      <x:c r="A51" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B51" s="0">
-        <x:v>153745</x:v>
-      </x:c>
-      <x:c r="C51" s="0">
-        <x:v>65.8000030517578</x:v>
-      </x:c>
-      <x:c r="D51" s="0">
-        <x:v>971211</x:v>
-      </x:c>
-      <x:c r="E51" s="0">
-        <x:v>65.8000030517578</x:v>
-      </x:c>
-      <x:c r="F51" s="0">
-        <x:v>1124956</x:v>
-      </x:c>
-      <x:c r="G51" s="0">
-        <x:v>6.86569120806836</x:v>
-      </x:c>
-      <x:c r="H51" s="0">
-        <x:v>-817466</x:v>
-      </x:c>
-      <x:c r="I51" s="0">
-        <x:v>65.8000030517578</x:v>
+        <x:v>67.9497794483648</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -40,151 +40,154 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
   </x:si>
   <x:si>
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
-    <x:t>FIBA</x:t>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
     <x:t>OYAK</x:t>
   </x:si>
   <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>IKON</x:t>
   </x:si>
   <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
+    <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
     <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
     <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -535,7 +538,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I50"/>
+  <x:dimension ref="A1:I51"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -572,28 +575,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>302726</x:v>
+        <x:v>1457541</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>67.979625216533</x:v>
+        <x:v>69.654065096494</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>26610</x:v>
+        <x:v>663480</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>67.9669952378242</x:v>
+        <x:v>69.7921696757943</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>329336</x:v>
+        <x:v>2121021</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>5.76273630235503</x:v>
+        <x:v>3.80028828153203</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>276116</x:v>
+        <x:v>794061</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>67.9808423996496</x:v>
+        <x:v>69.5386714097695</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -601,28 +604,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>329276</x:v>
+        <x:v>1101585</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>68.0480760213743</x:v>
+        <x:v>69.8132406303385</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>70824</x:v>
+        <x:v>392132</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>67.9562559221527</x:v>
+        <x:v>70.2902670013334</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>400100</x:v>
+        <x:v>1493717</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>7.00096799187531</x:v>
+        <x:v>2.67633145123277</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>258452</x:v>
+        <x:v>709453</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>68.0732376247175</x:v>
+        <x:v>69.549576504722</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -630,28 +633,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>264423</x:v>
+        <x:v>1904594</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>67.9589295758408</x:v>
+        <x:v>69.7961074155144</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>22448</x:v>
+        <x:v>1361880</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>67.8592887573895</x:v>
+        <x:v>70.5188142062781</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>286871</x:v>
+        <x:v>3266474</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>5.01968180154277</x:v>
+        <x:v>5.85262610041534</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>241975</x:v>
+        <x:v>542714</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>67.968173246024</x:v>
+        <x:v>67.9825556659645</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -659,28 +662,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>238255</x:v>
+        <x:v>426124</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>67.9699787035901</x:v>
+        <x:v>70.4527975303102</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>63859</x:v>
+        <x:v>26998</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>67.9451218958396</x:v>
+        <x:v>70.4042173013024</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>302114</x:v>
+        <x:v>453122</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>5.28640450861639</x:v>
+        <x:v>0.811870427829029</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>174396</x:v>
+        <x:v>399126</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>67.9790805802739</x:v>
+        <x:v>70.4560836330015</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -688,28 +691,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>213553</x:v>
+        <x:v>613066</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>67.9228664120477</x:v>
+        <x:v>69.2482329095297</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>51604</x:v>
+        <x:v>257863</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>67.9483065607012</x:v>
+        <x:v>69.9156354766588</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>265157</x:v>
+        <x:v>870929</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>4.63972924224364</x:v>
+        <x:v>1.56046605514345</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>161949</x:v>
+        <x:v>355203</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>67.9147600734404</x:v>
+        <x:v>68.7637256610898</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -717,28 +720,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>156434</x:v>
+        <x:v>756284</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>67.9421642184515</x:v>
+        <x:v>69.8237523107876</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>11519</x:v>
+        <x:v>425922</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>67.9512384512201</x:v>
+        <x:v>70.1649876167412</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>167953</x:v>
+        <x:v>1182206</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>2.93884923054095</x:v>
+        <x:v>2.11818912125663</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>144915</x:v>
+        <x:v>330362</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>67.9414429260576</x:v>
+        <x:v>69.3838118092095</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -746,28 +749,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>109145</x:v>
+        <x:v>3016370</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>67.8184780884348</x:v>
+        <x:v>69.8481532494654</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>4576</x:v>
+        <x:v>2696763</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>68.0526431790599</x:v>
+        <x:v>69.9938321981575</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>113721</x:v>
+        <x:v>5713133</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>1.98989522870295</x:v>
+        <x:v>10.2363684238553</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>104569</x:v>
+        <x:v>319607</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>67.8082308884549</x:v>
+        <x:v>68.6189511396495</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -775,28 +778,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>106490</x:v>
+        <x:v>717164</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>67.9351616058364</x:v>
+        <x:v>69.7720307438568</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>16974</x:v>
+        <x:v>406346</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>67.9513703408392</x:v>
+        <x:v>70.1307677416244</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>123464</x:v>
+        <x:v>1123510</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>2.16037868570081</x:v>
+        <x:v>2.01302197723834</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>89516</x:v>
+        <x:v>310818</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>67.9320881098364</x:v>
+        <x:v>69.3030381369458</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -804,28 +807,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>95482</x:v>
+        <x:v>518627</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>67.9851738163529</x:v>
+        <x:v>68.8324316907598</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>19710</x:v>
+        <x:v>209046</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>67.9570344496233</x:v>
+        <x:v>70.1614053211471</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>115192</x:v>
+        <x:v>727673</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>2.01563485358685</x:v>
+        <x:v>1.30379056816847</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>75772</x:v>
+        <x:v>309581</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>67.9924934980063</x:v>
+        <x:v>67.9350361091901</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -833,28 +836,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>144279</x:v>
+        <x:v>1250391</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>67.947750366711</x:v>
+        <x:v>69.5366867279682</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>71771</x:v>
+        <x:v>989921</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>67.9160323892368</x:v>
+        <x:v>69.901822627173</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>216050</x:v>
+        <x:v>2240312</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>3.78045272343079</x:v>
+        <x:v>4.01402505707184</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>72508</x:v>
+        <x:v>260470</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>67.9791459501128</x:v>
+        <x:v>68.1489810632974</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -862,28 +865,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>123251</x:v>
+        <x:v>1014465</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>68.0174772854644</x:v>
+        <x:v>69.3980442994697</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>52197</x:v>
+        <x:v>858158</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>67.9980959861304</x:v>
+        <x:v>69.6400093565151</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>175448</x:v>
+        <x:v>1872623</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>3.06999708132602</x:v>
+        <x:v>3.35522714891901</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>71054</x:v>
+        <x:v>156307</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>68.0317149875126</x:v>
+        <x:v>68.069605717551</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -891,28 +894,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>45309</x:v>
+        <x:v>108019</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>67.9169745404944</x:v>
+        <x:v>69.7129771399001</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>1130</x:v>
+        <x:v>38166</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>67.875928213744</x:v>
+        <x:v>70.3958884690322</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>46439</x:v>
+        <x:v>146185</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.812591733503368</x:v>
+        <x:v>0.261923452165613</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>44179</x:v>
+        <x:v>69853</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>67.9180244137199</x:v>
+        <x:v>69.3398508062042</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -920,28 +923,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>39182</x:v>
+        <x:v>61981</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>67.9881796652602</x:v>
+        <x:v>68.7693998113656</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>913</x:v>
+        <x:v>19389</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>68.0194425885805</x:v>
+        <x:v>70.492529052045</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>40095</x:v>
+        <x:v>81370</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.701584133052338</x:v>
+        <x:v>0.145792737303526</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>38269</x:v>
+        <x:v>42592</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>67.9874338122462</x:v>
+        <x:v>67.9849860048402</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -949,28 +952,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>47236</x:v>
+        <x:v>577518</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>68.069689212256</x:v>
+        <x:v>69.843098719696</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>16924</x:v>
+        <x:v>550900</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>67.9469108991774</x:v>
+        <x:v>69.7570398889286</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>64160</x:v>
+        <x:v>1128418</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>1.12267459724749</x:v>
+        <x:v>2.02181576800504</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>30312</x:v>
+        <x:v>26618</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>68.1382396269612</x:v>
+        <x:v>71.6242171309105</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -978,28 +981,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>35083</x:v>
+        <x:v>121334</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>68.1152668980587</x:v>
+        <x:v>69.1615004902225</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>9000</x:v>
+        <x:v>97996</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>68.0166642930773</x:v>
+        <x:v>69.8042502649084</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>44083</x:v>
+        <x:v>219330</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.771366338380003</x:v>
+        <x:v>0.392979243858698</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>26083</x:v>
+        <x:v>23338</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>68.1492899569413</x:v>
+        <x:v>66.4626014020349</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1007,28 +1010,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>30966</x:v>
+        <x:v>52202</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>68.051616850283</x:v>
+        <x:v>69.9121463885687</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>9310</x:v>
+        <x:v>29919</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>67.9975989918448</x:v>
+        <x:v>70.7110948327064</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>40276</x:v>
+        <x:v>82121</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.704751279282104</x:v>
+        <x:v>0.147138323461999</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>21656</x:v>
+        <x:v>22283</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>68.0748393411428</x:v>
+        <x:v>68.8394120843835</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1036,28 +1039,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>23216</x:v>
+        <x:v>53644</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>67.9833215799601</x:v>
+        <x:v>69.9249712638465</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>3064</x:v>
+        <x:v>31413</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>68.002169439749</x:v>
+        <x:v>70.3327573321403</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>26280</x:v>
+        <x:v>85057</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.459848634907481</x:v>
+        <x:v>0.152398830734005</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>20152</x:v>
+        <x:v>22231</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>67.980455867257</x:v>
+        <x:v>69.3487585985003</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1065,28 +1068,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>28225</x:v>
+        <x:v>130189</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>68.0180286344624</x:v>
+        <x:v>70.4829754110758</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>12771</x:v>
+        <x:v>108210</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>68.0788897764579</x:v>
+        <x:v>69.895032595839</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>40996</x:v>
+        <x:v>238399</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.717349872019296</x:v>
+        <x:v>0.427145665238088</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>15454</x:v>
+        <x:v>21979</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>67.9677337176497</x:v>
+        <x:v>73.3776153872697</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1094,28 +1097,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>13961</x:v>
+        <x:v>17268</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>67.9491374109598</x:v>
+        <x:v>67.6583640624562</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>1463</x:v>
+        <x:v>5442</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>67.9316449637944</x:v>
+        <x:v>69.7927430646028</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>15424</x:v>
+        <x:v>22710</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.269889853303386</x:v>
+        <x:v>0.040690095418005</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>12498</x:v>
+        <x:v>11826</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>67.951185054599</x:v>
+        <x:v>66.6761815383836</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1123,28 +1126,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>12010</x:v>
+        <x:v>39489</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>66.7383548263308</x:v>
+        <x:v>70.2888664157312</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>330</x:v>
+        <x:v>29654</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>67.1463621197325</x:v>
+        <x:v>70.0206928388246</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>12340</x:v>
+        <x:v>69143</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.215925881079083</x:v>
+        <x:v>0.12388530460093</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>11680</x:v>
+        <x:v>9835</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>66.726827223007</x:v>
+        <x:v>71.0974499693242</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1152,28 +1155,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>7416</x:v>
+        <x:v>491645</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>68.144591573244</x:v>
+        <x:v>69.9434115619239</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>384</x:v>
+        <x:v>484927</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>68.0071618954341</x:v>
+        <x:v>69.8242554570184</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>7800</x:v>
+        <x:v>976572</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.136484754652905</x:v>
+        <x:v>1.74974935546244</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>7032</x:v>
+        <x:v>6718</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>68.1520962655476</x:v>
+        <x:v>78.5444851676848</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1181,28 +1184,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>7487</x:v>
+        <x:v>707317</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>67.9689569902528</x:v>
+        <x:v>70.9187878983378</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>1120</x:v>
+        <x:v>700935</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>68.0031684058053</x:v>
+        <x:v>69.161767079567</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>8607</x:v>
+        <x:v>1408252</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.15060567734584</x:v>
+        <x:v>2.52320159632745</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>6367</x:v>
+        <x:v>6382</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>67.9629389620734</x:v>
+        <x:v>263.892367905414</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1210,28 +1213,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>52735</x:v>
+        <x:v>1019</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>67.5224917110068</x:v>
+        <x:v>70.0315970738105</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>46669</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>67.7069616135674</x:v>
+        <x:v>69.2499991522895</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>99404</x:v>
+        <x:v>1073</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>1.739375711733</x:v>
+        <x:v>0.00192252190152001</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>6066</x:v>
+        <x:v>965</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>66.1032655516592</x:v>
+        <x:v>70.0753341595744</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1239,28 +1242,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>3907</x:v>
+        <x:v>200961</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>66.7521499817348</x:v>
+        <x:v>70.3159634054483</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>903</x:v>
+        <x:v>200054</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>67.9104075637767</x:v>
+        <x:v>70.415660637076</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>4810</x:v>
+        <x:v>401015</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0841655987026249</x:v>
+        <x:v>0.718508965832289</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>3004</x:v>
+        <x:v>907</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>66.4039786779452</x:v>
+        <x:v>48.3260736854494</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1268,28 +1271,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>5246</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>67.7768841364254</x:v>
+        <x:v>70.5447799488198</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>2854</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>66.9737760146849</x:v>
+        <x:v>69.2154087203588</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>8100</x:v>
+        <x:v>4383</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.141734168293402</x:v>
+        <x:v>0.00785313466389766</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>2392</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>68.7351076228164</x:v>
+        <x:v>75.9118066475752</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1297,28 +1300,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>1762</x:v>
+        <x:v>5355</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>67.7986355195928</x:v>
+        <x:v>69.3815984688553</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>348</x:v>
+        <x:v>5262</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>68.0081883134513</x:v>
+        <x:v>70.6186218638694</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>2110</x:v>
+        <x:v>10617</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0369208759381577</x:v>
+        <x:v>0.0190227539873606</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>1414</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>67.7470624133249</x:v>
+        <x:v>-0.609983300649992</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1326,28 +1329,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>2501</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>67.8800298179068</x:v>
+        <x:v>68.3943761825562</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>1321</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>67.9499969482422</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>3822</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.0668775297799236</x:v>
+        <x:v>0.000143338072806711</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>1180</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>67.8017022084382</x:v>
+        <x:v>68.3943761825562</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1355,28 +1358,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>2353</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>67.8031218107639</x:v>
+        <x:v>70.362295807385</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1214</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>67.9765637254794</x:v>
+        <x:v>70.0162174121754</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>3567</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0624155281855017</x:v>
+        <x:v>0.000526767417564662</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>1139</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>67.6182592256327</x:v>
+        <x:v>70.8958333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1384,28 +1387,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>80</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>68.3943761825562</x:v>
+        <x:v>70.6986669921875</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>0</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>0</x:v>
+        <x:v>69.9680790874244</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>80</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.0013998436374657</x:v>
+        <x:v>0.000720273815853721</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>80</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>68.3943761825562</x:v>
+        <x:v>73.3927098910014</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1413,28 +1416,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>66.3499984741211</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>28</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>67.9499969482422</x:v>
+        <x:v>70.5297704798575</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>55</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.000962392500757665</x:v>
+        <x:v>0.000234716094220989</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-1</x:v>
+        <x:v>-131</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>111.149955749512</x:v>
+        <x:v>70.5297704798575</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1448,22 +1451,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>10</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>67.9499969482422</x:v>
+        <x:v>70.8027389735392</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>10</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.000174980454683212</x:v>
+        <x:v>0.000523183965744494</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-10</x:v>
+        <x:v>-292</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>67.9499969482422</x:v>
+        <x:v>70.8027389735392</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1471,28 +1474,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>0</x:v>
+        <x:v>155677</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>0</x:v>
+        <x:v>71.9432625576957</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>27</x:v>
+        <x:v>156326</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>68</x:v>
+        <x:v>71.9985866436089</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>27</x:v>
+        <x:v>312003</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.000472447227644672</x:v>
+        <x:v>0.559023859123902</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-27</x:v>
+        <x:v>-649</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>68</x:v>
+        <x:v>85.2692919174218</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1500,28 +1503,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>0</x:v>
+        <x:v>54281</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>0</x:v>
+        <x:v>70.1259166160726</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>38</x:v>
+        <x:v>55585</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>68.0565769797877</x:v>
+        <x:v>70.0291940941467</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>38</x:v>
+        <x:v>109866</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.000664925727796205</x:v>
+        <x:v>0.196849758837276</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-38</x:v>
+        <x:v>-1304</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>68.0565769797877</x:v>
+        <x:v>66.0029707715555</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1529,28 +1532,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>0</x:v>
+        <x:v>4823</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>0</x:v>
+        <x:v>67.5331846692368</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>56</x:v>
+        <x:v>12375</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>67.1000022888184</x:v>
+        <x:v>70.9552560918018</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>56</x:v>
+        <x:v>17198</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.000979890546225987</x:v>
+        <x:v>0.0308141022016226</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-56</x:v>
+        <x:v>-7552</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>67.1000022888184</x:v>
+        <x:v>73.140723580021</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1558,28 +1561,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>27</x:v>
+        <x:v>727646</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>68.0500030517578</x:v>
+        <x:v>71.0021834927648</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>193</x:v>
+        <x:v>739857</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>68.1375646245294</x:v>
+        <x:v>70.7872063147568</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>220</x:v>
+        <x:v>1467503</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.00384957000303066</x:v>
+        <x:v>2.62936314822583</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-166</x:v>
+        <x:v>-12211</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>68.1518065670887</x:v>
+        <x:v>57.9768481402576</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1587,28 +1590,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>94</x:v>
+        <x:v>62465</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>67.9234036384745</x:v>
+        <x:v>70.8401626009198</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>890</x:v>
+        <x:v>92079</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>68.0068541194616</x:v>
+        <x:v>69.2950393518004</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>984</x:v>
+        <x:v>154544</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.017218076740828</x:v>
+        <x:v>0.276900489048004</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-796</x:v>
+        <x:v>-29614</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>68.0167088245028</x:v>
+        <x:v>66.0359009795357</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1616,28 +1619,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>3798</x:v>
+        <x:v>244139</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>68.1072254934206</x:v>
+        <x:v>69.448183225795</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>4818</x:v>
+        <x:v>287081</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>67.325851798305</x:v>
+        <x:v>69.9484820227197</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>8616</x:v>
+        <x:v>531220</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.150763159755055</x:v>
+        <x:v>0.951800637954761</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-1020</x:v>
+        <x:v>-42942</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>64.4163838629629</x:v>
+        <x:v>72.7928406455688</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1645,28 +1648,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>5367</x:v>
+        <x:v>183401</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>67.965445090433</x:v>
+        <x:v>70.6989767045351</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>7721</x:v>
+        <x:v>229684</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>67.9698869339343</x:v>
+        <x:v>70.3457045747524</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>13088</x:v>
+        <x:v>413085</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.229014419089388</x:v>
+        <x:v>0.740135097567001</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-2354</x:v>
+        <x:v>-46283</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>67.9800141106851</x:v>
+        <x:v>68.9458285538747</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1674,28 +1677,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>3200</x:v>
+        <x:v>2179030</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>67.9499969482422</x:v>
+        <x:v>70.2384909338616</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>9150</x:v>
+        <x:v>2228343</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>67.9502975613954</x:v>
+        <x:v>70.3628369473121</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>12350</x:v>
+        <x:v>4407373</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.216100861533767</x:v>
+        <x:v>7.89680439950414</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-5950</x:v>
+        <x:v>-49313</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>67.9504592356962</x:v>
+        <x:v>75.8574062026614</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1703,28 +1706,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>28250</x:v>
+        <x:v>710300</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>66.8192971434467</x:v>
+        <x:v>72.1822011870994</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>49144</x:v>
+        <x:v>781001</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>67.932838065644</x:v>
+        <x:v>70.8634602851773</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>77394</x:v>
+        <x:v>1491301</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>1.35424373097525</x:v>
+        <x:v>2.67200264143401</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-20894</x:v>
+        <x:v>-70701</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>69.438415315193</x:v>
+        <x:v>57.6146849830563</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1732,28 +1735,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>14863</x:v>
+        <x:v>618951</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>67.9492400351022</x:v>
+        <x:v>69.7661355765618</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>40426</x:v>
+        <x:v>693628</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>67.9476321558263</x:v>
+        <x:v>70.0096402564825</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>55289</x:v>
+        <x:v>1312579</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.96744943589801</x:v>
+        <x:v>2.35178180333199</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-25563</x:v>
+        <x:v>-74677</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>67.9466972925599</x:v>
+        <x:v>72.0278984235434</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1761,28 +1764,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>8191</x:v>
+        <x:v>220653</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>67.2978373441253</x:v>
+        <x:v>71.9555391717737</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>51903</x:v>
+        <x:v>331765</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>67.9344979224034</x:v>
+        <x:v>71.1986736529008</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>60094</x:v>
+        <x:v>552418</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>1.05152754437329</x:v>
+        <x:v>0.989781643796719</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-43712</x:v>
+        <x:v>-111112</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>68.0537989563684</x:v>
+        <x:v>69.6956438511166</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1790,28 +1793,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>1085</x:v>
+        <x:v>1250733</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>67.9735021635135</x:v>
+        <x:v>70.6214104325408</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>60763</x:v>
+        <x:v>1370492</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>67.9500339783598</x:v>
+        <x:v>70.2663699744094</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>61848</x:v>
+        <x:v>2621225</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>1.08221911612473</x:v>
+        <x:v>4.69651674865963</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-59678</x:v>
+        <x:v>-119759</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>67.9496073055341</x:v>
+        <x:v>66.5584163565594</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1819,28 +1822,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>16322</x:v>
+        <x:v>308725</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>67.7895161638422</x:v>
+        <x:v>72.3074379552356</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>95438</x:v>
+        <x:v>444474</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>68.0933799731661</x:v>
+        <x:v>71.1867460249146</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>111760</x:v>
+        <x:v>753199</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.95558156153958</x:v>
+        <x:v>1.34952616374927</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-79116</x:v>
+        <x:v>-135749</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>68.15606849503</x:v>
+        <x:v>68.6380302613486</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1848,28 +1851,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>9468</x:v>
+        <x:v>289273</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>67.969325211867</x:v>
+        <x:v>70.1861155220823</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>93548</x:v>
+        <x:v>529324</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>67.9830569128098</x:v>
+        <x:v>69.2903797040462</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>103016</x:v>
+        <x:v>818597</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.80257865196458</x:v>
+        <x:v>1.46670145481694</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-84080</x:v>
+        <x:v>-240051</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>67.9846031990196</x:v>
+        <x:v>68.210974963842</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1877,28 +1880,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>137978</x:v>
+        <x:v>636618</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>67.9265913928552</x:v>
+        <x:v>70.8869460716653</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>259651</x:v>
+        <x:v>883906</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>67.9979858125761</x:v>
+        <x:v>70.4124572875731</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>397629</x:v>
+        <x:v>1520524</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>6.95773032152308</x:v>
+        <x:v>2.72436224770439</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-121673</x:v>
+        <x:v>-247288</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>68.0789475645198</x:v>
+        <x:v>69.1909337977506</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1906,28 +1909,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>11803</x:v>
+        <x:v>263415</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>67.9510772415494</x:v>
+        <x:v>70.4865655873306</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>143576</x:v>
+        <x:v>838601</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>67.9500631237918</x:v>
+        <x:v>71.4090337671154</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>155379</x:v>
+        <x:v>1102016</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>2.71882880682228</x:v>
+        <x:v>1.974510620527</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-131773</x:v>
+        <x:v>-575186</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>67.9499722885532</x:v>
+        <x:v>71.8314918164734</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1935,28 +1938,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>124572</x:v>
+        <x:v>1872124</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>67.9501244542809</x:v>
+        <x:v>71.7290215940048</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>464213</x:v>
+        <x:v>2468939</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>67.8591529158595</x:v>
+        <x:v>69.9608229247748</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>588785</x:v>
+        <x:v>4341063</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>10.3025867010655</x:v>
+        <x:v>7.77799505440647</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-339641</x:v>
+        <x:v>-596815</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>67.8257867837253</x:v>
+        <x:v>64.4142345088777</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1964,28 +1967,57 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>50428</x:v>
+        <x:v>109743</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>67.9513524706721</x:v>
+        <x:v>69.7938951097589</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>1054059</x:v>
+        <x:v>711639</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>67.9498547044642</x:v>
+        <x:v>71.977168276889</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>1104487</x:v>
+        <x:v>821382</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>19.3263637451697</x:v>
+        <x:v>1.47169141147652</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-1003631</x:v>
+        <x:v>-601896</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>67.9497794483648</x:v>
+        <x:v>72.3752419427389</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:9">
+      <x:c r="A51" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B51" s="0">
+        <x:v>2666984</x:v>
+      </x:c>
+      <x:c r="C51" s="0">
+        <x:v>70.395695446701</x:v>
+      </x:c>
+      <x:c r="D51" s="0">
+        <x:v>4457464</x:v>
+      </x:c>
+      <x:c r="E51" s="0">
+        <x:v>70.123198028522</x:v>
+      </x:c>
+      <x:c r="F51" s="0">
+        <x:v>7124448</x:v>
+      </x:c>
+      <x:c r="G51" s="0">
+        <x:v>12.7650580766453</x:v>
+      </x:c>
+      <x:c r="H51" s="0">
+        <x:v>-1790480</x:v>
+      </x:c>
+      <x:c r="I51" s="0">
+        <x:v>69.7173033777444</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -46,6 +46,9 @@
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
     <x:t>IS</x:t>
   </x:si>
   <x:si>
@@ -55,15 +58,12 @@
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
@@ -73,102 +73,102 @@
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEB</x:t>
   </x:si>
   <x:si>
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
+    <x:t>IKON</x:t>
   </x:si>
   <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
     <x:t>ATA</x:t>
   </x:si>
   <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
@@ -181,10 +181,10 @@
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
+    <x:t>TRIVE</x:t>
+  </x:si>
+  <x:si>
     <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRIVE</x:t>
   </x:si>
   <x:si>
     <x:t>A1 CAPITAL</x:t>
@@ -575,28 +575,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1457541</x:v>
+        <x:v>1860842</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>69.654065096494</x:v>
+        <x:v>69.7196177748038</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>663480</x:v>
+        <x:v>902605</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>69.7921696757943</x:v>
+        <x:v>69.7532551415603</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2121021</x:v>
+        <x:v>2763447</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>3.80028828153203</x:v>
+        <x:v>4.1134644915839</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>794061</x:v>
+        <x:v>958237</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>69.5386714097695</x:v>
+        <x:v>69.6879332798185</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -604,28 +604,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1101585</x:v>
+        <x:v>1440025</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>69.8132406303385</x:v>
+        <x:v>69.7881128957942</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>392132</x:v>
+        <x:v>615505</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>70.2902670013334</x:v>
+        <x:v>70.149723491346</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1493717</x:v>
+        <x:v>2055530</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>2.67633145123277</x:v>
+        <x:v>3.05971117462555</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>709453</x:v>
+        <x:v>824520</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>69.549576504722</x:v>
+        <x:v>69.5181702265866</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -633,28 +633,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>1904594</x:v>
+        <x:v>990596</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>69.7961074155144</x:v>
+        <x:v>69.753554167663</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>1361880</x:v>
+        <x:v>488617</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>70.5188142062781</x:v>
+        <x:v>70.0911641885453</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>3266474</x:v>
+        <x:v>1479213</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>5.85262610041534</x:v>
+        <x:v>2.20184796415104</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>542714</x:v>
+        <x:v>501979</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>67.9825556659645</x:v>
+        <x:v>69.424930867538</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -662,28 +662,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>426124</x:v>
+        <x:v>2215552</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>70.4527975303102</x:v>
+        <x:v>69.7986008589048</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>26998</x:v>
+        <x:v>1810823</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>70.4042173013024</x:v>
+        <x:v>70.3192258477085</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>453122</x:v>
+        <x:v>4026375</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>0.811870427829029</x:v>
+        <x:v>5.99336647031809</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>399126</x:v>
+        <x:v>404729</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>70.4560836330015</x:v>
+        <x:v>67.4692404619468</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -691,28 +691,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>613066</x:v>
+        <x:v>466433</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>69.2482329095297</x:v>
+        <x:v>70.3998677443747</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>257863</x:v>
+        <x:v>87976</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>69.9156354766588</x:v>
+        <x:v>69.4766062469149</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>870929</x:v>
+        <x:v>554409</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>1.56046605514345</x:v>
+        <x:v>0.825252568735546</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>355203</x:v>
+        <x:v>378457</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>68.7637256610898</x:v>
+        <x:v>70.6144888334298</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -720,28 +720,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>756284</x:v>
+        <x:v>720431</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>69.8237523107876</x:v>
+        <x:v>69.3371794635344</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>425922</x:v>
+        <x:v>345027</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>70.1649876167412</x:v>
+        <x:v>69.9477629690624</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1182206</x:v>
+        <x:v>1065458</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>2.11818912125663</x:v>
+        <x:v>1.58596262214329</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>330362</x:v>
+        <x:v>375404</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>69.3838118092095</x:v>
+        <x:v>68.7760032502767</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -749,28 +749,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>3016370</x:v>
+        <x:v>4236699</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>69.8481532494654</x:v>
+        <x:v>69.8434373707396</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>2696763</x:v>
+        <x:v>3871443</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>69.9938321981575</x:v>
+        <x:v>69.966117705256</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>5713133</x:v>
+        <x:v>8108142</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>10.2363684238553</x:v>
+        <x:v>12.0691854085568</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>319607</x:v>
+        <x:v>365256</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>68.6189511396495</x:v>
+        <x:v>68.5431167126214</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -778,28 +778,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>717164</x:v>
+        <x:v>873752</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>69.7720307438568</x:v>
+        <x:v>69.7744785370973</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>406346</x:v>
+        <x:v>539387</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>70.1307677416244</x:v>
+        <x:v>70.1126758519632</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>1123510</x:v>
+        <x:v>1413139</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>2.01302197723834</x:v>
+        <x:v>2.10349505460839</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>310818</x:v>
+        <x:v>334365</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>69.3030381369458</x:v>
+        <x:v>69.2289093684536</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -807,28 +807,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>518627</x:v>
+        <x:v>573350</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>68.8324316907598</x:v>
+        <x:v>68.8908086802648</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>209046</x:v>
+        <x:v>239293</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>70.1614053211471</x:v>
+        <x:v>70.1186866823223</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>727673</x:v>
+        <x:v>812643</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.30379056816847</x:v>
+        <x:v>1.20964075838408</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>309581</x:v>
+        <x:v>334057</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>67.9350361091901</x:v>
+        <x:v>68.0112503691193</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -836,28 +836,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1250391</x:v>
+        <x:v>1561462</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>69.5366867279682</x:v>
+        <x:v>69.5697090697005</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>989921</x:v>
+        <x:v>1247647</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>69.901822627173</x:v>
+        <x:v>69.9070451173588</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>2240312</x:v>
+        <x:v>2809109</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>4.01402505707184</x:v>
+        <x:v>4.18143359524853</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>260470</x:v>
+        <x:v>313815</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>68.1489810632974</x:v>
+        <x:v>68.2285484882982</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -865,28 +865,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>1014465</x:v>
+        <x:v>1206503</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>69.3980442994697</x:v>
+        <x:v>69.4540092717619</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>858158</x:v>
+        <x:v>1071626</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>69.6400093565151</x:v>
+        <x:v>69.6816228682429</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>1872623</x:v>
+        <x:v>2278129</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>3.35522714891901</x:v>
+        <x:v>3.39105571727901</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>156307</x:v>
+        <x:v>134877</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>68.069605717551</x:v>
+        <x:v>67.645571599345</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -894,28 +894,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>108019</x:v>
+        <x:v>896309</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>69.7129771399001</x:v>
+        <x:v>70.748449033559</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>38166</x:v>
+        <x:v>825041</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>70.3958884690322</x:v>
+        <x:v>70.6927151684472</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>146185</x:v>
+        <x:v>1721350</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.261923452165613</x:v>
+        <x:v>2.56227534039478</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>69853</x:v>
+        <x:v>71268</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>69.3398508062042</x:v>
+        <x:v>71.393657595687</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -923,28 +923,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>61981</x:v>
+        <x:v>130366</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>68.7693998113656</x:v>
+        <x:v>69.7471870462276</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>19389</x:v>
+        <x:v>72429</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>70.492529052045</x:v>
+        <x:v>70.1666338471769</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>81370</x:v>
+        <x:v>202795</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.145792737303526</x:v>
+        <x:v>0.301865760975607</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>42592</x:v>
+        <x:v>57937</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>67.9849860048402</x:v>
+        <x:v>69.2228224373256</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -952,28 +952,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>577518</x:v>
+        <x:v>68626</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>69.843098719696</x:v>
+        <x:v>68.8715183453833</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>550900</x:v>
+        <x:v>26915</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>69.7570398889286</x:v>
+        <x:v>70.3741518426336</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>1128418</x:v>
+        <x:v>95541</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>2.02181576800504</x:v>
+        <x:v>0.142215324191279</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>26618</x:v>
+        <x:v>41711</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>71.6242171309105</x:v>
+        <x:v>67.901908875975</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -981,28 +981,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>121334</x:v>
+        <x:v>76208</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>69.1615004902225</x:v>
+        <x:v>69.870663544973</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>97996</x:v>
+        <x:v>37442</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>69.8042502649084</x:v>
+        <x:v>70.4895626384156</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>219330</x:v>
+        <x:v>113650</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.392979243858698</x:v>
+        <x:v>0.169171053205837</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>23338</x:v>
+        <x:v>38766</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>66.4626014020349</x:v>
+        <x:v>69.2729021082326</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1010,28 +1010,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>52202</x:v>
+        <x:v>140777</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>69.9121463885687</x:v>
+        <x:v>69.2785826978901</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>29919</x:v>
+        <x:v>105152</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>70.7110948327064</x:v>
+        <x:v>69.8020262426526</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>82121</x:v>
+        <x:v>245929</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.147138323461999</x:v>
+        <x:v>0.366071869281639</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>22283</x:v>
+        <x:v>35625</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>68.8394120843835</x:v>
+        <x:v>67.733568364729</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1039,28 +1039,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>53644</x:v>
+        <x:v>66746</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>69.9249712638465</x:v>
+        <x:v>70.1231225880478</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>31413</x:v>
+        <x:v>33503</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>70.3327573321403</x:v>
+        <x:v>70.0341216047689</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>85057</x:v>
+        <x:v>100249</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.152398830734005</x:v>
+        <x:v>0.149223307636005</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>22231</x:v>
+        <x:v>33243</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>69.3487585985003</x:v>
+        <x:v>70.2128196654113</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,28 +1068,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>130189</x:v>
+        <x:v>89481</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>70.4829754110758</x:v>
+        <x:v>69.6561960766082</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>108210</x:v>
+        <x:v>57568</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>69.895032595839</x:v>
+        <x:v>70.0288963190644</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>238399</x:v>
+        <x:v>147049</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.427145665238088</x:v>
+        <x:v>0.218886354622658</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>21979</x:v>
+        <x:v>31913</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>73.3776153872697</x:v>
+        <x:v>68.9838804824079</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1097,28 +1097,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>17268</x:v>
+        <x:v>67477</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>67.6583640624562</x:v>
+        <x:v>69.8830061318555</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>5442</x:v>
+        <x:v>48537</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>69.7927430646028</x:v>
+        <x:v>70.0707337074336</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>22710</x:v>
+        <x:v>116014</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.040690095418005</x:v>
+        <x:v>0.17268993019465</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>11826</x:v>
+        <x:v>18940</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>66.6761815383836</x:v>
+        <x:v>69.4019220064157</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1126,28 +1126,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>39489</x:v>
+        <x:v>24291</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>70.2888664157312</x:v>
+        <x:v>68.1215046106883</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>29654</x:v>
+        <x:v>5617</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>70.0206928388246</x:v>
+        <x:v>69.8030368519016</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>69143</x:v>
+        <x:v>29908</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.12388530460093</x:v>
+        <x:v>0.0445188548990776</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>9835</x:v>
+        <x:v>18674</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>71.0974499693242</x:v>
+        <x:v>67.6157122470332</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1155,28 +1155,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>491645</x:v>
+        <x:v>572311</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>69.9434115619239</x:v>
+        <x:v>69.897553987116</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>484927</x:v>
+        <x:v>555179</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>69.8242554570184</x:v>
+        <x:v>69.8188369633975</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>976572</x:v>
+        <x:v>1127490</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>1.74974935546244</x:v>
+        <x:v>1.67829890698679</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>6718</x:v>
+        <x:v>17132</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>78.5444851676848</x:v>
+        <x:v>72.4484551376532</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1184,28 +1184,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>707317</x:v>
+        <x:v>801947</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>70.9187878983378</x:v>
+        <x:v>70.7778589795672</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>700935</x:v>
+        <x:v>792141</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>69.161767079567</x:v>
+        <x:v>69.2499961673547</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>1408252</x:v>
+        <x:v>1594088</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>2.52320159632745</x:v>
+        <x:v>2.37284246249702</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>6382</x:v>
+        <x:v>9806</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>263.892367905414</x:v>
+        <x:v>194.200536516669</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1213,28 +1213,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>1019</x:v>
+        <x:v>267199</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>70.0315970738105</x:v>
+        <x:v>70.1866744826025</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>54</x:v>
+        <x:v>260568</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>69.2499991522895</x:v>
+        <x:v>70.284248004411</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1073</x:v>
+        <x:v>527767</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.00192252190152001</x:v>
+        <x:v>0.785595241859084</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>965</x:v>
+        <x:v>6631</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>70.0753341595744</x:v>
+        <x:v>66.3524809325196</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1242,28 +1242,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>200961</x:v>
+        <x:v>167135</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>70.3159634054483</x:v>
+        <x:v>70.4459064166959</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>200054</x:v>
+        <x:v>162763</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>70.415660637076</x:v>
+        <x:v>69.8647082046326</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>401015</x:v>
+        <x:v>329898</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.718508965832289</x:v>
+        <x:v>0.491061963136816</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>907</x:v>
+        <x:v>4372</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>48.3260736854494</x:v>
+        <x:v>92.0830437886202</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1271,28 +1271,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>2433</x:v>
+        <x:v>160181</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>70.5447799488198</x:v>
+        <x:v>71.8946338498077</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>1950</x:v>
+        <x:v>157117</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>69.2154087203588</x:v>
+        <x:v>71.9865100908936</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>4383</x:v>
+        <x:v>317298</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00785313466389766</x:v>
+        <x:v>0.47230652740964</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>483</x:v>
+        <x:v>3064</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>75.9118066475752</x:v>
+        <x:v>67.183367736657</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1300,28 +1300,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>5355</x:v>
+        <x:v>1019</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>69.3815984688553</x:v>
+        <x:v>70.0315970738105</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>5262</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>70.6186218638694</x:v>
+        <x:v>69.1919356315367</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>10617</x:v>
+        <x:v>1112</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0190227539873606</x:v>
+        <x:v>0.00165524162925553</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>93</x:v>
+        <x:v>926</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>-0.609983300649992</x:v>
+        <x:v>70.1159259227646</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1329,28 +1329,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>80</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>68.3943761825562</x:v>
+        <x:v>70.5447799488198</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>0</x:v>
+        <x:v>2034</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>0</x:v>
+        <x:v>69.2581352038838</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>80</x:v>
+        <x:v>4467</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.000143338072806711</x:v>
+        <x:v>0.00664924852327737</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>80</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>68.3943761825562</x:v>
+        <x:v>77.1037659418015</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1358,28 +1358,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>183</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>70.362295807385</x:v>
+        <x:v>68.3943761825562</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>111</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>70.0162174121754</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>294</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.000526767417564662</x:v>
+        <x:v>0.000119082131601117</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>72</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>70.8958333333333</x:v>
+        <x:v>68.3943761825562</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1387,28 +1387,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>225</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>70.6986669921875</x:v>
+        <x:v>70.2267614015391</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>177</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>69.9680790874244</x:v>
+        <x:v>70.2402984846884</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>402</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.000720273815853721</x:v>
+        <x:v>0.00061625003103578</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>48</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>73.3927098910014</x:v>
+        <x:v>70.0000152587891</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1431,7 +1431,7 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.000234716094220989</x:v>
+        <x:v>0.000194996990496829</x:v>
       </x:c>
       <x:c r="H31" s="0">
         <x:v>-131</x:v>
@@ -1451,22 +1451,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>292</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>70.8027389735392</x:v>
+        <x:v>70.6924758002302</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>292</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.000523183965744494</x:v>
+        <x:v>0.000474839999759454</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-292</x:v>
+        <x:v>-319</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>70.8027389735392</x:v>
+        <x:v>70.6924758002302</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1474,28 +1474,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>155677</x:v>
+        <x:v>6098</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>71.9432625576957</x:v>
+        <x:v>69.34940296347</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>156326</x:v>
+        <x:v>6872</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>71.9985866436089</x:v>
+        <x:v>70.5090925074567</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>312003</x:v>
+        <x:v>12970</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.559023859123902</x:v>
+        <x:v>0.0193061905858311</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-649</x:v>
+        <x:v>-774</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>85.2692919174218</x:v>
+        <x:v>79.6457680103391</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1503,28 +1503,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>54281</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>70.1259166160726</x:v>
+        <x:v>70.6969029924511</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>55585</x:v>
+        <x:v>2177</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>70.0291940941467</x:v>
+        <x:v>69.5507357294646</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>109866</x:v>
+        <x:v>2403</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.196849758837276</x:v>
+        <x:v>0.00357692952796855</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-1304</x:v>
+        <x:v>-1951</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>66.0029707715555</x:v>
+        <x:v>69.4179659696312</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1532,28 +1532,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>4823</x:v>
+        <x:v>5458</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>67.5331846692368</x:v>
+        <x:v>67.7950714757129</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>12375</x:v>
+        <x:v>12945</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>70.9552560918018</x:v>
+        <x:v>70.8999454502711</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>17198</x:v>
+        <x:v>18403</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.0308141022016226</x:v>
+        <x:v>0.027393355848192</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-7552</x:v>
+        <x:v>-7487</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>73.140723580021</x:v>
+        <x:v>73.1633890395778</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1561,28 +1561,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>727646</x:v>
+        <x:v>80657</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>71.0021834927648</x:v>
+        <x:v>70.5769922431533</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>739857</x:v>
+        <x:v>95931</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>70.7872063147568</x:v>
+        <x:v>69.3186178315061</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>1467503</x:v>
+        <x:v>176588</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>2.62936314822583</x:v>
+        <x:v>0.262855943189726</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-12211</x:v>
+        <x:v>-15274</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>57.9768481402576</x:v>
+        <x:v>62.6735540027626</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1590,28 +1590,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>62465</x:v>
+        <x:v>289450</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>70.8401626009198</x:v>
+        <x:v>69.4980440472609</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>92079</x:v>
+        <x:v>322188</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>69.2950393518004</x:v>
+        <x:v>69.9430830578746</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>154544</x:v>
+        <x:v>611638</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.276900489048004</x:v>
+        <x:v>0.91043946010305</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-29614</x:v>
+        <x:v>-32738</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>66.0359009795357</x:v>
+        <x:v>73.8778543213029</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1619,28 +1619,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>244139</x:v>
+        <x:v>710791</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>69.448183225795</x:v>
+        <x:v>69.7979872627138</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>287081</x:v>
+        <x:v>747227</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>69.9484820227197</x:v>
+        <x:v>69.8275267941234</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>531220</x:v>
+        <x:v>1458018</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.951800637954761</x:v>
+        <x:v>2.17029864190997</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-42942</x:v>
+        <x:v>-36436</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>72.7928406455688</x:v>
+        <x:v>70.4037819557806</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1648,28 +1648,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>183401</x:v>
+        <x:v>2476112</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>70.6989767045351</x:v>
+        <x:v>70.2075668079548</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>229684</x:v>
+        <x:v>2519113</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>70.3457045747524</x:v>
+        <x:v>70.2773951997018</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>413085</x:v>
+        <x:v>4995225</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.740135097567001</x:v>
+        <x:v>7.43552551033987</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-46283</x:v>
+        <x:v>-43001</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>68.9458285538747</x:v>
+        <x:v>74.2982998006508</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1677,28 +1677,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>2179030</x:v>
+        <x:v>240985</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>70.2384909338616</x:v>
+        <x:v>70.5803811123701</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>2228343</x:v>
+        <x:v>294702</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>70.3628369473121</x:v>
+        <x:v>70.2196851573812</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>4407373</x:v>
+        <x:v>535687</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>7.89680439950414</x:v>
+        <x:v>0.797384372887595</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-49313</x:v>
+        <x:v>-53717</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>75.8574062026614</x:v>
+        <x:v>68.6015323433186</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1706,28 +1706,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>710300</x:v>
+        <x:v>713193</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>72.1822011870994</x:v>
+        <x:v>72.1724061382326</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>781001</x:v>
+        <x:v>781440</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>70.8634602851773</x:v>
+        <x:v>70.8628734725016</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>1491301</x:v>
+        <x:v>1494633</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>2.67200264143401</x:v>
+        <x:v>2.22480104501715</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-70701</x:v>
+        <x:v>-68247</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>57.6146849830563</x:v>
+        <x:v>57.1780297362097</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1735,28 +1735,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>618951</x:v>
+        <x:v>722954</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>69.7661355765618</x:v>
+        <x:v>69.7827436795358</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>693628</x:v>
+        <x:v>799319</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>70.0096402564825</x:v>
+        <x:v>69.9578610214656</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>1312579</x:v>
+        <x:v>1522273</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>2.35178180333199</x:v>
+        <x:v>2.26594392148534</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-74677</x:v>
+        <x:v>-76365</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>72.0278984235434</x:v>
+        <x:v>71.6157119062618</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1764,28 +1764,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>220653</x:v>
+        <x:v>1422555</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>71.9555391717737</x:v>
+        <x:v>70.5342949692547</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>331765</x:v>
+        <x:v>1505828</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>71.1986736529008</x:v>
+        <x:v>70.2518824038747</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>552418</x:v>
+        <x:v>2928383</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.989781643796719</x:v>
+        <x:v>4.35897612230592</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-111112</x:v>
+        <x:v>-83273</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>69.6956438511166</x:v>
+        <x:v>65.4274206102061</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1793,28 +1793,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>1250733</x:v>
+        <x:v>227835</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>70.6214104325408</x:v>
+        <x:v>71.8984165312286</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>1370492</x:v>
+        <x:v>334533</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>70.2663699744094</x:v>
+        <x:v>71.1876637332566</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>2621225</x:v>
+        <x:v>562368</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>4.69651674865963</x:v>
+        <x:v>0.837099752303212</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-119759</x:v>
+        <x:v>-106698</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>66.5584163565594</x:v>
+        <x:v>69.6699748944225</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1822,28 +1822,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>308725</x:v>
+        <x:v>308810</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>72.3074379552356</x:v>
+        <x:v>72.306662778804</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>444474</x:v>
+        <x:v>444529</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>71.1867460249146</x:v>
+        <x:v>71.1865738853436</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>753199</x:v>
+        <x:v>753339</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.34952616374927</x:v>
+        <x:v>1.12136517422817</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-135749</x:v>
+        <x:v>-135719</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>68.6380302613486</x:v>
+        <x:v>68.6379649861511</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1851,28 +1851,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>289273</x:v>
+        <x:v>350214</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>70.1861155220823</x:v>
+        <x:v>70.1292433667227</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>529324</x:v>
+        <x:v>627326</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>69.2903797040462</x:v>
+        <x:v>69.3911666004686</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>818597</x:v>
+        <x:v>977540</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.46670145481694</x:v>
+        <x:v>1.45509433656695</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-240051</x:v>
+        <x:v>-277112</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>68.210974963842</x:v>
+        <x:v>68.4583855710764</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1880,28 +1880,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>636618</x:v>
+        <x:v>751740</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>70.8869460716653</x:v>
+        <x:v>70.7085007943416</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>883906</x:v>
+        <x:v>1067858</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>70.4124572875731</x:v>
+        <x:v>70.2680586742379</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1520524</x:v>
+        <x:v>1819598</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>2.72436224770439</x:v>
+        <x:v>2.70852010621412</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-247288</x:v>
+        <x:v>-316118</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>69.1909337977506</x:v>
+        <x:v>69.2206714347679</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1909,28 +1909,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>263415</x:v>
+        <x:v>292087</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>70.4865655873306</x:v>
+        <x:v>70.4130903183936</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>838601</x:v>
+        <x:v>849313</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>71.4090337671154</x:v>
+        <x:v>71.3911521693127</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>1102016</x:v>
+        <x:v>1141400</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.974510620527</x:v>
+        <x:v>1.69900431261894</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-575186</x:v>
+        <x:v>-557226</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>71.8314918164734</x:v>
+        <x:v>71.9038331135785</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1938,28 +1938,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>1872124</x:v>
+        <x:v>169479</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>71.7290215940048</x:v>
+        <x:v>69.7195784384257</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>2468939</x:v>
+        <x:v>768838</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>69.9608229247748</x:v>
+        <x:v>71.797003667676</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>4341063</x:v>
+        <x:v>938317</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>7.77799505440647</x:v>
+        <x:v>1.39670985596957</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-596815</x:v>
+        <x:v>-599359</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>64.4142345088777</x:v>
+        <x:v>72.3844311534201</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1967,28 +1967,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>109743</x:v>
+        <x:v>2117581</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>69.7938951097589</x:v>
+        <x:v>71.4990885265831</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>711639</x:v>
+        <x:v>3045262</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>71.977168276889</x:v>
+        <x:v>69.8777556129841</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>821382</x:v>
+        <x:v>5162843</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>1.47169141147652</x:v>
+        <x:v>7.68502936952382</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-601896</x:v>
+        <x:v>-927681</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>72.3752419427389</x:v>
+        <x:v>66.1768026210484</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1996,28 +1996,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>2666984</x:v>
+        <x:v>3025593</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>70.395695446701</x:v>
+        <x:v>70.3299189683484</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>4457464</x:v>
+        <x:v>5002162</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>70.123198028522</x:v>
+        <x:v>70.0900186981897</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>7124448</x:v>
+        <x:v>8027755</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>12.7650580766453</x:v>
+        <x:v>11.9495272171441</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-1790480</x:v>
+        <x:v>-1976569</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>69.7173033777444</x:v>
+        <x:v>69.7227962141326</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -46,127 +46,127 @@
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>IS</x:t>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GEDIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
+    <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
-    <x:t>OYAK</x:t>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
   </x:si>
   <x:si>
     <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
   </x:si>
   <x:si>
     <x:t>COLENDI</x:t>
@@ -575,28 +575,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1860842</x:v>
+        <x:v>2480268</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>69.7196177748038</x:v>
+        <x:v>69.463</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>902605</x:v>
+        <x:v>1139497</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>69.7532551415603</x:v>
+        <x:v>69.524</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>2763447</x:v>
+        <x:v>3619765</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>4.1134644915839</x:v>
+        <x:v>4.43631587256809</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>958237</x:v>
+        <x:v>1340771</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>69.6879332798185</x:v>
+        <x:v>69.411</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -604,28 +604,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1440025</x:v>
+        <x:v>1911041</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>69.7881128957942</x:v>
+        <x:v>69.528</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>615505</x:v>
+        <x:v>934542</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>70.149723491346</x:v>
+        <x:v>69.7</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>2055530</x:v>
+        <x:v>2845583</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>3.05971117462555</x:v>
+        <x:v>3.48749298079017</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>824520</x:v>
+        <x:v>976499</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>69.5181702265866</x:v>
+        <x:v>69.364</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -633,28 +633,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>990596</x:v>
+        <x:v>2828122</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>69.753554167663</x:v>
+        <x:v>69.551</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>488617</x:v>
+        <x:v>2195032</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>70.0911641885453</x:v>
+        <x:v>70.03</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>1479213</x:v>
+        <x:v>5023154</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>2.20184796415104</x:v>
+        <x:v>6.15628302405098</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>501979</x:v>
+        <x:v>633090</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>69.424930867538</x:v>
+        <x:v>67.89</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -662,28 +662,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>2215552</x:v>
+        <x:v>1239708</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>69.7986008589048</x:v>
+        <x:v>69.55</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>1810823</x:v>
+        <x:v>672328</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>70.3192258477085</x:v>
+        <x:v>69.613</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>4026375</x:v>
+        <x:v>1912036</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>5.99336647031809</x:v>
+        <x:v>2.34335534370922</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>404729</x:v>
+        <x:v>567380</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>67.4692404619468</x:v>
+        <x:v>69.475</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -691,28 +691,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>466433</x:v>
+        <x:v>5714538</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>70.3998677443747</x:v>
+        <x:v>69.57</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>87976</x:v>
+        <x:v>5283292</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>69.4766062469149</x:v>
+        <x:v>69.643</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>554409</x:v>
+        <x:v>10997830</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>0.825252568735546</x:v>
+        <x:v>13.4787335069557</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>378457</x:v>
+        <x:v>431246</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>70.6144888334298</x:v>
+        <x:v>68.674</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -720,28 +720,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>720431</x:v>
+        <x:v>1972204</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>69.3371794635344</x:v>
+        <x:v>69.386</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>345027</x:v>
+        <x:v>1554686</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>69.9477629690624</x:v>
+        <x:v>69.674</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1065458</x:v>
+        <x:v>3526890</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>1.58596262214329</x:v>
+        <x:v>4.3224900201537</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>375404</x:v>
+        <x:v>417518</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>68.7760032502767</x:v>
+        <x:v>68.311</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -749,28 +749,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>4236699</x:v>
+        <x:v>1018985</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>69.8434373707396</x:v>
+        <x:v>69.603</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>3871443</x:v>
+        <x:v>647378</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>69.966117705256</x:v>
+        <x:v>69.853</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>8108142</x:v>
+        <x:v>1666363</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>12.0691854085568</x:v>
+        <x:v>2.04226313762362</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>365256</x:v>
+        <x:v>371607</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>68.5431167126214</x:v>
+        <x:v>69.168</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -778,28 +778,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>873752</x:v>
+        <x:v>785286</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>69.7744785370973</x:v>
+        <x:v>69.288</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>539387</x:v>
+        <x:v>415404</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>70.1126758519632</x:v>
+        <x:v>69.643</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>1413139</x:v>
+        <x:v>1200690</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>2.10349505460839</x:v>
+        <x:v>1.47154307117555</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>334365</x:v>
+        <x:v>369882</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>69.2289093684536</x:v>
+        <x:v>68.89</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -807,28 +807,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>573350</x:v>
+        <x:v>677341</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>68.8908086802648</x:v>
+        <x:v>68.869</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>239293</x:v>
+        <x:v>333218</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>70.1186866823223</x:v>
+        <x:v>69.716</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>812643</x:v>
+        <x:v>1010559</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.20964075838408</x:v>
+        <x:v>1.23852209518202</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>334057</x:v>
+        <x:v>344123</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>68.0112503691193</x:v>
+        <x:v>68.048</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -836,28 +836,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1561462</x:v>
+        <x:v>510785</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>69.5697090697005</x:v>
+        <x:v>70.263</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>1247647</x:v>
+        <x:v>176177</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>69.9070451173588</x:v>
+        <x:v>68.739</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>2809109</x:v>
+        <x:v>686962</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>4.18143359524853</x:v>
+        <x:v>0.841927700956034</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>313815</x:v>
+        <x:v>334608</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>68.2285484882982</x:v>
+        <x:v>71.065</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -865,28 +865,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>1206503</x:v>
+        <x:v>1499008</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>69.4540092717619</x:v>
+        <x:v>69.29</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>1071626</x:v>
+        <x:v>1341687</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>69.6816228682429</x:v>
+        <x:v>69.488</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>2278129</x:v>
+        <x:v>2840695</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>3.39105571727901</x:v>
+        <x:v>3.48150233996539</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>134877</x:v>
+        <x:v>157321</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>67.645571599345</x:v>
+        <x:v>67.605</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -894,28 +894,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>896309</x:v>
+        <x:v>171064</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>70.748449033559</x:v>
+        <x:v>69.501</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>825041</x:v>
+        <x:v>85451</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>70.6927151684472</x:v>
+        <x:v>69.908</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>1721350</x:v>
+        <x:v>256515</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>2.56227534039478</x:v>
+        <x:v>0.31437995727673</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>71268</x:v>
+        <x:v>85613</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>71.393657595687</x:v>
+        <x:v>69.094</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -923,28 +923,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>130366</x:v>
+        <x:v>74771</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>69.7471870462276</x:v>
+        <x:v>68.838</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>72429</x:v>
+        <x:v>33969</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>70.1666338471769</x:v>
+        <x:v>69.936</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>202795</x:v>
+        <x:v>108740</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.301865760975607</x:v>
+        <x:v>0.133269697890071</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>57937</x:v>
+        <x:v>40802</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>69.2228224373256</x:v>
+        <x:v>67.923</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -952,28 +952,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>68626</x:v>
+        <x:v>85194</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>68.8715183453833</x:v>
+        <x:v>69.717</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>26915</x:v>
+        <x:v>48898</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>70.3741518426336</x:v>
+        <x:v>70.134</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>95541</x:v>
+        <x:v>134092</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.142215324191279</x:v>
+        <x:v>0.164340632053296</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>41711</x:v>
+        <x:v>36296</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>67.901908875975</x:v>
+        <x:v>69.156</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -981,28 +981,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>76208</x:v>
+        <x:v>88925</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>69.870663544973</x:v>
+        <x:v>69.702</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>37442</x:v>
+        <x:v>53130</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>70.4895626384156</x:v>
+        <x:v>69.945</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>113650</x:v>
+        <x:v>142055</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.169171053205837</x:v>
+        <x:v>0.174099935017235</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>38766</x:v>
+        <x:v>35795</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>69.2729021082326</x:v>
+        <x:v>69.342</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1010,28 +1010,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>140777</x:v>
+        <x:v>150481</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>69.2785826978901</x:v>
+        <x:v>69.23</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>105152</x:v>
+        <x:v>117198</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>69.8020262426526</x:v>
+        <x:v>69.685</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>245929</x:v>
+        <x:v>267679</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.366071869281639</x:v>
+        <x:v>0.328062345608942</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>35625</x:v>
+        <x:v>33283</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>67.733568364729</x:v>
+        <x:v>67.626</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1039,28 +1039,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>66746</x:v>
+        <x:v>73220</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>70.1231225880478</x:v>
+        <x:v>70.03</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>33503</x:v>
+        <x:v>42504</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>70.0341216047689</x:v>
+        <x:v>69.718</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>100249</x:v>
+        <x:v>115724</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.149223307636005</x:v>
+        <x:v>0.141829156875396</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>33243</x:v>
+        <x:v>30716</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>70.2128196654113</x:v>
+        <x:v>70.462</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,28 +1068,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>89481</x:v>
+        <x:v>101229</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>69.6561960766082</x:v>
+        <x:v>69.423</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>57568</x:v>
+        <x:v>78107</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>70.0288963190644</x:v>
+        <x:v>69.602</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>147049</x:v>
+        <x:v>179336</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.218886354622658</x:v>
+        <x:v>0.219790827118023</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>31913</x:v>
+        <x:v>23122</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>68.9838804824079</x:v>
+        <x:v>68.818</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1097,28 +1097,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>67477</x:v>
+        <x:v>27391</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>69.8830061318555</x:v>
+        <x:v>68.183</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>48537</x:v>
+        <x:v>11881</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>70.0707337074336</x:v>
+        <x:v>69.206</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>116014</x:v>
+        <x:v>39272</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.17268993019465</x:v>
+        <x:v>0.048131024237069</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>18940</x:v>
+        <x:v>15510</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>69.4019220064157</x:v>
+        <x:v>67.399</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1126,28 +1126,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>24291</x:v>
+        <x:v>190427</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>68.1215046106883</x:v>
+        <x:v>70.257</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>5617</x:v>
+        <x:v>177491</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>69.8030368519016</x:v>
+        <x:v>69.772</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>29908</x:v>
+        <x:v>367918</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.0445188548990776</x:v>
+        <x:v>0.450913377858371</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>18674</x:v>
+        <x:v>12936</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>67.6157122470332</x:v>
+        <x:v>76.918</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1155,28 +1155,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>572311</x:v>
+        <x:v>766216</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>69.897553987116</x:v>
+        <x:v>69.567</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>555179</x:v>
+        <x:v>760645</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>69.8188369633975</x:v>
+        <x:v>69.504</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>1127490</x:v>
+        <x:v>1526861</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>1.67829890698679</x:v>
+        <x:v>1.87129211136778</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>17132</x:v>
+        <x:v>5571</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>72.4484551376532</x:v>
+        <x:v>78.122</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1184,28 +1184,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>801947</x:v>
+        <x:v>353272</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>70.7778589795672</x:v>
+        <x:v>69.83</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>792141</x:v>
+        <x:v>348028</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>69.2499961673547</x:v>
+        <x:v>69.905</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>1594088</x:v>
+        <x:v>701300</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>2.37284246249702</x:v>
+        <x:v>0.859500083964567</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>9806</x:v>
+        <x:v>5244</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>194.200536516669</x:v>
+        <x:v>64.825</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1213,28 +1213,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>267199</x:v>
+        <x:v>171088</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>70.1866744826025</x:v>
+        <x:v>71.694</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>260568</x:v>
+        <x:v>166973</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>70.284248004411</x:v>
+        <x:v>71.762</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>527767</x:v>
+        <x:v>338061</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.785595241859084</x:v>
+        <x:v>0.414321200463632</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>6631</x:v>
+        <x:v>4115</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>66.3524809325196</x:v>
+        <x:v>68.939</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1242,28 +1242,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>167135</x:v>
+        <x:v>389339</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>70.4459064166959</x:v>
+        <x:v>69.327</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>162763</x:v>
+        <x:v>387275</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>69.8647082046326</x:v>
+        <x:v>69.743</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>329898</x:v>
+        <x:v>776614</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.491061963136816</x:v>
+        <x:v>0.95180350521611</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>4372</x:v>
+        <x:v>2064</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>92.0830437886202</x:v>
+        <x:v>-8.761</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1271,28 +1271,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>160181</x:v>
+        <x:v>1019</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>71.8946338498077</x:v>
+        <x:v>70.031</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>157117</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>71.9865100908936</x:v>
+        <x:v>69.194</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>317298</x:v>
+        <x:v>1112</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.47230652740964</x:v>
+        <x:v>0.00136284627601397</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>3064</x:v>
+        <x:v>926</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>67.183367736657</x:v>
+        <x:v>70.116</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1300,28 +1300,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>1019</x:v>
+        <x:v>2433</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>70.0315970738105</x:v>
+        <x:v>70.545</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>93</x:v>
+        <x:v>2144</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>69.1919356315367</x:v>
+        <x:v>69.236</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1112</x:v>
+        <x:v>4577</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00165524162925553</x:v>
+        <x:v>0.00560948507672298</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>926</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>70.1159259227646</x:v>
+        <x:v>80.249</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1329,28 +1329,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>2433</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>70.5447799488198</x:v>
+        <x:v>68.388</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>2034</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>69.2581352038838</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>4467</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00664924852327737</x:v>
+        <x:v>9.80464946772642E-05</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>399</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>77.1037659418015</x:v>
+        <x:v>68.388</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1358,28 +1358,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>80</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>68.3943761825562</x:v>
+        <x:v>69.856</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>0</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>0</x:v>
+        <x:v>70.075</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>80</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.000119082131601117</x:v>
+        <x:v>0.000577248737412393</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>80</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>68.3943761825562</x:v>
+        <x:v>66.533</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1387,28 +1387,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>213</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>70.2267614015391</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>201</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>70.2402984846884</x:v>
+        <x:v>70.527</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>414</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00061625003103578</x:v>
+        <x:v>0.00016055113503402</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>12</x:v>
+        <x:v>-131</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>70.0000152587891</x:v>
+        <x:v>70.527</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1422,22 +1422,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>131</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>70.5297704798575</x:v>
+        <x:v>70.416</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>131</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.000194996990496829</x:v>
+        <x:v>0.000459592943799676</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-131</x:v>
+        <x:v>-375</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>70.5297704798575</x:v>
+        <x:v>70.416</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1445,28 +1445,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>0</x:v>
+        <x:v>6619</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>0</x:v>
+        <x:v>69.306</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>319</x:v>
+        <x:v>7050</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>70.6924758002302</x:v>
+        <x:v>70.467</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>319</x:v>
+        <x:v>13669</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.000474839999759454</x:v>
+        <x:v>0.016752469196794</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-319</x:v>
+        <x:v>-431</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>70.6924758002302</x:v>
+        <x:v>88.285</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1474,28 +1474,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>6098</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>69.34940296347</x:v>
+        <x:v>70.38</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>6872</x:v>
+        <x:v>2292</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>70.5090925074567</x:v>
+        <x:v>69.454</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>12970</x:v>
+        <x:v>2568</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.0193061905858311</x:v>
+        <x:v>0.00314729247914018</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-774</x:v>
+        <x:v>-2016</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>79.6457680103391</x:v>
+        <x:v>69.327</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1503,28 +1503,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>226</x:v>
+        <x:v>7462</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>70.6969029924511</x:v>
+        <x:v>68.051</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>2177</x:v>
+        <x:v>13310</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>69.5507357294646</x:v>
+        <x:v>70.84</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>2403</x:v>
+        <x:v>20772</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00357692952796855</x:v>
+        <x:v>0.0254577723429516</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-1951</x:v>
+        <x:v>-5848</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>69.4179659696312</x:v>
+        <x:v>74.398</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1532,28 +1532,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>5458</x:v>
+        <x:v>861672</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>67.7950714757129</x:v>
+        <x:v>70.612</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>12945</x:v>
+        <x:v>868953</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>70.8999454502711</x:v>
+        <x:v>69.203</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>18403</x:v>
+        <x:v>1730625</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.027393355848192</x:v>
+        <x:v>2.1210214356355</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-7487</x:v>
+        <x:v>-7281</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>73.1633890395778</x:v>
+        <x:v>-97.64</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1561,28 +1561,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>80657</x:v>
+        <x:v>996842</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>70.5769922431533</x:v>
+        <x:v>70.498</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>95931</x:v>
+        <x:v>1009304</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>69.3186178315061</x:v>
+        <x:v>70.356</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>176588</x:v>
+        <x:v>2006146</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.262855943189726</x:v>
+        <x:v>2.45869478888518</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-15274</x:v>
+        <x:v>-12462</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>62.6735540027626</x:v>
+        <x:v>58.976</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1590,28 +1590,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>289450</x:v>
+        <x:v>838742</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>69.4980440472609</x:v>
+        <x:v>69.639</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>322188</x:v>
+        <x:v>851739</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>69.9430830578746</x:v>
+        <x:v>69.877</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>611638</x:v>
+        <x:v>1690481</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.91043946010305</x:v>
+        <x:v>2.07182170460645</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-32738</x:v>
+        <x:v>-12997</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>73.8778543213029</x:v>
+        <x:v>85.223</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1619,28 +1619,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>710791</x:v>
+        <x:v>84639</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>69.7979872627138</x:v>
+        <x:v>70.485</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>747227</x:v>
+        <x:v>100644</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>69.8275267941234</x:v>
+        <x:v>69.287</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>1458018</x:v>
+        <x:v>185283</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>2.17029864190997</x:v>
+        <x:v>0.227079358416094</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-36436</x:v>
+        <x:v>-16005</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>70.4037819557806</x:v>
+        <x:v>62.95</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1648,28 +1648,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>2476112</x:v>
+        <x:v>2772507</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>70.2075668079548</x:v>
+        <x:v>70.032</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>2519113</x:v>
+        <x:v>2803587</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>70.2773951997018</x:v>
+        <x:v>70.107</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>4995225</x:v>
+        <x:v>5576094</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>7.43552551033987</x:v>
+        <x:v>6.83395588363656</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-43001</x:v>
+        <x:v>-31080</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>74.2982998006508</x:v>
+        <x:v>76.776</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1677,28 +1677,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>240985</x:v>
+        <x:v>242676</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>70.5803811123701</x:v>
+        <x:v>70.566</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>294702</x:v>
+        <x:v>304775</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>70.2196851573812</x:v>
+        <x:v>70.166</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>535687</x:v>
+        <x:v>547451</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.797384372887595</x:v>
+        <x:v>0.670945644469537</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-53717</x:v>
+        <x:v>-62099</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>68.6015323433186</x:v>
+        <x:v>68.602</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1706,28 +1706,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>713193</x:v>
+        <x:v>713458</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>72.1724061382326</x:v>
+        <x:v>72.171</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>781440</x:v>
+        <x:v>781777</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>70.8628734725016</x:v>
+        <x:v>70.862</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>1494633</x:v>
+        <x:v>1495235</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>2.22480104501715</x:v>
+        <x:v>1.83253188085949</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-68247</x:v>
+        <x:v>-68319</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>57.1780297362097</x:v>
+        <x:v>57.191</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1735,28 +1735,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>722954</x:v>
+        <x:v>1561282</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>69.7827436795358</x:v>
+        <x:v>70.348</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>799319</x:v>
+        <x:v>1652508</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>69.9578610214656</x:v>
+        <x:v>70.116</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>1522273</x:v>
+        <x:v>3213790</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>2.26594392148534</x:v>
+        <x:v>3.93876055161056</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-76365</x:v>
+        <x:v>-91226</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>71.6157119062618</x:v>
+        <x:v>66.138</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1764,28 +1764,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>1422555</x:v>
+        <x:v>233320</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>70.5342949692547</x:v>
+        <x:v>71.827</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>1505828</x:v>
+        <x:v>342442</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>70.2518824038747</x:v>
+        <x:v>71.122</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>2928383</x:v>
+        <x:v>575762</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>4.35897612230592</x:v>
+        <x:v>0.705643073354637</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-83273</x:v>
+        <x:v>-109122</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>65.4274206102061</x:v>
+        <x:v>69.615</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1793,28 +1793,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>227835</x:v>
+        <x:v>928102</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>71.8984165312286</x:v>
+        <x:v>69.442</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>334533</x:v>
+        <x:v>1054994</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>71.1876637332566</x:v>
+        <x:v>69.412</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>562368</x:v>
+        <x:v>1983096</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.837099752303212</x:v>
+        <x:v>2.4304451426063</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-106698</x:v>
+        <x:v>-126892</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>69.6699748944225</x:v>
+        <x:v>69.197</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1822,28 +1822,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>308810</x:v>
+        <x:v>309845</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>72.306662778804</x:v>
+        <x:v>72.291</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>444529</x:v>
+        <x:v>445661</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>71.1865738853436</x:v>
+        <x:v>71.18</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>753339</x:v>
+        <x:v>755506</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.12136517422817</x:v>
+        <x:v>0.925933937595514</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-135719</x:v>
+        <x:v>-135816</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>68.6379649861511</x:v>
+        <x:v>68.647</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1851,28 +1851,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>350214</x:v>
+        <x:v>450080</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>70.1292433667227</x:v>
+        <x:v>69.789</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>627326</x:v>
+        <x:v>642672</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>69.3911666004686</x:v>
+        <x:v>69.358</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>977540</x:v>
+        <x:v>1092752</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.45509433656695</x:v>
+        <x:v>1.33925628939462</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-277112</x:v>
+        <x:v>-192592</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>68.4583855710764</x:v>
+        <x:v>68.351</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1880,28 +1880,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>751740</x:v>
+        <x:v>854797</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>70.7085007943416</x:v>
+        <x:v>70.405</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1067858</x:v>
+        <x:v>1195810</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>70.2680586742379</x:v>
+        <x:v>70.056</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1819598</x:v>
+        <x:v>2050607</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>2.70852010621412</x:v>
+        <x:v>2.51318535388326</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-316118</x:v>
+        <x:v>-341013</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>69.2206714347679</x:v>
+        <x:v>69.183</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1909,28 +1909,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>292087</x:v>
+        <x:v>361323</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>70.4130903183936</x:v>
+        <x:v>69.906</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>849313</x:v>
+        <x:v>867169</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>71.3911521693127</x:v>
+        <x:v>71.332</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>1141400</x:v>
+        <x:v>1228492</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.69900431261894</x:v>
+        <x:v>1.50561667923827</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-557226</x:v>
+        <x:v>-505846</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>71.9038331135785</x:v>
+        <x:v>72.352</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1938,28 +1938,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>169479</x:v>
+        <x:v>342408</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>69.7195784384257</x:v>
+        <x:v>69.186</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>768838</x:v>
+        <x:v>1300332</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>71.797003667676</x:v>
+        <x:v>70.62</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>938317</x:v>
+        <x:v>1642740</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>1.39670985596957</x:v>
+        <x:v>2.01331123332661</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-599359</x:v>
+        <x:v>-957924</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>72.3844311534201</x:v>
+        <x:v>71.133</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1967,28 +1967,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>2117581</x:v>
+        <x:v>2625008</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>71.4990885265831</x:v>
+        <x:v>70.972</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>3045262</x:v>
+        <x:v>3732600</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>69.8777556129841</x:v>
+        <x:v>69.629</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>5162843</x:v>
+        <x:v>6357608</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>7.68502936952382</x:v>
+        <x:v>7.79176473665165</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-927681</x:v>
+        <x:v>-1107592</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>66.1768026210484</x:v>
+        <x:v>66.445</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1996,28 +1996,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>3025593</x:v>
+        <x:v>3322235</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>70.3299189683484</x:v>
+        <x:v>70.17</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>5002162</x:v>
+        <x:v>5811590</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>70.0900186981897</x:v>
+        <x:v>69.889</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>8027755</x:v>
+        <x:v>9133825</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>11.9495272171441</x:v>
+        <x:v>11.1942440530695</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-1976569</x:v>
+        <x:v>-2489355</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>69.7227962141326</x:v>
+        <x:v>69.514</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -49,136 +49,139 @@
     <x:t>IS</x:t>
   </x:si>
   <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
-    <x:t>ZIRAAT</x:t>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEO MENKUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
   </x:si>
   <x:si>
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
     <x:t>IKON</x:t>
   </x:si>
   <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
-    <x:t>SEKER</x:t>
+    <x:t>ATA</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
+    <x:t>TERA</x:t>
   </x:si>
   <x:si>
     <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
-    <x:t>TERA</x:t>
+    <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>ALNUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>TRIVE</x:t>
@@ -538,7 +541,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I51"/>
+  <x:dimension ref="A1:I52"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -575,28 +578,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>2480268</x:v>
+        <x:v>3124416</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>69.463</x:v>
+        <x:v>69.015</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>1139497</x:v>
+        <x:v>1514712</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>69.524</x:v>
+        <x:v>69.05</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>3619765</x:v>
+        <x:v>4639128</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>4.43631587256809</x:v>
+        <x:v>4.50995302351002</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>1340771</x:v>
+        <x:v>1609704</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>69.411</x:v>
+        <x:v>68.981</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -604,28 +607,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>1911041</x:v>
+        <x:v>2525811</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>69.528</x:v>
+        <x:v>69.021</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>934542</x:v>
+        <x:v>1335436</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>69.7</x:v>
+        <x:v>69.057</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>2845583</x:v>
+        <x:v>3861247</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>3.48749298079017</x:v>
+        <x:v>3.75373186128277</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>976499</x:v>
+        <x:v>1190375</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>69.364</x:v>
+        <x:v>68.981</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -633,28 +636,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>2828122</x:v>
+        <x:v>3694074</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>69.551</x:v>
+        <x:v>69.038</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>2195032</x:v>
+        <x:v>2551587</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>70.03</x:v>
+        <x:v>69.705</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>5023154</x:v>
+        <x:v>6245661</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>6.15628302405098</x:v>
+        <x:v>6.07175264635264</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>633090</x:v>
+        <x:v>1142487</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>67.89</x:v>
+        <x:v>67.547</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -662,28 +665,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>1239708</x:v>
+        <x:v>2762349</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>69.55</x:v>
+        <x:v>68.795</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>672328</x:v>
+        <x:v>1908128</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>69.613</x:v>
+        <x:v>69.302</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>1912036</x:v>
+        <x:v>4670477</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.34335534370922</x:v>
+        <x:v>4.54042912102964</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>567380</x:v>
+        <x:v>854221</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>69.475</x:v>
+        <x:v>67.663</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -691,28 +694,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>5714538</x:v>
+        <x:v>1693464</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>69.57</x:v>
+        <x:v>68.949</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>5283292</x:v>
+        <x:v>879540</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>69.643</x:v>
+        <x:v>69.075</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>10997830</x:v>
+        <x:v>2573004</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>13.4787335069557</x:v>
+        <x:v>2.50135955923255</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>431246</x:v>
+        <x:v>813924</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>68.674</x:v>
+        <x:v>68.812</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -720,28 +723,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>1972204</x:v>
+        <x:v>7541596</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>69.386</x:v>
+        <x:v>69.035</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>1554686</x:v>
+        <x:v>6932624</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>69.674</x:v>
+        <x:v>69.119</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>3526890</x:v>
+        <x:v>14474220</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>4.3224900201537</x:v>
+        <x:v>14.0711901572772</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>417518</x:v>
+        <x:v>608972</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>68.311</x:v>
+        <x:v>68.079</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -749,28 +752,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>1018985</x:v>
+        <x:v>2049881</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>69.603</x:v>
+        <x:v>68.825</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>647378</x:v>
+        <x:v>1573111</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>69.853</x:v>
+        <x:v>69.217</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>1666363</x:v>
+        <x:v>3622992</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>2.04226313762362</x:v>
+        <x:v>3.52211099252976</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>371607</x:v>
+        <x:v>476770</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>69.168</x:v>
+        <x:v>67.532</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -778,28 +781,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>785286</x:v>
+        <x:v>888334</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>69.288</x:v>
+        <x:v>68.485</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>415404</x:v>
+        <x:v>467553</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>69.643</x:v>
+        <x:v>69.05</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>1200690</x:v>
+        <x:v>1355887</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.47154307117555</x:v>
+        <x:v>1.31813277736418</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>369882</x:v>
+        <x:v>420781</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>68.89</x:v>
+        <x:v>67.857</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -807,28 +810,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>677341</x:v>
+        <x:v>899643</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>68.869</x:v>
+        <x:v>69.096</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>333218</x:v>
+        <x:v>523840</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>69.716</x:v>
+        <x:v>69.205</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1010559</x:v>
+        <x:v>1423483</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.23852209518202</x:v>
+        <x:v>1.38384658922218</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>344123</x:v>
+        <x:v>375803</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>68.048</x:v>
+        <x:v>68.945</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -836,28 +839,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>510785</x:v>
+        <x:v>1149729</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>70.263</x:v>
+        <x:v>69.358</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>176177</x:v>
+        <x:v>1024942</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>68.739</x:v>
+        <x:v>68.875</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>686962</x:v>
+        <x:v>2174671</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.841927700956034</x:v>
+        <x:v>2.11411800915809</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>334608</x:v>
+        <x:v>124787</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>71.065</x:v>
+        <x:v>73.321</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -865,28 +868,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>1499008</x:v>
+        <x:v>1121287</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>69.29</x:v>
+        <x:v>68.87</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>1341687</x:v>
+        <x:v>1004274</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>69.488</x:v>
+        <x:v>68.971</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>2840695</x:v>
+        <x:v>2125561</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>3.48150233996539</x:v>
+        <x:v>2.06637546077732</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>157321</x:v>
+        <x:v>117013</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>67.605</x:v>
+        <x:v>68.001</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -894,28 +897,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>171064</x:v>
+        <x:v>173940</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>69.501</x:v>
+        <x:v>68.621</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>85451</x:v>
+        <x:v>62968</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>69.908</x:v>
+        <x:v>69.544</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>256515</x:v>
+        <x:v>236908</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.31437995727673</x:v>
+        <x:v>0.230311375520079</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>85613</x:v>
+        <x:v>110972</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>69.094</x:v>
+        <x:v>68.098</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -923,28 +926,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>74771</x:v>
+        <x:v>208081</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>68.838</x:v>
+        <x:v>69.047</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>33969</x:v>
+        <x:v>99009</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>69.936</x:v>
+        <x:v>69.563</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>108740</x:v>
+        <x:v>307090</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.133269697890071</x:v>
+        <x:v>0.298539181068014</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>40802</x:v>
+        <x:v>109072</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>67.923</x:v>
+        <x:v>68.579</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -952,28 +955,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>85194</x:v>
+        <x:v>1285520</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>69.717</x:v>
+        <x:v>69.813</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>48898</x:v>
+        <x:v>1213383</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>70.134</x:v>
+        <x:v>69.888</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>134092</x:v>
+        <x:v>2498903</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.164340632053296</x:v>
+        <x:v>2.42932187693641</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>36296</x:v>
+        <x:v>72137</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>69.156</x:v>
+        <x:v>68.538</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -981,28 +984,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>88925</x:v>
+        <x:v>177883</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>69.702</x:v>
+        <x:v>68.906</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>53130</x:v>
+        <x:v>123583</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>69.945</x:v>
+        <x:v>69.559</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>142055</x:v>
+        <x:v>301466</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.174099935017235</x:v>
+        <x:v>0.29307177947784</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>35795</x:v>
+        <x:v>54300</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>69.342</x:v>
+        <x:v>67.42</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1010,28 +1013,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>150481</x:v>
+        <x:v>1065349</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>69.23</x:v>
+        <x:v>70.032</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>117198</x:v>
+        <x:v>1013251</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>69.685</x:v>
+        <x:v>68.955</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>267679</x:v>
+        <x:v>2078600</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.328062345608942</x:v>
+        <x:v>2.02072207420617</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>33283</x:v>
+        <x:v>52098</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>67.626</x:v>
+        <x:v>90.991</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1039,28 +1042,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>73220</x:v>
+        <x:v>93351</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>70.03</x:v>
+        <x:v>68.532</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>42504</x:v>
+        <x:v>45756</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>69.718</x:v>
+        <x:v>69.232</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>115724</x:v>
+        <x:v>139107</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.141829156875396</x:v>
+        <x:v>0.135233611842874</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>30716</x:v>
+        <x:v>47595</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>70.462</x:v>
+        <x:v>67.86</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1068,28 +1071,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>101229</x:v>
+        <x:v>101110</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>69.423</x:v>
+        <x:v>69.496</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>78107</x:v>
+        <x:v>54743</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>69.602</x:v>
+        <x:v>69.171</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>179336</x:v>
+        <x:v>155853</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.219790827118023</x:v>
+        <x:v>0.151513325041496</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>23122</x:v>
+        <x:v>46367</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>68.818</x:v>
+        <x:v>69.88</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1097,28 +1100,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>27391</x:v>
+        <x:v>98293</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>68.183</x:v>
+        <x:v>69.514</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>11881</x:v>
+        <x:v>62123</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>69.206</x:v>
+        <x:v>69.515</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>39272</x:v>
+        <x:v>160416</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.048131024237069</x:v>
+        <x:v>0.155949269823851</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>15510</x:v>
+        <x:v>36170</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>67.399</x:v>
+        <x:v>69.513</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1126,28 +1129,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>190427</x:v>
+        <x:v>554694</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>70.257</x:v>
+        <x:v>68.721</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>177491</x:v>
+        <x:v>524089</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>69.772</x:v>
+        <x:v>69.155</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>367918</x:v>
+        <x:v>1078783</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.450913377858371</x:v>
+        <x:v>1.04874464609754</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>12936</x:v>
+        <x:v>30605</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>76.918</x:v>
+        <x:v>61.293</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1155,28 +1158,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>766216</x:v>
+        <x:v>122505</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>69.567</x:v>
+        <x:v>68.973</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>760645</x:v>
+        <x:v>99017</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>69.504</x:v>
+        <x:v>69.086</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>1526861</x:v>
+        <x:v>221522</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>1.87129211136778</x:v>
+        <x:v>0.215353793573703</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>5571</x:v>
+        <x:v>23488</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>78.122</x:v>
+        <x:v>68.495</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1184,28 +1187,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>353272</x:v>
+        <x:v>32832</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>69.83</x:v>
+        <x:v>68.162</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>348028</x:v>
+        <x:v>15326</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>69.905</x:v>
+        <x:v>69.114</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>701300</x:v>
+        <x:v>48158</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.859500083964567</x:v>
+        <x:v>0.0468170565041955</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>5244</x:v>
+        <x:v>17506</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>64.825</x:v>
+        <x:v>67.328</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1213,28 +1216,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>171088</x:v>
+        <x:v>502786</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>71.694</x:v>
+        <x:v>69.047</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>166973</x:v>
+        <x:v>485682</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>71.762</x:v>
+        <x:v>69.13</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>338061</x:v>
+        <x:v>988468</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.414321200463632</x:v>
+        <x:v>0.960944437239693</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>4115</x:v>
+        <x:v>17104</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>68.939</x:v>
+        <x:v>66.681</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1242,28 +1245,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>389339</x:v>
+        <x:v>228811</x:v>
       </x:c>
       <x:c r="C25" s="0">
+        <x:v>69.703</x:v>
+      </x:c>
+      <x:c r="D25" s="0">
+        <x:v>218947</x:v>
+      </x:c>
+      <x:c r="E25" s="0">
         <x:v>69.327</x:v>
       </x:c>
-      <x:c r="D25" s="0">
-        <x:v>387275</x:v>
-      </x:c>
-      <x:c r="E25" s="0">
-        <x:v>69.743</x:v>
-      </x:c>
       <x:c r="F25" s="0">
-        <x:v>776614</x:v>
+        <x:v>447758</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.95180350521611</x:v>
+        <x:v>0.435290327384974</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>2064</x:v>
+        <x:v>9864</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>-8.761</x:v>
+        <x:v>78.045</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1271,28 +1274,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>1019</x:v>
+        <x:v>995129</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>70.031</x:v>
+        <x:v>69.222</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>93</x:v>
+        <x:v>987749</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>69.194</x:v>
+        <x:v>69.496</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1112</x:v>
+        <x:v>1982878</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.00136284627601397</x:v>
+        <x:v>1.92766542146531</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>926</x:v>
+        <x:v>7380</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>70.116</x:v>
+        <x:v>32.439</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1300,28 +1303,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>2433</x:v>
+        <x:v>176085</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>70.545</x:v>
+        <x:v>71.572</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>2144</x:v>
+        <x:v>169730</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>69.236</x:v>
+        <x:v>71.704</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>4577</x:v>
+        <x:v>345815</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00560948507672298</x:v>
+        <x:v>0.336185896320412</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>289</x:v>
+        <x:v>6355</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>80.249</x:v>
+        <x:v>68.06</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1329,28 +1332,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>80</x:v>
+        <x:v>1019</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>68.388</x:v>
+        <x:v>70.031</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>0</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>0</x:v>
+        <x:v>69.125</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>80</x:v>
+        <x:v>1139</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>9.80464946772642E-05</x:v>
+        <x:v>0.00110728492375677</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>80</x:v>
+        <x:v>899</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>68.388</x:v>
+        <x:v>70.152</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1358,28 +1361,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>243</x:v>
+        <x:v>2620</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>69.856</x:v>
+        <x:v>70.295</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>228</x:v>
+        <x:v>2172</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>70.075</x:v>
+        <x:v>69.237</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>471</x:v>
+        <x:v>4792</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.000577248737412393</x:v>
+        <x:v>0.00465856835350523</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>15</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>66.533</x:v>
+        <x:v>75.429</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1387,28 +1390,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="C30" s="0">
+        <x:v>66.799</x:v>
+      </x:c>
+      <x:c r="D30" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C30" s="0">
+      <x:c r="E30" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D30" s="0">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="E30" s="0">
-        <x:v>70.527</x:v>
-      </x:c>
       <x:c r="F30" s="0">
-        <x:v>131</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00016055113503402</x:v>
+        <x:v>0.000300395997753155</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>-131</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>70.527</x:v>
+        <x:v>66.799</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1416,28 +1419,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C31" s="0">
+        <x:v>68.207</x:v>
+      </x:c>
+      <x:c r="D31" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C31" s="0">
+      <x:c r="E31" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D31" s="0">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="E31" s="0">
-        <x:v>70.416</x:v>
-      </x:c>
       <x:c r="F31" s="0">
-        <x:v>375</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.000459592943799676</x:v>
+        <x:v>0.000145823299880172</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>-375</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>70.416</x:v>
+        <x:v>68.207</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1445,28 +1448,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>6619</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>69.306</x:v>
+        <x:v>69.485</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>7050</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>70.467</x:v>
+        <x:v>69.558</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>13669</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.016752469196794</x:v>
+        <x:v>0.000597875529508706</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-431</x:v>
+        <x:v>-9</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>88.285</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1474,28 +1477,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>276</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>70.38</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>2292</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>69.454</x:v>
+        <x:v>70.527</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>2568</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.00314729247914018</x:v>
+        <x:v>0.000127352348562017</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-2016</x:v>
+        <x:v>-131</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>69.327</x:v>
+        <x:v>70.527</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1503,28 +1506,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>7462</x:v>
+        <x:v>6855</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>68.051</x:v>
+        <x:v>69.225</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>13310</x:v>
+        <x:v>7220</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>70.84</x:v>
+        <x:v>70.395</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>20772</x:v>
+        <x:v>14075</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0254577723429516</x:v>
+        <x:v>0.0136830863054228</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-5848</x:v>
+        <x:v>-365</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>74.398</x:v>
+        <x:v>92.359</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1532,28 +1535,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>861672</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>70.612</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>868953</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>69.203</x:v>
+        <x:v>70.416</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>1730625</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>2.1210214356355</x:v>
+        <x:v>0.00036455824970043</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-7281</x:v>
+        <x:v>-375</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>-97.64</x:v>
+        <x:v>70.416</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1561,28 +1564,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>996842</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>70.498</x:v>
+        <x:v>70.38</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>1009304</x:v>
+        <x:v>2295</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>70.356</x:v>
+        <x:v>69.451</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>2006146</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>2.45869478888518</x:v>
+        <x:v>0.00249941135994615</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-12462</x:v>
+        <x:v>-2019</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>58.976</x:v>
+        <x:v>69.323</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1590,28 +1593,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>838742</x:v>
+        <x:v>1198233</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>69.639</x:v>
+        <x:v>68.958</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>851739</x:v>
+        <x:v>1200775</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>69.877</x:v>
+        <x:v>69.163</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>1690481</x:v>
+        <x:v>2399008</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>2.07182170460645</x:v>
+        <x:v>2.33220841999288</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-12997</x:v>
+        <x:v>-2542</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>85.223</x:v>
+        <x:v>165.586</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1619,28 +1622,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>84639</x:v>
+        <x:v>20617</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>70.485</x:v>
+        <x:v>67.49</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>100644</x:v>
+        <x:v>27374</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>69.287</x:v>
+        <x:v>68.894</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>185283</x:v>
+        <x:v>47991</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.227079358416094</x:v>
+        <x:v>0.0466547065636623</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-16005</x:v>
+        <x:v>-6757</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>62.95</x:v>
+        <x:v>73.179</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1648,28 +1651,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>2772507</x:v>
+        <x:v>103311</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>70.032</x:v>
+        <x:v>69.839</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>2803587</x:v>
+        <x:v>125507</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>70.107</x:v>
+        <x:v>68.897</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>5576094</x:v>
+        <x:v>228818</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>6.83395588363656</x:v>
+        <x:v>0.222446638879875</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-31080</x:v>
+        <x:v>-22196</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>76.776</x:v>
+        <x:v>64.512</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1677,28 +1680,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>242676</x:v>
+        <x:v>742086</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>70.566</x:v>
+        <x:v>71.982</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>304775</x:v>
+        <x:v>787115</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>70.166</x:v>
+        <x:v>70.834</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>547451</x:v>
+        <x:v>1529201</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.670945644469537</x:v>
+        <x:v>1.48662090666706</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-62099</x:v>
+        <x:v>-45029</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>68.602</x:v>
+        <x:v>51.925</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1706,28 +1709,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>713458</x:v>
+        <x:v>533377</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>72.171</x:v>
+        <x:v>70.213</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>781777</x:v>
+        <x:v>582351</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>70.862</x:v>
+        <x:v>67.643</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>1495235</x:v>
+        <x:v>1115728</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>1.83253188085949</x:v>
+        <x:v>1.08466092485803</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-68319</x:v>
+        <x:v>-48974</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>57.191</x:v>
+        <x:v>39.648</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1735,28 +1738,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>1561282</x:v>
+        <x:v>3097022</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>70.348</x:v>
+        <x:v>69.726</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>1652508</x:v>
+        <x:v>3153522</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>70.116</x:v>
+        <x:v>69.773</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>3213790</x:v>
+        <x:v>6250544</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>3.93876055161056</x:v>
+        <x:v>6.0764996808414</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-91226</x:v>
+        <x:v>-56500</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>66.138</x:v>
+        <x:v>72.362</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1764,28 +1767,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>233320</x:v>
+        <x:v>303227</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>71.827</x:v>
+        <x:v>69.874</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>342442</x:v>
+        <x:v>360017</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>71.122</x:v>
+        <x:v>69.696</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>575762</x:v>
+        <x:v>663244</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.705643073354637</x:v>
+        <x:v>0.644776191371499</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-109122</x:v>
+        <x:v>-56790</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>69.615</x:v>
+        <x:v>68.744</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1793,28 +1796,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>928102</x:v>
+        <x:v>270242</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>69.442</x:v>
+        <x:v>71.193</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>1054994</x:v>
+        <x:v>351287</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>69.412</x:v>
+        <x:v>71.025</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>1983096</x:v>
+        <x:v>621529</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>2.4304451426063</x:v>
+        <x:v>0.604222731674823</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-126892</x:v>
+        <x:v>-81045</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>69.197</x:v>
+        <x:v>70.462</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1822,28 +1825,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>309845</x:v>
+        <x:v>1774326</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>72.291</x:v>
+        <x:v>69.963</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>445661</x:v>
+        <x:v>1872648</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>71.18</x:v>
+        <x:v>69.773</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>755506</x:v>
+        <x:v>3646974</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.925933937595514</x:v>
+        <x:v>3.54542522171461</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-135816</x:v>
+        <x:v>-98322</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>68.647</x:v>
+        <x:v>66.337</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1851,28 +1854,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>450080</x:v>
+        <x:v>538442</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>69.789</x:v>
+        <x:v>69.435</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>642672</x:v>
+        <x:v>672382</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>69.358</x:v>
+        <x:v>69.287</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>1092752</x:v>
+        <x:v>1210824</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.33925628939462</x:v>
+        <x:v>1.17710900836073</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-192592</x:v>
+        <x:v>-133940</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>68.351</x:v>
+        <x:v>68.693</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1880,28 +1883,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>854797</x:v>
+        <x:v>316345</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>70.405</x:v>
+        <x:v>72.182</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>1195810</x:v>
+        <x:v>452161</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>70.056</x:v>
+        <x:v>71.121</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>2050607</x:v>
+        <x:v>768506</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>2.51318535388326</x:v>
+        <x:v>0.747107205984744</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-341013</x:v>
+        <x:v>-135816</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>69.183</x:v>
+        <x:v>68.651</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1909,28 +1912,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>361323</x:v>
+        <x:v>710802</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>69.906</x:v>
+        <x:v>68.384</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>867169</x:v>
+        <x:v>1687975</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>71.332</x:v>
+        <x:v>69.068</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>1228492</x:v>
+        <x:v>2398777</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>1.50561667923827</x:v>
+        <x:v>2.33198385211106</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-505846</x:v>
+        <x:v>-977173</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>72.352</x:v>
+        <x:v>69.566</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1938,28 +1941,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>342408</x:v>
+        <x:v>991505</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>69.186</x:v>
+        <x:v>69.911</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>1300332</x:v>
+        <x:v>2272562</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>70.62</x:v>
+        <x:v>68.895</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>1642740</x:v>
+        <x:v>3264067</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>2.01331123332661</x:v>
+        <x:v>3.17318013979983</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-957924</x:v>
+        <x:v>-1281057</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>71.133</x:v>
+        <x:v>68.108</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1967,28 +1970,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>2625008</x:v>
+        <x:v>563138</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>70.972</x:v>
+        <x:v>68.89</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>3732600</x:v>
+        <x:v>2017456</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>69.629</x:v>
+        <x:v>69.546</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>6357608</x:v>
+        <x:v>2580594</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>7.79176473665165</x:v>
+        <x:v>2.50873821820649</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-1107592</x:v>
+        <x:v>-1454318</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>66.445</x:v>
+        <x:v>69.801</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1996,28 +1999,57 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>3322235</x:v>
+        <x:v>2999082</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>70.17</x:v>
+        <x:v>70.555</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>5811590</x:v>
+        <x:v>4494718</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>69.889</x:v>
+        <x:v>69.177</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>9133825</x:v>
+        <x:v>7493800</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>11.1942440530695</x:v>
+        <x:v>7.28513763094689</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-2489355</x:v>
+        <x:v>-1495636</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>69.514</x:v>
+        <x:v>66.412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:9">
+      <x:c r="A52" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B52" s="0">
+        <x:v>3991870</x:v>
+      </x:c>
+      <x:c r="C52" s="0">
+        <x:v>69.699</x:v>
+      </x:c>
+      <x:c r="D52" s="0">
+        <x:v>6470532</x:v>
+      </x:c>
+      <x:c r="E52" s="0">
+        <x:v>69.65</x:v>
+      </x:c>
+      <x:c r="F52" s="0">
+        <x:v>10462402</x:v>
+      </x:c>
+      <x:c r="G52" s="0">
+        <x:v>10.1710798954194</x:v>
+      </x:c>
+      <x:c r="H52" s="0">
+        <x:v>-2478662</x:v>
+      </x:c>
+      <x:c r="I52" s="0">
+        <x:v>69.57</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -49,22 +49,37 @@
     <x:t>IS</x:t>
   </x:si>
   <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
-    <x:t>PHILLIP</x:t>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
     <x:t>GEDIK</x:t>
@@ -73,31 +88,22 @@
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
   </x:si>
   <x:si>
     <x:t>BURGAN</x:t>
   </x:si>
   <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
     <x:t>ING</x:t>
   </x:si>
   <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
-    <x:t>OYAK</x:t>
+    <x:t>HALK</x:t>
   </x:si>
   <x:si>
     <x:t>UNLU</x:t>
@@ -106,21 +112,24 @@
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>ACAR</x:t>
   </x:si>
   <x:si>
-    <x:t>GLOBAL</x:t>
+    <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
     <x:t>DESTEK</x:t>
   </x:si>
   <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
     <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
@@ -130,64 +139,55 @@
     <x:t>HSBC</x:t>
   </x:si>
   <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
     <x:t>DINAMIK</x:t>
   </x:si>
   <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
     <x:t>BIZIM</x:t>
   </x:si>
   <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
     <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
     <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
     <x:t>ATA</x:t>
   </x:si>
   <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
     <x:t>A1 CAPITAL</x:t>
@@ -578,28 +578,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>3124416</x:v>
+        <x:v>3493619</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>69.015</x:v>
+        <x:v>68.7146353049048</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>1514712</x:v>
+        <x:v>1827470</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>69.05</x:v>
+        <x:v>68.5583352089914</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>4639128</x:v>
+        <x:v>5321089</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>4.50995302351002</x:v>
+        <x:v>4.70303836651723</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>1609704</x:v>
+        <x:v>1666149</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>68.981</x:v>
+        <x:v>68.8860687939137</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -607,28 +607,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>2525811</x:v>
+        <x:v>2774219</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>69.021</x:v>
+        <x:v>68.7337186245993</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1335436</x:v>
+        <x:v>1524304</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>69.057</x:v>
+        <x:v>68.6269856258401</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>3861247</x:v>
+        <x:v>4298523</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>3.75373186128277</x:v>
+        <x:v>3.7992445885338</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>1190375</x:v>
+        <x:v>1249915</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>68.981</x:v>
+        <x:v>68.8638823052822</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -636,28 +636,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>3694074</x:v>
+        <x:v>4734856</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>69.038</x:v>
+        <x:v>68.3721498449583</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>2551587</x:v>
+        <x:v>3740184</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>69.705</x:v>
+        <x:v>68.6168689605209</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>6245661</x:v>
+        <x:v>8475040</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>6.07175264635264</x:v>
+        <x:v>7.49065431489084</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>1142487</x:v>
+        <x:v>994672</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>67.547</x:v>
+        <x:v>67.4519525130527</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -665,28 +665,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>2762349</x:v>
+        <x:v>1883228</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>68.795</x:v>
+        <x:v>68.631089535328</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>1908128</x:v>
+        <x:v>1028270</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>69.302</x:v>
+        <x:v>68.5675829636374</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>4670477</x:v>
+        <x:v>2911498</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>4.54042912102964</x:v>
+        <x:v>2.57332414436936</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>854221</x:v>
+        <x:v>854958</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>67.663</x:v>
+        <x:v>68.7074697814596</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -694,28 +694,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>1693464</x:v>
+        <x:v>2933374</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>68.949</x:v>
+        <x:v>68.6241948054935</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>879540</x:v>
+        <x:v>2260196</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>69.075</x:v>
+        <x:v>68.7314435788164</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>2573004</x:v>
+        <x:v>5193570</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>2.50135955923255</x:v>
+        <x:v>4.59033084565827</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>813924</x:v>
+        <x:v>673178</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>68.812</x:v>
+        <x:v>68.2641069112525</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -723,28 +723,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>7541596</x:v>
+        <x:v>8364525</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>69.035</x:v>
+        <x:v>68.7192514519946</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>6932624</x:v>
+        <x:v>7728421</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>69.119</x:v>
+        <x:v>68.7763714182348</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>14474220</x:v>
+        <x:v>16092946</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>14.0711901572772</x:v>
+        <x:v>14.2237317339158</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>608972</x:v>
+        <x:v>636104</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>68.079</x:v>
+        <x:v>68.0252656468282</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -752,28 +752,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>2049881</x:v>
+        <x:v>2217052</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>68.825</x:v>
+        <x:v>68.6045704159143</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>1573111</x:v>
+        <x:v>1706663</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>69.217</x:v>
+        <x:v>68.9475485323904</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>3622992</x:v>
+        <x:v>3923715</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>3.52211099252976</x:v>
+        <x:v>3.46797097065641</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>476770</x:v>
+        <x:v>510389</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>67.532</x:v>
+        <x:v>67.4577038862683</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -781,28 +781,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>888334</x:v>
+        <x:v>939915</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>68.485</x:v>
+        <x:v>68.9543483003976</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>467553</x:v>
+        <x:v>570645</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>69.05</x:v>
+        <x:v>68.9111442113552</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>1355887</x:v>
+        <x:v>1510560</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.31813277736418</x:v>
+        <x:v>1.33510671122514</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>420781</x:v>
+        <x:v>369270</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>67.857</x:v>
+        <x:v>69.0211129912516</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -810,28 +810,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>899643</x:v>
+        <x:v>928840</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>69.096</x:v>
+        <x:v>68.3697489515416</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>523840</x:v>
+        <x:v>683356</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>69.205</x:v>
+        <x:v>67.8617184037501</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1423483</x:v>
+        <x:v>1612196</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.38384658922218</x:v>
+        <x:v>1.42493757243031</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>375803</x:v>
+        <x:v>245484</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>68.945</x:v>
+        <x:v>69.7839581179908</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -839,28 +839,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1149729</x:v>
+        <x:v>1403777</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>69.358</x:v>
+        <x:v>69.4564284340364</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>1024942</x:v>
+        <x:v>1280718</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>68.875</x:v>
+        <x:v>69.6654148989805</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>2174671</x:v>
+        <x:v>2684495</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>2.11411800915809</x:v>
+        <x:v>2.37268780501955</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>124787</x:v>
+        <x:v>123059</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>73.321</x:v>
+        <x:v>67.2814332901604</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -868,28 +868,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>1121287</x:v>
+        <x:v>181159</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>68.87</x:v>
+        <x:v>68.5112251975488</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>1004274</x:v>
+        <x:v>66156</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>68.971</x:v>
+        <x:v>69.3545463098869</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>2125561</x:v>
+        <x:v>247315</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>2.06637546077732</x:v>
+        <x:v>0.218589077088395</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>117013</x:v>
+        <x:v>115003</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>68.001</x:v>
+        <x:v>68.0261008833323</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -897,28 +897,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>173940</x:v>
+        <x:v>1209481</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>68.621</x:v>
+        <x:v>69.5179350297025</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>62968</x:v>
+        <x:v>1102354</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>69.544</x:v>
+        <x:v>68.6898876427486</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>236908</x:v>
+        <x:v>2311835</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.230311375520079</x:v>
+        <x:v>2.04331269446111</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>110972</x:v>
+        <x:v>107127</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>68.098</x:v>
+        <x:v>78.0386753584542</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -926,28 +926,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>208081</x:v>
+        <x:v>222169</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>69.047</x:v>
+        <x:v>68.8205346381516</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>99009</x:v>
+        <x:v>128045</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>69.563</x:v>
+        <x:v>68.6003949965367</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>307090</x:v>
+        <x:v>350214</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.298539181068014</x:v>
+        <x:v>0.309536239384732</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>109072</x:v>
+        <x:v>94124</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>68.579</x:v>
+        <x:v>69.1200095904547</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -955,28 +955,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>1285520</x:v>
+        <x:v>678696</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>69.813</x:v>
+        <x:v>69.2118715240413</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>1213383</x:v>
+        <x:v>590880</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>69.888</x:v>
+        <x:v>67.6194503646151</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>2498903</x:v>
+        <x:v>1269576</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>2.42932187693641</x:v>
+        <x:v>1.12211328117411</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>72137</x:v>
+        <x:v>87816</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>68.538</x:v>
+        <x:v>79.9266594292265</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -984,28 +984,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>177883</x:v>
+        <x:v>1179239</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>68.906</x:v>
+        <x:v>69.269960868154</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>123583</x:v>
+        <x:v>1095182</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>69.559</x:v>
+        <x:v>68.6759937733218</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>301466</x:v>
+        <x:v>2274421</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.29307177947784</x:v>
+        <x:v>2.01024437377621</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>54300</x:v>
+        <x:v>84057</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>67.42</x:v>
+        <x:v>77.0087817974343</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1013,28 +1013,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>1065349</x:v>
+        <x:v>1151150</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>70.032</x:v>
+        <x:v>68.774350902473</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>1013251</x:v>
+        <x:v>1073102</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>68.955</x:v>
+        <x:v>68.7531736381974</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>2078600</x:v>
+        <x:v>2224252</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2.02072207420617</x:v>
+        <x:v>1.965902561074</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>52098</x:v>
+        <x:v>78048</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>90.991</x:v>
+        <x:v>69.0655225487506</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1042,28 +1042,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>93351</x:v>
+        <x:v>659950</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>68.532</x:v>
+        <x:v>68.1981504313112</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>45756</x:v>
+        <x:v>599339</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>69.232</x:v>
+        <x:v>68.6846024914034</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>139107</x:v>
+        <x:v>1259289</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.135233611842874</x:v>
+        <x:v>1.11302112810613</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>47595</x:v>
+        <x:v>60611</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>67.86</x:v>
+        <x:v>63.3879725552894</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1071,28 +1071,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>101110</x:v>
+        <x:v>104110</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>69.496</x:v>
+        <x:v>68.2487794885076</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>54743</x:v>
+        <x:v>48203</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>69.171</x:v>
+        <x:v>69.0658874597188</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>155853</x:v>
+        <x:v>152313</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.151513325041496</x:v>
+        <x:v>0.134621669120614</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>46367</x:v>
+        <x:v>55907</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>69.88</x:v>
+        <x:v>67.5442692208077</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1100,28 +1100,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>98293</x:v>
+        <x:v>182222</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>69.514</x:v>
+        <x:v>68.8228368908522</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>62123</x:v>
+        <x:v>130391</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>69.515</x:v>
+        <x:v>69.3534056688841</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>160416</x:v>
+        <x:v>312613</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.155949269823851</x:v>
+        <x:v>0.27630263896583</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>36170</x:v>
+        <x:v>51831</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>69.513</x:v>
+        <x:v>67.4880875413053</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1129,28 +1129,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>554694</x:v>
+        <x:v>103590</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>68.721</x:v>
+        <x:v>69.3996094402538</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>524089</x:v>
+        <x:v>55899</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>69.155</x:v>
+        <x:v>69.1037422725708</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>1078783</x:v>
+        <x:v>159489</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>1.04874464609754</x:v>
+        <x:v>0.140964168431963</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>30605</x:v>
+        <x:v>47691</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>61.293</x:v>
+        <x:v>69.7463976981288</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1158,28 +1158,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>122505</x:v>
+        <x:v>105238</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>68.973</x:v>
+        <x:v>69.2830992382059</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>99017</x:v>
+        <x:v>65129</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>69.086</x:v>
+        <x:v>69.3386772646707</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>221522</x:v>
+        <x:v>170367</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.215353793573703</x:v>
+        <x:v>0.150578676167311</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>23488</x:v>
+        <x:v>40109</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>68.495</x:v>
+        <x:v>69.1928516307954</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1187,28 +1187,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>32832</x:v>
+        <x:v>1287509</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>68.162</x:v>
+        <x:v>68.7404337744898</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>15326</x:v>
+        <x:v>1261133</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>69.114</x:v>
+        <x:v>68.9837883230858</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>48158</x:v>
+        <x:v>2548642</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.0468170565041955</x:v>
+        <x:v>2.25261428788679</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>17506</x:v>
+        <x:v>26376</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>67.328</x:v>
+        <x:v>57.1047630156753</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1216,28 +1216,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>502786</x:v>
+        <x:v>135851</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>69.047</x:v>
+        <x:v>68.69563511605</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>485682</x:v>
+        <x:v>110522</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>69.13</x:v>
+        <x:v>68.702642401483</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>988468</x:v>
+        <x:v>246373</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.960944437239693</x:v>
+        <x:v>0.217756491476453</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>17104</x:v>
+        <x:v>25329</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>66.681</x:v>
+        <x:v>68.6650591280275</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1245,28 +1245,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>228811</x:v>
+        <x:v>33582</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>69.703</x:v>
+        <x:v>68.1066354464536</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>218947</x:v>
+        <x:v>15353</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>69.327</x:v>
+        <x:v>69.1096338811142</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>447758</x:v>
+        <x:v>48935</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.435290327384974</x:v>
+        <x:v>0.0432511432275462</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>9864</x:v>
+        <x:v>18229</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>78.045</x:v>
+        <x:v>67.2618806619156</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1274,28 +1274,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>995129</x:v>
+        <x:v>262002</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>69.222</x:v>
+        <x:v>69.1787635435209</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>987749</x:v>
+        <x:v>249533</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>69.496</x:v>
+        <x:v>68.7694821429788</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1982878</x:v>
+        <x:v>511535</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>1.92766542146531</x:v>
+        <x:v>0.452119618900641</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>7380</x:v>
+        <x:v>12469</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>32.439</x:v>
+        <x:v>77.3694136134126</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1303,28 +1303,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>176085</x:v>
+        <x:v>560853</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>71.572</x:v>
+        <x:v>68.7155173759684</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>169730</x:v>
+        <x:v>549765</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>71.704</x:v>
+        <x:v>68.7268673442048</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>345815</x:v>
+        <x:v>1110618</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.336185896320412</x:v>
+        <x:v>0.981618436478818</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>6355</x:v>
+        <x:v>11088</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>68.06</x:v>
+        <x:v>68.152763471975</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1332,28 +1332,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>1019</x:v>
+        <x:v>178470</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>70.031</x:v>
+        <x:v>71.4966604120252</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>120</x:v>
+        <x:v>171383</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>69.125</x:v>
+        <x:v>71.6421617857936</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1139</x:v>
+        <x:v>349853</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00110728492375677</x:v>
+        <x:v>0.309217169951706</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>899</x:v>
+        <x:v>7087</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>70.152</x:v>
+        <x:v>67.9780401297411</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1361,28 +1361,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>2620</x:v>
+        <x:v>1045574</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>70.295</x:v>
+        <x:v>69.0527259092262</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>2172</x:v>
+        <x:v>1041444</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>69.237</x:v>
+        <x:v>69.3061233978897</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>4792</x:v>
+        <x:v>2087018</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.00465856835350523</x:v>
+        <x:v>1.84460844868636</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>448</x:v>
+        <x:v>4130</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>75.429</x:v>
+        <x:v>5.15459172431262</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1390,28 +1390,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>309</x:v>
+        <x:v>1119</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>66.799</x:v>
+        <x:v>69.6512039225479</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>0</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>0</x:v>
+        <x:v>68.4780403343407</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>309</x:v>
+        <x:v>1267</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.000300395997753155</x:v>
+        <x:v>0.00111983648654953</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>309</x:v>
+        <x:v>971</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>66.799</x:v>
+        <x:v>69.8300177341386</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1419,28 +1419,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>150</x:v>
+        <x:v>8076</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>68.207</x:v>
+        <x:v>68.6890674834797</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>0</x:v>
+        <x:v>7384</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>0</x:v>
+        <x:v>70.2930504198581</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>150</x:v>
+        <x:v>15460</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.000145823299880172</x:v>
+        <x:v>0.0136643031429011</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>150</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>68.207</x:v>
+        <x:v>51.5737351103325</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1448,28 +1448,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>303</x:v>
+        <x:v>2623</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>69.485</x:v>
+        <x:v>70.2903161523363</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>312</x:v>
+        <x:v>2228</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>69.558</x:v>
+        <x:v>69.1516144922006</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>615</x:v>
+        <x:v>4851</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.000597875529508706</x:v>
+        <x:v>0.00428755074684432</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>-9</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>72</x:v>
+        <x:v>76.713170073304</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1477,28 +1477,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="C33" s="0">
+        <x:v>66.6592025146484</x:v>
+      </x:c>
+      <x:c r="D33" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C33" s="0">
+      <x:c r="E33" s="0">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D33" s="0">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="E33" s="0">
-        <x:v>70.527</x:v>
-      </x:c>
       <x:c r="F33" s="0">
-        <x:v>131</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.000127352348562017</x:v>
+        <x:v>0.000331443316855622</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>-131</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>70.527</x:v>
+        <x:v>66.6592025146484</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1506,28 +1506,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>6855</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>69.225</x:v>
+        <x:v>68.21033396403</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>7220</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>70.395</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>14075</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0136830863054228</x:v>
+        <x:v>0.000132577326742249</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>-365</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>92.359</x:v>
+        <x:v>68.21033396403</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1541,22 +1541,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>375</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>70.416</x:v>
+        <x:v>70.5297704798575</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>375</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.00036455824970043</x:v>
+        <x:v>0.00011578419868823</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-375</x:v>
+        <x:v>-131</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>70.416</x:v>
+        <x:v>70.5297704798575</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1564,28 +1564,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>276</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>70.38</x:v>
+        <x:v>69.4861396562935</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>2295</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>69.451</x:v>
+        <x:v>68.4992221238878</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>2571</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.00249941135994615</x:v>
+        <x:v>0.000665538180246088</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-2019</x:v>
+        <x:v>-147</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>69.323</x:v>
+        <x:v>66.4649635366842</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1593,28 +1593,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>1198233</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>68.958</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>1200775</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>69.163</x:v>
+        <x:v>70.4173325195312</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>2399008</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>2.33220841999288</x:v>
+        <x:v>0.000331443316855622</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-2542</x:v>
+        <x:v>-375</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>165.586</x:v>
+        <x:v>70.4173325195312</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1622,28 +1622,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>20617</x:v>
+        <x:v>26752</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>67.49</x:v>
+        <x:v>67.1084381393268</x:v>
       </x:c>
       <x:c r="D38" s="0">
         <x:v>27374</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>68.894</x:v>
+        <x:v>68.8943517766738</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>47991</x:v>
+        <x:v>54126</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.0466547065636623</x:v>
+        <x:v>0.047839202581673</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-6757</x:v>
+        <x:v>-622</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>73.179</x:v>
+        <x:v>145.705865645332</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1651,28 +1651,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>103311</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>69.839</x:v>
+        <x:v>70.3804345061814</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>125507</x:v>
+        <x:v>2295</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>68.897</x:v>
+        <x:v>69.4503927525872</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>228818</x:v>
+        <x:v>2571</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.222446638879875</x:v>
+        <x:v>0.00227237538036214</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-22196</x:v>
+        <x:v>-2019</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>64.512</x:v>
+        <x:v>69.32325480113</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1680,28 +1680,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>742086</x:v>
+        <x:v>106329</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>71.982</x:v>
+        <x:v>69.732156010164</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>787115</x:v>
+        <x:v>139289</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>70.834</x:v>
+        <x:v>68.653315205715</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>1529201</x:v>
+        <x:v>245618</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>1.48662090666706</x:v>
+        <x:v>0.217089185598517</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-45029</x:v>
+        <x:v>-32960</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>51.925</x:v>
+        <x:v>65.17297346129</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1709,28 +1709,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>533377</x:v>
+        <x:v>308868</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>70.213</x:v>
+        <x:v>69.7783865248195</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>582351</x:v>
+        <x:v>360641</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>67.643</x:v>
+        <x:v>69.6883723917882</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>1115728</x:v>
+        <x:v>669509</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>1.08466092485803</x:v>
+        <x:v>0.591744756332507</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-48974</x:v>
+        <x:v>-51773</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>39.648</x:v>
+        <x:v>69.1513649701377</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1738,28 +1738,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>3097022</x:v>
+        <x:v>3288504</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>69.726</x:v>
+        <x:v>69.4876126411709</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>3153522</x:v>
+        <x:v>3345004</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>69.773</x:v>
+        <x:v>69.5376944123484</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>6250544</x:v>
+        <x:v>6633508</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>6.0764996808414</x:v>
+        <x:v>5.86301838375547</x:v>
       </x:c>
       <x:c r="H42" s="0">
         <x:v>-56500</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>72.362</x:v>
+        <x:v>72.4526343210946</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1767,28 +1767,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>303227</x:v>
+        <x:v>745503</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>69.874</x:v>
+        <x:v>71.9540329007124</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>360017</x:v>
+        <x:v>806770</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>69.696</x:v>
+        <x:v>70.7089485898516</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>663244</x:v>
+        <x:v>1552273</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.644776191371499</x:v>
+        <x:v>1.37197469809447</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-56790</x:v>
+        <x:v>-61267</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>68.744</x:v>
+        <x:v>55.5586378352908</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1796,28 +1796,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>270242</x:v>
+        <x:v>276031</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>71.193</x:v>
+        <x:v>71.0739990320003</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>351287</x:v>
+        <x:v>358312</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>71.025</x:v>
+        <x:v>70.9237369315144</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>621529</x:v>
+        <x:v>634343</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.604222731674823</x:v>
+        <x:v>0.560663327851054</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-81045</x:v>
+        <x:v>-82281</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>70.462</x:v>
+        <x:v>70.4196473135076</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1825,28 +1825,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>1774326</x:v>
+        <x:v>564876</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>69.963</x:v>
+        <x:v>69.2374106518532</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>1872648</x:v>
+        <x:v>673410</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>69.773</x:v>
+        <x:v>69.2811018418282</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>3646974</x:v>
+        <x:v>1238286</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>3.54542522171461</x:v>
+        <x:v>1.09445765081568</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-98322</x:v>
+        <x:v>-108534</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>66.337</x:v>
+        <x:v>69.508496986468</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1854,28 +1854,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>538442</x:v>
+        <x:v>316345</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>69.435</x:v>
+        <x:v>72.1815321454019</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>672382</x:v>
+        <x:v>452245</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>69.287</x:v>
+        <x:v>71.120179598746</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>1210824</x:v>
+        <x:v>768590</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>1.17710900836073</x:v>
+        <x:v>0.679317383738832</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-133940</x:v>
+        <x:v>-135900</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>68.693</x:v>
+        <x:v>68.6495867262525</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1883,28 +1883,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>316345</x:v>
+        <x:v>1870935</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>72.182</x:v>
+        <x:v>69.7393639768848</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>452161</x:v>
+        <x:v>2111018</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>71.121</x:v>
+        <x:v>69.3017463386282</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>768506</x:v>
+        <x:v>3981953</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.747107205984744</x:v>
+        <x:v>3.51944455968851</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-135816</x:v>
+        <x:v>-240083</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>68.651</x:v>
+        <x:v>65.8914500826183</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1912,28 +1912,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>710802</x:v>
+        <x:v>1088701</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>68.384</x:v>
+        <x:v>67.3790171901174</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>1687975</x:v>
+        <x:v>1700787</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>69.068</x:v>
+        <x:v>69.0401738756271</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>2398777</x:v>
+        <x:v>2789488</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>2.33198385211106</x:v>
+        <x:v>2.46548574679721</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-977173</x:v>
+        <x:v>-612086</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>69.566</x:v>
+        <x:v>71.9948288500442</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1941,28 +1941,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>991505</x:v>
+        <x:v>1080623</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>69.911</x:v>
+        <x:v>69.5561186482853</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>2272562</x:v>
+        <x:v>2383991</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>68.895</x:v>
+        <x:v>68.7474592693983</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>3264067</x:v>
+        <x:v>3464614</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.17318013979983</x:v>
+        <x:v>3.06219508209179</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-1281057</x:v>
+        <x:v>-1303368</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>68.108</x:v>
+        <x:v>68.0769994115599</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1970,28 +1970,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>563138</x:v>
+        <x:v>3100735</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>68.89</x:v>
+        <x:v>70.3967032212652</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>2017456</x:v>
+        <x:v>4554532</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>69.546</x:v>
+        <x:v>69.1293813872399</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>2580594</x:v>
+        <x:v>7655267</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>2.50873821820649</x:v>
+        <x:v>6.76609889572102</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-1454318</x:v>
+        <x:v>-1453797</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>69.801</x:v>
+        <x:v>66.4263704668523</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1999,28 +1999,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>2999082</x:v>
+        <x:v>569413</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>70.555</x:v>
+        <x:v>68.8584017608334</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>4494718</x:v>
+        <x:v>2182408</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>69.177</x:v>
+        <x:v>69.2586449919141</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>7493800</x:v>
+        <x:v>2751821</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>7.28513763094689</x:v>
+        <x:v>2.43219381235454</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-1495636</x:v>
+        <x:v>-1612995</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>66.412</x:v>
+        <x:v>69.3999372457272</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2028,28 +2028,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>3991870</x:v>
+        <x:v>4259972</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>69.699</x:v>
+        <x:v>69.4530208719385</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>6470532</x:v>
+        <x:v>6757927</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>69.65</x:v>
+        <x:v>69.4679310939881</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>10462402</x:v>
+        <x:v>11017899</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>10.1710798954194</x:v>
+        <x:v>9.73815730490729</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-2478662</x:v>
+        <x:v>-2497955</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>69.57</x:v>
+        <x:v>69.4933587451849</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -40,24 +40,24 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>MIDAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARANTI BBVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
     <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
-    <x:t>MIDAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARANTI BBVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
@@ -67,130 +67,139 @@
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVEYT TURK</x:t>
+    <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
-    <x:t>TEB</x:t>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEO MENKUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
   </x:si>
   <x:si>
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
-    <x:t>GEDIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEO MENKUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
+    <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
     <x:t>TERA</x:t>
   </x:si>
   <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
-    <x:t>DENIZ</x:t>
+    <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
     <x:t>TRIVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -541,7 +550,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I52"/>
+  <x:dimension ref="A1:I55"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -578,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>3493619</x:v>
+        <x:v>3751037</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>68.7146353049048</x:v>
+        <x:v>68.1672107037962</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>1827470</x:v>
+        <x:v>2361629</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>68.5583352089914</x:v>
+        <x:v>68.0094174350196</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>5321089</x:v>
+        <x:v>6112666</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>4.70303836651723</x:v>
+        <x:v>4.01835509779697</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>1666149</x:v>
+        <x:v>1389408</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>68.8860687939137</x:v>
+        <x:v>68.4354178535661</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -607,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>2774219</x:v>
+        <x:v>5609687</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>68.7337186245993</x:v>
+        <x:v>68.0532057211187</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>1524304</x:v>
+        <x:v>4445747</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>68.6269856258401</x:v>
+        <x:v>68.3140408589217</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>4298523</x:v>
+        <x:v>10055434</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>3.7992445885338</x:v>
+        <x:v>6.61025884196209</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>1249915</x:v>
+        <x:v>1163940</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>68.8638823052822</x:v>
+        <x:v>67.0569283946395</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -636,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>4734856</x:v>
+        <x:v>2379348</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>68.3721498449583</x:v>
+        <x:v>68.1746726721599</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>3740184</x:v>
+        <x:v>1425515</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>68.6168689605209</x:v>
+        <x:v>68.0494956341753</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>8475040</x:v>
+        <x:v>3804863</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>7.49065431489084</x:v>
+        <x:v>2.50124751335491</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>994672</x:v>
+        <x:v>953833</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>67.4519525130527</x:v>
+        <x:v>68.3617512753352</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -665,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>1883228</x:v>
+        <x:v>3732641</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>68.631089535328</x:v>
+        <x:v>68.1698701201605</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>1028270</x:v>
+        <x:v>2967110</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>68.5675829636374</x:v>
+        <x:v>68.2283447065705</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>2911498</x:v>
+        <x:v>6699751</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.57332414436936</x:v>
+        <x:v>4.40429406494979</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>854958</x:v>
+        <x:v>765531</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>68.7074697814596</x:v>
+        <x:v>67.9432293569742</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -694,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>2933374</x:v>
+        <x:v>11432930</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>68.6241948054935</x:v>
+        <x:v>68.1433558078982</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>2260196</x:v>
+        <x:v>10677747</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>68.7314435788164</x:v>
+        <x:v>68.2043511497115</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>5193570</x:v>
+        <x:v>22110677</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>4.59033084565827</x:v>
+        <x:v>14.5351556323693</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>673178</x:v>
+        <x:v>755183</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>68.2641069112525</x:v>
+        <x:v>67.2809253399714</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -723,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>8364525</x:v>
+        <x:v>4052910</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>68.7192514519946</x:v>
+        <x:v>68.4213933901062</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>7728421</x:v>
+        <x:v>3480363</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>68.7763714182348</x:v>
+        <x:v>67.7957944159108</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>16092946</x:v>
+        <x:v>7533273</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>14.2237317339158</x:v>
+        <x:v>4.95223621945748</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>636104</x:v>
+        <x:v>572547</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>68.0252656468282</x:v>
+        <x:v>72.2242454225644</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -752,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>2217052</x:v>
+        <x:v>2713626</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>68.6045704159143</x:v>
+        <x:v>68.2273530852817</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>1706663</x:v>
+        <x:v>2172961</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>68.9475485323904</x:v>
+        <x:v>68.5369900669746</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>3923715</x:v>
+        <x:v>4886587</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>3.46797097065641</x:v>
+        <x:v>3.21235313401361</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>510389</x:v>
+        <x:v>540665</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>67.4577038862683</x:v>
+        <x:v>66.9829058113199</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -781,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>939915</x:v>
+        <x:v>1116230</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>68.9543483003976</x:v>
+        <x:v>68.5397203239104</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>570645</x:v>
+        <x:v>741434</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>68.9111442113552</x:v>
+        <x:v>68.4082500262654</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>1510560</x:v>
+        <x:v>1857664</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.33510671122514</x:v>
+        <x:v>1.2211944189972</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>369270</x:v>
+        <x:v>374796</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>69.0211129912516</x:v>
+        <x:v>68.7997992699614</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -810,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>928840</x:v>
+        <x:v>1089751</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>68.3697489515416</x:v>
+        <x:v>68.0850360505162</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>683356</x:v>
+        <x:v>882589</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>67.8617184037501</x:v>
+        <x:v>67.5690152954916</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1612196</x:v>
+        <x:v>1972340</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.42493757243031</x:v>
+        <x:v>1.29658032903955</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>245484</x:v>
+        <x:v>207162</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>69.7839581179908</x:v>
+        <x:v>70.283480949467</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -839,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1403777</x:v>
+        <x:v>1046762</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>69.4564284340364</x:v>
+        <x:v>67.5668269343284</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>1280718</x:v>
+        <x:v>872679</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>69.6654148989805</x:v>
+        <x:v>68.0836136439986</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>2684495</x:v>
+        <x:v>1919441</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>2.37268780501955</x:v>
+        <x:v>1.26180549162518</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>123059</x:v>
+        <x:v>174083</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>67.2814332901604</x:v>
+        <x:v>64.9761724246505</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -868,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>181159</x:v>
+        <x:v>309565</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>68.5112251975488</x:v>
+        <x:v>68.2391628793843</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>66156</x:v>
+        <x:v>165662</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>69.3545463098869</x:v>
+        <x:v>68.2030654536768</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>247315</x:v>
+        <x:v>475227</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.218589077088395</x:v>
+        <x:v>0.31240555889374</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>115003</x:v>
+        <x:v>143903</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>68.0261008833323</x:v>
+        <x:v>68.2807184531912</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -897,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>1209481</x:v>
+        <x:v>221777</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>69.5179350297025</x:v>
+        <x:v>68.0812584655088</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>1102354</x:v>
+        <x:v>108075</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>68.6898876427486</x:v>
+        <x:v>68.451265516526</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>2311835</x:v>
+        <x:v>329852</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>2.04331269446111</x:v>
+        <x:v>0.21683868637981</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>107127</x:v>
+        <x:v>113702</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>78.0386753584542</x:v>
+        <x:v>67.729562699043</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -926,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>222169</x:v>
+        <x:v>1583204</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>68.8205346381516</x:v>
+        <x:v>68.3239584633434</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>128045</x:v>
+        <x:v>1480229</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>68.6003949965367</x:v>
+        <x:v>68.6688517128632</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>350214</x:v>
+        <x:v>3063433</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.309536239384732</x:v>
+        <x:v>2.01384495935317</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>94124</x:v>
+        <x:v>102975</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>69.1200095904547</x:v>
+        <x:v>63.366240669282</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -955,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>678696</x:v>
+        <x:v>1816607</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>69.2118715240413</x:v>
+        <x:v>68.7614699063414</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>590880</x:v>
+        <x:v>1716596</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>67.6194503646151</x:v>
+        <x:v>68.9534463140594</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>1269576</x:v>
+        <x:v>3533203</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>1.12211328117411</x:v>
+        <x:v>2.32266318601435</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>87816</x:v>
+        <x:v>100011</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>79.9266594292265</x:v>
+        <x:v>65.4663730311657</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -984,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>1179239</x:v>
+        <x:v>1369453</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>69.269960868154</x:v>
+        <x:v>68.8780548705396</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>1095182</x:v>
+        <x:v>1286679</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>68.6759937733218</x:v>
+        <x:v>68.3521864793114</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>2274421</x:v>
+        <x:v>2656132</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>2.01024437377621</x:v>
+        <x:v>1.74609271349386</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>84057</x:v>
+        <x:v>82774</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>77.0087817974343</x:v>
+        <x:v>77.0524069105179</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1013,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>1151150</x:v>
+        <x:v>1516901</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>68.774350902473</x:v>
+        <x:v>68.8401557341702</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>1073102</x:v>
+        <x:v>1434919</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>68.7531736381974</x:v>
+        <x:v>68.2036255566179</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>2224252</x:v>
+        <x:v>2951820</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>1.965902561074</x:v>
+        <x:v>1.94047260962386</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>78048</x:v>
+        <x:v>81982</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>69.0655225487506</x:v>
+        <x:v>79.9812506799283</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1042,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>659950</x:v>
+        <x:v>1815147</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>68.1981504313112</x:v>
+        <x:v>68.100770574617</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>599339</x:v>
+        <x:v>1744450</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>68.6846024914034</x:v>
+        <x:v>67.9954862417575</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1259289</x:v>
+        <x:v>3559597</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>1.11302112810613</x:v>
+        <x:v>2.34001412003417</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>60611</x:v>
+        <x:v>70697</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>63.3879725552894</x:v>
+        <x:v>70.6986637590043</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1071,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>104110</x:v>
+        <x:v>119947</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>68.2487794885076</x:v>
+        <x:v>68.0782770404941</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>48203</x:v>
+        <x:v>55464</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>69.0658874597188</x:v>
+        <x:v>68.7706209793762</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>152313</x:v>
+        <x:v>175411</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.134621669120614</x:v>
+        <x:v>0.115311990882483</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>55907</x:v>
+        <x:v>64483</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>67.5442692208077</x:v>
+        <x:v>67.4827687014566</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1100,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>182222</x:v>
+        <x:v>152364</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>68.8228368908522</x:v>
+        <x:v>68.2523923081589</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>130391</x:v>
+        <x:v>91685</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>69.3534056688841</x:v>
+        <x:v>68.3513941142657</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>312613</x:v>
+        <x:v>244049</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.27630263896583</x:v>
+        <x:v>0.160433359725896</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>51831</x:v>
+        <x:v>60679</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>67.4880875413053</x:v>
+        <x:v>68.1028021601191</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1129,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>103590</x:v>
+        <x:v>230116</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>69.3996094402538</x:v>
+        <x:v>68.4766499738947</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>55899</x:v>
+        <x:v>173191</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>69.1037422725708</x:v>
+        <x:v>68.8782312814204</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>159489</x:v>
+        <x:v>403307</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.140964168431963</x:v>
+        <x:v>0.265126663133108</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>47691</x:v>
+        <x:v>56925</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>69.7463976981288</x:v>
+        <x:v>67.2548622140059</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1158,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>105238</x:v>
+        <x:v>149748</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>69.2830992382059</x:v>
+        <x:v>68.4697207378444</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>65129</x:v>
+        <x:v>94169</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>69.3386772646707</x:v>
+        <x:v>68.2862315256151</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>170367</x:v>
+        <x:v>243917</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.150578676167311</x:v>
+        <x:v>0.160346585334344</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>40109</x:v>
+        <x:v>55579</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>69.1928516307954</x:v>
+        <x:v>68.7806114632339</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1187,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>1287509</x:v>
+        <x:v>1695808</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>68.7404337744898</x:v>
+        <x:v>68.1938501440202</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>1261133</x:v>
+        <x:v>1658606</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>68.9837883230858</x:v>
+        <x:v>68.4111787561788</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>2548642</x:v>
+        <x:v>3354414</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>2.25261428788679</x:v>
+        <x:v>2.20513055956624</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>26376</x:v>
+        <x:v>37202</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>57.1047630156753</x:v>
+        <x:v>58.5045178474249</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1216,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>135851</x:v>
+        <x:v>189725</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>68.69563511605</x:v>
+        <x:v>68.0368261445302</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>110522</x:v>
+        <x:v>164124</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>68.702642401483</x:v>
+        <x:v>68.0468393896044</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>246373</x:v>
+        <x:v>353849</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.217756491476453</x:v>
+        <x:v>0.23261387633487</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>25329</x:v>
+        <x:v>25601</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>68.6650591280275</x:v>
+        <x:v>67.9726327991705</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1245,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>33582</x:v>
+        <x:v>283547</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>68.1066354464536</x:v>
+        <x:v>69.019695808431</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>15353</x:v>
+        <x:v>260992</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>69.1096338811142</x:v>
+        <x:v>68.6934342082076</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>48935</x:v>
+        <x:v>544539</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.0432511432275462</x:v>
+        <x:v>0.35797000303947</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>18229</x:v>
+        <x:v>22555</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>67.2618806619156</x:v>
+        <x:v>72.7949858800558</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1274,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>262002</x:v>
+        <x:v>212349</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>69.1787635435209</x:v>
+        <x:v>70.8248428138784</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>249533</x:v>
+        <x:v>196931</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>68.7694821429788</x:v>
+        <x:v>71.1877024656225</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>511535</x:v>
+        <x:v>409280</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.452119618900641</x:v>
+        <x:v>0.269053204350826</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>12469</x:v>
+        <x:v>15418</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>77.3694136134126</x:v>
+        <x:v>66.1901097695394</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1303,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>560853</x:v>
+        <x:v>45507</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>68.7155173759684</x:v>
+        <x:v>67.9143357484073</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>549765</x:v>
+        <x:v>30598</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>68.7268673442048</x:v>
+        <x:v>68.3780845257104</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>1110618</x:v>
+        <x:v>76105</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.981618436478818</x:v>
+        <x:v>0.0500300384018755</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>11088</x:v>
+        <x:v>14909</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>68.152763471975</x:v>
+        <x:v>66.9625760671462</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1332,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>178470</x:v>
+        <x:v>804476</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>71.4966604120252</x:v>
+        <x:v>68.1164387832911</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>171383</x:v>
+        <x:v>799405</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>71.6421617857936</x:v>
+        <x:v>68.1268663088741</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>349853</x:v>
+        <x:v>1603881</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.309217169951706</x:v>
+        <x:v>1.05436210527611</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>7087</x:v>
+        <x:v>5071</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>67.9780401297411</x:v>
+        <x:v>66.4726178231876</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1361,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>1045574</x:v>
+        <x:v>9214</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>69.0527259092262</x:v>
+        <x:v>68.4424579886156</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1041444</x:v>
+        <x:v>7532</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>69.3061233978897</x:v>
+        <x:v>70.2336476579728</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>2087018</x:v>
+        <x:v>16746</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>1.84460844868636</x:v>
+        <x:v>0.0110085148554997</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>4130</x:v>
+        <x:v>1682</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>5.15459172431262</x:v>
+        <x:v>60.421506389568</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1390,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>1119</x:v>
+        <x:v>1619</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>69.6512039225479</x:v>
+        <x:v>68.3907951934607</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>148</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>68.4780403343407</x:v>
+        <x:v>68.091761675748</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1267</x:v>
+        <x:v>1795</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00111983648654953</x:v>
+        <x:v>0.00118000024875326</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>971</x:v>
+        <x:v>1443</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>69.8300177341386</x:v>
+        <x:v>68.4272677500216</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1419,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>8076</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>68.6890674834797</x:v>
+        <x:v>66.0004500274658</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>7384</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>70.2930504198581</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>15460</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.0136643031429011</x:v>
+        <x:v>0.000657381754180087</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>692</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>51.5737351103325</x:v>
+        <x:v>66.0004500274658</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1448,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>2623</x:v>
+        <x:v>5978</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>70.2903161523363</x:v>
+        <x:v>66.9964049598691</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>2228</x:v>
+        <x:v>5578</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>69.1516144922006</x:v>
+        <x:v>67.1205628067843</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>4851</x:v>
+        <x:v>11556</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00428755074684432</x:v>
+        <x:v>0.00759670355130508</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>395</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>76.713170073304</x:v>
+        <x:v>65.2650237846374</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1492,7 +1501,7 @@
         <x:v>375</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.000331443316855622</x:v>
+        <x:v>0.000246518157817533</x:v>
       </x:c>
       <x:c r="H33" s="0">
         <x:v>375</x:v>
@@ -1506,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>150</x:v>
+        <x:v>2683</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>68.21033396403</x:v>
+        <x:v>70.2146847981194</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>0</x:v>
+        <x:v>2323</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>0</x:v>
+        <x:v>69.0449191556118</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>150</x:v>
+        <x:v>5006</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.000132577326742249</x:v>
+        <x:v>0.00329085306142551</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>150</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>68.21033396403</x:v>
+        <x:v>77.7629225413004</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1535,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>0</x:v>
+        <x:v>1658</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>0</x:v>
+        <x:v>67.2881778077424</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>131</x:v>
+        <x:v>1458</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>70.5297704798575</x:v>
+        <x:v>67.6160486532664</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>131</x:v>
+        <x:v>3116</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.00011578419868823</x:v>
+        <x:v>0.00204840154602515</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>-131</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>70.5297704798575</x:v>
+        <x:v>64.8979993438721</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1564,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>303</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>69.4861396562935</x:v>
+        <x:v>66.5999984741211</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>450</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>68.4992221238878</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>753</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.000665538180246088</x:v>
+        <x:v>6.57381754180087E-05</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>-147</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>66.4649635366842</x:v>
+        <x:v>66.5999984741211</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1599,22 +1608,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>375</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>70.4173325195312</x:v>
+        <x:v>70.5297704798575</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>375</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.000331443316855622</x:v>
+        <x:v>8.61170097975914E-05</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-375</x:v>
+        <x:v>-131</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>70.4173325195312</x:v>
+        <x:v>70.5297704798575</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1622,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>26752</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>67.1084381393268</x:v>
+        <x:v>69.4861396562935</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>27374</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>68.8943517766738</x:v>
+        <x:v>67.7234539762701</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>54126</x:v>
+        <x:v>966</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.047839202581673</x:v>
+        <x:v>0.000635030774537964</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-622</x:v>
+        <x:v>-360</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>145.705865645332</x:v>
+        <x:v>66.2398601955838</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1651,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>276</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>70.3804345061814</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>2295</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>69.4503927525872</x:v>
+        <x:v>70.4173325195312</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>2571</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.00227237538036214</x:v>
+        <x:v>0.000246518157817533</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-2019</x:v>
+        <x:v>-375</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>69.32325480113</x:v>
+        <x:v>70.4173325195312</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1680,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>106329</x:v>
+        <x:v>48648</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>69.732156010164</x:v>
+        <x:v>66.9226460518795</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>139289</x:v>
+        <x:v>49693</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>68.653315205715</x:v>
+        <x:v>68.0605425603304</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>245618</x:v>
+        <x:v>98341</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.217089185598517</x:v>
+        <x:v>0.0646475790878239</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-32960</x:v>
+        <x:v>-1045</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>65.17297346129</x:v>
+        <x:v>121.033163941306</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1709,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>308868</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>69.7783865248195</x:v>
+        <x:v>70.3804345061814</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>360641</x:v>
+        <x:v>2297</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>69.6883723917882</x:v>
+        <x:v>69.4469966797088</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>669509</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.591744756332507</x:v>
+        <x:v>0.00169144325350536</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-51773</x:v>
+        <x:v>-2021</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>69.1513649701377</x:v>
+        <x:v>69.3195207568456</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1738,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>3288504</x:v>
+        <x:v>807602</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>69.4876126411709</x:v>
+        <x:v>71.5237277324361</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>3345004</x:v>
+        <x:v>816787</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>69.5376944123484</x:v>
+        <x:v>70.6641325197893</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>6633508</x:v>
+        <x:v>1624389</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>5.86301838375547</x:v>
+        <x:v>1.06784369029084</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-56500</x:v>
+        <x:v>-9185</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>72.4526343210946</x:v>
+        <x:v>-4.91679430916443</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1767,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>745503</x:v>
+        <x:v>222794</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>71.9540329007124</x:v>
+        <x:v>67.9521305260894</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>806770</x:v>
+        <x:v>240343</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>70.7089485898516</x:v>
+        <x:v>67.7218298195016</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>1552273</x:v>
+        <x:v>463137</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>1.37197469809447</x:v>
+        <x:v>0.304457813485703</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-61267</x:v>
+        <x:v>-17549</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>55.5586378352908</x:v>
+        <x:v>64.7980383998465</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1796,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>276031</x:v>
+        <x:v>4530573</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>71.0739990320003</x:v>
+        <x:v>68.8339301465601</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>358312</x:v>
+        <x:v>4569273</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>70.9237369315144</x:v>
+        <x:v>68.8520994052951</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>634343</x:v>
+        <x:v>9099846</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.560663327851054</x:v>
+        <x:v>5.98207272624865</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-82281</x:v>
+        <x:v>-38700</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>70.4196473135076</x:v>
+        <x:v>70.9791576237642</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1825,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>564876</x:v>
+        <x:v>447859</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>69.2374106518532</x:v>
+        <x:v>68.8198029471785</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>673410</x:v>
+        <x:v>505298</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>69.2811018418282</x:v>
+        <x:v>68.8154162679111</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>1238286</x:v>
+        <x:v>953157</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>1.09445765081568</x:v>
+        <x:v>0.626588020669029</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-108534</x:v>
+        <x:v>-57439</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>69.508496986468</x:v>
+        <x:v>68.7812127861302</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1854,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>316345</x:v>
+        <x:v>306163</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>72.1815321454019</x:v>
+        <x:v>70.6109671670944</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>452245</x:v>
+        <x:v>380001</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>71.120179598746</x:v>
+        <x:v>70.7078232329156</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>768590</x:v>
+        <x:v>686164</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.679317383738832</x:v>
+        <x:v>0.451071693975225</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-135900</x:v>
+        <x:v>-73838</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>68.6495867262525</x:v>
+        <x:v>71.1094286891853</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1883,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>1870935</x:v>
+        <x:v>745035</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>69.7393639768848</x:v>
+        <x:v>68.906201880464</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>2111018</x:v>
+        <x:v>833700</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>69.3017463386282</x:v>
+        <x:v>67.2249847089528</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>3981953</x:v>
+        <x:v>1578735</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>3.51944455968851</x:v>
+        <x:v>1.0378315836855</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-240083</x:v>
+        <x:v>-88665</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>65.8914500826183</x:v>
+        <x:v>53.0980390666268</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1912,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>1088701</x:v>
+        <x:v>322345</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>67.3790171901174</x:v>
+        <x:v>72.0709597656475</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>1700787</x:v>
+        <x:v>458382</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>69.0401738756271</x:v>
+        <x:v>71.064415085865</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>2789488</x:v>
+        <x:v>780727</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>2.46548574679721</x:v>
+        <x:v>0.513235684795757</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-612086</x:v>
+        <x:v>-136037</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>71.9948288500442</x:v>
+        <x:v>68.6793680412779</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1941,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>1080623</x:v>
+        <x:v>594475</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>69.5561186482853</x:v>
+        <x:v>69.1271236222775</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>2383991</x:v>
+        <x:v>756162</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>68.7474592693983</x:v>
+        <x:v>69.0532244117749</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>3464614</x:v>
+        <x:v>1350637</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>3.06219508209179</x:v>
+        <x:v>0.88788412032053</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-1303368</x:v>
+        <x:v>-161687</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>68.0769994115599</x:v>
+        <x:v>68.7815189984548</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1970,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>3100735</x:v>
+        <x:v>2386761</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>70.3967032212652</x:v>
+        <x:v>69.007942576596</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>4554532</x:v>
+        <x:v>2695075</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>69.1293813872399</x:v>
+        <x:v>68.6278099989786</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>7655267</x:v>
+        <x:v>5081836</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>6.76609889572102</x:v>
+        <x:v>3.34070626413552</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-1453797</x:v>
+        <x:v>-308314</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>66.4263704668523</x:v>
+        <x:v>65.6850775538523</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -1999,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>569413</x:v>
+        <x:v>1581489</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>68.8584017608334</x:v>
+        <x:v>66.8743808647411</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2182408</x:v>
+        <x:v>2095004</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>69.2586449919141</x:v>
+        <x:v>68.8146102346548</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>2751821</x:v>
+        <x:v>3676493</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>2.43219381235454</x:v>
+        <x:v>2.41685941757081</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-1612995</x:v>
+        <x:v>-513515</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>69.3999372457272</x:v>
+        <x:v>74.7899983070489</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2028,28 +2037,115 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>4259972</x:v>
+        <x:v>4054906</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>69.4530208719385</x:v>
+        <x:v>69.5783157705294</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>6757927</x:v>
+        <x:v>5072738</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>69.4679310939881</x:v>
+        <x:v>68.9223376944735</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>11017899</x:v>
+        <x:v>9127644</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>9.73815730490729</x:v>
+        <x:v>6.00034662425134</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-2497955</x:v>
+        <x:v>-1017832</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>69.4933587451849</x:v>
+        <x:v>66.3090091329156</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:9">
+      <x:c r="A53" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B53" s="0">
+        <x:v>1398152</x:v>
+      </x:c>
+      <x:c r="C53" s="0">
+        <x:v>68.9102620453309</x:v>
+      </x:c>
+      <x:c r="D53" s="0">
+        <x:v>2679257</x:v>
+      </x:c>
+      <x:c r="E53" s="0">
+        <x:v>68.531674656392</x:v>
+      </x:c>
+      <x:c r="F53" s="0">
+        <x:v>4077409</x:v>
+      </x:c>
+      <x:c r="G53" s="0">
+        <x:v>2.68041428092967</x:v>
+      </x:c>
+      <x:c r="H53" s="0">
+        <x:v>-1281105</x:v>
+      </x:c>
+      <x:c r="I53" s="0">
+        <x:v>68.1184979729666</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:9">
+      <x:c r="A54" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B54" s="0">
+        <x:v>8450065</x:v>
+      </x:c>
+      <x:c r="C54" s="0">
+        <x:v>68.4250194290346</x:v>
+      </x:c>
+      <x:c r="D54" s="0">
+        <x:v>10230517</x:v>
+      </x:c>
+      <x:c r="E54" s="0">
+        <x:v>68.5363157438372</x:v>
+      </x:c>
+      <x:c r="F54" s="0">
+        <x:v>18680582</x:v>
+      </x:c>
+      <x:c r="G54" s="0">
+        <x:v>12.280273764265</x:v>
+      </x:c>
+      <x:c r="H54" s="0">
+        <x:v>-1780452</x:v>
+      </x:c>
+      <x:c r="I54" s="0">
+        <x:v>69.0645305422941</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:9">
+      <x:c r="A55" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B55" s="0">
+        <x:v>698070</x:v>
+      </x:c>
+      <x:c r="C55" s="0">
+        <x:v>68.446936458425</x:v>
+      </x:c>
+      <x:c r="D55" s="0">
+        <x:v>3166994</x:v>
+      </x:c>
+      <x:c r="E55" s="0">
+        <x:v>68.2650020480506</x:v>
+      </x:c>
+      <x:c r="F55" s="0">
+        <x:v>3865064</x:v>
+      </x:c>
+      <x:c r="G55" s="0">
+        <x:v>2.5408225523383</x:v>
+      </x:c>
+      <x:c r="H55" s="0">
+        <x:v>-2468924</x:v>
+      </x:c>
+      <x:c r="I55" s="0">
+        <x:v>68.2135614391659</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -40,12 +40,12 @@
     <x:t>Maliyet</x:t>
   </x:si>
   <x:si>
+    <x:t>IS</x:t>
+  </x:si>
+  <x:si>
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
-    <x:t>IS</x:t>
-  </x:si>
-  <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
@@ -55,139 +55,139 @@
     <x:t>AK</x:t>
   </x:si>
   <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PHILLIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
     <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHILLIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEO MENKUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEO MENKUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
     <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>DENIZ</x:t>
@@ -587,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>3751037</x:v>
+        <x:v>7216086</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>68.1672107037962</x:v>
+        <x:v>67.299</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>2361629</x:v>
+        <x:v>5300910</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>68.0094174350196</x:v>
+        <x:v>67.745</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>6112666</x:v>
+        <x:v>12516996</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>4.01835509779697</x:v>
+        <x:v>6.84341359310897</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>1389408</x:v>
+        <x:v>1915176</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>68.4354178535661</x:v>
+        <x:v>66.066</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>5609687</x:v>
+        <x:v>4692191</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>68.0532057211187</x:v>
+        <x:v>67.451</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>4445747</x:v>
+        <x:v>2927996</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>68.3140408589217</x:v>
+        <x:v>67.399</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>10055434</x:v>
+        <x:v>7620187</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>6.61025884196209</x:v>
+        <x:v>4.16618262863008</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>1163940</x:v>
+        <x:v>1764195</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>67.0569283946395</x:v>
+        <x:v>67.538</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>2379348</x:v>
+        <x:v>2955319</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>68.1746726721599</x:v>
+        <x:v>67.429</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>1425515</x:v>
+        <x:v>1734484</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>68.0494956341753</x:v>
+        <x:v>67.364</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>3804863</x:v>
+        <x:v>4689803</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>2.50124751335491</x:v>
+        <x:v>2.56405463413132</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>953833</x:v>
+        <x:v>1220835</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>68.3617512753352</x:v>
+        <x:v>67.522</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>3732641</x:v>
+        <x:v>4484700</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>68.1698701201605</x:v>
+        <x:v>67.57</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>2967110</x:v>
+        <x:v>3428120</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>68.2283447065705</x:v>
+        <x:v>67.758</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>6699751</x:v>
+        <x:v>7912820</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>4.40429406494979</x:v>
+        <x:v>4.32617378385553</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>765531</x:v>
+        <x:v>1056580</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>67.9432293569742</x:v>
+        <x:v>66.96</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>11432930</x:v>
+        <x:v>13464241</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>68.1433558078982</x:v>
+        <x:v>67.601</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>10677747</x:v>
+        <x:v>12545627</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>68.2043511497115</x:v>
+        <x:v>67.677</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>22110677</x:v>
+        <x:v>26009868</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>14.5351556323693</x:v>
+        <x:v>14.2203675886906</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>755183</x:v>
+        <x:v>918614</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>67.2809253399714</x:v>
+        <x:v>66.558</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>4052910</x:v>
+        <x:v>3294710</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>68.4213933901062</x:v>
+        <x:v>67.521</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>3480363</x:v>
+        <x:v>2576743</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>67.7957944159108</x:v>
+        <x:v>67.882</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>7533273</x:v>
+        <x:v>5871453</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>4.95223621945748</x:v>
+        <x:v>3.21009779594884</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>572547</x:v>
+        <x:v>717967</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>72.2242454225644</x:v>
+        <x:v>66.223</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>2713626</x:v>
+        <x:v>1290722</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>68.2273530852817</x:v>
+        <x:v>67.91</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>2172961</x:v>
+        <x:v>864311</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>68.5369900669746</x:v>
+        <x:v>67.784</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>4886587</x:v>
+        <x:v>2155033</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>3.21235313401361</x:v>
+        <x:v>1.17822056712317</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>540665</x:v>
+        <x:v>426411</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>66.9829058113199</x:v>
+        <x:v>68.165</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>1116230</x:v>
+        <x:v>1319345</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>68.5397203239104</x:v>
+        <x:v>67.458</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>741434</x:v>
+        <x:v>1011501</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>68.4082500262654</x:v>
+        <x:v>67.176</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>1857664</x:v>
+        <x:v>2330846</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.2211944189972</x:v>
+        <x:v>1.2743427576268</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>374796</x:v>
+        <x:v>307844</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>68.7997992699614</x:v>
+        <x:v>68.382</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>1089751</x:v>
+        <x:v>1933416</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>68.0850360505162</x:v>
+        <x:v>67.635</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>882589</x:v>
+        <x:v>1650303</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>67.5690152954916</x:v>
+        <x:v>68.219</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1972340</x:v>
+        <x:v>3583719</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.29658032903955</x:v>
+        <x:v>1.95932564957941</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>207162</x:v>
+        <x:v>283113</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>70.283480949467</x:v>
+        <x:v>64.229</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1046762</x:v>
+        <x:v>1160490</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>67.5668269343284</x:v>
+        <x:v>67.279</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>872679</x:v>
+        <x:v>945437</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>68.0836136439986</x:v>
+        <x:v>67.816</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>1919441</x:v>
+        <x:v>2105927</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>1.26180549162518</x:v>
+        <x:v>1.15137285798407</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>174083</x:v>
+        <x:v>215053</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>64.9761724246505</x:v>
+        <x:v>64.915</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>309565</x:v>
+        <x:v>2335124</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>68.2391628793843</x:v>
+        <x:v>67.802</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>165662</x:v>
+        <x:v>2137896</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>68.2030654536768</x:v>
+        <x:v>68.114</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>475227</x:v>
+        <x:v>4473020</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.31240555889374</x:v>
+        <x:v>2.44553292740912</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>143903</x:v>
+        <x:v>197228</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>68.2807184531912</x:v>
+        <x:v>64.42</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>221777</x:v>
+        <x:v>287399</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>68.0812584655088</x:v>
+        <x:v>67.11</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>108075</x:v>
+        <x:v>118969</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>68.451265516526</x:v>
+        <x:v>68.129</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>329852</x:v>
+        <x:v>406368</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.21683868637981</x:v>
+        <x:v>0.22217345879191</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>113702</x:v>
+        <x:v>168430</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>67.729562699043</x:v>
+        <x:v>66.39</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>1583204</x:v>
+        <x:v>375598</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>68.3239584633434</x:v>
+        <x:v>67.485</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>1480229</x:v>
+        <x:v>222809</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>68.6688517128632</x:v>
+        <x:v>67.375</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>3063433</x:v>
+        <x:v>598407</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>2.01384495935317</x:v>
+        <x:v>0.327166885569953</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>102975</x:v>
+        <x:v>152789</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>63.366240669282</x:v>
+        <x:v>67.646</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>1816607</x:v>
+        <x:v>2007524</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>68.7614699063414</x:v>
+        <x:v>67.612</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>1716596</x:v>
+        <x:v>1869019</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>68.9534463140594</x:v>
+        <x:v>67.264</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>3533203</x:v>
+        <x:v>3876543</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>2.32266318601435</x:v>
+        <x:v>2.11942123017946</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>100011</x:v>
+        <x:v>138505</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>65.4663730311657</x:v>
+        <x:v>72.315</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>1369453</x:v>
+        <x:v>4590103</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>68.8780548705396</x:v>
+        <x:v>67.987</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>1286679</x:v>
+        <x:v>4501802</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>68.3521864793114</x:v>
+        <x:v>67.141</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>2656132</x:v>
+        <x:v>9091905</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>1.74609271349386</x:v>
+        <x:v>4.9708145839669</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>82774</x:v>
+        <x:v>88301</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>77.0524069105179</x:v>
+        <x:v>111.126</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>1516901</x:v>
+        <x:v>2308284</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>68.8401557341702</x:v>
+        <x:v>67.305</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>1434919</x:v>
+        <x:v>2227497</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>68.2036255566179</x:v>
+        <x:v>67.247</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>2951820</x:v>
+        <x:v>4535781</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>1.94047260962386</x:v>
+        <x:v>2.47984623073822</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>81982</x:v>
+        <x:v>80787</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>79.9812506799283</x:v>
+        <x:v>68.909</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>1815147</x:v>
+        <x:v>2011427</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>68.100770574617</x:v>
+        <x:v>67.598</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>1744450</x:v>
+        <x:v>1931356</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>67.9954862417575</x:v>
+        <x:v>67.842</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>3559597</x:v>
+        <x:v>3942783</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>2.34001412003417</x:v>
+        <x:v>2.15563660616964</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>70697</x:v>
+        <x:v>80071</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>70.6986637590043</x:v>
+        <x:v>61.7</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>119947</x:v>
+        <x:v>155037</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>68.0782770404941</x:v>
+        <x:v>67.266</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>55464</x:v>
+        <x:v>77068</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>68.7706209793762</x:v>
+        <x:v>67.318</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>175411</x:v>
+        <x:v>232105</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.115311990882483</x:v>
+        <x:v>0.126898699338768</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>64483</x:v>
+        <x:v>77969</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>67.4827687014566</x:v>
+        <x:v>67.215</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>152364</x:v>
+        <x:v>184593</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>68.2523923081589</x:v>
+        <x:v>67.735</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>91685</x:v>
+        <x:v>108419</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>68.3513941142657</x:v>
+        <x:v>67.731</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>244049</x:v>
+        <x:v>293012</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.160433359725896</x:v>
+        <x:v>0.160198365785532</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>60679</x:v>
+        <x:v>76174</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>68.1028021601191</x:v>
+        <x:v>67.741</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>230116</x:v>
+        <x:v>191274</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>68.4766499738947</x:v>
+        <x:v>67.496</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>173191</x:v>
+        <x:v>119752</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>68.8782312814204</x:v>
+        <x:v>67.448</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>403307</x:v>
+        <x:v>311026</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.265126663133108</x:v>
+        <x:v>0.170047154781412</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>56925</x:v>
+        <x:v>71522</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>67.2548622140059</x:v>
+        <x:v>67.576</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>149748</x:v>
+        <x:v>342639</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>68.4697207378444</x:v>
+        <x:v>68.093</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>94169</x:v>
+        <x:v>276433</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>68.2862315256151</x:v>
+        <x:v>68.431</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>243917</x:v>
+        <x:v>619072</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.160346585334344</x:v>
+        <x:v>0.338465055027033</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>55579</x:v>
+        <x:v>66206</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>68.7806114632339</x:v>
+        <x:v>66.681</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>1695808</x:v>
+        <x:v>253338</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>68.1938501440202</x:v>
+        <x:v>68.037</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>1658606</x:v>
+        <x:v>228944</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>68.4111787561788</x:v>
+        <x:v>67.639</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>3354414</x:v>
+        <x:v>482282</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>2.20513055956624</x:v>
+        <x:v>0.263677897996594</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>37202</x:v>
+        <x:v>24394</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>58.5045178474249</x:v>
+        <x:v>71.772</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>189725</x:v>
+        <x:v>232849</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>68.0368261445302</x:v>
+        <x:v>67.53</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>164124</x:v>
+        <x:v>211146</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>68.0468393896044</x:v>
+        <x:v>67.251</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>353849</x:v>
+        <x:v>443995</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.23261387633487</x:v>
+        <x:v>0.242745257589953</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>25601</x:v>
+        <x:v>21703</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>67.9726327991705</x:v>
+        <x:v>70.242</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>283547</x:v>
+        <x:v>222402</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>69.019695808431</x:v>
+        <x:v>70.496</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>260992</x:v>
+        <x:v>202492</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>68.6934342082076</x:v>
+        <x:v>71.014</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>544539</x:v>
+        <x:v>424894</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.35797000303947</x:v>
+        <x:v>0.232302173399308</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>22555</x:v>
+        <x:v>19910</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>72.7949858800558</x:v>
+        <x:v>65.231</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>212349</x:v>
+        <x:v>49330</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>70.8248428138784</x:v>
+        <x:v>67.72</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>196931</x:v>
+        <x:v>30725</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>71.1877024656225</x:v>
+        <x:v>68.369</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>409280</x:v>
+        <x:v>80055</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.269053204350826</x:v>
+        <x:v>0.0437684469337801</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>15418</x:v>
+        <x:v>18605</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>66.1901097695394</x:v>
+        <x:v>66.65</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>45507</x:v>
+        <x:v>13430</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>67.9143357484073</x:v>
+        <x:v>63.695</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>30598</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>68.3780845257104</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>76105</x:v>
+        <x:v>13430</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0500300384018755</x:v>
+        <x:v>0.00734258000525473</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>14909</x:v>
+        <x:v>13430</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>66.9625760671462</x:v>
+        <x:v>63.695</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>804476</x:v>
+        <x:v>355585</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>68.1164387832911</x:v>
+        <x:v>66.708</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>799405</x:v>
+        <x:v>348425</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>68.1268663088741</x:v>
+        <x:v>66.935</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>1603881</x:v>
+        <x:v>704010</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>1.05436210527611</x:v>
+        <x:v>0.384903183134727</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>5071</x:v>
+        <x:v>7160</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>66.4726178231876</x:v>
+        <x:v>55.658</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>9214</x:v>
+        <x:v>1189946</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>68.4424579886156</x:v>
+        <x:v>67.098</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>7532</x:v>
+        <x:v>1183241</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>70.2336476579728</x:v>
+        <x:v>67.091</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>16746</x:v>
+        <x:v>2373187</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0110085148554997</x:v>
+        <x:v>1.29749184027777</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>1682</x:v>
+        <x:v>6705</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>60.421506389568</x:v>
+        <x:v>68.252</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>1619</x:v>
+        <x:v>3810</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>68.3907951934607</x:v>
+        <x:v>66.036</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>176</x:v>
+        <x:v>1458</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>68.091761675748</x:v>
+        <x:v>67.616</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>1795</x:v>
+        <x:v>5268</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00118000024875326</x:v>
+        <x:v>0.00288017211226224</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>1443</x:v>
+        <x:v>2352</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>68.4272677500216</x:v>
+        <x:v>65.057</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>1000</x:v>
+        <x:v>10186</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>66.0004500274658</x:v>
+        <x:v>67.922</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>0</x:v>
+        <x:v>7890</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>0</x:v>
+        <x:v>69.918</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>1000</x:v>
+        <x:v>18076</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.000657381754180087</x:v>
+        <x:v>0.00988268623789907</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>1000</x:v>
+        <x:v>2296</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>66.0004500274658</x:v>
+        <x:v>61.061</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>5978</x:v>
+        <x:v>7565</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>66.9964049598691</x:v>
+        <x:v>66.525</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>5578</x:v>
+        <x:v>5603</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>67.1205628067843</x:v>
+        <x:v>67.102</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>11556</x:v>
+        <x:v>13168</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00759670355130508</x:v>
+        <x:v>0.00719933682123561</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>400</x:v>
+        <x:v>1962</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>65.2650237846374</x:v>
+        <x:v>64.875</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>375</x:v>
+        <x:v>2369</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>66.6592025146484</x:v>
+        <x:v>67.114</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>0</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>0</x:v>
+        <x:v>65.427</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>375</x:v>
+        <x:v>2795</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.000246518157817533</x:v>
+        <x:v>0.00152810953944058</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>375</x:v>
+        <x:v>1943</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>66.6592025146484</x:v>
+        <x:v>67.483</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>2683</x:v>
+        <x:v>61132</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>70.2146847981194</x:v>
+        <x:v>66.54</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>2323</x:v>
+        <x:v>59956</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>69.0449191556118</x:v>
+        <x:v>67.533</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>5006</x:v>
+        <x:v>121088</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00329085306142551</x:v>
+        <x:v>0.0662024071240718</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>360</x:v>
+        <x:v>1176</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>77.7629225413004</x:v>
+        <x:v>15.943</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>1658</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>67.2881778077424</x:v>
+        <x:v>65.459</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>1458</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>67.6160486532664</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>3116</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.00204840154602515</x:v>
+        <x:v>0.000336238771647927</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>200</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>64.8979993438721</x:v>
+        <x:v>65.459</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1576,25 +1576,25 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>66.5999984741211</x:v>
+        <x:v>66.6</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>0</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>0</x:v>
+        <x:v>62.44</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>100</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>6.57381754180087E-05</x:v>
+        <x:v>8.20094564994944E-05</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>66.5999984741211</x:v>
+        <x:v>70.76</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>0</x:v>
+        <x:v>2693</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>0</x:v>
+        <x:v>70.196</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>131</x:v>
+        <x:v>2822</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>70.5297704798575</x:v>
+        <x:v>68.241</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>131</x:v>
+        <x:v>5515</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>8.61170097975914E-05</x:v>
+        <x:v>0.00301521435063141</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-131</x:v>
+        <x:v>-129</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>70.5297704798575</x:v>
+        <x:v>27.419</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1631,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>303</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>69.4861396562935</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>663</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>67.7234539762701</x:v>
+        <x:v>70.527</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>966</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.000635030774537964</x:v>
+        <x:v>7.16215920095584E-05</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-360</x:v>
+        <x:v>-131</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>66.2398601955838</x:v>
+        <x:v>70.527</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>0</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>0</x:v>
+        <x:v>68.448</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>375</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>70.4173325195312</x:v>
+        <x:v>67.395</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>375</x:v>
+        <x:v>1158</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.000246518157817533</x:v>
+        <x:v>0.000633113004176097</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-375</x:v>
+        <x:v>-332</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>70.4173325195312</x:v>
+        <x:v>66.084</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>48648</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>66.9226460518795</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>49693</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>68.0605425603304</x:v>
+        <x:v>69.454</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>98341</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.0646475790878239</x:v>
+        <x:v>0.000255322774568426</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-1045</x:v>
+        <x:v>-467</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>121.033163941306</x:v>
+        <x:v>69.454</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1721,25 +1721,25 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>70.3804345061814</x:v>
+        <x:v>70.38</x:v>
       </x:c>
       <x:c r="D41" s="0">
         <x:v>2297</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>69.4469966797088</x:v>
+        <x:v>69.447</x:v>
       </x:c>
       <x:c r="F41" s="0">
         <x:v>2573</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.00169144325350536</x:v>
+        <x:v>0.00140673554382133</x:v>
       </x:c>
       <x:c r="H41" s="0">
         <x:v>-2021</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>69.3195207568456</x:v>
+        <x:v>69.32</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>807602</x:v>
+        <x:v>819293</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>71.5237277324361</x:v>
+        <x:v>71.435</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>816787</x:v>
+        <x:v>825585</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>70.6641325197893</x:v>
+        <x:v>70.579</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>1624389</x:v>
+        <x:v>1644878</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>1.06784369029084</x:v>
+        <x:v>0.899303671919835</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-9185</x:v>
+        <x:v>-6292</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>-4.91679430916443</x:v>
+        <x:v>-40.86</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>222794</x:v>
+        <x:v>5014943</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>67.9521305260894</x:v>
+        <x:v>68.395</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>240343</x:v>
+        <x:v>5031060</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>67.7218298195016</x:v>
+        <x:v>68.442</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>463137</x:v>
+        <x:v>10046003</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.304457813485703</x:v>
+        <x:v>5.49244830681527</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-17549</x:v>
+        <x:v>-16117</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>64.7980383998465</x:v>
+        <x:v>83.021</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>4530573</x:v>
+        <x:v>905622</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>68.8339301465601</x:v>
+        <x:v>66.798</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>4569273</x:v>
+        <x:v>943601</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>68.8520994052951</x:v>
+        <x:v>66.542</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>9099846</x:v>
+        <x:v>1849223</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>5.98207272624865</x:v>
+        <x:v>1.0110251545091</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-38700</x:v>
+        <x:v>-37979</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>70.9791576237642</x:v>
+        <x:v>60.428</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>447859</x:v>
+        <x:v>350119</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>68.8198029471785</x:v>
+        <x:v>69.83</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>505298</x:v>
+        <x:v>414690</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>68.8154162679111</x:v>
+        <x:v>70.14</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>953157</x:v>
+        <x:v>764809</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.626588020669029</x:v>
+        <x:v>0.418143802772812</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-57439</x:v>
+        <x:v>-64571</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>68.7812127861302</x:v>
+        <x:v>71.822</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1863,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>306163</x:v>
+        <x:v>2198862</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>70.6109671670944</x:v>
+        <x:v>66.516</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>380001</x:v>
+        <x:v>2291352</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>70.7078232329156</x:v>
+        <x:v>68.533</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>686164</x:v>
+        <x:v>4490214</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.451071693975225</x:v>
+        <x:v>2.4549333980428</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-73838</x:v>
+        <x:v>-92490</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>71.1094286891853</x:v>
+        <x:v>116.49</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1895,25 +1895,25 @@
         <x:v>745035</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>68.906201880464</x:v>
+        <x:v>68.906</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>833700</x:v>
+        <x:v>856555</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>67.2249847089528</x:v>
+        <x:v>67.151</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1578735</x:v>
+        <x:v>1601590</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>1.0378315836855</x:v>
+        <x:v>0.875636836233501</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-88665</x:v>
+        <x:v>-111520</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>53.0980390666268</x:v>
+        <x:v>55.422</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>322345</x:v>
+        <x:v>646404</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>72.0709597656475</x:v>
+        <x:v>68.791</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>458382</x:v>
+        <x:v>758640</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>71.064415085865</x:v>
+        <x:v>69.036</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>780727</x:v>
+        <x:v>1405044</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>0.513235684795757</x:v>
+        <x:v>0.768179298652504</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-136037</x:v>
+        <x:v>-112236</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>68.6793680412779</x:v>
+        <x:v>70.451</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>594475</x:v>
+        <x:v>343905</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>69.1271236222775</x:v>
+        <x:v>71.628</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>756162</x:v>
+        <x:v>474909</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>69.0532244117749</x:v>
+        <x:v>70.847</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>1350637</x:v>
+        <x:v>818814</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.88788412032053</x:v>
+        <x:v>0.44766994076118</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-161687</x:v>
+        <x:v>-131004</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>68.7815189984548</x:v>
+        <x:v>68.794</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>2386761</x:v>
+        <x:v>1726969</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>69.007942576596</x:v>
+        <x:v>68.09</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>2695075</x:v>
+        <x:v>2243273</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>68.6278099989786</x:v>
+        <x:v>66.528</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>5081836</x:v>
+        <x:v>3970242</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>3.34070626413552</x:v>
+        <x:v>2.17064925727644</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-308314</x:v>
+        <x:v>-516304</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>65.6850775538523</x:v>
+        <x:v>61.303</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>1581489</x:v>
+        <x:v>2664526</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>66.8743808647411</x:v>
+        <x:v>68.516</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>2095004</x:v>
+        <x:v>3362555</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>68.8146102346548</x:v>
+        <x:v>67.633</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>3676493</x:v>
+        <x:v>6027081</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>2.41685941757081</x:v>
+        <x:v>3.29518424725619</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-513515</x:v>
+        <x:v>-698029</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>74.7899983070489</x:v>
+        <x:v>64.265</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>4054906</x:v>
+        <x:v>4504576</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>69.5783157705294</x:v>
+        <x:v>69.062</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>5072738</x:v>
+        <x:v>5629289</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>68.9223376944735</x:v>
+        <x:v>68.422</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>9127644</x:v>
+        <x:v>10133865</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>6.00034662425134</x:v>
+        <x:v>5.54048507259499</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-1017832</x:v>
+        <x:v>-1124713</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>66.3090091329156</x:v>
+        <x:v>65.862</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>1398152</x:v>
+        <x:v>1874681</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>68.9102620453309</x:v>
+        <x:v>67.724</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>2679257</x:v>
+        <x:v>3138954</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>68.531674656392</x:v>
+        <x:v>67.93</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>4077409</x:v>
+        <x:v>5013635</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>2.68041428092967</x:v>
+        <x:v>2.74110320957895</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-1281105</x:v>
+        <x:v>-1264273</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>68.1184979729666</x:v>
+        <x:v>68.235</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2095,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>8450065</x:v>
+        <x:v>9867699</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>68.4250194290346</x:v>
+        <x:v>67.908</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>10230517</x:v>
+        <x:v>12022597</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>68.5363157438372</x:v>
+        <x:v>68.001</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>18680582</x:v>
+        <x:v>21890296</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>12.280273764265</x:v>
+        <x:v>11.9680751838204</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-1780452</x:v>
+        <x:v>-2154898</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>69.0645305422941</x:v>
+        <x:v>68.425</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2124,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>698070</x:v>
+        <x:v>783973</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>68.446936458425</x:v>
+        <x:v>67.961</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>3166994</x:v>
+        <x:v>4596538</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>68.2650020480506</x:v>
+        <x:v>67.233</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>3865064</x:v>
+        <x:v>5380511</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>2.5408225523383</x:v>
+        <x:v>2.94168521866367</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-2468924</x:v>
+        <x:v>-3812565</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>68.2135614391659</x:v>
+        <x:v>67.083</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -61,139 +61,139 @@
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
+    <x:t>HALK</x:t>
+  </x:si>
+  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
-    <x:t>HALK</x:t>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
     <x:t>OYAK</x:t>
   </x:si>
   <x:si>
+    <x:t>TACIRLER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEO MENKUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
   </x:si>
   <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEO MENKUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
   </x:si>
   <x:si>
     <x:t>IKON</x:t>
   </x:si>
   <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
   </x:si>
   <x:si>
     <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
+    <x:t>ALNUS</x:t>
+  </x:si>
+  <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
     <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALNUS</x:t>
   </x:si>
   <x:si>
     <x:t>A1 CAPITAL</x:t>
@@ -587,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>7216086</x:v>
+        <x:v>8055375</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>67.299</x:v>
+        <x:v>66.761</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>5300910</x:v>
+        <x:v>5783066</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>67.745</x:v>
+        <x:v>67.271</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>12516996</x:v>
+        <x:v>13838441</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>6.84341359310897</x:v>
+        <x:v>6.88933552699089</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>1915176</x:v>
+        <x:v>2272309</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>66.066</x:v>
+        <x:v>65.463</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>4692191</x:v>
+        <x:v>5154232</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>67.451</x:v>
+        <x:v>66.982</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>2927996</x:v>
+        <x:v>3290848</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>67.399</x:v>
+        <x:v>66.815</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>7620187</x:v>
+        <x:v>8445080</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>4.16618262863008</x:v>
+        <x:v>4.20430232511597</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>1764195</x:v>
+        <x:v>1863384</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>67.538</x:v>
+        <x:v>67.278</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>2955319</x:v>
+        <x:v>3347985</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>67.429</x:v>
+        <x:v>66.82</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>1734484</x:v>
+        <x:v>1893306</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>67.364</x:v>
+        <x:v>66.923</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>4689803</x:v>
+        <x:v>5241291</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>2.56405463413132</x:v>
+        <x:v>2.60932660648679</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>1220835</x:v>
+        <x:v>1454679</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>67.522</x:v>
+        <x:v>66.685</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>4484700</x:v>
+        <x:v>4932277</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>67.57</x:v>
+        <x:v>67.082</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>3428120</x:v>
+        <x:v>3749452</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>67.758</x:v>
+        <x:v>67.28</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>7912820</x:v>
+        <x:v>8681729</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>4.32617378385553</x:v>
+        <x:v>4.3221157668994</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>1056580</x:v>
+        <x:v>1182825</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>66.96</x:v>
+        <x:v>66.457</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>13464241</x:v>
+        <x:v>14501786</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>67.601</x:v>
+        <x:v>67.214</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>12545627</x:v>
+        <x:v>13402585</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>67.677</x:v>
+        <x:v>67.325</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>26009868</x:v>
+        <x:v>27904371</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>14.2203675886906</x:v>
+        <x:v>13.8919242773542</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>918614</x:v>
+        <x:v>1099201</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>66.558</x:v>
+        <x:v>65.859</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>3294710</x:v>
+        <x:v>3968279</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>67.521</x:v>
+        <x:v>66.615</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>2576743</x:v>
+        <x:v>2983156</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>67.882</x:v>
+        <x:v>67.102</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>5871453</x:v>
+        <x:v>6951435</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>3.21009779594884</x:v>
+        <x:v>3.46070544428147</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>717967</x:v>
+        <x:v>985123</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>66.223</x:v>
+        <x:v>65.141</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>1290722</x:v>
+        <x:v>1479790</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>67.91</x:v>
+        <x:v>67.167</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>864311</x:v>
+        <x:v>1035270</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>67.784</x:v>
+        <x:v>66.851</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>2155033</x:v>
+        <x:v>2515060</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>1.17822056712317</x:v>
+        <x:v>1.25209857168981</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>426411</x:v>
+        <x:v>444520</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>68.165</x:v>
+        <x:v>67.904</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>1319345</x:v>
+        <x:v>2330182</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>67.458</x:v>
+        <x:v>66.709</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>1011501</x:v>
+        <x:v>1897676</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>67.176</x:v>
+        <x:v>67.407</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>2330846</x:v>
+        <x:v>4227858</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.2743427576268</x:v>
+        <x:v>2.10479867800662</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>307844</x:v>
+        <x:v>432506</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>68.382</x:v>
+        <x:v>63.647</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>1933416</x:v>
+        <x:v>1441855</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>67.635</x:v>
+        <x:v>67.014</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>1650303</x:v>
+        <x:v>1089295</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>68.219</x:v>
+        <x:v>66.819</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>3583719</x:v>
+        <x:v>2531150</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.95932564957941</x:v>
+        <x:v>1.26010882433527</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>283113</x:v>
+        <x:v>352560</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>64.229</x:v>
+        <x:v>67.615</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1160490</x:v>
+        <x:v>493197</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>67.279</x:v>
+        <x:v>66.2</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>945437</x:v>
+        <x:v>246156</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>67.816</x:v>
+        <x:v>66.864</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>2105927</x:v>
+        <x:v>739353</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>1.15137285798407</x:v>
+        <x:v>0.368079821266521</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>215053</x:v>
+        <x:v>247041</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>64.915</x:v>
+        <x:v>65.538</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>2335124</x:v>
+        <x:v>372406</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>67.802</x:v>
+        <x:v>65.909</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>2137896</x:v>
+        <x:v>132844</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>68.114</x:v>
+        <x:v>67.51</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>4473020</x:v>
+        <x:v>505250</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>2.44553292740912</x:v>
+        <x:v>0.251533881237933</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>197228</x:v>
+        <x:v>239562</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>64.42</x:v>
+        <x:v>65.022</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>287399</x:v>
+        <x:v>1273346</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>67.11</x:v>
+        <x:v>66.832</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>118969</x:v>
+        <x:v>1062918</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>68.129</x:v>
+        <x:v>67.196</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>406368</x:v>
+        <x:v>2336264</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>0.22217345879191</x:v>
+        <x:v>1.16308669275895</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>168430</x:v>
+        <x:v>210428</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>66.39</x:v>
+        <x:v>64.996</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>375598</x:v>
+        <x:v>2218488</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>67.485</x:v>
+        <x:v>67.094</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>222809</x:v>
+        <x:v>2057363</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>67.375</x:v>
+        <x:v>67.497</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>598407</x:v>
+        <x:v>4275851</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>0.327166885569953</x:v>
+        <x:v>2.12869153414171</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>152789</x:v>
+        <x:v>161125</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>67.646</x:v>
+        <x:v>61.938</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>2007524</x:v>
+        <x:v>2217505</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>67.612</x:v>
+        <x:v>67.084</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>1869019</x:v>
+        <x:v>2061308</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>67.264</x:v>
+        <x:v>66.775</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>3876543</x:v>
+        <x:v>4278813</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>2.11942123017946</x:v>
+        <x:v>2.1301661375187</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>138505</x:v>
+        <x:v>156197</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>72.315</x:v>
+        <x:v>71.164</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>4590103</x:v>
+        <x:v>431394</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>67.987</x:v>
+        <x:v>66.947</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>4501802</x:v>
+        <x:v>321614</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>67.141</x:v>
+        <x:v>67.611</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>9091905</x:v>
+        <x:v>753008</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>4.9708145839669</x:v>
+        <x:v>0.374877832445747</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>88301</x:v>
+        <x:v>109780</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>111.126</x:v>
+        <x:v>65.001</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>2308284</x:v>
+        <x:v>222426</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>67.305</x:v>
+        <x:v>66.742</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>2227497</x:v>
+        <x:v>131218</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>67.247</x:v>
+        <x:v>66.96</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>4535781</x:v>
+        <x:v>353644</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>2.47984623073822</x:v>
+        <x:v>0.176058283812979</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>80787</x:v>
+        <x:v>91208</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>68.909</x:v>
+        <x:v>66.429</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>2011427</x:v>
+        <x:v>207298</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>67.598</x:v>
+        <x:v>67.108</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>1931356</x:v>
+        <x:v>122814</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>67.842</x:v>
+        <x:v>67.091</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>3942783</x:v>
+        <x:v>330112</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>2.15563660616964</x:v>
+        <x:v>0.164343102628831</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>80071</x:v>
+        <x:v>84484</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>61.7</x:v>
+        <x:v>67.132</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>155037</x:v>
+        <x:v>193985</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>67.266</x:v>
+        <x:v>66.256</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>77068</x:v>
+        <x:v>119575</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>67.318</x:v>
+        <x:v>65.418</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>232105</x:v>
+        <x:v>313560</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.126898699338768</x:v>
+        <x:v>0.156102847701071</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>77969</x:v>
+        <x:v>74410</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>67.215</x:v>
+        <x:v>67.603</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>184593</x:v>
+        <x:v>4809176</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>67.735</x:v>
+        <x:v>67.732</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>108419</x:v>
+        <x:v>4746520</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>67.731</x:v>
+        <x:v>66.889</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>293012</x:v>
+        <x:v>9555696</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>0.160198365785532</x:v>
+        <x:v>4.75721188087045</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>76174</x:v>
+        <x:v>62656</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>67.741</x:v>
+        <x:v>131.566</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>191274</x:v>
+        <x:v>2361507</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>67.496</x:v>
+        <x:v>66.23</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>119752</x:v>
+        <x:v>2334457</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>67.448</x:v>
+        <x:v>68.414</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>311026</x:v>
+        <x:v>4695964</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.170047154781412</x:v>
+        <x:v>2.33784077402001</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>71522</x:v>
+        <x:v>27050</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>67.576</x:v>
+        <x:v>-122.248</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>342639</x:v>
+        <x:v>232862</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>68.093</x:v>
+        <x:v>70.119</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>276433</x:v>
+        <x:v>206090</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>68.431</x:v>
+        <x:v>70.867</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>619072</x:v>
+        <x:v>438952</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.338465055027033</x:v>
+        <x:v>0.218528055887488</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>66206</x:v>
+        <x:v>26772</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>66.681</x:v>
+        <x:v>64.361</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>253338</x:v>
+        <x:v>237141</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>68.037</x:v>
+        <x:v>67.438</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>228944</x:v>
+        <x:v>212748</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>67.639</x:v>
+        <x:v>67.214</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>482282</x:v>
+        <x:v>449889</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.263677897996594</x:v>
+        <x:v>0.223972936756561</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>24394</x:v>
+        <x:v>24393</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>71.772</x:v>
+        <x:v>69.391</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>232849</x:v>
+        <x:v>53140</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>67.53</x:v>
+        <x:v>67.299</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>211146</x:v>
+        <x:v>30927</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>67.251</x:v>
+        <x:v>68.328</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>443995</x:v>
+        <x:v>84067</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.242745257589953</x:v>
+        <x:v>0.0418519520911021</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>21703</x:v>
+        <x:v>22213</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>70.242</x:v>
+        <x:v>65.865</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>222402</x:v>
+        <x:v>1482287</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>70.496</x:v>
+        <x:v>66.122</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>202492</x:v>
+        <x:v>1468854</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>71.014</x:v>
+        <x:v>66.132</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>424894</x:v>
+        <x:v>2951141</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.232302173399308</x:v>
+        <x:v>1.46919732768015</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>19910</x:v>
+        <x:v>13433</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>65.231</x:v>
+        <x:v>65.066</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>49330</x:v>
+        <x:v>39865</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>67.72</x:v>
+        <x:v>62.688</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>30725</x:v>
+        <x:v>26824</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>68.369</x:v>
+        <x:v>62.266</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>80055</x:v>
+        <x:v>66689</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0437684469337801</x:v>
+        <x:v>0.0332004809616557</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>18605</x:v>
+        <x:v>13041</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>66.65</x:v>
+        <x:v>63.556</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>13430</x:v>
+        <x:v>28308</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>63.695</x:v>
+        <x:v>63.086</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>0</x:v>
+        <x:v>15291</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>0</x:v>
+        <x:v>62.748</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>13430</x:v>
+        <x:v>43599</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.00734258000525473</x:v>
+        <x:v>0.0217053452510493</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>13430</x:v>
+        <x:v>13017</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>63.695</x:v>
+        <x:v>63.483</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>355585</x:v>
+        <x:v>263023</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>66.708</x:v>
+        <x:v>67.828</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>348425</x:v>
+        <x:v>252783</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>66.935</x:v>
+        <x:v>67.101</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>704010</x:v>
+        <x:v>515806</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.384903183134727</x:v>
+        <x:v>0.256789084900175</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>7160</x:v>
+        <x:v>10240</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>55.658</x:v>
+        <x:v>85.795</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>1189946</x:v>
+        <x:v>832448</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>67.098</x:v>
+        <x:v>71.294</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1183241</x:v>
+        <x:v>825800</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>67.091</x:v>
+        <x:v>70.577</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>2373187</x:v>
+        <x:v>1658248</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>1.29749184027777</x:v>
+        <x:v>0.82554291043056</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>6705</x:v>
+        <x:v>6648</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>68.252</x:v>
+        <x:v>160.328</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>3810</x:v>
+        <x:v>2704590</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>66.036</x:v>
+        <x:v>67.025</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>1458</x:v>
+        <x:v>2698808</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>67.616</x:v>
+        <x:v>66.883</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>5268</x:v>
+        <x:v>5403398</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00288017211226224</x:v>
+        <x:v>2.6900300263499</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>2352</x:v>
+        <x:v>5782</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>65.057</x:v>
+        <x:v>133.221</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>10186</x:v>
+        <x:v>75007</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>67.922</x:v>
+        <x:v>65.655</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>7890</x:v>
+        <x:v>70831</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>69.918</x:v>
+        <x:v>66.697</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>18076</x:v>
+        <x:v>145838</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00988268623789907</x:v>
+        <x:v>0.072604053779273</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>2296</x:v>
+        <x:v>4176</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>61.061</x:v>
+        <x:v>47.977</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>7565</x:v>
+        <x:v>3419</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>66.525</x:v>
+        <x:v>65.588</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>5603</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>67.102</x:v>
+        <x:v>65.241</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>13168</x:v>
+        <x:v>3872</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00719933682123561</x:v>
+        <x:v>0.00192763817546418</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>1962</x:v>
+        <x:v>2966</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>64.875</x:v>
+        <x:v>65.641</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>2369</x:v>
+        <x:v>6910</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>67.114</x:v>
+        <x:v>64.284</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>426</x:v>
+        <x:v>4558</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>65.427</x:v>
+        <x:v>63.925</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>2795</x:v>
+        <x:v>11468</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.00152810953944058</x:v>
+        <x:v>0.00570923414158658</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>1943</x:v>
+        <x:v>2352</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>67.483</x:v>
+        <x:v>64.981</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>61132</x:v>
+        <x:v>10348</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>66.54</x:v>
+        <x:v>67.824</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>59956</x:v>
+        <x:v>8004</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>67.533</x:v>
+        <x:v>69.812</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>121088</x:v>
+        <x:v>18352</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0662024071240718</x:v>
+        <x:v>0.00913636771593973</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>1176</x:v>
+        <x:v>2344</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>15.943</x:v>
+        <x:v>61.036</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>615</x:v>
+        <x:v>7565</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>65.459</x:v>
+        <x:v>66.525</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>0</x:v>
+        <x:v>5603</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>0</x:v>
+        <x:v>67.102</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>615</x:v>
+        <x:v>13168</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.000336238771647927</x:v>
+        <x:v>0.00655556288597943</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>615</x:v>
+        <x:v>1962</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>65.459</x:v>
+        <x:v>64.875</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>100</x:v>
+        <x:v>461834</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>66.6</x:v>
+        <x:v>65.683</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>50</x:v>
+        <x:v>460880</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>62.44</x:v>
+        <x:v>65.802</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>150</x:v>
+        <x:v>922714</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>8.20094564994944E-05</x:v>
+        <x:v>0.459364341796296</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>50</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>70.76</x:v>
+        <x:v>8.321</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>2693</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>70.196</x:v>
+        <x:v>64.944</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>2822</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>68.241</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>5515</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.00301521435063141</x:v>
+        <x:v>0.000353964551331362</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>-129</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>27.419</x:v>
+        <x:v>64.944</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1631,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>0</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>0</x:v>
+        <x:v>65.3</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>131</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>70.527</x:v>
+        <x:v>62.44</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>131</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>7.16215920095584E-05</x:v>
+        <x:v>9.95680875756292E-05</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-131</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>70.527</x:v>
+        <x:v>66.73</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1660,28 +1660,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>413</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>68.448</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>745</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>67.395</x:v>
+        <x:v>70.527</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>1158</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.000633113004176097</x:v>
+        <x:v>6.52170973620371E-05</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-332</x:v>
+        <x:v>-131</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>66.084</x:v>
+        <x:v>70.527</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>0</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>0</x:v>
+        <x:v>66.994</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>467</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>69.454</x:v>
+        <x:v>66.926</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>467</x:v>
+        <x:v>1360</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.000255322774568426</x:v>
+        <x:v>0.000677062995514279</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-467</x:v>
+        <x:v>-294</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>69.454</x:v>
+        <x:v>66.803</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>276</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>70.38</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>2297</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>69.447</x:v>
+        <x:v>67.535</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>2573</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.00140673554382133</x:v>
+        <x:v>0.000319115720679892</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-2021</x:v>
+        <x:v>-641</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>69.32</x:v>
+        <x:v>67.535</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>819293</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>71.435</x:v>
+        <x:v>70.38</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>825585</x:v>
+        <x:v>2297</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>70.579</x:v>
+        <x:v>69.447</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>1644878</x:v>
+        <x:v>2573</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.899303671919835</x:v>
+        <x:v>0.00128094344666047</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-6292</x:v>
+        <x:v>-2021</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>-40.86</x:v>
+        <x:v>69.32</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>5014943</x:v>
+        <x:v>2544018</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>68.395</x:v>
+        <x:v>66.844</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>5031060</x:v>
+        <x:v>2574733</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>68.442</x:v>
+        <x:v>66.571</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>10046003</x:v>
+        <x:v>5118751</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>5.49244830681527</x:v>
+        <x:v>2.5483212392292</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-16117</x:v>
+        <x:v>-30715</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>83.021</x:v>
+        <x:v>44.036</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>905622</x:v>
+        <x:v>371437</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>66.798</x:v>
+        <x:v>69.36</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>943601</x:v>
+        <x:v>417187</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>66.542</x:v>
+        <x:v>70.093</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>1849223</x:v>
+        <x:v>788624</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>1.0110251545091</x:v>
+        <x:v>0.392608917481215</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-37979</x:v>
+        <x:v>-45750</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>60.428</x:v>
+        <x:v>76.039</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>350119</x:v>
+        <x:v>928942</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>69.83</x:v>
+        <x:v>66.685</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>414690</x:v>
+        <x:v>982272</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>70.14</x:v>
+        <x:v>66.387</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>764809</x:v>
+        <x:v>1911214</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.418143802772812</x:v>
+        <x:v>0.951479614638843</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-64571</x:v>
+        <x:v>-53330</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>71.822</x:v>
+        <x:v>61.196</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1863,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>2198862</x:v>
+        <x:v>5179343</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>66.516</x:v>
+        <x:v>68.198</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>2291352</x:v>
+        <x:v>5235842</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>68.533</x:v>
+        <x:v>68.196</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>4490214</x:v>
+        <x:v>10415185</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>2.4549333980428</x:v>
+        <x:v>5.1851002609819</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-92490</x:v>
+        <x:v>-56499</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>116.49</x:v>
+        <x:v>68.03</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>745035</x:v>
+        <x:v>677786</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>68.906</x:v>
+        <x:v>68.484</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>856555</x:v>
+        <x:v>797229</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>67.151</x:v>
+        <x:v>68.701</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1601590</x:v>
+        <x:v>1475015</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.875636836233501</x:v>
+        <x:v>0.734322113476833</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-111520</x:v>
+        <x:v>-119443</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>55.422</x:v>
+        <x:v>69.929</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>646404</x:v>
+        <x:v>361405</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>68.791</x:v>
+        <x:v>71.165</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>758640</x:v>
+        <x:v>493436</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>69.036</x:v>
+        <x:v>70.52</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>1405044</x:v>
+        <x:v>854841</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>0.768179298652504</x:v>
+        <x:v>0.425574417756192</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-112236</x:v>
+        <x:v>-132031</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>70.451</x:v>
+        <x:v>68.753</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>343905</x:v>
+        <x:v>745035</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>71.628</x:v>
+        <x:v>68.906</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>474909</x:v>
+        <x:v>881926</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>70.847</x:v>
+        <x:v>67.002</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>818814</x:v>
+        <x:v>1626961</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.44766994076118</x:v>
+        <x:v>0.809966976650666</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-131004</x:v>
+        <x:v>-136891</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>68.794</x:v>
+        <x:v>56.641</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>1726969</x:v>
+        <x:v>1873563</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>68.09</x:v>
+        <x:v>67.622</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>2243273</x:v>
+        <x:v>2914213</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>66.528</x:v>
+        <x:v>65.536</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>3970242</x:v>
+        <x:v>4787776</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>2.17064925727644</x:v>
+        <x:v>2.38354850030248</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-516304</x:v>
+        <x:v>-1040650</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>61.303</x:v>
+        <x:v>61.78</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>2664526</x:v>
+        <x:v>2238729</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>68.516</x:v>
+        <x:v>66.808</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>3362555</x:v>
+        <x:v>3521771</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>67.633</x:v>
+        <x:v>67.298</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>6027081</x:v>
+        <x:v>5760500</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>3.29518424725619</x:v>
+        <x:v>2.86780984239706</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-698029</x:v>
+        <x:v>-1283042</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>64.265</x:v>
+        <x:v>68.152</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>4504576</x:v>
+        <x:v>2909088</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>69.062</x:v>
+        <x:v>67.992</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>5629289</x:v>
+        <x:v>4201079</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>68.422</x:v>
+        <x:v>66.548</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>10133865</x:v>
+        <x:v>7110167</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>5.54048507259499</x:v>
+        <x:v>3.53972865266674</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-1124713</x:v>
+        <x:v>-1291991</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>65.862</x:v>
+        <x:v>63.298</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>1874681</x:v>
+        <x:v>4635765</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>67.724</x:v>
+        <x:v>68.864</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>3138954</x:v>
+        <x:v>6129446</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>67.93</x:v>
+        <x:v>67.923</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>5013635</x:v>
+        <x:v>10765211</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>2.74110320957895</x:v>
+        <x:v>5.35935735809063</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-1264273</x:v>
+        <x:v>-1493681</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>68.235</x:v>
+        <x:v>65.003</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2095,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>9867699</x:v>
+        <x:v>10646128</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>67.908</x:v>
+        <x:v>67.493</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>12022597</x:v>
+        <x:v>12611328</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>68.001</x:v>
+        <x:v>67.737</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>21890296</x:v>
+        <x:v>23257456</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>11.9680751838204</x:v>
+        <x:v>11.5785020789717</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-2154898</x:v>
+        <x:v>-1965200</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>68.425</x:v>
+        <x:v>69.061</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2124,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>783973</x:v>
+        <x:v>869641</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>67.961</x:v>
+        <x:v>67.365</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>4596538</x:v>
+        <x:v>4919483</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>67.233</x:v>
+        <x:v>66.907</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>5380511</x:v>
+        <x:v>5789124</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>2.94168521866367</x:v>
+        <x:v>2.88206002709088</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-3812565</x:v>
+        <x:v>-4049842</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>67.083</x:v>
+        <x:v>66.808</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -52,115 +52,118 @@
     <x:t>ZIRAAT</x:t>
   </x:si>
   <x:si>
+    <x:t>VAKIF</x:t>
+  </x:si>
+  <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
-    <x:t>VAKIF</x:t>
+    <x:t>HALK</x:t>
   </x:si>
   <x:si>
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
-    <x:t>HALK</x:t>
-  </x:si>
-  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
     <x:t>TEB</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVEYT TURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIBA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIBA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QNB YATIRIM</x:t>
+    <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
     <x:t>BULLS YATIRIM</x:t>
   </x:si>
   <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>UNLU</x:t>
   </x:si>
   <x:si>
-    <x:t>INVEST AZ</x:t>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
   </x:si>
   <x:si>
     <x:t>ACAR</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEO MENKUL</x:t>
   </x:si>
   <x:si>
     <x:t>INTEGRAL</x:t>
   </x:si>
   <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
   </x:si>
   <x:si>
     <x:t>MEKSA</x:t>
   </x:si>
   <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEO MENKUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
+    <x:t>IKON</x:t>
   </x:si>
   <x:si>
     <x:t>PUSULA YAT.</x:t>
@@ -170,9 +173,6 @@
   </x:si>
   <x:si>
     <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
   </x:si>
   <x:si>
     <x:t>TERA</x:t>
@@ -587,28 +587,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>8055375</x:v>
+        <x:v>8953853</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>66.761</x:v>
+        <x:v>66.358</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>5783066</x:v>
+        <x:v>6628481</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>67.271</x:v>
+        <x:v>66.679</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>13838441</x:v>
+        <x:v>15582334</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>6.88933552699089</x:v>
+        <x:v>7.0729048162381</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>2272309</x:v>
+        <x:v>2325372</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>65.463</x:v>
+        <x:v>65.443</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +616,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>5154232</x:v>
+        <x:v>5950082</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>66.982</x:v>
+        <x:v>66.425</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>3290848</x:v>
+        <x:v>4106812</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>66.815</x:v>
+        <x:v>66.02</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>8445080</x:v>
+        <x:v>10056894</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>4.20430232511597</x:v>
+        <x:v>4.56487802205986</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>1863384</x:v>
+        <x:v>1843270</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>67.278</x:v>
+        <x:v>67.327</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +645,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>3347985</x:v>
+        <x:v>3923486</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>66.82</x:v>
+        <x:v>66.214</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>1893306</x:v>
+        <x:v>2379442</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>66.923</x:v>
+        <x:v>66.074</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>5241291</x:v>
+        <x:v>6302928</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>2.60932660648679</x:v>
+        <x:v>2.86093275934157</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>1454679</x:v>
+        <x:v>1544044</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>66.685</x:v>
+        <x:v>66.431</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +674,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>4932277</x:v>
+        <x:v>5549577</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>67.082</x:v>
+        <x:v>66.602</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>3749452</x:v>
+        <x:v>4298064</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>67.28</x:v>
+        <x:v>66.695</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>8681729</x:v>
+        <x:v>9847641</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>4.3221157668994</x:v>
+        <x:v>4.46989696520969</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>1182825</x:v>
+        <x:v>1251513</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>66.457</x:v>
+        <x:v>66.283</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +703,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>14501786</x:v>
+        <x:v>4693947</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>67.214</x:v>
+        <x:v>66.023</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>13402585</x:v>
+        <x:v>3649433</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>67.325</x:v>
+        <x:v>66.303</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>27904371</x:v>
+        <x:v>8343380</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>13.8919242773542</x:v>
+        <x:v>3.787104844865</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>1099201</x:v>
+        <x:v>1044514</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>65.859</x:v>
+        <x:v>65.047</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +732,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>3968279</x:v>
+        <x:v>15391405</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>66.615</x:v>
+        <x:v>66.955</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>2983156</x:v>
+        <x:v>14371615</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>67.102</x:v>
+        <x:v>67.019</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>6951435</x:v>
+        <x:v>29763020</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>3.46070544428147</x:v>
+        <x:v>13.5095941021281</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>985123</x:v>
+        <x:v>1019790</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>65.141</x:v>
+        <x:v>66.047</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +761,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>1479790</x:v>
+        <x:v>2646055</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>67.167</x:v>
+        <x:v>66.232</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>1035270</x:v>
+        <x:v>2190716</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>66.851</x:v>
+        <x:v>66.788</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>2515060</x:v>
+        <x:v>4836771</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>1.25209857168981</x:v>
+        <x:v>2.19543624857103</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>444520</x:v>
+        <x:v>455339</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>67.904</x:v>
+        <x:v>63.558</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +790,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>2330182</x:v>
+        <x:v>1562553</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>66.709</x:v>
+        <x:v>66.919</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>1897676</x:v>
+        <x:v>1153009</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>67.407</x:v>
+        <x:v>66.418</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>4227858</x:v>
+        <x:v>2715562</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>2.10479867800662</x:v>
+        <x:v>1.2326081284481</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>432506</x:v>
+        <x:v>409544</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>63.647</x:v>
+        <x:v>68.33</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +819,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>1441855</x:v>
+        <x:v>1638419</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>67.014</x:v>
+        <x:v>66.497</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>1089295</x:v>
+        <x:v>1258951</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>66.819</x:v>
+        <x:v>66.296</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>2531150</x:v>
+        <x:v>2897370</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.26010882433527</x:v>
+        <x:v>1.31513175288271</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>352560</x:v>
+        <x:v>379468</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>67.615</x:v>
+        <x:v>67.165</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +848,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>493197</x:v>
+        <x:v>553635</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>66.2</x:v>
+        <x:v>64.879</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>246156</x:v>
+        <x:v>269744</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>66.864</x:v>
+        <x:v>65.118</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>739353</x:v>
+        <x:v>823379</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.368079821266521</x:v>
+        <x:v>0.373736135721985</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>247041</x:v>
+        <x:v>283891</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>65.538</x:v>
+        <x:v>64.651</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +877,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>372406</x:v>
+        <x:v>1480154</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>65.909</x:v>
+        <x:v>66.281</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>132844</x:v>
+        <x:v>1270693</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>67.51</x:v>
+        <x:v>66.481</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>505250</x:v>
+        <x:v>2750847</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>0.251533881237933</x:v>
+        <x:v>1.24862417883188</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>239562</x:v>
+        <x:v>209461</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>65.022</x:v>
+        <x:v>65.065</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +906,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>1273346</x:v>
+        <x:v>2467793</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>66.832</x:v>
+        <x:v>66.635</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>1062918</x:v>
+        <x:v>2271142</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>67.196</x:v>
+        <x:v>66.406</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>2336264</x:v>
+        <x:v>4738935</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>1.16308669275895</x:v>
+        <x:v>2.1510279644461</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>210428</x:v>
+        <x:v>196651</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>64.996</x:v>
+        <x:v>69.276</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +935,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>2218488</x:v>
+        <x:v>5235650</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>67.094</x:v>
+        <x:v>67.336</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>2057363</x:v>
+        <x:v>5052249</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>67.497</x:v>
+        <x:v>66.647</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>4275851</x:v>
+        <x:v>10287899</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>2.12869153414171</x:v>
+        <x:v>4.66973242815044</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>161125</x:v>
+        <x:v>183401</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>61.938</x:v>
+        <x:v>86.31</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +964,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>2217505</x:v>
+        <x:v>553675</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>67.084</x:v>
+        <x:v>65.826</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>2061308</x:v>
+        <x:v>392940</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>66.775</x:v>
+        <x:v>65.235</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>4278813</x:v>
+        <x:v>946615</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>2.1301661375187</x:v>
+        <x:v>0.429673615815399</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>156197</x:v>
+        <x:v>160735</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>71.164</x:v>
+        <x:v>67.271</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +993,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>431394</x:v>
+        <x:v>262653</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>66.947</x:v>
+        <x:v>66.219</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>321614</x:v>
+        <x:v>142551</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>67.611</x:v>
+        <x:v>66.467</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>753008</x:v>
+        <x:v>405204</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.374877832445747</x:v>
+        <x:v>0.183924264693527</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>109780</x:v>
+        <x:v>120102</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>65.001</x:v>
+        <x:v>65.925</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1022,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>222426</x:v>
+        <x:v>262330</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>66.742</x:v>
+        <x:v>66.099</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>131218</x:v>
+        <x:v>160645</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>66.96</x:v>
+        <x:v>66.161</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>353644</x:v>
+        <x:v>422975</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.176058283812979</x:v>
+        <x:v>0.191990616723291</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>91208</x:v>
+        <x:v>101685</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>66.429</x:v>
+        <x:v>66.001</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1051,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>207298</x:v>
+        <x:v>217270</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>67.108</x:v>
+        <x:v>65.867</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>122814</x:v>
+        <x:v>156384</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>67.091</x:v>
+        <x:v>64.842</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>330112</x:v>
+        <x:v>373654</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.164343102628831</x:v>
+        <x:v>0.169603550803534</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>84484</x:v>
+        <x:v>60886</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>67.132</x:v>
+        <x:v>68.499</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1080,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>193985</x:v>
+        <x:v>442298</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>66.256</x:v>
+        <x:v>66.84</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>119575</x:v>
+        <x:v>385792</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>65.418</x:v>
+        <x:v>66.812</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>313560</x:v>
+        <x:v>828090</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.156102847701071</x:v>
+        <x:v>0.375874483840393</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>74410</x:v>
+        <x:v>56506</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>67.603</x:v>
+        <x:v>67.03</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1109,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>4809176</x:v>
+        <x:v>2484868</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>67.732</x:v>
+        <x:v>66.059</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>4746520</x:v>
+        <x:v>2439733</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>66.889</x:v>
+        <x:v>68.174</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>9555696</x:v>
+        <x:v>4924601</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>4.75721188087045</x:v>
+        <x:v>2.23530275573293</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>62656</x:v>
+        <x:v>45135</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>131.566</x:v>
+        <x:v>-48.256</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1138,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>2361507</x:v>
+        <x:v>2452723</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>66.23</x:v>
+        <x:v>66.689</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>2334457</x:v>
+        <x:v>2414265</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>68.414</x:v>
+        <x:v>66.827</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>4695964</x:v>
+        <x:v>4866988</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>2.33784077402001</x:v>
+        <x:v>2.20915190662535</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>27050</x:v>
+        <x:v>38458</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>-122.248</x:v>
+        <x:v>57.999</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1167,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>232862</x:v>
+        <x:v>75230</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>70.119</x:v>
+        <x:v>66.065</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>206090</x:v>
+        <x:v>41186</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>70.867</x:v>
+        <x:v>66.923</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>438952</x:v>
+        <x:v>116416</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.218528055887488</x:v>
+        <x:v>0.0528418455853388</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>26772</x:v>
+        <x:v>34044</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>64.361</x:v>
+        <x:v>65.027</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1196,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>237141</x:v>
+        <x:v>239722</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>67.438</x:v>
+        <x:v>69.907</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>212748</x:v>
+        <x:v>212708</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>67.214</x:v>
+        <x:v>70.615</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>449889</x:v>
+        <x:v>452430</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.223972936756561</x:v>
+        <x:v>0.205360398898561</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>24393</x:v>
+        <x:v>27014</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>69.391</x:v>
+        <x:v>64.335</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1225,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>53140</x:v>
+        <x:v>282060</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>67.299</x:v>
+        <x:v>67.492</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>30927</x:v>
+        <x:v>258515</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>68.328</x:v>
+        <x:v>67.01</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>84067</x:v>
+        <x:v>540575</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.0418519520911021</x:v>
+        <x:v>0.245369886246689</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>22213</x:v>
+        <x:v>23545</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>65.865</x:v>
+        <x:v>72.776</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1254,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>1482287</x:v>
+        <x:v>241285</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>66.122</x:v>
+        <x:v>67.359</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>1468854</x:v>
+        <x:v>218179</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>66.132</x:v>
+        <x:v>67.1</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>2951141</x:v>
+        <x:v>459464</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>1.46919732768015</x:v>
+        <x:v>0.208553169152196</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>13433</x:v>
+        <x:v>23106</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>65.066</x:v>
+        <x:v>69.8</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1283,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>39865</x:v>
+        <x:v>849536</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>62.688</x:v>
+        <x:v>71.121</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>26824</x:v>
+        <x:v>831189</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>62.266</x:v>
+        <x:v>70.526</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>66689</x:v>
+        <x:v>1680725</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0332004809616557</x:v>
+        <x:v>0.762890074572383</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>13041</x:v>
+        <x:v>18347</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>63.556</x:v>
+        <x:v>98.063</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1312,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>28308</x:v>
+        <x:v>73787</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>63.086</x:v>
+        <x:v>62.706</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>15291</x:v>
+        <x:v>55816</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>62.748</x:v>
+        <x:v>62.355</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>43599</x:v>
+        <x:v>129603</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0217053452510493</x:v>
+        <x:v>0.0588274954765381</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>13017</x:v>
+        <x:v>17971</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>63.483</x:v>
+        <x:v>63.795</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1341,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>263023</x:v>
+        <x:v>12298</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>67.828</x:v>
+        <x:v>63.707</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>252783</x:v>
+        <x:v>4558</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>67.101</x:v>
+        <x:v>63.925</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>515806</x:v>
+        <x:v>16856</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.256789084900175</x:v>
+        <x:v>0.00765102863168697</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>10240</x:v>
+        <x:v>7740</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>85.795</x:v>
+        <x:v>63.579</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1370,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>832448</x:v>
+        <x:v>1689354</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>71.294</x:v>
+        <x:v>65.703</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>825800</x:v>
+        <x:v>1683768</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>70.577</x:v>
+        <x:v>65.703</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>1658248</x:v>
+        <x:v>3373122</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.82554291043056</x:v>
+        <x:v>1.53107813242603</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>6648</x:v>
+        <x:v>5586</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>160.328</x:v>
+        <x:v>65.66</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1399,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>2704590</x:v>
+        <x:v>3519</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>67.025</x:v>
+        <x:v>65.477</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>2698808</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>66.883</x:v>
+        <x:v>64.373</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>5403398</x:v>
+        <x:v>4250</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>2.6900300263499</x:v>
+        <x:v>0.00192909775063299</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>5782</x:v>
+        <x:v>2788</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>133.221</x:v>
+        <x:v>65.766</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1428,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>75007</x:v>
+        <x:v>7969</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>65.655</x:v>
+        <x:v>66.371</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>70831</x:v>
+        <x:v>6107</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>66.697</x:v>
+        <x:v>66.741</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>145838</x:v>
+        <x:v>14076</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.072604053779273</x:v>
+        <x:v>0.00638917175009645</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>4176</x:v>
+        <x:v>1862</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>47.977</x:v>
+        <x:v>65.159</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1457,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>3419</x:v>
+        <x:v>10348</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>65.588</x:v>
+        <x:v>67.824</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>453</x:v>
+        <x:v>8720</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>65.241</x:v>
+        <x:v>69.246</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>3872</x:v>
+        <x:v>19068</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.00192763817546418</x:v>
+        <x:v>0.0086550672727223</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>2966</x:v>
+        <x:v>1628</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>65.641</x:v>
+        <x:v>60.21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1486,28 +1486,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>6910</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>64.284</x:v>
+        <x:v>64.944</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>4558</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E33" s="0">
-        <x:v>63.925</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>11468</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.00570923414158658</x:v>
+        <x:v>0.000322726706047071</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>2352</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>64.981</x:v>
+        <x:v>64.944</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1515,28 +1515,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>10348</x:v>
+        <x:v>28308</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>67.824</x:v>
+        <x:v>63.086</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>8004</x:v>
+        <x:v>27737</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>69.812</x:v>
+        <x:v>62.645</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>18352</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.00913636771593973</x:v>
+        <x:v>0.0254391255139355</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>2344</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>61.036</x:v>
+        <x:v>84.538</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1544,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>7565</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>66.525</x:v>
+        <x:v>65.3</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>5603</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>67.102</x:v>
+        <x:v>62.44</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>13168</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.00655556288597943</x:v>
+        <x:v>9.07810706180229E-05</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>1962</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>64.875</x:v>
+        <x:v>66.73</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1573,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>461834</x:v>
+        <x:v>98032</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>65.683</x:v>
+        <x:v>64.944</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>460880</x:v>
+        <x:v>97969</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>65.802</x:v>
+        <x:v>65.551</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>922714</x:v>
+        <x:v>196001</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.459364341796296</x:v>
+        <x:v>0.0889659031110155</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>954</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>8.321</x:v>
+        <x:v>-879.889</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1602,28 +1602,28 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B37" s="0">
-        <x:v>711</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C37" s="0">
-        <x:v>64.944</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>0</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>0</x:v>
+        <x:v>70.527</x:v>
       </x:c>
       <x:c r="F37" s="0">
-        <x:v>711</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>0.000353964551331362</x:v>
+        <x:v>5.9461601254805E-05</x:v>
       </x:c>
       <x:c r="H37" s="0">
-        <x:v>711</x:v>
+        <x:v>-131</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>64.944</x:v>
+        <x:v>70.527</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1631,28 +1631,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>150</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>65.3</x:v>
+        <x:v>66.652</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>50</x:v>
+        <x:v>910</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>62.44</x:v>
+        <x:v>66.549</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>200</x:v>
+        <x:v>1493</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>9.95680875756292E-05</x:v>
+        <x:v>0.000677680692163541</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>100</x:v>
+        <x:v>-327</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>66.73</x:v>
+        <x:v>66.367</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1666,22 +1666,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>131</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>70.527</x:v>
+        <x:v>67.521</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>131</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>6.52170973620371E-05</x:v>
+        <x:v>0.000291861142036944</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-131</x:v>
+        <x:v>-643</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>70.527</x:v>
+        <x:v>67.521</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,28 +1689,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>533</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>66.994</x:v>
+        <x:v>70.38</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>827</x:v>
+        <x:v>2301</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>66.926</x:v>
+        <x:v>69.436</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>1360</x:v>
+        <x:v>2577</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.000677062995514279</x:v>
+        <x:v>0.00116971409491323</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-294</x:v>
+        <x:v>-2025</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>66.803</x:v>
+        <x:v>69.307</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1718,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>0</x:v>
+        <x:v>531471</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>0</x:v>
+        <x:v>65.328</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>641</x:v>
+        <x:v>540798</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>67.535</x:v>
+        <x:v>65.371</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>641</x:v>
+        <x:v>1072269</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.000319115720679892</x:v>
+        <x:v>0.486708639052584</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-641</x:v>
+        <x:v>-9327</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>67.535</x:v>
+        <x:v>67.814</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1747,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>276</x:v>
+        <x:v>3016379</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>70.38</x:v>
+        <x:v>66.59</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>2297</x:v>
+        <x:v>3043611</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>69.447</x:v>
+        <x:v>66.415</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>2573</x:v>
+        <x:v>6059990</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.00128094344666047</x:v>
+        <x:v>2.75066190067256</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-2021</x:v>
+        <x:v>-27232</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>69.32</x:v>
+        <x:v>47.025</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1776,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>2544018</x:v>
+        <x:v>5249447</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>66.844</x:v>
+        <x:v>68.127</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>2574733</x:v>
+        <x:v>5277947</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>66.571</x:v>
+        <x:v>68.153</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>5118751</x:v>
+        <x:v>10527394</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>2.5483212392292</x:v>
+        <x:v>4.77844049068875</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-30715</x:v>
+        <x:v>-28500</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>44.036</x:v>
+        <x:v>72.854</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1805,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>371437</x:v>
+        <x:v>2572001</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>69.36</x:v>
+        <x:v>66.799</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>417187</x:v>
+        <x:v>2603113</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>70.093</x:v>
+        <x:v>66.531</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>788624</x:v>
+        <x:v>5175114</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>0.392608917481215</x:v>
+        <x:v>2.3490119474516</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-45750</x:v>
+        <x:v>-31112</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>76.039</x:v>
+        <x:v>44.406</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,28 +1834,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>928942</x:v>
+        <x:v>412662</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>66.685</x:v>
+        <x:v>68.696</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>982272</x:v>
+        <x:v>449542</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>66.387</x:v>
+        <x:v>69.565</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>1911214</x:v>
+        <x:v>862204</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.951479614638843</x:v>
+        <x:v>0.391359011055709</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-53330</x:v>
+        <x:v>-36880</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>61.196</x:v>
+        <x:v>79.291</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1863,28 +1863,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>5179343</x:v>
+        <x:v>944090</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>68.198</x:v>
+        <x:v>66.621</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>5235842</x:v>
+        <x:v>985745</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>68.196</x:v>
+        <x:v>66.374</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>10415185</x:v>
+        <x:v>1929835</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>5.1851002609819</x:v>
+        <x:v>0.875962437080661</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-56499</x:v>
+        <x:v>-41655</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>68.03</x:v>
+        <x:v>60.776</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1892,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>677786</x:v>
+        <x:v>731574</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>68.484</x:v>
+        <x:v>68.087</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>797229</x:v>
+        <x:v>836113</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>68.701</x:v>
+        <x:v>68.43</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1475015</x:v>
+        <x:v>1567687</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.734322113476833</x:v>
+        <x:v>0.711581521269782</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-119443</x:v>
+        <x:v>-104539</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>69.929</x:v>
+        <x:v>70.833</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1921,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>361405</x:v>
+        <x:v>385465</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>71.165</x:v>
+        <x:v>70.633</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>493436</x:v>
+        <x:v>522463</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>70.52</x:v>
+        <x:v>70.091</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>854841</x:v>
+        <x:v>907928</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>0.425574417756192</x:v>
+        <x:v>0.412113379420402</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-132031</x:v>
+        <x:v>-136998</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>68.753</x:v>
+        <x:v>68.564</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1950,28 +1950,28 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B49" s="0">
-        <x:v>745035</x:v>
+        <x:v>760175</x:v>
       </x:c>
       <x:c r="C49" s="0">
-        <x:v>68.906</x:v>
+        <x:v>68.761</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>881926</x:v>
+        <x:v>961096</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>67.002</x:v>
+        <x:v>66.639</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>1626961</x:v>
+        <x:v>1721271</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.809966976650666</x:v>
+        <x:v>0.781294121018775</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-136891</x:v>
+        <x:v>-200921</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>56.641</x:v>
+        <x:v>58.61</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1979,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>1873563</x:v>
+        <x:v>2389564</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>67.622</x:v>
+        <x:v>66.601</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>2914213</x:v>
+        <x:v>3306477</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>65.536</x:v>
+        <x:v>65.233</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>4787776</x:v>
+        <x:v>5696041</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>2.38354850030248</x:v>
+        <x:v>2.58546350132077</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-1040650</x:v>
+        <x:v>-916913</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>61.78</x:v>
+        <x:v>61.668</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2008,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>2238729</x:v>
+        <x:v>2536706</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>66.808</x:v>
+        <x:v>66.304</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>3521771</x:v>
+        <x:v>3817598</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>67.298</x:v>
+        <x:v>66.931</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>5760500</x:v>
+        <x:v>6354304</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>2.86780984239706</x:v>
+        <x:v>2.88425260076193</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-1283042</x:v>
+        <x:v>-1280892</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>68.152</x:v>
+        <x:v>68.172</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2037,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>2909088</x:v>
+        <x:v>3125726</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>67.992</x:v>
+        <x:v>67.611</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>4201079</x:v>
+        <x:v>4605483</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>66.548</x:v>
+        <x:v>66.174</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>7110167</x:v>
+        <x:v>7731209</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>3.53972865266674</x:v>
+        <x:v>3.50923715095847</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-1291991</x:v>
+        <x:v>-1479757</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>63.298</x:v>
+        <x:v>63.137</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2066,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>4635765</x:v>
+        <x:v>4869738</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>68.864</x:v>
+        <x:v>68.57</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>6129446</x:v>
+        <x:v>6393194</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>67.923</x:v>
+        <x:v>67.713</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>10765211</x:v>
+        <x:v>11262932</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>5.35935735809063</x:v>
+        <x:v>5.11230512628995</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-1493681</x:v>
+        <x:v>-1523456</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>65.003</x:v>
+        <x:v>64.973</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2095,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>10646128</x:v>
+        <x:v>11374314</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>67.493</x:v>
+        <x:v>67.183</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>12611328</x:v>
+        <x:v>13380001</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>67.737</x:v>
+        <x:v>67.451</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>23257456</x:v>
+        <x:v>24754315</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>11.5785020789717</x:v>
+        <x:v>11.2361160905789</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-1965200</x:v>
+        <x:v>-2005687</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>69.061</x:v>
+        <x:v>68.973</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2124,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>869641</x:v>
+        <x:v>920217</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>67.365</x:v>
+        <x:v>67.101</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>4919483</x:v>
+        <x:v>4988063</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>66.907</x:v>
+        <x:v>66.85</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>5789124</x:v>
+        <x:v>5908280</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>2.88206002709088</x:v>
+        <x:v>2.68179991955526</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-4049842</x:v>
+        <x:v>-4067846</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>66.808</x:v>
+        <x:v>66.793</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -46,12 +46,12 @@
     <x:t>MIDAS</x:t>
   </x:si>
   <x:si>
+    <x:t>ZIRAAT</x:t>
+  </x:si>
+  <x:si>
     <x:t>GARANTI BBVA</x:t>
   </x:si>
   <x:si>
-    <x:t>ZIRAAT</x:t>
-  </x:si>
-  <x:si>
     <x:t>VAKIF</x:t>
   </x:si>
   <x:si>
@@ -61,129 +61,132 @@
     <x:t>HALK</x:t>
   </x:si>
   <x:si>
+    <x:t>KUVEYT TURK</x:t>
+  </x:si>
+  <x:si>
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>OSMANLI</x:t>
   </x:si>
   <x:si>
-    <x:t>KUVEYT TURK</x:t>
+    <x:t>YAPI KREDI</x:t>
   </x:si>
   <x:si>
     <x:t>OYAK</x:t>
   </x:si>
   <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTCTURK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
     <x:t>MARBAS</x:t>
   </x:si>
   <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTCTURK</x:t>
+    <x:t>GLOBAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
     <x:t>FIBA</x:t>
   </x:si>
   <x:si>
-    <x:t>GLOBAL</x:t>
+    <x:t>INVEST AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PUSULA YAT.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEO MENKUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ATA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IKON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SEKER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLENDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TERA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BANK OF AMERICA</x:t>
   </x:si>
   <x:si>
     <x:t>QNB YATIRIM</x:t>
   </x:si>
   <x:si>
-    <x:t>TACIRLER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INVEST AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SEKER</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEO MENKUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IKON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PUSULA YAT.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ATA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TERA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLENDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BANK OF AMERICA</x:t>
-  </x:si>
-  <x:si>
     <x:t>GEDIK</x:t>
   </x:si>
   <x:si>
@@ -193,10 +196,10 @@
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
+    <x:t>A1 CAPITAL</x:t>
+  </x:si>
+  <x:si>
     <x:t>DENIZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>A1 CAPITAL</x:t>
   </x:si>
   <x:si>
     <x:t>TRIVE</x:t>
@@ -550,7 +553,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I55"/>
+  <x:dimension ref="A1:I56"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -587,28 +590,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>8953853</x:v>
+        <x:v>10945770</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>66.358</x:v>
+        <x:v>65.989</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>6628481</x:v>
+        <x:v>8777418</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>66.679</x:v>
+        <x:v>66.245</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>15582334</x:v>
+        <x:v>19723188</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>7.0729048162381</x:v>
+        <x:v>7.23809643760899</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>2325372</x:v>
+        <x:v>2168352</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>65.443</x:v>
+        <x:v>64.954</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -616,28 +619,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>5950082</x:v>
+        <x:v>7551815</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>66.425</x:v>
+        <x:v>66.001</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>4106812</x:v>
+        <x:v>5545714</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>66.02</x:v>
+        <x:v>65.537</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>10056894</x:v>
+        <x:v>13097529</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>4.56487802205986</x:v>
+        <x:v>4.80658491904962</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>1843270</x:v>
+        <x:v>2006101</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>67.327</x:v>
+        <x:v>67.282</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -645,28 +648,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>3923486</x:v>
+        <x:v>7077154</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>66.214</x:v>
+        <x:v>66.13</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>2379442</x:v>
+        <x:v>5467702</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>66.074</x:v>
+        <x:v>66.198</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>6302928</x:v>
+        <x:v>12544856</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>2.86093275934157</x:v>
+        <x:v>4.6037627144211</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>1544044</x:v>
+        <x:v>1609452</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>66.431</x:v>
+        <x:v>65.897</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -674,28 +677,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>5549577</x:v>
+        <x:v>4520689</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>66.602</x:v>
+        <x:v>65.94</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>4298064</x:v>
+        <x:v>2943864</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>66.695</x:v>
+        <x:v>65.718</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>9847641</x:v>
+        <x:v>7464553</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>4.46989696520969</x:v>
+        <x:v>2.73937227985879</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>1251513</x:v>
+        <x:v>1576825</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>66.283</x:v>
+        <x:v>66.355</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -703,28 +706,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>4693947</x:v>
+        <x:v>5898109</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>66.023</x:v>
+        <x:v>65.719</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>3649433</x:v>
+        <x:v>4652916</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>66.303</x:v>
+        <x:v>65.87</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>8343380</x:v>
+        <x:v>10551025</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>3.787104844865</x:v>
+        <x:v>3.87205843526023</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>1044514</x:v>
+        <x:v>1245193</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>65.047</x:v>
+        <x:v>65.157</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -732,28 +735,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>15391405</x:v>
+        <x:v>18089232</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>66.955</x:v>
+        <x:v>66.597</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>14371615</x:v>
+        <x:v>16960622</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>67.019</x:v>
+        <x:v>66.644</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>29763020</x:v>
+        <x:v>35049854</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>13.5095941021281</x:v>
+        <x:v>12.8627391969349</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>1019790</x:v>
+        <x:v>1128610</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>66.047</x:v>
+        <x:v>65.894</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -761,28 +764,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>2646055</x:v>
+        <x:v>3396130</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>66.232</x:v>
+        <x:v>65.815</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>2190716</x:v>
+        <x:v>2873064</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>66.788</x:v>
+        <x:v>66.171</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>4836771</x:v>
+        <x:v>6269194</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>2.19543624857103</x:v>
+        <x:v>2.30069453062454</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>455339</x:v>
+        <x:v>523066</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>63.558</x:v>
+        <x:v>63.863</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -790,28 +793,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>1562553</x:v>
+        <x:v>835613</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>66.919</x:v>
+        <x:v>64.621</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>1153009</x:v>
+        <x:v>398892</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>66.418</x:v>
+        <x:v>65.296</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>2715562</x:v>
+        <x:v>1234505</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>1.2326081284481</x:v>
+        <x:v>0.453043708892826</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>409544</x:v>
+        <x:v>436721</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>68.33</x:v>
+        <x:v>64.004</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -819,28 +822,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>1638419</x:v>
+        <x:v>1912947</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>66.497</x:v>
+        <x:v>66.41</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>1258951</x:v>
+        <x:v>1528607</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>66.296</x:v>
+        <x:v>65.925</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>2897370</x:v>
+        <x:v>3441554</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.31513175288271</x:v>
+        <x:v>1.26299560432314</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>379468</x:v>
+        <x:v>384340</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>67.165</x:v>
+        <x:v>68.337</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -848,28 +851,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>553635</x:v>
+        <x:v>1458150</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>64.879</x:v>
+        <x:v>65.994</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>269744</x:v>
+        <x:v>1097534</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>65.118</x:v>
+        <x:v>66.252</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>823379</x:v>
+        <x:v>2555684</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.373736135721985</x:v>
+        <x:v>0.937895397846144</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>283891</x:v>
+        <x:v>360616</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>64.651</x:v>
+        <x:v>65.208</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -877,28 +880,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>1480154</x:v>
+        <x:v>2066407</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>66.281</x:v>
+        <x:v>66.086</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>1270693</x:v>
+        <x:v>1732201</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>66.481</x:v>
+        <x:v>65.725</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>2750847</x:v>
+        <x:v>3798608</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>1.24862417883188</x:v>
+        <x:v>1.39402874589407</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>209461</x:v>
+        <x:v>334206</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>65.065</x:v>
+        <x:v>67.959</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -906,28 +909,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>2467793</x:v>
+        <x:v>7167571</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>66.635</x:v>
+        <x:v>66.562</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>2271142</x:v>
+        <x:v>6842458</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>66.406</x:v>
+        <x:v>66.196</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>4738935</x:v>
+        <x:v>14010029</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>2.1510279644461</x:v>
+        <x:v>5.14145791216403</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>196651</x:v>
+        <x:v>325113</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>69.276</x:v>
+        <x:v>74.259</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -935,28 +938,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>5235650</x:v>
+        <x:v>1898092</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>67.336</x:v>
+        <x:v>65.833</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>5052249</x:v>
+        <x:v>1600674</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>66.647</x:v>
+        <x:v>66.069</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>10287899</x:v>
+        <x:v>3498766</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>4.66973242815044</x:v>
+        <x:v>1.28399149876924</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>183401</x:v>
+        <x:v>297418</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>86.31</x:v>
+        <x:v>64.561</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -964,28 +967,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>553675</x:v>
+        <x:v>727425</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>65.826</x:v>
+        <x:v>65.308</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>392940</x:v>
+        <x:v>530056</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>65.235</x:v>
+        <x:v>64.957</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>946615</x:v>
+        <x:v>1257481</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.429673615815399</x:v>
+        <x:v>0.461475535621371</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>160735</x:v>
+        <x:v>197369</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>67.271</x:v>
+        <x:v>66.251</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -993,28 +996,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>262653</x:v>
+        <x:v>346615</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>66.219</x:v>
+        <x:v>65.626</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>142551</x:v>
+        <x:v>192943</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>66.467</x:v>
+        <x:v>65.806</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>405204</x:v>
+        <x:v>539558</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.183924264693527</x:v>
+        <x:v>0.198009208130219</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>120102</x:v>
+        <x:v>153672</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>65.925</x:v>
+        <x:v>65.4</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1022,28 +1025,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>262330</x:v>
+        <x:v>321366</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>66.099</x:v>
+        <x:v>66.004</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>160645</x:v>
+        <x:v>212670</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>66.161</x:v>
+        <x:v>65.799</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>422975</x:v>
+        <x:v>534036</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.191990616723291</x:v>
+        <x:v>0.195982721918736</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>101685</x:v>
+        <x:v>108696</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>66.001</x:v>
+        <x:v>66.404</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1051,28 +1054,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>217270</x:v>
+        <x:v>3147670</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>65.867</x:v>
+        <x:v>66.101</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>156384</x:v>
+        <x:v>3051168</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>64.842</x:v>
+        <x:v>65.873</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>373654</x:v>
+        <x:v>6198838</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>0.169603550803534</x:v>
+        <x:v>2.27487499714119</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>60886</x:v>
+        <x:v>96502</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>68.499</x:v>
+        <x:v>73.331</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1080,28 +1083,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>442298</x:v>
+        <x:v>519406</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>66.84</x:v>
+        <x:v>66.504</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>385792</x:v>
+        <x:v>439480</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>66.812</x:v>
+        <x:v>66.531</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>828090</x:v>
+        <x:v>958886</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.375874483840393</x:v>
+        <x:v>0.351895917671785</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>56506</x:v>
+        <x:v>79926</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>67.03</x:v>
+        <x:v>66.351</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1109,28 +1112,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>2484868</x:v>
+        <x:v>3033736</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>66.059</x:v>
+        <x:v>66.264</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>2439733</x:v>
+        <x:v>2967710</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>68.174</x:v>
+        <x:v>66.412</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>4924601</x:v>
+        <x:v>6001446</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>2.23530275573293</x:v>
+        <x:v>2.20243527127068</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>45135</x:v>
+        <x:v>66026</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>-48.256</x:v>
+        <x:v>59.657</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1138,28 +1141,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>2452723</x:v>
+        <x:v>325211</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>66.689</x:v>
+        <x:v>65.413</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>2414265</x:v>
+        <x:v>274904</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>66.827</x:v>
+        <x:v>64.302</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>4866988</x:v>
+        <x:v>600115</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>2.20915190662535</x:v>
+        <x:v>0.220232664397648</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>38458</x:v>
+        <x:v>50307</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>57.999</x:v>
+        <x:v>71.489</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1167,28 +1170,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>75230</x:v>
+        <x:v>107775</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>66.065</x:v>
+        <x:v>65.486</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>41186</x:v>
+        <x:v>78282</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>66.923</x:v>
+        <x:v>66.173</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>116416</x:v>
+        <x:v>186057</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0528418455853388</x:v>
+        <x:v>0.0682799610738495</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>34044</x:v>
+        <x:v>29493</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>65.027</x:v>
+        <x:v>63.663</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1196,28 +1199,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>239722</x:v>
+        <x:v>2927133</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>69.907</x:v>
+        <x:v>66.466</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>212708</x:v>
+        <x:v>2901625</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>70.615</x:v>
+        <x:v>66.278</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>452430</x:v>
+        <x:v>5828758</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>0.205360398898561</x:v>
+        <x:v>2.13906152065705</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>27014</x:v>
+        <x:v>25508</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>64.335</x:v>
+        <x:v>87.78</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1225,28 +1228,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>282060</x:v>
+        <x:v>333811</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>67.492</x:v>
+        <x:v>67.072</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>258515</x:v>
+        <x:v>316327</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>67.01</x:v>
+        <x:v>66.558</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>540575</x:v>
+        <x:v>650138</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.245369886246689</x:v>
+        <x:v>0.238590310134154</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>23545</x:v>
+        <x:v>17484</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>72.776</x:v>
+        <x:v>76.358</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1254,28 +1257,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>241285</x:v>
+        <x:v>301902</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>67.359</x:v>
+        <x:v>68.882</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>218179</x:v>
+        <x:v>285491</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>67.1</x:v>
+        <x:v>69.199</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>459464</x:v>
+        <x:v>587393</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.208553169152196</x:v>
+        <x:v>0.215563892651455</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>23106</x:v>
+        <x:v>16411</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>69.8</x:v>
+        <x:v>63.364</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1283,28 +1286,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>849536</x:v>
+        <x:v>42865</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>71.121</x:v>
+        <x:v>63.427</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>831189</x:v>
+        <x:v>28645</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>70.526</x:v>
+        <x:v>62.669</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>1680725</x:v>
+        <x:v>71510</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.762890074572383</x:v>
+        <x:v>0.0262430331371084</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>18347</x:v>
+        <x:v>14220</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>98.063</x:v>
+        <x:v>64.952</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1312,28 +1315,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>73787</x:v>
+        <x:v>2056967</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>62.706</x:v>
+        <x:v>65.411</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>55816</x:v>
+        <x:v>2049284</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>62.355</x:v>
+        <x:v>65.415</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>129603</x:v>
+        <x:v>4106251</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>0.0588274954765381</x:v>
+        <x:v>1.50692883599894</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>17971</x:v>
+        <x:v>7683</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>63.795</x:v>
+        <x:v>64.351</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1341,28 +1344,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>12298</x:v>
+        <x:v>18044</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>63.707</x:v>
+        <x:v>63.479</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>4558</x:v>
+        <x:v>11826</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>63.925</x:v>
+        <x:v>64.167</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>16856</x:v>
+        <x:v>29870</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.00765102863168697</x:v>
+        <x:v>0.01096181512803</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>7740</x:v>
+        <x:v>6218</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>63.579</x:v>
+        <x:v>62.172</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1370,28 +1373,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>1689354</x:v>
+        <x:v>105226</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>65.703</x:v>
+        <x:v>64.857</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>1683768</x:v>
+        <x:v>101164</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>65.703</x:v>
+        <x:v>65.496</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>3373122</x:v>
+        <x:v>206390</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>1.53107813242603</x:v>
+        <x:v>0.0757418488206937</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>5586</x:v>
+        <x:v>4062</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>65.66</x:v>
+        <x:v>48.943</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1399,28 +1402,28 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>3519</x:v>
+        <x:v>3769</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>65.477</x:v>
+        <x:v>65.27</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>731</x:v>
+        <x:v>1008</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>64.373</x:v>
+        <x:v>63.889</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>4250</x:v>
+        <x:v>4777</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00192909775063299</x:v>
+        <x:v>0.00175308305546031</x:v>
       </x:c>
       <x:c r="H30" s="0">
-        <x:v>2788</x:v>
+        <x:v>2761</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>65.766</x:v>
+        <x:v>65.774</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1428,28 +1431,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>7969</x:v>
+        <x:v>9379</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>66.371</x:v>
+        <x:v>65.714</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>6107</x:v>
+        <x:v>7465</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>66.741</x:v>
+        <x:v>66.479</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>14076</x:v>
+        <x:v>16844</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00638917175009645</x:v>
+        <x:v>0.00618148021481547</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>1862</x:v>
+        <x:v>1914</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>65.159</x:v>
+        <x:v>62.731</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1457,28 +1460,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>10348</x:v>
+        <x:v>10448</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>67.824</x:v>
+        <x:v>67.776</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>8720</x:v>
+        <x:v>8754</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>69.246</x:v>
+        <x:v>69.227</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>19068</x:v>
+        <x:v>19202</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0086550672727223</x:v>
+        <x:v>0.0070468287274333</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>1628</x:v>
+        <x:v>1694</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>60.21</x:v>
+        <x:v>60.279</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1501,7 +1504,7 @@
         <x:v>711</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.000322726706047071</x:v>
+        <x:v>0.000260925696552707</x:v>
       </x:c>
       <x:c r="H33" s="0">
         <x:v>711</x:v>
@@ -1515,28 +1518,28 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="0">
-        <x:v>28308</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>63.086</x:v>
+        <x:v>62.8</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>27737</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E34" s="0">
-        <x:v>62.645</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F34" s="0">
-        <x:v>56045</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>0.0254391255139355</x:v>
+        <x:v>5.68825358166942E-05</x:v>
       </x:c>
       <x:c r="H34" s="0">
-        <x:v>571</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>84.538</x:v>
+        <x:v>62.8</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1544,28 +1547,28 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>150</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>65.3</x:v>
+        <x:v>65.05</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E35" s="0">
-        <x:v>62.44</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>200</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>9.07810706180229E-05</x:v>
+        <x:v>0.000110095230612957</x:v>
       </x:c>
       <x:c r="H35" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>66.73</x:v>
+        <x:v>67.1</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1573,28 +1576,28 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="0">
-        <x:v>98032</x:v>
+        <x:v>82787</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>64.944</x:v>
+        <x:v>62.815</x:v>
       </x:c>
       <x:c r="D36" s="0">
-        <x:v>97969</x:v>
+        <x:v>82787</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>65.551</x:v>
+        <x:v>62.545</x:v>
       </x:c>
       <x:c r="F36" s="0">
-        <x:v>196001</x:v>
+        <x:v>165574</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.0889659031110155</x:v>
+        <x:v>0.0607630257116989</x:v>
       </x:c>
       <x:c r="H36" s="0">
-        <x:v>63</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>-879.889</x:v>
+        <x:v>62.815</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1617,7 +1620,7 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>5.9461601254805E-05</x:v>
+        <x:v>4.80749173676577E-05</x:v>
       </x:c>
       <x:c r="H37" s="0">
         <x:v>-131</x:v>
@@ -1631,28 +1634,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="0">
-        <x:v>583</x:v>
+        <x:v>40674</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>66.652</x:v>
+        <x:v>63.229</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>910</x:v>
+        <x:v>41066</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>66.549</x:v>
+        <x:v>63.994</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>1493</x:v>
+        <x:v>81740</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.000677680692163541</x:v>
+        <x:v>0.0299972805010102</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-327</x:v>
+        <x:v>-392</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>66.367</x:v>
+        <x:v>143.36</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1666,22 +1669,22 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>643</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>67.521</x:v>
+        <x:v>67.184</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>643</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.000291861142036944</x:v>
+        <x:v>0.000253586014511843</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-643</x:v>
+        <x:v>-691</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>67.521</x:v>
+        <x:v>67.184</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1689,10 +1692,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>276</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>70.38</x:v>
+        <x:v>68.698</x:v>
       </x:c>
       <x:c r="D40" s="0">
         <x:v>2301</x:v>
@@ -1701,16 +1704,16 @@
         <x:v>69.436</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>2577</x:v>
+        <x:v>2752</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.00116971409491323</x:v>
+        <x:v>0.00100994024882285</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-2025</x:v>
+        <x:v>-1850</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>69.307</x:v>
+        <x:v>69.616</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1718,28 +1721,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>531471</x:v>
+        <x:v>242069</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>65.328</x:v>
+        <x:v>67.353</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>540798</x:v>
+        <x:v>244396</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>65.371</x:v>
+        <x:v>66.608</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>1072269</x:v>
+        <x:v>486465</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.486708639052584</x:v>
+        <x:v>0.17852492120044</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-9327</x:v>
+        <x:v>-2327</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>67.814</x:v>
+        <x:v>-10.875</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1747,28 +1750,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>3016379</x:v>
+        <x:v>654357</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>66.59</x:v>
+        <x:v>65.241</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>3043611</x:v>
+        <x:v>656899</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>66.415</x:v>
+        <x:v>65.292</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>6059990</x:v>
+        <x:v>1311256</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>2.75066190067256</x:v>
+        <x:v>0.481210105708743</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-27232</x:v>
+        <x:v>-2542</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>47.025</x:v>
+        <x:v>78.421</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1776,28 +1779,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>5249447</x:v>
+        <x:v>455193</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>68.127</x:v>
+        <x:v>68.208</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>5277947</x:v>
+        <x:v>476299</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>68.153</x:v>
+        <x:v>69.303</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>10527394</x:v>
+        <x:v>931492</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>4.77844049068875</x:v>
+        <x:v>0.341842755180414</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-28500</x:v>
+        <x:v>-21106</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>72.854</x:v>
+        <x:v>92.928</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1805,28 +1808,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>2572001</x:v>
+        <x:v>6680531</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>66.799</x:v>
+        <x:v>67.391</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>2603113</x:v>
+        <x:v>6724581</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>66.531</x:v>
+        <x:v>67.43</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>5175114</x:v>
+        <x:v>13405112</x:v>
       </x:c>
       <x:c r="G44" s="0">
-        <x:v>2.3490119474516</x:v>
+        <x:v>4.91946299010837</x:v>
       </x:c>
       <x:c r="H44" s="0">
-        <x:v>-31112</x:v>
+        <x:v>-44050</x:v>
       </x:c>
       <x:c r="I44" s="0">
-        <x:v>44.406</x:v>
+        <x:v>73.409</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
@@ -1834,28 +1837,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="0">
-        <x:v>412662</x:v>
+        <x:v>3221770</x:v>
       </x:c>
       <x:c r="C45" s="0">
-        <x:v>68.696</x:v>
+        <x:v>66.43</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>449542</x:v>
+        <x:v>3280567</x:v>
       </x:c>
       <x:c r="E45" s="0">
-        <x:v>69.565</x:v>
+        <x:v>66.248</x:v>
       </x:c>
       <x:c r="F45" s="0">
-        <x:v>862204</x:v>
+        <x:v>6502337</x:v>
       </x:c>
       <x:c r="G45" s="0">
-        <x:v>0.391359011055709</x:v>
+        <x:v>2.3862543051272</x:v>
       </x:c>
       <x:c r="H45" s="0">
-        <x:v>-36880</x:v>
+        <x:v>-58797</x:v>
       </x:c>
       <x:c r="I45" s="0">
-        <x:v>79.291</x:v>
+        <x:v>56.242</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
@@ -1863,28 +1866,28 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B46" s="0">
-        <x:v>944090</x:v>
+        <x:v>896339</x:v>
       </x:c>
       <x:c r="C46" s="0">
-        <x:v>66.621</x:v>
+        <x:v>70.774</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>985745</x:v>
+        <x:v>959733</x:v>
       </x:c>
       <x:c r="E46" s="0">
-        <x:v>66.374</x:v>
+        <x:v>69.667</x:v>
       </x:c>
       <x:c r="F46" s="0">
-        <x:v>1929835</x:v>
+        <x:v>1856072</x:v>
       </x:c>
       <x:c r="G46" s="0">
-        <x:v>0.875962437080661</x:v>
+        <x:v>0.681148916247505</x:v>
       </x:c>
       <x:c r="H46" s="0">
-        <x:v>-41655</x:v>
+        <x:v>-63394</x:v>
       </x:c>
       <x:c r="I46" s="0">
-        <x:v>60.776</x:v>
+        <x:v>54.014</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
@@ -1892,28 +1895,28 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="0">
-        <x:v>731574</x:v>
+        <x:v>403620</x:v>
       </x:c>
       <x:c r="C47" s="0">
-        <x:v>68.087</x:v>
+        <x:v>70.278</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>836113</x:v>
+        <x:v>540618</x:v>
       </x:c>
       <x:c r="E47" s="0">
-        <x:v>68.43</x:v>
+        <x:v>69.842</x:v>
       </x:c>
       <x:c r="F47" s="0">
-        <x:v>1567687</x:v>
+        <x:v>944238</x:v>
       </x:c>
       <x:c r="G47" s="0">
-        <x:v>0.711581521269782</x:v>
+        <x:v>0.346520334545056</x:v>
       </x:c>
       <x:c r="H47" s="0">
-        <x:v>-104539</x:v>
+        <x:v>-136998</x:v>
       </x:c>
       <x:c r="I47" s="0">
-        <x:v>70.833</x:v>
+        <x:v>68.56</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
@@ -1921,28 +1924,28 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B48" s="0">
-        <x:v>385465</x:v>
+        <x:v>842278</x:v>
       </x:c>
       <x:c r="C48" s="0">
-        <x:v>70.633</x:v>
+        <x:v>67.49</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>522463</x:v>
+        <x:v>987119</x:v>
       </x:c>
       <x:c r="E48" s="0">
-        <x:v>70.091</x:v>
+        <x:v>67.758</x:v>
       </x:c>
       <x:c r="F48" s="0">
-        <x:v>907928</x:v>
+        <x:v>1829397</x:v>
       </x:c>
       <x:c r="G48" s="0">
-        <x:v>0.412113379420402</x:v>
+        <x:v>0.671359615325503</x:v>
       </x:c>
       <x:c r="H48" s="0">
-        <x:v>-136998</x:v>
+        <x:v>-144841</x:v>
       </x:c>
       <x:c r="I48" s="0">
-        <x:v>68.564</x:v>
+        <x:v>69.321</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
@@ -1956,22 +1959,22 @@
         <x:v>68.761</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>961096</x:v>
+        <x:v>1013174</x:v>
       </x:c>
       <x:c r="E49" s="0">
-        <x:v>66.639</x:v>
+        <x:v>66.484</x:v>
       </x:c>
       <x:c r="F49" s="0">
-        <x:v>1721271</x:v>
+        <x:v>1773349</x:v>
       </x:c>
       <x:c r="G49" s="0">
-        <x:v>0.781294121018775</x:v>
+        <x:v>0.650790890374186</x:v>
       </x:c>
       <x:c r="H49" s="0">
-        <x:v>-200921</x:v>
+        <x:v>-252999</x:v>
       </x:c>
       <x:c r="I49" s="0">
-        <x:v>58.61</x:v>
+        <x:v>59.641</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
@@ -1979,28 +1982,28 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B50" s="0">
-        <x:v>2389564</x:v>
+        <x:v>2611785</x:v>
       </x:c>
       <x:c r="C50" s="0">
-        <x:v>66.601</x:v>
+        <x:v>65.941</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>3306477</x:v>
+        <x:v>3416617</x:v>
       </x:c>
       <x:c r="E50" s="0">
-        <x:v>65.233</x:v>
+        <x:v>67.267</x:v>
       </x:c>
       <x:c r="F50" s="0">
-        <x:v>5696041</x:v>
+        <x:v>6028402</x:v>
       </x:c>
       <x:c r="G50" s="0">
-        <x:v>2.58546350132077</x:v>
+        <x:v>2.21232769472536</x:v>
       </x:c>
       <x:c r="H50" s="0">
-        <x:v>-916913</x:v>
+        <x:v>-804832</x:v>
       </x:c>
       <x:c r="I50" s="0">
-        <x:v>61.668</x:v>
+        <x:v>71.568</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
@@ -2008,28 +2011,28 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="0">
-        <x:v>2536706</x:v>
+        <x:v>3851837</x:v>
       </x:c>
       <x:c r="C51" s="0">
-        <x:v>66.304</x:v>
+        <x:v>65.793</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>3817598</x:v>
+        <x:v>4773970</x:v>
       </x:c>
       <x:c r="E51" s="0">
-        <x:v>66.931</x:v>
+        <x:v>65.078</x:v>
       </x:c>
       <x:c r="F51" s="0">
-        <x:v>6354304</x:v>
+        <x:v>8625807</x:v>
       </x:c>
       <x:c r="G51" s="0">
-        <x:v>2.88425260076193</x:v>
+        <x:v>3.16553403629285</x:v>
       </x:c>
       <x:c r="H51" s="0">
-        <x:v>-1280892</x:v>
+        <x:v>-922133</x:v>
       </x:c>
       <x:c r="I51" s="0">
-        <x:v>68.172</x:v>
+        <x:v>62.088</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
@@ -2037,28 +2040,28 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B52" s="0">
-        <x:v>3125726</x:v>
+        <x:v>3073536</x:v>
       </x:c>
       <x:c r="C52" s="0">
-        <x:v>67.611</x:v>
+        <x:v>65.972</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>4605483</x:v>
+        <x:v>4370283</x:v>
       </x:c>
       <x:c r="E52" s="0">
-        <x:v>66.174</x:v>
+        <x:v>66.614</x:v>
       </x:c>
       <x:c r="F52" s="0">
-        <x:v>7731209</x:v>
+        <x:v>7443819</x:v>
       </x:c>
       <x:c r="G52" s="0">
-        <x:v>3.50923715095847</x:v>
+        <x:v>2.73176323148702</x:v>
       </x:c>
       <x:c r="H52" s="0">
-        <x:v>-1479757</x:v>
+        <x:v>-1296747</x:v>
       </x:c>
       <x:c r="I52" s="0">
-        <x:v>63.137</x:v>
+        <x:v>68.136</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
@@ -2066,28 +2069,28 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B53" s="0">
-        <x:v>4869738</x:v>
+        <x:v>3805373</x:v>
       </x:c>
       <x:c r="C53" s="0">
-        <x:v>68.57</x:v>
+        <x:v>66.993</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>6393194</x:v>
+        <x:v>5172246</x:v>
       </x:c>
       <x:c r="E53" s="0">
-        <x:v>67.713</x:v>
+        <x:v>65.981</x:v>
       </x:c>
       <x:c r="F53" s="0">
-        <x:v>11262932</x:v>
+        <x:v>8977619</x:v>
       </x:c>
       <x:c r="G53" s="0">
-        <x:v>5.11230512628995</x:v>
+        <x:v>3.29464344720087</x:v>
       </x:c>
       <x:c r="H53" s="0">
-        <x:v>-1523456</x:v>
+        <x:v>-1366873</x:v>
       </x:c>
       <x:c r="I53" s="0">
-        <x:v>64.973</x:v>
+        <x:v>63.163</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
@@ -2095,28 +2098,28 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B54" s="0">
-        <x:v>11374314</x:v>
+        <x:v>14442774</x:v>
       </x:c>
       <x:c r="C54" s="0">
-        <x:v>67.183</x:v>
+        <x:v>66.695</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>13380001</x:v>
+        <x:v>16405945</x:v>
       </x:c>
       <x:c r="E54" s="0">
-        <x:v>67.451</x:v>
+        <x:v>66.878</x:v>
       </x:c>
       <x:c r="F54" s="0">
-        <x:v>24754315</x:v>
+        <x:v>30848719</x:v>
       </x:c>
       <x:c r="G54" s="0">
-        <x:v>11.2361160905789</x:v>
+        <x:v>11.3209894413976</x:v>
       </x:c>
       <x:c r="H54" s="0">
-        <x:v>-2005687</x:v>
+        <x:v>-1963171</x:v>
       </x:c>
       <x:c r="I54" s="0">
-        <x:v>68.973</x:v>
+        <x:v>68.223</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
@@ -2124,28 +2127,57 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B55" s="0">
-        <x:v>920217</x:v>
+        <x:v>5963995</x:v>
       </x:c>
       <x:c r="C55" s="0">
-        <x:v>67.101</x:v>
+        <x:v>67.859</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>4988063</x:v>
+        <x:v>8077961</x:v>
       </x:c>
       <x:c r="E55" s="0">
-        <x:v>66.85</x:v>
+        <x:v>66.892</x:v>
       </x:c>
       <x:c r="F55" s="0">
-        <x:v>5908280</x:v>
+        <x:v>14041956</x:v>
       </x:c>
       <x:c r="G55" s="0">
-        <x:v>2.68179991955526</x:v>
+        <x:v>5.15317461358996</x:v>
       </x:c>
       <x:c r="H55" s="0">
-        <x:v>-4067846</x:v>
+        <x:v>-2113966</x:v>
       </x:c>
       <x:c r="I55" s="0">
-        <x:v>66.793</x:v>
+        <x:v>64.164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:9">
+      <x:c r="A56" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B56" s="0">
+        <x:v>1058647</x:v>
+      </x:c>
+      <x:c r="C56" s="0">
+        <x:v>66.664</x:v>
+      </x:c>
+      <x:c r="D56" s="0">
+        <x:v>5137732</x:v>
+      </x:c>
+      <x:c r="E56" s="0">
+        <x:v>66.768</x:v>
+      </x:c>
+      <x:c r="F56" s="0">
+        <x:v>6196379</x:v>
+      </x:c>
+      <x:c r="G56" s="0">
+        <x:v>2.27397258323427</x:v>
+      </x:c>
+      <x:c r="H56" s="0">
+        <x:v>-4079085</x:v>
+      </x:c>
+      <x:c r="I56" s="0">
+        <x:v>66.795</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/app/halka-arz/data/ekdemir-araci-kurum.xlsx
+++ b/app/halka-arz/data/ekdemir-araci-kurum.xlsx
@@ -64,36 +64,36 @@
     <x:t>KUVEYT TURK</x:t>
   </x:si>
   <x:si>
+    <x:t>MARBAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OSMANLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YATIRIM FINANSMAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OYAK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YAPI KREDI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TEB</x:t>
+  </x:si>
+  <x:si>
     <x:t>PHILLIP</x:t>
   </x:si>
   <x:si>
-    <x:t>YATIRIM FINANSMAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OSMANLI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YAPI KREDI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OYAK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TEB</x:t>
+    <x:t>ING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GLOBAL</x:t>
   </x:si>
   <x:si>
     <x:t>BTCTURK</x:t>
   </x:si>
   <x:si>
-    <x:t>ING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MARBAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GLOBAL</x:t>
-  </x:si>
-  <x:si>
     <x:t>TACIRLER</x:t>
   </x:si>
   <x:si>
@@ -103,75 +103,75 @@
     <x:t>INVEST AZ</x:t>
   </x:si>
   <x:si>
+    <x:t>BULLS YATIRIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTEGRAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BURGAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ACAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANADOLU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSBC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ICBC TURKEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DESTEK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEKSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALTERNATIF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEO MENKUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NCM INVESTMENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GCM</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ALLBATROSS </x:t>
+  </x:si>
+  <x:si>
+    <x:t>TURKISH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DINAMIK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHLATCI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIZIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PIRAMIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNLU</x:t>
+  </x:si>
+  <x:si>
     <x:t>PUSULA YAT.</x:t>
   </x:si>
   <x:si>
-    <x:t>BURGAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BULLS YATIRIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTEGRAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ACAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HSBC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ICBC TURKEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DESTEK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANADOLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALTERNATIF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEO MENKUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NCM INVESTMENT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GCM</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ALLBATROSS </x:t>
-  </x:si>
-  <x:si>
-    <x:t>TURKISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DINAMIK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIZIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PIRAMIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNLU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHLATCI</x:t>
-  </x:si>
-  <x:si>
     <x:t>ATA</x:t>
   </x:si>
   <x:si>
     <x:t>IKON</x:t>
   </x:si>
   <x:si>
-    <x:t>MEKSA</x:t>
-  </x:si>
-  <x:si>
     <x:t>SEKER</x:t>
   </x:si>
   <x:si>
@@ -196,10 +196,10 @@
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
+    <x:t>DENIZ</x:t>
+  </x:si>
+  <x:si>
     <x:t>A1 CAPITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DENIZ</x:t>
   </x:si>
   <x:si>
     <x:t>TRIVE</x:t>
@@ -590,28 +590,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>10945770</x:v>
+        <x:v>11268995</x:v>
       </x:c>
       <x:c r="C2" s="0">
-        <x:v>65.989</x:v>
+        <x:v>65.8944513498856</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>8777418</x:v>
+        <x:v>9207854</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>66.245</x:v>
+        <x:v>66.0837018011762</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>19723188</x:v>
+        <x:v>20476849</x:v>
       </x:c>
       <x:c r="G2" s="0">
-        <x:v>7.23809643760899</x:v>
+        <x:v>7.326409802951</x:v>
       </x:c>
       <x:c r="H2" s="0">
-        <x:v>2168352</x:v>
+        <x:v>2061141</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>64.954</x:v>
+        <x:v>65.0490018998393</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -619,28 +619,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>7551815</x:v>
+        <x:v>7741387</x:v>
       </x:c>
       <x:c r="C3" s="0">
-        <x:v>66.001</x:v>
+        <x:v>65.9213989256204</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>5545714</x:v>
+        <x:v>5703337</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>65.537</x:v>
+        <x:v>65.4613998080857</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>13097529</x:v>
+        <x:v>13444724</x:v>
       </x:c>
       <x:c r="G3" s="0">
-        <x:v>4.80658491904962</x:v>
+        <x:v>4.81038648629829</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>2006101</x:v>
+        <x:v>2038050</x:v>
       </x:c>
       <x:c r="I3" s="0">
-        <x:v>67.282</x:v>
+        <x:v>67.2086735199646</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -648,28 +648,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>7077154</x:v>
+        <x:v>7294518</x:v>
       </x:c>
       <x:c r="C4" s="0">
-        <x:v>66.13</x:v>
+        <x:v>66.0294178254102</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>5467702</x:v>
+        <x:v>5643878</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>66.198</x:v>
+        <x:v>66.0897350143413</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>12544856</x:v>
+        <x:v>12938396</x:v>
       </x:c>
       <x:c r="G4" s="0">
-        <x:v>4.6037627144211</x:v>
+        <x:v>4.62922744065076</x:v>
       </x:c>
       <x:c r="H4" s="0">
-        <x:v>1609452</x:v>
+        <x:v>1650640</x:v>
       </x:c>
       <x:c r="I4" s="0">
-        <x:v>65.897</x:v>
+        <x:v>65.8231809381241</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -677,28 +677,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>4520689</x:v>
+        <x:v>4606120</x:v>
       </x:c>
       <x:c r="C5" s="0">
-        <x:v>65.94</x:v>
+        <x:v>65.8815797535973</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>2943864</x:v>
+        <x:v>3029978</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>65.718</x:v>
+        <x:v>65.6309305753659</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>7464553</x:v>
+        <x:v>7636098</x:v>
       </x:c>
       <x:c r="G5" s="0">
-        <x:v>2.73937227985879</x:v>
+        <x:v>2.73211875730951</x:v>
       </x:c>
       <x:c r="H5" s="0">
-        <x:v>1576825</x:v>
+        <x:v>1576142</x:v>
       </x:c>
       <x:c r="I5" s="0">
-        <x:v>66.355</x:v>
+        <x:v>66.363428150353</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -706,28 +706,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>5898109</x:v>
+        <x:v>6097326</x:v>
       </x:c>
       <x:c r="C6" s="0">
-        <x:v>65.719</x:v>
+        <x:v>65.6218712615846</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>4652916</x:v>
+        <x:v>4884135</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>65.87</x:v>
+        <x:v>65.7265032526267</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>10551025</x:v>
+        <x:v>10981461</x:v>
       </x:c>
       <x:c r="G6" s="0">
-        <x:v>3.87205843526023</x:v>
+        <x:v>3.92905585820964</x:v>
       </x:c>
       <x:c r="H6" s="0">
-        <x:v>1245193</x:v>
+        <x:v>1213191</x:v>
       </x:c>
       <x:c r="I6" s="0">
-        <x:v>65.157</x:v>
+        <x:v>65.2006376969039</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -735,28 +735,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>18089232</x:v>
+        <x:v>18304583</x:v>
       </x:c>
       <x:c r="C7" s="0">
-        <x:v>66.597</x:v>
+        <x:v>66.5504983411877</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>16960622</x:v>
+        <x:v>17140816</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>66.644</x:v>
+        <x:v>66.6027696972276</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>35049854</x:v>
+        <x:v>35445399</x:v>
       </x:c>
       <x:c r="G7" s="0">
-        <x:v>12.8627391969349</x:v>
+        <x:v>12.6820058448988</x:v>
       </x:c>
       <x:c r="H7" s="0">
-        <x:v>1128610</x:v>
+        <x:v>1163767</x:v>
       </x:c>
       <x:c r="I7" s="0">
-        <x:v>65.894</x:v>
+        <x:v>65.7806073785204</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -764,28 +764,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>3396130</x:v>
+        <x:v>3457090</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>65.815</x:v>
+        <x:v>65.759676865956</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>2873064</x:v>
+        <x:v>2950090</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>66.171</x:v>
+        <x:v>66.0853058503872</x:v>
       </x:c>
       <x:c r="F8" s="0">
-        <x:v>6269194</x:v>
+        <x:v>6407180</x:v>
       </x:c>
       <x:c r="G8" s="0">
-        <x:v>2.30069453062454</x:v>
+        <x:v>2.29242430616506</x:v>
       </x:c>
       <x:c r="H8" s="0">
-        <x:v>523066</x:v>
+        <x:v>507000</x:v>
       </x:c>
       <x:c r="I8" s="0">
-        <x:v>63.863</x:v>
+        <x:v>63.8649336496236</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -793,28 +793,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>835613</x:v>
+        <x:v>844014</x:v>
       </x:c>
       <x:c r="C9" s="0">
-        <x:v>64.621</x:v>
+        <x:v>64.6020594379652</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>398892</x:v>
+        <x:v>407272</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>65.296</x:v>
+        <x:v>65.2382179573206</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>1234505</x:v>
+        <x:v>1251286</x:v>
       </x:c>
       <x:c r="G9" s="0">
-        <x:v>0.453043708892826</x:v>
+        <x:v>0.447697495678918</x:v>
       </x:c>
       <x:c r="H9" s="0">
-        <x:v>436721</x:v>
+        <x:v>436742</x:v>
       </x:c>
       <x:c r="I9" s="0">
-        <x:v>64.004</x:v>
+        <x:v>64.0088269288525</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -822,28 +822,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>1912947</x:v>
+        <x:v>3594231</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>66.41</x:v>
+        <x:v>65.7161088843088</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>1528607</x:v>
+        <x:v>3178806</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>65.925</x:v>
+        <x:v>65.7569944995567</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>3441554</x:v>
+        <x:v>6773037</x:v>
       </x:c>
       <x:c r="G10" s="0">
-        <x:v>1.26299560432314</x:v>
+        <x:v>2.42332424644777</x:v>
       </x:c>
       <x:c r="H10" s="0">
-        <x:v>384340</x:v>
+        <x:v>415425</x:v>
       </x:c>
       <x:c r="I10" s="0">
-        <x:v>68.337</x:v>
+        <x:v>65.4032547251613</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -851,28 +851,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>1458150</x:v>
+        <x:v>2138821</x:v>
       </x:c>
       <x:c r="C11" s="0">
-        <x:v>65.994</x:v>
+        <x:v>65.963773187528</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>1097534</x:v>
+        <x:v>1771509</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>66.252</x:v>
+        <x:v>65.6606519183075</x:v>
       </x:c>
       <x:c r="F11" s="0">
-        <x:v>2555684</x:v>
+        <x:v>3910330</x:v>
       </x:c>
       <x:c r="G11" s="0">
-        <x:v>0.937895397846144</x:v>
+        <x:v>1.39907658862813</x:v>
       </x:c>
       <x:c r="H11" s="0">
-        <x:v>360616</x:v>
+        <x:v>367312</x:v>
       </x:c>
       <x:c r="I11" s="0">
-        <x:v>65.208</x:v>
+        <x:v>67.4256967198804</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -880,28 +880,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>2066407</x:v>
+        <x:v>1502884</x:v>
       </x:c>
       <x:c r="C12" s="0">
-        <x:v>66.086</x:v>
+        <x:v>65.8952505858874</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>1732201</x:v>
+        <x:v>1141138</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>65.725</x:v>
+        <x:v>66.1152689840231</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>3798608</x:v>
+        <x:v>2644022</x:v>
       </x:c>
       <x:c r="G12" s="0">
-        <x:v>1.39402874589407</x:v>
+        <x:v>0.94600437303699</x:v>
       </x:c>
       <x:c r="H12" s="0">
-        <x:v>334206</x:v>
+        <x:v>361746</x:v>
       </x:c>
       <x:c r="I12" s="0">
-        <x:v>67.959</x:v>
+        <x:v>65.2011963190489</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -909,28 +909,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>7167571</x:v>
+        <x:v>1957363</x:v>
       </x:c>
       <x:c r="C13" s="0">
-        <x:v>66.562</x:v>
+        <x:v>65.7404387439921</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>6842458</x:v>
+        <x:v>1660079</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>66.196</x:v>
+        <x:v>65.9487180765282</x:v>
       </x:c>
       <x:c r="F13" s="0">
-        <x:v>14010029</x:v>
+        <x:v>3617442</x:v>
       </x:c>
       <x:c r="G13" s="0">
-        <x:v>5.14145791216403</x:v>
+        <x:v>1.29428421972573</x:v>
       </x:c>
       <x:c r="H13" s="0">
-        <x:v>325113</x:v>
+        <x:v>297284</x:v>
       </x:c>
       <x:c r="I13" s="0">
-        <x:v>74.259</x:v>
+        <x:v>64.5773753228959</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -938,28 +938,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>1898092</x:v>
+        <x:v>7331015</x:v>
       </x:c>
       <x:c r="C14" s="0">
-        <x:v>65.833</x:v>
+        <x:v>66.4755052406975</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>1600674</x:v>
+        <x:v>7089128</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>66.069</x:v>
+        <x:v>66.0779820390766</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>3498766</x:v>
+        <x:v>14420143</x:v>
       </x:c>
       <x:c r="G14" s="0">
-        <x:v>1.28399149876924</x:v>
+        <x:v>5.15938155500171</x:v>
       </x:c>
       <x:c r="H14" s="0">
-        <x:v>297418</x:v>
+        <x:v>241887</x:v>
       </x:c>
       <x:c r="I14" s="0">
-        <x:v>64.561</x:v>
+        <x:v>78.1259571428653</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -967,28 +967,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>727425</x:v>
+        <x:v>734648</x:v>
       </x:c>
       <x:c r="C15" s="0">
-        <x:v>65.308</x:v>
+        <x:v>65.2818589313011</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>530056</x:v>
+        <x:v>548188</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>64.957</x:v>
+        <x:v>64.8897684570999</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>1257481</x:v>
+        <x:v>1282836</x:v>
       </x:c>
       <x:c r="G15" s="0">
-        <x:v>0.461475535621371</x:v>
+        <x:v>0.458985767096219</x:v>
       </x:c>
       <x:c r="H15" s="0">
-        <x:v>197369</x:v>
+        <x:v>186460</x:v>
       </x:c>
       <x:c r="I15" s="0">
-        <x:v>66.251</x:v>
+        <x:v>66.4345956730763</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -996,28 +996,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>346615</x:v>
+        <x:v>1961688</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>65.626</x:v>
+        <x:v>66.3241913921489</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>192943</x:v>
+        <x:v>1805332</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>65.806</x:v>
+        <x:v>65.390753522653</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>539558</x:v>
+        <x:v>3767020</x:v>
       </x:c>
       <x:c r="G16" s="0">
-        <x:v>0.198009208130219</x:v>
+        <x:v>1.34780171773072</x:v>
       </x:c>
       <x:c r="H16" s="0">
-        <x:v>153672</x:v>
+        <x:v>156356</x:v>
       </x:c>
       <x:c r="I16" s="0">
-        <x:v>65.4</x:v>
+        <x:v>77.1019374064545</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1025,28 +1025,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>321366</x:v>
+        <x:v>328783</x:v>
       </x:c>
       <x:c r="C17" s="0">
-        <x:v>66.004</x:v>
+        <x:v>65.9232290928143</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>212670</x:v>
+        <x:v>227809</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>65.799</x:v>
+        <x:v>65.6134122886664</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>534036</x:v>
+        <x:v>556592</x:v>
       </x:c>
       <x:c r="G17" s="0">
-        <x:v>0.195982721918736</x:v>
+        <x:v>0.199142997296318</x:v>
       </x:c>
       <x:c r="H17" s="0">
-        <x:v>108696</x:v>
+        <x:v>100974</x:v>
       </x:c>
       <x:c r="I17" s="0">
-        <x:v>66.404</x:v>
+        <x:v>66.622211566878</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1054,28 +1054,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>3147670</x:v>
+        <x:v>544550</x:v>
       </x:c>
       <x:c r="C18" s="0">
-        <x:v>66.101</x:v>
+        <x:v>66.3463041071462</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>3051168</x:v>
+        <x:v>444130</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>65.873</x:v>
+        <x:v>66.4911747780299</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>6198838</x:v>
+        <x:v>988680</x:v>
       </x:c>
       <x:c r="G18" s="0">
-        <x:v>2.27487499714119</x:v>
+        <x:v>0.353739720597715</x:v>
       </x:c>
       <x:c r="H18" s="0">
-        <x:v>96502</x:v>
+        <x:v>100420</x:v>
       </x:c>
       <x:c r="I18" s="0">
-        <x:v>73.331</x:v>
+        <x:v>65.7055810334601</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
@@ -1083,28 +1083,28 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>519406</x:v>
+        <x:v>350179</x:v>
       </x:c>
       <x:c r="C19" s="0">
-        <x:v>66.504</x:v>
+        <x:v>65.5923034732873</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>439480</x:v>
+        <x:v>259833</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>66.531</x:v>
+        <x:v>64.9646097804476</x:v>
       </x:c>
       <x:c r="F19" s="0">
-        <x:v>958886</x:v>
+        <x:v>610012</x:v>
       </x:c>
       <x:c r="G19" s="0">
-        <x:v>0.351895917671785</x:v>
+        <x:v>0.218256133876738</x:v>
       </x:c>
       <x:c r="H19" s="0">
-        <x:v>79926</x:v>
+        <x:v>90346</x:v>
       </x:c>
       <x:c r="I19" s="0">
-        <x:v>66.351</x:v>
+        <x:v>67.3975359715895</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1112,28 +1112,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>3033736</x:v>
+        <x:v>3072950</x:v>
       </x:c>
       <x:c r="C20" s="0">
-        <x:v>66.264</x:v>
+        <x:v>66.219959418085</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>2967710</x:v>
+        <x:v>2983752</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>66.412</x:v>
+        <x:v>66.3923187195783</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>6001446</x:v>
+        <x:v>6056702</x:v>
       </x:c>
       <x:c r="G20" s="0">
-        <x:v>2.20243527127068</x:v>
+        <x:v>2.16702681678968</x:v>
       </x:c>
       <x:c r="H20" s="0">
-        <x:v>66026</x:v>
+        <x:v>89198</x:v>
       </x:c>
       <x:c r="I20" s="0">
-        <x:v>59.657</x:v>
+        <x:v>60.4543883228877</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
@@ -1141,28 +1141,28 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>325211</x:v>
+        <x:v>335697</x:v>
       </x:c>
       <x:c r="C21" s="0">
-        <x:v>65.413</x:v>
+        <x:v>65.327612277106</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>274904</x:v>
+        <x:v>283348</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>64.302</x:v>
+        <x:v>64.2418875388464</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>600115</x:v>
+        <x:v>619045</x:v>
       </x:c>
       <x:c r="G21" s="0">
-        <x:v>0.220232664397648</x:v>
+        <x:v>0.221488050064138</x:v>
       </x:c>
       <x:c r="H21" s="0">
-        <x:v>50307</x:v>
+        <x:v>52349</x:v>
       </x:c>
       <x:c r="I21" s="0">
-        <x:v>71.489</x:v>
+        <x:v>71.2042848618042</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
@@ -1170,28 +1170,28 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>107775</x:v>
+        <x:v>110703</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>65.486</x:v>
+        <x:v>65.40074727416</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>78282</x:v>
+        <x:v>79533</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>66.173</x:v>
+        <x:v>66.1271988322635</x:v>
       </x:c>
       <x:c r="F22" s="0">
-        <x:v>186057</x:v>
+        <x:v>190236</x:v>
       </x:c>
       <x:c r="G22" s="0">
-        <x:v>0.0682799610738495</x:v>
+        <x:v>0.0680645198523556</x:v>
       </x:c>
       <x:c r="H22" s="0">
-        <x:v>29493</x:v>
+        <x:v>31170</x:v>
       </x:c>
       <x:c r="I22" s="0">
-        <x:v>63.663</x:v>
+        <x:v>63.5471421483774</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
@@ -1199,28 +1199,28 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>2927133</x:v>
+        <x:v>305170</x:v>
       </x:c>
       <x:c r="C23" s="0">
-        <x:v>66.466</x:v>
+        <x:v>68.8194613106626</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>2901625</x:v>
+        <x:v>288264</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>66.278</x:v>
+        <x:v>69.1392773678336</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>5828758</x:v>
+        <x:v>593434</x:v>
       </x:c>
       <x:c r="G23" s="0">
-        <x:v>2.13906152065705</x:v>
+        <x:v>0.212324692876547</x:v>
       </x:c>
       <x:c r="H23" s="0">
-        <x:v>25508</x:v>
+        <x:v>16906</x:v>
       </x:c>
       <x:c r="I23" s="0">
-        <x:v>87.78</x:v>
+        <x:v>63.3662816168048</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
@@ -1228,28 +1228,28 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>333811</x:v>
+        <x:v>42865</x:v>
       </x:c>
       <x:c r="C24" s="0">
-        <x:v>67.072</x:v>
+        <x:v>63.4265949620814</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>316327</x:v>
+        <x:v>28645</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>66.558</x:v>
+        <x:v>62.6693889488078</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>650138</x:v>
+        <x:v>71510</x:v>
       </x:c>
       <x:c r="G24" s="0">
-        <x:v>0.238590310134154</x:v>
+        <x:v>0.0255855559128764</x:v>
       </x:c>
       <x:c r="H24" s="0">
-        <x:v>17484</x:v>
+        <x:v>14220</x:v>
       </x:c>
       <x:c r="I24" s="0">
-        <x:v>76.358</x:v>
+        <x:v>64.9519231090734</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
@@ -1257,28 +1257,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>301902</x:v>
+        <x:v>344735</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>68.882</x:v>
+        <x:v>66.9494396696326</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>285491</x:v>
+        <x:v>331649</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>69.199</x:v>
+        <x:v>66.3984171419466</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>587393</x:v>
+        <x:v>676384</x:v>
       </x:c>
       <x:c r="G25" s="0">
-        <x:v>0.215563892651455</x:v>
+        <x:v>0.24200336527164</x:v>
       </x:c>
       <x:c r="H25" s="0">
-        <x:v>16411</x:v>
+        <x:v>13086</x:v>
       </x:c>
       <x:c r="I25" s="0">
-        <x:v>63.364</x:v>
+        <x:v>80.9144458047808</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
@@ -1286,28 +1286,28 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>42865</x:v>
+        <x:v>2128061</x:v>
       </x:c>
       <x:c r="C26" s="0">
-        <x:v>63.427</x:v>
+        <x:v>65.3156255769937</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>28645</x:v>
+        <x:v>2122663</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>62.669</x:v>
+        <x:v>65.317517251232</x:v>
       </x:c>
       <x:c r="F26" s="0">
-        <x:v>71510</x:v>
+        <x:v>4250724</x:v>
       </x:c>
       <x:c r="G26" s="0">
-        <x:v>0.0262430331371084</x:v>
+        <x:v>1.5208661246288</x:v>
       </x:c>
       <x:c r="H26" s="0">
-        <x:v>14220</x:v>
+        <x:v>5398</x:v>
       </x:c>
       <x:c r="I26" s="0">
-        <x:v>64.952</x:v>
+        <x:v>64.5717599020043</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
@@ -1315,28 +1315,28 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>2056967</x:v>
+        <x:v>11975</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>65.411</x:v>
+        <x:v>64.9305015643604</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>2049284</x:v>
+        <x:v>7465</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>65.415</x:v>
+        <x:v>66.4785737335961</x:v>
       </x:c>
       <x:c r="F27" s="0">
-        <x:v>4106251</x:v>
+        <x:v>19440</x:v>
       </x:c>
       <x:c r="G27" s="0">
-        <x:v>1.50692883599894</x:v>
+        <x:v>0.0069554357005498</x:v>
       </x:c>
       <x:c r="H27" s="0">
-        <x:v>7683</x:v>
+        <x:v>4510</x:v>
       </x:c>
       <x:c r="I27" s="0">
-        <x:v>64.351</x:v>
+        <x:v>62.3681160336852</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
@@ -1344,28 +1344,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>18044</x:v>
+        <x:v>18398</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>63.479</x:v>
+        <x:v>63.4555741890784</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>11826</x:v>
+        <x:v>13888</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>64.167</x:v>
+        <x:v>64.0274951655744</x:v>
       </x:c>
       <x:c r="F28" s="0">
-        <x:v>29870</x:v>
+        <x:v>32286</x:v>
       </x:c>
       <x:c r="G28" s="0">
-        <x:v>0.01096181512803</x:v>
+        <x:v>0.0115516047853884</x:v>
       </x:c>
       <x:c r="H28" s="0">
-        <x:v>6218</x:v>
+        <x:v>4510</x:v>
       </x:c>
       <x:c r="I28" s="0">
-        <x:v>62.172</x:v>
+        <x:v>61.6944126543608</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
@@ -1373,28 +1373,28 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>105226</x:v>
+        <x:v>105696</x:v>
       </x:c>
       <x:c r="C29" s="0">
-        <x:v>64.857</x:v>
+        <x:v>64.8483008938488</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>101164</x:v>
+        <x:v>101325</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>65.496</x:v>
+        <x:v>65.4917323142842</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>206390</x:v>
+        <x:v>207021</x:v>
       </x:c>
       <x:c r="G29" s="0">
-        <x:v>0.0757418488206937</x:v>
+        <x:v>0.074070023362321</x:v>
       </x:c>
       <x:c r="H29" s="0">
-        <x:v>4062</x:v>
+        <x:v>4371</x:v>
       </x:c>
       <x:c r="I29" s="0">
-        <x:v>48.943</x:v>
+        <x:v>49.9327921600097</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
@@ -1405,25 +1405,25 @@
         <x:v>3769</x:v>
       </x:c>
       <x:c r="C30" s="0">
-        <x:v>65.27</x:v>
+        <x:v>65.2698853174677</x:v>
       </x:c>
       <x:c r="D30" s="0">
         <x:v>1008</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>63.889</x:v>
+        <x:v>63.8886906570858</x:v>
       </x:c>
       <x:c r="F30" s="0">
         <x:v>4777</x:v>
       </x:c>
       <x:c r="G30" s="0">
-        <x:v>0.00175308305546031</x:v>
+        <x:v>0.00170916236324724</x:v>
       </x:c>
       <x:c r="H30" s="0">
         <x:v>2761</x:v>
       </x:c>
       <x:c r="I30" s="0">
-        <x:v>65.774</x:v>
+        <x:v>65.7741389276324</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
@@ -1431,28 +1431,28 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>9379</x:v>
+        <x:v>3304534</x:v>
       </x:c>
       <x:c r="C31" s="0">
-        <x:v>65.714</x:v>
+        <x:v>66.3494437097944</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>7465</x:v>
+        <x:v>3302171</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>66.479</x:v>
+        <x:v>66.2271819443479</x:v>
       </x:c>
       <x:c r="F31" s="0">
-        <x:v>16844</x:v>
+        <x:v>6606705</x:v>
       </x:c>
       <x:c r="G31" s="0">
-        <x:v>0.00618148021481547</x:v>
+        <x:v>2.3638123364198</x:v>
       </x:c>
       <x:c r="H31" s="0">
-        <x:v>1914</x:v>
+        <x:v>2363</x:v>
       </x:c>
       <x:c r="I31" s="0">
-        <x:v>62.731</x:v>
+        <x:v>237.203974503861</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
@@ -1460,28 +1460,28 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="0">
-        <x:v>10448</x:v>
+        <x:v>10722</x:v>
       </x:c>
       <x:c r="C32" s="0">
-        <x:v>67.776</x:v>
+        <x:v>67.6462048440032</x:v>
       </x:c>
       <x:c r="D32" s="0">
         <x:v>8754</x:v>
       </x:c>
       <x:c r="E32" s="0">
-        <x:v>69.227</x:v>
+        <x:v>69.2267345897351</x:v>
       </x:c>
       <x:c r="F32" s="0">
-        <x:v>19202</x:v>
+        <x:v>19476</x:v>
       </x:c>
       <x:c r="G32" s="0">
-        <x:v>0.0070468287274333</x:v>
+        <x:v>0.0069683161370323</x:v>
       </x:c>
       <x:c r="H32" s="0">
-        <x:v>1694</x:v>
+        <x:v>1968</x:v>
       </x:c>
       <x:c r="I32" s="0">
-        <x:v>60.279</x:v>
+        <x:v>60.6157386884457</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
@@ -1489,10 +1489,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B33" s="0">
-        <x:v>711</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="C33" s="0">
-        <x:v>64.944</x:v>
+        <x:v>64.7639756569496</x:v>
       </x:c>
       <x:c r="D33" s="0">
         <x:v>0</x:v>
@@ -1501,16 +1501,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F33" s="0">
-        <x:v>711</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="G33" s="0">
-        <x:v>0.000260925696552707</x:v>
+        <x:v>0.000279076123787492</x:v>
       </x:c>
       <x:c r="H33" s="0">
-        <x:v>711</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="I33" s="0">
-        <x:v>64.944</x:v>
+        <x:v>64.7639756569496</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
@@ -1521,7 +1521,7 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="C34" s="0">
-        <x:v>62.8</x:v>
+        <x:v>62.8048378729051</x:v>
       </x:c>
       <x:c r="D34" s="0">
         <x:v>0</x:v>
@@ -1533,13 +1533,13 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="G34" s="0">
-        <x:v>5.68825358166942E-05</x:v>
+        <x:v>5.54574348552068E-05</x:v>
       </x:c>
       <x:c r="H34" s="0">
         <x:v>155</x:v>
       </x:c>
       <x:c r="I34" s="0">
-        <x:v>62.8</x:v>
+        <x:v>62.8048378729051</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
@@ -1547,10 +1547,10 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B35" s="0">
-        <x:v>200</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C35" s="0">
-        <x:v>65.05</x:v>
+        <x:v>64.6381355220989</x:v>
       </x:c>
       <x:c r="D35" s="0">
         <x:v>100</x:v>
@@ -1559,16 +1559,16 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="F35" s="0">
-        <x:v>300</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="G35" s="0">
-        <x:v>0.000110095230612957</x:v>
+        <x:v>0.000120217407169997</x:v>
       </x:c>
       <x:c r="H35" s="0">
-        <x:v>100</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="I35" s="0">
-        <x:v>67.1</x:v>
+        <x:v>65.8426469354068</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
@@ -1579,25 +1579,25 @@
         <x:v>82787</x:v>
       </x:c>
       <x:c r="C36" s="0">
-        <x:v>62.815</x:v>
+        <x:v>62.8153394947252</x:v>
       </x:c>
       <x:c r="D36" s="0">
         <x:v>82787</x:v>
       </x:c>
       <x:c r="E36" s="0">
-        <x:v>62.545</x:v>
+        <x:v>62.5449481970885</x:v>
       </x:c>
       <x:c r="F36" s="0">
         <x:v>165574</x:v>
       </x:c>
       <x:c r="G36" s="0">
-        <x:v>0.0607630257116989</x:v>
+        <x:v>0.0592407052820387</x:v>
       </x:c>
       <x:c r="H36" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="I36" s="0">
-        <x:v>62.815</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
@@ -1614,19 +1614,19 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="E37" s="0">
-        <x:v>70.527</x:v>
+        <x:v>70.5297704798575</x:v>
       </x:c>
       <x:c r="F37" s="0">
         <x:v>131</x:v>
       </x:c>
       <x:c r="G37" s="0">
-        <x:v>4.80749173676577E-05</x:v>
+        <x:v>4.6870477200207E-05</x:v>
       </x:c>
       <x:c r="H37" s="0">
         <x:v>-131</x:v>
       </x:c>
       <x:c r="I37" s="0">
-        <x:v>70.527</x:v>
+        <x:v>70.5297704798575</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
@@ -1637,25 +1637,25 @@
         <x:v>40674</x:v>
       </x:c>
       <x:c r="C38" s="0">
-        <x:v>63.229</x:v>
+        <x:v>63.2293096932419</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>41066</x:v>
+        <x:v>41094</x:v>
       </x:c>
       <x:c r="E38" s="0">
-        <x:v>63.994</x:v>
+        <x:v>63.9935353001046</x:v>
       </x:c>
       <x:c r="F38" s="0">
-        <x:v>81740</x:v>
+        <x:v>81768</x:v>
       </x:c>
       <x:c r="G38" s="0">
-        <x:v>0.0299972805010102</x:v>
+        <x:v>0.0292557647305842</x:v>
       </x:c>
       <x:c r="H38" s="0">
-        <x:v>-392</x:v>
+        <x:v>-420</x:v>
       </x:c>
       <x:c r="I38" s="0">
-        <x:v>143.36</x:v>
+        <x:v>138.00332657042</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
@@ -1663,28 +1663,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B39" s="0">
-        <x:v>0</x:v>
+        <x:v>665218</x:v>
       </x:c>
       <x:c r="C39" s="0">
-        <x:v>0</x:v>
+        <x:v>65.199964040728</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>691</x:v>
+        <x:v>665839</x:v>
       </x:c>
       <x:c r="E39" s="0">
-        <x:v>67.184</x:v>
+        <x:v>65.2585952978113</x:v>
       </x:c>
       <x:c r="F39" s="0">
-        <x:v>691</x:v>
+        <x:v>1331057</x:v>
       </x:c>
       <x:c r="G39" s="0">
-        <x:v>0.000253586014511843</x:v>
+        <x:v>0.476238753974625</x:v>
       </x:c>
       <x:c r="H39" s="0">
-        <x:v>-691</x:v>
+        <x:v>-621</x:v>
       </x:c>
       <x:c r="I39" s="0">
-        <x:v>67.184</x:v>
+        <x:v>128.064662245353</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
@@ -1692,28 +1692,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B40" s="0">
-        <x:v>451</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C40" s="0">
-        <x:v>68.698</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D40" s="0">
-        <x:v>2301</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="E40" s="0">
-        <x:v>69.436</x:v>
+        <x:v>67.1836464215291</x:v>
       </x:c>
       <x:c r="F40" s="0">
-        <x:v>2752</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="G40" s="0">
-        <x:v>0.00100994024882285</x:v>
+        <x:v>0.000247232822483535</x:v>
       </x:c>
       <x:c r="H40" s="0">
-        <x:v>-1850</x:v>
+        <x:v>-691</x:v>
       </x:c>
       <x:c r="I40" s="0">
-        <x:v>69.616</x:v>
+        <x:v>67.1836464215291</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
@@ -1721,28 +1721,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="0">
-        <x:v>242069</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="C41" s="0">
-        <x:v>67.353</x:v>
+        <x:v>68.7001118797421</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>244396</x:v>
+        <x:v>2329</x:v>
       </x:c>
       <x:c r="E41" s="0">
-        <x:v>66.608</x:v>
+        <x:v>69.3615935453789</x:v>
       </x:c>
       <x:c r="F41" s="0">
-        <x:v>486465</x:v>
+        <x:v>2780</x:v>
       </x:c>
       <x:c r="G41" s="0">
-        <x:v>0.17852492120044</x:v>
+        <x:v>0.000994655928370805</x:v>
       </x:c>
       <x:c r="H41" s="0">
-        <x:v>-2327</x:v>
+        <x:v>-1878</x:v>
       </x:c>
       <x:c r="I41" s="0">
-        <x:v>-10.875</x:v>
+        <x:v>69.5204477685963</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
@@ -1750,28 +1750,28 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B42" s="0">
-        <x:v>654357</x:v>
+        <x:v>244873</x:v>
       </x:c>
       <x:c r="C42" s="0">
-        <x:v>65.241</x:v>
+        <x:v>67.2994047135482</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>656899</x:v>
+        <x:v>246976</x:v>
       </x:c>
       <x:c r="E42" s="0">
-        <x:v>65.292</x:v>
+        <x:v>66.5727070075269</x:v>
       </x:c>
       <x:c r="F42" s="0">
-        <x:v>1311256</x:v>
+        <x:v>491849</x:v>
       </x:c>
       <x:c r="G42" s="0">
-        <x:v>0.481210105708743</x:v>
+        <x:v>0.175978605652249</x:v>
       </x:c>
       <x:c r="H42" s="0">
-        <x:v>-2542</x:v>
+        <x:v>-2103</x:v>
       </x:c>
       <x:c r="I42" s="0">
-        <x:v>78.421</x:v>
+        <x:v>-18.0438633046715</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
@@ -1779,28 +1779,28 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B43" s="0">
-        <x:v>455193</x:v>
+        <x:v>2980503</x:v>
       </x:c>
       <x:c r="C43" s="0">
-        <x:v>68.208</x:v>
+        <x:v>66.4028259309415</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>476299</x:v>
+        <x:v>2989839</x:v>
       </x:c>
       <x:c r="E43" s="0">
-        <x:v>69.303</x:v>
+        <x:v>66.1793400826855</x:v>
       </x:c>
       <x:c r="F43" s="0">
-        <x:v>931492</x:v>
+        <x:v>5970342</x:v>
       </x:c>
       <x:c r="G43" s="0">
-        <x:v>0.341842755180414</x:v>
+        <x:v>2.13612808082777</x:v>
       </x:c>
       <x:c r="H43" s="0">
-        <x:v>-21106</x:v>
+        <x:v>-9336</x:v>
       </x:c>
       <x:c r="I43" s="0">
-        <x:v>92.928</x:v>
+        <x:v>-5.1681579019437</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
@@ -1808,28 +1808,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="0">
-        <x:v>6680531</x:v>
+        <x:v>466670</x:v>
       </x:c>
       <x:c r="C44" s="0">
-        <x:v>67.391</x:v>
+        <x:v>68.0791155673035</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>6724581</x:v>
+        <x:v>482597</x:v>
       </x:c>
       <x:c r="E44" s="0">
-        <x:v>67.43</x:v>
+        <x:v>69.221377593264</x:v>
       </x:c>
       <x:c r="F44" s="0">
-        <x:v>13405112</x: